--- a/data/frise-philosophes-france.xlsx
+++ b/data/frise-philosophes-france.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Philosophes" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Mode_d_emploi" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Philosophes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mode_d_emploi" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Philosophes'!$A$3:$I$138</definedName>
@@ -896,7 +896,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:M141"/>
+  <dimension ref="A1:L141"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="4.59" customWidth="1" style="44" min="1" max="1"/>
@@ -1680,7 +1680,7 @@
       <c r="F16" s="57" t="n"/>
       <c r="G16" s="63" t="inlineStr">
         <is>
-          <t>
+          <t xml:space="preserve">
 </t>
         </is>
       </c>
@@ -1790,7 +1790,7 @@
       <c r="F18" s="57" t="n"/>
       <c r="G18" s="63" t="inlineStr">
         <is>
-          <t>
+          <t xml:space="preserve">
 </t>
         </is>
       </c>
@@ -7008,7 +7008,7 @@
       </c>
       <c r="H114" s="62" t="inlineStr">
         <is>
-          <t>https://www.laphilo.fr/pho/bbourgeois-mini</t>
+          <t>https://www.laphilo.fr/pho/bbourgeois-mini.webp</t>
         </is>
       </c>
       <c r="J114" s="45" t="inlineStr">

--- a/data/frise-philosophes-france.xlsx
+++ b/data/frise-philosophes-france.xlsx
@@ -2551,7 +2551,7 @@
       </c>
       <c r="L31" s="48" t="inlineStr">
         <is>
-          <t>philosophe français spécialiste d'histoire et de philosophie des sciences.</t>
+          <t>philosophe français des sciences, pionnier du conventionnalisme et spécialiste des fondements de la géométrie.</t>
         </is>
       </c>
     </row>
@@ -3406,7 +3406,7 @@
       </c>
       <c r="L47" s="48" t="inlineStr">
         <is>
-          <t>philosophe français spécialiste d'histoire et de philosophie des sciences.</t>
+          <t>philosophe français, historien des sciences et cofondateur de l'Institut d'histoire des sciences en 1932.</t>
         </is>
       </c>
     </row>

--- a/data/frise-philosophes-france.xlsx
+++ b/data/frise-philosophes-france.xlsx
@@ -938,7 +938,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:L142"/>
+  <dimension ref="A1:M141"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="4.59" customWidth="1" style="47" min="1" max="1"/>
@@ -1031,6 +1031,11 @@
           <t>Description</t>
         </is>
       </c>
+      <c r="M3" s="53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Traditions</t>
+        </is>
+      </c>
     </row>
     <row r="4" ht="222" customHeight="1" s="49">
       <c r="A4" s="54" t="n">
@@ -2397,6 +2402,11 @@
           <t>philosophe français fondateur de l’ethnologie &amp; de la sociologie de la connaissance.</t>
         </is>
       </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">juive</t>
+        </is>
+      </c>
     </row>
     <row r="29" ht="131.25" customHeight="1" s="49">
       <c r="A29" s="54" t="n">
@@ -2504,6 +2514,11 @@
           <t>philosophe français et fondateur de la Sociologie moderne.</t>
         </is>
       </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">juive</t>
+        </is>
+      </c>
     </row>
     <row r="31" ht="189" customHeight="1" s="49">
       <c r="A31" s="57" t="n">
@@ -2610,6 +2625,11 @@
           <t>philosophe français qui proposa une philosophie Rationaliste et Cartésienne.</t>
         </is>
       </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">juive</t>
+        </is>
+      </c>
     </row>
     <row r="33" ht="154.5" customHeight="1" s="49">
       <c r="A33" s="57" t="n">
@@ -2718,6 +2738,11 @@
           <t>philosophe des sciences français d'origine polonaise.</t>
         </is>
       </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">juive</t>
+        </is>
+      </c>
     </row>
     <row r="35" ht="177" customHeight="1" s="49">
       <c r="A35" s="57" t="n">
@@ -3093,6 +3118,11 @@
           <t>philosophe idéaliste français le plus important de la première moitié du XXe siècle.</t>
         </is>
       </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">juive</t>
+        </is>
+      </c>
     </row>
     <row r="42" ht="192" customHeight="1" s="49">
       <c r="A42" s="57" t="n">
@@ -3148,6 +3178,11 @@
           <t>philosophe français auteur d'une œuvre monumentale sur la pensée et la société britanniques.</t>
         </is>
       </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">juive</t>
+        </is>
+      </c>
     </row>
     <row r="43" ht="195.75" customHeight="1" s="49">
       <c r="A43" s="57" t="n">
@@ -3357,6 +3392,11 @@
           <t xml:space="preserve">Penseur et sociologue français et l’un des fondateurs de l’anthropologie. </t>
         </is>
       </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">juive</t>
+        </is>
+      </c>
     </row>
     <row r="47" ht="177" customHeight="1" s="49">
       <c r="A47" s="57" t="n">
@@ -3738,6 +3778,11 @@
           <t>philosophe, poétesse et mystique franco-russe de tradition juive.</t>
         </is>
       </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">juive</t>
+        </is>
+      </c>
     </row>
     <row r="54" ht="238.05" customHeight="1" s="49">
       <c r="A54" s="54" t="n">
@@ -4067,6 +4112,11 @@
           <t>philosophe français capital dans la réception des philosophies étrangères en France.</t>
         </is>
       </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t xml:space="preserve">juive</t>
+        </is>
+      </c>
     </row>
     <row r="60" ht="284.25" customHeight="1" s="49">
       <c r="A60" s="57" t="n">
@@ -4226,6 +4276,11 @@
           <t>philosophe français et un des fondateurs de l'histoire des sciences modernes.</t>
         </is>
       </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t xml:space="preserve">juive</t>
+        </is>
+      </c>
     </row>
     <row r="63" ht="300.75" customHeight="1" s="49">
       <c r="A63" s="57" t="n">
@@ -4663,6 +4718,11 @@
           <t>philosophe &amp; musicologue français connu pour sa pensée mêlant morale, temps et musique.</t>
         </is>
       </c>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t xml:space="preserve">juive</t>
+        </is>
+      </c>
     </row>
     <row r="71" ht="198" customHeight="1" s="49">
       <c r="A71" s="57" t="n">
@@ -4717,6 +4777,11 @@
           <t>philosophe français communiste connu pour sa critique précoce de la psychologie universitaire.</t>
         </is>
       </c>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t xml:space="preserve">juive</t>
+        </is>
+      </c>
     </row>
     <row r="72" ht="192" customHeight="1" s="49">
       <c r="A72" s="54" t="n">
@@ -4885,6 +4950,11 @@
           <t>philosophe français représentant du libéralisme politique face aux totalitarismes.</t>
         </is>
       </c>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">juive</t>
+        </is>
+      </c>
     </row>
     <row r="75" ht="251.25" customHeight="1" s="49">
       <c r="A75" s="54" t="n">
@@ -4995,6 +5065,11 @@
           <t>philosophe français centré sur la question éthique et métaphysique d'autrui.</t>
         </is>
       </c>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t xml:space="preserve">juive</t>
+        </is>
+      </c>
     </row>
     <row r="77" ht="132.75" customHeight="1" s="49">
       <c r="A77" s="54" t="n">
@@ -5431,6 +5506,11 @@
           <t>philosophe français des mathématiques et résistant arrêté.</t>
         </is>
       </c>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t xml:space="preserve">juive</t>
+        </is>
+      </c>
     </row>
     <row r="85" ht="330.75" customHeight="1" s="49">
       <c r="A85" s="54" t="n">
@@ -5484,6 +5564,11 @@
           <t>philosophe et anthropologue français qui  fonda l’anthropologie structurale.</t>
         </is>
       </c>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t xml:space="preserve">juive</t>
+        </is>
+      </c>
     </row>
     <row r="86" ht="242.25" customHeight="1" s="49">
       <c r="A86" s="57" t="n">
@@ -5540,6 +5625,11 @@
           <t>philosophe française humaniste et profondément spirituelle.</t>
         </is>
       </c>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t xml:space="preserve">juive</t>
+        </is>
+      </c>
     </row>
     <row r="87" ht="227.25" customHeight="1" s="49">
       <c r="A87" s="54" t="n">
@@ -5921,6 +6011,11 @@
           <t xml:space="preserve"> philosophe et sociologue français d’origine roumaine, fortement marqué par Marx.</t>
         </is>
       </c>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t xml:space="preserve">juive</t>
+        </is>
+      </c>
     </row>
     <row r="94" ht="249.75" customHeight="1" s="49">
       <c r="A94" s="54" t="n">
@@ -6358,6 +6453,11 @@
           <t>philosophe français connu pour sa pensée complexe et son approche  transdisciplinaire.</t>
         </is>
       </c>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t xml:space="preserve">juive</t>
+        </is>
+      </c>
     </row>
     <row r="102" ht="209.25" customHeight="1" s="49">
       <c r="A102" s="57" t="n">
@@ -7234,6 +7334,11 @@
           <t>philosophe français qui développa la pensée déconstructionniste.</t>
         </is>
       </c>
+      <c r="M117" t="inlineStr">
+        <is>
+          <t xml:space="preserve">juive</t>
+        </is>
+      </c>
     </row>
     <row r="118" ht="226.5" customHeight="1" s="49">
       <c r="A118" s="54" t="n">
@@ -8212,6 +8317,11 @@
       <c r="L135" s="48" t="inlineStr">
         <is>
           <t>philosophe français marxiste, intellectuel important de la gauche radicale française.</t>
+        </is>
+      </c>
+      <c r="M135" t="inlineStr">
+        <is>
+          <t xml:space="preserve">juive</t>
         </is>
       </c>
     </row>

--- a/data/frise-philosophes-france.xlsx
+++ b/data/frise-philosophes-france.xlsx
@@ -7124,7 +7124,7 @@
       </c>
       <c r="C114" s="57" t="inlineStr">
         <is>
-          <t>1927 – 2017</t>
+          <t xml:space="preserve">1928 – 2017</t>
         </is>
       </c>
       <c r="D114" s="58" t="inlineStr">

--- a/data/frise-philosophes-france.xlsx
+++ b/data/frise-philosophes-france.xlsx
@@ -1036,6 +1036,16 @@
           <t xml:space="preserve">Traditions</t>
         </is>
       </c>
+      <c r="N3" s="53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Groupe</t>
+        </is>
+      </c>
+      <c r="O3" s="53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Importance</t>
+        </is>
+      </c>
     </row>
     <row r="4" ht="222" customHeight="1" s="49">
       <c r="A4" s="54" t="n">
@@ -1091,6 +1101,11 @@
           <t>philosophe français, fondateur de l'école sociétaire et du phalanstère.</t>
         </is>
       </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="156" customHeight="1" s="49">
       <c r="A5" s="57" t="n">
@@ -1146,6 +1161,11 @@
           <t>philosophe français qui réforma l'enseignement de la philosophie dans les lycées.</t>
         </is>
       </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="162" customHeight="1" s="49">
       <c r="A6" s="57" t="n">
@@ -1199,6 +1219,11 @@
           <t>philosophe français représentant marquant de l'école spiritualiste.</t>
         </is>
       </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="201.75" customHeight="1" s="49">
       <c r="A7" s="57" t="n">
@@ -1250,6 +1275,11 @@
       <c r="L7" s="48" t="inlineStr">
         <is>
           <t>philosophe français co-fondateur du socialisme humaniste et de la pensée républicaine sociale.</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
         </is>
       </c>
     </row>
@@ -1311,6 +1341,14 @@
           <t>philosophe français connu pour son système de pensée appelé Positivisme.</t>
         </is>
       </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+      <c r="O8">
+        <v>2</v>
+      </c>
     </row>
     <row r="9" ht="201" customHeight="1" s="49">
       <c r="A9" s="57" t="n">
@@ -1370,6 +1408,11 @@
           <t>philosophe français qui posa les  bases de l'analyse moderne des structures du marché.</t>
         </is>
       </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="10" ht="183.75" customHeight="1" s="49">
       <c r="A10" s="54" t="n">
@@ -1425,6 +1468,11 @@
           <t>philosophe français précurseur de la sociologie.</t>
         </is>
       </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="11" ht="224.25" customHeight="1" s="49">
       <c r="A11" s="57" t="n">
@@ -1480,6 +1528,11 @@
           <t>philosophe français précurseur de l'anarchisme.</t>
         </is>
       </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="12" ht="154.5" customHeight="1" s="49">
       <c r="A12" s="54" t="n">
@@ -1535,6 +1588,11 @@
           <t>philosophe français figure majeure du spiritualisme français du XIXe siècle.</t>
         </is>
       </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="13" ht="198" customHeight="1" s="49">
       <c r="A13" s="57" t="n">
@@ -1590,6 +1648,11 @@
           <t>philosophe français connu comme "philosophe de la liberté" &amp; précurseur de l'existentialisme.</t>
         </is>
       </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="14" ht="161.25" customHeight="1" s="49">
       <c r="A14" s="54" t="n">
@@ -1646,6 +1709,11 @@
           <t>philosophe français fondateur de la doctrine dite du "néocriticisme" ou "personnalisme".</t>
         </is>
       </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="15" ht="205.5" customHeight="1" s="49">
       <c r="A15" s="57" t="n">
@@ -1701,6 +1769,11 @@
           <t>philosophe français connu pour son approche critique des religions et sa réflexion sur la nation.</t>
         </is>
       </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="16" ht="196.5" customHeight="1" s="49">
       <c r="A16" s="57" t="n">
@@ -1756,6 +1829,11 @@
           <t>philosophe français représentant connu du spiritualisme éclectique.</t>
         </is>
       </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="17" ht="144" customHeight="1" s="49">
       <c r="A17" s="54" t="n">
@@ -1811,6 +1889,11 @@
           <t>philosophe français figure influente de la philosophie universitaire française fin du XIXe siècle.</t>
         </is>
       </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="18" ht="169.5" customHeight="1" s="49">
       <c r="A18" s="57" t="n">
@@ -1866,6 +1949,11 @@
           <t>philosophe français qui concilia idéalisme et naturalisme à travers le concept d'"idée-force".</t>
         </is>
       </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="19" ht="171" customHeight="1" s="49">
       <c r="A19" s="57" t="n">
@@ -1920,6 +2008,11 @@
           <t>philosophe français fondateur de la psychologie scientifique et expérimentale en France.</t>
         </is>
       </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="20" ht="187.5" customHeight="1" s="49">
       <c r="A20" s="57" t="n">
@@ -1975,6 +2068,11 @@
           <t>philosophe français figure originale des sciences sociales du XIXe et XXe siècles.</t>
         </is>
       </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="21" ht="168" customHeight="1" s="49">
       <c r="A21" s="57" t="n">
@@ -2030,6 +2128,11 @@
           <t>philosophe français représentant du spiritualisme et figure de la philosophie des sciences.</t>
         </is>
       </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="22" ht="198.75" customHeight="1" s="49">
       <c r="A22" s="54" t="n">
@@ -2085,6 +2188,11 @@
           <t>philosophe français connu pour sa théorie du syndicalisme révolutionnaire.</t>
         </is>
       </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="23" ht="163.5" customHeight="1" s="49">
       <c r="A23" s="57" t="n">
@@ -2140,6 +2248,11 @@
           <t>philosophe français connu pour ses travaux fondamentaux sur le scepticisme grec.</t>
         </is>
       </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="24" ht="172.5" customHeight="1" s="49">
       <c r="A24" s="54" t="n">
@@ -2192,6 +2305,11 @@
           <t>philosophe français qui s'inscrit dans la tradition spiritualiste française.</t>
         </is>
       </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="25" ht="177" customHeight="1" s="49">
       <c r="A25" s="57" t="n">
@@ -2242,6 +2360,11 @@
           <t>philosophe français spiritualiste, proche de la philosophie de l’art et de la morale.</t>
         </is>
       </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="26" ht="194.25" customHeight="1" s="49">
       <c r="A26" s="57" t="n">
@@ -2296,6 +2419,11 @@
           <t>philosophe français qui proposa une éthique vitaliste fondée sur la surabondance de la vie.</t>
         </is>
       </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="27" ht="176.25" customHeight="1" s="49">
       <c r="A27" s="57" t="n">
@@ -2346,6 +2474,11 @@
           <t>philosophe français l'un des représentants les plus rigoureux de l'idéalisme néo-kantien.</t>
         </is>
       </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="28" ht="180" customHeight="1" s="49">
       <c r="A28" s="57" t="n">
@@ -2407,6 +2540,11 @@
           <t xml:space="preserve">juive</t>
         </is>
       </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="29" ht="131.25" customHeight="1" s="49">
       <c r="A29" s="54" t="n">
@@ -2459,6 +2597,11 @@
           <t>philosophe français spécialiste de psychologie et de philosophie morale.</t>
         </is>
       </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="30" ht="176.25" customHeight="1" s="49">
       <c r="A30" s="57" t="n">
@@ -2519,6 +2662,14 @@
           <t xml:space="preserve">juive</t>
         </is>
       </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+      <c r="O30">
+        <v>2</v>
+      </c>
     </row>
     <row r="31" ht="189" customHeight="1" s="49">
       <c r="A31" s="57" t="n">
@@ -2569,6 +2720,11 @@
           <t>philosophe français des sciences, pionnier du conventionnalisme et spécialiste des fondements de la géométrie.</t>
         </is>
       </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="32" ht="213" customHeight="1" s="49">
       <c r="A32" s="54" t="n">
@@ -2630,6 +2786,14 @@
           <t xml:space="preserve">juive</t>
         </is>
       </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+      <c r="O32">
+        <v>3</v>
+      </c>
     </row>
     <row r="33" ht="154.5" customHeight="1" s="49">
       <c r="A33" s="57" t="n">
@@ -2685,6 +2849,11 @@
           <t>philosophe français spécialiste de philosophie morale et de sociologie.</t>
         </is>
       </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="34" ht="184.5" customHeight="1" s="49">
       <c r="A34" s="69" t="n">
@@ -2743,6 +2912,11 @@
           <t xml:space="preserve">juive</t>
         </is>
       </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="35" ht="177" customHeight="1" s="49">
       <c r="A35" s="57" t="n">
@@ -2797,6 +2971,11 @@
           <t>philosophe français pour qui l'action constitue la structure fondamentale de l'existence humaine.</t>
         </is>
       </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="36" ht="148.5" customHeight="1" s="49">
       <c r="A36" s="57" t="n">
@@ -2847,6 +3026,11 @@
           <t>philosophe français représentant du courant empiriste et pragmatiste.</t>
         </is>
       </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="37" ht="150.75" customHeight="1" s="49">
       <c r="A37" s="54" t="n">
@@ -2899,6 +3083,11 @@
           <t>philosophe français fondateur de la revue La Revue de Synthèse historique.</t>
         </is>
       </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="38" ht="185.25" customHeight="1" s="49">
       <c r="A38" s="57" t="n">
@@ -2953,6 +3142,11 @@
           <t>philosophe français grand connaisseur de la philosophie allemande.</t>
         </is>
       </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="39" ht="181.5" customHeight="1" s="49">
       <c r="A39" s="57" t="n">
@@ -3009,6 +3203,11 @@
           <t>philosophe français auteur du Vocabulaire technique et critique de la philosophie.</t>
         </is>
       </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="40" ht="208.5" customHeight="1" s="49">
       <c r="A40" s="57" t="n">
@@ -3063,6 +3262,11 @@
           <t>philosophe français pour qui  la raison et la volonté sont les seules puissances.</t>
         </is>
       </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="41" ht="141" customHeight="1" s="49">
       <c r="A41" s="54" t="n">
@@ -3123,6 +3327,11 @@
           <t xml:space="preserve">juive</t>
         </is>
       </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="42" ht="192" customHeight="1" s="49">
       <c r="A42" s="57" t="n">
@@ -3183,6 +3392,11 @@
           <t xml:space="preserve">juive</t>
         </is>
       </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="43" ht="195.75" customHeight="1" s="49">
       <c r="A43" s="57" t="n">
@@ -3233,6 +3447,11 @@
           <t>philosophe français figure majeure du mouvement moderniste catholique au début du XXe siècle.</t>
         </is>
       </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="44" ht="194.25" customHeight="1" s="49">
       <c r="A44" s="57" t="n">
@@ -3283,6 +3502,11 @@
           <t>philosophe français connu pour ses travaux de synthèse sur la philosophie française contemporaine.</t>
         </is>
       </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="45" ht="168.75" customHeight="1" s="49">
       <c r="A45" s="54" t="n">
@@ -3338,6 +3562,11 @@
           <t>philosophe français figure majeure du rationalisme scientifique du XXe siècle.</t>
         </is>
       </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="46" ht="269.25" customHeight="1" s="49">
       <c r="A46" s="54" t="n">
@@ -3397,6 +3626,11 @@
           <t xml:space="preserve">juive</t>
         </is>
       </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="47" ht="177" customHeight="1" s="49">
       <c r="A47" s="57" t="n">
@@ -3449,6 +3683,11 @@
           <t>philosophe français, historien des sciences et cofondateur de l'Institut d'histoire des sciences en 1932.</t>
         </is>
       </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="48" ht="197.25" customHeight="1" s="49">
       <c r="A48" s="54" t="n">
@@ -3504,6 +3743,11 @@
           <t>philosophe français et l'un des plus grands historiens de la philosophie du XXe siècle.</t>
         </is>
       </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="49" ht="212.25" customHeight="1" s="49">
       <c r="A49" s="57" t="n">
@@ -3558,6 +3802,11 @@
           <t>philosophe français figure profonde et discrète de la philosophie réflexive française du XXe siècle.</t>
         </is>
       </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="50" ht="266.25" customHeight="1" s="49">
       <c r="A50" s="57" t="n">
@@ -3612,6 +3861,11 @@
           <t>philosophe français qui s’inscrit dans un courant spiritualiste et catholique influencé par Bergson.</t>
         </is>
       </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="51" ht="198" customHeight="1" s="49">
       <c r="A51" s="57" t="n">
@@ -3667,6 +3921,11 @@
           <t xml:space="preserve">philosophe thomiste chrétien qui renouvela la pensée de saint Thomas d’Aquin. </t>
         </is>
       </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="52" ht="158.25" customHeight="1" s="49">
       <c r="A52" s="54" t="n">
@@ -3723,6 +3982,11 @@
           <t xml:space="preserve">philosophe français spiritualiste, connu pour sa philosophie des valeurs et ses travaux de morale. </t>
         </is>
       </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="53" ht="185.8" customHeight="1" s="49">
       <c r="A53" s="57" t="n">
@@ -3783,6 +4047,11 @@
           <t xml:space="preserve">juive</t>
         </is>
       </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="54" ht="238.05" customHeight="1" s="49">
       <c r="A54" s="54" t="n">
@@ -3838,6 +4107,11 @@
           <t>philosophe français cofondateur du mouvement philosophique dit "La Philosophie de l'Esprit".</t>
         </is>
       </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="55" ht="421.6" customHeight="1" s="49">
       <c r="A55" s="54" t="n">
@@ -3892,6 +4166,11 @@
           <t>Philosophe français, considéré comme l’un des fondateurs de l’islamologie moderne et un pionnier du dialogue islamo-chrétien.</t>
         </is>
       </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="56" ht="273" customHeight="1" s="49">
       <c r="A56" s="57" t="n">
@@ -3947,6 +4226,11 @@
           <t>philosophe français des sciences et de la poésie, représentant de l'épistémologie historique.</t>
         </is>
       </c>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="57" ht="222" customHeight="1" s="49">
       <c r="A57" s="54" t="n">
@@ -4002,6 +4286,11 @@
           <t>philosophe français spécialiste en histoire de la philosophie médiévale.</t>
         </is>
       </c>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="58" ht="220.5" customHeight="1" s="49">
       <c r="A58" s="57" t="n">
@@ -4057,6 +4346,11 @@
           <t>philosophe et métaphysicien français qui prône le retour du traditionalisme.</t>
         </is>
       </c>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="59" ht="229.5" customHeight="1" s="49">
       <c r="A59" s="57" t="n">
@@ -4117,6 +4411,11 @@
           <t xml:space="preserve">juive</t>
         </is>
       </c>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="60" ht="284.25" customHeight="1" s="49">
       <c r="A60" s="57" t="n">
@@ -4171,6 +4470,11 @@
           <t>philosophe et dramaturge français  représentant  de l’existentialisme chrétien et du personnalisme.</t>
         </is>
       </c>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="61" ht="201.75" customHeight="1" s="49">
       <c r="A61" s="54" t="n">
@@ -4223,6 +4527,11 @@
           <t>philosophe français de la méthode d'histoire de la philosophie par analyse interne des textes.</t>
         </is>
       </c>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="62" ht="161.25" customHeight="1" s="49">
       <c r="A62" s="57" t="n">
@@ -4278,7 +4587,12 @@
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t xml:space="preserve">juive</t>
+          <t xml:space="preserve">juive;russe</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
         </is>
       </c>
     </row>
@@ -4332,6 +4646,11 @@
           <t xml:space="preserve"> philosophe spiritualiste français connu surtout pour sa « trilogie » sur la conscience.</t>
         </is>
       </c>
+      <c r="N63" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="64" ht="156.75" customHeight="1" s="49">
       <c r="A64" s="57" t="n">
@@ -4389,6 +4708,11 @@
           <t>philosophe français connu pour avoir développé la notion de Prospective.</t>
         </is>
       </c>
+      <c r="N64" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="65" ht="294" customHeight="1" s="49">
       <c r="A65" s="57" t="n">
@@ -4444,6 +4768,11 @@
           <t>philosophe et écrivain français qualifié de métaphysicien du mal pour son intérêt pour le sexe, à la mort, la dégradation et le pouvoir de l'obscène.</t>
         </is>
       </c>
+      <c r="N65" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="66" ht="323.25" customHeight="1" s="49">
       <c r="A66" s="57" t="n">
@@ -4495,6 +4824,11 @@
           <t>philosophe français spiritualiste, historien de la philosophie médiévale et métaphysicien d’inspiration thomiste et augustinienne.</t>
         </is>
       </c>
+      <c r="N66" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="67" ht="188.25" customHeight="1" s="49">
       <c r="A67" s="54" t="n">
@@ -4550,6 +4884,11 @@
           <t>philosophe français qui chercha à réconcilier la foi et la raison au XXème.</t>
         </is>
       </c>
+      <c r="N67" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="68" ht="217.5" customHeight="1" s="49">
       <c r="A68" s="57" t="n">
@@ -4606,6 +4945,11 @@
           <t>philosophe français qui renouvela la compréhension de la philosophie islamique.</t>
         </is>
       </c>
+      <c r="N68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="69" ht="225" customHeight="1" s="49">
       <c r="A69" s="54" t="n">
@@ -4662,6 +5006,11 @@
           <t>philosophe français des mathématiques et héros intellectuel de la Résistance.</t>
         </is>
       </c>
+      <c r="N69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="70" ht="194.25" customHeight="1" s="49">
       <c r="A70" s="57" t="n">
@@ -4723,6 +5072,11 @@
           <t xml:space="preserve">juive</t>
         </is>
       </c>
+      <c r="N70" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="71" ht="198" customHeight="1" s="49">
       <c r="A71" s="57" t="n">
@@ -4782,6 +5136,11 @@
           <t xml:space="preserve">juive</t>
         </is>
       </c>
+      <c r="N71" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="72" ht="192" customHeight="1" s="49">
       <c r="A72" s="54" t="n">
@@ -4839,6 +5198,11 @@
           <t>philosophe &amp; résistant français épistémologiste des sciences du vivant.</t>
         </is>
       </c>
+      <c r="N72" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="73" ht="182.25" customHeight="1" s="49">
       <c r="A73" s="57" t="n">
@@ -4895,6 +5259,14 @@
           <t>philosophe français qui développa la théorie de l'Existentialisme.</t>
         </is>
       </c>
+      <c r="N73" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+      <c r="O73">
+        <v>3</v>
+      </c>
     </row>
     <row r="74" ht="212.25" customHeight="1" s="49">
       <c r="A74" s="54" t="n">
@@ -4955,6 +5327,11 @@
           <t xml:space="preserve">juive</t>
         </is>
       </c>
+      <c r="N74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="75" ht="251.25" customHeight="1" s="49">
       <c r="A75" s="54" t="n">
@@ -5009,6 +5386,11 @@
           <t>philosophe français connu comme le fondateur du personnalisme.</t>
         </is>
       </c>
+      <c r="N75" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="76" ht="217.5" customHeight="1" s="49">
       <c r="A76" s="57" t="n">
@@ -5070,6 +5452,14 @@
           <t xml:space="preserve">juive</t>
         </is>
       </c>
+      <c r="N76" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+      <c r="O76">
+        <v>3</v>
+      </c>
     </row>
     <row r="77" ht="132.75" customHeight="1" s="49">
       <c r="A77" s="54" t="n">
@@ -5125,6 +5515,11 @@
           <t>philosophe français connu pour son rôle de passeur entre traditions philosophiques.</t>
         </is>
       </c>
+      <c r="N77" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="78" ht="174.75" customHeight="1" s="49">
       <c r="A78" s="57" t="n">
@@ -5178,6 +5573,11 @@
           <t>philosophe français spécialiste de Descartes et du cartésianisme.</t>
         </is>
       </c>
+      <c r="N78" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="79" ht="150" customHeight="1" s="49">
       <c r="A79" s="57" t="n">
@@ -5233,6 +5633,11 @@
           <t>philosophe français qui introduisit Hegel en France au XXe siècle.</t>
         </is>
       </c>
+      <c r="N79" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="80" ht="155.25" customHeight="1" s="49">
       <c r="A80" s="54" t="n">
@@ -5288,6 +5693,11 @@
           <t>philosophe français figure singulière et influente de la pensée française du XXe siècle.</t>
         </is>
       </c>
+      <c r="N80" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="81" ht="175.5" customHeight="1" s="49">
       <c r="A81" s="57" t="n">
@@ -5340,6 +5750,11 @@
           <t>philosophe français introducteur et interprète de la philosophie de Martin Heidegger.</t>
         </is>
       </c>
+      <c r="N81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="82" ht="156" customHeight="1" s="49">
       <c r="A82" s="54" t="n">
@@ -5395,6 +5810,14 @@
           <t>philosophe française et intellectuelle anticonformiste figure de l'existentialisme.</t>
         </is>
       </c>
+      <c r="N82" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+      <c r="O82">
+        <v>3</v>
+      </c>
     </row>
     <row r="83" ht="204" customHeight="1" s="49">
       <c r="A83" s="57" t="n">
@@ -5451,6 +5874,11 @@
           <t>philosophe français connu pour ses contributions à la phénoménologie.</t>
         </is>
       </c>
+      <c r="N83" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="84" ht="210" customHeight="1" s="49">
       <c r="A84" s="54" t="n">
@@ -5511,6 +5939,11 @@
           <t xml:space="preserve">juive</t>
         </is>
       </c>
+      <c r="N84" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="85" ht="330.75" customHeight="1" s="49">
       <c r="A85" s="54" t="n">
@@ -5569,6 +6002,11 @@
           <t xml:space="preserve">juive</t>
         </is>
       </c>
+      <c r="N85" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="86" ht="242.25" customHeight="1" s="49">
       <c r="A86" s="57" t="n">
@@ -5630,6 +6068,11 @@
           <t xml:space="preserve">juive</t>
         </is>
       </c>
+      <c r="N86" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="87" ht="227.25" customHeight="1" s="49">
       <c r="A87" s="54" t="n">
@@ -5685,6 +6128,11 @@
           <t>philosophe français pionnier de la critique écologique.</t>
         </is>
       </c>
+      <c r="N87" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="88" ht="162" customHeight="1" s="49">
       <c r="A88" s="57" t="n">
@@ -5735,6 +6183,11 @@
           <t>philosophe français passeur entre les cultures philosophiques française et américaine.</t>
         </is>
       </c>
+      <c r="N88" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="89" ht="186" customHeight="1" s="49">
       <c r="A89" s="57" t="n">
@@ -5791,6 +6244,11 @@
           <t>philosophe français critique de la technique moderne &amp; des effets aliénants sur la société.</t>
         </is>
       </c>
+      <c r="N89" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="90" ht="183.75" customHeight="1" s="49">
       <c r="A90" s="54" t="n">
@@ -5846,6 +6304,11 @@
           <t>philosophe français figure importante de la phénoménologie française.</t>
         </is>
       </c>
+      <c r="N90" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="91" ht="225.75" customHeight="1" s="49">
       <c r="A91" s="57" t="n">
@@ -5902,6 +6365,11 @@
           <t>philosophe et écrivain français existentialiste connu pour sa vision de l'absurde.</t>
         </is>
       </c>
+      <c r="N91" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="92" ht="267" customHeight="1" s="49">
       <c r="A92" s="54" t="n">
@@ -5958,6 +6426,11 @@
           <t>philosophe français s'inscrivant dans les courants phénoménologiques et herméneutiques.</t>
         </is>
       </c>
+      <c r="N92" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="93" ht="404.25" customHeight="1" s="49">
       <c r="A93" s="54" t="n">
@@ -6016,6 +6489,11 @@
           <t xml:space="preserve">juive</t>
         </is>
       </c>
+      <c r="N93" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="94" ht="249.75" customHeight="1" s="49">
       <c r="A94" s="54" t="n">
@@ -6070,6 +6548,11 @@
           <t xml:space="preserve"> pas une philosophe au sens académique, mais son œuvre littéraire, cinématographique et théâtrale déploie une pensée originale, centrée sur l’écriture, le désir, la mémoire et la condition humaine.</t>
         </is>
       </c>
+      <c r="N94" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="95" ht="247.5" customHeight="1" s="49">
       <c r="A95" s="57" t="n">
@@ -6125,6 +6608,11 @@
           <t>philosophe français à l'origine d'un renouvellement de la pensée marxiste.</t>
         </is>
       </c>
+      <c r="N95" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="96" ht="174.75" customHeight="1" s="49">
       <c r="A96" s="54" t="n">
@@ -6180,6 +6668,11 @@
           <t>philosophe français spécialiste de philosophie antique et de pensée chrétienne.</t>
         </is>
       </c>
+      <c r="N96" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="97" ht="159.75" customHeight="1" s="49">
       <c r="A97" s="57" t="n">
@@ -6232,6 +6725,11 @@
           <t>philosophe française spécialiste de phénoménologie et de logique.</t>
         </is>
       </c>
+      <c r="N97" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="98" ht="129.75" customHeight="1" s="49">
       <c r="A98" s="54" t="n">
@@ -6287,6 +6785,11 @@
           <t>philosophe français connu pour son travail en philosophie analytique &amp; en épistémologie.</t>
         </is>
       </c>
+      <c r="N98" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="99" ht="132" customHeight="1" s="49">
       <c r="A99" s="57" t="n">
@@ -6343,6 +6846,11 @@
           <t>philosophe français connu pour son travail sur l'épistémologie comparative.</t>
         </is>
       </c>
+      <c r="N99" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="100" ht="197.25" customHeight="1" s="49">
       <c r="A100" s="54" t="n">
@@ -6398,6 +6906,11 @@
           <t>philosophe français spécialiste de philosophie antique et de patristique.</t>
         </is>
       </c>
+      <c r="N100" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="101" ht="342" customHeight="1" s="49">
       <c r="A101" s="54" t="n">
@@ -6458,6 +6971,11 @@
           <t xml:space="preserve">juive</t>
         </is>
       </c>
+      <c r="N101" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="102" ht="209.25" customHeight="1" s="49">
       <c r="A102" s="57" t="n">
@@ -6513,6 +7031,11 @@
           <t>philosophe français connu pour son athéisme radical, son naturalisme.</t>
         </is>
       </c>
+      <c r="N102" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="103" ht="171" customHeight="1" s="49">
       <c r="A103" s="54" t="n">
@@ -6568,6 +7091,11 @@
           <t>philosophe français spécialiste de philosophie antique.</t>
         </is>
       </c>
+      <c r="N103" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="104" ht="257.25" customHeight="1" s="49">
       <c r="A104" s="57" t="n">
@@ -6623,6 +7151,11 @@
           <t>philosophe et anthropologue français père de la "théorie mimétique".</t>
         </is>
       </c>
+      <c r="N104" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="105" ht="167.25" customHeight="1" s="49">
       <c r="A105" s="54" t="n">
@@ -6678,6 +7211,11 @@
           <t>philosophe et humaniste français spécialiste reconnu de la pensée de la Renaissance.</t>
         </is>
       </c>
+      <c r="N105" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="106" ht="189.75" customHeight="1" s="49">
       <c r="A106" s="57" t="n">
@@ -6733,6 +7271,11 @@
           <t>philosophe français figure du postmodernisme qui aboutit à une remise en cause radicale.</t>
         </is>
       </c>
+      <c r="N106" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="107" ht="185.25" customHeight="1" s="49">
       <c r="A107" s="54" t="n">
@@ -6788,6 +7331,11 @@
           <t>philosophe français auteur d'une œuvre sur la relation entre l'humain et la machine.</t>
         </is>
       </c>
+      <c r="N107" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="108" ht="223.5" customHeight="1" s="49">
       <c r="A108" s="57" t="n">
@@ -6845,6 +7393,14 @@
           <t>philosophe français qui chercha à penser la différence en elle-même (French Theory).</t>
         </is>
       </c>
+      <c r="N108" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+      <c r="O108">
+        <v>2</v>
+      </c>
     </row>
     <row r="109" ht="152.25" customHeight="1" s="49">
       <c r="A109" s="57" t="n">
@@ -6900,6 +7456,11 @@
           <t>philosophe français spécialiste de la philosophie médiévale arabe et latine.</t>
         </is>
       </c>
+      <c r="N109" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="110" ht="205.5" customHeight="1" s="49">
       <c r="A110" s="57" t="n">
@@ -6950,6 +7511,11 @@
           <t xml:space="preserve"> philosophe et éditeur français connu pour avoir promu le structuralisme et la psychanalyse aux Éditions du Seuil.</t>
         </is>
       </c>
+      <c r="N110" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="111" ht="246" customHeight="1" s="49">
       <c r="A111" s="54" t="n">
@@ -7006,6 +7572,14 @@
           <t>philosophe français qui a exploré la folie, la prison et la sexualité.</t>
         </is>
       </c>
+      <c r="N111" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+      <c r="O111">
+        <v>3</v>
+      </c>
     </row>
     <row r="112" ht="248.25" customHeight="1" s="49">
       <c r="A112" s="47" t="n">
@@ -7059,6 +7633,11 @@
           <t>théologien, historien et patrologue orthodoxe français figure de la patristique orthodoxe.</t>
         </is>
       </c>
+      <c r="N112" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="113" ht="245.25" customHeight="1" s="49">
       <c r="A113" s="57" t="n">
@@ -7114,6 +7693,11 @@
           <t>philosophe français critique du libéralisme libertaire et du capitalisme.</t>
         </is>
       </c>
+      <c r="N113" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="114" ht="330.75" customHeight="1" s="49">
       <c r="A114" s="57" t="n">
@@ -7168,6 +7752,11 @@
           <t>philosophe, historien et théoricien de l’art français, figure majeure de la pensée visuelle et de l’iconologie analytique.</t>
         </is>
       </c>
+      <c r="N114" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="115" ht="228.75" customHeight="1" s="49">
       <c r="A115" s="57" t="n">
@@ -7222,6 +7811,11 @@
           <t xml:space="preserve">philosophe français connu comme le grand traducteur et interprète de Hegel en langue française. </t>
         </is>
       </c>
+      <c r="N115" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="116" ht="216" customHeight="1" s="49">
       <c r="A116" s="54" t="n">
@@ -7278,6 +7872,11 @@
           <t>philosophe français majeur du postmodernisme &amp; connu pour ses analyses.</t>
         </is>
       </c>
+      <c r="N116" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="117" ht="201.75" customHeight="1" s="49">
       <c r="A117" s="57" t="n">
@@ -7339,6 +7938,14 @@
           <t xml:space="preserve">juive</t>
         </is>
       </c>
+      <c r="N117" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+      <c r="O117">
+        <v>3</v>
+      </c>
     </row>
     <row r="118" ht="226.5" customHeight="1" s="49">
       <c r="A118" s="54" t="n">
@@ -7394,6 +8001,11 @@
           <t>philosophe, sociologue français et figure intellectuelle importante.</t>
         </is>
       </c>
+      <c r="N118" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="119" ht="257.25" customHeight="1" s="49">
       <c r="A119" s="54" t="n">
@@ -7448,6 +8060,11 @@
           <t>philosophe français du courant post-structuraliste et de la pensée critique.</t>
         </is>
       </c>
+      <c r="N119" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="120" ht="150.75" customHeight="1" s="49">
       <c r="A120" s="57" t="n">
@@ -7503,6 +8120,11 @@
           <t>philosophe franco-brésilien spécialiste de la philosophie allemande.</t>
         </is>
       </c>
+      <c r="N120" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="121" ht="180.75" customHeight="1" s="49">
       <c r="A121" s="54" t="n">
@@ -7559,6 +8181,11 @@
           <t>philosophe français reliant sciences, techniques, littérature et réflexion écologique.</t>
         </is>
       </c>
+      <c r="N121" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="122" ht="150.75" customHeight="1" s="49">
       <c r="A122" s="57" t="n">
@@ -7606,6 +8233,11 @@
           <t>philosophe français traducteur avec commentaires des œuvres de Husserl et Heidegger.</t>
         </is>
       </c>
+      <c r="N122" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="123" ht="164.25" customHeight="1" s="49">
       <c r="A123" s="54" t="n">
@@ -7661,6 +8293,11 @@
           <t>philosophe social français, figure importante de la sociologie française.</t>
         </is>
       </c>
+      <c r="N123" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="124" ht="164.25" customHeight="1" s="49">
       <c r="A124" s="57" t="n">
@@ -7716,6 +8353,11 @@
           <t>philosophe français, principal traducteur de Martin Heidegger en français.</t>
         </is>
       </c>
+      <c r="N124" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="125" ht="164.25" customHeight="1" s="49">
       <c r="A125" s="54" t="n">
@@ -7771,6 +8413,11 @@
           <t>philosophe française fondatrice du féminisme matérialiste &amp; de la théorie Queer.</t>
         </is>
       </c>
+      <c r="N125" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="126" ht="129" customHeight="1" s="49">
       <c r="A126" s="47" t="n">
@@ -7825,6 +8472,11 @@
           <t>philosophe français grand connaisseur de la philosophie indienne.</t>
         </is>
       </c>
+      <c r="N126" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="127" ht="185.25" customHeight="1" s="49">
       <c r="A127" s="57" t="n">
@@ -7880,6 +8532,11 @@
           <t>philosophe français spécialiste de l'idéalisme allemand et de la mystique.</t>
         </is>
       </c>
+      <c r="N127" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="128" ht="216.75" customHeight="1" s="49">
       <c r="A128" s="54" t="n">
@@ -7935,6 +8592,11 @@
           <t>philosophe français du tragique et de la théorie du réel.</t>
         </is>
       </c>
+      <c r="N128" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="129" ht="199.5" customHeight="1" s="49">
       <c r="A129" s="57" t="n">
@@ -7990,6 +8652,11 @@
           <t>philosophe français du courant analytique d'un rationalisme exigeant.</t>
         </is>
       </c>
+      <c r="N129" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="130" ht="164.25" customHeight="1" s="49">
       <c r="A130" s="54" t="n">
@@ -8045,6 +8712,11 @@
           <t>philosophe français qui porta le « sens du monde », la communauté, le corps et le toucher.</t>
         </is>
       </c>
+      <c r="N130" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="131" ht="201" customHeight="1" s="49">
       <c r="A131" s="54" t="n">
@@ -8099,6 +8771,11 @@
           <t xml:space="preserve"> philosophe et théoricien français connu pour ses travaux sur la mimésis et le romantisme allemand.</t>
         </is>
       </c>
+      <c r="N131" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="132" ht="209.25" customHeight="1" s="49">
       <c r="A132" s="57" t="n">
@@ -8154,6 +8831,11 @@
           <t>philosophe français spécialiste de philosophie des sciences médicales et biologiques.</t>
         </is>
       </c>
+      <c r="N132" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="133" ht="218.25" customHeight="1" s="49">
       <c r="A133" s="54" t="n">
@@ -8209,6 +8891,11 @@
           <t>philosophe français connu pour ses travaux en philosophie des sciences.</t>
         </is>
       </c>
+      <c r="N133" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="134" ht="157.5" customHeight="1" s="49">
       <c r="A134" s="57" t="n">
@@ -8264,6 +8951,11 @@
           <t>philosophe et sociologue français spécialiste d'épistémologie des sciences sociales.</t>
         </is>
       </c>
+      <c r="N134" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="135" ht="166.5" customHeight="1" s="49">
       <c r="A135" s="54" t="n">
@@ -8324,6 +9016,11 @@
           <t xml:space="preserve">juive</t>
         </is>
       </c>
+      <c r="N135" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="136" ht="210" customHeight="1" s="49">
       <c r="A136" s="57" t="n">
@@ -8379,6 +9076,11 @@
           <t>philosophe français inscrit dans le mouvement du Nouveau Réalisme.</t>
         </is>
       </c>
+      <c r="N136" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="137" ht="166.5" customHeight="1" s="49">
       <c r="A137" s="54" t="n">
@@ -8434,6 +9136,11 @@
           <t>religieux français spécialiste de l'autorité politique &amp; des tensions démocratiques.</t>
         </is>
       </c>
+      <c r="N137" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="138" ht="210.75" customHeight="1" s="49">
       <c r="A138" s="57" t="n">
@@ -8490,6 +9197,11 @@
           <t>philosophe française majeure de la philosophie politique contemporaine.</t>
         </is>
       </c>
+      <c r="N138" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="139" ht="171.75" customHeight="1" s="49">
       <c r="A139" s="54" t="n">
@@ -8545,6 +9257,11 @@
           <t>philosophe français qui fit une analyse ambitieuse de la technique et de ses effets.</t>
         </is>
       </c>
+      <c r="N139" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="140" ht="135.75" customHeight="1" s="49">
       <c r="A140" s="57" t="n">
@@ -8600,6 +9317,11 @@
           <t>philosophe français spécialiste de dialectique et de philosophie hégélienne.</t>
         </is>
       </c>
+      <c r="N140" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="141" ht="176.25" customHeight="1" s="49">
       <c r="A141" s="47" t="n">
@@ -8653,6 +9375,11 @@
       <c r="L141" s="48" t="inlineStr">
         <is>
           <t>philosophe et psychanalyste française fine analyste, qui explore la vulnérabilité humaine.</t>
+        </is>
+      </c>
+      <c r="N141" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
         </is>
       </c>
     </row>

--- a/data/frise-philosophes-france.xlsx
+++ b/data/frise-philosophes-france.xlsx
@@ -938,7 +938,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:M141"/>
+  <dimension ref="A1:N142"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="4.59" customWidth="1" style="47" min="1" max="1"/>
@@ -4044,7 +4044,7 @@
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t xml:space="preserve">juive</t>
+          <t xml:space="preserve">juive;femme</t>
         </is>
       </c>
       <c r="N53" t="inlineStr">
@@ -5810,6 +5810,11 @@
           <t>philosophe française et intellectuelle anticonformiste figure de l'existentialisme.</t>
         </is>
       </c>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t xml:space="preserve">femme</t>
+        </is>
+      </c>
       <c r="N82" t="inlineStr">
         <is>
           <t xml:space="preserve">occident</t>
@@ -6065,7 +6070,7 @@
       </c>
       <c r="M86" t="inlineStr">
         <is>
-          <t xml:space="preserve">juive</t>
+          <t xml:space="preserve">juive;femme</t>
         </is>
       </c>
       <c r="N86" t="inlineStr">
@@ -6548,6 +6553,11 @@
           <t xml:space="preserve"> pas une philosophe au sens académique, mais son œuvre littéraire, cinématographique et théâtrale déploie une pensée originale, centrée sur l’écriture, le désir, la mémoire et la condition humaine.</t>
         </is>
       </c>
+      <c r="M94" t="inlineStr">
+        <is>
+          <t xml:space="preserve">femme</t>
+        </is>
+      </c>
       <c r="N94" t="inlineStr">
         <is>
           <t xml:space="preserve">occident</t>
@@ -6725,6 +6735,11 @@
           <t>philosophe française spécialiste de phénoménologie et de logique.</t>
         </is>
       </c>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t xml:space="preserve">femme</t>
+        </is>
+      </c>
       <c r="N97" t="inlineStr">
         <is>
           <t xml:space="preserve">occident</t>
@@ -8413,6 +8428,11 @@
           <t>philosophe française fondatrice du féminisme matérialiste &amp; de la théorie Queer.</t>
         </is>
       </c>
+      <c r="M125" t="inlineStr">
+        <is>
+          <t xml:space="preserve">femme</t>
+        </is>
+      </c>
       <c r="N125" t="inlineStr">
         <is>
           <t xml:space="preserve">occident</t>
@@ -9197,6 +9217,11 @@
           <t>philosophe française majeure de la philosophie politique contemporaine.</t>
         </is>
       </c>
+      <c r="M138" t="inlineStr">
+        <is>
+          <t xml:space="preserve">femme</t>
+        </is>
+      </c>
       <c r="N138" t="inlineStr">
         <is>
           <t xml:space="preserve">occident</t>
@@ -9377,6 +9402,11 @@
           <t>philosophe et psychanalyste française fine analyste, qui explore la vulnérabilité humaine.</t>
         </is>
       </c>
+      <c r="M141" t="inlineStr">
+        <is>
+          <t xml:space="preserve">femme</t>
+        </is>
+      </c>
       <c r="N141" t="inlineStr">
         <is>
           <t xml:space="preserve">occident</t>
@@ -9384,12 +9414,54 @@
       </c>
     </row>
     <row r="142" ht="255.75" customHeight="1" s="49">
-      <c r="E142" s="47" t="n"/>
+      <c r="A142" s="47">
+        <v>1934</v>
+      </c>
+      <c r="B142" s="47">
+        <v>1994</v>
+      </c>
+      <c r="C142" s="47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1934 - 1994</t>
+        </is>
+      </c>
+      <c r="D142" s="47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sarah KOFMAN</t>
+        </is>
+      </c>
+      <c r="E142" s="47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Sarah_Kofman"  title=" Wikipedia"&gt;Sarah KOFMAN&lt;/a&gt; (1934-1994) est une philosophe française, née à Paris dans une famille juive d'origine polonaise. En 1942, son père, rabbin, fut arrêté lors de la rafle du Vél' d'Hiv et assassiné à Auschwitz. Cachée pendant la guerre, elle raconta bien plus tard cette enfance dans &lt;em&gt;Rue Ordener, rue Labat&lt;/em&gt; (1994), un récit bouleversant.&lt;/p&gt; &lt;p&gt;Professeure à la Sorbonne, proche de Jacques Derrida, elle consacra une grande partie de son œuvre à des lectures minutieuses de Nietzsche et de Freud, dont elle montre les ambiguïtés et les contradictions. Dans &lt;em&gt;L'Énigme de la femme&lt;/em&gt; (1980), elle analyse la manière dont Freud a pensé la féminité et ce que sa théorie révèle de ses propres préjugés. Elle écrivit aussi sur l'art, le rire et la littérature.&lt;/p&gt; &lt;p&gt;Sa méthode consiste à lire les grands textes au plus près, en repérant les métaphores, les exemples et les détails apparemment secondaires, pour y faire apparaître ce que l'auteur ne dit pas explicitement. Ses livres sur Nietzsche, comme &lt;em&gt;Nietzsche et la métaphore&lt;/em&gt; (1972), ont renouvelé la lecture de ce philosophe en France, en montrant l'importance du style et des images dans sa pensée.&lt;/p&gt; &lt;p&gt;Dans &lt;em&gt;Paroles suffoquées&lt;/em&gt; (1987), elle réfléchit, à partir de Maurice Blanchot et de Robert Antelme, à l'impossibilité et à la nécessité de parler d'Auschwitz. Elle mit fin à ses jours en 1994, le jour anniversaire de la naissance de Nietzsche. Son œuvre, d'une trentaine de livres, allie rigueur philosophique, écoute de la psychanalyse et mémoire de la Shoah.&lt;/p&gt;</t>
+        </is>
+      </c>
       <c r="G142" s="47" t="n"/>
       <c r="H142" s="47" t="n"/>
-      <c r="J142" s="47" t="n"/>
-      <c r="K142" s="47" t="n"/>
-      <c r="L142" s="47" t="n"/>
+      <c r="J142" s="47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">esthetique ; ethique</t>
+        </is>
+      </c>
+      <c r="K142" s="47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Déconstructionnisme</t>
+        </is>
+      </c>
+      <c r="L142" s="47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">philosophe française, lectrice de Nietzsche et de Freud, proche de Derrida, marquée par la Shoah.</t>
+        </is>
+      </c>
+      <c r="M142" t="inlineStr">
+        <is>
+          <t xml:space="preserve">femme ; juive</t>
+        </is>
+      </c>
+      <c r="N142" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="1048566" ht="12.75" customHeight="1" s="49"/>
     <row r="1048567" ht="12.75" customHeight="1" s="49"/>

--- a/data/frise-philosophes-france.xlsx
+++ b/data/frise-philosophes-france.xlsx
@@ -9244,12 +9244,12 @@
       </c>
       <c r="D139" s="55" t="inlineStr">
         <is>
-          <t>Bernard STEIGLER</t>
+          <t xml:space="preserve">Bernard STIEGLER</t>
         </is>
       </c>
       <c r="E139" s="56" t="inlineStr">
         <is>
-          <t>&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Bernard_Stiegler"  title=" Wikipedia"&gt;Bernard STIEGLER&lt;/a&gt; était un philosophe français, l'une des figures les plus originales et les plus influentes de la philosophie française. Né à Villebon-sur-Yvette, son parcours intellectuel fut marqué par une expérience singulière : il prépara sa thèse en philosophie pendant les cinq années qu'il passa en prison (1978-1983), condamné pour braquages. Docteur en philosophie sous la direction de Jacques Derrida, il fut directeur du département du développement culturel du Centre Pompidou puis directeur de l'Institut de Recherche et d'Innovation (IRI). &lt;/p&gt; &lt;p&gt; Son œuvre maîtresse, la trilogie &lt;em&gt;&lt;a href="https://www.youtube.com/watch?v=nwmOFXzCJUg" title="Bernard Steigler a propos de la technique par Adrien Payet"&gt;La Technique et le Temps&lt;/a&gt; &lt;/em&gt; (1994-2001), constitue l'une des analyses philosophiques les plus ambitieuses de la technique et de ses effets sur la temporalité humaine. S'appuyant sur Simondon, Derrida et Heidegger, il y défend la thèse que l'être humain est fondamentalement un être technique : c'est par la technique — les « rétentions tertiaires », les objets qui externalisent la mémoire — que l'humain se constitue comme tel. La technique n'est pas un simple outil mais la condition même de la temporalité humaine et de la transmission culturelle. &lt;/p&gt; &lt;p&gt; Dans ses ouvrages ultérieurs — &lt;em&gt;De la misère symbolique&lt;/em&gt; (2004), &lt;em&gt;Prendre soin&lt;/em&gt; (2008), &lt;em&gt;États de choc&lt;/em&gt; (2012) — il  &lt;a href="https://www.youtube.com/watch?v=IOei5Kb1cQI" title="Bernard Steigler par France 24"&gt;développa une critique &lt;/a&gt;  de l'économie de l'attention et du capitalisme des plateformes numériques, montrant comment ceux-ci détruisent les « savoirs faire » et « savoirs vivre » qui constituent le tissu de l'existence humaine. Sa pensée, nourrie d'une profonde inquiétude sur les effets destructeurs des industries culturelles et numériques, propose une pharmacologie de la technique : la technique est un pharmakon, à la fois poison et remède. &lt;/p&gt;  &lt;audio controls title="Bernard Steigler : je reflechis au rapport entre tehnique et le mal  par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/13915-05.11.2017-ITEMA_21460251-5.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;</t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Bernard_Stiegler"  title=" Wikipedia"&gt;Bernard STIEGLER&lt;/a&gt; était un philosophe français, l'une des figures les plus originales et les plus influentes de la philosophie française. Né à Villebon-sur-Yvette, son parcours intellectuel fut marqué par une expérience singulière : il prépara sa thèse en philosophie pendant les cinq années qu'il passa en prison (1978-1983), condamné pour braquages. Docteur en philosophie sous la direction de Jacques Derrida, il fut directeur du département du développement culturel du Centre Pompidou puis directeur de l'Institut de Recherche et d'Innovation (IRI). &lt;/p&gt; &lt;p&gt; Son œuvre maîtresse, la trilogie &lt;em&gt;&lt;a href="https://www.youtube.com/watch?v=nwmOFXzCJUg" title="Bernard Stiegler a propos de la technique par Adrien Payet"&gt;La Technique et le Temps&lt;/a&gt; &lt;/em&gt; (1994-2001), constitue l'une des analyses philosophiques les plus ambitieuses de la technique et de ses effets sur la temporalité humaine. S'appuyant sur Simondon, Derrida et Heidegger, il y défend la thèse que l'être humain est fondamentalement un être technique : c'est par la technique — les « rétentions tertiaires », les objets qui externalisent la mémoire — que l'humain se constitue comme tel. La technique n'est pas un simple outil mais la condition même de la temporalité humaine et de la transmission culturelle. &lt;/p&gt; &lt;p&gt; Dans ses ouvrages ultérieurs — &lt;em&gt;De la misère symbolique&lt;/em&gt; (2004), &lt;em&gt;Prendre soin&lt;/em&gt; (2008), &lt;em&gt;États de choc&lt;/em&gt; (2012) — il  &lt;a href="https://www.youtube.com/watch?v=IOei5Kb1cQI" title="Bernard Stiegler par France 24"&gt;développa une critique &lt;/a&gt;  de l'économie de l'attention et du capitalisme des plateformes numériques, montrant comment ceux-ci détruisent les « savoirs faire » et « savoirs vivre » qui constituent le tissu de l'existence humaine. Sa pensée, nourrie d'une profonde inquiétude sur les effets destructeurs des industries culturelles et numériques, propose une pharmacologie de la technique : la technique est un pharmakon, à la fois poison et remède. &lt;/p&gt;  &lt;audio controls title="Bernard Stiegler : je reflechis au rapport entre technique et le mal  par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/13915-05.11.2017-ITEMA_21460251-5.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;</t>
         </is>
       </c>
       <c r="F139" s="54" t="inlineStr">

--- a/data/frise-philosophes-france.xlsx
+++ b/data/frise-philosophes-france.xlsx
@@ -6545,7 +6545,7 @@
       </c>
       <c r="K94" s="48" t="inlineStr">
         <is>
-          <t>Monisme ; Existentialisme</t>
+          <t xml:space="preserve">Existentialisme</t>
         </is>
       </c>
       <c r="L94" s="76" t="inlineStr">

--- a/data/frise-philosophes-france.xlsx
+++ b/data/frise-philosophes-france.xlsx
@@ -8226,8 +8226,16 @@
           <t>&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/G%C3%A9rard_Granel"  title=" Wikipedia"&gt;Gérard GRANEL&lt;/a&gt; était un philosophe français, connu pour ses traductions et commentaires des œuvres de Husserl et Heidegger, et pour ses réflexions originales sur le capitalisme contemporain et l'enseignement philosophique. Agrégé de philosophie et professeur à l'Université de Toulouse-le Mirail, il fut l'une des &lt;a href="//www.gerardgranel.com"  title=" gerard granel"&gt;figures les plus singulières &lt;/a&gt;  de la philosophie française de la seconde moitié du XXe siècle, associant une rigueur herméneutique exigeante à un engagement politique radical. &lt;/p&gt; &lt;p&gt; Ses traductions de textes fondamentaux de Husserl — notamment les &lt;em&gt;Leçons pour une phénoménologie de la conscience intime du temps&lt;/em&gt; (1964) — et de Heidegger — &lt;em&gt;Être et Temps&lt;/em&gt; (1986), traduction très discutée mais d'une grande rigueur herméneutique — constituent des apports décisifs à la diffusion de la phénoménologie en France. Dans son essai &lt;em&gt;L'Équivoque ontologique de la pensée kantienne&lt;/em&gt; (1970), il offre une interprétation originale de Kant à la lumière de la phénoménologie. &lt;/p&gt; &lt;p&gt; Dans &lt;a href="https://www.youtube.com/watch?v=DBGFMdmXgik"  title=" gerard granel apolis par Politproductions"&gt;ses essais tardifs, &lt;/a&gt; réunis notamment dans &lt;em&gt;De l'Université&lt;/em&gt; (1982) et &lt;em&gt;Traditionis traditio&lt;/em&gt; (1972), il développe une réflexion acérée sur la crise de l'université et de la transmission du savoir philosophique à l'ère capitaliste. Sa critique des formes contemporaines de la domination économique et culturelle, menée à partir des outils de la phénoménologie et du marxisme, est l'une des contributions les plus originales de sa pensée à la compréhension de la modernité. Penseur exigeant et inclassable, il garde aujourd'hui une audience fidèle parmi les philosophes français. &lt;/p&gt;</t>
         </is>
       </c>
-      <c r="F122" s="57" t="n"/>
-      <c r="G122" s="59" t="n"/>
+      <c r="F122" s="57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DBGFMdmXgik</t>
+        </is>
+      </c>
+      <c r="G122" s="59" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"Présentation de  «  Apolis » de Gérard Granel" par Politproductions</t>
+        </is>
+      </c>
       <c r="H122" s="65" t="inlineStr">
         <is>
           <t>https://www.laphilo.fr/pho/granel-mini.webp</t>
@@ -8314,1147 +8322,1160 @@
         </is>
       </c>
     </row>
-    <row r="124" ht="164.25" customHeight="1" s="49">
-      <c r="A124" s="57" t="n">
+    <row r="124" ht="255.75" customHeight="1" s="49">
+      <c r="A124" s="47">
+        <v>1934</v>
+      </c>
+      <c r="B124" s="47">
+        <v>1994</v>
+      </c>
+      <c r="C124" s="47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1934 - 1994</t>
+        </is>
+      </c>
+      <c r="D124" s="47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sarah KOFMAN</t>
+        </is>
+      </c>
+      <c r="E124" s="47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Sarah_Kofman" title=" Wikipedia"&gt;Sarah KOFMAN&lt;/a&gt;&amp;nbsp;était une philosophe française, née à Paris dans une famille juive d'origine polonaise. En 1942, son père, rabbin, fut arrêté lors de la rafle du Vél' d'Hiv et assassiné à Auschwitz. Cachée pendant la guerre, elle raconta bien plus tard cette enfance dans &lt;em&gt;&lt;a href="https://www.youtube.com/watch?v=VIAbVde4ePM" title="Rue Ordener Rue Labat par exekow"&gt;Rue Ordener, rue Labat&lt;/a&gt;&lt;/em&gt; (1994), un récit bouleversant.&lt;/p&gt; &lt;p&gt;Professeure à la Sorbonne, proche de Jacques Derrida, elle consacra une grande partie de son œuvre à des lectures minutieuses de Nietzsche et de Freud, dont elle montre les ambiguïtés et les contradictions. Dans &lt;em&gt;L'Énigme de la femme&lt;/em&gt; (1980), elle analyse la manière dont Freud a pensé la féminité et ce que sa théorie révèle de ses propres préjugés. Elle écrivit aussi sur l'art, le rire et la littérature.&lt;/p&gt; &lt;p&gt;Sa méthode consiste à lire les grands textes au plus près, en repérant les métaphores, les exemples et les détails apparemment secondaires, pour y faire apparaître ce que l'auteur ne dit pas explicitement. Ses livres sur Nietzsche, comme &lt;em&gt;Nietzsche et la métaphore&lt;/em&gt; (1972), ont renouvelé la lecture de ce philosophe en France, en montrant l'importance du style et des images dans sa pensée.&lt;/p&gt; &lt;p&gt;Dans &lt;em&gt;Paroles suffoquées&lt;/em&gt; (1987), elle réfléchit, à partir de Maurice Blanchot et de Robert Antelme, à l'impossibilité et à la nécessité de parler d'Auschwitz. Elle mit &lt;a href="https://www.persee.fr/doc/grif_0770-6081_1997_hos_3_1_1922" title="Comment philosophe une femme par persée"&gt;fin à ses jours en 1994&lt;/a&gt;, le jour anniversaire de la naissance de Nietzsche. Son œuvre, d'une trentaine de livres, allie rigueur philosophique, écoute de la psychanalyse et mémoire de la Shoah.&lt;/p&gt;  &lt;audio controls title="Sarah Kofman, une enfance cachée entre la rue Ordener et la rue Labat par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/24541-12.10.2023-ITEMA_23517920-2010C3372E1858-21.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t xml:space="preserve">KdLreZP9TuI</t>
+        </is>
+      </c>
+      <c r="G124" s="47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"Sarah Kofman - Entretien (Agora)" par Artesquieu</t>
+        </is>
+      </c>
+      <c r="H124" s="47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/sarahkofman-mini.webp</t>
+        </is>
+      </c>
+      <c r="J124" s="47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">esthetique ; ethique</t>
+        </is>
+      </c>
+      <c r="K124" s="47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Déconstructionnisme</t>
+        </is>
+      </c>
+      <c r="L124" s="47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">philosophe française, lectrice de Nietzsche et de Freud, proche de Derrida, marquée par la Shoah.</t>
+        </is>
+      </c>
+      <c r="M124" t="inlineStr">
+        <is>
+          <t xml:space="preserve">femme ; juive</t>
+        </is>
+      </c>
+      <c r="N124" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+    </row>
+    <row r="125" ht="164.25" customHeight="1" s="49">
+      <c r="A125" s="57" t="n">
         <v>1935</v>
       </c>
-      <c r="B124" s="57" t="inlineStr">
+      <c r="B125" s="57" t="inlineStr">
         <is>
           <t>2021</t>
         </is>
       </c>
-      <c r="C124" s="57" t="inlineStr">
+      <c r="C125" s="57" t="inlineStr">
         <is>
           <t>1935 – 2021</t>
         </is>
       </c>
-      <c r="D124" s="58" t="inlineStr">
+      <c r="D125" s="58" t="inlineStr">
         <is>
           <t>François FÉDIER</t>
         </is>
       </c>
-      <c r="E124" s="59" t="inlineStr">
+      <c r="E125" s="59" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Fran%C3%A7ois_F%C3%A9dier"  title=" Wikipedia"&gt;François FÉDIER&lt;/a&gt; était un philosophe français, principal traducteur de Martin Heidegger en français après Jean Beaufret dont il fut le disciple. Agrégé de philosophie et maître de conférences à la Sorbonne, il consacra l'essentiel de sa vie intellectuelle à la traduction, au commentaire et à la défense de l'œuvre de Heidegger, notamment face aux controverses suscitées par l'engagement politique du philosophe allemand.  &lt;a href="https://www.youtube.com/watch?v=ggAIziycK9c"  title=" françois fedier partage formel par philosopphies TV"&gt;Sa fidélité &lt;/a&gt; à Heidegger, absolue et parfois polémique, fit de lui une figure de référence mais aussi de controverse dans la philosophie française. &lt;/p&gt; &lt;p&gt; Ses traductions de textes heideggeriens — notamment &lt;em&gt;Acheminement vers la parole&lt;/em&gt; (1959), des textes sur Hölderlin, et de nombreux fragments et cours — sont caractérisées par une attention extrême à la lettre allemande et par le refus de faciliter l'accès au texte au détriment de sa pensée propre. Cette conception exigeante de la traduction philosophique, qui cherche à faire  &lt;a href="https://www.youtube.com/watch?v=i8Nb3W1stIo"  title=" françois fedier apport à la philosophie par Philosophie TV"&gt;résonner en français &lt;/a&gt; la langue même de la pensée heideggerienne, a été à la fois admirée pour sa rigueur et critiquée pour son obscurité. &lt;/p&gt; &lt;p&gt; Dans ses essais critiques — notamment &lt;em&gt;Heidegger : anatomie d'un scandale&lt;/em&gt; (1988), réponse aux attaques de Victor Farias —il  prit la défense de Heidegger face aux accusations de nazisme, défendant la thèse d'une erreur politique ponctuelle sans rapport avec le cœur de la pensée philosophique. Cette posture, vivement contestée, a nourri l'une des controverses les plus vives de la philosophie française de la fin du XXe siècle. Il reste une figure incontournable et clivante de la réception française de Heidegger. &lt;/p&gt;</t>
         </is>
       </c>
-      <c r="F124" s="57" t="inlineStr">
+      <c r="F125" s="57" t="inlineStr">
         <is>
           <t>i8Nb3W1stIo</t>
         </is>
       </c>
-      <c r="G124" s="59" t="inlineStr">
+      <c r="G125" s="59" t="inlineStr">
         <is>
           <t>"Francois Fédier Apports à la philosophie. De l'avenance" par Philosophie TV</t>
         </is>
       </c>
-      <c r="H124" s="65" t="inlineStr">
+      <c r="H125" s="65" t="inlineStr">
         <is>
           <t>https://www.laphilo.fr/pho/fedier-mini.webp</t>
         </is>
       </c>
-      <c r="J124" s="48" t="inlineStr">
+      <c r="J125" s="48" t="inlineStr">
         <is>
           <t>metaphysique</t>
         </is>
       </c>
-      <c r="K124" s="48" t="inlineStr">
+      <c r="K125" s="48" t="inlineStr">
         <is>
           <t>Phénoménologie</t>
         </is>
       </c>
-      <c r="L124" s="48" t="inlineStr">
+      <c r="L125" s="48" t="inlineStr">
         <is>
           <t>philosophe français, principal traducteur de Martin Heidegger en français.</t>
         </is>
       </c>
-      <c r="N124" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-    </row>
-    <row r="125" ht="164.25" customHeight="1" s="49">
-      <c r="A125" s="54" t="n">
+      <c r="N125" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+    </row>
+    <row r="126" ht="164.25" customHeight="1" s="49">
+      <c r="A126" s="54" t="n">
         <v>1935</v>
       </c>
-      <c r="B125" s="54" t="inlineStr">
+      <c r="B126" s="54" t="inlineStr">
         <is>
           <t>2003</t>
         </is>
       </c>
-      <c r="C125" s="54" t="inlineStr">
+      <c r="C126" s="54" t="inlineStr">
         <is>
           <t>1935 – 2003</t>
         </is>
       </c>
-      <c r="D125" s="55" t="inlineStr">
+      <c r="D126" s="55" t="inlineStr">
         <is>
           <t>Monique WITTIG</t>
         </is>
       </c>
-      <c r="E125" s="56" t="inlineStr">
+      <c r="E126" s="56" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Monique_Wittig"  title=" Wikipedia"&gt;Monique WITTIG&lt;/a&gt; était une écrivaine et philosophe française, figure fondatrice du féminisme matérialiste et de la théorie queer en France. Elle fut l'une des fondatrices du Mouvement de libération des femmes (MLF) en 1970. Auteure d'une œuvre littéraire et théorique  &lt;a href="https://laviedesidees.fr/Renversements-de-Monique-Wittig-6277"  title=" reversements de Monique WITTIG par laviedesidees"&gt;d'une grande originalité, &lt;/a&gt; elle s'installa aux États-Unis dans les années 1970 où elle enseigna dans plusieurs universités, contribuant à diffuser la pensée féministe française à l'échelle internationale. &lt;/p&gt; &lt;p&gt; Son premier roman, &lt;em&gt;L'Opoponax&lt;/em&gt; (1964, prix Médicis), est une œuvre expérimentale qui décrit l'enfance à travers un pronom impersonnel qui efface le genre, préfigurant ses réflexions théoriques ultérieures sur la langue et le genre. &lt;em&gt;Les Guérillères&lt;/em&gt; (1969) est un roman collectif qui figure une utopie féministe radicale. &lt;em&gt;Le Corps lesbien&lt;/em&gt; (1973) propose une réécriture poétique et politique du corps féminin et de la sexualité lesbienne. Ces œuvres litté raires mettent en pratique une déconstruction du langage comme vecteur de l'oppression patriarcale. &lt;/p&gt; &lt;p&gt; Dans ses essais théoriques, réunis dans &lt;em&gt;La Pensée straight&lt;/em&gt; (2001), Wittig développe une critique radicale de l'hétérosexualité obligatoire comme régime politique qui produit les catégories de « femme » et d'« homme » comme classes. Sa thèse centrale —  &lt;a href="https://www.youtube.com/watch?v=xTga507vuE8"  title=" c’est quoi être une femme du coup par Marinette"&gt;« les lesbiennes ne sont pas des femmes » &lt;/a&gt; — affirme que la catégorie « femme » est une construction politique de l'hétérosexualité dominante et que les lesbiennes, en refusant ce rapport, échappent à cette catégorie. Cette pensée a profondément influencé Judith Butler et les théories queer contemporaines. &lt;/p&gt;   &lt;audio controls title="La renaissance Wittig par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/25343-02.05.2025-ITEMA_24121665-2025C53458S0122-NET_MFC_69CE613B-224D-46F3-B177-81981898A856-21.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;  </t>
         </is>
       </c>
-      <c r="F125" s="54" t="inlineStr">
+      <c r="F126" s="54" t="inlineStr">
         <is>
           <t>cZH0FRIe0LM</t>
         </is>
       </c>
-      <c r="G125" s="56" t="inlineStr">
+      <c r="G126" s="56" t="inlineStr">
         <is>
           <t>"Monique Wittig, la révolutionnaire des sexes" par France Culture</t>
         </is>
       </c>
-      <c r="H125" s="62" t="inlineStr">
+      <c r="H126" s="62" t="inlineStr">
         <is>
           <t>https://www.laphilo.fr/pho/mwittig-mini.webp</t>
         </is>
       </c>
-      <c r="J125" s="48" t="inlineStr">
+      <c r="J126" s="48" t="inlineStr">
         <is>
           <t>politique ; ethique</t>
         </is>
       </c>
-      <c r="K125" s="48" t="inlineStr">
+      <c r="K126" s="48" t="inlineStr">
         <is>
           <t>Post-structuralisme ; Féminisme</t>
         </is>
       </c>
-      <c r="L125" s="48" t="inlineStr">
+      <c r="L126" s="48" t="inlineStr">
         <is>
           <t>philosophe française fondatrice du féminisme matérialiste &amp; de la théorie Queer.</t>
         </is>
       </c>
-      <c r="M125" t="inlineStr">
+      <c r="M126" t="inlineStr">
         <is>
           <t xml:space="preserve">femme</t>
         </is>
       </c>
-      <c r="N125" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-    </row>
-    <row r="126" ht="129" customHeight="1" s="49">
-      <c r="A126" s="47" t="n">
+      <c r="N126" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+    </row>
+    <row r="127" ht="129" customHeight="1" s="49">
+      <c r="A127" s="47" t="n">
         <v>1936</v>
       </c>
-      <c r="B126" s="47" t="n">
+      <c r="B127" s="47" t="n">
         <v>2026</v>
       </c>
-      <c r="C126" s="47" t="inlineStr">
+      <c r="C127" s="47" t="inlineStr">
         <is>
           <t>1936 – 2026</t>
         </is>
       </c>
-      <c r="D126" s="47" t="inlineStr">
+      <c r="D127" s="47" t="inlineStr">
         <is>
           <t>Michel HULIN</t>
         </is>
       </c>
-      <c r="E126" s="48" t="inlineStr">
+      <c r="E127" s="48" t="inlineStr">
         <is>
           <t xml:space="preserve"> &lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Michel_Hulin"  title=" Wikipedia"&gt;Michel HULIN&lt;/a&gt; était un philosophe français récemment décédé, grand spécialiste de la &lt;a href="https://www.youtube.com/watch?v=tJFic9y58Sc" title=" Aperçu de l’hindouisme avec Michel Hulin par Resonances "&gt;philosophie indienne &lt;/a&gt; et de la comparaison entre pensée européenne et pensée asiatique, notamment de l’Advaïta Vedānta, le courant « non‑dualiste » du vedānta. Longtemps professeur de philosophie indienne et comparée à l’université Paris‑Sorbonne, il a joué un rôle central dans la diffusion en France des grandes écoles de pensée de l’Inde. Sa carrière s’est accompagnée d’un important travail de traduction du sanskrit et de vulgarisation, accessible à un public non spécialiste. &lt;/p&gt; &lt;p&gt; Ses recherches portent d’une part sur  &lt;a href="https://www.youtube.com/watch?v=kaJP8yDwHeY" title=" For intérieur par Resonnances "&gt;la pensée indienne classique &lt;/a&gt;  (notion d’ahamkāra, textes vedāntins et shivaïtes d’inspiration tantrique), d’autre part sur les questions épistémologiques et métaphysiques que soulève la rencontre entre les traditions européennes et asiatiques. Dans sa thèse, Le Principe de l’ego dans la pensée indienne classique, il analyse la notion de « faux moi » et montre comment elle éclaire notre expérience ordinaire de la conscience. Il s’intéresse également à la question du temps, de l’éternité et des expériences dites mystiques, qu’il relie à des vécus très concrets. &lt;/p&gt; &lt;p&gt; Dans des ouvrages comme La Face cachée du temps, La Mystique sauvage, Hegel et l’Orient, Shankara et la non‑dualité ou encore l’anthologie L’Inde des sages, il  conjugue une érudition très précise et un style volontairement clair. Il montre comment des interrogations métaphysiques complexes – sur le moi, le temps, l’au‑delà ou l’expérience spirituelle – touchent directement la vie intérieure de chacun. Par son enseignement et ses livres, il a contribué à installer durablement en France une philosophie comparée attentive au dialogue entre Europe et Inde. &lt;p&gt; &lt;/p&gt;&lt;audio controls title="  Philosophies indiennes (1/4) : Upanishads, les textes fondateurs ?  par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/10467-16.12.2013-ITEMA_20562153-2013C12410S0350-NET_FC_A092AF0E-5BC1-49EE-A72F-E62BB6A2A8B1-21.mp3" type="audio/mpeg" align="center"&gt;&lt;/audio&gt;  &lt;p&gt;  &lt;/p&gt;
 </t>
         </is>
       </c>
-      <c r="F126" s="47" t="inlineStr">
+      <c r="F127" s="47" t="inlineStr">
         <is>
           <t>cLbyvPtJW2c</t>
         </is>
       </c>
-      <c r="G126" s="90" t="inlineStr">
+      <c r="G127" s="90" t="inlineStr">
         <is>
           <t>le message des Upanishads par BAGLIS TV</t>
         </is>
       </c>
-      <c r="H126" s="48" t="inlineStr">
+      <c r="H127" s="48" t="inlineStr">
         <is>
           <t>https://www.laphilo.fr/pho/mhulin-mini.webp</t>
         </is>
       </c>
-      <c r="J126" s="48" t="inlineStr">
+      <c r="J127" s="48" t="inlineStr">
         <is>
           <t>metaphysique ; spiritualite</t>
         </is>
       </c>
-      <c r="K126" s="48" t="inlineStr">
+      <c r="K127" s="48" t="inlineStr">
         <is>
           <t>Spiritualisme</t>
         </is>
       </c>
-      <c r="L126" s="48" t="inlineStr">
+      <c r="L127" s="48" t="inlineStr">
         <is>
           <t>philosophe français grand connaisseur de la philosophie indienne.</t>
         </is>
       </c>
-      <c r="N126" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-    </row>
-    <row r="127" ht="185.25" customHeight="1" s="49">
-      <c r="A127" s="57" t="n">
+      <c r="N127" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+    </row>
+    <row r="128" ht="185.25" customHeight="1" s="49">
+      <c r="A128" s="57" t="n">
         <v>1938</v>
       </c>
-      <c r="B127" s="57" t="inlineStr">
+      <c r="B128" s="57" t="inlineStr">
         <is>
           <t>2017</t>
         </is>
       </c>
-      <c r="C127" s="57" t="inlineStr">
+      <c r="C128" s="57" t="inlineStr">
         <is>
           <t>1938 – 2017</t>
         </is>
       </c>
-      <c r="D127" s="58" t="inlineStr">
+      <c r="D128" s="58" t="inlineStr">
         <is>
           <t>Jean-François MARQUET</t>
         </is>
       </c>
-      <c r="E127" s="59" t="inlineStr">
+      <c r="E128" s="59" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Jean-Fran%C3%A7ois_Marquet"  title=" Wikipedia"&gt;Jean-François MARQUET&lt;/a&gt; était un philosophe français spécialiste de l'idéalisme allemand et de la mystique, connu pour ses travaux sur Schelling, Hegel, Böhme et &lt;a href="https://fr.wikipedia.org/wiki/N%C3%A9oplatonisme"  title=" neoplatonisme par Wikipedia"&gt;le néoplatonisme. &lt;/a&gt; Agrégé de philosophie et professeur à l'Université Paris-Sorbonne, il fut l'un des meilleurs connaisseurs français de Schelling et l'un des rares philosophes à s'être intéressé aux connexions entre la philosophie spéculative allemande et les traditions mystiques occidentales. &lt;/p&gt; &lt;p&gt; Sa thèse principale, &lt;em&gt;Liberté et Existence. Étude sur la formation de la philosophie de Schelling&lt;/em&gt; (1973), est une analyse rigoureuse et pénétrante du développement de la pensée de Schelling, depuis les premiers textes influencés par Fichte jusqu'à la philosophie tardive de la liberté et de la mythologie. Il y montre la cohérence profonde d'une pensée souvent jugée dispersée, en la centrant sur la problématique de la liberté comme indifférence originaire de l'être. &lt;/p&gt; &lt;p&gt; Dans &lt;em&gt;Miroirs de l'identité. La Littérature hantée par la philosophie&lt;/em&gt; (1996), il explore les relations entre philosophie et littérature à travers des auteurs comme Novalis, Kleist, Hoffmann et Nerval. Ses études sur Jakob Böhme et les thiosophes germaniques contribuèrent à ouvrir la philosophie française à des courants méconnus mais essentiels pour comprendre l'émergence de l'idéalisme allemand. Il représente un philosophe  &lt;a href="https://www.persee.fr/doc/abpo_0399-0826_1976_num_83_2_2819"  title=" les calendriers positivistes par persée"&gt;d'une rare érudition, &lt;/a&gt; capable de naviguer entre la rigueur conceptuelle et l'ouverture aux dimensions poétiques et spirituelles de la pensée. &lt;/p&gt;  &lt;audio controls title="Les strategies du secret par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/10194-14.02.2007-ITEMA_20058582-2007C3035S0033-MEM_000035816_RF-21.mp3" type="audio/mpeg" align="center"&gt;&lt;/audio&gt;  </t>
         </is>
       </c>
-      <c r="F127" s="57" t="inlineStr">
+      <c r="F128" s="57" t="inlineStr">
         <is>
           <t>W1PdYExCQRY</t>
         </is>
       </c>
-      <c r="G127" s="59" t="inlineStr">
+      <c r="G128" s="59" t="inlineStr">
         <is>
           <t>"JEAN FRANCOIS MARQUET" par Didier Doc Pilot</t>
         </is>
       </c>
-      <c r="H127" s="65" t="inlineStr">
+      <c r="H128" s="65" t="inlineStr">
         <is>
           <t>https://www.laphilo.fr/pho/jfmarquet-mini.webp</t>
         </is>
       </c>
-      <c r="J127" s="48" t="inlineStr">
+      <c r="J128" s="48" t="inlineStr">
         <is>
           <t>metaphysique</t>
         </is>
       </c>
-      <c r="K127" s="48" t="inlineStr">
+      <c r="K128" s="48" t="inlineStr">
         <is>
           <t>Phénoménologie</t>
         </is>
       </c>
-      <c r="L127" s="48" t="inlineStr">
+      <c r="L128" s="48" t="inlineStr">
         <is>
           <t>philosophe français spécialiste de l'idéalisme allemand et de la mystique.</t>
         </is>
       </c>
-      <c r="N127" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-    </row>
-    <row r="128" ht="216.75" customHeight="1" s="49">
-      <c r="A128" s="54" t="n">
+      <c r="N128" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+    </row>
+    <row r="129" ht="216.75" customHeight="1" s="49">
+      <c r="A129" s="54" t="n">
         <v>1939</v>
       </c>
-      <c r="B128" s="54" t="inlineStr">
+      <c r="B129" s="54" t="inlineStr">
         <is>
           <t>2018</t>
         </is>
       </c>
-      <c r="C128" s="54" t="inlineStr">
+      <c r="C129" s="54" t="inlineStr">
         <is>
           <t>1939 – 2018</t>
         </is>
       </c>
-      <c r="D128" s="55" t="inlineStr">
+      <c r="D129" s="55" t="inlineStr">
         <is>
           <t>Clément ROSSET</t>
         </is>
       </c>
-      <c r="E128" s="62" t="inlineStr">
+      <c r="E129" s="62" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Cl%C3%A9ment_Rosset" title=" Wikipedia"&gt;Clément ROSSET&lt;/a&gt; était un philosophe français connu pour sa pensée radicale et son style d'écriture d'une grande clarté. Son œuvre est principalement centrée sur le concept du  &lt;a href="https://www.youtube.com/watch?v=I50Jbj6uQEU" title="Clément Rosset : la réalité ne convient pas ! par Kosmos"&gt;"réel"&lt;/a&gt;  et l'incapacité ou la difficulté de l'homme à l'accepter dans sa singularité et souvent sa cruauté. Voici les points essentiels concernant sa philosophie : &lt;/p&gt; &lt;p&gt; - &lt;a href="https://www.youtube.com/watch?v=8m_kXVBdtwg"  title=" Le réel et son double, Clément Rosset, 2.2 avant-propos par Thibault BELZACQ"&gt;Le Réel sans double&lt;/a&gt; : Son idée maîtresse est que le réel est unique, singulier et dépourvu de tout "double". Il n'y a pas d'arrière-monde, pas de sens caché, pas de consolation ou d'illusion qui puisse atténuer sa nature brute. Le réel est simplement ce qui est, dans son évidence la plus nue. &lt;/p&gt; &lt;p&gt; - Le Refus du double et de l'illusion : Une grande partie de son travail consiste à traquer les différentes formes d'illusions et de doubles que l'humanité crée pour  &lt;a href="https://philitt.fr/2023/09/12/clement-rosset-tout-est-sans-raison/"  title="Clément Rosset : tout est sans raison par Phillitt"&gt;échapper à la confrontation&lt;/a&gt; directe avec le réel. Ces doubles peuvent être d'ordre métaphysique, moral, psychologique, ou même esthétique.&lt;/p&gt; &lt;p&gt; - &lt;a href="https://www.youtube.com/watch?v=JDcudFE_uBQ"  title="Entretien avec Pierre Dumayet (1961) par Archives"&gt;Philosophie tragique&lt;/a&gt; et Joie : Bien que sa pensée puisse sembler sombre en insistant sur la cruauté et l'absurdité du réel, il développe une philosophie que l'on qualifie souvent de "tragique" au sens nietzschéen du terme. Il ne s'agit pas de désespoir, mais plutôt de l'affirmation de la vie et du réel tels qu'ils sont, y compris dans leurs aspects les plus difficiles. &lt;/p&gt; &lt;p&gt; Il est également remarquable par son style d'écriture. Loin du jargon philosophique abscons, il privilégie une langue simple, directe et percutante. Cette clarté formelle est au service de la clarté de sa pensée, cherchant à énoncer le réel avec le moins d'interférences possible. Son œuvre, bien que parfois restée en marge des courants universitaires dominants, a marqué par sa radicalité, sa lucidité et sa défense d'une confrontation sans fard avec le réel.  &lt;/p&gt; &lt;audio controls title="Clément Rosset par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/10080-20.12.2013-ITEMA_20564152-2013C3403E0215-21.mp3" type="audio/mpeg" align="center"&gt;&lt;/audio&gt;  </t>
         </is>
       </c>
-      <c r="F128" s="54" t="inlineStr">
+      <c r="F129" s="54" t="inlineStr">
         <is>
           <t>9m6CPt4pRlw</t>
         </is>
       </c>
-      <c r="G128" s="56" t="inlineStr">
+      <c r="G129" s="56" t="inlineStr">
         <is>
           <t>"Clément Rosset (1): Heureux, malgré tout" par Camille Tassel</t>
         </is>
       </c>
-      <c r="H128" s="62" t="inlineStr">
+      <c r="H129" s="62" t="inlineStr">
         <is>
           <t>https://www.laphilo.fr/pho/rosset-mini.webp</t>
         </is>
       </c>
-      <c r="J128" s="48" t="inlineStr">
+      <c r="J129" s="48" t="inlineStr">
         <is>
           <t>metaphysique ; ethique</t>
         </is>
       </c>
-      <c r="K128" s="48" t="inlineStr">
+      <c r="K129" s="48" t="inlineStr">
         <is>
           <t>Naturalisme</t>
         </is>
       </c>
-      <c r="L128" s="48" t="inlineStr">
+      <c r="L129" s="48" t="inlineStr">
         <is>
           <t>philosophe français du tragique et de la théorie du réel.</t>
         </is>
       </c>
-      <c r="N128" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-    </row>
-    <row r="129" ht="199.5" customHeight="1" s="49">
-      <c r="A129" s="57" t="n">
+      <c r="N129" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+    </row>
+    <row r="130" ht="199.5" customHeight="1" s="49">
+      <c r="A130" s="57" t="n">
         <v>1940</v>
       </c>
-      <c r="B129" s="57" t="inlineStr">
+      <c r="B130" s="57" t="inlineStr">
         <is>
           <t>2021</t>
         </is>
       </c>
-      <c r="C129" s="57" t="inlineStr">
+      <c r="C130" s="57" t="inlineStr">
         <is>
           <t>1940 – 2021</t>
         </is>
       </c>
-      <c r="D129" s="58" t="inlineStr">
+      <c r="D130" s="58" t="inlineStr">
         <is>
           <t>Jacques BOUVERESSE</t>
         </is>
       </c>
-      <c r="E129" s="65" t="inlineStr">
+      <c r="E130" s="65" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Jacques_Bouveresse"  title=" Wikipedia"&gt;Jacques BOUVERESSE&lt;/a&gt; était un philosophe français du courant analytique, connu pour son rationalisme exigeant, son &lt;a href="https://www.youtube.com/watch?v=mfGM00nmj20"  title=" Wittgenstein et l'intériorité 一 Jacques Bouveresse par Andrea Cirla "&gt;travail sur Wittgenstein &lt;/a&gt; et sa critique des dérives du milieu intellectuel français. Il a largement contribué à introduire et stabiliser en France une philosophie soucieuse de vérité, de clarté et d’argumentation rigoureuse. &lt;/p&gt; &lt;p&gt; Ses domaines privilégiés sont la philosophie de la connaissance, des sciences, des mathématiques, de la logique, du langage, ainsi qu’une philosophie de la culture attentive à la littérature et à la critique sociale.  Il se réclame du rationalisme des Lumières et s’inspire fortement de la philosophie analytique, du Cercle de Vienne, de Frege, de Gödel et de la tradition d’Europe centrale. Wittgenstein, qu’il contribue à faire connaître en France, est l’une de ses références centrales. &lt;/p&gt; &lt;p&gt; Il défend une position rationaliste dont le prolongement éthique est ce qu’il appelle la  &lt;a href="https://www.persee.fr/doc/lgge_0458-726x_1971_num_6_21_2079" title="Langage ordinaire et philosophie par Persée "&gt;"modestie intellectuelle" &lt;/a&gt; : ne pas exagérer ce que la philosophie peut faire, refuser le pathos et le prestige facile. Il combat le relativisme, l’historicisme radical et les remises en cause globales de la notion de vérité, notamment chez certains auteurs français, tout en reconnaissant par ailleurs leur importance. &lt;/p&gt; &lt;p&gt; Sa grande thèse, "Le Mythe de l’intériorité", porte sur Wittgenstein, le langage privé, l’expérience et la signification, et a joué un rôle clé dans la réception française de Wittgenstein. Il consacre de nombreux travaux à Robert Musil et Karl Kraus, qu’il lit comme des alliés dans un combat pour l’exactitude, la critique de la bêtise et des illusions de la culture moderne. &lt;/p&gt;  &lt;audio controls title="Jacques Bouveresse, à la recherche de la clarté par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/10351-11.05.2021-ITEMA_23961779-2000C3500E0287-21.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;</t>
         </is>
       </c>
-      <c r="F129" s="57" t="inlineStr">
+      <c r="F130" s="57" t="inlineStr">
         <is>
           <t>72_NdVNiFbg</t>
         </is>
       </c>
-      <c r="G129" s="59" t="inlineStr">
+      <c r="G130" s="59" t="inlineStr">
         <is>
           <t>"Jacques Bouveresse, Prodiges et vertiges de l'analogie" par philosophie Analytique</t>
         </is>
       </c>
-      <c r="H129" s="65" t="inlineStr">
+      <c r="H130" s="65" t="inlineStr">
         <is>
           <t>https://www.laphilo.fr/pho/bouveresse-mini.webp</t>
         </is>
       </c>
-      <c r="J129" s="48" t="inlineStr">
+      <c r="J130" s="48" t="inlineStr">
         <is>
           <t>epistemologie ; logique</t>
         </is>
       </c>
-      <c r="K129" s="48" t="inlineStr">
+      <c r="K130" s="48" t="inlineStr">
         <is>
           <t>Analytique</t>
         </is>
       </c>
-      <c r="L129" s="48" t="inlineStr">
+      <c r="L130" s="48" t="inlineStr">
         <is>
           <t>philosophe français du courant analytique d'un rationalisme exigeant.</t>
         </is>
       </c>
-      <c r="N129" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-    </row>
-    <row r="130" ht="164.25" customHeight="1" s="49">
-      <c r="A130" s="54" t="n">
-        <v>1940</v>
-      </c>
-      <c r="B130" s="54" t="inlineStr">
-        <is>
-          <t>2021</t>
-        </is>
-      </c>
-      <c r="C130" s="54" t="inlineStr">
-        <is>
-          <t>1940 – 2021</t>
-        </is>
-      </c>
-      <c r="D130" s="55" t="inlineStr">
-        <is>
-          <t>Jean-Luc NANCY</t>
-        </is>
-      </c>
-      <c r="E130" s="62" t="inlineStr">
-        <is>
-          <t>&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Jean-Luc_Nancy"  title=" Wikipedia"&gt;Jean-Luc NANCY&lt;/a&gt; était un philosophe français, agrégé de philosophie, il fut professeur à l'Université de Strasbourg jusqu'à sa retraite. Sa pensée, en dialogue constant avec Heidegger, Derrida et Lacoue-Labarthe — avec lequel il collabora étroitement — porte sur le « sens du monde », la communauté, le corps et le toucher. &lt;/p&gt; &lt;p&gt; Son œuvre est marquée par le questionnement du « with » (avec), du « being-with » heideggerien. Dans &lt;em&gt;La Communauté désoeuvrée&lt;/em&gt; (1986), il développe une pensée de la communauté qui refuse toute forme d'immanentisme ou de fusion : la communauté véritable n'est pas une substance commune, mais  &lt;a href="https://www.youtube.com/watch?v=fZK6pEAPxEw"  title="jean luc Nancy par Institut Humanités "&gt;l'exposition partagée &lt;/a&gt; de la singularité de chacun. Cette réflexion, en dialogue critique avec Blanchot et Bataille, a eu un retentissement considérable dans les débats contemporains sur la politique, la communauté et l'identité. &lt;/p&gt; &lt;p&gt; Dans &lt;em&gt;Corpus&lt;/em&gt; (1992) et &lt;em&gt;Noli me tangere&lt;/em&gt; (2003), il explore  &lt;a href="https://www.youtube.com/watch?v=1kCExw6Wp9k"  title="jean luc Nancy par Lacan TV "&gt;la philosophie du corps &lt;/a&gt; et du toucher comme modes fondamentaux de l'être-au-monde. Son essai sur le sens — &lt;em&gt;Le Sens du monde&lt;/em&gt; (1993) — aborde la question de la possibilité du sens dans un monde déserté par les transcendances. &lt;em&gt;L'Intrus&lt;/em&gt; (2000), bref récit autobiographique sur sa transplantation cardiaque, mêle réflexion philosophique et expérience personnelle de la maladie et de l'altérité. Son œuvre, immense et diverse, témoigne d'une pensée vivante et rigoureuse toujours en dialogue avec la littérature, l'art et la politique. &lt;/p&gt;  &lt;audio controls title="Jean luc Nancy par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/11472-06.02.2011-ITEMA_20267545-2011C16153E0003-ITE_00040439_RSCE-21.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;</t>
-        </is>
-      </c>
-      <c r="F130" s="54" t="inlineStr">
-        <is>
-          <t>0ONnn-EL0BA</t>
-        </is>
-      </c>
-      <c r="G130" s="56" t="inlineStr">
-        <is>
-          <t>"Jean-Luc Nancy, philosophe à l'intelligence sensible" par France Culture</t>
-        </is>
-      </c>
-      <c r="H130" s="62" t="inlineStr">
-        <is>
-          <t>https://www.laphilo.fr/pho/jlnancy-mini.webp</t>
-        </is>
-      </c>
-      <c r="J130" s="48" t="inlineStr">
-        <is>
-          <t>metaphysique ; politique</t>
-        </is>
-      </c>
-      <c r="K130" s="48" t="inlineStr">
-        <is>
-          <t>Post-structuralisme</t>
-        </is>
-      </c>
-      <c r="L130" s="48" t="inlineStr">
-        <is>
-          <t>philosophe français qui porta le « sens du monde », la communauté, le corps et le toucher.</t>
-        </is>
-      </c>
       <c r="N130" t="inlineStr">
         <is>
           <t xml:space="preserve">occident</t>
         </is>
       </c>
     </row>
-    <row r="131" ht="201" customHeight="1" s="49">
+    <row r="131" ht="164.25" customHeight="1" s="49">
       <c r="A131" s="54" t="n">
         <v>1940</v>
       </c>
-      <c r="B131" s="54" t="n">
+      <c r="B131" s="54" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="C131" s="54" t="inlineStr">
+        <is>
+          <t>1940 – 2021</t>
+        </is>
+      </c>
+      <c r="D131" s="55" t="inlineStr">
+        <is>
+          <t>Jean-Luc NANCY</t>
+        </is>
+      </c>
+      <c r="E131" s="62" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Jean-Luc_Nancy"  title=" Wikipedia"&gt;Jean-Luc NANCY&lt;/a&gt; était un philosophe français, agrégé de philosophie, il fut professeur à l'Université de Strasbourg jusqu'à sa retraite. Sa pensée, en dialogue constant avec Heidegger, Derrida et Lacoue-Labarthe — avec lequel il collabora étroitement — porte sur le « sens du monde », la communauté, le corps et le toucher. &lt;/p&gt; &lt;p&gt; Son œuvre est marquée par le questionnement du « with » (avec), du « being-with » heideggerien. Dans &lt;em&gt;La Communauté désoeuvrée&lt;/em&gt; (1986), il développe une pensée de la communauté qui refuse toute forme d'immanentisme ou de fusion : la communauté véritable n'est pas une substance commune, mais  &lt;a href="https://www.youtube.com/watch?v=fZK6pEAPxEw"  title="jean luc Nancy par Institut Humanités "&gt;l'exposition partagée &lt;/a&gt; de la singularité de chacun. Cette réflexion, en dialogue critique avec Blanchot et Bataille, a eu un retentissement considérable dans les débats contemporains sur la politique, la communauté et l'identité. &lt;/p&gt; &lt;p&gt; Dans &lt;em&gt;Corpus&lt;/em&gt; (1992) et &lt;em&gt;Noli me tangere&lt;/em&gt; (2003), il explore  &lt;a href="https://www.youtube.com/watch?v=1kCExw6Wp9k"  title="jean luc Nancy par Lacan TV "&gt;la philosophie du corps &lt;/a&gt; et du toucher comme modes fondamentaux de l'être-au-monde. Son essai sur le sens — &lt;em&gt;Le Sens du monde&lt;/em&gt; (1993) — aborde la question de la possibilité du sens dans un monde déserté par les transcendances. &lt;em&gt;L'Intrus&lt;/em&gt; (2000), bref récit autobiographique sur sa transplantation cardiaque, mêle réflexion philosophique et expérience personnelle de la maladie et de l'altérité. Son œuvre, immense et diverse, témoigne d'une pensée vivante et rigoureuse toujours en dialogue avec la littérature, l'art et la politique. &lt;/p&gt;  &lt;audio controls title="Jean luc Nancy par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/11472-06.02.2011-ITEMA_20267545-2011C16153E0003-ITE_00040439_RSCE-21.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;</t>
+        </is>
+      </c>
+      <c r="F131" s="54" t="inlineStr">
+        <is>
+          <t>0ONnn-EL0BA</t>
+        </is>
+      </c>
+      <c r="G131" s="56" t="inlineStr">
+        <is>
+          <t>"Jean-Luc Nancy, philosophe à l'intelligence sensible" par France Culture</t>
+        </is>
+      </c>
+      <c r="H131" s="62" t="inlineStr">
+        <is>
+          <t>https://www.laphilo.fr/pho/jlnancy-mini.webp</t>
+        </is>
+      </c>
+      <c r="J131" s="48" t="inlineStr">
+        <is>
+          <t>metaphysique ; politique</t>
+        </is>
+      </c>
+      <c r="K131" s="48" t="inlineStr">
+        <is>
+          <t>Post-structuralisme</t>
+        </is>
+      </c>
+      <c r="L131" s="48" t="inlineStr">
+        <is>
+          <t>philosophe français qui porta le « sens du monde », la communauté, le corps et le toucher.</t>
+        </is>
+      </c>
+      <c r="N131" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+    </row>
+    <row r="132" ht="201" customHeight="1" s="49">
+      <c r="A132" s="54" t="n">
+        <v>1940</v>
+      </c>
+      <c r="B132" s="54" t="n">
         <v>2007</v>
       </c>
-      <c r="C131" s="54" t="inlineStr">
+      <c r="C132" s="54" t="inlineStr">
         <is>
           <t>1940 – 2007</t>
         </is>
       </c>
-      <c r="D131" s="55" t="inlineStr">
+      <c r="D132" s="55" t="inlineStr">
         <is>
           <t>Philippe LACOUE-LABARTHE</t>
         </is>
       </c>
-      <c r="E131" s="62" t="inlineStr">
+      <c r="E132" s="62" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Philippe_Lacoue-Labarthe"  title=" Wikipedia"&gt;Philippe LACOUE-LABARTHE&lt;/a&gt; était un philosophe, critique littéraire, traducteur et théoricien français né à Tours et connu pour ses travaux sur la mimésis, le romantisme allemand, Hölderlin, Heidegger, Derrida et la relation entre esthétique et politique. Il a aussi beaucoup compté dans le milieu intellectuel de Strasbourg, où il a enseigné longtemps et travaillé avec Jean-Luc Nancy. &lt;/p&gt; &lt;p&gt; Son  &lt;a href="https://maitron.fr/lacoue-labarthe-philippe/"  title=" lacoue-labarthe par le maitron"&gt;œuvre interroge &lt;/a&gt; la façon dont l’art, la philosophie et la politique s’entrecroisent, notamment à travers la notion de mimésis et la critique de l’“esthétisation du politique”. Il a aussi travaillé sur le romantisme allemand et sur la réception de Hölderlin, qu’il considérait comme une figure majeure. &lt;/p&gt; &lt;p&gt; Parmi les livres souvent cités, on trouve Le Titre de la lettre avec Jean-Luc Nancy, L’Absolu littéraire, L’Imitation des modernes, La Fiction du politique et Heidegger, la politique du poème. Il a également traduit plusieurs auteurs allemands majeurs, dont Heidegger, Hölderlin, Nietzsche, Benjamin et Celan. &lt;/p&gt; &lt;p&gt; Sa pensée tourne autour de trois idées principales : - La représentation n’est jamais transparente : ce que nous montrons, racontons ou jouons n’est jamais la réalité elle-même, mais une forme, un masque, une imitation. - La littérature et le théâtre sont essentiels pour comprendre la philosophie, parce qu’ils révèlent ce que les concepts cachent ou simplifient.popups. - Le lien entre esthétique et politique est dangereux : il a beaucoup réfléchi à la manière dont l’art, les mythes et les images peuvent servir le politique, y compris dans des formes fascisantes. &lt;/p&gt; 
  &lt;audio controls title="les versions de philippe lacoue labarthe par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/16409-16.03.2007-ITEMA_20062386-2007C6409S0011-MEM_000036772_RF-21.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;  </t>
         </is>
       </c>
-      <c r="F131" s="54" t="inlineStr">
+      <c r="F132" s="54" t="inlineStr">
         <is>
           <t>CI6zYPSwsoY</t>
         </is>
       </c>
-      <c r="G131" s="56" t="inlineStr">
+      <c r="G132" s="56" t="inlineStr">
         <is>
           <t>voyage a tubingen par capuseen</t>
         </is>
       </c>
-      <c r="H131" s="62" t="inlineStr">
+      <c r="H132" s="62" t="inlineStr">
         <is>
           <t>https://www.laphilo.fr/pho/pllabarthe-mini.webp</t>
         </is>
       </c>
-      <c r="J131" s="48" t="inlineStr">
+      <c r="J132" s="48" t="inlineStr">
         <is>
           <t>politique ; epistemologie</t>
         </is>
       </c>
-      <c r="K131" s="48" t="inlineStr">
+      <c r="K132" s="48" t="inlineStr">
         <is>
           <t>Déconstructionnisme</t>
         </is>
       </c>
-      <c r="L131" s="85" t="inlineStr">
+      <c r="L132" s="85" t="inlineStr">
         <is>
           <t xml:space="preserve"> philosophe et théoricien français connu pour ses travaux sur la mimésis et le romantisme allemand.</t>
         </is>
       </c>
-      <c r="N131" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-    </row>
-    <row r="132" ht="209.25" customHeight="1" s="49">
-      <c r="A132" s="57" t="n">
+      <c r="N132" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+    </row>
+    <row r="133" ht="209.25" customHeight="1" s="49">
+      <c r="A133" s="57" t="n">
         <v>1941</v>
       </c>
-      <c r="B132" s="57" t="inlineStr">
+      <c r="B133" s="57" t="inlineStr">
         <is>
           <t>2019</t>
         </is>
       </c>
-      <c r="C132" s="57" t="inlineStr">
+      <c r="C133" s="57" t="inlineStr">
         <is>
           <t>1941 – 2019</t>
         </is>
       </c>
-      <c r="D132" s="58" t="inlineStr">
+      <c r="D133" s="58" t="inlineStr">
         <is>
           <t>François DELAPORTE</t>
         </is>
       </c>
-      <c r="E132" s="59" t="inlineStr">
+      <c r="E133" s="59" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Fran%C3%A7ois_Delaporte"  title=" Wikipedia"&gt;François DELAPORTE&lt;/a&gt; était un philosophe français spécialiste d'histoire et de philosophie des sciences médicales et biologiques, connu notamment pour ses travaux sur l'histoire des maladies et la philosophie de Georges Canguilhem. Professeur à l'Université de Picardie, il fut l'un des continuateurs de la tradition canguilhémienne d'histoire et philosophie des sciences en France, appliquant cette approche à l'histoire de la médecine et de la biologie. &lt;/p&gt; &lt;p&gt; Son œuvre la plus importante, &lt;em&gt;   &lt;a href="https://www.persee.fr/doc/bec_0373-6237_1993_num_151_2_450700_t1_0415_0000_001"  title=" le savoir sur la maladie par persée"&gt;Le Savoir de la maladie. &lt;/a&gt; Essai sur le choléra de 1832 à Paris&lt;/em&gt; (1990), est une analyse philosophique de l'épidémie de choléra qui ravagea Paris en 1832. Suivant la méthode de Canguilhem et Foucault, il montre comment la compréhension d'une maladie est toujours insérée dans un réseau de savoirs, de pratiques et de pouvoirs qui configurent sa signification médicale et sociale. Cette étude est un modèle du genre pour l'articulation entre histoire des sciences et analyse philosophique. &lt;/p&gt; &lt;p&gt; Il contribua également à faire connaître la pensée de Canguilhem, notamment à travers des études sur &lt;em&gt;Le Normal et le Pathologique&lt;/em&gt; et sur la philosophie biologique canguilhémienne. Ses travaux sur l'histoire des figures du visage, réunis dans &lt;em&gt;Figures de la médecine&lt;/em&gt; (2009), constituent une autre contribution originale à l'intersection de l'histoire de l'art médical et de la philosophie du corps. Delaporte incarne une tradition française de philosophie de la médecine d'une grande rigueur et d'une réelle originalité. &lt;/p&gt;   &lt;audio controls title="François Laporte le vie monastique, pensée en mouvement  par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/11983-19.12.2013-ITEMA_20563752-2013C18137S0353-25.m4a" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;  </t>
         </is>
       </c>
-      <c r="F132" s="57" t="inlineStr">
+      <c r="F133" s="57" t="inlineStr">
         <is>
           <t>Y3FnglRhPxs</t>
         </is>
       </c>
-      <c r="G132" s="59" t="inlineStr">
+      <c r="G133" s="59" t="inlineStr">
         <is>
           <t>"François DELAPORTE 2014" par Colin Guillaume</t>
         </is>
       </c>
-      <c r="H132" s="65" t="inlineStr">
+      <c r="H133" s="65" t="inlineStr">
         <is>
           <t>https://www.laphilo.fr/pho/fdelaporte-mini.webp</t>
         </is>
       </c>
-      <c r="J132" s="48" t="inlineStr">
+      <c r="J133" s="48" t="inlineStr">
         <is>
           <t>epistemologie</t>
         </is>
       </c>
-      <c r="K132" s="48" t="inlineStr">
+      <c r="K133" s="48" t="inlineStr">
         <is>
           <t>Constructivisme</t>
         </is>
       </c>
-      <c r="L132" s="48" t="inlineStr">
+      <c r="L133" s="48" t="inlineStr">
         <is>
           <t>philosophe français spécialiste de philosophie des sciences médicales et biologiques.</t>
         </is>
       </c>
-      <c r="N132" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-    </row>
-    <row r="133" ht="218.25" customHeight="1" s="49">
-      <c r="A133" s="54" t="n">
+      <c r="N133" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+    </row>
+    <row r="134" ht="218.25" customHeight="1" s="49">
+      <c r="A134" s="54" t="n">
         <v>1944</v>
       </c>
-      <c r="B133" s="54" t="inlineStr">
+      <c r="B134" s="54" t="inlineStr">
         <is>
           <t>2022</t>
         </is>
       </c>
-      <c r="C133" s="54" t="inlineStr">
+      <c r="C134" s="54" t="inlineStr">
         <is>
           <t>1944 – 2022</t>
         </is>
       </c>
-      <c r="D133" s="55" t="inlineStr">
+      <c r="D134" s="55" t="inlineStr">
         <is>
           <t>Dominique LECOURT</t>
         </is>
       </c>
-      <c r="E133" s="63" t="inlineStr">
+      <c r="E134" s="63" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Dominique_Lecourt" title=" Wikipedia"&gt;Dominique LECOURT&lt;/a&gt; était un philosophe français connu pour ses travaux en philosophie des sciences et pour avoir prolongé, de manière originale, l’héritage de Gaston Bachelard et de Georges Canguilhem. Sa philosophie se déploie autour de la philosophie des sciences, des rapports entre savoir et pouvoir, et d’une réflexion éthique et politique sur la technoscience. &lt;/p&gt; &lt;p&gt; Disciple de Bachelard, il défend un "rationalisme appliqué" : la raison scientifique n’est pas une abstraction pure, mais une activité qui se confronte à des obstacles, des erreurs, des idéologies, et qui progresse en les surmontant. Dans cet esprit, il insiste sur le rôle des   &lt;a href="https://www.youtube.com/watch?v=YyntmVUC1wE"  title=" D Lecourt par booksmag"&gt;"obstacles épistémologiques" &lt;/a&gt;  qui déroutent la recherche et qu’il faut analyser pour comprendre les progrès de la science. Il montre aussi que l’imagination n’est pas l’ennemie de la science : elle est indispensable à l’invention scientifique autant qu’à la rigueur des démonstrations. &lt;/p&gt; &lt;p&gt; Il cherche à contrer à la fois  l’"arrogance du scientisme"  et la technophobie ou le catastrophisme qui voient dans la technique uniquement une menace. Pour lui, la philosophie des sciences doit donner les moyens de penser la puissance des technosciences sans la sacraliser ni la diaboliser. Cela implique un dialogue étroit avec les scientifiques, mais aussi avec les juristes, médecins, sociologues, responsables politiques, pour éclairer les choix collectifs. &lt;/p&gt; &lt;p&gt; Il développe une conception de la liberté qui refuse aussi bien l’individualisme égoïste que le "moralisme libertaire". La liberté, pour lui, se joue dans le rapport aux savoirs et aux techniques : il s’agit d’en faire des instruments d’émancipation plutôt que de domination.&lt;/p&gt; &lt;p&gt; Parmi ses nombreux livres (plus d’une trentaine), on peut citer : -"Lyssenko, histoire réelle d’une "science prolétarienne" : analyse de la manipulation politique de la biologie en URSS.  - "L’Amérique entre la Bible et Darwin" : sur les tensions entre science et religion aux États‑Unis. - "Contre la peur" : proposition d’une éthique de la recherche qui affirme la valeur de l’esprit critique face aux discours alarmistes. -  &lt;a href="https://www.youtube.com/watch?v=3e2K5Ogywl4"  title=" De quoi le transhumanisme est-il le nom ? par Editions M-Editer"&gt;"Humain post‑humain" &lt;/a&gt;  : réflexion sur les promesses et les dangers du transhumanisme. &lt;/p&gt;   &lt;audio controls title="L'age de la peur par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/10075-03.03.2010-ITEMA_20218172-2010C6608S0062-NET_E99ABA70-9EA1-4399-B0F4-9460EA040C60-21.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;  </t>
         </is>
       </c>
-      <c r="F133" s="54" t="inlineStr">
+      <c r="F134" s="54" t="inlineStr">
         <is>
           <t>YyntmVUC1wE</t>
         </is>
       </c>
-      <c r="G133" s="56" t="inlineStr">
+      <c r="G134" s="56" t="inlineStr">
         <is>
           <t>"D Lecourt" par Booksmag</t>
         </is>
       </c>
-      <c r="H133" s="62" t="inlineStr">
+      <c r="H134" s="62" t="inlineStr">
         <is>
           <t>https://www.laphilo.fr/pho/lecourt-mini.webp</t>
         </is>
       </c>
-      <c r="J133" s="48" t="inlineStr">
+      <c r="J134" s="48" t="inlineStr">
         <is>
           <t>epistemologie</t>
         </is>
       </c>
-      <c r="K133" s="48" t="inlineStr">
+      <c r="K134" s="48" t="inlineStr">
         <is>
           <t>Marxisme ; Constructivisme</t>
         </is>
       </c>
-      <c r="L133" s="48" t="inlineStr">
+      <c r="L134" s="48" t="inlineStr">
         <is>
           <t>philosophe français connu pour ses travaux en philosophie des sciences.</t>
         </is>
       </c>
-      <c r="N133" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-    </row>
-    <row r="134" ht="157.5" customHeight="1" s="49">
-      <c r="A134" s="57" t="n">
+      <c r="N134" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+    </row>
+    <row r="135" ht="157.5" customHeight="1" s="49">
+      <c r="A135" s="57" t="n">
         <v>1945</v>
       </c>
-      <c r="B134" s="57" t="inlineStr">
+      <c r="B135" s="57" t="inlineStr">
         <is>
           <t>2006</t>
         </is>
       </c>
-      <c r="C134" s="57" t="inlineStr">
+      <c r="C135" s="57" t="inlineStr">
         <is>
           <t>1945 – 2006</t>
         </is>
       </c>
-      <c r="D134" s="58" t="inlineStr">
+      <c r="D135" s="58" t="inlineStr">
         <is>
           <t>Jean-Michel BERTHELOT</t>
         </is>
       </c>
-      <c r="E134" s="65" t="inlineStr">
+      <c r="E135" s="65" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Jean-Michel_Berthelot"  title=" Wikipedia"&gt;Jean-Michel BERTHELOT&lt;/a&gt; était un philosophe et sociologue français spécialiste d'épistémologie des sciences sociales. Professeur à l'Université de Paris IV-Sorbonne et à l'Université du Québec à Montréal, il contribua de manière décisive à la réflexion philosophique sur les fondements et les méthodes des sciences humaines et sociales. Son œuvre joint la rigueur épistémologique à une large culture philosophique et sociologique. &lt;/p&gt; &lt;p&gt; Son ouvrage principal, &lt;em&gt; &lt;a href="https://www.persee.fr/doc/sotra_0038-0296_1992_num_34_3_2605_t1_0388_0000_3"  title="l’intelligence du social par persée "&gt; L'Intelligence du social&lt;/a&gt; &lt;/em&gt; (1990), est une analyse approfondie des schèmes d'intelligibilité que les sciences sociales utilisent pour rendre compte de la réalité sociale : le schème causal, le schème fonctionnel, le schème structural, le schème herméneutique et d'autres modes d'explication. Berthelot montre que chaque paradigme sociologique privilégie un mode d'intelligibilité particulier, ce qui permet de comprendre à la fois leurs apports spécifiques et leurs limites. Ce livre constitue l'une des contributions les plus claires et les plus systématiques à la philosophie des sciences sociales en langue française. &lt;/p&gt; &lt;p&gt; Dans &lt;em&gt;Epistémologie des sciences sociales&lt;/em&gt; (2001, ouvrage collectif qu'il dirigea), il offrit un panorama complet des questions épistémologiques fondamentales que posent les sciences humaines et sociales : la causalité, la compréhension, la mesure, la modélisation, la réflexivité et les rapports entre science et valeurs. Ses travaux contribuèrent à établir l'épistémologie des sciences sociales comme une discipline à part entière dans le paysage universitaire français, en dialogue constant avec la philosophie des sciences anglophones et continentale. &lt;/p&gt;</t>
         </is>
       </c>
-      <c r="F134" s="57" t="inlineStr">
+      <c r="F135" s="57" t="inlineStr">
         <is>
           <t>032-iGqk37A</t>
         </is>
       </c>
-      <c r="G134" s="59" t="inlineStr">
+      <c r="G135" s="59" t="inlineStr">
         <is>
           <t>"JM BERTHELOT" par SFCR</t>
         </is>
       </c>
-      <c r="H134" s="65" t="inlineStr">
+      <c r="H135" s="65" t="inlineStr">
         <is>
           <t>https://www.laphilo.fr/pho/jmberthelot-mini.webp</t>
         </is>
       </c>
-      <c r="J134" s="48" t="inlineStr">
+      <c r="J135" s="48" t="inlineStr">
         <is>
           <t>epistemologie</t>
         </is>
       </c>
-      <c r="K134" s="48" t="inlineStr">
+      <c r="K135" s="48" t="inlineStr">
         <is>
           <t>Constructivisme</t>
         </is>
       </c>
-      <c r="L134" s="48" t="inlineStr">
+      <c r="L135" s="48" t="inlineStr">
         <is>
           <t>philosophe et sociologue français spécialiste d'épistémologie des sciences sociales.</t>
         </is>
       </c>
-      <c r="N134" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-    </row>
-    <row r="135" ht="166.5" customHeight="1" s="49">
-      <c r="A135" s="54" t="n">
+      <c r="N135" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+    </row>
+    <row r="136" ht="166.5" customHeight="1" s="49">
+      <c r="A136" s="54" t="n">
         <v>1946</v>
       </c>
-      <c r="B135" s="54" t="inlineStr">
+      <c r="B136" s="54" t="inlineStr">
         <is>
           <t>2010</t>
         </is>
       </c>
-      <c r="C135" s="54" t="inlineStr">
+      <c r="C136" s="54" t="inlineStr">
         <is>
           <t>1946 – 2010</t>
         </is>
       </c>
-      <c r="D135" s="55" t="inlineStr">
+      <c r="D136" s="55" t="inlineStr">
         <is>
           <t>Daniel BENSAÏD</t>
         </is>
       </c>
-      <c r="E135" s="62" t="inlineStr">
+      <c r="E136" s="62" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Daniel_Bensa%C3%AFd"  title=" Wikipedia"&gt;Daniel BENSAÏD&lt;/a&gt; était un philosophe français marxiste, l'un des intellectuels les plus importants de la gauche radicale française de son époque. Né à Paris dans une famille juive d'origine algérienne, il fut l'un des leaders de la révolte étudiante de mai 1968 à Paris-Nanterre aux côtés de Daniel Cohn-Bendit. Professeur de philosophie à l'Université Paris VIII-Saint-Denis, il fut membre dirigeant de la Ligue communiste révolutionnaire (LCR) et de son successeur le Nouveau Parti Anticapitaliste (NPA). &lt;/p&gt; &lt;p&gt; Sa pensée philosophique chercha à renouveler le marxisme en le débarrassant des &lt;a href="https://www.youtube.com/watch?v=uxBvxfRI2CE"  title="la privatisation du monde par bibou11slalala "&gt; simplifications téléologiques &lt;/a&gt; et en l'ouvrant à des problématiques nouvelles. Dans &lt;em&gt;Marx l'intempestif&lt;/em&gt; (1995), il défend un Marx débarrassé du déterminisme historique et de la philosophie du progrès, un Marx « intempestif » qui pense la politique comme art du possible et de l'impossible, en dialogue avec Blaise Pascal et Walter Benjamin. Ce livre renouvela profondément la  &lt;a href="https://www.youtube.com/watch?v=is8Ya038-Q4"  title="l’héritage de Marx par socialtram "&gt; lecture de Marx &lt;/a&gt; dans la gauche française. &lt;/p&gt; &lt;p&gt; Dans &lt;em&gt;Le Pari mélancolique&lt;/em&gt; (1997) et &lt;em&gt;Résistances&lt;/em&gt; (2001), il développe une philosophie de l'engagement politique nourrie par la mélancolie des défaites mais portée par une fidélité irréductible à l'émancipation. Sa réflexion sur les rapports entre philosophie et politique, entre utopie et stratégie, constitue l'une des contributions les plus originales à la pensée marxiste contemporaine. Polémiste redoutable et pédagogue exigeant, il laissa une empreinte profonde sur plusieurs générations de militants et d'intellectuels de gauche. &lt;/p&gt;  &lt;audio controls title="Daniel Bensaid  par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/10075-11.12.2006-ITEMA_20049670-2006C6608S0221-MEM_000033324_RF-21.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt; </t>
         </is>
       </c>
-      <c r="F135" s="54" t="inlineStr">
+      <c r="F136" s="54" t="inlineStr">
         <is>
           <t>xFJLPfAwApo</t>
         </is>
       </c>
-      <c r="G135" s="56" t="inlineStr">
+      <c r="G136" s="56" t="inlineStr">
         <is>
           <t>"Daniel Bensaïd sur l'idée du communisme" par Videos Politiques</t>
         </is>
       </c>
-      <c r="H135" s="62" t="inlineStr">
+      <c r="H136" s="62" t="inlineStr">
         <is>
           <t>https://www.laphilo.fr/pho/bensaid-mini.webp</t>
         </is>
       </c>
-      <c r="J135" s="48" t="inlineStr">
+      <c r="J136" s="48" t="inlineStr">
         <is>
           <t>politique</t>
         </is>
       </c>
-      <c r="K135" s="48" t="inlineStr">
+      <c r="K136" s="48" t="inlineStr">
         <is>
           <t>Marxisme</t>
         </is>
       </c>
-      <c r="L135" s="48" t="inlineStr">
+      <c r="L136" s="48" t="inlineStr">
         <is>
           <t>philosophe français marxiste, intellectuel important de la gauche radicale française.</t>
         </is>
       </c>
-      <c r="M135" t="inlineStr">
+      <c r="M136" t="inlineStr">
         <is>
           <t xml:space="preserve">juive</t>
         </is>
       </c>
-      <c r="N135" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-    </row>
-    <row r="136" ht="210" customHeight="1" s="49">
-      <c r="A136" s="57" t="n">
+      <c r="N136" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+    </row>
+    <row r="137" ht="210" customHeight="1" s="49">
+      <c r="A137" s="57" t="n">
         <v>1947</v>
       </c>
-      <c r="B136" s="57" t="inlineStr">
+      <c r="B137" s="57" t="inlineStr">
         <is>
           <t>2022</t>
         </is>
       </c>
-      <c r="C136" s="57" t="inlineStr">
+      <c r="C137" s="57" t="inlineStr">
         <is>
           <t>1947 - 2022</t>
         </is>
       </c>
-      <c r="D136" s="58" t="inlineStr">
+      <c r="D137" s="58" t="inlineStr">
         <is>
           <t>Bruno LATOUR</t>
         </is>
       </c>
-      <c r="E136" s="59" t="inlineStr">
+      <c r="E137" s="59" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Bruno_Latour"  title=" Wikipedia"&gt;Bruno LATOUR&lt;/a&gt;  est un sociologue, anthropologue et philosophe français connu pour ses travaux sur la sociologie des sciences, la philosophie des sciences et l'anthropologie des modernes.&lt;/p&gt; &lt;p&gt; L'un des concepts clés développés par Latour est celui de l'acteur-réseau, également connu sous le nom de &lt;a href="https://fr.wikipedia.org/wiki/Th%C3%A9orie_de_l%27acteur-r%C3%A9seau"  title="Théorie de l'acteur-réseau par Wikipedia "&gt; théorie de l'acteur-réseau (ANT) &lt;/a&gt;. Selon cette approche, les acteurs humains et non humains sont considérés comme des "actants" qui agissent en collaboration pour produire des réalités sociales complexes. L'ANT remet en question la distinction traditionnelle entre les sujets humains et les objets inanimés, soulignant plutôt les relations et les interactions entre eux. &lt;/p&gt; &lt;p&gt; Il s'est  intéressé aux enjeux environnementaux et a contribué au développement de l'écologie politique. Il a souligné l'importance de prendre en compte les dimensions politiques et sociales dans la compréhension des questions écologiques et climatiques. Son livre &lt;a href="http://www.bruno-latour.fr/sites/default/files/uploads/TELERAMA.pdf"  title="Nous n'avons jamais été moderne par Bruno-Latour "&gt; "Nous n'avons jamais été modernes" &lt;/a&gt; (1991) remet en question la distinction entre nature et culture, mettant en lumière les façons dont les sciences et les technologies façonnent notre compréhension du monde. &lt;/p&gt; &lt;p&gt; En plus de ses travaux académiques, Bruno Latour a également participé à des &lt;a href="https://profondeurdechamps.com/2012/10/19/entretien-avec-bruno-latour-12-lart-et-la-science/"  title="L'art et la science par Profondeurdechamps "&gt; projets artistiques &lt;/a&gt; et curatoriaux. Il a collaboré avec des artistes contemporains et a contribué à des expositions d'art qui explorent les thèmes de la science, de la technologie et de l'environnement.&lt;/p&gt; &lt;audio controls title="Introduction à la pensée de Bruno LATOUR par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/22676-06.05.2022-ITEMA_23017705-2022F45096S0126-22.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt; </t>
         </is>
       </c>
-      <c r="F136" s="57" t="inlineStr">
+      <c r="F137" s="57" t="inlineStr">
         <is>
           <t>BqM-sk_ZLeU</t>
         </is>
       </c>
-      <c r="G136" s="65" t="inlineStr">
+      <c r="G137" s="65" t="inlineStr">
         <is>
           <t>"Ce virus est là pour nous préparer au nouveau régime climatique" par France Culture</t>
         </is>
       </c>
-      <c r="H136" s="65" t="inlineStr">
+      <c r="H137" s="65" t="inlineStr">
         <is>
           <t>https://www.laphilo.fr/pho/latour-mini.webp</t>
         </is>
       </c>
-      <c r="J136" s="48" t="inlineStr">
+      <c r="J137" s="48" t="inlineStr">
         <is>
           <t>epistemologie ; politique</t>
         </is>
       </c>
-      <c r="K136" s="48" t="inlineStr">
+      <c r="K137" s="48" t="inlineStr">
         <is>
           <t>Constructivisme</t>
         </is>
       </c>
-      <c r="L136" s="48" t="inlineStr">
+      <c r="L137" s="48" t="inlineStr">
         <is>
           <t>philosophe français inscrit dans le mouvement du Nouveau Réalisme.</t>
         </is>
       </c>
-      <c r="N136" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-    </row>
-    <row r="137" ht="166.5" customHeight="1" s="49">
-      <c r="A137" s="54" t="n">
+      <c r="N137" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+    </row>
+    <row r="138" ht="166.5" customHeight="1" s="49">
+      <c r="A138" s="54" t="n">
         <v>1949</v>
       </c>
-      <c r="B137" s="54" t="inlineStr">
+      <c r="B138" s="54" t="inlineStr">
         <is>
           <t>2017</t>
         </is>
       </c>
-      <c r="C137" s="54" t="inlineStr">
+      <c r="C138" s="54" t="inlineStr">
         <is>
           <t>1949 – 2017</t>
         </is>
       </c>
-      <c r="D137" s="55" t="inlineStr">
+      <c r="D138" s="55" t="inlineStr">
         <is>
           <t>Robert DAMIEN</t>
         </is>
       </c>
-      <c r="E137" s="56" t="inlineStr">
+      <c r="E138" s="56" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Robert_Damien"  title=" Wikipedia"&gt;Robert DAMIEN&lt;/a&gt;   était un philosophe français  spécialiste de l'autorité politique et des tensions démocratiques, connu pour sa réhabilitation éthique de l'autorité comme principe d'élévation collective. Il incarna un rationalisme républicain franc et dialogique. &lt;/p&gt; &lt;p&gt; Il réfléchit aux tensions indépassables de la démocratie : décision vs connaissance, immanence vs autorité, pluralisme vs unité. L'autorité n'est pas abus ou force, mais "augmentation" (étymologiquement) : réciproque, fraternelle, légitime si elle élève sans domination, en rendant des comptes publics. Il prône un "pluralisme cohérent" (inspiré de Bachelard), un cogito relationnel et un État stratège sous souverainetés plurielles, face au déclin des absolus. &lt;/p&gt; &lt;p&gt; Joueur et &lt;a href="https://www.dailymotion.com/video/x18br7c" title="Robert Damien : de la figure de l'entraîneur à celle de Mandela par mediapart"&gt;entraîneur de rugby &lt;/a&gt; au CS Lons-le-Saunier, il intégrait le sport comme modèle philosophique du collectif et de l'autorité républicaine. Le rugby incarne pour lui une coopération interdépendante où la diversité des talents (puissants et habiles) fusionne en "Nous" : circulation du ballon prime sur l'individualisme, reliant partenaires contre adversaire. Pas de "joueurs isolés", mais des équipes où le "jeu sans ballon" (replacements, soutiens obscurs) assure continuité, révélant un "Moi nouveau" via le collectif. Dans "Activité physique et exercices spirituels" paru en 2005, le sport n'est pas idéologique mais matrice de fraternité : effort charnel révèle puissances collectives, appliquées à politique et bibliothèques (pluralité ordonnée). &lt;/p&gt;</t>
         </is>
       </c>
-      <c r="F137" s="54" t="inlineStr">
+      <c r="F138" s="54" t="inlineStr">
         <is>
           <t>iBriZ4Lhzfg</t>
         </is>
       </c>
-      <c r="G137" s="56" t="inlineStr">
+      <c r="G138" s="56" t="inlineStr">
         <is>
           <t>"robert damien les trois qualites de l autorite" par Sylvie Formero</t>
         </is>
       </c>
-      <c r="H137" s="62" t="inlineStr">
+      <c r="H138" s="62" t="inlineStr">
         <is>
           <t>https://www.laphilo.fr/pho/rdamien-mini.webp</t>
         </is>
       </c>
-      <c r="J137" s="48" t="inlineStr">
+      <c r="J138" s="48" t="inlineStr">
         <is>
           <t>politique ; epistemologie</t>
         </is>
       </c>
-      <c r="K137" s="48" t="inlineStr">
+      <c r="K138" s="48" t="inlineStr">
         <is>
           <t>Herméneutique</t>
         </is>
       </c>
-      <c r="L137" s="48" t="inlineStr">
+      <c r="L138" s="48" t="inlineStr">
         <is>
           <t>religieux français spécialiste de l'autorité politique &amp; des tensions démocratiques.</t>
         </is>
       </c>
-      <c r="N137" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-    </row>
-    <row r="138" ht="210.75" customHeight="1" s="49">
-      <c r="A138" s="57" t="n">
+      <c r="N138" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+    </row>
+    <row r="139" ht="210.75" customHeight="1" s="49">
+      <c r="A139" s="57" t="n">
         <v>1950</v>
       </c>
-      <c r="B138" s="57" t="inlineStr">
+      <c r="B139" s="57" t="inlineStr">
         <is>
           <t>2022</t>
         </is>
       </c>
-      <c r="C138" s="57" t="inlineStr">
+      <c r="C139" s="57" t="inlineStr">
         <is>
           <t>1950 – 2022</t>
         </is>
       </c>
-      <c r="D138" s="58" t="inlineStr">
+      <c r="D139" s="58" t="inlineStr">
         <is>
           <t>Catherine COLLIOT-THELENE</t>
         </is>
       </c>
-      <c r="E138" s="65" t="inlineStr">
+      <c r="E139" s="65" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Catherine_Colliot-Th%C3%A9l%C3%A8ne" title=" Wikipedia"&gt;Catherine COLLIOT-THELENE&lt;/a&gt; était une philosophe française  majeure de la philosophie politique contemporaine, spécialiste de Max Weber et penseuse des droits, de la démocratie et de la propriété dans un cadre cosmopolitique. Membre de l’Institut universitaire de France, elle est reconnue comme une référence internationale des études wébériennes. &lt;/p&gt; &lt;p&gt; Son travail se situe au croisement de la philosophie politique et des sciences sociales, avec trois pôles principaux :  &lt;a href="https://www.youtube.com/watch?v=krUYFtq9Jww" title="Max Weber et la violence légitime de l’état par France Culture"&gt;Max Weber, la démocratie et les droits, &lt;/a&gt;  la propriété et le cosmopolitisme.  Elle traduit et commente plusieurs textes de Weber, notamment Le Savant et le politique et Les Communautés, en montrant en détail ses concepts de rationalisation, de désenchantement et de domination. &lt;/p&gt; &lt;p&gt; À partir des années 2000, elle se concentre sur les droits subjectifs, leur articulation avec l’individualisme contemporain et la transformation des rapports entre pouvoirs politiques et économiques. Elle insiste sur la nécessité de penser la normativité (ce qui doit être) à partir d’une analyse précise des structures sociales réelles, d’où son dialogue constant avec le droit, l’histoire et la sociologie. &lt;/p&gt; &lt;p&gt; Dans "La Démocratie sans “demos”  paru en 2011, elle remet en question l’identification classique entre "peuple" et "démocratie". Elle critique la superposition entre souveraineté du peuple et souveraineté territoriale de l’État, qui conduit selon elle à des versions exclusives de la démocratie. &lt;a href="https://www.youtube.com/watch?v=ps2ixtEpgYI" title="la democratie c’est le droit de resistance par Journal l’Humanitét"&gt;Sa philosophie cherche &lt;/a&gt;  une démocratie fondée sur des droits universalisables et sur la participation de tous les sujets, plutôt que sur l’appartenance à une communauté nationale préconstituée. &lt;/p&gt; &lt;p&gt; Elle refuse la séparation entre théorie pure et monde social : pour elle, la philosophie politique doit dialoguer avec les sciences sociales pour produire une critique efficace des institutions et des inégalités. Elle a accompagné, sans posture militante classique mais avec une forte implication intellectuelle, les luttes pour les droits des femmes, des exclus et des étrangers, en cherchant à fournir des outils conceptuels pour penser l’égalité aujourd’hui. &lt;/p&gt; 
  &lt;audio controls title="Les défis juridiques de la migration : existe-t-il un droit à la libre circulation ? par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/21447-09.02.2022-ITEMA_22927630-2022C27677S0040-21.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;</t>
         </is>
       </c>
-      <c r="F138" s="57" t="inlineStr">
+      <c r="F139" s="57" t="inlineStr">
         <is>
           <t>g_YhgkqNE98</t>
         </is>
       </c>
-      <c r="G138" s="59" t="inlineStr">
+      <c r="G139" s="59" t="inlineStr">
         <is>
           <t>"La démocratie des droits : de Weber à Kant", entretien avec Catherine Colliot-Thélène" par Politika</t>
         </is>
       </c>
-      <c r="H138" s="65" t="inlineStr">
+      <c r="H139" s="65" t="inlineStr">
         <is>
           <t>https://www.laphilo.fr/pho/thelene-mini.webp</t>
         </is>
       </c>
-      <c r="J138" s="48" t="inlineStr">
+      <c r="J139" s="48" t="inlineStr">
         <is>
           <t>politique</t>
         </is>
       </c>
-      <c r="K138" s="48" t="inlineStr">
+      <c r="K139" s="48" t="inlineStr">
         <is>
           <t>Libéralisme</t>
         </is>
       </c>
-      <c r="L138" s="48" t="inlineStr">
+      <c r="L139" s="48" t="inlineStr">
         <is>
           <t>philosophe française majeure de la philosophie politique contemporaine.</t>
         </is>
       </c>
-      <c r="M138" t="inlineStr">
+      <c r="M139" t="inlineStr">
         <is>
           <t xml:space="preserve">femme</t>
         </is>
       </c>
-      <c r="N138" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-    </row>
-    <row r="139" ht="171.75" customHeight="1" s="49">
-      <c r="A139" s="54" t="n">
+      <c r="N139" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+    </row>
+    <row r="140" ht="171.75" customHeight="1" s="49">
+      <c r="A140" s="54" t="n">
         <v>1952</v>
       </c>
-      <c r="B139" s="54" t="inlineStr">
+      <c r="B140" s="54" t="inlineStr">
         <is>
           <t>2020</t>
         </is>
       </c>
-      <c r="C139" s="54" t="inlineStr">
+      <c r="C140" s="54" t="inlineStr">
         <is>
           <t>1952 – 2020</t>
         </is>
       </c>
-      <c r="D139" s="55" t="inlineStr">
+      <c r="D140" s="55" t="inlineStr">
         <is>
           <t xml:space="preserve">Bernard STIEGLER</t>
         </is>
       </c>
-      <c r="E139" s="56" t="inlineStr">
+      <c r="E140" s="56" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Bernard_Stiegler"  title=" Wikipedia"&gt;Bernard STIEGLER&lt;/a&gt; était un philosophe français, l'une des figures les plus originales et les plus influentes de la philosophie française. Né à Villebon-sur-Yvette, son parcours intellectuel fut marqué par une expérience singulière : il prépara sa thèse en philosophie pendant les cinq années qu'il passa en prison (1978-1983), condamné pour braquages. Docteur en philosophie sous la direction de Jacques Derrida, il fut directeur du département du développement culturel du Centre Pompidou puis directeur de l'Institut de Recherche et d'Innovation (IRI). &lt;/p&gt; &lt;p&gt; Son œuvre maîtresse, la trilogie &lt;em&gt;&lt;a href="https://www.youtube.com/watch?v=nwmOFXzCJUg" title="Bernard Stiegler a propos de la technique par Adrien Payet"&gt;La Technique et le Temps&lt;/a&gt; &lt;/em&gt; (1994-2001), constitue l'une des analyses philosophiques les plus ambitieuses de la technique et de ses effets sur la temporalité humaine. S'appuyant sur Simondon, Derrida et Heidegger, il y défend la thèse que l'être humain est fondamentalement un être technique : c'est par la technique — les « rétentions tertiaires », les objets qui externalisent la mémoire — que l'humain se constitue comme tel. La technique n'est pas un simple outil mais la condition même de la temporalité humaine et de la transmission culturelle. &lt;/p&gt; &lt;p&gt; Dans ses ouvrages ultérieurs — &lt;em&gt;De la misère symbolique&lt;/em&gt; (2004), &lt;em&gt;Prendre soin&lt;/em&gt; (2008), &lt;em&gt;États de choc&lt;/em&gt; (2012) — il  &lt;a href="https://www.youtube.com/watch?v=IOei5Kb1cQI" title="Bernard Stiegler par France 24"&gt;développa une critique &lt;/a&gt;  de l'économie de l'attention et du capitalisme des plateformes numériques, montrant comment ceux-ci détruisent les « savoirs faire » et « savoirs vivre » qui constituent le tissu de l'existence humaine. Sa pensée, nourrie d'une profonde inquiétude sur les effets destructeurs des industries culturelles et numériques, propose une pharmacologie de la technique : la technique est un pharmakon, à la fois poison et remède. &lt;/p&gt;  &lt;audio controls title="Bernard Stiegler : je reflechis au rapport entre technique et le mal  par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/13915-05.11.2017-ITEMA_21460251-5.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;</t>
         </is>
       </c>
-      <c r="F139" s="54" t="inlineStr">
+      <c r="F140" s="54" t="inlineStr">
         <is>
           <t>Q10Ski-xusk</t>
         </is>
       </c>
-      <c r="G139" s="56" t="inlineStr">
+      <c r="G140" s="56" t="inlineStr">
         <is>
           <t>"Mémoire et personnalité - Bernard Stiegler" par Obserbatoire B2V des Mémoires</t>
         </is>
       </c>
-      <c r="H139" s="62" t="inlineStr">
+      <c r="H140" s="62" t="inlineStr">
         <is>
           <t>https://www.laphilo.fr/pho/bstiegler-mini.webp</t>
         </is>
       </c>
-      <c r="J139" s="48" t="inlineStr">
+      <c r="J140" s="48" t="inlineStr">
         <is>
           <t>politique ; epistemologie</t>
         </is>
       </c>
-      <c r="K139" s="48" t="inlineStr">
+      <c r="K140" s="48" t="inlineStr">
         <is>
           <t>Post-structuralisme</t>
         </is>
       </c>
-      <c r="L139" s="48" t="inlineStr">
+      <c r="L140" s="48" t="inlineStr">
         <is>
           <t>philosophe français qui fit une analyse ambitieuse de la technique et de ses effets.</t>
         </is>
       </c>
-      <c r="N139" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-    </row>
-    <row r="140" ht="135.75" customHeight="1" s="49">
-      <c r="A140" s="57" t="n">
+      <c r="N140" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+    </row>
+    <row r="141" ht="135.75" customHeight="1" s="49">
+      <c r="A141" s="57" t="n">
         <v>1959</v>
       </c>
-      <c r="B140" s="57" t="inlineStr">
+      <c r="B141" s="57" t="inlineStr">
         <is>
           <t>2014</t>
         </is>
       </c>
-      <c r="C140" s="57" t="inlineStr">
+      <c r="C141" s="57" t="inlineStr">
         <is>
           <t>1959 – 2014</t>
         </is>
       </c>
-      <c r="D140" s="58" t="inlineStr">
+      <c r="D141" s="58" t="inlineStr">
         <is>
           <t>Bernard MABILLE</t>
         </is>
       </c>
-      <c r="E140" s="65" t="inlineStr">
+      <c r="E141" s="65" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Bernard_Mabille_(philosophe)"  style="color:#6A142A"  title=" Wikipedia"&gt;Bernard MABILLE&lt;/a&gt; était un philosophe français spécialiste de dialectique et de philosophie hégélienne, ainsi que de métaphysique contemporaine. Agrégé de philosophie et professeur à l'Université Paris IV-Sorbonne, il fut l'un des meilleurs connaisseurs français de Hegel et contribua de manière significative au renouvellement des études hégéliennes en France dans les dernières décennies du XXe siècle. &lt;/p&gt; &lt;p&gt; Sa thèse principale, &lt;em&gt;Hegel : l'épreuve de la contingence&lt;/em&gt; (1999), est une lecture originale de la philosophie hégélienne à la lumière de la problématique de la contingence. Contre les lectures qui réduisent Hegel à un penseur du nécessaire et du rationnel, Mabille montre que la contingence est au cœur même du système hégélien et que la dialectique est précisément la méthode qui permet de penser le passage du contingent au nécessaire sans l'éliminer. Cette relecture contribua à ouvrir la philosophie hégélienne à des problématiques contemporaines. &lt;/p&gt; &lt;p&gt; Dans ses travaux sur la métaphysique et la dialectique, Mabille s'intéressa également aux rapports entre la philosophie hégélienne et la phénoménologie française, notamment Merleau-Ponty et Henry. Son enseignement à la Sorbonne forma plusieurs générations d'étudiants à la rigueur de la pensée dialectique. Sa disparition prématurée priva la philosophie française d'un penseur rigoureux dont l'œuvre, bien que de volume limité, témoigne d'une lecture profonde et originale de l'idéalisme allemand et de ses prolongements contemporains. &lt;/p&gt;</t>
         </is>
       </c>
-      <c r="F140" s="57" t="inlineStr">
+      <c r="F141" s="57" t="inlineStr">
         <is>
           <t>2ZxXXD2lk_Q</t>
         </is>
       </c>
-      <c r="G140" s="59" t="inlineStr">
+      <c r="G141" s="59" t="inlineStr">
         <is>
           <t>Bernard MABILLE par La Compagnie des indes TV</t>
         </is>
       </c>
-      <c r="H140" s="65" t="inlineStr">
+      <c r="H141" s="65" t="inlineStr">
         <is>
           <t>https://www.laphilo.fr/pho/bnabille-mini.webp</t>
         </is>
       </c>
-      <c r="J140" s="48" t="inlineStr">
+      <c r="J141" s="48" t="inlineStr">
         <is>
           <t>metaphysique</t>
         </is>
       </c>
-      <c r="K140" s="48" t="inlineStr">
+      <c r="K141" s="48" t="inlineStr">
         <is>
           <t>Idéalisme allemand</t>
         </is>
       </c>
-      <c r="L140" s="48" t="inlineStr">
+      <c r="L141" s="48" t="inlineStr">
         <is>
           <t>philosophe français spécialiste de dialectique et de philosophie hégélienne.</t>
         </is>
       </c>
-      <c r="N140" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-    </row>
-    <row r="141" ht="176.25" customHeight="1" s="49">
-      <c r="A141" s="47" t="n">
+      <c r="N141" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+    </row>
+    <row r="142" ht="176.25" customHeight="1" s="49">
+      <c r="A142" s="47" t="n">
         <v>1964</v>
       </c>
-      <c r="B141" s="47" t="n">
+      <c r="B142" s="47" t="n">
         <v>2017</v>
       </c>
-      <c r="C141" s="47" t="inlineStr">
+      <c r="C142" s="47" t="inlineStr">
         <is>
           <t>1964 – 2017</t>
         </is>
       </c>
-      <c r="D141" s="47" t="inlineStr">
+      <c r="D142" s="47" t="inlineStr">
         <is>
           <t>Anne DUFOURMANTELLE</t>
         </is>
       </c>
-      <c r="E141" s="85" t="inlineStr">
+      <c r="E142" s="85" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Anne_Dufourmantelle"  title=" Wikipedia"&gt;Anne DUFOURMANTELLE&lt;/a&gt; était une philosophe et psychanalyste française dont l’œuvre, marquée par une grande finesse d’analyse, explore la vulnérabilité humaine, le risque, le secret et l’hospitalité. Bien qu’elle ne soit pas une théoricienne du &lt;a href="https://fr.wikipedia.org/wiki/Constructivisme_(%C3%A9pist%C3%A9mologie)"  title="Constructivisme par Wikipedia"&gt;« constructivisme »&lt;/a&gt;  au sens politique ou académique strict, sa pensée entre en résonance avec une réflexion sur la manière dont nous bâtissons notre rapport au monde et à l’autre. &lt;/p&gt; &lt;p&gt; Son concept d'&lt;a href="https://www.umc.org/fr/content/what-is-radical-hospitality"  title="Qu’est ce que l’hospitalité radicale par umc"&gt;« hospitalité radicale », &lt;/a&gt; nourri de ses travaux avec Jacques Derrida, propose d'accueillir l'inconnu sans conditions, voyant dans cette ouverture une forme de résistance à la fermeture du monde. Elle invite à une éthique de la rencontre où la vulnérabilité n'est pas un défaut, mais un espace de croissance mutuelle qui défie les normes sociales établies. &lt;/p&gt; &lt;p&gt; '&lt;a href="https://www.youtube.com/watch?v=QAlsJD3IAs0"  title="L’envers du feu par Librairie mollat"&gt;Dans des ouvrages &lt;/a&gt; comme Éloge du risque, elle explore la tension entre la sécurité et l'aventure de vivre, encourageant une liberté de penser et d'aimer qui dépasse les discours ambiants. Elle percevait la psychanalyse et la philosophie comme des outils pour « traquer » les mutations invisibles de notre époque et redonner du sens à nos vies intérieures. &lt;/p&gt; &lt;p&gt; Sa disparition brutale en 2017, alors qu'elle portait secours à des enfants en mer, a été perçue comme l'incarnation ultime de son engagement philosophique : une éthique en actes où le souci de l'autre devient une responsabilité immédiate. Son héritage intellectuel reste une source d'inspiration pour ceux qui cherchent à penser la douceur, l'enfance et la résistance dans un monde en mutation. &lt;/p&gt; 
 &lt;audio controls title="Anne Dufourmantelle par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/11189-07.11.2011-ITEMA_20320628-2011C15000E0211-ITE_00045291_RSCE-21.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;
 </t>
         </is>
       </c>
-      <c r="F141" s="47" t="inlineStr">
+      <c r="F142" s="47" t="inlineStr">
         <is>
           <t>PCCcMUiurLo</t>
         </is>
       </c>
-      <c r="G141" s="48" t="inlineStr">
+      <c r="G142" s="48" t="inlineStr">
         <is>
           <t>Hommage à Anne DUFOURMANTELLE par PhiloCloud</t>
         </is>
       </c>
-      <c r="H141" s="48" t="inlineStr">
+      <c r="H142" s="48" t="inlineStr">
         <is>
           <t>https://www.laphilo.fr/pho/adufourmantelle-mini.webp</t>
         </is>
       </c>
-      <c r="J141" s="48" t="inlineStr">
+      <c r="J142" s="48" t="inlineStr">
         <is>
           <t>ethique ; esthetique</t>
         </is>
       </c>
-      <c r="K141" s="48" t="inlineStr">
+      <c r="K142" s="48" t="inlineStr">
         <is>
           <t>Phénoménologie</t>
         </is>
       </c>
-      <c r="L141" s="48" t="inlineStr">
+      <c r="L142" s="48" t="inlineStr">
         <is>
           <t>philosophe et psychanalyste française fine analyste, qui explore la vulnérabilité humaine.</t>
         </is>
       </c>
-      <c r="M141" t="inlineStr">
+      <c r="M142" t="inlineStr">
         <is>
           <t xml:space="preserve">femme</t>
-        </is>
-      </c>
-      <c r="N141" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-    </row>
-    <row r="142" ht="255.75" customHeight="1" s="49">
-      <c r="A142" s="47">
-        <v>1934</v>
-      </c>
-      <c r="B142" s="47">
-        <v>1994</v>
-      </c>
-      <c r="C142" s="47" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1934 - 1994</t>
-        </is>
-      </c>
-      <c r="D142" s="47" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Sarah KOFMAN</t>
-        </is>
-      </c>
-      <c r="E142" s="47" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Sarah_Kofman"  title=" Wikipedia"&gt;Sarah KOFMAN&lt;/a&gt; (1934-1994) est une philosophe française, née à Paris dans une famille juive d'origine polonaise. En 1942, son père, rabbin, fut arrêté lors de la rafle du Vél' d'Hiv et assassiné à Auschwitz. Cachée pendant la guerre, elle raconta bien plus tard cette enfance dans &lt;em&gt;Rue Ordener, rue Labat&lt;/em&gt; (1994), un récit bouleversant.&lt;/p&gt; &lt;p&gt;Professeure à la Sorbonne, proche de Jacques Derrida, elle consacra une grande partie de son œuvre à des lectures minutieuses de Nietzsche et de Freud, dont elle montre les ambiguïtés et les contradictions. Dans &lt;em&gt;L'Énigme de la femme&lt;/em&gt; (1980), elle analyse la manière dont Freud a pensé la féminité et ce que sa théorie révèle de ses propres préjugés. Elle écrivit aussi sur l'art, le rire et la littérature.&lt;/p&gt; &lt;p&gt;Sa méthode consiste à lire les grands textes au plus près, en repérant les métaphores, les exemples et les détails apparemment secondaires, pour y faire apparaître ce que l'auteur ne dit pas explicitement. Ses livres sur Nietzsche, comme &lt;em&gt;Nietzsche et la métaphore&lt;/em&gt; (1972), ont renouvelé la lecture de ce philosophe en France, en montrant l'importance du style et des images dans sa pensée.&lt;/p&gt; &lt;p&gt;Dans &lt;em&gt;Paroles suffoquées&lt;/em&gt; (1987), elle réfléchit, à partir de Maurice Blanchot et de Robert Antelme, à l'impossibilité et à la nécessité de parler d'Auschwitz. Elle mit fin à ses jours en 1994, le jour anniversaire de la naissance de Nietzsche. Son œuvre, d'une trentaine de livres, allie rigueur philosophique, écoute de la psychanalyse et mémoire de la Shoah.&lt;/p&gt;</t>
-        </is>
-      </c>
-      <c r="G142" s="47" t="n"/>
-      <c r="H142" s="47" t="n"/>
-      <c r="J142" s="47" t="inlineStr">
-        <is>
-          <t xml:space="preserve">esthetique ; ethique</t>
-        </is>
-      </c>
-      <c r="K142" s="47" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Déconstructionnisme</t>
-        </is>
-      </c>
-      <c r="L142" s="47" t="inlineStr">
-        <is>
-          <t xml:space="preserve">philosophe française, lectrice de Nietzsche et de Freud, proche de Derrida, marquée par la Shoah.</t>
-        </is>
-      </c>
-      <c r="M142" t="inlineStr">
-        <is>
-          <t xml:space="preserve">femme ; juive</t>
         </is>
       </c>
       <c r="N142" t="inlineStr">
@@ -9558,34 +9579,34 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H121" display="https://www.laphilo.fr/pho/serres-mini.webp" r:id="rId75"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H122" display="https://www.laphilo.fr/pho/granel-mini.webp" r:id="rId76"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E123" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Raymond_Boudon&quot;  title=&quot; Wikipedia&quot;&gt;Raymond BOUDON&lt;/a&gt; était un sociologue et philosophe social français, l'une des figures les plus importantes de la sociologie française de la seconde moitié du XXe siècle et un ardent défenseur du libéralisme intellectuel et de la rationalité. Son œuvre,  &lt;a href=&quot;https://www.quesaisje.com/raymond-boudon&quot;  title=&quot; Boudon raymond par que sais je ?&quot;&gt;immense et plurielle, &lt;/a&gt; porte à la fois sur la méthodologie des sciences sociales, la théorie de l'action et la philosophie sociale. &lt;/p&gt; &lt;p&gt; Sa contribution la plus connue est l'élaboration d'une sociologie de l'individualisme méthodologique. Dans &lt;em&gt;L'Inégalité des chances&lt;/em&gt; (1973) et surtout dans &lt;em&gt;La Logique du social&lt;/em&gt; (1979) et &lt;em&gt;L'Art de se persuader des idées douteuses, fragiles ou fausses&lt;/em&gt; (1990), il défend l'idée que les faits sociaux s'expliquent par les actions et les croyances des individus, et que ces actions sont généralement rationnelles au sens large, c'est-à-dire fondées sur de « bonnes raisons » qui ne se réduisent pas  &lt;a href=&quot;https://www.youtube.com/watch?v=tMmKcRuoxp4&quot;  title=&quot; boudon l’inégalité des chances par La Sociothèque&quot;&gt;aux seuls intérêts matériels.&lt;/a&gt;  Cette position s'oppose à la fois au structuralisme durkheimien et au réductionnisme économique. &lt;/p&gt; &lt;p&gt; Dans ses dernières œuvres — &lt;em&gt;Pourquoi les intellectuels n'aiment pas le libéralisme&lt;/em&gt; (2004), &lt;em&gt;La Rationalité&lt;/em&gt; (2009) — il s'engagea dans une défense résolue du libéralisme politique et intellectuel contre ce qu'il percevait comme les dérives relativistes et collectivistes de la pensée française contemporaine. Sociologue rigoureux et polémiste redoutable, il fut l'un des penseurs français les plus lus à l'étranger, notamment aux États-Unis et en Allemagne, où son travail sur la rationalité et les croyances sociales est largement reconnu. &lt;/p&gt;     &lt;audio controls title=&quot;Raymond Boudon par France Culture&quot;&gt; &lt;source src=&quot;https://media.radiofrance-podcast.net/podcast09/12003-15.01.2014-ITEMA_20575231-2014C18006S0015-21.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt;&lt;/audio&gt;  " r:id="rId77"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H124" display="https://www.laphilo.fr/pho/fedier-mini.webp" r:id="rId78"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H125" display="https://www.laphilo.fr/pho/mwittig-mini.webp" r:id="rId79"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E126" display=" &lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Michel_Hulin&quot;  title=&quot; Wikipedia&quot;&gt;Michel HULIN&lt;/a&gt; était un philosophe français récemment décédé, grand spécialiste de la &lt;a href=&quot;https://www.youtube.com/watch?v=tJFic9y58Sc&quot; title=&quot; Aperçu de l’hindouisme avec Michel Hulin par Resonances &quot;&gt;philosophie indienne &lt;/a&gt; et de la comparaison entre pensée européenne et pensée asiatique, notamment de l’Advaïta Vedānta, le courant « non‑dualiste » du vedānta. Longtemps professeur de philosophie indienne et comparée à l’université Paris‑Sorbonne, il a joué un rôle central dans la diffusion en France des grandes écoles de pensée de l’Inde. Sa carrière s’est accompagnée d’un important travail de traduction du sanskrit et de vulgarisation, accessible à un public non spécialiste. &lt;/p&gt; &lt;p&gt; Ses recherches portent d’une part sur  &lt;a href=&quot;https://www.youtube.com/watch?v=kaJP8yDwHeY&quot; title=&quot; For intérieur par Resonnances &quot;&gt;la pensée indienne classique &lt;/a&gt;  (notion d’ahamkāra, textes vedāntins et shivaïtes d’inspiration tantrique), d’autre part sur les questions épistémologiques et métaphysiques que soulève la rencontre entre les traditions européennes et asiatiques. Dans sa thèse, Le Principe de l’ego dans la pensée indienne classique, il analyse la notion de « faux moi » et montre comment elle éclaire notre expérience ordinaire de la conscience. Il s’intéresse également à la question du temps, de l’éternité et des expériences dites mystiques, qu’il relie à des vécus très concrets. &lt;/p&gt; &lt;p&gt; Dans des ouvrages comme La Face cachée du temps, La Mystique sauvage, Hegel et l’Orient, Shankara et la non‑dualité ou encore l’anthologie L’Inde des sages, il  conjugue une érudition très précise et un style volontairement clair. Il montre comment des interrogations métaphysiques complexes – sur le moi, le temps, l’au‑delà ou l’expérience spirituelle – touchent directement la vie intérieure de chacun. Par son enseignement et ses livres, il a contribué à installer durablement en France une philosophie comparée attentive au dialogue entre Europe et Inde. &lt;p&gt; &lt;/p&gt;&lt;audio controls title=&quot;  Philosophies indiennes (1/4) : Upanishads, les textes fondateurs ?  par France Culture&quot;&gt; &lt;source src=&quot;https://media.radiofrance-podcast.net/podcast09/10467-16.12.2013-ITEMA_20562153-2013C12410S0350-NET_FC_A092AF0E-5BC1-49EE-A72F-E62BB6A2A8B1-21.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt;&lt;/audio&gt;  &lt;p&gt;  &lt;/p&gt;&#10;" r:id="rId80"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H126" display="https://www.laphilo.fr/pho/mhulin-mini.webp" r:id="rId81"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H127" display="https://www.laphilo.fr/pho/jfmarquet-mini.webp" r:id="rId82"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E128" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Cl%C3%A9ment_Rosset&quot; title=&quot; Wikipedia&quot;&gt;Clément ROSSET&lt;/a&gt; était un philosophe français connu pour sa pensée radicale et son style d'écriture d'une grande clarté. Son œuvre est principalement centrée sur le concept du  &lt;a href=&quot;https://www.youtube.com/watch?v=I50Jbj6uQEU&quot; title=&quot;Clément Rosset : la réalité ne convient pas ! par Kosmos&quot;&gt;&quot;réel&quot;&lt;/a&gt;  et l'incapacité ou la difficulté de l'homme à l'accepter dans sa singularité et souvent sa cruauté. Voici les points essentiels concernant sa philosophie : &lt;/p&gt; &lt;p&gt; - &lt;a href=&quot;https://www.youtube.com/watch?v=8m_kXVBdtwg&quot;  title=&quot; Le réel et son double, Clément Rosset, 2.2 avant-propos par Thibault BELZACQ&quot;&gt;Le Réel sans double&lt;/a&gt; : Son idée maîtresse est que le réel est unique, singulier et dépourvu de tout &quot;double&quot;. Il n'y a pas d'arrière-monde, pas de sens caché, pas de consolation ou d'illusion qui puisse atténuer sa nature brute. Le réel est simplement ce qui est, dans son évidence la plus nue. &lt;/p&gt; &lt;p&gt; - Le Refus du double et de l'illusion : Une grande partie de son travail consiste à traquer les différentes formes d'illusions et de doubles que l'humanité crée pour  &lt;a href=&quot;https://philitt.fr/2023/09/12/clement-rosset-tout-est-sans-raison/&quot;  title=&quot;Clément Rosset : tout est sans raison par Phillitt&quot;&gt;échapper à la confrontation&lt;/a&gt; directe avec le réel. Ces doubles peuvent être d'ordre métaphysique, moral, psychologique, ou même esthétique.&lt;/p&gt; &lt;p&gt; - &lt;a href=&quot;https://www.youtube.com/watch?v=JDcudFE_uBQ&quot;  title=&quot;Entretien avec Pierre Dumayet (1961) par Archives&quot;&gt;Philosophie tragique&lt;/a&gt; et Joie : Bien que sa pensée puisse sembler sombre en insistant sur la cruauté et l'absurdité du réel, il développe une philosophie que l'on qualifie souvent de &quot;tragique&quot; au sens nietzschéen du terme. Il ne s'agit pas de désespoir, mais plutôt de l'affirmation de la vie et du réel tels qu'ils sont, y compris dans leurs aspects les plus difficiles. &lt;/p&gt; &lt;p&gt; Il est également remarquable par son style d'écriture. Loin du jargon philosophique abscons, il privilégie une langue simple, directe et percutante. Cette clarté formelle est au service de la clarté de sa pensée, cherchant à énoncer le réel avec le moins d'interférences possible. Son œuvre, bien que parfois restée en marge des courants universitaires dominants, a marqué par sa radicalité, sa lucidité et sa défense d'une confrontation sans fard avec le réel.  &lt;/p&gt; &lt;audio controls title=&quot;Clément Rosset par France Culture&quot;&gt; &lt;source src=&quot;https://media.radiofrance-podcast.net/podcast09/10080-20.12.2013-ITEMA_20564152-2013C3403E0215-21.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt;&lt;/audio&gt;  " r:id="rId83"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H128" display="https://www.laphilo.fr/pho/rosset-mini.webp" r:id="rId84"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E129" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Jacques_Bouveresse&quot;  title=&quot; Wikipedia&quot;&gt;Jacques BOUVERESSE&lt;/a&gt; était un philosophe français du courant analytique, connu pour son rationalisme exigeant, son &lt;a href=&quot;https://www.youtube.com/watch?v=mfGM00nmj20&quot;  title=&quot; Wittgenstein et l'intériorité 一 Jacques Bouveresse par Andrea Cirla &quot;&gt;travail sur Wittgenstein &lt;/a&gt; et sa critique des dérives du milieu intellectuel français. Il a largement contribué à introduire et stabiliser en France une philosophie soucieuse de vérité, de clarté et d’argumentation rigoureuse. &lt;/p&gt; &lt;p&gt; Ses domaines privilégiés sont la philosophie de la connaissance, des sciences, des mathématiques, de la logique, du langage, ainsi qu’une philosophie de la culture attentive à la littérature et à la critique sociale.  Il se réclame du rationalisme des Lumières et s’inspire fortement de la philosophie analytique, du Cercle de Vienne, de Frege, de Gödel et de la tradition d’Europe centrale. Wittgenstein, qu’il contribue à faire connaître en France, est l’une de ses références centrales. &lt;/p&gt; &lt;p&gt; Il défend une position rationaliste dont le prolongement éthique est ce qu’il appelle la  &lt;a href=&quot;https://www.persee.fr/doc/lgge_0458-726x_1971_num_6_21_2079&quot; title=&quot;Langage ordinaire et philosophie par Persée &quot;&gt;&quot;modestie intellectuelle&quot; &lt;/a&gt; : ne pas exagérer ce que la philosophie peut faire, refuser le pathos et le prestige facile. Il combat le relativisme, l’historicisme radical et les remises en cause globales de la notion de vérité, notamment chez certains auteurs français, tout en reconnaissant par ailleurs leur importance. &lt;/p&gt; &lt;p&gt; Sa grande thèse, &quot;Le Mythe de l’intériorité&quot;, porte sur Wittgenstein, le langage privé, l’expérience et la signification, et a joué un rôle clé dans la réception française de Wittgenstein. Il consacre de nombreux travaux à Robert Musil et Karl Kraus, qu’il lit comme des alliés dans un combat pour l’exactitude, la critique de la bêtise et des illusions de la culture moderne. &lt;/p&gt;  &lt;audio controls title=&quot;Jacques Bouveresse, à la recherche de la clarté par France Culture&quot;&gt; &lt;source src=&quot;https://media.radiofrance-podcast.net/podcast09/10351-11.05.2021-ITEMA_23961779-2000C3500E0287-21.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt;" r:id="rId85"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H129" display="https://www.laphilo.fr/pho/bouveresse-mini.webp" r:id="rId86"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E130" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Jean-Luc_Nancy&quot;  title=&quot; Wikipedia&quot;&gt;Jean-Luc NANCY&lt;/a&gt; était un philosophe français, agrégé de philosophie, il fut professeur à l'Université de Strasbourg jusqu'à sa retraite. Sa pensée, en dialogue constant avec Heidegger, Derrida et Lacoue-Labarthe — avec lequel il collabora étroitement — porte sur le « sens du monde », la communauté, le corps et le toucher. &lt;/p&gt; &lt;p&gt; Son œuvre est marquée par le questionnement du « with » (avec), du « being-with » heideggerien. Dans &lt;em&gt;La Communauté désoeuvrée&lt;/em&gt; (1986), il développe une pensée de la communauté qui refuse toute forme d'immanentisme ou de fusion : la communauté véritable n'est pas une substance commune, mais  &lt;a href=&quot;https://www.youtube.com/watch?v=fZK6pEAPxEw&quot;  title=&quot;jean luc Nancy par Institut Humanités &quot;&gt;l'exposition partagée &lt;/a&gt; de la singularité de chacun. Cette réflexion, en dialogue critique avec Blanchot et Bataille, a eu un retentissement considérable dans les débats contemporains sur la politique, la communauté et l'identité. &lt;/p&gt; &lt;p&gt; Dans &lt;em&gt;Corpus&lt;/em&gt; (1992) et &lt;em&gt;Noli me tangere&lt;/em&gt; (2003), il explore  &lt;a href=&quot;https://www.youtube.com/watch?v=1kCExw6Wp9k&quot;  title=&quot;jean luc Nancy par Lacan TV &quot;&gt;la philosophie du corps &lt;/a&gt; et du toucher comme modes fondamentaux de l'être-au-monde. Son essai sur le sens — &lt;em&gt;Le Sens du monde&lt;/em&gt; (1993) — aborde la question de la possibilité du sens dans un monde déserté par les transcendances. &lt;em&gt;L'Intrus&lt;/em&gt; (2000), bref récit autobiographique sur sa transplantation cardiaque, mêle réflexion philosophique et expérience personnelle de la maladie et de l'altérité. Son œuvre, immense et diverse, témoigne d'une pensée vivante et rigoureuse toujours en dialogue avec la littérature, l'art et la politique. &lt;/p&gt;  &lt;audio controls title=&quot;Jean luc Nancy par France Culture&quot;&gt; &lt;source src=&quot;https://media.radiofrance-podcast.net/podcast09/11472-06.02.2011-ITEMA_20267545-2011C16153E0003-ITE_00040439_RSCE-21.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt;" r:id="rId87"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H130" display="https://www.laphilo.fr/pho/jlnancy-mini.webp" r:id="rId88"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E131" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Philippe_Lacoue-Labarthe&quot;  title=&quot; Wikipedia&quot;&gt;Philippe LACOUE-LABARTHE&lt;/a&gt; était un philosophe, critique littéraire, traducteur et théoricien français né à Tours et connu pour ses travaux sur la mimésis, le romantisme allemand, Hölderlin, Heidegger, Derrida et la relation entre esthétique et politique. Il a aussi beaucoup compté dans le milieu intellectuel de Strasbourg, où il a enseigné longtemps et travaillé avec Jean-Luc Nancy. &lt;/p&gt; &lt;p&gt; Son  &lt;a href=&quot;https://maitron.fr/lacoue-labarthe-philippe/&quot;  title=&quot; lacoue-labarthe par le maitron&quot;&gt;œuvre interroge &lt;/a&gt; la façon dont l’art, la philosophie et la politique s’entrecroisent, notamment à travers la notion de mimésis et la critique de l’“esthétisation du politique”. Il a aussi travaillé sur le romantisme allemand et sur la réception de Hölderlin, qu’il considérait comme une figure majeure. &lt;/p&gt; &lt;p&gt; Parmi les livres souvent cités, on trouve Le Titre de la lettre avec Jean-Luc Nancy, L’Absolu littéraire, L’Imitation des modernes, La Fiction du politique et Heidegger, la politique du poème. Il a également traduit plusieurs auteurs allemands majeurs, dont Heidegger, Hölderlin, Nietzsche, Benjamin et Celan. &lt;/p&gt; &lt;p&gt; Sa pensée tourne autour de trois idées principales : - La représentation n’est jamais transparente : ce que nous montrons, racontons ou jouons n’est jamais la réalité elle-même, mais une forme, un masque, une imitation. - La littérature et le théâtre sont essentiels pour comprendre la philosophie, parce qu’ils révèlent ce que les concepts cachent ou simplifient.popups. - Le lien entre esthétique et politique est dangereux : il a beaucoup réfléchi à la manière dont l’art, les mythes et les images peuvent servir le politique, y compris dans des formes fascisantes. &lt;/p&gt; &#10; &lt;audio controls title=&quot;les versions de philippe lacoue labarthe par France Culture&quot;&gt; &lt;source src=&quot;https://media.radiofrance-podcast.net/podcast09/16409-16.03.2007-ITEMA_20062386-2007C6409S0011-MEM_000036772_RF-21.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt;  " r:id="rId89"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H131" display="https://www.laphilo.fr/pho/pllabarthe-mini.webp" r:id="rId90"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H132" display="https://www.laphilo.fr/pho/fdelaporte-mini.webp" r:id="rId91"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H133" display="https://www.laphilo.fr/pho/lecourt-mini.webp" r:id="rId92"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E134" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Jean-Michel_Berthelot&quot;  title=&quot; Wikipedia&quot;&gt;Jean-Michel BERTHELOT&lt;/a&gt; était un philosophe et sociologue français spécialiste d'épistémologie des sciences sociales. Professeur à l'Université de Paris IV-Sorbonne et à l'Université du Québec à Montréal, il contribua de manière décisive à la réflexion philosophique sur les fondements et les méthodes des sciences humaines et sociales. Son œuvre joint la rigueur épistémologique à une large culture philosophique et sociologique. &lt;/p&gt; &lt;p&gt; Son ouvrage principal, &lt;em&gt; &lt;a href=&quot;https://www.persee.fr/doc/sotra_0038-0296_1992_num_34_3_2605_t1_0388_0000_3&quot;  title=&quot;l’intelligence du social par persée &quot;&gt; L'Intelligence du social&lt;/a&gt; &lt;/em&gt; (1990), est une analyse approfondie des schèmes d'intelligibilité que les sciences sociales utilisent pour rendre compte de la réalité sociale : le schème causal, le schème fonctionnel, le schème structural, le schème herméneutique et d'autres modes d'explication. Berthelot montre que chaque paradigme sociologique privilégie un mode d'intelligibilité particulier, ce qui permet de comprendre à la fois leurs apports spécifiques et leurs limites. Ce livre constitue l'une des contributions les plus claires et les plus systématiques à la philosophie des sciences sociales en langue française. &lt;/p&gt; &lt;p&gt; Dans &lt;em&gt;Epistémologie des sciences sociales&lt;/em&gt; (2001, ouvrage collectif qu'il dirigea), il offrit un panorama complet des questions épistémologiques fondamentales que posent les sciences humaines et sociales : la causalité, la compréhension, la mesure, la modélisation, la réflexivité et les rapports entre science et valeurs. Ses travaux contribuèrent à établir l'épistémologie des sciences sociales comme une discipline à part entière dans le paysage universitaire français, en dialogue constant avec la philosophie des sciences anglophones et continentale. &lt;/p&gt;" r:id="rId93"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H134" display="https://www.laphilo.fr/pho/jmberthelot-mini.webp" r:id="rId94"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E135" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Daniel_Bensa%C3%AFd&quot;  title=&quot; Wikipedia&quot;&gt;Daniel BENSAÏD&lt;/a&gt; était un philosophe français marxiste, l'un des intellectuels les plus importants de la gauche radicale française de son époque. Né à Paris dans une famille juive d'origine algérienne, il fut l'un des leaders de la révolte étudiante de mai 1968 à Paris-Nanterre aux côtés de Daniel Cohn-Bendit. Professeur de philosophie à l'Université Paris VIII-Saint-Denis, il fut membre dirigeant de la Ligue communiste révolutionnaire (LCR) et de son successeur le Nouveau Parti Anticapitaliste (NPA). &lt;/p&gt; &lt;p&gt; Sa pensée philosophique chercha à renouveler le marxisme en le débarrassant des &lt;a href=&quot;https://www.youtube.com/watch?v=uxBvxfRI2CE&quot;  title=&quot;la privatisation du monde par bibou11slalala &quot;&gt; simplifications téléologiques &lt;/a&gt; et en l'ouvrant à des problématiques nouvelles. Dans &lt;em&gt;Marx l'intempestif&lt;/em&gt; (1995), il défend un Marx débarrassé du déterminisme historique et de la philosophie du progrès, un Marx « intempestif » qui pense la politique comme art du possible et de l'impossible, en dialogue avec Blaise Pascal et Walter Benjamin. Ce livre renouvela profondément la  &lt;a href=&quot;https://www.youtube.com/watch?v=is8Ya038-Q4&quot;  title=&quot;l’héritage de Marx par socialtram &quot;&gt; lecture de Marx &lt;/a&gt; dans la gauche française. &lt;/p&gt; &lt;p&gt; Dans &lt;em&gt;Le Pari mélancolique&lt;/em&gt; (1997) et &lt;em&gt;Résistances&lt;/em&gt; (2001), il développe une philosophie de l'engagement politique nourrie par la mélancolie des défaites mais portée par une fidélité irréductible à l'émancipation. Sa réflexion sur les rapports entre philosophie et politique, entre utopie et stratégie, constitue l'une des contributions les plus originales à la pensée marxiste contemporaine. Polémiste redoutable et pédagogue exigeant, il laissa une empreinte profonde sur plusieurs générations de militants et d'intellectuels de gauche. &lt;/p&gt;  &lt;audio controls title=&quot;Daniel Bensaid  par France Culture&quot;&gt; &lt;source src=&quot;https://media.radiofrance-podcast.net/podcast09/10075-11.12.2006-ITEMA_20049670-2006C6608S0221-MEM_000033324_RF-21.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt; " r:id="rId95"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H135" display="https://www.laphilo.fr/pho/bensaid-mini.webp" r:id="rId96"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G136" display="&quot;Ce virus est là pour nous préparer au nouveau régime climatique&quot; par France Culture" r:id="rId97"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H136" display="https://www.laphilo.fr/pho/latour-mini.webp" r:id="rId98"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H137" display="https://www.laphilo.fr/pho/rdamien-mini.webp" r:id="rId99"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E138" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Catherine_Colliot-Th%C3%A9l%C3%A8ne&quot; title=&quot; Wikipedia&quot;&gt;Catherine COLLIOT-THELENE&lt;/a&gt; était une philosophe française  majeure de la philosophie politique contemporaine, spécialiste de Max Weber et penseuse des droits, de la démocratie et de la propriété dans un cadre cosmopolitique. Membre de l’Institut universitaire de France, elle est reconnue comme une référence internationale des études wébériennes. &lt;/p&gt; &lt;p&gt; Son travail se situe au croisement de la philosophie politique et des sciences sociales, avec trois pôles principaux :  &lt;a href=&quot;https://www.youtube.com/watch?v=krUYFtq9Jww&quot; title=&quot;Max Weber et la violence légitime de l’état par France Culture&quot;&gt;Max Weber, la démocratie et les droits, &lt;/a&gt;  la propriété et le cosmopolitisme.  Elle traduit et commente plusieurs textes de Weber, notamment Le Savant et le politique et Les Communautés, en montrant en détail ses concepts de rationalisation, de désenchantement et de domination. &lt;/p&gt; &lt;p&gt; À partir des années 2000, elle se concentre sur les droits subjectifs, leur articulation avec l’individualisme contemporain et la transformation des rapports entre pouvoirs politiques et économiques. Elle insiste sur la nécessité de penser la normativité (ce qui doit être) à partir d’une analyse précise des structures sociales réelles, d’où son dialogue constant avec le droit, l’histoire et la sociologie. &lt;/p&gt; &lt;p&gt; Dans &quot;La Démocratie sans “demos”  paru en 2011, elle remet en question l’identification classique entre &quot;peuple&quot; et &quot;démocratie&quot;. Elle critique la superposition entre souveraineté du peuple et souveraineté territoriale de l’État, qui conduit selon elle à des versions exclusives de la démocratie. &lt;a href=&quot;https://www.youtube.com/watch?v=ps2ixtEpgYI&quot; title=&quot;la democratie c’est le droit de resistance par Journal l’Humanitét&quot;&gt;Sa philosophie cherche &lt;/a&gt;  une démocratie fondée sur des droits universalisables et sur la participation de tous les sujets, plutôt que sur l’appartenance à une communauté nationale préconstituée. &lt;/p&gt; &lt;p&gt; Elle refuse la séparation entre théorie pure et monde social : pour elle, la philosophie politique doit dialoguer avec les sciences sociales pour produire une critique efficace des institutions et des inégalités. Elle a accompagné, sans posture militante classique mais avec une forte implication intellectuelle, les luttes pour les droits des femmes, des exclus et des étrangers, en cherchant à fournir des outils conceptuels pour penser l’égalité aujourd’hui. &lt;/p&gt; &#10; &lt;audio controls title=&quot;Les défis juridiques de la migration : existe-t-il un droit à la libre circulation ? par France Culture&quot;&gt; &lt;source src=&quot;https://media.radiofrance-podcast.net/podcast09/21447-09.02.2022-ITEMA_22927630-2022C27677S0040-21.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt;" r:id="rId100"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H138" display="https://www.laphilo.fr/pho/thelene-mini.webp" r:id="rId101"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H139" display="https://www.laphilo.fr/pho/bstiegler-mini.webp" r:id="rId102"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E140" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Bernard_Mabille_(philosophe)&quot;  style=&quot;color:#6A142A&quot;  title=&quot; Wikipedia&quot;&gt;Bernard MABILLE&lt;/a&gt; était un philosophe français spécialiste de dialectique et de philosophie hégélienne, ainsi que de métaphysique contemporaine. Agrégé de philosophie et professeur à l'Université Paris IV-Sorbonne, il fut l'un des meilleurs connaisseurs français de Hegel et contribua de manière significative au renouvellement des études hégéliennes en France dans les dernières décennies du XXe siècle. &lt;/p&gt; &lt;p&gt; Sa thèse principale, &lt;em&gt;Hegel : l'épreuve de la contingence&lt;/em&gt; (1999), est une lecture originale de la philosophie hégélienne à la lumière de la problématique de la contingence. Contre les lectures qui réduisent Hegel à un penseur du nécessaire et du rationnel, Mabille montre que la contingence est au cœur même du système hégélien et que la dialectique est précisément la méthode qui permet de penser le passage du contingent au nécessaire sans l'éliminer. Cette relecture contribua à ouvrir la philosophie hégélienne à des problématiques contemporaines. &lt;/p&gt; &lt;p&gt; Dans ses travaux sur la métaphysique et la dialectique, Mabille s'intéressa également aux rapports entre la philosophie hégélienne et la phénoménologie française, notamment Merleau-Ponty et Henry. Son enseignement à la Sorbonne forma plusieurs générations d'étudiants à la rigueur de la pensée dialectique. Sa disparition prématurée priva la philosophie française d'un penseur rigoureux dont l'œuvre, bien que de volume limité, témoigne d'une lecture profonde et originale de l'idéalisme allemand et de ses prolongements contemporains. &lt;/p&gt;" r:id="rId103"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H140" display="https://www.laphilo.fr/pho/bnabille-mini.webp" r:id="rId104"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H141" display="https://www.laphilo.fr/pho/adufourmantelle-mini.webp" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H125" display="https://www.laphilo.fr/pho/fedier-mini.webp" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H126" display="https://www.laphilo.fr/pho/mwittig-mini.webp" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E127" display=" &lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Michel_Hulin&quot;  title=&quot; Wikipedia&quot;&gt;Michel HULIN&lt;/a&gt; était un philosophe français récemment décédé, grand spécialiste de la &lt;a href=&quot;https://www.youtube.com/watch?v=tJFic9y58Sc&quot; title=&quot; Aperçu de l’hindouisme avec Michel Hulin par Resonances &quot;&gt;philosophie indienne &lt;/a&gt; et de la comparaison entre pensée européenne et pensée asiatique, notamment de l’Advaïta Vedānta, le courant « non‑dualiste » du vedānta. Longtemps professeur de philosophie indienne et comparée à l’université Paris‑Sorbonne, il a joué un rôle central dans la diffusion en France des grandes écoles de pensée de l’Inde. Sa carrière s’est accompagnée d’un important travail de traduction du sanskrit et de vulgarisation, accessible à un public non spécialiste. &lt;/p&gt; &lt;p&gt; Ses recherches portent d’une part sur  &lt;a href=&quot;https://www.youtube.com/watch?v=kaJP8yDwHeY&quot; title=&quot; For intérieur par Resonnances &quot;&gt;la pensée indienne classique &lt;/a&gt;  (notion d’ahamkāra, textes vedāntins et shivaïtes d’inspiration tantrique), d’autre part sur les questions épistémologiques et métaphysiques que soulève la rencontre entre les traditions européennes et asiatiques. Dans sa thèse, Le Principe de l’ego dans la pensée indienne classique, il analyse la notion de « faux moi » et montre comment elle éclaire notre expérience ordinaire de la conscience. Il s’intéresse également à la question du temps, de l’éternité et des expériences dites mystiques, qu’il relie à des vécus très concrets. &lt;/p&gt; &lt;p&gt; Dans des ouvrages comme La Face cachée du temps, La Mystique sauvage, Hegel et l’Orient, Shankara et la non‑dualité ou encore l’anthologie L’Inde des sages, il  conjugue une érudition très précise et un style volontairement clair. Il montre comment des interrogations métaphysiques complexes – sur le moi, le temps, l’au‑delà ou l’expérience spirituelle – touchent directement la vie intérieure de chacun. Par son enseignement et ses livres, il a contribué à installer durablement en France une philosophie comparée attentive au dialogue entre Europe et Inde. &lt;p&gt; &lt;/p&gt;&lt;audio controls title=&quot;  Philosophies indiennes (1/4) : Upanishads, les textes fondateurs ?  par France Culture&quot;&gt; &lt;source src=&quot;https://media.radiofrance-podcast.net/podcast09/10467-16.12.2013-ITEMA_20562153-2013C12410S0350-NET_FC_A092AF0E-5BC1-49EE-A72F-E62BB6A2A8B1-21.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt;&lt;/audio&gt;  &lt;p&gt;  &lt;/p&gt;&#10;" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H127" display="https://www.laphilo.fr/pho/mhulin-mini.webp" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H128" display="https://www.laphilo.fr/pho/jfmarquet-mini.webp" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E129" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Cl%C3%A9ment_Rosset&quot; title=&quot; Wikipedia&quot;&gt;Clément ROSSET&lt;/a&gt; était un philosophe français connu pour sa pensée radicale et son style d'écriture d'une grande clarté. Son œuvre est principalement centrée sur le concept du  &lt;a href=&quot;https://www.youtube.com/watch?v=I50Jbj6uQEU&quot; title=&quot;Clément Rosset : la réalité ne convient pas ! par Kosmos&quot;&gt;&quot;réel&quot;&lt;/a&gt;  et l'incapacité ou la difficulté de l'homme à l'accepter dans sa singularité et souvent sa cruauté. Voici les points essentiels concernant sa philosophie : &lt;/p&gt; &lt;p&gt; - &lt;a href=&quot;https://www.youtube.com/watch?v=8m_kXVBdtwg&quot;  title=&quot; Le réel et son double, Clément Rosset, 2.2 avant-propos par Thibault BELZACQ&quot;&gt;Le Réel sans double&lt;/a&gt; : Son idée maîtresse est que le réel est unique, singulier et dépourvu de tout &quot;double&quot;. Il n'y a pas d'arrière-monde, pas de sens caché, pas de consolation ou d'illusion qui puisse atténuer sa nature brute. Le réel est simplement ce qui est, dans son évidence la plus nue. &lt;/p&gt; &lt;p&gt; - Le Refus du double et de l'illusion : Une grande partie de son travail consiste à traquer les différentes formes d'illusions et de doubles que l'humanité crée pour  &lt;a href=&quot;https://philitt.fr/2023/09/12/clement-rosset-tout-est-sans-raison/&quot;  title=&quot;Clément Rosset : tout est sans raison par Phillitt&quot;&gt;échapper à la confrontation&lt;/a&gt; directe avec le réel. Ces doubles peuvent être d'ordre métaphysique, moral, psychologique, ou même esthétique.&lt;/p&gt; &lt;p&gt; - &lt;a href=&quot;https://www.youtube.com/watch?v=JDcudFE_uBQ&quot;  title=&quot;Entretien avec Pierre Dumayet (1961) par Archives&quot;&gt;Philosophie tragique&lt;/a&gt; et Joie : Bien que sa pensée puisse sembler sombre en insistant sur la cruauté et l'absurdité du réel, il développe une philosophie que l'on qualifie souvent de &quot;tragique&quot; au sens nietzschéen du terme. Il ne s'agit pas de désespoir, mais plutôt de l'affirmation de la vie et du réel tels qu'ils sont, y compris dans leurs aspects les plus difficiles. &lt;/p&gt; &lt;p&gt; Il est également remarquable par son style d'écriture. Loin du jargon philosophique abscons, il privilégie une langue simple, directe et percutante. Cette clarté formelle est au service de la clarté de sa pensée, cherchant à énoncer le réel avec le moins d'interférences possible. Son œuvre, bien que parfois restée en marge des courants universitaires dominants, a marqué par sa radicalité, sa lucidité et sa défense d'une confrontation sans fard avec le réel.  &lt;/p&gt; &lt;audio controls title=&quot;Clément Rosset par France Culture&quot;&gt; &lt;source src=&quot;https://media.radiofrance-podcast.net/podcast09/10080-20.12.2013-ITEMA_20564152-2013C3403E0215-21.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt;&lt;/audio&gt;  " r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H129" display="https://www.laphilo.fr/pho/rosset-mini.webp" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E130" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Jacques_Bouveresse&quot;  title=&quot; Wikipedia&quot;&gt;Jacques BOUVERESSE&lt;/a&gt; était un philosophe français du courant analytique, connu pour son rationalisme exigeant, son &lt;a href=&quot;https://www.youtube.com/watch?v=mfGM00nmj20&quot;  title=&quot; Wittgenstein et l'intériorité 一 Jacques Bouveresse par Andrea Cirla &quot;&gt;travail sur Wittgenstein &lt;/a&gt; et sa critique des dérives du milieu intellectuel français. Il a largement contribué à introduire et stabiliser en France une philosophie soucieuse de vérité, de clarté et d’argumentation rigoureuse. &lt;/p&gt; &lt;p&gt; Ses domaines privilégiés sont la philosophie de la connaissance, des sciences, des mathématiques, de la logique, du langage, ainsi qu’une philosophie de la culture attentive à la littérature et à la critique sociale.  Il se réclame du rationalisme des Lumières et s’inspire fortement de la philosophie analytique, du Cercle de Vienne, de Frege, de Gödel et de la tradition d’Europe centrale. Wittgenstein, qu’il contribue à faire connaître en France, est l’une de ses références centrales. &lt;/p&gt; &lt;p&gt; Il défend une position rationaliste dont le prolongement éthique est ce qu’il appelle la  &lt;a href=&quot;https://www.persee.fr/doc/lgge_0458-726x_1971_num_6_21_2079&quot; title=&quot;Langage ordinaire et philosophie par Persée &quot;&gt;&quot;modestie intellectuelle&quot; &lt;/a&gt; : ne pas exagérer ce que la philosophie peut faire, refuser le pathos et le prestige facile. Il combat le relativisme, l’historicisme radical et les remises en cause globales de la notion de vérité, notamment chez certains auteurs français, tout en reconnaissant par ailleurs leur importance. &lt;/p&gt; &lt;p&gt; Sa grande thèse, &quot;Le Mythe de l’intériorité&quot;, porte sur Wittgenstein, le langage privé, l’expérience et la signification, et a joué un rôle clé dans la réception française de Wittgenstein. Il consacre de nombreux travaux à Robert Musil et Karl Kraus, qu’il lit comme des alliés dans un combat pour l’exactitude, la critique de la bêtise et des illusions de la culture moderne. &lt;/p&gt;  &lt;audio controls title=&quot;Jacques Bouveresse, à la recherche de la clarté par France Culture&quot;&gt; &lt;source src=&quot;https://media.radiofrance-podcast.net/podcast09/10351-11.05.2021-ITEMA_23961779-2000C3500E0287-21.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt;" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H130" display="https://www.laphilo.fr/pho/bouveresse-mini.webp" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E131" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Jean-Luc_Nancy&quot;  title=&quot; Wikipedia&quot;&gt;Jean-Luc NANCY&lt;/a&gt; était un philosophe français, agrégé de philosophie, il fut professeur à l'Université de Strasbourg jusqu'à sa retraite. Sa pensée, en dialogue constant avec Heidegger, Derrida et Lacoue-Labarthe — avec lequel il collabora étroitement — porte sur le « sens du monde », la communauté, le corps et le toucher. &lt;/p&gt; &lt;p&gt; Son œuvre est marquée par le questionnement du « with » (avec), du « being-with » heideggerien. Dans &lt;em&gt;La Communauté désoeuvrée&lt;/em&gt; (1986), il développe une pensée de la communauté qui refuse toute forme d'immanentisme ou de fusion : la communauté véritable n'est pas une substance commune, mais  &lt;a href=&quot;https://www.youtube.com/watch?v=fZK6pEAPxEw&quot;  title=&quot;jean luc Nancy par Institut Humanités &quot;&gt;l'exposition partagée &lt;/a&gt; de la singularité de chacun. Cette réflexion, en dialogue critique avec Blanchot et Bataille, a eu un retentissement considérable dans les débats contemporains sur la politique, la communauté et l'identité. &lt;/p&gt; &lt;p&gt; Dans &lt;em&gt;Corpus&lt;/em&gt; (1992) et &lt;em&gt;Noli me tangere&lt;/em&gt; (2003), il explore  &lt;a href=&quot;https://www.youtube.com/watch?v=1kCExw6Wp9k&quot;  title=&quot;jean luc Nancy par Lacan TV &quot;&gt;la philosophie du corps &lt;/a&gt; et du toucher comme modes fondamentaux de l'être-au-monde. Son essai sur le sens — &lt;em&gt;Le Sens du monde&lt;/em&gt; (1993) — aborde la question de la possibilité du sens dans un monde déserté par les transcendances. &lt;em&gt;L'Intrus&lt;/em&gt; (2000), bref récit autobiographique sur sa transplantation cardiaque, mêle réflexion philosophique et expérience personnelle de la maladie et de l'altérité. Son œuvre, immense et diverse, témoigne d'une pensée vivante et rigoureuse toujours en dialogue avec la littérature, l'art et la politique. &lt;/p&gt;  &lt;audio controls title=&quot;Jean luc Nancy par France Culture&quot;&gt; &lt;source src=&quot;https://media.radiofrance-podcast.net/podcast09/11472-06.02.2011-ITEMA_20267545-2011C16153E0003-ITE_00040439_RSCE-21.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt;" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H131" display="https://www.laphilo.fr/pho/jlnancy-mini.webp" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E132" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Philippe_Lacoue-Labarthe&quot;  title=&quot; Wikipedia&quot;&gt;Philippe LACOUE-LABARTHE&lt;/a&gt; était un philosophe, critique littéraire, traducteur et théoricien français né à Tours et connu pour ses travaux sur la mimésis, le romantisme allemand, Hölderlin, Heidegger, Derrida et la relation entre esthétique et politique. Il a aussi beaucoup compté dans le milieu intellectuel de Strasbourg, où il a enseigné longtemps et travaillé avec Jean-Luc Nancy. &lt;/p&gt; &lt;p&gt; Son  &lt;a href=&quot;https://maitron.fr/lacoue-labarthe-philippe/&quot;  title=&quot; lacoue-labarthe par le maitron&quot;&gt;œuvre interroge &lt;/a&gt; la façon dont l’art, la philosophie et la politique s’entrecroisent, notamment à travers la notion de mimésis et la critique de l’“esthétisation du politique”. Il a aussi travaillé sur le romantisme allemand et sur la réception de Hölderlin, qu’il considérait comme une figure majeure. &lt;/p&gt; &lt;p&gt; Parmi les livres souvent cités, on trouve Le Titre de la lettre avec Jean-Luc Nancy, L’Absolu littéraire, L’Imitation des modernes, La Fiction du politique et Heidegger, la politique du poème. Il a également traduit plusieurs auteurs allemands majeurs, dont Heidegger, Hölderlin, Nietzsche, Benjamin et Celan. &lt;/p&gt; &lt;p&gt; Sa pensée tourne autour de trois idées principales : - La représentation n’est jamais transparente : ce que nous montrons, racontons ou jouons n’est jamais la réalité elle-même, mais une forme, un masque, une imitation. - La littérature et le théâtre sont essentiels pour comprendre la philosophie, parce qu’ils révèlent ce que les concepts cachent ou simplifient.popups. - Le lien entre esthétique et politique est dangereux : il a beaucoup réfléchi à la manière dont l’art, les mythes et les images peuvent servir le politique, y compris dans des formes fascisantes. &lt;/p&gt; &#10; &lt;audio controls title=&quot;les versions de philippe lacoue labarthe par France Culture&quot;&gt; &lt;source src=&quot;https://media.radiofrance-podcast.net/podcast09/16409-16.03.2007-ITEMA_20062386-2007C6409S0011-MEM_000036772_RF-21.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt;  " r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H132" display="https://www.laphilo.fr/pho/pllabarthe-mini.webp" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H133" display="https://www.laphilo.fr/pho/fdelaporte-mini.webp" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H134" display="https://www.laphilo.fr/pho/lecourt-mini.webp" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E135" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Jean-Michel_Berthelot&quot;  title=&quot; Wikipedia&quot;&gt;Jean-Michel BERTHELOT&lt;/a&gt; était un philosophe et sociologue français spécialiste d'épistémologie des sciences sociales. Professeur à l'Université de Paris IV-Sorbonne et à l'Université du Québec à Montréal, il contribua de manière décisive à la réflexion philosophique sur les fondements et les méthodes des sciences humaines et sociales. Son œuvre joint la rigueur épistémologique à une large culture philosophique et sociologique. &lt;/p&gt; &lt;p&gt; Son ouvrage principal, &lt;em&gt; &lt;a href=&quot;https://www.persee.fr/doc/sotra_0038-0296_1992_num_34_3_2605_t1_0388_0000_3&quot;  title=&quot;l’intelligence du social par persée &quot;&gt; L'Intelligence du social&lt;/a&gt; &lt;/em&gt; (1990), est une analyse approfondie des schèmes d'intelligibilité que les sciences sociales utilisent pour rendre compte de la réalité sociale : le schème causal, le schème fonctionnel, le schème structural, le schème herméneutique et d'autres modes d'explication. Berthelot montre que chaque paradigme sociologique privilégie un mode d'intelligibilité particulier, ce qui permet de comprendre à la fois leurs apports spécifiques et leurs limites. Ce livre constitue l'une des contributions les plus claires et les plus systématiques à la philosophie des sciences sociales en langue française. &lt;/p&gt; &lt;p&gt; Dans &lt;em&gt;Epistémologie des sciences sociales&lt;/em&gt; (2001, ouvrage collectif qu'il dirigea), il offrit un panorama complet des questions épistémologiques fondamentales que posent les sciences humaines et sociales : la causalité, la compréhension, la mesure, la modélisation, la réflexivité et les rapports entre science et valeurs. Ses travaux contribuèrent à établir l'épistémologie des sciences sociales comme une discipline à part entière dans le paysage universitaire français, en dialogue constant avec la philosophie des sciences anglophones et continentale. &lt;/p&gt;" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H135" display="https://www.laphilo.fr/pho/jmberthelot-mini.webp" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E136" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Daniel_Bensa%C3%AFd&quot;  title=&quot; Wikipedia&quot;&gt;Daniel BENSAÏD&lt;/a&gt; était un philosophe français marxiste, l'un des intellectuels les plus importants de la gauche radicale française de son époque. Né à Paris dans une famille juive d'origine algérienne, il fut l'un des leaders de la révolte étudiante de mai 1968 à Paris-Nanterre aux côtés de Daniel Cohn-Bendit. Professeur de philosophie à l'Université Paris VIII-Saint-Denis, il fut membre dirigeant de la Ligue communiste révolutionnaire (LCR) et de son successeur le Nouveau Parti Anticapitaliste (NPA). &lt;/p&gt; &lt;p&gt; Sa pensée philosophique chercha à renouveler le marxisme en le débarrassant des &lt;a href=&quot;https://www.youtube.com/watch?v=uxBvxfRI2CE&quot;  title=&quot;la privatisation du monde par bibou11slalala &quot;&gt; simplifications téléologiques &lt;/a&gt; et en l'ouvrant à des problématiques nouvelles. Dans &lt;em&gt;Marx l'intempestif&lt;/em&gt; (1995), il défend un Marx débarrassé du déterminisme historique et de la philosophie du progrès, un Marx « intempestif » qui pense la politique comme art du possible et de l'impossible, en dialogue avec Blaise Pascal et Walter Benjamin. Ce livre renouvela profondément la  &lt;a href=&quot;https://www.youtube.com/watch?v=is8Ya038-Q4&quot;  title=&quot;l’héritage de Marx par socialtram &quot;&gt; lecture de Marx &lt;/a&gt; dans la gauche française. &lt;/p&gt; &lt;p&gt; Dans &lt;em&gt;Le Pari mélancolique&lt;/em&gt; (1997) et &lt;em&gt;Résistances&lt;/em&gt; (2001), il développe une philosophie de l'engagement politique nourrie par la mélancolie des défaites mais portée par une fidélité irréductible à l'émancipation. Sa réflexion sur les rapports entre philosophie et politique, entre utopie et stratégie, constitue l'une des contributions les plus originales à la pensée marxiste contemporaine. Polémiste redoutable et pédagogue exigeant, il laissa une empreinte profonde sur plusieurs générations de militants et d'intellectuels de gauche. &lt;/p&gt;  &lt;audio controls title=&quot;Daniel Bensaid  par France Culture&quot;&gt; &lt;source src=&quot;https://media.radiofrance-podcast.net/podcast09/10075-11.12.2006-ITEMA_20049670-2006C6608S0221-MEM_000033324_RF-21.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt; " r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H136" display="https://www.laphilo.fr/pho/bensaid-mini.webp" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G137" display="&quot;Ce virus est là pour nous préparer au nouveau régime climatique&quot; par France Culture" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H137" display="https://www.laphilo.fr/pho/latour-mini.webp" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H138" display="https://www.laphilo.fr/pho/rdamien-mini.webp" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E139" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Catherine_Colliot-Th%C3%A9l%C3%A8ne&quot; title=&quot; Wikipedia&quot;&gt;Catherine COLLIOT-THELENE&lt;/a&gt; était une philosophe française  majeure de la philosophie politique contemporaine, spécialiste de Max Weber et penseuse des droits, de la démocratie et de la propriété dans un cadre cosmopolitique. Membre de l’Institut universitaire de France, elle est reconnue comme une référence internationale des études wébériennes. &lt;/p&gt; &lt;p&gt; Son travail se situe au croisement de la philosophie politique et des sciences sociales, avec trois pôles principaux :  &lt;a href=&quot;https://www.youtube.com/watch?v=krUYFtq9Jww&quot; title=&quot;Max Weber et la violence légitime de l’état par France Culture&quot;&gt;Max Weber, la démocratie et les droits, &lt;/a&gt;  la propriété et le cosmopolitisme.  Elle traduit et commente plusieurs textes de Weber, notamment Le Savant et le politique et Les Communautés, en montrant en détail ses concepts de rationalisation, de désenchantement et de domination. &lt;/p&gt; &lt;p&gt; À partir des années 2000, elle se concentre sur les droits subjectifs, leur articulation avec l’individualisme contemporain et la transformation des rapports entre pouvoirs politiques et économiques. Elle insiste sur la nécessité de penser la normativité (ce qui doit être) à partir d’une analyse précise des structures sociales réelles, d’où son dialogue constant avec le droit, l’histoire et la sociologie. &lt;/p&gt; &lt;p&gt; Dans &quot;La Démocratie sans “demos”  paru en 2011, elle remet en question l’identification classique entre &quot;peuple&quot; et &quot;démocratie&quot;. Elle critique la superposition entre souveraineté du peuple et souveraineté territoriale de l’État, qui conduit selon elle à des versions exclusives de la démocratie. &lt;a href=&quot;https://www.youtube.com/watch?v=ps2ixtEpgYI&quot; title=&quot;la democratie c’est le droit de resistance par Journal l’Humanitét&quot;&gt;Sa philosophie cherche &lt;/a&gt;  une démocratie fondée sur des droits universalisables et sur la participation de tous les sujets, plutôt que sur l’appartenance à une communauté nationale préconstituée. &lt;/p&gt; &lt;p&gt; Elle refuse la séparation entre théorie pure et monde social : pour elle, la philosophie politique doit dialoguer avec les sciences sociales pour produire une critique efficace des institutions et des inégalités. Elle a accompagné, sans posture militante classique mais avec une forte implication intellectuelle, les luttes pour les droits des femmes, des exclus et des étrangers, en cherchant à fournir des outils conceptuels pour penser l’égalité aujourd’hui. &lt;/p&gt; &#10; &lt;audio controls title=&quot;Les défis juridiques de la migration : existe-t-il un droit à la libre circulation ? par France Culture&quot;&gt; &lt;source src=&quot;https://media.radiofrance-podcast.net/podcast09/21447-09.02.2022-ITEMA_22927630-2022C27677S0040-21.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt;" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H139" display="https://www.laphilo.fr/pho/thelene-mini.webp" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H140" display="https://www.laphilo.fr/pho/bstiegler-mini.webp" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E141" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Bernard_Mabille_(philosophe)&quot;  style=&quot;color:#6A142A&quot;  title=&quot; Wikipedia&quot;&gt;Bernard MABILLE&lt;/a&gt; était un philosophe français spécialiste de dialectique et de philosophie hégélienne, ainsi que de métaphysique contemporaine. Agrégé de philosophie et professeur à l'Université Paris IV-Sorbonne, il fut l'un des meilleurs connaisseurs français de Hegel et contribua de manière significative au renouvellement des études hégéliennes en France dans les dernières décennies du XXe siècle. &lt;/p&gt; &lt;p&gt; Sa thèse principale, &lt;em&gt;Hegel : l'épreuve de la contingence&lt;/em&gt; (1999), est une lecture originale de la philosophie hégélienne à la lumière de la problématique de la contingence. Contre les lectures qui réduisent Hegel à un penseur du nécessaire et du rationnel, Mabille montre que la contingence est au cœur même du système hégélien et que la dialectique est précisément la méthode qui permet de penser le passage du contingent au nécessaire sans l'éliminer. Cette relecture contribua à ouvrir la philosophie hégélienne à des problématiques contemporaines. &lt;/p&gt; &lt;p&gt; Dans ses travaux sur la métaphysique et la dialectique, Mabille s'intéressa également aux rapports entre la philosophie hégélienne et la phénoménologie française, notamment Merleau-Ponty et Henry. Son enseignement à la Sorbonne forma plusieurs générations d'étudiants à la rigueur de la pensée dialectique. Sa disparition prématurée priva la philosophie française d'un penseur rigoureux dont l'œuvre, bien que de volume limité, témoigne d'une lecture profonde et originale de l'idéalisme allemand et de ses prolongements contemporains. &lt;/p&gt;" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H141" display="https://www.laphilo.fr/pho/bnabille-mini.webp" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H142" display="https://www.laphilo.fr/pho/adufourmantelle-mini.webp" r:id="rId105"/>
   </hyperlinks>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>

--- a/data/frise-philosophes-france.xlsx
+++ b/data/frise-philosophes-france.xlsx
@@ -938,7 +938,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:N142"/>
+  <dimension ref="A1:O143"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="4.59" customWidth="1" style="47" min="1" max="1"/>
@@ -9482,6 +9482,59 @@
         <is>
           <t xml:space="preserve">occident</t>
         </is>
+      </c>
+    </row>
+    <row r="143" ht="176.25" customHeight="1" s="49">
+      <c r="A143" s="47">
+        <v>1881</v>
+      </c>
+      <c r="B143" s="47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1955</t>
+        </is>
+      </c>
+      <c r="C143" s="47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1881 – 1955</t>
+        </is>
+      </c>
+      <c r="D143" s="47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pierre TEILHARD DE CHARDIN</t>
+        </is>
+      </c>
+      <c r="E143" s="85" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Pierre_Teilhard_de_Chardin" title=" Wikipedia"&gt;Pierre TEILHARD DE CHARDIN&lt;/a&gt; est un prêtre jésuite, paléontologue et philosophe français, qui a voulu réconcilier la foi chrétienne et la théorie de l’évolution. Né en Auvergne, il entre chez les jésuites et devient un spécialiste reconnu de la &lt;a href="https://fr.wikipedia.org/wiki/Pal%C3%A9ontologie" title=" Wikipedia"&gt;paléontologie&lt;/a&gt;. Brancardier pendant la Première Guerre mondiale, il passe ensuite plus de vingt ans en Chine, où il participe aux recherches sur l’&lt;a href="https://fr.wikipedia.org/wiki/Homme_de_P%C3%A9kin" title=" Wikipedia"&gt;Homme de Pékin&lt;/a&gt;, l’un des plus anciens fossiles humains connus, et prend part en 1931-1932 à la &lt;a href="https://fr.wikipedia.org/wiki/Croisi%C3%A8re_jaune" title=" Wikipedia"&gt;Croisière jaune&lt;/a&gt;, grande expédition à travers l’Asie centrale.&lt;/p&gt; &lt;p&gt;Dans &lt;em&gt;Le Phénomène humain&lt;/em&gt;, écrit dans les années 1930 et publié après sa mort, il décrit l’univers comme un grand mouvement d’évolution, de la matière à la vie, puis de la vie à la pensée. À mesure que la matière se complexifie, la conscience grandit : c’est la « loi de complexité-conscience ». Avec l’homme apparaît une nouvelle couche de la Terre, la &lt;a href="https://fr.wikipedia.org/wiki/Noosph%C3%A8re" title=" Wikipedia"&gt;noosphère&lt;/a&gt;, la sphère de la pensée, qui relie peu à peu tous les esprits.&lt;/p&gt; &lt;p&gt;Cette évolution est selon lui orientée vers un point de convergence final, le &lt;a href="https://fr.wikipedia.org/wiki/Point_Om%C3%A9ga" title=" Wikipedia"&gt;point Oméga&lt;/a&gt;, qu’il identifie au Christ cosmique, où l’humanité s’unira sans perdre la personnalité de chacun. Son autre grand texte, &lt;em&gt;Le Milieu divin&lt;/em&gt;, médite sur la présence de Dieu dans toutes les activités humaines. Ses idées inquiètent Rome, qui lui interdit de publier ses écrits philosophiques et l’éloigne de France. Il meurt à New York en 1955. Publiée après sa mort, son œuvre connaît un succès mondial, et l’on voit parfois dans la noosphère une anticipation d’Internet.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="H143" s="48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/teilhard-mini.webp</t>
+        </is>
+      </c>
+      <c r="J143" s="48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">metaphysique ; spiritualite</t>
+        </is>
+      </c>
+      <c r="K143" s="48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Spiritualisme ; Panenthéisme</t>
+        </is>
+      </c>
+      <c r="L143" s="48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">jésuite et paléontologue français, penseur d’une évolution cosmique orientée vers la conscience et l’esprit.</t>
+        </is>
+      </c>
+      <c r="N143" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+      <c r="O143">
+        <v>2</v>
       </c>
     </row>
     <row r="1048566" ht="12.75" customHeight="1" s="49"/>

--- a/data/frise-philosophes-france.xlsx
+++ b/data/frise-philosophes-france.xlsx
@@ -6034,7 +6034,7 @@
       </c>
       <c r="E86" s="59" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt; &lt;a href="https://fr.wikipedia.org/wiki/Simone_Weil"  title=" Wikipedia"&gt; Simone WEIL&lt;/a&gt; était une philosophe Française qui a étudié la philosophie antique et les textes religieux. Elle était profondément spirituelle et religieuse et a rejeté les institutions traditionnelles. Elle a exploré les aspects mystiques de différentes religions et a essayé de les intégrer dans une vision du monde plus large.  Elle souhaite faire de la philosophie une manière de vivre, non pour acquérir des connaissances, mais pour être dans la vérité. Elle écrira plusieurs livres dont &lt;a href="https://www.youtube.com/watch?v=6CR2PcTPvCk&amp;ab_channel=Al%C3%A8theiar" title="Les besoins de l'âme par Alèteia"&gt; "l'Enracinement" &lt;/a&gt; et "la Pesanteur et la grâce".  &lt;/p&gt; &lt;p&gt;C'était une &lt;a   title="L'activisme politique est une attitude, une règle de conduite ou un engagement politique qui privilégie l'action directe à court terme par rapport aux principes théoriques et aux actions à long terme"&gt; activiste politique &lt;/a&gt;  engagée, qui a participé à divers mouvements sociaux et politiques, notamment la grève générale en France en 1936 et la guerre d'Espagne. &lt;/p&gt; &lt;p&gt; En 1942, elle a participé à la lutte contre l'occupation nazie en se joignant à la résistance. Dans son ouvrage, &lt;a href="https://www.youtube.com/watch?v=Pg0qv0kIaKo&amp;ab_channel=LePr%C3%A9cepteur"  style="color:#88A1E9"  title="Supprimer les parties politiques par le Précepteur"&gt; "La Condition ouvrière" &lt;/a&gt;.   elle prône la suppression des partis politiques et défend l'idée selon laquelle les partis politiques sont souvent motivés par leurs intérêts partisans plutôt que par le bien-être général de la société et qu'ils sont des obstacles à la véritable démocratie en concentrant le pouvoir entre les mains d'une élite restreinte et en limitant les voix de la majorité. &lt;/p&gt;  &lt;audio controls title="Une intellectuelle à l'usine par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/21936-01.01.2021-ITEMA_22534096-2019C12410E0194.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt; 
+          <t xml:space="preserve">&lt;p&gt; &lt;a href="https://fr.wikipedia.org/wiki/Simone_Weil"  title=" Wikipedia"&gt; Simone WEIL&lt;/a&gt; était une philosophe Française qui a étudié la philosophie antique et les textes religieux. Elle était profondément spirituelle et religieuse et a rejeté les institutions traditionnelles. Elle a exploré les aspects mystiques de différentes religions et a essayé de les intégrer dans une vision du monde plus large.  Elle souhaite faire de la philosophie une manière de vivre, non pour acquérir des connaissances, mais pour être dans la vérité. Elle écrira plusieurs livres dont &lt;a href="https://www.youtube.com/watch?v=6CR2PcTPvCk&amp;ab_channel=Al%C3%A8theiar" title="Les besoins de l'âme par Alèteia"&gt; "l'Enracinement" &lt;/a&gt; et "la Pesanteur et la grâce".  &lt;/p&gt; &lt;p&gt;C'était une &lt;span title="L'activisme politique est une attitude, une règle de conduite ou un engagement politique qui privilégie l'action directe à court terme par rapport aux principes théoriques et aux actions à long terme"&gt; activiste politique &lt;/span&gt;  engagée, qui a participé à divers mouvements sociaux et politiques, notamment la grève générale en France en 1936 et la guerre d'Espagne. &lt;/p&gt; &lt;p&gt; En 1942, elle a participé à la lutte contre l'occupation nazie en se joignant à la résistance. Dans son ouvrage, &lt;a href="https://www.youtube.com/watch?v=Pg0qv0kIaKo&amp;ab_channel=LePr%C3%A9cepteur"  style="color:#88A1E9"  title="Supprimer les parties politiques par le Précepteur"&gt; "La Condition ouvrière" &lt;/a&gt;.   elle prône la suppression des partis politiques et défend l'idée selon laquelle les partis politiques sont souvent motivés par leurs intérêts partisans plutôt que par le bien-être général de la société et qu'ils sont des obstacles à la véritable démocratie en concentrant le pouvoir entre les mains d'une élite restreinte et en limitant les voix de la majorité. &lt;/p&gt;  &lt;audio controls title="Une intellectuelle à l'usine par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/21936-01.01.2021-ITEMA_22534096-2019C12410E0194.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt; 
 </t>
         </is>
       </c>

--- a/data/frise-philosophes-france.xlsx
+++ b/data/frise-philosophes-france.xlsx
@@ -1505,7 +1505,7 @@
       </c>
       <c r="G11" s="59" t="inlineStr">
         <is>
-          <t>"Joseph PROUDHON: champion of Anarchism " par " VIS PHILO</t>
+          <t xml:space="preserve">"Joseph PROUDHON: champion of Anarchism " par VIS PHILO</t>
         </is>
       </c>
       <c r="H11" s="59" t="inlineStr">
@@ -4203,7 +4203,7 @@
       </c>
       <c r="G56" s="59" t="inlineStr">
         <is>
-          <t>"Gaston Bachelard, philosophe français des sciences" par radio-canada Archives</t>
+          <t xml:space="preserve">"Gaston Bachelard, philosophe français des sciences" par Radio-Canada Archives</t>
         </is>
       </c>
       <c r="H56" s="59" t="inlineStr">
@@ -4323,7 +4323,7 @@
       </c>
       <c r="G58" s="59" t="inlineStr">
         <is>
-          <t>La fin des temps par le Précepteur</t>
+          <t xml:space="preserve">La fin des temps par Le Précepteur</t>
         </is>
       </c>
       <c r="H58" s="59" t="inlineStr">
@@ -5236,7 +5236,7 @@
       </c>
       <c r="G73" s="59" t="inlineStr">
         <is>
-          <t>Sartre par 'The school of Life'</t>
+          <t xml:space="preserve">Sartre par The School of Life</t>
         </is>
       </c>
       <c r="H73" s="59" t="inlineStr">
@@ -5363,7 +5363,7 @@
       </c>
       <c r="G75" s="56" t="inlineStr">
         <is>
-          <t>emmanuel mounier par regards protestants</t>
+          <t xml:space="preserve">emmanuel mounier par Regards protestants</t>
         </is>
       </c>
       <c r="H75" s="62" t="inlineStr">
@@ -5979,7 +5979,7 @@
       </c>
       <c r="G85" s="56" t="inlineStr">
         <is>
-          <t>claude levi-strauss le structuralisme par ina culture</t>
+          <t xml:space="preserve">claude levi-strauss le structuralisme par Ina Culture</t>
         </is>
       </c>
       <c r="H85" s="62" t="inlineStr">
@@ -6530,7 +6530,7 @@
       </c>
       <c r="G94" s="56" t="inlineStr">
         <is>
-          <t>Une vie : Marguerite DURAS par BRUT</t>
+          <t xml:space="preserve">Une vie : Marguerite DURAS par Brut</t>
         </is>
       </c>
       <c r="H94" s="62" t="inlineStr">
@@ -7083,7 +7083,7 @@
       </c>
       <c r="G103" s="56" t="inlineStr">
         <is>
-          <t>"Pierre Hadot : La simplicité comme exercice spirituel" par Resonances</t>
+          <t xml:space="preserve">"Pierre Hadot : La simplicité comme exercice spirituel" par Résonances</t>
         </is>
       </c>
       <c r="H103" s="56" t="inlineStr">
@@ -7685,7 +7685,7 @@
       </c>
       <c r="G113" s="59" t="inlineStr">
         <is>
-          <t>"L'idéologie du désir par le Précepteur"</t>
+          <t xml:space="preserve">"L'idéologie du désir par Le Précepteur</t>
         </is>
       </c>
       <c r="H113" s="59" t="inlineStr">
@@ -8540,7 +8540,7 @@
       </c>
       <c r="G127" s="90" t="inlineStr">
         <is>
-          <t>le message des Upanishads par BAGLIS TV</t>
+          <t xml:space="preserve">le message des Upanishads par Baglis Tv</t>
         </is>
       </c>
       <c r="H127" s="48" t="inlineStr">
@@ -8720,7 +8720,7 @@
       </c>
       <c r="G130" s="59" t="inlineStr">
         <is>
-          <t>"Jacques Bouveresse, Prodiges et vertiges de l'analogie" par philosophie Analytique</t>
+          <t xml:space="preserve">"Jacques Bouveresse, Prodiges et vertiges de l'analogie" par Philosophie Analytique</t>
         </is>
       </c>
       <c r="H130" s="65" t="inlineStr">

--- a/data/frise-philosophes-france.xlsx
+++ b/data/frise-philosophes-france.xlsx
@@ -1375,7 +1375,7 @@
 &lt;dd&gt; -  &lt;a href="https://www.youtube.com/watch?v=9gFUQXcllFI"  title="Le Duopole de Cournot : modèle et généralisation à N firmes par NeoEconomicus"&gt;Théorie du duopole&lt;/a&gt; : Premier modèle formel de concurrence entre deux entreprises (duopole). Il a analysé comment deux vendeurs sur un marché déterminent leurs quantités produites pour maximiser leurs profits, en tenant compte des actions de l'autre. Ce modèle est devenu un pilier de la théorie microéconomique. &lt;/dd&gt; 
 &lt;dd&gt; - Équilibre de Cournot : Concept d'équilibre, où chaque entreprise choisit sa production de manière optimale, étant donné la production de l'autre. Cet équilibre est maintenant connu sous le nom d'équilibre de Cournot. &lt;/dd&gt; 
 &lt;dd&gt; - Analyse des monopoles : Comment un vendeur unique sur un marché peut fixer les prix pour maximiser son profit. &lt;/dd&gt; 
-&lt;dd&gt; - Application des mathématiques à l'économie : Mathématiques pour modéliser les comportements économiques.&lt;/dd&gt; &lt;p&gt; Il était un philosophe des sciences et a écrit sur des sujets tels que la probabilité, la causalité et la nature de la connaissance scientifique.  Dans son ouvrage"Exposition de la théorie des chances et des probabilités" , il a exploré les fondements des probabilités et leur application à des problèmes pratiques.  Dans son livre "Matérialisme, vitalisme, rationalisme", il porte ses réflexions sur les limites de la science et les questions métaphysiques. &lt;/p&gt; &lt;p&gt; Il a marqué l'histoire de la pensée économique en introduisant des méthodes mathématiques rigoureuses et ses travaux sur le duopole, les monopoles et l'équilibre économique restent des références essentielles dans l'étude de la concurrence et des marchés. &lt;/p&gt; </t>
+&lt;dd&gt; - Application des mathématiques à l'économie : Mathématiques pour modéliser les comportements économiques.&lt;/dd&gt; &lt;p&gt; Il était un philosophe des sciences et a écrit sur des sujets tels que la probabilité, la causalité et la nature de la connaissance scientifique.  Dans son ouvrage"Exposition de la théorie des chances et des probabilités", il a exploré les fondements des probabilités et leur application à des problèmes pratiques.  Dans son livre "Matérialisme, vitalisme, rationalisme", il porte ses réflexions sur les limites de la science et les questions métaphysiques. &lt;/p&gt; &lt;p&gt; Il a marqué l'histoire de la pensée économique en introduisant des méthodes mathématiques rigoureuses et ses travaux sur le duopole, les monopoles et l'équilibre économique restent des références essentielles dans l'étude de la concurrence et des marchés. &lt;/p&gt; </t>
         </is>
       </c>
       <c r="F9" s="57" t="inlineStr">
@@ -1555,7 +1555,7 @@
       </c>
       <c r="E12" s="56" t="inlineStr">
         <is>
-          <t>&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/F%C3%A9lix_Ravaisson"  title=" Wikipedia"&gt;Félix RAVAISSON&lt;/a&gt; était un philosophe du spiritualisme français . Ancien élève de l'École normale supérieure et disciple de Schelling, il occupa des postes importants dans l'administration culturelle française, notamment comme inspecteur général des bibliothèques et conservateur au département des antiquités du Louvre. Ses travaux philosophiques, bien que peu nombreux, exercèrent une influence profonde et durable sur la pensée française. &lt;/p&gt; &lt;p&gt; Son œuvre maîtresse, &lt;em&gt;De l'habitude&lt;/em&gt; (1838), est un court essai d'une originalité remarquable. Il y montre que l'habitude, loin d'être une simple répétition mécanique, révèle la structure profonde de l'existence : à travers elle, ce qui était d'abord conscient et volontaire devient naturel et spontané, révélant ainsi une continuité entre la nature et l'esprit. L'habitude est pour lui la médiation entre la nature et la liberté, entre le corps et l'âme. Cette analyse préfigure des thématiques centrales de  &lt;a href="https://fr.wikipedia.org/wiki/Ph%C3%A9nom%C3%A9nologie_(philosophie)"  title="Phenomenologie par Wikipedia"&gt;la phénoménologie &lt;/a&gt; et de la philosophie du corps. &lt;/p&gt; &lt;p&gt; Dans son &lt;em&gt;Rapport sur la philosophie en France au XIXe siècle&lt;/em&gt; (1867), il dressait un panorama de la pensée française contemporaine et &lt;a href="https://www.youtube.com/watch?v=1W8EWIT3Gpc"  title="French Spititualism in Phenomenology par Socratic Swansongs"&gt;défendait un spiritualisme &lt;/a&gt; fondé sur la grâce plutôt que sur l'effort, proche d'une inspiration néo-platonicienne et chrétienne. Henri Bergson reconnut en lui l'un de ses plus grands prédécesseurs, saluant sa conception d'une réalité vivante et active qui déborde toute analyse mécanique. Ravaisson reste une référence essentielle pour comprendre l'émergence du bergsonisme et de la phénoménologie en France. &lt;/p&gt;</t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/F%C3%A9lix_Ravaisson"  title=" Wikipedia"&gt;Félix RAVAISSON&lt;/a&gt; était un philosophe du spiritualisme français. Ancien élève de l'École normale supérieure et disciple de Schelling, il occupa des postes importants dans l'administration culturelle française, notamment comme inspecteur général des bibliothèques et conservateur au département des antiquités du Louvre. Ses travaux philosophiques, bien que peu nombreux, exercèrent une influence profonde et durable sur la pensée française. &lt;/p&gt; &lt;p&gt; Son œuvre maîtresse, &lt;em&gt;De l'habitude&lt;/em&gt; (1838), est un court essai d'une originalité remarquable. Il y montre que l'habitude, loin d'être une simple répétition mécanique, révèle la structure profonde de l'existence : à travers elle, ce qui était d'abord conscient et volontaire devient naturel et spontané, révélant ainsi une continuité entre la nature et l'esprit. L'habitude est pour lui la médiation entre la nature et la liberté, entre le corps et l'âme. Cette analyse préfigure des thématiques centrales de  &lt;a href="https://fr.wikipedia.org/wiki/Ph%C3%A9nom%C3%A9nologie_(philosophie)"  title="Phenomenologie par Wikipedia"&gt;la phénoménologie &lt;/a&gt; et de la philosophie du corps. &lt;/p&gt; &lt;p&gt; Dans son &lt;em&gt;Rapport sur la philosophie en France au XIXe siècle&lt;/em&gt; (1867), il dressait un panorama de la pensée française contemporaine et &lt;a href="https://www.youtube.com/watch?v=1W8EWIT3Gpc"  title="French Spititualism in Phenomenology par Socratic Swansongs"&gt;défendait un spiritualisme &lt;/a&gt; fondé sur la grâce plutôt que sur l'effort, proche d'une inspiration néo-platonicienne et chrétienne. Henri Bergson reconnut en lui l'un de ses plus grands prédécesseurs, saluant sa conception d'une réalité vivante et active qui déborde toute analyse mécanique. Ravaisson reste une référence essentielle pour comprendre l'émergence du bergsonisme et de la phénoménologie en France. &lt;/p&gt;</t>
         </is>
       </c>
       <c r="F12" s="54" t="inlineStr">
@@ -3354,7 +3354,7 @@
       </c>
       <c r="E42" s="59" t="inlineStr">
         <is>
-          <t>&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/%C3%89lie_Hal%C3%A9vy"  title=" Wikipedia"&gt;Élie HALÉVY&lt;/a&gt; était un philosophe et historien français, auteur d'une œuvre monumentale sur l'histoire de la pensée et de la société britannique. Né à Paris dans une famille de la haute bourgeoisie intellectuelle, normalien et agrégé de philosophie, il consacra l'essentiel de sa carrière à l'École libre des sciences politiques. Philosophe de formation et historien par vocation, il fut l'un des &lt;a href="https://www.youtube.com/watch?v=EYYWI9q8myE" title="Elie Halévy, les œuvres complètes par les belles lettres"&gt; penseurs les plus lucides &lt;/a&gt;  sur les relations entre libéralisme, démocratie et socialisme. &lt;/p&gt; &lt;p&gt; Son œuvre historique la plus importante, &lt;em&gt;La Formation du radicalisme philosophique&lt;/em&gt; (3 volumes, 1901-1904), est une étude magistrale de l'utilitarisme benthamien et de son influence sur le libéralisme anglais. Il y montre avec une rigueur exemplaire comment la doctrine de l'utilité et du calcul des plaisirs et des peines s'articula avec la pensée économique de Ricardo et les réformes politiques et sociales de la Grande-Bretagne au XIXe siècle. Cette œuvre reste une référence indispensable pour comprendre les fondements intellectuels du libéralisme moderne. &lt;/p&gt; &lt;p&gt; Son autre grand projet, &lt;em&gt;L'Histoire du peuple anglais au XIXe siècle&lt;/em&gt; (6 volumes, publiés entre 1912 et 1932), est une fresque sans équivalent de la société britannique victorienne, alliant l'analyse politique, économique, religieuse et culturelle. Sa fameuse conférence de 1929, &lt;em&gt; &lt;a href="https://legrandcontinent.eu/fr/2025/01/03/tel-est-le-siecle-elie-halevy-et-la-resistance-a-lere-des-tyrannies/" title="l’ère des tyrannies par grand continent"&gt;L'Ère des tyrannies &lt;/a&gt; &lt;/em&gt;, prévit avec une lucidité saisissante l'émergence des totalitarismes en Europe. Il représente l'un des meilleurs exemples de l'alliance entre rigueur philosophique et ambition historique dans la tradition intellectuelle française. &lt;/p&gt;   &lt;audio controls title=les œuvres de elie Halévy par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/12014-06.04.2016-ITEMA_20954575-2016C18009S0097-21.mp3" type="audio/mpeg" align="center"&gt;&lt;/audio&gt;</t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/%C3%89lie_Hal%C3%A9vy"  title=" Wikipedia"&gt;Élie HALÉVY&lt;/a&gt; était un philosophe et historien français, auteur d'une œuvre monumentale sur l'histoire de la pensée et de la société britannique. Né à Paris dans une famille de la haute bourgeoisie intellectuelle, normalien et agrégé de philosophie, il consacra l'essentiel de sa carrière à l'École libre des sciences politiques. Philosophe de formation et historien par vocation, il fut l'un des &lt;a href="https://www.youtube.com/watch?v=EYYWI9q8myE" title="Elie Halévy, les œuvres complètes par les belles lettres"&gt; penseurs les plus lucides &lt;/a&gt;  sur les relations entre libéralisme, démocratie et socialisme. &lt;/p&gt; &lt;p&gt; Son œuvre historique la plus importante, &lt;em&gt;La Formation du radicalisme philosophique&lt;/em&gt; (3 volumes, 1901-1904), est une étude magistrale de l'utilitarisme benthamien et de son influence sur le libéralisme anglais. Il y montre avec une rigueur exemplaire comment la doctrine de l'utilité et du calcul des plaisirs et des peines s'articula avec la pensée économique de Ricardo et les réformes politiques et sociales de la Grande-Bretagne au XIXe siècle. Cette œuvre reste une référence indispensable pour comprendre les fondements intellectuels du libéralisme moderne. &lt;/p&gt; &lt;p&gt; Son autre grand projet, &lt;em&gt;L'Histoire du peuple anglais au XIXe siècle&lt;/em&gt; (6 volumes, publiés entre 1912 et 1932), est une fresque sans équivalent de la société britannique victorienne, alliant l'analyse politique, économique, religieuse et culturelle. Sa fameuse conférence de 1929, &lt;em&gt; &lt;a href="https://legrandcontinent.eu/fr/2025/01/03/tel-est-le-siecle-elie-halevy-et-la-resistance-a-lere-des-tyrannies/" title="l’ère des tyrannies par grand continent"&gt;L'Ère des tyrannies&lt;/a&gt; &lt;/em&gt;, prévit avec une lucidité saisissante l'émergence des totalitarismes en Europe. Il représente l'un des meilleurs exemples de l'alliance entre rigueur philosophique et ambition historique dans la tradition intellectuelle française. &lt;/p&gt;   &lt;audio controls title=les œuvres de elie Halévy par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/12014-06.04.2016-ITEMA_20954575-2016C18009S0097-21.mp3" type="audio/mpeg" align="center"&gt;&lt;/audio&gt;</t>
         </is>
       </c>
       <c r="F42" s="57" t="inlineStr">
@@ -4193,7 +4193,7 @@
       </c>
       <c r="E56" s="59" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Gaston_Bachelard"  title=" Wikipedia"&gt;Gaston BACHELARD&lt;/a&gt; était un  philosophe français des sciences et de la poésie et  resta la figure emblématique majeure de l’épistémologie française. Il mena de front une réflexion sur la raison scientifique et sur l'imagination poétique, qu'il considérait comme deux activités distinctes de l'esprit humain.  &lt;a href="https://www.youtube.com/watch?v=UY6EZsKqb8w" title="Une Vie, une œuvre : Gaston Bachelard, une enfance parmi les eaux par Rien ne veut rien dire"&gt;Sa philosophie&lt;/a&gt; peut être abordée selon deux axes principaux, souvent appelés "le diurne" (la raison, la science) et "le nocturne" (le rêve, la poésie). &lt;/p&gt; &lt;p&gt;  Il  a révolutionné l'épistémologie en insistant sur le fait que la science moderne (la physique quantique, la relativité) n'est pas une simple continuation ou un perfectionnement de la connaissance ordinaire, mais une rupture radicale avec elle. Pour comprendre le monde tel que le révèlent Einstein ou Bohr, il faut briser ("rompre") avec les intuitions, les préjugés et les images sensibles qui structurent notre expérience commune du monde. L'objet scientifique (un atome, un électron) n'est pas un "petit caillou" ; il est une construction mathématique qui défie l'imagination.  Ce qui empêche cette rupture, ce sont les "obstacles" ancrés dans notre esprit : l'expérience première, l'opinion (doxa), les métaphores trop faciles. Le travail du scientifique est un combat contre ces obstacles pour laisser place à une raison abstraite et rigoureuse.&lt;/p&gt; &lt;p&gt;  Il montre que le progrès scientifique se fait souvent par la négation des théories anciennes. Une nouvelle théorie ne complète pas l'ancienne ; elle la contredit et la dépasse.  &lt;a href="https://www.persee.fr/doc/phlou_0035-3841_1963_num_61_72_5231"title="Psychanalyse de la raison chez Gaston Bachelard par Persée"&gt; La raison scientifique&lt;/a&gt;   doit donc être "ouverte", dialectique, capable de se réformer en permanence ("rationalisme appliqué" ou "matérialisme technique"). &lt;/p&gt; &lt;p&gt; Parallèlement à son  &lt;a href="https://www.youtube.com/watch?v=HlrsFGSneh4" title="Gaston Bachelard, philosophe français des sciences par Mathieu"&gt;travail sur la science&lt;/a&gt; , il a développé une philosophie de l'imagination matérielle et de la poésie, peut-être même plus célèbre aujourd'hui. Il ne s'intéresse pas aux images comme copies du réel, mais comme forces productrices. Il étudie comment  &lt;a href="https://www.youtube.com/watch?v=X05w-ggXXQM" title="Gaston Bachelard s'exprime sur le dormeur éveillé par l'élan du savoir"&gt; l'esprit rêveur&lt;/a&gt; entre en communion avec les éléments matériels primordiaux (le feu, &lt;a href="https://www.youtube.com/watch?v=Z65E177AEHc" title="Gaston Bachelard La poésie et l'eau éveillé par Résonances"&gt;  l'eau&lt;/a&gt;, l'air, la terre). Chaque élément inspire un réseau d'images et de sentiments spécifiques. Il distingue la rêverie (état de conscience poétique, heureux, dirigé vers le monde) du rêve nocturne (inconscient, souvent perturbé). La rêverie est une activité créatrice et solitaire qui nous reconnecte à l'enfance et au bonheur d'imaginer. &lt;/p&gt; &lt;p&gt; Il nous invite ainsi à une vie intellectuelle complète : à être rigoureux dans notre quête de vérité scientifique et à cultiver, par la poésie, une âme rêveuse et émerveillée par le monde. &lt;/p&gt; &lt;audio controls title="Gaston Bachelard : "Nous sommes des dormeurs éveillés, des rêveurs lucides" par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/24554-19.01.2024-ITEMA_23620023-2016C3372E0751-21.mp3" type="audio/mpeg" align="center"&gt;&lt;/audio&gt;  </t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Gaston_Bachelard"  title=" Wikipedia"&gt;Gaston BACHELARD&lt;/a&gt; était un  philosophe français des sciences et de la poésie et  resta la figure emblématique majeure de l’épistémologie française. Il mena de front une réflexion sur la raison scientifique et sur l'imagination poétique, qu'il considérait comme deux activités distinctes de l'esprit humain.  &lt;a href="https://www.youtube.com/watch?v=UY6EZsKqb8w" title="Une Vie, une œuvre : Gaston Bachelard, une enfance parmi les eaux par Rien ne veut rien dire"&gt;Sa philosophie&lt;/a&gt; peut être abordée selon deux axes principaux, souvent appelés "le diurne" (la raison, la science) et "le nocturne" (le rêve, la poésie). &lt;/p&gt; &lt;p&gt;  Il  a révolutionné l'épistémologie en insistant sur le fait que la science moderne (la physique quantique, la relativité) n'est pas une simple continuation ou un perfectionnement de la connaissance ordinaire, mais une rupture radicale avec elle. Pour comprendre le monde tel que le révèlent Einstein ou Bohr, il faut briser ("rompre") avec les intuitions, les préjugés et les images sensibles qui structurent notre expérience commune du monde. L'objet scientifique (un atome, un électron) n'est pas un "petit caillou" ; il est une construction mathématique qui défie l'imagination.  Ce qui empêche cette rupture, ce sont les "obstacles" ancrés dans notre esprit : l'expérience première, l'opinion (doxa), les métaphores trop faciles. Le travail du scientifique est un combat contre ces obstacles pour laisser place à une raison abstraite et rigoureuse.&lt;/p&gt; &lt;p&gt;  Il montre que le progrès scientifique se fait souvent par la négation des théories anciennes. Une nouvelle théorie ne complète pas l'ancienne ; elle la contredit et la dépasse.  &lt;a href="https://www.persee.fr/doc/phlou_0035-3841_1963_num_61_72_5231"title="Psychanalyse de la raison chez Gaston Bachelard par Persée"&gt; La raison scientifique&lt;/a&gt;   doit donc être "ouverte", dialectique, capable de se réformer en permanence ("rationalisme appliqué" ou "matérialisme technique"). &lt;/p&gt; &lt;p&gt; Parallèlement à son  &lt;a href="https://www.youtube.com/watch?v=HlrsFGSneh4" title="Gaston Bachelard, philosophe français des sciences par Mathieu"&gt;travail sur la science&lt;/a&gt;, il a développé une philosophie de l'imagination matérielle et de la poésie, peut-être même plus célèbre aujourd'hui. Il ne s'intéresse pas aux images comme copies du réel, mais comme forces productrices. Il étudie comment  &lt;a href="https://www.youtube.com/watch?v=X05w-ggXXQM" title="Gaston Bachelard s'exprime sur le dormeur éveillé par l'élan du savoir"&gt; l'esprit rêveur&lt;/a&gt; entre en communion avec les éléments matériels primordiaux (le feu, &lt;a href="https://www.youtube.com/watch?v=Z65E177AEHc" title="Gaston Bachelard La poésie et l'eau éveillé par Résonances"&gt;  l'eau&lt;/a&gt;, l'air, la terre). Chaque élément inspire un réseau d'images et de sentiments spécifiques. Il distingue la rêverie (état de conscience poétique, heureux, dirigé vers le monde) du rêve nocturne (inconscient, souvent perturbé). La rêverie est une activité créatrice et solitaire qui nous reconnecte à l'enfance et au bonheur d'imaginer. &lt;/p&gt; &lt;p&gt; Il nous invite ainsi à une vie intellectuelle complète : à être rigoureux dans notre quête de vérité scientifique et à cultiver, par la poésie, une âme rêveuse et émerveillée par le monde. &lt;/p&gt; &lt;audio controls title="Gaston Bachelard : "Nous sommes des dormeurs éveillés, des rêveurs lucides" par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/24554-19.01.2024-ITEMA_23620023-2016C3372E0751-21.mp3" type="audio/mpeg" align="center"&gt;&lt;/audio&gt;  </t>
         </is>
       </c>
       <c r="F56" s="57" t="inlineStr">
@@ -4851,7 +4851,7 @@
       </c>
       <c r="E67" s="56" t="inlineStr">
         <is>
-          <t>&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Jean_Guitton" title=" Wikipedia"&gt;Jean GUITTON&lt;/a&gt; était un philosophe, écrivain et académicien français, figure majeure de la pensée catholique car sa pensée est profondément ancrée dans le catholicisme. Il a cherché à réconcilier la foi et la raison, le christianisme et les questionnements contemporains. Il s'est intéressé aux convergences entre la science la plus récente (notamment la physique quantique) et le christianisme, comme en témoigne son livre  &lt;a href="https://www.youtube.com/watch?v=QuHD0eMvmkc"  title="Jean Guitton, Igor et Grichka Bogdanoff "Dieu et la science" par Ina Sciences"&gt;"Dieu et la science"&lt;/a&gt; co-écrit avec les frères Bogdanov. &lt;/p&gt; &lt;p&gt;  Ses œuvres abordent des sujets fondamentaux tels que le temps et l'éternité (sa thèse portait sur Plotin et Saint Augustin), l'amour humain et divin, le problème de Jésus, et la question du sens de l'existence.  Il était connu pour sa capacité au dialogue et à la réflexion ouverte. Il fut notamment le seul laïc autorisé par le Pape à siéger au Concile Vatican II, ce qui souligne son rôle important dans la vie intellectuelle et religieuse de son temps. &lt;/p&gt; &lt;p&gt; Il  a laissé une œuvre considérable et variée, comprenant des essais philosophiques, des critiques religieuses, des biographies et des écrits plus personnels. Parmi ses titres notables, on peut citer "La philosophie de Newman", "Le Problème de Jésus", "L'Amour humain",   &lt;a href="https://www.persee.fr/doc/phlou_0035-3841_1952_num_50_25_7895_t1_0187_0000_2"  title="Jean Guitton, Le travail intellectuel. Conseils à ceux qui étudient et à ceux qui écrivent par Persée"&gt;"Le Travail intellectuel"&lt;/a&gt; , "Dialogues avec Paul VI", "Profils parallèles", et "La pensée et la guerre". &lt;/p&gt; &lt;p&gt; Il fut une figure intellectuelle  marquante dont la philosophie cherchait à unir la profondeur de la foi catholique avec les exigences de la raison et les évolutions du monde moderne. &lt;/p&gt;</t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Jean_Guitton" title=" Wikipedia"&gt;Jean GUITTON&lt;/a&gt; était un philosophe, écrivain et académicien français, figure majeure de la pensée catholique car sa pensée est profondément ancrée dans le catholicisme. Il a cherché à réconcilier la foi et la raison, le christianisme et les questionnements contemporains. Il s'est intéressé aux convergences entre la science la plus récente (notamment la physique quantique) et le christianisme, comme en témoigne son livre  &lt;a href="https://www.youtube.com/watch?v=QuHD0eMvmkc"  title="Jean Guitton, Igor et Grichka Bogdanoff "Dieu et la science" par Ina Sciences"&gt;"Dieu et la science"&lt;/a&gt; co-écrit avec les frères Bogdanov. &lt;/p&gt; &lt;p&gt;  Ses œuvres abordent des sujets fondamentaux tels que le temps et l'éternité (sa thèse portait sur Plotin et Saint Augustin), l'amour humain et divin, le problème de Jésus, et la question du sens de l'existence.  Il était connu pour sa capacité au dialogue et à la réflexion ouverte. Il fut notamment le seul laïc autorisé par le Pape à siéger au Concile Vatican II, ce qui souligne son rôle important dans la vie intellectuelle et religieuse de son temps. &lt;/p&gt; &lt;p&gt; Il  a laissé une œuvre considérable et variée, comprenant des essais philosophiques, des critiques religieuses, des biographies et des écrits plus personnels. Parmi ses titres notables, on peut citer "La philosophie de Newman", "Le Problème de Jésus", "L'Amour humain",   &lt;a href="https://www.persee.fr/doc/phlou_0035-3841_1952_num_50_25_7895_t1_0187_0000_2"  title="Jean Guitton, Le travail intellectuel. Conseils à ceux qui étudient et à ceux qui écrivent par Persée"&gt;"Le Travail intellectuel"&lt;/a&gt;, "Dialogues avec Paul VI", "Profils parallèles", et "La pensée et la guerre". &lt;/p&gt; &lt;p&gt; Il fut une figure intellectuelle  marquante dont la philosophie cherchait à unir la profondeur de la foi catholique avec les exigences de la raison et les évolutions du monde moderne. &lt;/p&gt;</t>
         </is>
       </c>
       <c r="F67" s="54" t="inlineStr">
@@ -5225,7 +5225,7 @@
       </c>
       <c r="E73" s="59" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Jean-Paul_Sartre"   title=" Wikipedia"&gt;Jean-Paul SARTRE&lt;/a&gt; était un philosophe Français &lt;a href="https://www.youtube.com/watch?v=kX3saEPOG-g&amp;t=51s&amp;ab_channel=Coursitout" title="Nous sommes condamnés à être libre par Yapi Florent AKICHI"&gt;Existentialiste&lt;/a&gt;, qui met l'accent sur la liberté humaine et la responsabilité personnelle dans la détermination de la signification de la vie.  Il n’y a pas d’essence humaine figée et préétablie, essence qui précéderait l’existence. &lt;/p&gt; &lt;p&gt;  Dans son œuvre  "L'Être et le Néant", il développe le fait que les individus sont définis par leurs actions et leurs choix, et non par des caractéristiques innées ou des conditions sociales. Pour lui, exister, c’est être là, dans un univers absurde et contingent, l’homme surgit et il y dessine son chemin. &lt;/p&gt; &lt;p&gt;  Il a exploré les inconvénients et les joies d'être fondamentalement  &lt;a href="https://www.youtube.com/watch?v=xN0ysLkGiP8&amp;ab_channel=LePr%C3%A9cepteur"   title="Nous sommes condamnés à être libre par le Précepteur"&gt;Libre&lt;/a&gt;. Il a également été un militant politique actif et un fervent défenseur de la liberté et de la justice sociale.&lt;/p&gt; &lt;p&gt;   Il accorde une très grande importance au &lt;a href="https://www.youtube.com/watch?v=BJIM41TnDHI&amp;ab_channel=LePr%C3%A9cepteur"  title="Le regard des autres par le Précepteur"&gt;"regard des autres"&lt;/a&gt; et une de ses citations les plus connus "l'enfer, c'est les autres", huis clos théatral écrit en 1943 et dans lequel il illustre parfaitement la difficile coexistence des consciences, le fait qu'autrui est ce qui nous aliène et nous enferme dans une nature donnée, ce qui nous prive de liberté.&lt;/p&gt; &lt;p&gt;   Il partagera pendant plus de 50 ans sa vie avec Simone de BEAUVOIR dans une &lt;a href="https://www.youtube.com/watch?v=5BCjCYimqlc&amp;ab_channel=LePr%C3%A9cepteur"  title="L'amour par le Précepteur"&gt;relation libre&lt;/a&gt; , couple mythique et anticonformiste.&lt;/p&gt;   &lt;audio controls title="Le roman comme expérience par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/22054-28.03.2021-ITEMA_22624288-2017C24632S0115.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt; 
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Jean-Paul_Sartre"   title=" Wikipedia"&gt;Jean-Paul SARTRE&lt;/a&gt; était un philosophe Français &lt;a href="https://www.youtube.com/watch?v=kX3saEPOG-g&amp;t=51s&amp;ab_channel=Coursitout" title="Nous sommes condamnés à être libre par Yapi Florent AKICHI"&gt;Existentialiste&lt;/a&gt;, qui met l'accent sur la liberté humaine et la responsabilité personnelle dans la détermination de la signification de la vie.  Il n’y a pas d’essence humaine figée et préétablie, essence qui précéderait l’existence. &lt;/p&gt; &lt;p&gt;  Dans son œuvre  "L'Être et le Néant", il développe le fait que les individus sont définis par leurs actions et leurs choix, et non par des caractéristiques innées ou des conditions sociales. Pour lui, exister, c’est être là, dans un univers absurde et contingent, l’homme surgit et il y dessine son chemin. &lt;/p&gt; &lt;p&gt;  Il a exploré les inconvénients et les joies d'être fondamentalement  &lt;a href="https://www.youtube.com/watch?v=xN0ysLkGiP8&amp;ab_channel=LePr%C3%A9cepteur"   title="Nous sommes condamnés à être libre par le Précepteur"&gt;Libre&lt;/a&gt;. Il a également été un militant politique actif et un fervent défenseur de la liberté et de la justice sociale.&lt;/p&gt; &lt;p&gt;   Il accorde une très grande importance au &lt;a href="https://www.youtube.com/watch?v=BJIM41TnDHI&amp;ab_channel=LePr%C3%A9cepteur"  title="Le regard des autres par le Précepteur"&gt;"regard des autres"&lt;/a&gt; et une de ses citations les plus connus "l'enfer, c'est les autres", huis clos théatral écrit en 1943 et dans lequel il illustre parfaitement la difficile coexistence des consciences, le fait qu'autrui est ce qui nous aliène et nous enferme dans une nature donnée, ce qui nous prive de liberté.&lt;/p&gt; &lt;p&gt;   Il partagera pendant plus de 50 ans sa vie avec Simone de BEAUVOIR dans une &lt;a href="https://www.youtube.com/watch?v=5BCjCYimqlc&amp;ab_channel=LePr%C3%A9cepteur"  title="L'amour par le Précepteur"&gt;relation libre&lt;/a&gt;, couple mythique et anticonformiste.&lt;/p&gt;   &lt;audio controls title="Le roman comme expérience par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/22054-28.03.2021-ITEMA_22624288-2017C24632S0115.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt; 
 </t>
         </is>
       </c>
@@ -5352,7 +5352,7 @@
       </c>
       <c r="E75" s="75" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Emmanuel_Mounier"  title=" Wikipedia"&gt;Emmanuel MOUNIER&lt;/a&gt; était un philosophe français connu comme le fondateur du personnalisme, un courant qui veut remettre la personne humaine au centre de la pensée et de la vie sociale. &lt;/p&gt; &lt;p&gt; Sa philosophie naît dans un contexte de crise : montée du capitalisme, du fascisme, du marxisme et sentiment que l’homme est écrasé par des systèmes trop abstraits. Il refuse à la fois l’individualisme, qui isole l’être humain, et le collectivisme, qui le dissout dans le groupe. &lt;/p&gt; &lt;p&gt; Pour lui, la personne n’est pas seulement un individu biologique ou social.  &lt;a href="https://www.youtube.com/watch?v=T8tZ7E0D49k"  title="emmanuel mounier par kto tv"&gt;"C’est un être libre, &lt;/a&gt; responsable, ouvert aux autres et appelé à se construire dans l’engagement, la relation et la vie communautaire. Cette idée donne à sa pensée une dimension à la fois morale, politique et spirituelle. &lt;/p&gt; &lt;p&gt; Il est aussi profondément chrétien, mais un chrétien engagé dans le monde. Avec  &lt;a href="https://maitron.fr/mounier-emmanuel-hippolyte-henri/"  title="emmanuel mounier par maitron"&gt;la revue Esprit, &lt;/a&gt; qu’il fonde en 1932, il cherche à faire dialoguer la foi, la réflexion philosophique et les grands problèmes de son époque, comme la guerre, la démocratie ou la justice sociale. Il défend une forme de « révolution spirituelle », c’est-à-dire une transformation intérieure et sociale de l’homme et des institutions. &lt;/p&gt; &lt;p&gt; la philosophie de Mounier propose une vision exigeante de l’humain : la personne doit être respectée dans sa dignité, sa liberté et sa vocation relationnelle. Son influence a été importante sur la pensée chrétienne, la philosophie sociale et les débats sur la démocratie au XXe siècle. &lt;/p&gt; &lt;audio controls title="Les murs blancs revue esprit par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/17473-14.03.2021-ITEMA_22602800-2021B20595S0073.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt; 
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Emmanuel_Mounier"  title=" Wikipedia"&gt;Emmanuel MOUNIER&lt;/a&gt; était un philosophe français connu comme le fondateur du personnalisme, un courant qui veut remettre la personne humaine au centre de la pensée et de la vie sociale. &lt;/p&gt; &lt;p&gt; Sa philosophie naît dans un contexte de crise : montée du capitalisme, du fascisme, du marxisme et sentiment que l’homme est écrasé par des systèmes trop abstraits. Il refuse à la fois l’individualisme, qui isole l’être humain, et le collectivisme, qui le dissout dans le groupe. &lt;/p&gt; &lt;p&gt; Pour lui, la personne n’est pas seulement un individu biologique ou social.  &lt;a href="https://www.youtube.com/watch?v=T8tZ7E0D49k"  title="emmanuel mounier par kto tv"&gt;"C’est un être libre, &lt;/a&gt; responsable, ouvert aux autres et appelé à se construire dans l’engagement, la relation et la vie communautaire. Cette idée donne à sa pensée une dimension à la fois morale, politique et spirituelle. &lt;/p&gt; &lt;p&gt; Il est aussi profondément chrétien, mais un chrétien engagé dans le monde. Avec  &lt;a href="https://maitron.fr/mounier-emmanuel-hippolyte-henri/"  title="emmanuel mounier par maitron"&gt;la revue Esprit, &lt;/a&gt; qu’il fonde en 1932, il cherche à faire dialoguer la foi, la réflexion philosophique et les grands problèmes de son époque, comme la guerre, la démocratie ou la justice sociale. Il défend une forme de « révolution spirituelle », c’est-à-dire une transformation intérieure et sociale de l’homme et des institutions. &lt;/p&gt; &lt;p&gt; La philosophie de Mounier propose une vision exigeante de l’humain : la personne doit être respectée dans sa dignité, sa liberté et sa vocation relationnelle. Son influence a été importante sur la pensée chrétienne, la philosophie sociale et les débats sur la démocratie au XXe siècle. &lt;/p&gt; &lt;audio controls title="Les murs blancs revue esprit par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/17473-14.03.2021-ITEMA_22602800-2021B20595S0073.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt; 
 </t>
         </is>
       </c>
@@ -5482,7 +5482,7 @@
       </c>
       <c r="E77" s="56" t="inlineStr">
         <is>
-          <t>&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Maurice_de_Gandillac"  title=" Wikipedia"&gt;Maurice de GANDILLAC&lt;/a&gt;  était un philosophe français spécialiste de la pensée médiévale et de la Renaissance, connu pour son ouverture d'esprit et son &lt;a href="https://www.youtube.com/watch?v=wMU50jMSLdo"  title=" Maurice de Gandillac et les décades de Pontigny (1926-1938) par adriano meis"&gt;rôle de passeur &lt;/a&gt; entre traditions philosophiques. Professeur à la Sorbonne pendant trois décennies, il a influencé des générations d'étudiants et traduit des auteurs majeurs comme Nicolas de Cues, Walter Benjamin et Nietzsche. Catholique initialement proche de Maritain et Mounier, il s'engage dans des revues comme Esprit et Dieu vivant, et préside les rencontres de Cerisy de 1954 à 1999. &lt;/p&gt; &lt;p&gt;  Sa thèse de 1941 (La Philosophie de Nicolas de Cues) et de multiples traductions (dont De docta ignorantia) en font l'un des principaux introducteurs du Cusain en France, explorant l'infini, la "docte ignorance" et l'unité des contraires. Premier à traduire Walter Benjamin en français, ainsi que Novalis, Hegel, Nietzsche (avec Deleuze), Ernst Bloch et Dante (Divine Comédie). &lt;/p&gt; &lt;p&gt; Il incarne un &lt;a href="https://www.persee.fr/doc/homso_0018-4306_1999_num_131_1_3626"  title="Maurice de Gandillac, Le siècle traversé. Souvenirs de neuf décennies, Paris, Albin Michel, 1998 par Persée"&gt;humanisme érudit &lt;/a&gt;, liant Moyen Âge, Renaissance et modernité, avec un souci des silences et opacités de la pensée face à l'indicible. Son œuvre, mêlant histoire philosophique, poésie (Bestiaire latéral, 1974) et dialogues interdisciplinaires, reste une référence pour l'étude des marges de la rationalité. &lt;/p&gt;</t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Maurice_de_Gandillac"  title=" Wikipedia"&gt;Maurice de GANDILLAC&lt;/a&gt;  était un philosophe français spécialiste de la pensée médiévale et de la Renaissance, connu pour son ouverture d'esprit et son &lt;a href="https://www.youtube.com/watch?v=wMU50jMSLdo"  title=" Maurice de Gandillac et les décades de Pontigny (1926-1938) par adriano meis"&gt;rôle de passeur &lt;/a&gt; entre traditions philosophiques. Professeur à la Sorbonne pendant trois décennies, il a influencé des générations d'étudiants et traduit des auteurs majeurs comme Nicolas de Cues, Walter Benjamin et Nietzsche. Catholique initialement proche de Maritain et Mounier, il s'engage dans des revues comme Esprit et Dieu vivant, et préside les rencontres de Cerisy de 1954 à 1999. &lt;/p&gt; &lt;p&gt;  Sa thèse de 1941 (La Philosophie de Nicolas de Cues) et de multiples traductions (dont De docta ignorantia) en font l'un des principaux introducteurs du Cusain en France, explorant l'infini, la "docte ignorance" et l'unité des contraires. Premier à traduire Walter Benjamin en français, ainsi que Novalis, Hegel, Nietzsche (avec Deleuze), Ernst Bloch et Dante (Divine Comédie). &lt;/p&gt; &lt;p&gt; Il incarne un &lt;a href="https://www.persee.fr/doc/homso_0018-4306_1999_num_131_1_3626"  title="Maurice de Gandillac, Le siècle traversé. Souvenirs de neuf décennies, Paris, Albin Michel, 1998 par Persée"&gt;humanisme érudit&lt;/a&gt;, liant Moyen Âge, Renaissance et modernité, avec un souci des silences et opacités de la pensée face à l'indicible. Son œuvre, mêlant histoire philosophique, poésie (Bestiaire latéral, 1974) et dialogues interdisciplinaires, reste une référence pour l'étude des marges de la rationalité. &lt;/p&gt;</t>
         </is>
       </c>
       <c r="F77" s="54" t="inlineStr">
@@ -5777,7 +5777,7 @@
       </c>
       <c r="E82" s="56" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt; &lt;a href="https://fr.wikipedia.org/wiki/Simone_de_Beauvoir"  title=" Wikipedia"&gt; Simone de BEAUVOIR&lt;/a&gt; était une philosophe et intellectuelle anticonformiste. Elle fut une figure importante du &lt;a href="https://www.youtube.com/watch?v=J3AW5eQEs68&amp;ab_channel=LePr%C3%A9cepteur"  title="Le Féminisme Existentialiste par le Précepteur"&gt; "Féminisme Existentialiste" &lt;/a&gt;  en France et a écrit de nombreux livres dont des essais philosophiques comme "La force des choses" ou encore "Tous les hommes sont mortels"mais surtout &lt;a href="https://www.youtube.com/watch?v=QsnELrcARYU"  title="Le Deuxième Sexe de Simone de BEAUVOIR"&gt; "Le Deuxième Sexe" &lt;/a&gt; publié en 1949, qui a influencé la pensée féministe du XXe siècle et qui a établi la distinction entre "femme" comme une construction sociale et "femelle" comme une caractéristique biologique. &lt;/p&gt; &lt;p&gt; Elle était également une activiste sociale et politique engagée et a travaillé pour les droits des femmes et la liberté de choix en matière de contraception et d'avortement. &lt;/p&gt; &lt;p&gt; Elle a également été une défenseure des droits des personnes LGBT et des minorités ethniques. Elle a établi une distinction fondamentale entre le sexe (biologique) et le genre (socialement construit) et a soutenu que les femmes étaient soumises à une "aliénation ontologique" et à une "oppression politique", car la société les définissait comme des "autres" en opposition aux hommes. Une de ses phrases les plus connus: &lt;a href="https://fr.wikipedia.org/wiki/Le_Deuxi%C3%A8me_Sexe"  title=" Le deuxième sexe par wikipedia"&gt; "on ne naît pas femme, on le devient" &lt;/a&gt;. &lt;/p&gt; &lt;p&gt; Elle partagera pendant 51 ans sa vie avec le philosophe Jean-Paul SARTRE.  &lt;/p&gt;   &lt;audio controls title="Jean BEAUFRETpar France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/10471-17.04.2008-ITEMA_20120174-2008C3330E0015-ITE_00016512_RSCE-21.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt; </t>
+          <t xml:space="preserve">&lt;p&gt; &lt;a href="https://fr.wikipedia.org/wiki/Simone_de_Beauvoir"  title=" Wikipedia"&gt; Simone de BEAUVOIR&lt;/a&gt; était une philosophe et intellectuelle anticonformiste. Elle fut une figure importante du &lt;a href="https://www.youtube.com/watch?v=J3AW5eQEs68&amp;ab_channel=LePr%C3%A9cepteur"  title="Le Féminisme Existentialiste par le Précepteur"&gt; "Féminisme Existentialiste" &lt;/a&gt;  en France et a écrit de nombreux livres dont des essais philosophiques comme "La force des choses" ou encore "Tous les hommes sont mortels"mais surtout &lt;a href="https://www.youtube.com/watch?v=QsnELrcARYU"  title="Le Deuxième Sexe de Simone de BEAUVOIR"&gt; "Le Deuxième Sexe" &lt;/a&gt; publié en 1949, qui a influencé la pensée féministe du XXe siècle et qui a établi la distinction entre "femme" comme une construction sociale et "femelle" comme une caractéristique biologique. &lt;/p&gt; &lt;p&gt; Elle était également une activiste sociale et politique engagée et a travaillé pour les droits des femmes et la liberté de choix en matière de contraception et d'avortement. &lt;/p&gt; &lt;p&gt; Elle a également été une défenseure des droits des personnes LGBT et des minorités ethniques. Elle a établi une distinction fondamentale entre le sexe (biologique) et le genre (socialement construit) et a soutenu que les femmes étaient soumises à une "aliénation ontologique" et à une "oppression politique", car la société les définissait comme des "autres" en opposition aux hommes. Une de ses phrases les plus connus: &lt;a href="https://fr.wikipedia.org/wiki/Le_Deuxi%C3%A8me_Sexe"  title=" Le deuxième sexe par wikipedia"&gt; "on ne naît pas femme, on le devient"&lt;/a&gt;. &lt;/p&gt; &lt;p&gt; Elle partagera pendant 51 ans sa vie avec le philosophe Jean-Paul SARTRE.  &lt;/p&gt;   &lt;audio controls title="Jean BEAUFRETpar France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/10471-17.04.2008-ITEMA_20120174-2008C3330E0015-ITE_00016512_RSCE-21.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt; </t>
         </is>
       </c>
       <c r="F82" s="54" t="inlineStr">
@@ -5846,7 +5846,7 @@
       <c r="E83" s="65" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Maurice_Merleau-Ponty" title=" Wikipedia"&gt;Maurice MERLEAU-PONTY&lt;/a&gt; était un philosophe français connu pour ses contributions à la phénoménologie, à la philosophie de la perception et à l’existentialisme. Il  s’inspire de plusieurs courants et penseurs et  reprend l’idée d’une description des expériences vécues, mais critique l’idéalisme husserlien. Dans son oeurvre majeure &lt;a href="https://www.youtube.com/watch?v=RrD5SEiXr_A"  title=" La phénoménologie de Maurice Merleau-Ponty par Tes grands auteurs en petits morceaux"&gt;"Phénoménalogie de la perception"&lt;/a&gt; il  y développe une critique radicale des approches traditionnelles de la perception pour proposer une vision incarnée et existentielle de l’expérience humaine. Il rejette la séparation cartésienne entre le corps et l’esprit &lt;a href="https://classiques.uqam.ca/classiques/merleau_ponty_maurice/sens_et_non_sens/sens_et_non_sens.html"  title="  Maurice Merleau-Ponty sens et non sens  par UQAM"&gt;(sens et non sens)&lt;/a&gt;. Pour lui, le corps n’est pas un objet, mais un sujet percevant :  &lt;/p&gt; &lt;p&gt;
--  Le corps propre : C’est par lui que nous faisons l’expérience du monde. Il est à la fois sujet et objet, toujours déjà engagé dans un environnement. &lt;/p&gt; &lt;p&gt; - La perception comme ouverture au monde : &lt;a href="https://www.youtube.com/watch?v=yiHMPFMCUvo" title="MERLEAU-PONTY - L'OEIL ET L'ESPRIT par Kosmos"&gt;Percevoir&lt;/a&gt; , c’est être en dialogue avec le monde, pas simplement recevoir des données sensorielles. &lt;/p&gt;  &lt;p&gt;   Il  s’intéresse au langage comme geste corporel. Pour lui, la parole n’est pas un simple véhicule de la pensée, mais une incarnation du sens et l’art montre comment l’expression émerge de la perception. &lt;/p&gt; &lt;p&gt; Dans "Le Visible et l’invisible", il développe une  &lt;a href="https://www.youtube.com/watch?v=wZNUUGSZHMs"  title=" Maurice Merleau-Ponty - Entretien : Heure de culture française par Artesquieu "&gt;ontologie originale&lt;/a&gt; où le "chair" est ni matière ni esprit, c’est une substance sensible qui unit le corps et le monde.  Chiasme : Concept décrivant l’entrelacs du voyant et du visible, du touchant et du touché (ex. : quand je me touche la main, je suis à la fois sujet et objet).  L’invisible : Non pas l’absence de visible, mais ce qui le structure. &lt;/p&gt;   &lt;audio controls title="Maurice Merleau-Ponty : Partie 8/12- La crise de la pensée religieuse par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/13915-20.11.2014-ITEMA_20690515-2013C3372E0710-21.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;  </t>
+-  Le corps propre : C’est par lui que nous faisons l’expérience du monde. Il est à la fois sujet et objet, toujours déjà engagé dans un environnement. &lt;/p&gt; &lt;p&gt; - La perception comme ouverture au monde : &lt;a href="https://www.youtube.com/watch?v=yiHMPFMCUvo" title="MERLEAU-PONTY - L'OEIL ET L'ESPRIT par Kosmos"&gt;Percevoir&lt;/a&gt;, c’est être en dialogue avec le monde, pas simplement recevoir des données sensorielles. &lt;/p&gt;  &lt;p&gt;   Il  s’intéresse au langage comme geste corporel. Pour lui, la parole n’est pas un simple véhicule de la pensée, mais une incarnation du sens et l’art montre comment l’expression émerge de la perception. &lt;/p&gt; &lt;p&gt; Dans "Le Visible et l’invisible", il développe une  &lt;a href="https://www.youtube.com/watch?v=wZNUUGSZHMs"  title=" Maurice Merleau-Ponty - Entretien : Heure de culture française par Artesquieu "&gt;ontologie originale&lt;/a&gt; où le "chair" est ni matière ni esprit, c’est une substance sensible qui unit le corps et le monde.  Chiasme : Concept décrivant l’entrelacs du voyant et du visible, du touchant et du touché (ex. : quand je me touche la main, je suis à la fois sujet et objet).  L’invisible : Non pas l’absence de visible, mais ce qui le structure. &lt;/p&gt;   &lt;audio controls title="Maurice Merleau-Ponty : Partie 8/12- La crise de la pensée religieuse par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/13915-20.11.2014-ITEMA_20690515-2013C3372E0710-21.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;  </t>
         </is>
       </c>
       <c r="F83" s="57" t="inlineStr">
@@ -6034,7 +6034,7 @@
       </c>
       <c r="E86" s="59" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt; &lt;a href="https://fr.wikipedia.org/wiki/Simone_Weil"  title=" Wikipedia"&gt; Simone WEIL&lt;/a&gt; était une philosophe Française qui a étudié la philosophie antique et les textes religieux. Elle était profondément spirituelle et religieuse et a rejeté les institutions traditionnelles. Elle a exploré les aspects mystiques de différentes religions et a essayé de les intégrer dans une vision du monde plus large.  Elle souhaite faire de la philosophie une manière de vivre, non pour acquérir des connaissances, mais pour être dans la vérité. Elle écrira plusieurs livres dont &lt;a href="https://www.youtube.com/watch?v=6CR2PcTPvCk&amp;ab_channel=Al%C3%A8theiar" title="Les besoins de l'âme par Alèteia"&gt; "l'Enracinement" &lt;/a&gt; et "la Pesanteur et la grâce".  &lt;/p&gt; &lt;p&gt;C'était une &lt;span title="L'activisme politique est une attitude, une règle de conduite ou un engagement politique qui privilégie l'action directe à court terme par rapport aux principes théoriques et aux actions à long terme"&gt; activiste politique &lt;/span&gt;  engagée, qui a participé à divers mouvements sociaux et politiques, notamment la grève générale en France en 1936 et la guerre d'Espagne. &lt;/p&gt; &lt;p&gt; En 1942, elle a participé à la lutte contre l'occupation nazie en se joignant à la résistance. Dans son ouvrage, &lt;a href="https://www.youtube.com/watch?v=Pg0qv0kIaKo&amp;ab_channel=LePr%C3%A9cepteur"  style="color:#88A1E9"  title="Supprimer les parties politiques par le Précepteur"&gt; "La Condition ouvrière" &lt;/a&gt;.   elle prône la suppression des partis politiques et défend l'idée selon laquelle les partis politiques sont souvent motivés par leurs intérêts partisans plutôt que par le bien-être général de la société et qu'ils sont des obstacles à la véritable démocratie en concentrant le pouvoir entre les mains d'une élite restreinte et en limitant les voix de la majorité. &lt;/p&gt;  &lt;audio controls title="Une intellectuelle à l'usine par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/21936-01.01.2021-ITEMA_22534096-2019C12410E0194.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt; 
+          <t xml:space="preserve">&lt;p&gt; &lt;a href="https://fr.wikipedia.org/wiki/Simone_Weil"  title=" Wikipedia"&gt; Simone WEIL&lt;/a&gt; était une philosophe Française qui a étudié la philosophie antique et les textes religieux. Elle était profondément spirituelle et religieuse et a rejeté les institutions traditionnelles. Elle a exploré les aspects mystiques de différentes religions et a essayé de les intégrer dans une vision du monde plus large.  Elle souhaite faire de la philosophie une manière de vivre, non pour acquérir des connaissances, mais pour être dans la vérité. Elle écrira plusieurs livres dont &lt;a href="https://www.youtube.com/watch?v=6CR2PcTPvCk&amp;ab_channel=Al%C3%A8theiar" title="Les besoins de l'âme par Alèteia"&gt; "l'Enracinement" &lt;/a&gt; et "la Pesanteur et la grâce".  &lt;/p&gt; &lt;p&gt;C'était une &lt;span title="L'activisme politique est une attitude, une règle de conduite ou un engagement politique qui privilégie l'action directe à court terme par rapport aux principes théoriques et aux actions à long terme"&gt; activiste politique &lt;/span&gt;  engagée, qui a participé à divers mouvements sociaux et politiques, notamment la grève générale en France en 1936 et la guerre d'Espagne. &lt;/p&gt; &lt;p&gt; En 1942, elle a participé à la lutte contre l'occupation nazie en se joignant à la résistance. Dans son ouvrage, &lt;a href="https://www.youtube.com/watch?v=Pg0qv0kIaKo&amp;ab_channel=LePr%C3%A9cepteur"  style="color:#88A1E9"  title="Supprimer les parties politiques par le Précepteur"&gt; "La Condition ouvrière"&lt;/a&gt;. Elle prône la suppression des partis politiques et défend l'idée selon laquelle les partis politiques sont souvent motivés par leurs intérêts partisans plutôt que par le bien-être général de la société et qu'ils sont des obstacles à la véritable démocratie en concentrant le pouvoir entre les mains d'une élite restreinte et en limitant les voix de la majorité. &lt;/p&gt;  &lt;audio controls title="Une intellectuelle à l'usine par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/21936-01.01.2021-ITEMA_22534096-2019C12410E0194.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt; 
 </t>
         </is>
       </c>
@@ -6397,7 +6397,7 @@
       </c>
       <c r="E92" s="62" t="inlineStr">
         <is>
-          <t>&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Paul_Ric%C5%93ur"   title=" Wikipedia"&gt;Paul RICOEUR&lt;/a&gt; était un  philosophe français considéré comme le dernier &lt;a href="https://www.lemonde.fr/a-la-une/article/2005/05/21/paul-ricoeur-philosophe-de-tous-les-dialogues_652552_3208.html"  title="Paul Ricoeur, philosophe de tous les dialogues par Le Monde"&gt;"grands penseurs" &lt;/a&gt; à la croisée de la phénoménologie, de l’herméneutique, de la philosophie du langage et de l’éthique. &lt;/p&gt; &lt;p&gt; Dans “Le volontaire et l’involontaire” et “Finitude et culpabilité”, il analyse la volonté humaine comme toujours prise entre liberté et contraintes, capacité d’agir et fragilité, ce qui nourrit sa réflexion sur la faute et la responsabilité.  Ses travaux sur le symbole et l’interprétation montrent que l’être humain se comprend à travers  &lt;a href="https://www.youtube.com/watch?v=QLOwycKenCI" title="En 1965, le philosophe Paul Ricoeur commente la contre-culture beatnik par Radio-Canada"&gt; des symboles &lt;/a&gt;, des récits et des textes, dont le sens n’est jamais donné immédiatement mais demande un travail d’interprétation. Son projet est de tenir ensemble la compréhension “interprétative” et les approches critiques (psychanalyse, structuralisme), en assumant les “conflits d’interprétations” plutôt que de chercher une seule lecture définitive. &lt;/p&gt; &lt;p&gt; Il conçoit  &lt;a href="https://www.youtube.com/watch?v=uX76UVhBIqs"  title="Paul Ricoeur, l’herméneutique du soupçon par Baglis Tv"&gt; l’herméneutique&lt;/a&gt; comme une philosophie de l’interprétation qui assume la distance entre nous et les textes, les événements, les autres, et qui cherche une vérité située dans ce travail d’interprétation plutôt que dans une évidence immédiate.​ Il insiste sur le fait qu’il n’existe pas de philosophie “sans présuppositions” : toute compréhension passe par des pré-compréhensions, que la critique vient transformer, ce qui l’amène à articuler la lecture soupçonneuse (Marx, Nietzsche, Freud) et la lecture de confiance. &lt;/p&gt; &lt;p&gt; Il développe une éthique de la “vie bonne, avec et pour les autres, dans des institutions justes” (formule célèbre de “Soi-même comme un autre”), où l’éthique (visée de la vie bonne) précède la morale (règles, normes).​ 
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Paul_Ric%C5%93ur"   title=" Wikipedia"&gt;Paul RICOEUR&lt;/a&gt; était un  philosophe français considéré comme le dernier &lt;a href="https://www.lemonde.fr/a-la-une/article/2005/05/21/paul-ricoeur-philosophe-de-tous-les-dialogues_652552_3208.html"  title="Paul Ricoeur, philosophe de tous les dialogues par Le Monde"&gt;"grands penseurs" &lt;/a&gt; à la croisée de la phénoménologie, de l’herméneutique, de la philosophie du langage et de l’éthique. &lt;/p&gt; &lt;p&gt; Dans “Le volontaire et l’involontaire” et “Finitude et culpabilité”, il analyse la volonté humaine comme toujours prise entre liberté et contraintes, capacité d’agir et fragilité, ce qui nourrit sa réflexion sur la faute et la responsabilité.  Ses travaux sur le symbole et l’interprétation montrent que l’être humain se comprend à travers  &lt;a href="https://www.youtube.com/watch?v=QLOwycKenCI" title="En 1965, le philosophe Paul Ricoeur commente la contre-culture beatnik par Radio-Canada"&gt; des symboles&lt;/a&gt;, des récits et des textes, dont le sens n’est jamais donné immédiatement mais demande un travail d’interprétation. Son projet est de tenir ensemble la compréhension “interprétative” et les approches critiques (psychanalyse, structuralisme), en assumant les “conflits d’interprétations” plutôt que de chercher une seule lecture définitive. &lt;/p&gt; &lt;p&gt; Il conçoit  &lt;a href="https://www.youtube.com/watch?v=uX76UVhBIqs"  title="Paul Ricoeur, l’herméneutique du soupçon par Baglis Tv"&gt; l’herméneutique&lt;/a&gt; comme une philosophie de l’interprétation qui assume la distance entre nous et les textes, les événements, les autres, et qui cherche une vérité située dans ce travail d’interprétation plutôt que dans une évidence immédiate.​ Il insiste sur le fait qu’il n’existe pas de philosophie “sans présuppositions” : toute compréhension passe par des pré-compréhensions, que la critique vient transformer, ce qui l’amène à articuler la lecture soupçonneuse (Marx, Nietzsche, Freud) et la lecture de confiance. &lt;/p&gt; &lt;p&gt; Il développe une éthique de la “vie bonne, avec et pour les autres, dans des institutions justes” (formule célèbre de “Soi-même comme un autre”), où l’éthique (visée de la vie bonne) précède la morale (règles, normes).​ 
 Il met au centre le “sujet capable” (capable de parler, agir, se raconter, se tenir pour responsable) mais toujours fragile, et pense la justice comme articulation entre la reconnaissance de la vulnérabilité des personnes et la nécessité d’institutions justes.​ &lt;/p&gt; &lt;p&gt; Ses analyses de la mémoire, de l’histoire et du pardon nourrissent aussi les débats contemporains sur le “devoir de mémoire”, les violences politiques et les possibilités de réconciliation. &lt;/p&gt;   &lt;audio controls title="La pensée de Paul Ricoeur par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/10467-18.11.2013-ITEMA_20550371-2013C12410S0322-NET_FC_66E918EC-2266-4DF5-B6E4-489E465FA68D-21.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;</t>
         </is>
       </c>
@@ -6767,7 +6767,7 @@
       </c>
       <c r="E98" s="62" t="inlineStr">
         <is>
-          <t>&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Jules_Vuillemin"  title=" Wikipedia"&gt;Jules VUILLEMIN&lt;/a&gt;  était un philosophe français qui  s'est distingué par son travail en  &lt;a href="https://hal.science/hal-04409311v1/document" title="Jules Vuillemin, philosdophie analytique contrarié par hal"&gt;philosophie analytique &lt;/a&gt;, en épistémologie et en histoire de la philosophie.  Il diffuse en France les idées de Bertrand Russell, Rudolf Carnap et Willard Van Orman Quine, influençant des penseurs comme Jacques Bouveresse. Ses débuts touchent à  &lt;a href="https://lafrancebyzantine.blogspot.com/2016/09/jules-vuillemin-t-il-ete-existentialiste.html"  title="Jules Vuillemin at'il été existantialiste? par lafrancebyzantine"&gt;l'existentialisme &lt;/a&gt; et au marxisme, mais il évolue vers un rationalisme rigoureux, rejetant les excès de Sartre ou Heidegger. &lt;/p&gt; &lt;p&gt; Ses œuvres majeures : - "Nécessité ou contingence" paru en 1984, qui analyse les systèmes philosophiques par une approche logique et historique, et "La philosophie de l'algèbre" paru en 1962 ou il explore la nécessité, la contingence, la logique et les sciences, insistant sur la cohérence interne des systèmes selon l'héritage de Martial Gueroult. Épistémologue de premier plan avec Gilles Gaston Granger et René Thom, il défend une philosophie attentive aux mathématiques et à la physique. &lt;/p&gt; &lt;p&gt; Il s'intéresse à Kant, Descartes, la liberté et la métaphysique de la nature, tout en critiquant les réductions existentialistes au profit d'une raison objective. Ses archives sont conservées au Laboratoire de Philosophie et d'Histoire des Sciences à Nancy. Auteur de plus de vingt livres, il reste une figure de la rigueur philosophique française. &lt;/p&gt;</t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Jules_Vuillemin"  title=" Wikipedia"&gt;Jules VUILLEMIN&lt;/a&gt;  était un philosophe français qui  s'est distingué par son travail en  &lt;a href="https://hal.science/hal-04409311v1/document" title="Jules Vuillemin, philosdophie analytique contrarié par hal"&gt;philosophie analytique&lt;/a&gt;, en épistémologie et en histoire de la philosophie.  Il diffuse en France les idées de Bertrand Russell, Rudolf Carnap et Willard Van Orman Quine, influençant des penseurs comme Jacques Bouveresse. Ses débuts touchent à  &lt;a href="https://lafrancebyzantine.blogspot.com/2016/09/jules-vuillemin-t-il-ete-existentialiste.html"  title="Jules Vuillemin at'il été existantialiste? par lafrancebyzantine"&gt;l'existentialisme &lt;/a&gt; et au marxisme, mais il évolue vers un rationalisme rigoureux, rejetant les excès de Sartre ou Heidegger. &lt;/p&gt; &lt;p&gt; Ses œuvres majeures : - "Nécessité ou contingence" paru en 1984, qui analyse les systèmes philosophiques par une approche logique et historique, et "La philosophie de l'algèbre" paru en 1962 ou il explore la nécessité, la contingence, la logique et les sciences, insistant sur la cohérence interne des systèmes selon l'héritage de Martial Gueroult. Épistémologue de premier plan avec Gilles Gaston Granger et René Thom, il défend une philosophie attentive aux mathématiques et à la physique. &lt;/p&gt; &lt;p&gt; Il s'intéresse à Kant, Descartes, la liberté et la métaphysique de la nature, tout en critiquant les réductions existentialistes au profit d'une raison objective. Ses archives sont conservées au Laboratoire de Philosophie et d'Histoire des Sciences à Nancy. Auteur de plus de vingt livres, il reste une figure de la rigueur philosophique française. &lt;/p&gt;</t>
         </is>
       </c>
       <c r="F98" s="54" t="inlineStr">
@@ -6827,7 +6827,7 @@
       </c>
       <c r="E99" s="59" t="inlineStr">
         <is>
-          <t>&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Gilles_Gaston_Granger"   title=" Wikipedia"&gt;Gilles Gaston GRANGER&lt;/a&gt;  était un philosophe  et épistémologue français connu pour son travail sur l'épistémologie comparative et l'application des formes logico-mathématiques aux sciences humaines. Élève de l'École normale supérieure, agrégé de philosophie en 1943 et licencié en mathématiques, &lt;a href="https://www.persee.fr/authority/281588"title=" Gilles Gaston GRANGER par Persée"&gt; il enseigna &lt;/a&gt; au Brésil puis en France.  Il traduisit le "Tractatus logico-philosophicus" de Wittgenstein en français et fonda la revue L'Âge de la Science en 1968. &lt;/p&gt; &lt;p&gt; Il , &lt;a href="https://www.youtube.com/watch?v=koxZPXhxpt0&amp;t=699s" title="
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Gilles_Gaston_Granger"   title=" Wikipedia"&gt;Gilles Gaston GRANGER&lt;/a&gt;  était un philosophe  et épistémologue français connu pour son travail sur l'épistémologie comparative et l'application des formes logico-mathématiques aux sciences humaines. Élève de l'École normale supérieure, agrégé de philosophie en 1943 et licencié en mathématiques, &lt;a href="https://www.persee.fr/authority/281588"title=" Gilles Gaston GRANGER par Persée"&gt; il enseigna &lt;/a&gt; au Brésil puis en France.  Il traduisit le "Tractatus logico-philosophicus" de Wittgenstein en français et fonda la revue L'Âge de la Science en 1968. &lt;/p&gt; &lt;p&gt; Il, &lt;a href="https://www.youtube.com/watch?v=koxZPXhxpt0&amp;t=699s" title="
 Rationalité et raisonnement — Gilles-Gaston Granger par Andrea Cirla"&gt;développa &lt;/a&gt; une épistémologie comparatiste, unifiant sciences de la nature et humaines sur une échelle commune, inspirée d'Aristote et d'un rationalisme pragmatique. Il rejeta le platonisme (formes abstraites) et le positivisme strict (lois universelles pour les faits humains), privilégiant les modèles sémantiques et probabilistes en économie ou linguistique.  La raison est pour lui un "travail" et un "style" évolutif, appliquant formes mathématiques à des contenus concrets via abstraction. &lt;/p&gt; &lt;p&gt; Ses Œuvres clés sont : -"Méthodologie économique" paru en 1955 et "La Mathématique sociale du marquis de Condorcet" en 1956 : analyses pionnières des sciences humaines. - "Pensée formelle et sciences de l'homme" paru en 1960 : montre comment modéliser l'individuel (économie, langage, histoire). &lt;/p&gt;</t>
         </is>
       </c>
@@ -7496,7 +7496,7 @@
       </c>
       <c r="E110" s="89" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Fran%C3%A7ois_Wahl"  title=" Wikipedia"&gt;François WAHL&lt;/a&gt; était un philosophe et éditeur français, figure centrale de la vie intellectuelle française de la fin des années 1950 au début des années 1990, surtout connu pour avoir promu le structuralisme et la psychanalyse aux Éditions du Seuil. l a régné pendant trente ans sur le domaine des sciences humaines et la littérature italienne au Seuil, publiant Jacques Lacan, Françoise Dolto, Paul Ricœur, Roland Barthes, Philippe Sollers, Alain Badiou, Jean-Cla Milner, ainsi que des auteurs italiens comme Carlo Emilio Gadda et Italo Calvino. Il est décrit comme un « structuraliste dans l’âme », construisant son activité éditoriale comme une structure où chaque choix (acceptations, refus, retraductions) faisait système, appliquant la doctrine structuraliste à son métier d’éditeur. &lt;/p&gt; &lt;p&gt; Il est l’auteur de trois ouvrages majeurs :  &lt;a href="https://philosophie.ac-normandie.fr/spip.php?article148" title="qu’est ce que la philosophie par françois Wahl "&gt;Qu’est-ce que le structuralisme ? &lt;/a&gt; , Philosophie (1973), Introduction au discours du tableau (1996) et Le Perçu (2007). Dans Introduction au discours du tableau, il étudie les œuvres de Poussin, Memling ou Bellini pour montrer que le « visible » apparaît sous deux espèces : le paysage et le tableau, articulant ainsi esthétique et théorie du signe. Le Perçu propose une exploration critique des phénoménologies du XXᵉ siècle, en mobilisant les concepts de discours, sujet, désir et énoncé pour formaliser une analyse du « fait esthétique » . &lt;/p&gt; &lt;p&gt; La ligne directrice de sa pensée peut se résumer à un repérage du concept de sujet dans la philosophie contemporaine et son introduction dans le champ de l’esthétique. Il a écrit de nombreux articles discutant les œuvres d’auteurs comme Badiou, Bataille, Barthes, Foucault ou Lacan, et son dernier grand livre, La dissidence du sujet, rassemble ces réflexions sur le sujet, le désir et le discours dans la philosophie et l’art. &lt;/p&gt; &lt;audio controls title="les fluides d’Aristote /hommage à f Wahl par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/12003-17.09.2014-ITEMA_20670365-2014C18006S0260-21.mp3" type="audio/mpeg" align="center"&gt;&lt;/audio&gt;  </t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Fran%C3%A7ois_Wahl"  title=" Wikipedia"&gt;François WAHL&lt;/a&gt; était un philosophe et éditeur français, figure centrale de la vie intellectuelle française de la fin des années 1950 au début des années 1990, surtout connu pour avoir promu le structuralisme et la psychanalyse aux Éditions du Seuil. l a régné pendant trente ans sur le domaine des sciences humaines et la littérature italienne au Seuil, publiant Jacques Lacan, Françoise Dolto, Paul Ricœur, Roland Barthes, Philippe Sollers, Alain Badiou, Jean-Cla Milner, ainsi que des auteurs italiens comme Carlo Emilio Gadda et Italo Calvino. Il est décrit comme un « structuraliste dans l’âme », construisant son activité éditoriale comme une structure où chaque choix (acceptations, refus, retraductions) faisait système, appliquant la doctrine structuraliste à son métier d’éditeur. &lt;/p&gt; &lt;p&gt; Il est l’auteur de trois ouvrages majeurs :  &lt;a href="https://philosophie.ac-normandie.fr/spip.php?article148" title="qu’est ce que la philosophie par françois Wahl "&gt;Qu’est-ce que le structuralisme ? &lt;/a&gt; , Philosophie (1973), Introduction au discours du tableau (1996) et Le Perçu (2007). Dans Introduction au discours du tableau, il étudie les œuvres de Poussin, Memling ou Bellini pour montrer que le « visible » apparaît sous deux espèces : le paysage et le tableau, articulant ainsi esthétique et théorie du signe. Le Perçu propose une exploration critique des phénoménologies du XXᵉ siècle, en mobilisant les concepts de discours, sujet, désir et énoncé pour formaliser une analyse du « fait esthétique ». &lt;/p&gt; &lt;p&gt; La ligne directrice de sa pensée peut se résumer à un repérage du concept de sujet dans la philosophie contemporaine et son introduction dans le champ de l’esthétique. Il a écrit de nombreux articles discutant les œuvres d’auteurs comme Badiou, Bataille, Barthes, Foucault ou Lacan, et son dernier grand livre, La dissidence du sujet, rassemble ces réflexions sur le sujet, le désir et le discours dans la philosophie et l’art. &lt;/p&gt; &lt;audio controls title="les fluides d’Aristote /hommage à f Wahl par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/12003-17.09.2014-ITEMA_20670365-2014C18006S0260-21.mp3" type="audio/mpeg" align="center"&gt;&lt;/audio&gt;  </t>
         </is>
       </c>
       <c r="F110" s="57" t="n"/>
@@ -7615,7 +7615,7 @@
       </c>
       <c r="E112" s="48" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Jean_Meyendorff" title=" Wikipedia"&gt;Jean MEYENDORFF&lt;/a&gt; était un théologien, historien et patrologue orthodoxe français ,  figure de la patristique orthodoxe et de la théologie byzantine au XXe siècle. Né à Paris dans une famille russe exilée, formé à l'Institut Saint-Serge de Paris, il s'établit aux États-Unis où il enseigna au Séminaire Saint-Vladimir de New York, dont il fut le doyen, et à l'Université de Fordham et à l'Université de Princeton.&lt;/p&gt;&lt;p&gt;Sa contribution académique principale est l'étude historique et théologique du palamisme — la théologie de Grégoire Palamas sur la distinction entre l'essence et les énergies divines. Sa thèse de doctorat, &lt;em&gt;Introduction à l'étude de Grégoire Palamas&lt;/em&gt; (1959), suivie de sa traduction critique des œuvres de Palamas, constituent des &lt;a href="https://www.youtube.com/watch?v=gSvlrp9sYfU"  title="john meyendorff par the orhodox christian studies"&gt; contributions fondamentales &lt;/a&gt; à la connaissance de la théologie byzantine tardive. Dans son ouvrage &lt;em&gt;Byzantine Theology&lt;/em&gt; (1974), il offre une synthèse remarquable de la théologie byzantine du concile de Nicée au XVe siècle, devenue une référence indispensable pour les études byzantines.&lt;/p&gt;&lt;p&gt;Ses travaux sur le primat dans &lt;a href="https://orthodoxie.com/vient-de-paraitre-decouvrir-les-peres-de-leglise-nouveau-manuel-de-patristique/"  title="découvrir les pères de l’église par  orhodoxie"&gt;l'Église orthodoxe &lt;/a&gt; et sur le rapport entre papauté et orthodoxie constituent des contributions importantes au dialogue œcuménique. Sa réflexion théologique, toujours ancrée dans la tradition patristique byzantine, cherchait à en dégager la pertinence pour les questions contemporaines de l'Église et du monde. Il représente la tradition académique la plus rigoureuse de la patristique orthodoxe, alliant érudition historique et engagement théologique dans un dialogue permanent avec le monde occidental.&lt;/p&gt;   &lt;audio controls title="hommage au père Jean Meyendorff par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/10491-01.11.2013-ITEMA_20543654-2013C3184E0023-21.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt; </t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Jean_Meyendorff" title=" Wikipedia"&gt;Jean MEYENDORFF&lt;/a&gt; était un théologien, historien et patrologue orthodoxe français,  figure de la patristique orthodoxe et de la théologie byzantine au XXe siècle. Né à Paris dans une famille russe exilée, formé à l'Institut Saint-Serge de Paris, il s'établit aux États-Unis où il enseigna au Séminaire Saint-Vladimir de New York, dont il fut le doyen, et à l'Université de Fordham et à l'Université de Princeton.&lt;/p&gt;&lt;p&gt;Sa contribution académique principale est l'étude historique et théologique du palamisme — la théologie de Grégoire Palamas sur la distinction entre l'essence et les énergies divines. Sa thèse de doctorat, &lt;em&gt;Introduction à l'étude de Grégoire Palamas&lt;/em&gt; (1959), suivie de sa traduction critique des œuvres de Palamas, constituent des &lt;a href="https://www.youtube.com/watch?v=gSvlrp9sYfU"  title="john meyendorff par the orhodox christian studies"&gt; contributions fondamentales &lt;/a&gt; à la connaissance de la théologie byzantine tardive. Dans son ouvrage &lt;em&gt;Byzantine Theology&lt;/em&gt; (1974), il offre une synthèse remarquable de la théologie byzantine du concile de Nicée au XVe siècle, devenue une référence indispensable pour les études byzantines.&lt;/p&gt;&lt;p&gt;Ses travaux sur le primat dans &lt;a href="https://orthodoxie.com/vient-de-paraitre-decouvrir-les-peres-de-leglise-nouveau-manuel-de-patristique/"  title="découvrir les pères de l’église par  orhodoxie"&gt;l'Église orthodoxe &lt;/a&gt; et sur le rapport entre papauté et orthodoxie constituent des contributions importantes au dialogue œcuménique. Sa réflexion théologique, toujours ancrée dans la tradition patristique byzantine, cherchait à en dégager la pertinence pour les questions contemporaines de l'Église et du monde. Il représente la tradition académique la plus rigoureuse de la patristique orthodoxe, alliant érudition historique et engagement théologique dans un dialogue permanent avec le monde occidental.&lt;/p&gt;   &lt;audio controls title="hommage au père Jean Meyendorff par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/10491-01.11.2013-ITEMA_20543654-2013C3184E0023-21.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt; </t>
         </is>
       </c>
       <c r="F112" s="47" t="inlineStr">
@@ -9134,7 +9134,7 @@
       </c>
       <c r="E137" s="59" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Bruno_Latour"  title=" Wikipedia"&gt;Bruno LATOUR&lt;/a&gt;  est un sociologue, anthropologue et philosophe français connu pour ses travaux sur la sociologie des sciences, la philosophie des sciences et l'anthropologie des modernes.&lt;/p&gt; &lt;p&gt; L'un des concepts clés développés par Latour est celui de l'acteur-réseau, également connu sous le nom de &lt;a href="https://fr.wikipedia.org/wiki/Th%C3%A9orie_de_l%27acteur-r%C3%A9seau"  title="Théorie de l'acteur-réseau par Wikipedia "&gt; théorie de l'acteur-réseau (ANT) &lt;/a&gt;. Selon cette approche, les acteurs humains et non humains sont considérés comme des "actants" qui agissent en collaboration pour produire des réalités sociales complexes. L'ANT remet en question la distinction traditionnelle entre les sujets humains et les objets inanimés, soulignant plutôt les relations et les interactions entre eux. &lt;/p&gt; &lt;p&gt; Il s'est  intéressé aux enjeux environnementaux et a contribué au développement de l'écologie politique. Il a souligné l'importance de prendre en compte les dimensions politiques et sociales dans la compréhension des questions écologiques et climatiques. Son livre &lt;a href="http://www.bruno-latour.fr/sites/default/files/uploads/TELERAMA.pdf"  title="Nous n'avons jamais été moderne par Bruno-Latour "&gt; "Nous n'avons jamais été modernes" &lt;/a&gt; (1991) remet en question la distinction entre nature et culture, mettant en lumière les façons dont les sciences et les technologies façonnent notre compréhension du monde. &lt;/p&gt; &lt;p&gt; En plus de ses travaux académiques, Bruno Latour a également participé à des &lt;a href="https://profondeurdechamps.com/2012/10/19/entretien-avec-bruno-latour-12-lart-et-la-science/"  title="L'art et la science par Profondeurdechamps "&gt; projets artistiques &lt;/a&gt; et curatoriaux. Il a collaboré avec des artistes contemporains et a contribué à des expositions d'art qui explorent les thèmes de la science, de la technologie et de l'environnement.&lt;/p&gt; &lt;audio controls title="Introduction à la pensée de Bruno LATOUR par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/22676-06.05.2022-ITEMA_23017705-2022F45096S0126-22.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt; </t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Bruno_Latour"  title=" Wikipedia"&gt;Bruno LATOUR&lt;/a&gt;  est un sociologue, anthropologue et philosophe français connu pour ses travaux sur la sociologie des sciences, la philosophie des sciences et l'anthropologie des modernes.&lt;/p&gt; &lt;p&gt; L'un des concepts clés développés par Latour est celui de l'acteur-réseau, également connu sous le nom de &lt;a href="https://fr.wikipedia.org/wiki/Th%C3%A9orie_de_l%27acteur-r%C3%A9seau"  title="Théorie de l'acteur-réseau par Wikipedia "&gt; théorie de l'acteur-réseau (ANT)&lt;/a&gt;. Selon cette approche, les acteurs humains et non humains sont considérés comme des "actants" qui agissent en collaboration pour produire des réalités sociales complexes. L'ANT remet en question la distinction traditionnelle entre les sujets humains et les objets inanimés, soulignant plutôt les relations et les interactions entre eux. &lt;/p&gt; &lt;p&gt; Il s'est  intéressé aux enjeux environnementaux et a contribué au développement de l'écologie politique. Il a souligné l'importance de prendre en compte les dimensions politiques et sociales dans la compréhension des questions écologiques et climatiques. Son livre &lt;a href="http://www.bruno-latour.fr/sites/default/files/uploads/TELERAMA.pdf"  title="Nous n'avons jamais été moderne par Bruno-Latour "&gt; "Nous n'avons jamais été modernes" &lt;/a&gt; (1991) remet en question la distinction entre nature et culture, mettant en lumière les façons dont les sciences et les technologies façonnent notre compréhension du monde. &lt;/p&gt; &lt;p&gt; En plus de ses travaux académiques, Bruno Latour a également participé à des &lt;a href="https://profondeurdechamps.com/2012/10/19/entretien-avec-bruno-latour-12-lart-et-la-science/"  title="L'art et la science par Profondeurdechamps "&gt; projets artistiques &lt;/a&gt; et curatoriaux. Il a collaboré avec des artistes contemporains et a contribué à des expositions d'art qui explorent les thèmes de la science, de la technologie et de l'environnement.&lt;/p&gt; &lt;audio controls title="Introduction à la pensée de Bruno LATOUR par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/22676-06.05.2022-ITEMA_23017705-2022F45096S0126-22.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt; </t>
         </is>
       </c>
       <c r="F137" s="57" t="inlineStr">

--- a/data/frise-philosophes-france.xlsx
+++ b/data/frise-philosophes-france.xlsx
@@ -938,7 +938,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:O143"/>
+  <dimension ref="A1:O144"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="4.59" customWidth="1" style="47" min="1" max="1"/>
@@ -1269,7 +1269,7 @@
       </c>
       <c r="K7" s="48" t="inlineStr">
         <is>
-          <t>Utopisme ; Humanisme</t>
+          <t xml:space="preserve">Utopisme ; Humanisme ; Saint-Simonisme</t>
         </is>
       </c>
       <c r="L7" s="48" t="inlineStr">
@@ -1333,7 +1333,7 @@
       </c>
       <c r="K8" s="48" t="inlineStr">
         <is>
-          <t>Positivisme</t>
+          <t xml:space="preserve">Positivisme ; Saint-Simonisme</t>
         </is>
       </c>
       <c r="L8" s="48" t="inlineStr">
@@ -1761,7 +1761,7 @@
       </c>
       <c r="K15" s="48" t="inlineStr">
         <is>
-          <t>Positivisme</t>
+          <t xml:space="preserve">Positivisme ; Scientisme ; Orientalisme</t>
         </is>
       </c>
       <c r="L15" s="48" t="inlineStr">
@@ -2180,7 +2180,7 @@
       </c>
       <c r="K22" s="48" t="inlineStr">
         <is>
-          <t>Marxisme ; Anarchisme</t>
+          <t xml:space="preserve">Marxisme ; Anarchisme ; Anarcho-syndicalisme</t>
         </is>
       </c>
       <c r="L22" s="48" t="inlineStr">
@@ -2773,7 +2773,7 @@
       </c>
       <c r="K32" s="48" t="inlineStr">
         <is>
-          <t>Spiritualisme ; Vitalisme</t>
+          <t xml:space="preserve">Spiritualisme ; Vitalisme ; Irrationalisme</t>
         </is>
       </c>
       <c r="L32" s="48" t="inlineStr">
@@ -4158,7 +4158,7 @@
       </c>
       <c r="K55" s="48" t="inlineStr">
         <is>
-          <t>Soufisme</t>
+          <t xml:space="preserve">Soufisme ; Orientalisme</t>
         </is>
       </c>
       <c r="L55" s="80" t="inlineStr">
@@ -4937,7 +4937,7 @@
       </c>
       <c r="K68" s="48" t="inlineStr">
         <is>
-          <t>Ishraqisme ; Herméneutique</t>
+          <t xml:space="preserve">Ishraqisme ; Herméneutique ; Orientalisme</t>
         </is>
       </c>
       <c r="L68" s="48" t="inlineStr">
@@ -5190,7 +5190,7 @@
       </c>
       <c r="K72" s="48" t="inlineStr">
         <is>
-          <t>Rationalisme ; Scientisme</t>
+          <t xml:space="preserve">Rationalisme</t>
         </is>
       </c>
       <c r="L72" s="48" t="inlineStr">
@@ -5251,7 +5251,7 @@
       </c>
       <c r="K73" s="48" t="inlineStr">
         <is>
-          <t>Existentialisme ; Marxisme</t>
+          <t xml:space="preserve">Existentialisme ; Marxisme ; Athéisme ; Absurde</t>
         </is>
       </c>
       <c r="L73" s="48" t="inlineStr">
@@ -7400,7 +7400,7 @@
       </c>
       <c r="K108" s="48" t="inlineStr">
         <is>
-          <t>Post-structuralisme</t>
+          <t xml:space="preserve">Post-structuralisme ; Accélérationnisme</t>
         </is>
       </c>
       <c r="L108" s="48" t="inlineStr">
@@ -7579,7 +7579,7 @@
       </c>
       <c r="K111" s="48" t="inlineStr">
         <is>
-          <t>Post-structuralisme ; Biopolitique</t>
+          <t xml:space="preserve">Post-structuralisme ; Biopolitique ; Analogisme</t>
         </is>
       </c>
       <c r="L111" s="48" t="inlineStr">
@@ -7640,7 +7640,7 @@
       </c>
       <c r="K112" s="48" t="inlineStr">
         <is>
-          <t>Spiritualisme</t>
+          <t xml:space="preserve">Spiritualisme ; Hésychasme</t>
         </is>
       </c>
       <c r="L112" s="48" t="inlineStr">
@@ -9536,6 +9536,57 @@
       <c r="O143">
         <v>2</v>
       </c>
+    </row>
+    <row r="144" ht="176.25" customHeight="1" s="49">
+      <c r="A144" s="47">
+        <v>1868</v>
+      </c>
+      <c r="B144" s="47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1952</t>
+        </is>
+      </c>
+      <c r="C144" s="47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1868 – 1952</t>
+        </is>
+      </c>
+      <c r="D144" s="47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Charles MAURRAS</t>
+        </is>
+      </c>
+      <c r="E144" s="85" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Charles_Maurras" title=" Wikipedia"&gt;Charles MAURRAS&lt;/a&gt; est un écrivain, journaliste et théoricien politique français, le maître à penser de l’&lt;a href="https://fr.wikipedia.org/wiki/Action_fran%C3%A7aise" title=" Wikipedia"&gt;Action française&lt;/a&gt;. Né en 1868 à Martigues, en Provence, il devient sourd vers quatorze ans, perd la foi, et monte à Paris, où il se fait connaître comme critique littéraire et poète, défenseur d’un classicisme inspiré de la Grèce contre le romantisme, qu’il juge source de désordre. L’affaire Dreyfus le jette dans la politique : en 1898, il justifie le faux du colonel Henry au nom de l’intérêt de l’armée et de l’État.&lt;/p&gt; &lt;p&gt;Avec son &lt;em&gt;Enquête sur la monarchie&lt;/em&gt; (1900), il convertit l’Action française à la royauté. Sa doctrine, le « nationalisme intégral », place la nation au-dessus de tout : seule une monarchie héréditaire, antiparlementaire et décentralisée pourrait garantir l’ordre et la durée que la République, gouvernement des partis et de l’opinion, détruirait. Agnostique, il défend pourtant l’Église catholique comme une force d’ordre. Il appelle sa méthode l’« empirisme organisateur » : tirer de l’histoire les lois du bon gouvernement. Il dénonce les « quatre États confédérés » qui, selon lui, rongent la France : les juifs, les protestants, les francs-maçons et les « métèques ». Cet antisémitisme d’État est au cœur de sa pensée.&lt;/p&gt; &lt;p&gt;Son quotidien, &lt;em&gt;L’Action française&lt;/em&gt;, exerce une influence considérable sur la droite et sur une partie de la jeunesse intellectuelle, malgré la condamnation du mouvement par le pape Pie XI en 1926. Maurras entre à l’Académie française en 1938. Hostile à l’Allemagne, il soutient pourtant en 1940 le maréchal Pétain, dont l’arrivée au pouvoir est pour lui une « divine surprise ». Condamné en 1945 à la réclusion à perpétuité et à la dégradation nationale pour intelligence avec l’ennemi, il s’écrie : « C’est la revanche de Dreyfus ! » Gracié pour raison de santé, il meurt en 1952. Sa pensée a durablement marqué l’extrême droite française.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="H144" s="48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/maurras-mini.webp</t>
+        </is>
+      </c>
+      <c r="J144" s="48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">politique</t>
+        </is>
+      </c>
+      <c r="K144" s="48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Maurrassisme ; Conservatisme</t>
+        </is>
+      </c>
+      <c r="L144" s="48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">écrivain et théoricien politique français, chef de l’Action française et du « nationalisme intégral ».</t>
+        </is>
+      </c>
+      <c r="N144" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+      <c r="O144"/>
     </row>
     <row r="1048566" ht="12.75" customHeight="1" s="49"/>
     <row r="1048567" ht="12.75" customHeight="1" s="49"/>

--- a/data/frise-philosophes-france.xlsx
+++ b/data/frise-philosophes-france.xlsx
@@ -938,7 +938,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:O144"/>
+  <dimension ref="A1:O146"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="4.59" customWidth="1" style="47" min="1" max="1"/>
@@ -9587,6 +9587,108 @@
         </is>
       </c>
       <c r="O144"/>
+    </row>
+    <row r="145" ht="176.25" customHeight="1" s="49">
+      <c r="A145" s="47">
+        <v>1827</v>
+      </c>
+      <c r="B145" s="47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1907</t>
+        </is>
+      </c>
+      <c r="C145" s="47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1827 – 1907</t>
+        </is>
+      </c>
+      <c r="D145" s="47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Marcellin BERTHELOT</t>
+        </is>
+      </c>
+      <c r="E145" s="85" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Marcellin_Berthelot" title=" Wikipedia"&gt;Marcellin BERTHELOT&lt;/a&gt; est un chimiste, historien des sciences et homme politique français, l’une des figures les plus représentatives du &lt;a href="https://fr.wikipedia.org/wiki/Scientisme" title=" Wikipedia"&gt;scientisme&lt;/a&gt;. Né à Paris en 1827, fils d’un médecin, il devient l’un des fondateurs de la chimie organique de synthèse : il montre qu’on peut fabriquer en laboratoire, à partir des éléments, des corps jusque-là produits seulement par les êtres vivants, comme l’acétylène, le méthane ou l’alcool. Il en tire une leçon philosophique : il n’existe pas de « force vitale » mystérieuse, la vie obéit aux mêmes lois que la matière.&lt;/p&gt; &lt;p&gt;Pour Berthelot, la science expérimentale est la seule voie vers la vérité, et elle doit aussi fonder la morale et la politique. « Le monde est aujourd’hui sans mystère », écrit-il en 1885 : ce que la science ne sait pas encore, elle le saura demain. Ami de &lt;a href="https://fr.wikipedia.org/wiki/Ernest_Renan" title=" Wikipedia"&gt;Ernest Renan&lt;/a&gt;, avec qui il partage la foi dans l’avenir de la science, il expose ses idées dans &lt;em&gt;Science et morale&lt;/em&gt; (1897). En 1895, quand le critique Ferdinand Brunetière proclame la « faillite de la science », qui n’aurait pas tenu ses promesses morales, Berthelot devient le porte-parole de la réplique républicaine et laïque.&lt;/p&gt; &lt;p&gt;Sénateur inamovible, il est ministre de l’Instruction publique (1886-1887) puis des Affaires étrangères (1895-1896), et défend une école laïque fondée sur les sciences. Professeur au Collège de France, secrétaire perpétuel de l’Académie des sciences, il s’oppose aussi à la théorie atomique, qu’il juge trop hypothétique. Il meurt en 1907 le même jour que sa femme, et tous deux sont inhumés au Panthéon.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="H145" s="48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/berthelot-mini.webp</t>
+        </is>
+      </c>
+      <c r="J145" s="48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">epistemologie ; politique</t>
+        </is>
+      </c>
+      <c r="K145" s="48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Scientisme ; Positivisme</t>
+        </is>
+      </c>
+      <c r="L145" s="48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">chimiste et homme politique français, figure emblématique du scientisme.</t>
+        </is>
+      </c>
+      <c r="N145" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+      <c r="O145"/>
+    </row>
+    <row r="146" ht="176.25" customHeight="1" s="49">
+      <c r="A146" s="47">
+        <v>1861</v>
+      </c>
+      <c r="B146" s="47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1916</t>
+        </is>
+      </c>
+      <c r="C146" s="47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1861 – 1916</t>
+        </is>
+      </c>
+      <c r="D146" s="47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pierre DUHEM</t>
+        </is>
+      </c>
+      <c r="E146" s="85" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Pierre_Duhem" title=" Wikipedia"&gt;Pierre DUHEM&lt;/a&gt; est un physicien, philosophe et historien des sciences français. Né à Paris en 1861, brillant élève de l’École normale supérieure, il consacre ses travaux de physique à la thermodynamique. Une thèse où il critique les idées du chimiste Marcellin Berthelot est refusée ; Berthelot, très puissant, l’empêche ensuite d’obtenir un poste à Paris, et Duhem, catholique convaincu, fait sa carrière en province, à Lille, à Rennes, puis à Bordeaux.&lt;/p&gt; &lt;p&gt;Dans &lt;em&gt;La Théorie physique, son objet, sa structure&lt;/em&gt; (1906), il soutient qu’une théorie physique n’explique pas la réalité cachée des choses, ce qui relève de la métaphysique : elle est un système de propositions mathématiques qui représente et classe le plus simplement possible les lois expérimentales. Il faut, comme disaient les astronomes grecs, « sauver les phénomènes ». Surtout, une expérience ne peut jamais réfuter une hypothèse isolée : elle met en jeu tout un ensemble de théories et d’instruments, et si la prédiction échoue, on ne sait pas laquelle des hypothèses est fausse. Il n’y a donc pas d’« expérience cruciale ». Cette idée, reprise par Quine, est connue comme la &lt;a href="https://fr.wikipedia.org/wiki/Th%C3%A8se_de_Duhem-Quine" title=" Wikipedia"&gt;thèse de Duhem-Quine&lt;/a&gt;.&lt;/p&gt; &lt;p&gt;Duhem est aussi un grand historien des sciences. Dans les dix volumes du &lt;em&gt;Système du monde&lt;/em&gt;, il redécouvre la physique du Moyen Âge, celle de Jean Buridan et de Nicole Oresme, et montre que la science moderne ne naît pas d’une rupture brutale avec les siècles « obscurs », mais les prolonge. Il meurt en 1916. Son instrumentalisme et son holisme ont profondément marqué la philosophie des sciences du XXe siècle.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="H146" s="48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/duhem-mini.webp</t>
+        </is>
+      </c>
+      <c r="J146" s="48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">epistemologie</t>
+        </is>
+      </c>
+      <c r="K146" s="48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Instrumentalisme ; Holisme</t>
+        </is>
+      </c>
+      <c r="L146" s="48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">physicien et philosophe des sciences français, pour qui une hypothèse n’est jamais testée seule.</t>
+        </is>
+      </c>
+      <c r="N146" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+      <c r="O146"/>
     </row>
     <row r="1048566" ht="12.75" customHeight="1" s="49"/>
     <row r="1048567" ht="12.75" customHeight="1" s="49"/>

--- a/data/frise-philosophes-france.xlsx
+++ b/data/frise-philosophes-france.xlsx
@@ -938,7 +938,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:O146"/>
+  <dimension ref="A1:O153"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="4.59" customWidth="1" style="47" min="1" max="1"/>
@@ -9689,6 +9689,372 @@
         </is>
       </c>
       <c r="O146"/>
+    </row>
+    <row r="147" ht="176.25" customHeight="1" s="49">
+      <c r="A147" s="47">
+        <v>1854</v>
+      </c>
+      <c r="B147" s="47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1912</t>
+        </is>
+      </c>
+      <c r="C147" s="47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1854 – 1912</t>
+        </is>
+      </c>
+      <c r="D147" s="47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Henri POINCARÉ</t>
+        </is>
+      </c>
+      <c r="E147" s="85" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Henri_Poincar%C3%A9" title=" Wikipedia"&gt;Henri POINCARÉ&lt;/a&gt; est un mathématicien, physicien et philosophe des sciences français, l’un des derniers savants universels. Né à Nancy en 1854, polytechnicien et ingénieur des mines, il enseigne à la Sorbonne à partir de 1881. Il renouvelle presque toutes les branches des mathématiques : il fonde la topologie, découvre en étudiant le mouvement de trois corps célestes les comportements imprévisibles qu’on appellera « chaos », et pose en 1905, en même temps qu’Einstein, les bases mathématiques de la relativité restreinte.&lt;/p&gt; &lt;p&gt;Dans &lt;em&gt;La Science et l’Hypothèse&lt;/em&gt; (1902), il défend le &lt;a href="https://fr.wikipedia.org/wiki/Conventionnalisme" title=" Wikipedia"&gt;conventionnalisme&lt;/a&gt; : certains principes de la science ne sont ni des vérités a priori ni des faits d’expérience, mais des conventions. Ainsi, aucune expérience ne peut dire si l’espace est euclidien ou non : nous choisissons la géométrie d’Euclide parce qu’elle est la plus commode. Ces conventions ne sont pas arbitraires, car l’expérience nous guide, mais elles ne peuvent être ni vraies ni fausses. La science ne connaît pas les choses elles-mêmes, mais les rapports entre les choses.&lt;/p&gt; &lt;p&gt;Dans &lt;em&gt;La Valeur de la science&lt;/em&gt; (1905) et &lt;em&gt;Science et méthode&lt;/em&gt; (1908), il s’oppose aussi aux logiciens, comme Russell, qui veulent réduire les mathématiques à la logique : pour lui, le raisonnement mathématique repose sur une intuition. Il décrit le rôle de l’inconscient dans la découverte, à partir de ses propres illuminations soudaines, comme celle qui lui vint en montant dans un omnibus. Élu à l’Académie française en 1908, il meurt à Paris en 1912.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="H147" s="48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/poincare-mini.webp</t>
+        </is>
+      </c>
+      <c r="J147" s="48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">epistemologie ; logique</t>
+        </is>
+      </c>
+      <c r="K147" s="48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Conventionnalisme</t>
+        </is>
+      </c>
+      <c r="L147" s="48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mathématicien et physicien français, philosophe des sciences et fondateur du conventionnalisme.</t>
+        </is>
+      </c>
+      <c r="N147" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+      <c r="O147">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="148" ht="176.25" customHeight="1" s="49">
+      <c r="A148" s="47">
+        <v>1866</v>
+      </c>
+      <c r="B148" s="47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1947</t>
+        </is>
+      </c>
+      <c r="C148" s="47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1866 – 1947</t>
+        </is>
+      </c>
+      <c r="D148" s="47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Léon ROBIN</t>
+        </is>
+      </c>
+      <c r="E148" s="85" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/L%C3%A9on_Robin" title=" Wikipedia"&gt;Léon ROBIN&lt;/a&gt; est un philosophe et historien français de la philosophie, l’un des grands spécialistes de la pensée grecque. Né à Nantes en 1866, fils de marchand, il est reçu à l’agrégation de philosophie en 1891 et enseigne longtemps dans les lycées, à Compiègne, Vendôme et Angers. Élève et disciple d’Octave Hamelin, il publie après la mort de celui-ci son cours sur &lt;em&gt;Le Système d’Aristote&lt;/em&gt;. Il enseigne ensuite à Caen, puis à la Sorbonne de 1913 à 1937, où il occupe à partir de 1924 la chaire d’histoire de la philosophie antique.&lt;/p&gt; &lt;p&gt;Sa thèse, &lt;em&gt;La Théorie platonicienne des Idées et des nombres d’après Aristote&lt;/em&gt; (1908), s’appuie sur les témoignages d’Aristote pour reconstituer l’enseignement oral de &lt;a href="https://fr.wikipedia.org/wiki/Platon" title=" Wikipedia"&gt;Platon&lt;/a&gt; à l’Académie, où les Idées sont rattachées à des principes mathématiques, l’Un et la Dyade. Dans &lt;em&gt;La Pensée grecque et les origines de l’esprit scientifique&lt;/em&gt; (1923), il retrace la naissance de la raison grecque, des premiers physiciens d’Ionie jusqu’aux écoles hellénistiques. Il consacre aussi des livres à la morale antique, à Platon et au scepticisme de Pyrrhon, toujours appuyés sur une lecture rigoureuse des textes grecs.&lt;/p&gt; &lt;p&gt;Son œuvre la plus durable est la traduction des œuvres complètes de Platon pour la Bibliothèque de la Pléiade, qu’il dirige et dont il traduit lui-même la plus grande partie : précise et élégante, elle a fait lire Platon à des générations de lecteurs français. Il dirige aussi l’Institut international de philosophie. Il meurt à Paris en 1947. Pierre-Maxime Schuhl lui a succédé à la Sorbonne.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="H148" s="48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/leonrobin-mini.webp</t>
+        </is>
+      </c>
+      <c r="J148" s="48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">metaphysique ; epistemologie</t>
+        </is>
+      </c>
+      <c r="K148" s="48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Platonisme</t>
+        </is>
+      </c>
+      <c r="L148" s="48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">historien français de la philosophie grecque, grand interprète et traducteur de Platon.</t>
+        </is>
+      </c>
+      <c r="N148" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+      <c r="O148"/>
+    </row>
+    <row r="149" ht="176.25" customHeight="1" s="49">
+      <c r="A149" s="47">
+        <v>1898</v>
+      </c>
+      <c r="B149" s="47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1994</t>
+        </is>
+      </c>
+      <c r="C149" s="47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1898 – 1994</t>
+        </is>
+      </c>
+      <c r="D149" s="47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Henri GOUHIER</t>
+        </is>
+      </c>
+      <c r="E149" s="85" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Henri_Gouhier" title=" Wikipedia"&gt;Henri GOUHIER&lt;/a&gt; est un philosophe, historien de la philosophie et critique de théâtre français. Né à Auxerre en 1898, fils d’un clerc de notaire et d’une modiste, il entre à l’École normale supérieure en 1919 et est reçu premier à l’agrégation de philosophie en 1921. Élève d’&lt;a href="https://fr.wikipedia.org/wiki/%C3%89tienne_Gilson" title=" Wikipedia"&gt;Étienne Gilson&lt;/a&gt;, qui lui demande de faire pour la pensée française moderne ce qu’il fait lui-même pour le Moyen Âge, il enseigne à Lille, à Bordeaux, puis à la Sorbonne de 1941 à 1968, dans la chaire d’histoire de la pensée religieuse en France.&lt;/p&gt; &lt;p&gt;Il consacre sa vie à la philosophie française de Descartes à Bergson, qu’il lit en historien attentif aux convictions religieuses des auteurs. Il étudie la pensée religieuse de Descartes, Malebranche, Pascal, et surtout, dans trois volumes, la jeunesse d’Auguste Comte et la naissance du positivisme. Il montre comment le fondateur de la religion de l’Humanité a remplacé Dieu par l’humanité. Ces travaux inspirent le théologien Henri de Lubac pour &lt;em&gt;Le Drame de l’humanisme athée&lt;/em&gt; (1944). Il écrit aussi sur les conversions de Maine de Biran, sur Rousseau et sur Bergson, et défend l’idée d’une philosophie chrétienne.&lt;/p&gt; &lt;p&gt;Passionné de théâtre, il est pendant des décennies critique dramatique et publie &lt;em&gt;L’Essence du théâtre&lt;/em&gt; (1943), où il voit dans la représentation une présence réelle, une action vivante et non un simple texte. Membre de l’Académie des sciences morales et politiques, il est élu en 1979 à l’Académie française, au fauteuil de son maître Gilson. Il meurt à Paris en 1994.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="H149" s="48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/gouhier-mini.webp</t>
+        </is>
+      </c>
+      <c r="J149" s="48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">metaphysique ; spiritualite ; esthetique</t>
+        </is>
+      </c>
+      <c r="K149" s="48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Spiritualisme ; Cartésianisme</t>
+        </is>
+      </c>
+      <c r="L149" s="48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">historien français de la philosophie, de Descartes à Bergson, et critique dramatique.</t>
+        </is>
+      </c>
+      <c r="N149" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+      <c r="O149"/>
+    </row>
+    <row r="150" ht="176.25" customHeight="1" s="49">
+      <c r="A150" s="47">
+        <v>1918</v>
+      </c>
+      <c r="B150" s="47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1990</t>
+        </is>
+      </c>
+      <c r="C150" s="47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1918 – 1990</t>
+        </is>
+      </c>
+      <c r="D150" s="47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Henri BIRAULT</t>
+        </is>
+      </c>
+      <c r="E150" s="85" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Henri_Birault" title=" Wikipedia"&gt;Henri BIRAULT&lt;/a&gt; est un philosophe français. Né à Paris en 1918, il entre à l’École normale supérieure en 1939, dans la même promotion que Louis Althusser et Jules Vuillemin, et est reçu deuxième à l’agrégation de philosophie en 1945. Élève de Louis Lavelle et de Jean Nabert, il découvre ensuite l’œuvre de &lt;a href="https://fr.wikipedia.org/wiki/Martin_Heidegger" title=" Wikipedia"&gt;Martin Heidegger&lt;/a&gt;, dont il devient, avec Jean Beaufret, l’un des grands commentateurs français. Il enseigne en khâgne au lycée Henri-IV, puis à la Sorbonne.&lt;/p&gt; &lt;p&gt;Professeur admiré, il marque plusieurs générations d’étudiants par ses lectures lentes et minutieuses des textes, qu’il lit dans leur langue d’origine, en grec, en latin, en allemand. Sa réflexion, nourrie de Pascal, de Kant, de Nietzsche et de Heidegger, porte sur la question de l’être et sur la finitude humaine. Avec Heidegger, il cherche à comprendre ce que veut dire penser, au-delà de la métaphysique qui a réduit l’être à un objet disponible pour la science et la technique. Il en tire &lt;em&gt;Heidegger et l’expérience de la pensée&lt;/em&gt; (1978), qui reste l’une des grandes introductions françaises à cette œuvre difficile.&lt;/p&gt; &lt;p&gt;Sa contribution la plus célèbre, « De la béatitude chez Nietzsche », présentée en 1964 au colloque de Royaumont, montre que Nietzsche n’est pas seulement le penseur de la volonté de puissance et de la mort de Dieu, mais aussi celui d’une joie, d’une approbation sans réserve de la vie, de l’« amour du destin ». Respecté par Deleuze et ses contemporains, il publie peu et réécrit sans cesse. Il meurt en 1990. &lt;em&gt;De l’Être, du divin et des dieux&lt;/em&gt; paraît en 2005.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="H150" s="48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/birault-mini.webp</t>
+        </is>
+      </c>
+      <c r="J150" s="48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">metaphysique ; spiritualite</t>
+        </is>
+      </c>
+      <c r="K150" s="48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Phénoménologie</t>
+        </is>
+      </c>
+      <c r="L150" s="48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">philosophe français, grand lecteur de Heidegger, de Nietzsche et de Pascal.</t>
+        </is>
+      </c>
+      <c r="N150" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+      <c r="O150"/>
+    </row>
+    <row r="151" ht="176.25" customHeight="1" s="49">
+      <c r="A151" s="47">
+        <v>1923</v>
+      </c>
+      <c r="B151" s="47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2007</t>
+        </is>
+      </c>
+      <c r="C151" s="47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1923 – 2007</t>
+        </is>
+      </c>
+      <c r="D151" s="47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">André GORZ</t>
+        </is>
+      </c>
+      <c r="E151" s="85" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Andr%C3%A9_Gorz" title=" Wikipedia"&gt;André GORZ&lt;/a&gt; est un philosophe et journaliste français d’origine autrichienne, l’un des fondateurs de l’écologie politique. Né Gerhart Hirsch à Vienne en 1923, d’un père juif et d’une mère catholique, il est envoyé en Suisse en 1939 pour échapper à la guerre et y devient ingénieur chimiste. En 1946, il rencontre &lt;a href="https://fr.wikipedia.org/wiki/Jean-Paul_Sartre" title=" Wikipedia"&gt;Jean-Paul Sartre&lt;/a&gt;, qui le marque profondément. Installé à Paris en 1949, il écrit sous le nom de Michel Bosquet pour &lt;em&gt;L’Express&lt;/em&gt;, puis participe en 1964 à la fondation du &lt;em&gt;Nouvel Observateur&lt;/em&gt;.&lt;/p&gt; &lt;p&gt;Dans &lt;em&gt;Le Traître&lt;/em&gt; (1958), préfacé par Sartre, il analyse sa propre vie en existentialiste. Penseur du marxisme critique, il s’intéresse ensuite au travail : dans &lt;em&gt;Adieux au prolétariat&lt;/em&gt; (1980), il affirme que la classe ouvrière n’est plus le sujet de l’émancipation, et que la libération passe par la réduction du temps de travail. L’automatisation permettrait de travailler beaucoup moins, et de développer les activités libres, choisies pour elles-mêmes, plutôt que de produire et consommer toujours plus.&lt;/p&gt; &lt;p&gt;Dès &lt;em&gt;Écologie et politique&lt;/em&gt; (1975), il relie la crise écologique au capitalisme : la croissance infinie détruit la nature et les liens humains. L’écologie doit être une politique de l’autonomie, qui permette de « produire moins, vivre mieux ». Il défendra plus tard un revenu d’existence versé à tous, indépendamment de l’emploi. Dans &lt;em&gt;Lettre à D.&lt;/em&gt; (2006), il écrit un émouvant livre d’amour à sa femme Dorine, gravement malade. Ils se donnent la mort ensemble en 2007, dans leur maison de Vosnon, dans l’Aube.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="H151" s="48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/gorz-mini.webp</t>
+        </is>
+      </c>
+      <c r="J151" s="48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">politique ; ethique</t>
+        </is>
+      </c>
+      <c r="K151" s="48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ecologisme ; Marxisme</t>
+        </is>
+      </c>
+      <c r="L151" s="48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">philosophe et journaliste français, l’un des fondateurs de l’écologie politique.</t>
+        </is>
+      </c>
+      <c r="M151" t="inlineStr">
+        <is>
+          <t xml:space="preserve">juive</t>
+        </is>
+      </c>
+      <c r="N151" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+      <c r="O151">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="152" ht="176.25" customHeight="1" s="49">
+      <c r="A152" s="47">
+        <v>1936</v>
+      </c>
+      <c r="B152" s="47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2025</t>
+        </is>
+      </c>
+      <c r="C152" s="47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1936 – 2025</t>
+        </is>
+      </c>
+      <c r="D152" s="47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Alain ROGER</t>
+        </is>
+      </c>
+      <c r="E152" s="85" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Alain_Roger" title=" Wikipedia"&gt;Alain ROGER&lt;/a&gt; est un philosophe et écrivain français. Né à Mirecourt, dans les Vosges, en 1936, ancien élève de l’École normale supérieure, agrégé de philosophie et élève de &lt;a href="https://fr.wikipedia.org/wiki/Gilles_Deleuze" title=" Wikipedia"&gt;Gilles Deleuze&lt;/a&gt;, il enseigne l’esthétique à l’université de Clermont-Ferrand. Romancier, il publie notamment &lt;em&gt;La Travestie&lt;/em&gt; (1987), adaptée au cinéma par Yves Boisset. Mais il est surtout connu comme le grand théoricien français du &lt;a href="https://fr.wikipedia.org/wiki/Paysage" title=" Wikipedia"&gt;paysage&lt;/a&gt;, auquel il consacre l’essentiel de son œuvre de philosophe.&lt;/p&gt; &lt;p&gt;Dans &lt;em&gt;Nus et paysages&lt;/em&gt; (1978) puis dans le &lt;em&gt;Court traité du paysage&lt;/em&gt; (1997), il soutient que la beauté de la nature n’est pas naturelle : nous voyons le monde à travers les œuvres d’art. Il reprend à Montaigne le mot « artialisation » pour désigner cette transformation de la nature par l’art. Elle peut être directe, « in situ », quand on façonne un jardin ou un corps, ou indirecte, « in visu », quand la peinture, la poésie ou la photographie éduquent notre regard. Le paysage naît ainsi au XVe siècle dans la peinture flamande, par la « fenêtre » ouverte au fond des tableaux.&lt;/p&gt; &lt;p&gt;Il montre que des lieux longtemps jugés affreux, comme la montagne ou le bord de mer, ne sont devenus beaux qu’au XVIIIe siècle, grâce aux écrivains et aux peintres. Ses travaux inspirent paysagistes et aménageurs, et il enseigne à l’école d’architecture de Paris-La Villette. Il est aussi l’auteur d’un &lt;em&gt;Bréviaire de la bêtise&lt;/em&gt; (2008), recueil d’aphorismes sur la sottise et ses formes les plus savantes. Il meurt à Belley, dans l’Ain, le 7 octobre 2025.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="H152" s="48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/alainroger-mini.webp</t>
+        </is>
+      </c>
+      <c r="J152" s="48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">esthetique</t>
+        </is>
+      </c>
+      <c r="K152" s="48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Constructivisme</t>
+        </is>
+      </c>
+      <c r="L152" s="48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">philosophe et romancier français, théoricien de l’« artialisation » et de l’invention du paysage.</t>
+        </is>
+      </c>
+      <c r="N152" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+      <c r="O152"/>
+    </row>
+    <row r="153" ht="176.25" customHeight="1" s="49">
+      <c r="A153" s="47">
+        <v>1938</v>
+      </c>
+      <c r="B153" s="47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2021</t>
+        </is>
+      </c>
+      <c r="C153" s="47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1938 – 2021</t>
+        </is>
+      </c>
+      <c r="D153" s="47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pierre RABHI</t>
+        </is>
+      </c>
+      <c r="E153" s="85" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Pierre_Rabhi" title=" Wikipedia"&gt;Pierre RABHI&lt;/a&gt; est un agriculteur, essayiste et militant français, l’une des figures de l’&lt;a href="https://fr.wikipedia.org/wiki/%C3%89cologisme" title=" Wikipedia"&gt;écologie&lt;/a&gt; en France. Né Rabah Rabhi en 1938 à Kenadsa, une oasis du sud de l’Algérie, il perd sa mère très jeune et est confié à un couple de Français d’Oran ; il se convertit au catholicisme et prend le prénom de Pierre. Venu à Paris, il travaille comme ouvrier, puis s’installe en 1961 avec sa femme Michèle dans les Cévennes ardéchoises, où il devient paysan et pratique une agriculture sans produits chimiques.&lt;/p&gt; &lt;p&gt;À partir de 1981, il forme des paysans au Burkina Faso, puis dans d’autres pays d’Afrique, à l’« agroécologie », une agriculture qui respecte les sols et rend les communautés autonomes. Dans ses livres, comme &lt;em&gt;Vers la sobriété heureuse&lt;/em&gt; (2010), il critique la société de consommation et l’idéologie de la croissance : il faut apprendre à vivre avec moins pour être plus heureux. En 2007, il fonde le mouvement Colibris, d’après une légende amérindienne : pendant un incendie de forêt, le colibri apporte des gouttes d’eau dans son bec, car il « fait sa part ».&lt;/p&gt; &lt;p&gt;Très populaire, il est candidat à l’élection présidentielle de 2002, sans réunir les signatures nécessaires. Son discours spirituel, sa proximité avec l’anthroposophie et son peu d’intérêt pour les combats politiques lui valent aussi des critiques, notamment de journalistes et de scientifiques qui contestent certaines de ses affirmations sur l’agriculture. Il meurt à Lyon en 2021. Son appel à une « insurrection des consciences » a inspiré de nombreuses initiatives locales d’écologie.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="H153" s="48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/rabhi-mini.webp</t>
+        </is>
+      </c>
+      <c r="J153" s="48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ethique ; politique ; spiritualite</t>
+        </is>
+      </c>
+      <c r="K153" s="48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ecologisme</t>
+        </is>
+      </c>
+      <c r="L153" s="48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">agriculteur et essayiste français, pionnier de l’agroécologie et chantre de la « sobriété heureuse ».</t>
+        </is>
+      </c>
+      <c r="N153" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+      <c r="O153"/>
     </row>
     <row r="1048566" ht="12.75" customHeight="1" s="49"/>
     <row r="1048567" ht="12.75" customHeight="1" s="49"/>

--- a/data/frise-philosophes-france.xlsx
+++ b/data/frise-philosophes-france.xlsx
@@ -1304,11 +1304,7 @@
       </c>
       <c r="E8" s="56" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt; &lt;a href="https://fr.wikipedia.org/wiki/Auguste_Comte" title=" Wikipedia"&gt;Auguste COMTE&lt;/a&gt;  était un philosophe français connu pour être le fondateur de la discipline sociologique et pour son système de pensée appelé &lt;a href="https://www.youtube.com/watch?v=n1brw_hmcV8"  style="color:#88A1E9"  title="Le positivisme par Alain Bajomée"&gt;le positivisme&lt;/a&gt; qui est basé sur l'idée que le progrès de la société et de la connaissance doit reposer sur l'observation et l'étude des faits empiriques plutôt que sur la spéculation métaphysique ou religieuse. &lt;/p&gt; &lt;p&gt; 
-Il a également développé une vision hiérarchique des sciences, qu'il appelait &lt;a href="http://people.wku.edu/nathan.love/426-20th/auguste_comte.htm" title="La loi des trois états par Wku.edu "&gt;"la loi des trois états"&lt;/a&gt; où les connaissances humaines passent par trois étapes distinctes : l'état théologique (caractérisé par des explications basées sur des forces surnaturelles), l'état métaphysique (caractérisé par des explications abstraites et spéculatives) et l'état positif (caractérisé par l'observation, l'expérimentation et l'analyse des faits). &lt;/p&gt; &lt;p&gt; 
-Il a  développé le concept de "religion de l'humanité" en considérant que la société avait besoin d'une religion séculière qui mettrait l'accent sur l'altruisme, l'ordre social et la solidarité. La religion de l'humanité devait être basée sur la science et remplacer progressivement les anciennes religions théologiques. &lt;/p&gt; &lt;p&gt; 
-Malgré les critiques, le travail d'Auguste Comte a laissé une empreinte durable sur la philosophie, la sociologie et la pensée sociale. Ses idées ont contribué à façonner la manière dont nous comprenons la société et la façon dont la sociologie est pratiquée aujourd'hui. &lt;/p&gt;  &lt;audio controls title="Le XIXème à travers les âges, Auguste Comte et le positivisme  par France Culture"&gt; &lt;source src="https://cdn.radiofrance.fr/s3/cruiser-production/static/culture/sons/2011/06/s26/les_nouveaux_chemins--FRANCE_CULTURE--NET_05807070-63f3-49c1-99cb-1385ead5a4e2_DF.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt; 
-</t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Auguste_Comte" title=" Wikipedia"&gt;Auguste COMTE&lt;/a&gt; (1798-1857) est un philosophe français, fondateur du &lt;a href="https://www.youtube.com/watch?v=n1brw_hmcV8"  style="color:#88A1E9"  title="Le positivisme par Alain Bajomée"&gt;positivisme&lt;/a&gt; et inventeur du mot « sociologie ». Né à Montpellier, polytechnicien, il devient en 1817 le secrétaire du comte de Saint-Simon, dont il se sépare quelques années plus tard. Il expose sa doctrine dans les six volumes du &lt;em&gt;Cours de philosophie positive&lt;/em&gt; (1830-1842), puis dans le &lt;em&gt;Système de politique positive&lt;/em&gt; (1851-1854).&lt;/p&gt; &lt;p&gt;Selon &lt;a href="http://people.wku.edu/nathan.love/426-20th/auguste_comte.htm" title="La loi des trois états par Wku.edu "&gt;la loi des trois états&lt;/a&gt;, l’esprit humain, dans chaque domaine du savoir comme dans l’histoire des sociétés, passe par trois âges. À l’état théologique, il explique les phénomènes par la volonté de dieux ; à l’état métaphysique, par des forces abstraites, comme la « nature » ou la « vertu dormitive » ; à l’état positif enfin, il renonce à chercher les causes premières et se contente d’établir, par l’observation et le raisonnement, les lois qui relient les faits. Comte classe aussi les sciences selon leur complexité croissante : mathématiques, astronomie, physique, chimie, biologie, et enfin la science de la société, qu’il nomme sociologie en 1838. Celle-ci doit permettre de réorganiser une société troublée par la Révolution, en conciliant l’ordre et le progrès. Après la mort de Clotilde de Vaux, qu’il a aimée passionnément, Comte fonde une « religion de l’Humanité », avec son calendrier, ses fêtes et ses saints laïques, résumée par la devise : « l’Amour pour principe, l’Ordre pour base, et le Progrès pour but ». Il invente aussi le mot « altruisme ».&lt;/p&gt; &lt;p&gt;Son influence a été considérable, de John Stuart Mill et Littré à Durkheim ; la devise « Ordre et Progrès » figure sur le drapeau du Brésil.&lt;/p&gt;  &lt;audio controls title="Le XIXème à travers les âges, Auguste Comte et le positivisme  par France Culture"&gt; &lt;source src="https://cdn.radiofrance.fr/s3/cruiser-production/static/culture/sons/2011/06/s26/les_nouveaux_chemins--FRANCE_CULTURE--NET_05807070-63f3-49c1-99cb-1385ead5a4e2_DF.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;</t>
         </is>
       </c>
       <c r="F8" s="54" t="inlineStr">
@@ -2624,7 +2620,7 @@
       </c>
       <c r="E30" s="59" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/%C3%89mile_Durkheim"  title=" Wikipedia"&gt; Émile DURKHEIM&lt;/a&gt; était un sociologue français et l'un des fondateurs de la &lt;a  href="https://www.youtube.com/watch?v=Uy_ApDmnR-8&amp;ab_channel=LePr%C3%A9cepteur" style="color:#88A1E9"  title="L'invention de la sociologie  par Le Précepteur"&gt;sociologie&lt;/a&gt; moderne et il a contribué à l'étude de la théorie de la structure sociale.&lt;/p&gt; &lt;p&gt;  Il a cherché à établir la sociologie comme une discipline scientifique en se concentrant sur l'étude des faits sociaux, c'est-à-dire les comportements, les croyances et les institutions qui sont partagés par les membres d'une société. Il a soutenu que ces faits sociaux étaient des phénomènes objectifs qui pouvaient être étudiés de manière empirique et que la sociologie devait être basée sur l'observation et la mesure plutôt que sur des spéculations théoriques.&lt;/p&gt; &lt;p&gt; Durkheim a également développé la théorie de la solidarité sociale et de la &lt;a  href="https://www.youtube.com/watch?v=m5tpsuOB11g&amp;ab_channel=FranceCulture"  title="Ecoutez Durkheim parler en 1913 de la valeur des choses par France Culture"&gt;valeur des choses&lt;/a&gt;, qui est la force qui unit les membres d'une société. Il a distingué deux formes de solidarité: la solidarité mécanique, qui repose sur la similitude des individus, et la solidarité organique, qui repose sur la complémentarité des individus. &lt;/p&gt; &lt;p&gt; Un autre concept développé par Durkheim est celui d'anomie, qui se réfère à un état de désordre social dans lequel les individus ne sont plus liés par des normes sociales et des valeurs partagées.&lt;/p&gt;  &lt;audio controls title="Avoir raison avec Emile Durkheim par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/17397-25.08.2017-ITEMA_21416027-5.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt; </t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/%C3%89mile_Durkheim"  title=" Wikipedia"&gt;Émile DURKHEIM&lt;/a&gt; (1858-1917) est l’un des fondateurs de la &lt;a  href="https://www.youtube.com/watch?v=Uy_ApDmnR-8&amp;ab_channel=LePr%C3%A9cepteur" style="color:#88A1E9"  title="L'invention de la sociologie  par Le Précepteur"&gt;sociologie&lt;/a&gt; moderne. Né à Épinal dans une famille de rabbins, normalien, agrégé de philosophie, il donne à Bordeaux, en 1887, le premier cours de sciences sociales d’une université française, puis enseigne à la Sorbonne à partir de 1902. Il fonde en 1898 la revue &lt;em&gt;L’Année sociologique&lt;/em&gt;, avec son neveu Marcel Mauss.&lt;/p&gt; &lt;p&gt;Durkheim veut faire de la sociologie une science. Dans &lt;em&gt;Les Règles de la méthode sociologique&lt;/em&gt; (1895), il demande de « traiter les faits sociaux comme des choses » : les règles du droit, les croyances ou les modes existent hors des individus et s’imposent à eux par une contrainte. Ils doivent être expliqués par d’autres faits sociaux, et non par la psychologie individuelle. Dans &lt;em&gt;De la division du travail social&lt;/em&gt; (1893), il distingue la solidarité mécanique des sociétés traditionnelles, fondée sur la ressemblance, et la solidarité organique des sociétés modernes, fondée sur la complémentarité des fonctions. &lt;em&gt;Le Suicide&lt;/em&gt; (1897) montre qu’un acte en apparence très personnel varie selon l’intégration des individus dans leur groupe : il est plus fréquent chez les isolés et dans les périodes d’« anomie », quand les règles sociales se relâchent. Enfin, &lt;em&gt;Les Formes élémentaires de la vie religieuse&lt;/em&gt; (1912) voient dans la religion, fondée sur la distinction du sacré et du profane, une manière pour la société de se célébrer elle-même.&lt;/p&gt; &lt;p&gt;Engagé dans l’affaire Dreyfus et pour une morale laïque à l’école, il meurt en 1917, peu après son fils tombé à la guerre. On peut encore &lt;a  href="https://www.youtube.com/watch?v=m5tpsuOB11g&amp;ab_channel=FranceCulture"  title="Ecoutez Durkheim parler en 1913 de la valeur des choses par France Culture"&gt;l’entendre parler&lt;/a&gt;, en 1913, de la valeur des choses.&lt;/p&gt;  &lt;audio controls title="Avoir raison avec Emile Durkheim par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/17397-25.08.2017-ITEMA_21416027-5.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;</t>
         </is>
       </c>
       <c r="F30" s="57" t="inlineStr">
@@ -2747,8 +2743,7 @@
       </c>
       <c r="E32" s="62" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Henri_Bergson"  title=" Wikipedia"&gt;Henri BERGSON&lt;/a&gt; est un grand philosophe Français connut pour ses quatres principaux ouvrages, "Les données immédiates de la conscience" paru en 1889, vient ensuite "Matière et mémoire" paru en 1896, puis &lt;a  href="https://philosophie.cegeptr.qc.ca/wp-content/documents/L%C3%A9volution-cr%C3%A9atrice.pdf" title="L'évolution créatrice par Philo cegeptr"&gt;"L'évolution créatrice"&lt;/a&gt; paru en 1907 qui connut un succès phénoménal et enfin  &lt;a  href="https://www.youtube.com/watch?v=E6MNRoeU9Ak&amp;ab_channel=Kosmos"  title="La Conscience par Kosmos"&gt;"Les deux sources de la morale et la religion"&lt;/a&gt; paru en 1932 qui fut un chef d'oeuvre de mysticisme. &lt;/p&gt; &lt;p&gt; Il fut le permier philosophe à recevoir en 1927 le prix nobel de litérature. Il s'est intéressé à de nombreux sujets comme &lt;a  href="https://www.youtube.com/watch?v=M6-L2M_7ysk&amp;ab_channel=LePr%C3%A9cepteur"  title="Les limites du langage par Le Précepteur"&gt;les limites du langage&lt;/a&gt; ou encore &lt;a  href="https://www.youtube.com/watch?v=E-v2eO_m_Fg&amp;ab_channel=Kosmos"  title="La Conscience par Kosmos"&gt;la conscience&lt;/a&gt; mais aussi &lt;a  href="https://www.youtube.com/watch?v=RptdiM_WZrU&amp;ab_channel=LePr%C3%A9cepteur"  title="Le rire par Le Précepteur"&gt;le rire&lt;/a&gt; et la science. &lt;/p&gt;  &lt;p&gt; L'une de ses contributions les plus importantes est &lt;a  href="https://www.youtube.com/watch?v=SWgNY2E40y4&amp;ab_channel=LePr%C3%A9cepteur" style="color:#88A1E9"  title="Le Temps par le Précepteur"&gt;sa théorie sur le temps&lt;/a&gt; qui, pour lui, n'est pas une simple série linéaire d'instants passés, présents et futurs, mais plutôt une expérience continue et intérieure vécue par chaque individu. &lt;/p&gt; &lt;p&gt; Pou lui, l'intuition est un moyen plus direct de connaître la réalité que la seule raison analytique, et qu'elle peut permettre une compréhension plus profonde des phénomènes complexes.&lt;/p&gt; &lt;p&gt; Dans "Matière et mémoire", il examine la nature du corps et de l'esprit, en soutenant que la mémoire est une forme de rétention de l'expérience passée dans le corps, et qu'elle joue un rôle important dans la perception et la compréhension du temps. Il s'est aussi prononcé sur le rôle et l'importance de &lt;a  href="https://www.youtube.com/watch?v=s9SwcAMCPrM&amp;ab_channel=FranceCulture" title="l'unique archive audio de sa voix par France Culture"&gt;l'art dans nos vies&lt;/a&gt;.  &lt;/p&gt;   &lt;audio controls title="Le possible et le réel par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/10467-20.06.2017-ITEMA_21363346-2.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt; 
-</t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Henri_Bergson"  title=" Wikipedia"&gt;Henri BERGSON&lt;/a&gt; (1859-1941) est un philosophe français, l’un des plus célèbres de son temps. Normalien, professeur de lycée puis au Collège de France à partir de 1900, il attire à ses cours une foule cultivée. Élu à l’Académie française en 1914, il reçoit en 1927 le prix Nobel de littérature.&lt;/p&gt; &lt;p&gt;Sa thèse, l’&lt;em&gt;Essai sur les données immédiates de la conscience&lt;/em&gt; (1889), oppose deux temps. Le temps des horloges et des sciences est mesuré, fait d’instants juxtaposés comme des points sur une ligne. &lt;a  href="https://www.youtube.com/watch?v=SWgNY2E40y4&amp;ab_channel=LePr%C3%A9cepteur" style="color:#88A1E9"  title="Le Temps par le Précepteur"&gt;Le temps vécu&lt;/a&gt;, la « durée », est au contraire continu : nos états de &lt;a  href="https://www.youtube.com/watch?v=E-v2eO_m_Fg&amp;ab_channel=Kosmos"  title="La Conscience par Kosmos"&gt;conscience&lt;/a&gt; se fondent les uns dans les autres comme les notes d’une mélodie, et nous sommes libres quand nos actes jaillissent de notre personnalité tout entière. L’intelligence, faite pour agir sur la matière, découpe le réel et le fige, comme le fait &lt;a  href="https://www.youtube.com/watch?v=M6-L2M_7ysk&amp;ab_channel=LePr%C3%A9cepteur"  title="Les limites du langage par Le Précepteur"&gt;le langage&lt;/a&gt; avec ses mots généraux ; seule l’intuition saisit le mouvement de la vie. Dans &lt;em&gt;Matière et mémoire&lt;/em&gt; (1896), il montre que le souvenir n’est pas stocké dans le cerveau, qui sert surtout à l’action. Dans &lt;a  href="https://philosophie.cegeptr.qc.ca/wp-content/documents/L%C3%A9volution-cr%C3%A9atrice.pdf" title="L'évolution créatrice par Philo cegeptr"&gt;&lt;em&gt;L’Évolution créatrice&lt;/em&gt;&lt;/a&gt; (1907), il décrit la vie comme un « élan vital » qui invente sans cesse des formes nouvelles. Son essai sur &lt;a  href="https://www.youtube.com/watch?v=RptdiM_WZrU&amp;ab_channel=LePr%C3%A9cepteur"  title="Le rire par Le Précepteur"&gt;le rire&lt;/a&gt; y voit « du mécanique plaqué sur du vivant ». Enfin, &lt;a  href="https://www.youtube.com/watch?v=E6MNRoeU9Ak&amp;ab_channel=Kosmos"  title="La Conscience par Kosmos"&gt;&lt;em&gt;Les Deux Sources de la morale et de la religion&lt;/em&gt;&lt;/a&gt; (1932) opposent la morale close des sociétés à la morale ouverte des mystiques, qui s’adresse à l’humanité entière.&lt;/p&gt; &lt;p&gt;Il voit dans &lt;a  href="https://www.youtube.com/watch?v=s9SwcAMCPrM&amp;ab_channel=FranceCulture" title="l'unique archive audio de sa voix par France Culture"&gt;l’art&lt;/a&gt; un moyen de percevoir le réel au-delà de nos habitudes. Proche du catholicisme, il refuse de se convertir par solidarité avec les juifs persécutés, et meurt dans Paris occupé en 1941.&lt;/p&gt;  &lt;audio controls title="Le possible et le réel par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/10467-20.06.2017-ITEMA_21363346-2.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;</t>
         </is>
       </c>
       <c r="F32" s="54" t="inlineStr">
@@ -5225,8 +5220,7 @@
       </c>
       <c r="E73" s="59" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Jean-Paul_Sartre"   title=" Wikipedia"&gt;Jean-Paul SARTRE&lt;/a&gt; était un philosophe Français &lt;a href="https://www.youtube.com/watch?v=kX3saEPOG-g&amp;t=51s&amp;ab_channel=Coursitout" title="Nous sommes condamnés à être libre par Yapi Florent AKICHI"&gt;Existentialiste&lt;/a&gt;, qui met l'accent sur la liberté humaine et la responsabilité personnelle dans la détermination de la signification de la vie.  Il n’y a pas d’essence humaine figée et préétablie, essence qui précéderait l’existence. &lt;/p&gt; &lt;p&gt;  Dans son œuvre  "L'Être et le Néant", il développe le fait que les individus sont définis par leurs actions et leurs choix, et non par des caractéristiques innées ou des conditions sociales. Pour lui, exister, c’est être là, dans un univers absurde et contingent, l’homme surgit et il y dessine son chemin. &lt;/p&gt; &lt;p&gt;  Il a exploré les inconvénients et les joies d'être fondamentalement  &lt;a href="https://www.youtube.com/watch?v=xN0ysLkGiP8&amp;ab_channel=LePr%C3%A9cepteur"   title="Nous sommes condamnés à être libre par le Précepteur"&gt;Libre&lt;/a&gt;. Il a également été un militant politique actif et un fervent défenseur de la liberté et de la justice sociale.&lt;/p&gt; &lt;p&gt;   Il accorde une très grande importance au &lt;a href="https://www.youtube.com/watch?v=BJIM41TnDHI&amp;ab_channel=LePr%C3%A9cepteur"  title="Le regard des autres par le Précepteur"&gt;"regard des autres"&lt;/a&gt; et une de ses citations les plus connus "l'enfer, c'est les autres", huis clos théatral écrit en 1943 et dans lequel il illustre parfaitement la difficile coexistence des consciences, le fait qu'autrui est ce qui nous aliène et nous enferme dans une nature donnée, ce qui nous prive de liberté.&lt;/p&gt; &lt;p&gt;   Il partagera pendant plus de 50 ans sa vie avec Simone de BEAUVOIR dans une &lt;a href="https://www.youtube.com/watch?v=5BCjCYimqlc&amp;ab_channel=LePr%C3%A9cepteur"  title="L'amour par le Précepteur"&gt;relation libre&lt;/a&gt;, couple mythique et anticonformiste.&lt;/p&gt;   &lt;audio controls title="Le roman comme expérience par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/22054-28.03.2021-ITEMA_22624288-2017C24632S0115.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt; 
-</t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Jean-Paul_Sartre"   title=" Wikipedia"&gt;Jean-Paul SARTRE&lt;/a&gt; (1905-1980) est un philosophe, romancier et dramaturge français, la grande figure de l’&lt;a href="https://www.youtube.com/watch?v=kX3saEPOG-g&amp;t=51s&amp;ab_channel=Coursitout" title="Nous sommes condamnés à être libre par Yapi Florent AKICHI"&gt;existentialisme&lt;/a&gt;. Normalien, agrégé de philosophie en 1929, il découvre la phénoménologie de Husserl à Berlin en 1933, puis publie &lt;em&gt;La Nausée&lt;/em&gt; (1938), roman de l’absurdité d’exister. Prisonnier de guerre en 1940, il fait paraître en 1943 son grand traité, &lt;em&gt;L’Être et le Néant&lt;/em&gt;.&lt;/p&gt; &lt;p&gt;Pour Sartre, chez l’homme, « l’existence précède l’essence » : il n’y a pas de nature humaine fixée d’avance, chacun se définit par ses actes. La conscience n’est pas une chose, mais un néant, une ouverture qui ne coïncide jamais avec elle-même. L’homme est donc &lt;a href="https://www.youtube.com/watch?v=xN0ysLkGiP8&amp;ab_channel=LePr%C3%A9cepteur"   title="Nous sommes condamnés à être libre par le Précepteur"&gt;libre&lt;/a&gt;, et même « condamné à être libre » : il ne peut pas ne pas choisir, et il est responsable de ce qu’il fait de lui-même. Beaucoup fuient cette angoisse dans la « mauvaise foi », comme le garçon de café qui joue à être garçon de café pour se donner l’existence d’une chose. Sous &lt;a href="https://www.youtube.com/watch?v=BJIM41TnDHI&amp;ab_channel=LePr%C3%A9cepteur"  title="Le regard des autres par le Précepteur"&gt;le regard d’autrui&lt;/a&gt;, je deviens un objet, figé dans une image que je ne maîtrise pas, d’où la réplique de &lt;em&gt;Huis clos&lt;/em&gt; (1944) : « l’enfer, c’est les autres ». Après la guerre, Sartre fonde la revue &lt;em&gt;Les Temps modernes&lt;/em&gt; et défend l’engagement de l’écrivain. Il se rapproche du marxisme, qu’il veut concilier avec la liberté dans la &lt;em&gt;Critique de la raison dialectique&lt;/em&gt; (1960), et prend parti dans les luttes de son temps, contre la guerre d’Algérie, puis en Mai 68.&lt;/p&gt; &lt;p&gt;En 1964, il refuse le prix Nobel de littérature. Il partage sa vie avec Simone de Beauvoir dans une &lt;a href="https://www.youtube.com/watch?v=5BCjCYimqlc&amp;ab_channel=LePr%C3%A9cepteur"  title="L'amour par le Précepteur"&gt;relation libre&lt;/a&gt;, et ses funérailles, en 1980, rassemblent des dizaines de milliers de personnes.&lt;/p&gt;  &lt;audio controls title="Le roman comme expérience par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/22054-28.03.2021-ITEMA_22624288-2017C24632S0115.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;</t>
         </is>
       </c>
       <c r="F73" s="57" t="inlineStr">
@@ -5756,127 +5750,124 @@
         </is>
       </c>
     </row>
-    <row r="82" ht="156" customHeight="1" s="49">
-      <c r="A82" s="54" t="n">
+    <row r="82" ht="204" customHeight="1" s="49">
+      <c r="A82" s="57" t="n">
         <v>1908</v>
       </c>
-      <c r="B82" s="54" t="inlineStr">
-        <is>
-          <t>1986</t>
-        </is>
-      </c>
-      <c r="C82" s="54" t="inlineStr">
-        <is>
-          <t>1908 - 1986</t>
-        </is>
-      </c>
-      <c r="D82" s="55" t="inlineStr">
-        <is>
-          <t>Simone de BEAUVOIR</t>
-        </is>
-      </c>
-      <c r="E82" s="56" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;p&gt; &lt;a href="https://fr.wikipedia.org/wiki/Simone_de_Beauvoir"  title=" Wikipedia"&gt; Simone de BEAUVOIR&lt;/a&gt; était une philosophe et intellectuelle anticonformiste. Elle fut une figure importante du &lt;a href="https://www.youtube.com/watch?v=J3AW5eQEs68&amp;ab_channel=LePr%C3%A9cepteur"  title="Le Féminisme Existentialiste par le Précepteur"&gt; "Féminisme Existentialiste" &lt;/a&gt;  en France et a écrit de nombreux livres dont des essais philosophiques comme "La force des choses" ou encore "Tous les hommes sont mortels"mais surtout &lt;a href="https://www.youtube.com/watch?v=QsnELrcARYU"  title="Le Deuxième Sexe de Simone de BEAUVOIR"&gt; "Le Deuxième Sexe" &lt;/a&gt; publié en 1949, qui a influencé la pensée féministe du XXe siècle et qui a établi la distinction entre "femme" comme une construction sociale et "femelle" comme une caractéristique biologique. &lt;/p&gt; &lt;p&gt; Elle était également une activiste sociale et politique engagée et a travaillé pour les droits des femmes et la liberté de choix en matière de contraception et d'avortement. &lt;/p&gt; &lt;p&gt; Elle a également été une défenseure des droits des personnes LGBT et des minorités ethniques. Elle a établi une distinction fondamentale entre le sexe (biologique) et le genre (socialement construit) et a soutenu que les femmes étaient soumises à une "aliénation ontologique" et à une "oppression politique", car la société les définissait comme des "autres" en opposition aux hommes. Une de ses phrases les plus connus: &lt;a href="https://fr.wikipedia.org/wiki/Le_Deuxi%C3%A8me_Sexe"  title=" Le deuxième sexe par wikipedia"&gt; "on ne naît pas femme, on le devient"&lt;/a&gt;. &lt;/p&gt; &lt;p&gt; Elle partagera pendant 51 ans sa vie avec le philosophe Jean-Paul SARTRE.  &lt;/p&gt;   &lt;audio controls title="Jean BEAUFRETpar France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/10471-17.04.2008-ITEMA_20120174-2008C3330E0015-ITE_00016512_RSCE-21.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt; </t>
-        </is>
-      </c>
-      <c r="F82" s="54" t="inlineStr">
-        <is>
-          <t>PY3Ie8Mnw9E</t>
-        </is>
-      </c>
-      <c r="G82" s="56" t="inlineStr">
-        <is>
-          <t>Simone de Beauvoir par Brut</t>
-        </is>
-      </c>
-      <c r="H82" s="56" t="inlineStr">
-        <is>
-          <t>https://www.laphilo.fr/pho/beauvoir-mini.webp</t>
-        </is>
-      </c>
-      <c r="J82" s="48" t="inlineStr">
-        <is>
-          <t>ethique ; politique</t>
-        </is>
-      </c>
-      <c r="K82" s="48" t="inlineStr">
-        <is>
-          <t>Existentialisme ; Féminisme</t>
-        </is>
-      </c>
-      <c r="L82" s="48" t="inlineStr">
-        <is>
-          <t>philosophe française et intellectuelle anticonformiste figure de l'existentialisme.</t>
-        </is>
-      </c>
-      <c r="M82" t="inlineStr">
-        <is>
-          <t xml:space="preserve">femme</t>
-        </is>
-      </c>
-      <c r="N82" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-      <c r="O82">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="83" ht="204" customHeight="1" s="49">
-      <c r="A83" s="57" t="n">
-        <v>1908</v>
-      </c>
-      <c r="B83" s="57" t="inlineStr">
+      <c r="B82" s="57" t="inlineStr">
         <is>
           <t>1961</t>
         </is>
       </c>
-      <c r="C83" s="57" t="inlineStr">
+      <c r="C82" s="57" t="inlineStr">
         <is>
           <t>1908 – 1961</t>
         </is>
       </c>
-      <c r="D83" s="58" t="inlineStr">
+      <c r="D82" s="58" t="inlineStr">
         <is>
           <t>Maurice MERLEAU-PONTY</t>
         </is>
       </c>
-      <c r="E83" s="65" t="inlineStr">
+      <c r="E82" s="65" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Maurice_Merleau-Ponty" title=" Wikipedia"&gt;Maurice MERLEAU-PONTY&lt;/a&gt; était un philosophe français connu pour ses contributions à la phénoménologie, à la philosophie de la perception et à l’existentialisme. Il  s’inspire de plusieurs courants et penseurs et  reprend l’idée d’une description des expériences vécues, mais critique l’idéalisme husserlien. Dans son oeurvre majeure &lt;a href="https://www.youtube.com/watch?v=RrD5SEiXr_A"  title=" La phénoménologie de Maurice Merleau-Ponty par Tes grands auteurs en petits morceaux"&gt;"Phénoménalogie de la perception"&lt;/a&gt; il  y développe une critique radicale des approches traditionnelles de la perception pour proposer une vision incarnée et existentielle de l’expérience humaine. Il rejette la séparation cartésienne entre le corps et l’esprit &lt;a href="https://classiques.uqam.ca/classiques/merleau_ponty_maurice/sens_et_non_sens/sens_et_non_sens.html"  title="  Maurice Merleau-Ponty sens et non sens  par UQAM"&gt;(sens et non sens)&lt;/a&gt;. Pour lui, le corps n’est pas un objet, mais un sujet percevant :  &lt;/p&gt; &lt;p&gt;
 -  Le corps propre : C’est par lui que nous faisons l’expérience du monde. Il est à la fois sujet et objet, toujours déjà engagé dans un environnement. &lt;/p&gt; &lt;p&gt; - La perception comme ouverture au monde : &lt;a href="https://www.youtube.com/watch?v=yiHMPFMCUvo" title="MERLEAU-PONTY - L'OEIL ET L'ESPRIT par Kosmos"&gt;Percevoir&lt;/a&gt;, c’est être en dialogue avec le monde, pas simplement recevoir des données sensorielles. &lt;/p&gt;  &lt;p&gt;   Il  s’intéresse au langage comme geste corporel. Pour lui, la parole n’est pas un simple véhicule de la pensée, mais une incarnation du sens et l’art montre comment l’expression émerge de la perception. &lt;/p&gt; &lt;p&gt; Dans "Le Visible et l’invisible", il développe une  &lt;a href="https://www.youtube.com/watch?v=wZNUUGSZHMs"  title=" Maurice Merleau-Ponty - Entretien : Heure de culture française par Artesquieu "&gt;ontologie originale&lt;/a&gt; où le "chair" est ni matière ni esprit, c’est une substance sensible qui unit le corps et le monde.  Chiasme : Concept décrivant l’entrelacs du voyant et du visible, du touchant et du touché (ex. : quand je me touche la main, je suis à la fois sujet et objet).  L’invisible : Non pas l’absence de visible, mais ce qui le structure. &lt;/p&gt;   &lt;audio controls title="Maurice Merleau-Ponty : Partie 8/12- La crise de la pensée religieuse par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/13915-20.11.2014-ITEMA_20690515-2013C3372E0710-21.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;  </t>
         </is>
       </c>
-      <c r="F83" s="57" t="inlineStr">
+      <c r="F82" s="57" t="inlineStr">
         <is>
           <t>yiHMPFMCUvo</t>
         </is>
       </c>
-      <c r="G83" s="59" t="inlineStr">
+      <c r="G82" s="59" t="inlineStr">
         <is>
           <t>"MERLEAU-PONTY - L'OEIL ET L'ESPRIT" par Kosmos</t>
         </is>
       </c>
-      <c r="H83" s="59" t="inlineStr">
+      <c r="H82" s="59" t="inlineStr">
         <is>
           <t>https://www.laphilo.fr/pho/ponty-mini.webp</t>
         </is>
       </c>
+      <c r="J82" s="48" t="inlineStr">
+        <is>
+          <t>epistemologie ; metaphysique</t>
+        </is>
+      </c>
+      <c r="K82" s="48" t="inlineStr">
+        <is>
+          <t>Phénoménologie</t>
+        </is>
+      </c>
+      <c r="L82" s="48" t="inlineStr">
+        <is>
+          <t>philosophe français connu pour ses contributions à la phénoménologie.</t>
+        </is>
+      </c>
+      <c r="N82" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+    </row>
+    <row r="83" ht="210" customHeight="1" s="49">
+      <c r="A83" s="54" t="n">
+        <v>1908</v>
+      </c>
+      <c r="B83" s="54" t="inlineStr">
+        <is>
+          <t>1944</t>
+        </is>
+      </c>
+      <c r="C83" s="54" t="inlineStr">
+        <is>
+          <t>1908 – 1944</t>
+        </is>
+      </c>
+      <c r="D83" s="55" t="inlineStr">
+        <is>
+          <t>Albert LAUTMAN</t>
+        </is>
+      </c>
+      <c r="E83" s="56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Albert_Lautman" title=" Wikipedia"&gt;Albert LAUTMAN&lt;/a&gt; était un philosophe français des mathématiques, dont l'œuvre courte mais d'une originalité remarquable a exercé une influence durable sur la philosophie française des sciences et des mathématiques. Né à Paris dans une famille juive, normalien et agrégé de philosophie, il fut mobilisé en 1939 et, après l'armistice, rejoignit la Résistance. Arrêté par la Gestapo en 1944, il fut fusillé à Mont-de-Marsan le 1er août de la même année, à l'âge de 35 ans, laissant une œuvre inachevée mais fondamentale. &lt;/p&gt; &lt;p&gt; &lt;a href="https://www.youtube.com/watch?v=aBr6djRSCiE"  title=" Albert Lautman et le platonisme dynamique par Hamda Mlika"&gt;Sa philosophie &lt;/a&gt; s'articule autour d'une réflexion originale sur les rapports entre mathématiques et philosophie. Dans ses thèses et ses essais — réunis sous le titre posthume &lt;em&gt;Essai sur l'unité des mathématiques et divers écrits&lt;/em&gt; (1977) — il soutient que les grandes théories mathématiques  (topologie, algèbre abstraite, géométrie différentielle) ne sont pas de simples constructions formelles, mais réalisent dans leur domaine propre des structures dialectiques qui constituent des problèmes philosophiques fondamentaux, tels que la relation entre le local et le global, le continu et le discret, l'un et le multiple. &lt;/p&gt; &lt;p&gt; Cette thèse fait de lui un penseur singulier à l'intersection de la philosophie platonicienne — il voit dans les mathématiques une participation à des idées dialectiques — et de la philosophie des sciences modernes. Gilles Deleuze reconnut en lui un précurseur de sa propre théorie du problème et de la différence. Fernando Zalamea a contribué à renouveler l'intérêt pour sa pensée dans les débats contemporains sur la philosophie des mathématiques. &lt;/p&gt;  &lt;audio controls title="Pourquoi les philosophes mathématiciens se sont fait fusiller  par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/13957-15.01.2022-ITEMA_22900988-2022C22785S0015-NET_MFC_0B385814-1D52-4706-8B44-2A8E4B2A1FAF-21-a970caaf0dead3c1677f6dad167bee92.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;  </t>
+        </is>
+      </c>
+      <c r="F83" s="54" t="inlineStr">
+        <is>
+          <t>abLPmODCgA4</t>
+        </is>
+      </c>
+      <c r="G83" s="56" t="inlineStr">
+        <is>
+          <t>"1908 - 1944 | Albert Lautman | Philosopher of Mathematical Reality" par Essai</t>
+        </is>
+      </c>
+      <c r="H83" s="56" t="inlineStr">
+        <is>
+          <t>https://www.laphilo.fr/pho/lautman-mini.webp</t>
+        </is>
+      </c>
       <c r="J83" s="48" t="inlineStr">
         <is>
-          <t>epistemologie ; metaphysique</t>
+          <t>epistemologie</t>
         </is>
       </c>
       <c r="K83" s="48" t="inlineStr">
         <is>
-          <t>Phénoménologie</t>
+          <t>Rationalisme</t>
         </is>
       </c>
       <c r="L83" s="48" t="inlineStr">
         <is>
-          <t>philosophe français connu pour ses contributions à la phénoménologie.</t>
+          <t>philosophe français des mathématiques et résistant arrêté.</t>
+        </is>
+      </c>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t xml:space="preserve">juive</t>
         </is>
       </c>
       <c r="N83" t="inlineStr">
@@ -5885,58 +5876,56 @@
         </is>
       </c>
     </row>
-    <row r="84" ht="210" customHeight="1" s="49">
+    <row r="84" ht="330.75" customHeight="1" s="49">
       <c r="A84" s="54" t="n">
         <v>1908</v>
       </c>
-      <c r="B84" s="54" t="inlineStr">
-        <is>
-          <t>1944</t>
-        </is>
+      <c r="B84" s="54" t="n">
+        <v>2009</v>
       </c>
       <c r="C84" s="54" t="inlineStr">
         <is>
-          <t>1908 – 1944</t>
+          <t>1908 – 2009</t>
         </is>
       </c>
       <c r="D84" s="55" t="inlineStr">
         <is>
-          <t>Albert LAUTMAN</t>
-        </is>
-      </c>
-      <c r="E84" s="56" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Albert_Lautman" title=" Wikipedia"&gt;Albert LAUTMAN&lt;/a&gt; était un philosophe français des mathématiques, dont l'œuvre courte mais d'une originalité remarquable a exercé une influence durable sur la philosophie française des sciences et des mathématiques. Né à Paris dans une famille juive, normalien et agrégé de philosophie, il fut mobilisé en 1939 et, après l'armistice, rejoignit la Résistance. Arrêté par la Gestapo en 1944, il fut fusillé à Mont-de-Marsan le 1er août de la même année, à l'âge de 35 ans, laissant une œuvre inachevée mais fondamentale. &lt;/p&gt; &lt;p&gt; &lt;a href="https://www.youtube.com/watch?v=aBr6djRSCiE"  title=" Albert Lautman et le platonisme dynamique par Hamda Mlika"&gt;Sa philosophie &lt;/a&gt; s'articule autour d'une réflexion originale sur les rapports entre mathématiques et philosophie. Dans ses thèses et ses essais — réunis sous le titre posthume &lt;em&gt;Essai sur l'unité des mathématiques et divers écrits&lt;/em&gt; (1977) — il soutient que les grandes théories mathématiques  (topologie, algèbre abstraite, géométrie différentielle) ne sont pas de simples constructions formelles, mais réalisent dans leur domaine propre des structures dialectiques qui constituent des problèmes philosophiques fondamentaux, tels que la relation entre le local et le global, le continu et le discret, l'un et le multiple. &lt;/p&gt; &lt;p&gt; Cette thèse fait de lui un penseur singulier à l'intersection de la philosophie platonicienne — il voit dans les mathématiques une participation à des idées dialectiques — et de la philosophie des sciences modernes. Gilles Deleuze reconnut en lui un précurseur de sa propre théorie du problème et de la différence. Fernando Zalamea a contribué à renouveler l'intérêt pour sa pensée dans les débats contemporains sur la philosophie des mathématiques. &lt;/p&gt;  &lt;audio controls title="Pourquoi les philosophes mathématiciens se sont fait fusiller  par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/13957-15.01.2022-ITEMA_22900988-2022C22785S0015-NET_MFC_0B385814-1D52-4706-8B44-2A8E4B2A1FAF-21-a970caaf0dead3c1677f6dad167bee92.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;  </t>
+          <t>Claude LEVI-STRAUSS</t>
+        </is>
+      </c>
+      <c r="E84" s="87" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt; &lt;a href="https://fr.wikipedia.org/wiki/Claude_L%C3%A9vi-Strauss"  title=" Wikipedia"&gt;Claude LEVI-STRAUSS&lt;/a&gt; était un anthropologue et ethnologue français, considéré comme l’une des grandes figures intellectuelles du XXᵉ siècle. Après des études de droit puis de philosophie, il se tourne vers l’ethnologie et commence ses premières missions de terrain au Brésil dans les années 1930, auprès de peuples amérindiens du Mato Grosso et de l’Amazonie. De ces expériences, il tirera notamment le livre Tristes tropiques, qui le rend célèbre auprès d’un public plus large en mêlant récit de voyage, &lt;a href="https://www.youtube.com/watch?v=Fk7du0Avh7U" title="peuples amerindiens levi-strauss par ina culture"&gt; réflexion sur les sociétés &lt;/a&gt; dites « primitives » et critique de l’ethnocentrisme occidental. &lt;/p&gt; &lt;p&gt; Il est connu pour avoir fondé l’anthropologie structurale, une manière d’étudier les cultures qui cherche les structures profondes, souvent inconscientes, qui organisent les systèmes de parenté, les mythes, les rites et plus largement les formes de vie sociales. Inspiré par la linguistique structurale, il considère que les faits culturels sont comme des langages : ce qui compte, ce sont les relations entre les éléments, plutôt que les éléments pris isolément. Sa méthode vise à réduire la diversité apparente des cultures à des ensembles de relations et d’oppositions formelles, par exemple des oppositions binaires (nature/culture, cru/cuit, vie/mort) qui structurent l’imaginaire. &lt;/p&gt; &lt;p&gt; Une partie centrale de son œuvre concerne les systèmes de parenté et l’alliance matrimoniale, qu’il étudie en détail dans Les structures élémentaires de la parenté, publié en 1949. Il y développe la théorie de l’alliance, selon laquelle les liens de parenté ne sont pas seulement des liens de sang, mais aussi des échanges de femmes entre groupes qui créent des solidarités et des obligations réciproques. Le mariage devient ainsi un mécanisme de communication sociale, une manière d’établir des réseaux d’alliance qui rendent possible la cohésion de la société. &lt;/p&gt; &lt;p&gt; Un autre volet majeur de sa pensée est son travail sur les mythes, en particulier dans les quatre volumes des Mythologiques, où il cherche à montrer que les mythes des différentes cultures, malgré leur grande diversité, obéissent à des schémas de transformation et à des structures communes. Pour lui, le mythe n’est pas une simple histoire, mais un système logique qui met en scène des oppositions et des médiations  pour résoudre symboliquement des tensions fondamentales. En analysant les mythes comme des ensembles de relations, il soutient que  &lt;a href="https://www.youtube.com/watch?v=fC0HUuXknHk" title="etre pessimiste pour l’avenir par ina culture"&gt;l’esprit humain fonctionne &lt;/a&gt;  partout selon des structures universelles, même si le contenu des récits varie. &lt;/p&gt; &lt;p&gt; Il développa une réflexion plus générale sur la diversité culturelle et les effets du colonialisme et de la modernité, notamment dans Tristes tropiques où il critique la tendance du monde moderne à homogénéiser et à détruire les différences culturelles. Il affirme l’idée que toutes les cultures sont égales en dignité et que la diversité des formes de vie humaines représente une richesse qu’il faut préserver, plutôt qu’un obstacle à dépasser. Son œuvre, reconnue par de nombreuses distinctions (médaille d’or du CNRS, élection à l’Académie française, prix Érasme, etc.), a contribué à transformer notre manière de penser le rapport entre l’Occident et les autres sociétés, ainsi que les fondements mêmes des sciences sociales. &lt;/p&gt;    &lt;audio controls title="sur les pas de claude levi-dtrausspar France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/13019-03.08.2022-ITEMA_23099095-2022F20970S0215-22.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;  </t>
         </is>
       </c>
       <c r="F84" s="54" t="inlineStr">
         <is>
-          <t>abLPmODCgA4</t>
+          <t>EPebdq4ZAsQ</t>
         </is>
       </c>
       <c r="G84" s="56" t="inlineStr">
         <is>
-          <t>"1908 - 1944 | Albert Lautman | Philosopher of Mathematical Reality" par Essai</t>
-        </is>
-      </c>
-      <c r="H84" s="56" t="inlineStr">
-        <is>
-          <t>https://www.laphilo.fr/pho/lautman-mini.webp</t>
+          <t xml:space="preserve">claude levi-strauss le structuralisme par Ina Culture</t>
+        </is>
+      </c>
+      <c r="H84" s="62" t="inlineStr">
+        <is>
+          <t>https://www.laphilo.fr/pho/clstrauss-mini.webp</t>
         </is>
       </c>
       <c r="J84" s="48" t="inlineStr">
         <is>
-          <t>epistemologie</t>
+          <t>ethique</t>
         </is>
       </c>
       <c r="K84" s="48" t="inlineStr">
         <is>
-          <t>Rationalisme</t>
+          <t xml:space="preserve">Structuralisme ; Totémisme </t>
         </is>
       </c>
       <c r="L84" s="48" t="inlineStr">
         <is>
-          <t>philosophe français des mathématiques et résistant arrêté.</t>
+          <t>philosophe et anthropologue français qui  fonda l’anthropologie structurale.</t>
         </is>
       </c>
       <c r="M84" t="inlineStr">
@@ -5950,67 +5939,72 @@
         </is>
       </c>
     </row>
-    <row r="85" ht="330.75" customHeight="1" s="49">
+    <row r="85" ht="156" customHeight="1" s="49">
       <c r="A85" s="54" t="n">
         <v>1908</v>
       </c>
-      <c r="B85" s="54" t="n">
-        <v>2009</v>
+      <c r="B85" s="54" t="inlineStr">
+        <is>
+          <t>1986</t>
+        </is>
       </c>
       <c r="C85" s="54" t="inlineStr">
         <is>
-          <t>1908 – 2009</t>
+          <t>1908 - 1986</t>
         </is>
       </c>
       <c r="D85" s="55" t="inlineStr">
         <is>
-          <t>Claude LEVI-STRAUSS</t>
-        </is>
-      </c>
-      <c r="E85" s="87" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;p&gt; &lt;a href="https://fr.wikipedia.org/wiki/Claude_L%C3%A9vi-Strauss"  title=" Wikipedia"&gt;Claude LEVI-STRAUSS&lt;/a&gt; était un anthropologue et ethnologue français, considéré comme l’une des grandes figures intellectuelles du XXᵉ siècle. Après des études de droit puis de philosophie, il se tourne vers l’ethnologie et commence ses premières missions de terrain au Brésil dans les années 1930, auprès de peuples amérindiens du Mato Grosso et de l’Amazonie. De ces expériences, il tirera notamment le livre Tristes tropiques, qui le rend célèbre auprès d’un public plus large en mêlant récit de voyage, &lt;a href="https://www.youtube.com/watch?v=Fk7du0Avh7U" title="peuples amerindiens levi-strauss par ina culture"&gt; réflexion sur les sociétés &lt;/a&gt; dites « primitives » et critique de l’ethnocentrisme occidental. &lt;/p&gt; &lt;p&gt; Il est connu pour avoir fondé l’anthropologie structurale, une manière d’étudier les cultures qui cherche les structures profondes, souvent inconscientes, qui organisent les systèmes de parenté, les mythes, les rites et plus largement les formes de vie sociales. Inspiré par la linguistique structurale, il considère que les faits culturels sont comme des langages : ce qui compte, ce sont les relations entre les éléments, plutôt que les éléments pris isolément. Sa méthode vise à réduire la diversité apparente des cultures à des ensembles de relations et d’oppositions formelles, par exemple des oppositions binaires (nature/culture, cru/cuit, vie/mort) qui structurent l’imaginaire. &lt;/p&gt; &lt;p&gt; Une partie centrale de son œuvre concerne les systèmes de parenté et l’alliance matrimoniale, qu’il étudie en détail dans Les structures élémentaires de la parenté, publié en 1949. Il y développe la théorie de l’alliance, selon laquelle les liens de parenté ne sont pas seulement des liens de sang, mais aussi des échanges de femmes entre groupes qui créent des solidarités et des obligations réciproques. Le mariage devient ainsi un mécanisme de communication sociale, une manière d’établir des réseaux d’alliance qui rendent possible la cohésion de la société. &lt;/p&gt; &lt;p&gt; Un autre volet majeur de sa pensée est son travail sur les mythes, en particulier dans les quatre volumes des Mythologiques, où il cherche à montrer que les mythes des différentes cultures, malgré leur grande diversité, obéissent à des schémas de transformation et à des structures communes. Pour lui, le mythe n’est pas une simple histoire, mais un système logique qui met en scène des oppositions et des médiations  pour résoudre symboliquement des tensions fondamentales. En analysant les mythes comme des ensembles de relations, il soutient que  &lt;a href="https://www.youtube.com/watch?v=fC0HUuXknHk" title="etre pessimiste pour l’avenir par ina culture"&gt;l’esprit humain fonctionne &lt;/a&gt;  partout selon des structures universelles, même si le contenu des récits varie. &lt;/p&gt; &lt;p&gt; Il développa une réflexion plus générale sur la diversité culturelle et les effets du colonialisme et de la modernité, notamment dans Tristes tropiques où il critique la tendance du monde moderne à homogénéiser et à détruire les différences culturelles. Il affirme l’idée que toutes les cultures sont égales en dignité et que la diversité des formes de vie humaines représente une richesse qu’il faut préserver, plutôt qu’un obstacle à dépasser. Son œuvre, reconnue par de nombreuses distinctions (médaille d’or du CNRS, élection à l’Académie française, prix Érasme, etc.), a contribué à transformer notre manière de penser le rapport entre l’Occident et les autres sociétés, ainsi que les fondements mêmes des sciences sociales. &lt;/p&gt;    &lt;audio controls title="sur les pas de claude levi-dtrausspar France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/13019-03.08.2022-ITEMA_23099095-2022F20970S0215-22.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;  </t>
+          <t>Simone de BEAUVOIR</t>
+        </is>
+      </c>
+      <c r="E85" s="56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Simone_de_Beauvoir"  title=" Wikipedia"&gt;Simone de BEAUVOIR&lt;/a&gt; (1908-1986) est une philosophe et romancière française, l’une des grandes figures de l’existentialisme et du féminisme du XXe siècle. Née à Paris dans une famille bourgeoise et catholique, elle rompt avec ce milieu, réussit en 1929 l’agrégation de philosophie, où elle rencontre Jean-Paul Sartre, et enseigne dans plusieurs lycées. Ils resteront liés toute leur vie, sans se marier ni vivre ensemble.&lt;/p&gt; &lt;p&gt;Dans &lt;em&gt;Pour une morale de l’ambiguïté&lt;/em&gt; (1947), elle prolonge la pensée de Sartre : l’homme est libre, mais sa liberté n’a de sens que si elle veut aussi celle des autres. Elle en tire un &lt;a href="https://www.youtube.com/watch?v=J3AW5eQEs68&amp;ab_channel=LePr%C3%A9cepteur"  title="Le Féminisme Existentialiste par le Précepteur"&gt;féminisme existentialiste&lt;/a&gt;. Dans &lt;a href="https://www.youtube.com/watch?v=QsnELrcARYU"  title="Le Deuxième Sexe de Simone de BEAUVOIR"&gt;&lt;em&gt;Le Deuxième Sexe&lt;/em&gt;&lt;/a&gt; (1949), elle montre que l’humanité a été pensée au masculin, et que la femme a été définie comme « l’Autre » de l’homme. Ni la biologie, ni la psychanalyse, ni l’histoire ne justifient cette situation : elle résulte de l’éducation, des mythes et des institutions qui enferment les femmes dans les rôles d’épouse et de mère. &lt;a href="https://fr.wikipedia.org/wiki/Le_Deuxi%C3%A8me_Sexe"  title=" Le deuxième sexe par wikipedia"&gt;« On ne naît pas femme : on le devient »&lt;/a&gt;. L’émancipation passe par la liberté de choisir sa vie, et d’abord par le travail et l’indépendance économique. Le livre fait scandale, puis devient une référence du féminisme dans le monde entier.&lt;/p&gt; &lt;p&gt;Romancière, elle reçoit le prix Goncourt en 1954 pour &lt;em&gt;Les Mandarins&lt;/em&gt; et raconte sa jeunesse dans les &lt;em&gt;Mémoires d’une jeune fille rangée&lt;/em&gt;. Engagée, elle signe en 1971 le manifeste des 343 femmes déclarant avoir avorté. Elle étudie aussi le sort des personnes âgées dans &lt;em&gt;La Vieillesse&lt;/em&gt; (1970).&lt;/p&gt;  &lt;audio controls title="Les féministes contemporaines se réclament-elles toujours de Simone de Beauvoir par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/10175-14.04.2026-ITEMA_24475616-2026C53458S0104-NET_MFC_D6B88A9C-001A-4EAF-84CB-D43E021E8A90-21-89a773555bc6a04e1bca98fa20edba08.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;</t>
         </is>
       </c>
       <c r="F85" s="54" t="inlineStr">
         <is>
-          <t>EPebdq4ZAsQ</t>
+          <t>PY3Ie8Mnw9E</t>
         </is>
       </c>
       <c r="G85" s="56" t="inlineStr">
         <is>
-          <t xml:space="preserve">claude levi-strauss le structuralisme par Ina Culture</t>
-        </is>
-      </c>
-      <c r="H85" s="62" t="inlineStr">
-        <is>
-          <t>https://www.laphilo.fr/pho/clstrauss-mini.webp</t>
+          <t>Simone de Beauvoir par Brut</t>
+        </is>
+      </c>
+      <c r="H85" s="56" t="inlineStr">
+        <is>
+          <t>https://www.laphilo.fr/pho/beauvoir-mini.webp</t>
         </is>
       </c>
       <c r="J85" s="48" t="inlineStr">
         <is>
-          <t>ethique</t>
+          <t>ethique ; politique</t>
         </is>
       </c>
       <c r="K85" s="48" t="inlineStr">
         <is>
-          <t xml:space="preserve">Structuralisme ; Totémisme </t>
+          <t>Existentialisme ; Féminisme</t>
         </is>
       </c>
       <c r="L85" s="48" t="inlineStr">
         <is>
-          <t>philosophe et anthropologue français qui  fonda l’anthropologie structurale.</t>
+          <t>philosophe française et intellectuelle anticonformiste figure de l'existentialisme.</t>
         </is>
       </c>
       <c r="M85" t="inlineStr">
         <is>
-          <t xml:space="preserve">juive</t>
+          <t xml:space="preserve">femme</t>
         </is>
       </c>
       <c r="N85" t="inlineStr">
         <is>
           <t xml:space="preserve">occident</t>
         </is>
+      </c>
+      <c r="O85">
+        <v>3</v>
       </c>
     </row>
     <row r="86" ht="242.25" customHeight="1" s="49">
@@ -10119,9 +10113,9 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E75" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Emmanuel_Mounier&quot;  title=&quot; Wikipedia&quot;&gt;Emmanuel MOUNIER&lt;/a&gt; était un philosophe français connu comme le fondateur du personnalisme, un courant qui veut remettre la personne humaine au centre de la pensée et de la vie sociale. &lt;/p&gt; &lt;p&gt; Sa philosophie naît dans un contexte de crise : montée du capitalisme, du fascisme, du marxisme et sentiment que l’homme est écrasé par des systèmes trop abstraits. Il refuse à la fois l’individualisme, qui isole l’être humain, et le collectivisme, qui le dissout dans le groupe. &lt;/p&gt; &lt;p&gt; Pour lui, la personne n’est pas seulement un individu biologique ou social.  &lt;a href=&quot;https://www.youtube.com/watch?v=T8tZ7E0D49k&quot;  title=&quot;emmanuel mounier par kto tv&quot;&gt;&quot;C’est un être libre, &lt;/a&gt; responsable, ouvert aux autres et appelé à se construire dans l’engagement, la relation et la vie communautaire. Cette idée donne à sa pensée une dimension à la fois morale, politique et spirituelle. &lt;/p&gt; &lt;p&gt; Il est aussi profondément chrétien, mais un chrétien engagé dans le monde. Avec  &lt;a href=&quot;https://maitron.fr/mounier-emmanuel-hippolyte-henri/&quot;  title=&quot;emmanuel mounier par maitron&quot;&gt;la revue Esprit, &lt;/a&gt; qu’il fonde en 1932, il cherche à faire dialoguer la foi, la réflexion philosophique et les grands problèmes de son époque, comme la guerre, la démocratie ou la justice sociale. Il défend une forme de « révolution spirituelle », c’est-à-dire une transformation intérieure et sociale de l’homme et des institutions. &lt;/p&gt; &lt;p&gt; la philosophie de Mounier propose une vision exigeante de l’humain : la personne doit être respectée dans sa dignité, sa liberté et sa vocation relationnelle. Son influence a été importante sur la pensée chrétienne, la philosophie sociale et les débats sur la démocratie au XXe siècle. &lt;/p&gt; &lt;audio controls title=&quot;Les murs blancs revue esprit par France Culture&quot;&gt; &lt;source src=&quot;https://media.radiofrance-podcast.net/podcast09/17473-14.03.2021-ITEMA_22602800-2021B20595S0073.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt; &#10;" r:id="rId43"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H75" display="https://www.laphilo.fr/pho/emounier-mini.webp" r:id="rId44"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I81" display="https://www.laphilo.fr/photo/jbeaufret.webp" r:id="rId45"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E83" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Maurice_Merleau-Ponty&quot; title=&quot; Wikipedia&quot;&gt;Maurice MERLEAU-PONTY&lt;/a&gt; était un philosophe français connu pour ses contributions à la phénoménologie, à la philosophie de la perception et à l’existentialisme. Il  s’inspire de plusieurs courants et penseurs et  reprend l’idée d’une description des expériences vécues, mais critique l’idéalisme husserlien. Dans son oeurvre majeure &lt;a href=&quot;https://www.youtube.com/watch?v=RrD5SEiXr_A&quot;  title=&quot; La phénoménologie de Maurice Merleau-Ponty par Tes grands auteurs en petits morceaux&quot;&gt;&quot;Phénoménalogie de la perception&quot;&lt;/a&gt; il  y développe une critique radicale des approches traditionnelles de la perception pour proposer une vision incarnée et existentielle de l’expérience humaine. Il rejette la séparation cartésienne entre le corps et l’esprit &lt;a href=&quot;https://classiques.uqam.ca/classiques/merleau_ponty_maurice/sens_et_non_sens/sens_et_non_sens.html&quot;  title=&quot;  Maurice Merleau-Ponty sens et non sens  par UQAM&quot;&gt;(sens et non sens)&lt;/a&gt;. Pour lui, le corps n’est pas un objet, mais un sujet percevant :  &lt;/p&gt; &lt;p&gt;&#10;-  Le corps propre : C’est par lui que nous faisons l’expérience du monde. Il est à la fois sujet et objet, toujours déjà engagé dans un environnement. &lt;/p&gt; &lt;p&gt; - La perception comme ouverture au monde : &lt;a href=&quot;https://www.youtube.com/watch?v=yiHMPFMCUvo&quot; title=&quot;MERLEAU-PONTY - L'OEIL ET L'ESPRIT par Kosmos&quot;&gt;Percevoir&lt;/a&gt; , c’est être en dialogue avec le monde, pas simplement recevoir des données sensorielles. &lt;/p&gt;  &lt;p&gt;   Il  s’intéresse au langage comme geste corporel. Pour lui, la parole n’est pas un simple véhicule de la pensée, mais une incarnation du sens et l’art montre comment l’expression émerge de la perception. &lt;/p&gt; &lt;p&gt; Dans &quot;Le Visible et l’invisible&quot;, il développe une  &lt;a href=&quot;https://www.youtube.com/watch?v=wZNUUGSZHMs&quot;  title=&quot; Maurice Merleau-Ponty - Entretien : Heure de culture française par Artesquieu &quot;&gt;ontologie originale&lt;/a&gt; où le &quot;chair&quot; est ni matière ni esprit, c’est une substance sensible qui unit le corps et le monde.  Chiasme : Concept décrivant l’entrelacs du voyant et du visible, du touchant et du touché (ex. : quand je me touche la main, je suis à la fois sujet et objet).  L’invisible : Non pas l’absence de visible, mais ce qui le structure. &lt;/p&gt;   &lt;audio controls title=&quot;Maurice Merleau-Ponty : Partie 8/12- La crise de la pensée religieuse par France Culture&quot;&gt; &lt;source src=&quot;https://media.radiofrance-podcast.net/podcast09/13915-20.11.2014-ITEMA_20690515-2013C3372E0710-21.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt;  " r:id="rId46"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E85" display="&lt;p&gt; &lt;a href=&quot;https://fr.wikipedia.org/wiki/Claude_L%C3%A9vi-Strauss&quot;  title=&quot; Wikipedia&quot;&gt;Claude LEVI-STRAUSS&lt;/a&gt; était un anthropologue et ethnologue français, considéré comme l’une des grandes figures intellectuelles du XXᵉ siècle. Après des études de droit puis de philosophie, il se tourne vers l’ethnologie et commence ses premières missions de terrain au Brésil dans les années 1930, auprès de peuples amérindiens du Mato Grosso et de l’Amazonie. De ces expériences, il tirera notamment le livre Tristes tropiques, qui le rend célèbre auprès d’un public plus large en mêlant récit de voyage, &lt;a href=&quot;https://www.youtube.com/watch?v=Fk7du0Avh7U&quot; title=&quot;peuples amerindiens levi-strauss par ina culture&quot;&gt; réflexion sur les sociétés &lt;/a&gt; dites « primitives » et critique de l’ethnocentrisme occidental. &lt;/p&gt; &lt;p&gt; Il est connu pour avoir fondé l’anthropologie structurale, une manière d’étudier les cultures qui cherche les structures profondes, souvent inconscientes, qui organisent les systèmes de parenté, les mythes, les rites et plus largement les formes de vie sociales. Inspiré par la linguistique structurale, il considère que les faits culturels sont comme des langages : ce qui compte, ce sont les relations entre les éléments, plutôt que les éléments pris isolément. Sa méthode vise à réduire la diversité apparente des cultures à des ensembles de relations et d’oppositions formelles, par exemple des oppositions binaires (nature/culture, cru/cuit, vie/mort) qui structurent l’imaginaire. &lt;/p&gt; &lt;p&gt; Une partie centrale de son œuvre concerne les systèmes de parenté et l’alliance matrimoniale, qu’il étudie en détail dans Les structures élémentaires de la parenté, publié en 1949. Il y développe la théorie de l’alliance, selon laquelle les liens de parenté ne sont pas seulement des liens de sang, mais aussi des échanges de femmes entre groupes qui créent des solidarités et des obligations réciproques. Le mariage devient ainsi un mécanisme de communication sociale, une manière d’établir des réseaux d’alliance qui rendent possible la cohésion de la société. &lt;/p&gt; &lt;p&gt; Un autre volet majeur de sa pensée est son travail sur les mythes, en particulier dans les quatre volumes des Mythologiques, où il cherche à montrer que les mythes des différentes cultures, malgré leur grande diversité, obéissent à des schémas de transformation et à des structures communes. Pour lui, le mythe n’est pas une simple histoire, mais un système logique qui met en scène des oppositions et des médiations  pour résoudre symboliquement des tensions fondamentales. En analysant les mythes comme des ensembles de relations, il soutient que  &lt;a href=&quot;https://www.youtube.com/watch?v=fC0HUuXknHk&quot; title=&quot;etre pessimiste pour l’avenir par ina culture&quot;&gt;l’esprit humain fonctionne &lt;/a&gt;  partout selon des structures universelles, même si le contenu des récits varie. &lt;/p&gt; &lt;p&gt; Il développa une réflexion plus générale sur la diversité culturelle et les effets du colonialisme et de la modernité, notamment dans Tristes tropiques où il critique la tendance du monde moderne à homogénéiser et à détruire les différences culturelles. Il affirme l’idée que toutes les cultures sont égales en dignité et que la diversité des formes de vie humaines représente une richesse qu’il faut préserver, plutôt qu’un obstacle à dépasser. Son œuvre, reconnue par de nombreuses distinctions (médaille d’or du CNRS, élection à l’Académie française, prix Érasme, etc.), a contribué à transformer notre manière de penser le rapport entre l’Occident et les autres sociétés, ainsi que les fondements mêmes des sciences sociales. &lt;/p&gt;    &lt;audio controls title=&quot;sur les pas de claude levi-dtrausspar France Culture&quot;&gt; &lt;source src=&quot;https://media.radiofrance-podcast.net/podcast09/13019-03.08.2022-ITEMA_23099095-2022F20970S0215-22.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt;  " r:id="rId47"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H85" display="https://www.laphilo.fr/pho/clstrauss-mini.webp" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E82" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Maurice_Merleau-Ponty&quot; title=&quot; Wikipedia&quot;&gt;Maurice MERLEAU-PONTY&lt;/a&gt; était un philosophe français connu pour ses contributions à la phénoménologie, à la philosophie de la perception et à l’existentialisme. Il  s’inspire de plusieurs courants et penseurs et  reprend l’idée d’une description des expériences vécues, mais critique l’idéalisme husserlien. Dans son oeurvre majeure &lt;a href=&quot;https://www.youtube.com/watch?v=RrD5SEiXr_A&quot;  title=&quot; La phénoménologie de Maurice Merleau-Ponty par Tes grands auteurs en petits morceaux&quot;&gt;&quot;Phénoménalogie de la perception&quot;&lt;/a&gt; il  y développe une critique radicale des approches traditionnelles de la perception pour proposer une vision incarnée et existentielle de l’expérience humaine. Il rejette la séparation cartésienne entre le corps et l’esprit &lt;a href=&quot;https://classiques.uqam.ca/classiques/merleau_ponty_maurice/sens_et_non_sens/sens_et_non_sens.html&quot;  title=&quot;  Maurice Merleau-Ponty sens et non sens  par UQAM&quot;&gt;(sens et non sens)&lt;/a&gt;. Pour lui, le corps n’est pas un objet, mais un sujet percevant :  &lt;/p&gt; &lt;p&gt;&#10;-  Le corps propre : C’est par lui que nous faisons l’expérience du monde. Il est à la fois sujet et objet, toujours déjà engagé dans un environnement. &lt;/p&gt; &lt;p&gt; - La perception comme ouverture au monde : &lt;a href=&quot;https://www.youtube.com/watch?v=yiHMPFMCUvo&quot; title=&quot;MERLEAU-PONTY - L'OEIL ET L'ESPRIT par Kosmos&quot;&gt;Percevoir&lt;/a&gt; , c’est être en dialogue avec le monde, pas simplement recevoir des données sensorielles. &lt;/p&gt;  &lt;p&gt;   Il  s’intéresse au langage comme geste corporel. Pour lui, la parole n’est pas un simple véhicule de la pensée, mais une incarnation du sens et l’art montre comment l’expression émerge de la perception. &lt;/p&gt; &lt;p&gt; Dans &quot;Le Visible et l’invisible&quot;, il développe une  &lt;a href=&quot;https://www.youtube.com/watch?v=wZNUUGSZHMs&quot;  title=&quot; Maurice Merleau-Ponty - Entretien : Heure de culture française par Artesquieu &quot;&gt;ontologie originale&lt;/a&gt; où le &quot;chair&quot; est ni matière ni esprit, c’est une substance sensible qui unit le corps et le monde.  Chiasme : Concept décrivant l’entrelacs du voyant et du visible, du touchant et du touché (ex. : quand je me touche la main, je suis à la fois sujet et objet).  L’invisible : Non pas l’absence de visible, mais ce qui le structure. &lt;/p&gt;   &lt;audio controls title=&quot;Maurice Merleau-Ponty : Partie 8/12- La crise de la pensée religieuse par France Culture&quot;&gt; &lt;source src=&quot;https://media.radiofrance-podcast.net/podcast09/13915-20.11.2014-ITEMA_20690515-2013C3372E0710-21.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt;  " r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E84" display="&lt;p&gt; &lt;a href=&quot;https://fr.wikipedia.org/wiki/Claude_L%C3%A9vi-Strauss&quot;  title=&quot; Wikipedia&quot;&gt;Claude LEVI-STRAUSS&lt;/a&gt; était un anthropologue et ethnologue français, considéré comme l’une des grandes figures intellectuelles du XXᵉ siècle. Après des études de droit puis de philosophie, il se tourne vers l’ethnologie et commence ses premières missions de terrain au Brésil dans les années 1930, auprès de peuples amérindiens du Mato Grosso et de l’Amazonie. De ces expériences, il tirera notamment le livre Tristes tropiques, qui le rend célèbre auprès d’un public plus large en mêlant récit de voyage, &lt;a href=&quot;https://www.youtube.com/watch?v=Fk7du0Avh7U&quot; title=&quot;peuples amerindiens levi-strauss par ina culture&quot;&gt; réflexion sur les sociétés &lt;/a&gt; dites « primitives » et critique de l’ethnocentrisme occidental. &lt;/p&gt; &lt;p&gt; Il est connu pour avoir fondé l’anthropologie structurale, une manière d’étudier les cultures qui cherche les structures profondes, souvent inconscientes, qui organisent les systèmes de parenté, les mythes, les rites et plus largement les formes de vie sociales. Inspiré par la linguistique structurale, il considère que les faits culturels sont comme des langages : ce qui compte, ce sont les relations entre les éléments, plutôt que les éléments pris isolément. Sa méthode vise à réduire la diversité apparente des cultures à des ensembles de relations et d’oppositions formelles, par exemple des oppositions binaires (nature/culture, cru/cuit, vie/mort) qui structurent l’imaginaire. &lt;/p&gt; &lt;p&gt; Une partie centrale de son œuvre concerne les systèmes de parenté et l’alliance matrimoniale, qu’il étudie en détail dans Les structures élémentaires de la parenté, publié en 1949. Il y développe la théorie de l’alliance, selon laquelle les liens de parenté ne sont pas seulement des liens de sang, mais aussi des échanges de femmes entre groupes qui créent des solidarités et des obligations réciproques. Le mariage devient ainsi un mécanisme de communication sociale, une manière d’établir des réseaux d’alliance qui rendent possible la cohésion de la société. &lt;/p&gt; &lt;p&gt; Un autre volet majeur de sa pensée est son travail sur les mythes, en particulier dans les quatre volumes des Mythologiques, où il cherche à montrer que les mythes des différentes cultures, malgré leur grande diversité, obéissent à des schémas de transformation et à des structures communes. Pour lui, le mythe n’est pas une simple histoire, mais un système logique qui met en scène des oppositions et des médiations  pour résoudre symboliquement des tensions fondamentales. En analysant les mythes comme des ensembles de relations, il soutient que  &lt;a href=&quot;https://www.youtube.com/watch?v=fC0HUuXknHk&quot; title=&quot;etre pessimiste pour l’avenir par ina culture&quot;&gt;l’esprit humain fonctionne &lt;/a&gt;  partout selon des structures universelles, même si le contenu des récits varie. &lt;/p&gt; &lt;p&gt; Il développa une réflexion plus générale sur la diversité culturelle et les effets du colonialisme et de la modernité, notamment dans Tristes tropiques où il critique la tendance du monde moderne à homogénéiser et à détruire les différences culturelles. Il affirme l’idée que toutes les cultures sont égales en dignité et que la diversité des formes de vie humaines représente une richesse qu’il faut préserver, plutôt qu’un obstacle à dépasser. Son œuvre, reconnue par de nombreuses distinctions (médaille d’or du CNRS, élection à l’Académie française, prix Érasme, etc.), a contribué à transformer notre manière de penser le rapport entre l’Occident et les autres sociétés, ainsi que les fondements mêmes des sciences sociales. &lt;/p&gt;    &lt;audio controls title=&quot;sur les pas de claude levi-dtrausspar France Culture&quot;&gt; &lt;source src=&quot;https://media.radiofrance-podcast.net/podcast09/13019-03.08.2022-ITEMA_23099095-2022F20970S0215-22.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt;  " r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H84" display="https://www.laphilo.fr/pho/clstrauss-mini.webp" r:id="rId48"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I88" display="https://www.laphilo.fr/photo/morotsir.webp" r:id="rId49"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E90" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Henri_Maldiney&quot;  title=&quot; Wikipedia&quot;&gt;Henri MALDINEY&lt;/a&gt; était un philosophe français, l'une des figures les plus importantes de la phénoménologie française, connu pour sa réflexion originale sur l'art, la psychiatrie et l'existence. Né à Lyon, agrégé de philosophie, il enseigna à l'Université de Lyon pendant toute sa carrière. Sa pensée, &lt;a href=&quot;https://www.henri-maldiney.org/&quot;  title=&quot;henri MALDINEY&quot;&gt; d'une grande densité &lt;/a&gt; et d'un style exigeant, se développe à l'intersection de la phénoménologie husserlienne et heideggerienne, de la psychiatrie phénoménologique (notamment Binswanger) et d'une réflexion approfondie sur les arts plastiques et la musique. &lt;/p&gt; &lt;p&gt; Son œuvre maîtresse, &lt;em&gt;Regard, Parole, Espace&lt;/em&gt; (1973), est une méditation profonde sur la perception, le langage et l'espace à partir de l'analyse d'œuvres plastiques et poétiques.  &lt;a href=&quot;https://www.persee.fr/doc/chime_0986-6035_2001_num_44_1_2388/&quot;  title=&quot;henri MALDINEY par persée &quot;&gt; Il y développe &lt;/a&gt; une phénoménologie du pathique — du mode d'être fondamental par lequel nous sommes d'abord « touchés » par ce qui nous vient — par opposition au gnostique, qui serait le rapport détaché et objectivant à la réalité. Cette distinction lui permet d'analyser de manière originale la perception esthétique, l'expérience psychopathologique et la rencontre avec l'autre. &lt;/p&gt; &lt;p&gt; Dans &lt;em&gt;&lt;a href=&quot;https://fr.wikiversity.org/wiki/Penser_l%27homme_et_la_folie&quot;  title=&quot;pensée l’homme et la folie  par wikipedia &quot;&gt;Penser l'homme et la folie &lt;/a&gt; &lt;/em&gt; (1991) et &lt;em&gt;L'Art, l'éclair de l'être&lt;/em&gt; (1993), il approfondit sa réflexion sur les relations entre existence, folie et création artistique. Pour lui, l'art n'est pas un objet parmi d'autres mais une modalité d'existence, un surgissement de sens qui déborde toute représentation. Sa pensée, qui articule phénoménologie, psychiatrie et esthétique, a exercé une influence durable sur la psychiatrie phénoménologique française et sur les études d'esthétique philosophique. &lt;/p&gt;  &lt;audio controls title=&quot;hommage à Henri Maldiney par France Culture&quot;&gt; &lt;source src=&quot;https://media.radiofrance-podcast.net/podcast09/10080-14.12.2013-ITEMA_20561627-2013C3403E0239-21.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt; " r:id="rId50"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E91" display="&lt;p&gt; &lt;a href=&quot;https://fr.wikipedia.org/wiki/Albert_Camus&quot;  title=&quot; Wikipedia&quot;&gt;Albert CAMUS&lt;/a&gt; était un philosophe et écrivain français dont le courant de pensée est l'Existentialisme. Il a abordé de nombreux sujets philosophiques, notamment &lt;a href=&quot;https://www.youtube.com/watch?v=kAm_I8nwjnc&amp;t=498s&amp;ab_channel=LePr%C3%A9cepteur&quot;   title=&quot;L'absure par le Précepteur&quot;&gt;l'absurdité de la vie&lt;/a&gt;, la liberté individuelle, la révolte, l'amour.&lt;/p&gt; &lt;p&gt;Il a écrit plusieurs ouvrage comme  &lt;a href=&quot;https://www.youtube.com/watch?v=vpzwD2cqqII&amp;ab_channel=LePr%C3%A9cepteur&quot;  title=&quot;L'étranger par le Précepteur&quot;&gt;&quot;l'Étranger&quot;&lt;/a&gt;  ou &quot;Le Mythe de Sisyphe&quot; où il  a développé l'idée que la vie est fondamentalement absurde, car elle ne contient pas de sens intrinsèque ou de finalité. Il a expliqué que l'homme est confronté à un monde qui ne lui donne pas de réponses claires ou satisfaisantes à ses questions sur l'existence et que, par conséquent, il doit créer son propre sens de la vie. &lt;/p&gt; &lt;p&gt;Camus a également écrit sur la liberté individuelle et la révolte contre l'oppression avec son livre &lt;a href=&quot;https://www.youtube.com/watch?v=XLbXH2kVOJ8&quot;  title=&quot;La Peste par le France Culture&quot;&gt;&quot; la Peste&quot;&lt;/a&gt; sortie en 1947 où Il défend la position selon laquelle l'individu doit être libre de poursuivre ses propres intérêts et passions, et que la tyrannie et l'oppression sont des forces qui doivent être combattues. Après le cycle de l'absurde, il entame le cycle de la &lt;a href=&quot;https://www.youtube.com/watch?v=pkRWhuO0wX0&amp;ab_channel=AlainBajom%C3%A9er&quot; title=&quot;La Révolte par Alain Bajomée&quot;&gt;révolte.&lt;/a&gt; &lt;/p&gt; &lt;p&gt;Enfin, il a écrit sur l'amour et l'amitié, explorant la façon dont ces sentiments peuvent apporter de la signification et de la valeur à la vie et a réfléchi sur la solitude et l'isolement, soulignant que ces expériences peuvent être à la fois douloureuses et enrichissantes. &lt;/p&gt;   &lt;audio controls title=&quot;Albert Camus par France Culture&quot;&gt; &lt;source src=&quot;https://cdn.radiofrance.fr/s3/cruiser-production/static/inter/sons/2011/07/s27/NET_2f8a9ed7-086a-40ee-9d75-b184f9e5f99a.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt; &#10;" r:id="rId51"/>

--- a/data/frise-philosophes-france.xlsx
+++ b/data/frise-philosophes-france.xlsx
@@ -5159,7 +5159,7 @@
       <c r="E72" s="56" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Georges_Canguilhem"  title=" Wikipedia"&gt;Georges CANGUILHEM&lt;/a&gt; était un philosophe français,   historien des sciences et résistant, connu pour ses travaux en   &lt;a href="https://www.youtube.com/watch?v=SKBNSabxhUA"  title="
-Philosophie et sciences - Interview de Canguilhem par Badiou par Normezmoi"&gt;épistémologie des sciences &lt;/a&gt; du vivant. Normalien agrégé de philosophie et docteur en médecine sans exercer, il succéda à Gaston Bachelard à la direction de l'IHPST et influença profondément Foucault et Bourdieu. Élève de l'ENS avec Sartre et Nizan, il enseigna la philosophie avant de rejoindre la Résistance en 1940 sous le pseudonyme Lafont. &lt;/p&gt; &lt;p&gt; Il  refuse la réduction physico-chimique ou mécaniste de la vie, défendant sa spécificité organique et normative contre le scientisme. Dans "Le Normal et le Pathologique" paru en 1943, il montre que le pathologique n'est pas une simple négation quantitative du normal, mais une altération qualitative de la vie, rendant la norme contextuelle et historique. &lt;/p&gt; &lt;p&gt; Son historicisme épistémologique, nourri de Cavaillès et Marx, analyse les ruptures scientifiques comme des réponses vitales aux obstacles, valorisant une connaissance active et créatrice plutôt que positiviste. &lt;a href="https://www.persee.fr/doc/phlou_0035-3841_1966_num_64_82_5347"  title="Georges Canguilhem, La connaissance de la vie  par persée"&gt;"La Connaissance de la vie" &lt;/a&gt; paru en 1952 critique le réductionnisme biologique, affirmant que la vie excède les mécanismes pour inclure l'action et l'environnement. &lt;/p&gt;   &lt;audio controls title="Georges Canguilhem par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/10200-07.09.2006-ITEMA_20037357-2006C10589S0002-MEM_000030679_RF-21.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;  </t>
+Philosophie et sciences - Interview de Canguilhem par Badiou par Normezmoi"&gt;épistémologie des sciences &lt;/a&gt; du vivant. Normalien agrégé de philosophie et docteur en médecine sans exercer, il succéda à Gaston Bachelard à la direction de l'IHPST et influença profondément Foucault et Bourdieu. Élève de l'ENS avec Sartre et Nizan, il enseigna la philosophie avant de rejoindre la Résistance en 1940 sous le pseudonyme Lafont. &lt;/p&gt; &lt;p&gt; Il  refuse la réduction physico-chimique ou mécaniste de la vie, défendant sa spécificité organique et normative contre le scientisme. Dans "Le Normal et le Pathologique" paru en 1943, il montre que le pathologique n'est pas une simple négation quantitative du normal, mais une altération qualitative de la vie, rendant la norme contextuelle et historique. &lt;/p&gt; &lt;p&gt; Son historicisme épistémologique, nourri de Cavaillès et Marx, analyse les ruptures scientifiques comme des réponses vitales aux obstacles, valorisant une connaissance active et créatrice plutôt que positiviste. &lt;a href="https://www.persee.fr/doc/phlou_0035-3841_1966_num_64_82_5347"  title="Georges Canguilhem, La connaissance de la vie  par persée"&gt;"La Connaissance de la vie" &lt;/a&gt; paru en 1952 critique le réductionnisme biologique, affirmant que la vie excède les mécanismes pour inclure l'action et l'environnement. Pour lui, être en bonne santé, ce n’est pas seulement être conforme à une moyenne : c’est pouvoir créer de nouvelles normes de vie et faire face aux changements du milieu, alors que la maladie réduit cette capacité. Il a renouvelé l’histoire des sciences en étudiant la formation des concepts. Il a dirigé la thèse de Michel Foucault sur l’histoire de la folie et marqué toute une génération de philosophes. &lt;/p&gt;   &lt;audio controls title="Georges Canguilhem par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/10200-07.09.2006-ITEMA_20037357-2006C10589S0002-MEM_000030679_RF-21.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;  </t>
         </is>
       </c>
       <c r="F72" s="54" t="inlineStr">
@@ -5476,7 +5476,7 @@
       </c>
       <c r="E77" s="56" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Maurice_de_Gandillac"  title=" Wikipedia"&gt;Maurice de GANDILLAC&lt;/a&gt;  était un philosophe français spécialiste de la pensée médiévale et de la Renaissance, connu pour son ouverture d'esprit et son &lt;a href="https://www.youtube.com/watch?v=wMU50jMSLdo"  title=" Maurice de Gandillac et les décades de Pontigny (1926-1938) par adriano meis"&gt;rôle de passeur &lt;/a&gt; entre traditions philosophiques. Professeur à la Sorbonne pendant trois décennies, il a influencé des générations d'étudiants et traduit des auteurs majeurs comme Nicolas de Cues, Walter Benjamin et Nietzsche. Catholique initialement proche de Maritain et Mounier, il s'engage dans des revues comme Esprit et Dieu vivant, et préside les rencontres de Cerisy de 1954 à 1999. &lt;/p&gt; &lt;p&gt;  Sa thèse de 1941 (La Philosophie de Nicolas de Cues) et de multiples traductions (dont De docta ignorantia) en font l'un des principaux introducteurs du Cusain en France, explorant l'infini, la "docte ignorance" et l'unité des contraires. Premier à traduire Walter Benjamin en français, ainsi que Novalis, Hegel, Nietzsche (avec Deleuze), Ernst Bloch et Dante (Divine Comédie). &lt;/p&gt; &lt;p&gt; Il incarne un &lt;a href="https://www.persee.fr/doc/homso_0018-4306_1999_num_131_1_3626"  title="Maurice de Gandillac, Le siècle traversé. Souvenirs de neuf décennies, Paris, Albin Michel, 1998 par Persée"&gt;humanisme érudit&lt;/a&gt;, liant Moyen Âge, Renaissance et modernité, avec un souci des silences et opacités de la pensée face à l'indicible. Son œuvre, mêlant histoire philosophique, poésie (Bestiaire latéral, 1974) et dialogues interdisciplinaires, reste une référence pour l'étude des marges de la rationalité. &lt;/p&gt;</t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Maurice_de_Gandillac"  title=" Wikipedia"&gt;Maurice de GANDILLAC&lt;/a&gt;  était un philosophe français spécialiste de la pensée médiévale et de la Renaissance, connu pour son ouverture d'esprit et son &lt;a href="https://www.youtube.com/watch?v=wMU50jMSLdo"  title=" Maurice de Gandillac et les décades de Pontigny (1926-1938) par adriano meis"&gt;rôle de passeur &lt;/a&gt; entre traditions philosophiques. Professeur à la Sorbonne pendant trois décennies, il a influencé des générations d'étudiants et traduit des auteurs majeurs comme Nicolas de Cues, Walter Benjamin et Nietzsche. Catholique initialement proche de Maritain et Mounier, il s'engage dans des revues comme Esprit et Dieu vivant, et préside les rencontres de Cerisy de 1954 à 1999. &lt;/p&gt; &lt;p&gt;  Sa thèse de 1941 (La Philosophie de Nicolas de Cues) et de multiples traductions (dont De docta ignorantia) en font l'un des principaux introducteurs du Cusain en France, explorant l'infini, la "docte ignorance" et l'unité des contraires. Premier à traduire Walter Benjamin en français, ainsi que Novalis, Hegel, Nietzsche (avec Deleuze), Ernst Bloch et Dante (Divine Comédie). &lt;/p&gt; &lt;p&gt; Il incarne un &lt;a href="https://www.persee.fr/doc/homso_0018-4306_1999_num_131_1_3626"  title="Maurice de Gandillac, Le siècle traversé. Souvenirs de neuf décennies, Paris, Albin Michel, 1998 par Persée"&gt;humanisme érudit&lt;/a&gt;, liant Moyen Âge, Renaissance et modernité, avec un souci des silences et opacités de la pensée face à l'indicible. Son œuvre, mêlant histoire philosophique, poésie (Bestiaire latéral, 1974) et dialogues interdisciplinaires, reste une référence pour l'étude des marges de la rationalité. Né en Algérie en 1906, normalien, il a enseigné à la Sorbonne de 1946 à 1977, où il a dirigé ou accompagné les travaux de nombreux philosophes, de Gilles Deleuze à Jacques Derrida. Il a raconté ce parcours dans &lt;em&gt;Le Siècle traversé&lt;/em&gt; (1998). Mort en 2006 à près de cent ans, il reste le modèle d’un philosophe généreux et curieux de tout. &lt;/p&gt;</t>
         </is>
       </c>
       <c r="F77" s="54" t="inlineStr">
@@ -6028,8 +6028,7 @@
       </c>
       <c r="E86" s="59" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt; &lt;a href="https://fr.wikipedia.org/wiki/Simone_Weil"  title=" Wikipedia"&gt; Simone WEIL&lt;/a&gt; était une philosophe Française qui a étudié la philosophie antique et les textes religieux. Elle était profondément spirituelle et religieuse et a rejeté les institutions traditionnelles. Elle a exploré les aspects mystiques de différentes religions et a essayé de les intégrer dans une vision du monde plus large.  Elle souhaite faire de la philosophie une manière de vivre, non pour acquérir des connaissances, mais pour être dans la vérité. Elle écrira plusieurs livres dont &lt;a href="https://www.youtube.com/watch?v=6CR2PcTPvCk&amp;ab_channel=Al%C3%A8theiar" title="Les besoins de l'âme par Alèteia"&gt; "l'Enracinement" &lt;/a&gt; et "la Pesanteur et la grâce".  &lt;/p&gt; &lt;p&gt;C'était une &lt;span title="L'activisme politique est une attitude, une règle de conduite ou un engagement politique qui privilégie l'action directe à court terme par rapport aux principes théoriques et aux actions à long terme"&gt; activiste politique &lt;/span&gt;  engagée, qui a participé à divers mouvements sociaux et politiques, notamment la grève générale en France en 1936 et la guerre d'Espagne. &lt;/p&gt; &lt;p&gt; En 1942, elle a participé à la lutte contre l'occupation nazie en se joignant à la résistance. Dans son ouvrage, &lt;a href="https://www.youtube.com/watch?v=Pg0qv0kIaKo&amp;ab_channel=LePr%C3%A9cepteur"  style="color:#88A1E9"  title="Supprimer les parties politiques par le Précepteur"&gt; "La Condition ouvrière"&lt;/a&gt;. Elle prône la suppression des partis politiques et défend l'idée selon laquelle les partis politiques sont souvent motivés par leurs intérêts partisans plutôt que par le bien-être général de la société et qu'ils sont des obstacles à la véritable démocratie en concentrant le pouvoir entre les mains d'une élite restreinte et en limitant les voix de la majorité. &lt;/p&gt;  &lt;audio controls title="Une intellectuelle à l'usine par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/21936-01.01.2021-ITEMA_22534096-2019C12410E0194.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt; 
-</t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Simone_Weil"  title=" Wikipedia"&gt;Simone WEIL&lt;/a&gt; (1909-1943) est une philosophe française, dont l’œuvre unit la réflexion politique, l’expérience du travail et la recherche spirituelle. Élève du philosophe Alain, normalienne, agrégée de philosophie, elle enseigne dans plusieurs lycées et milite auprès des syndicats ouvriers. En 1934-1935, elle quitte l’enseignement pour travailler comme ouvrière dans des usines, chez Alsthom puis chez Renault, afin de connaître de l’intérieur l’oppression du travail à la chaîne : ses notes formeront &lt;em&gt;La Condition ouvrière&lt;/em&gt;.&lt;/p&gt; &lt;p&gt;En 1936, elle rejoint en Espagne une colonne anarchiste pendant la guerre civile, mais doit rentrer après un accident. À la fin des années 1930, elle vit une expérience mystique et se tourne vers le christianisme, sans jamais demander le baptême, par solidarité avec ceux qui restent hors de l’Église. Réfugiée à Marseille en 1941, elle travaille aux vendanges chez le philosophe paysan Gustave Thibon, qui publiera après sa mort des extraits de ses carnets, &lt;em&gt;La Pesanteur et la grâce&lt;/em&gt;. Elle y médite sur le malheur, sur l’attention, qui est « la forme la plus rare et la plus pure de la générosité », et sur la nécessité de se détacher de soi. En 1942, elle rejoint la France libre à Londres. Elle y écrit &lt;a href="https://www.youtube.com/watch?v=6CR2PcTPvCk&amp;ab_channel=Al%C3%A8theiar" title="Les besoins de l'âme par Alèteia"&gt;&lt;em&gt;L’Enracinement&lt;/em&gt;&lt;/a&gt;, où elle décrit les « besoins de l’âme » et la nécessité pour chacun d’avoir des racines. Dans sa &lt;em&gt;Note sur la &lt;a href="https://www.youtube.com/watch?v=Pg0qv0kIaKo&amp;ab_channel=LePr%C3%A9cepteur"  style="color:#88A1E9"  title="Supprimer les parties politiques par le Précepteur"&gt;suppression générale des partis politiques&lt;/a&gt;&lt;/em&gt;, elle accuse les partis de fabriquer de la passion collective et d’étouffer la pensée.&lt;/p&gt; &lt;p&gt;Épuisée, refusant de manger plus que les rations de la France occupée, elle meurt à trente-quatre ans en Angleterre.&lt;/p&gt;  &lt;audio controls title="Une intellectuelle à l'usine par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/21936-01.01.2021-ITEMA_22534096-2019C12410E0194.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;</t>
         </is>
       </c>
       <c r="F86" s="57" t="inlineStr">
@@ -6822,7 +6821,7 @@
       <c r="E99" s="59" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Gilles_Gaston_Granger"   title=" Wikipedia"&gt;Gilles Gaston GRANGER&lt;/a&gt;  était un philosophe  et épistémologue français connu pour son travail sur l'épistémologie comparative et l'application des formes logico-mathématiques aux sciences humaines. Élève de l'École normale supérieure, agrégé de philosophie en 1943 et licencié en mathématiques, &lt;a href="https://www.persee.fr/authority/281588"title=" Gilles Gaston GRANGER par Persée"&gt; il enseigna &lt;/a&gt; au Brésil puis en France.  Il traduisit le "Tractatus logico-philosophicus" de Wittgenstein en français et fonda la revue L'Âge de la Science en 1968. &lt;/p&gt; &lt;p&gt; Il, &lt;a href="https://www.youtube.com/watch?v=koxZPXhxpt0&amp;t=699s" title="
-Rationalité et raisonnement — Gilles-Gaston Granger par Andrea Cirla"&gt;développa &lt;/a&gt; une épistémologie comparatiste, unifiant sciences de la nature et humaines sur une échelle commune, inspirée d'Aristote et d'un rationalisme pragmatique. Il rejeta le platonisme (formes abstraites) et le positivisme strict (lois universelles pour les faits humains), privilégiant les modèles sémantiques et probabilistes en économie ou linguistique.  La raison est pour lui un "travail" et un "style" évolutif, appliquant formes mathématiques à des contenus concrets via abstraction. &lt;/p&gt; &lt;p&gt; Ses Œuvres clés sont : -"Méthodologie économique" paru en 1955 et "La Mathématique sociale du marquis de Condorcet" en 1956 : analyses pionnières des sciences humaines. - "Pensée formelle et sciences de l'homme" paru en 1960 : montre comment modéliser l'individuel (économie, langage, histoire). &lt;/p&gt;</t>
+Rationalité et raisonnement — Gilles-Gaston Granger par Andrea Cirla"&gt;développa &lt;/a&gt; une épistémologie comparatiste, unifiant sciences de la nature et humaines sur une échelle commune, inspirée d'Aristote et d'un rationalisme pragmatique. Il rejeta le platonisme (formes abstraites) et le positivisme strict (lois universelles pour les faits humains), privilégiant les modèles sémantiques et probabilistes en économie ou linguistique.  La raison est pour lui un "travail" et un "style" évolutif, appliquant formes mathématiques à des contenus concrets via abstraction. &lt;/p&gt; &lt;p&gt; Ses Œuvres clés sont : -"Méthodologie économique" paru en 1955 et "La Mathématique sociale du marquis de Condorcet" en 1956 : analyses pionnières des sciences humaines. - "Pensée formelle et sciences de l'homme" paru en 1960 : montre comment modéliser l'individuel (économie, langage, histoire). &lt;/p&gt; Il enseigne à l’université de São Paulo de 1947 à 1953, avant d’occuper de 1986 à 1991 une chaire d’épistémologie comparative au Collège de France. Dans &lt;em&gt;Essai d’une philosophie du style&lt;/em&gt; (1968), il montre que même la science, en apparence impersonnelle, porte la marque d’un style, c’est-à-dire d’une manière singulière d’organiser une expérience.</t>
         </is>
       </c>
       <c r="F99" s="57" t="inlineStr">

--- a/data/frise-philosophes-france.xlsx
+++ b/data/frise-philosophes-france.xlsx
@@ -1367,11 +1367,7 @@
       </c>
       <c r="E9" s="59" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Antoine-Augustin_Cournot"  title=" Wikipedia"&gt;Antoine COURNOT&lt;/a&gt; était un mathématicien, économiste et philosophe français,  pionnier de &lt;a href="https://www.youtube.com/watch?v=HvoU2MuIyx0" style="color:#88A1E9" title="Antoine-Augustin COURNOT : pionnier de l'économie mathématique par NeoEconomicus"&gt;l'économie mathématique&lt;/a&gt; et de la théorie des jeux. &lt;/p&gt; &lt;p&gt; Il est connu pour son ouvrage "Recherches sur les principes mathématiques de la théorie des richesses" (1838), qui a jeté les bases de l'économie mathématique. Voici quelques-unes de ses contributions majeures : &lt;/p&gt; 
-&lt;dd&gt; -  &lt;a href="https://www.youtube.com/watch?v=9gFUQXcllFI"  title="Le Duopole de Cournot : modèle et généralisation à N firmes par NeoEconomicus"&gt;Théorie du duopole&lt;/a&gt; : Premier modèle formel de concurrence entre deux entreprises (duopole). Il a analysé comment deux vendeurs sur un marché déterminent leurs quantités produites pour maximiser leurs profits, en tenant compte des actions de l'autre. Ce modèle est devenu un pilier de la théorie microéconomique. &lt;/dd&gt; 
-&lt;dd&gt; - Équilibre de Cournot : Concept d'équilibre, où chaque entreprise choisit sa production de manière optimale, étant donné la production de l'autre. Cet équilibre est maintenant connu sous le nom d'équilibre de Cournot. &lt;/dd&gt; 
-&lt;dd&gt; - Analyse des monopoles : Comment un vendeur unique sur un marché peut fixer les prix pour maximiser son profit. &lt;/dd&gt; 
-&lt;dd&gt; - Application des mathématiques à l'économie : Mathématiques pour modéliser les comportements économiques.&lt;/dd&gt; &lt;p&gt; Il était un philosophe des sciences et a écrit sur des sujets tels que la probabilité, la causalité et la nature de la connaissance scientifique.  Dans son ouvrage"Exposition de la théorie des chances et des probabilités", il a exploré les fondements des probabilités et leur application à des problèmes pratiques.  Dans son livre "Matérialisme, vitalisme, rationalisme", il porte ses réflexions sur les limites de la science et les questions métaphysiques. &lt;/p&gt; &lt;p&gt; Il a marqué l'histoire de la pensée économique en introduisant des méthodes mathématiques rigoureuses et ses travaux sur le duopole, les monopoles et l'équilibre économique restent des références essentielles dans l'étude de la concurrence et des marchés. &lt;/p&gt; </t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Antoine-Augustin_Cournot"  title=" Wikipedia"&gt;Antoine COURNOT&lt;/a&gt; était un mathématicien, économiste et philosophe français,  pionnier de &lt;a href="https://www.youtube.com/watch?v=HvoU2MuIyx0" style="color:#88A1E9" title="Antoine-Augustin COURNOT : pionnier de l'économie mathématique par NeoEconomicus"&gt;l'économie mathématique&lt;/a&gt; et de la théorie des jeux. &lt;/p&gt; &lt;p&gt; Il est connu pour son ouvrage "Recherches sur les principes mathématiques de la théorie des richesses" (1838), qui a jeté les bases de l'économie mathématique. &lt;/p&gt; &lt;p&gt;&lt;a href="https://www.youtube.com/watch?v=9gFUQXcllFI"  title="Le Duopole de Cournot : modèle et généralisation à N firmes par NeoEconomicus"&gt;Théorie du duopole&lt;/a&gt; : Premier modèle formel de concurrence entre deux entreprises (duopole). Il a analysé comment deux vendeurs sur un marché déterminent leurs quantités produites pour maximiser leurs profits, en tenant compte des actions de l'autre. Ce modèle est devenu un pilier de la théorie microéconomique. &lt;/p&gt; &lt;p&gt;Équilibre de Cournot : Concept d'équilibre, où chaque entreprise choisit sa production de manière optimale, étant donné la production de l'autre. Cet équilibre est maintenant connu sous le nom d'équilibre de Cournot. &lt;/p&gt; &lt;p&gt;Analyse des monopoles : Comment un vendeur unique sur un marché peut fixer les prix pour maximiser son profit. &lt;/p&gt; &lt;p&gt;Application des mathématiques à l'économie : Mathématiques pour modéliser les comportements économiques.&lt;/p&gt; &lt;p&gt; Il était un philosophe des sciences et a écrit sur des sujets tels que la probabilité, la causalité et la nature de la connaissance scientifique.  Dans son ouvrage"Exposition de la théorie des chances et des probabilités", il a exploré les fondements des probabilités et leur application à des problèmes pratiques.  Dans son livre "Matérialisme, vitalisme, rationalisme", il porte ses réflexions sur les limites de la science et les questions métaphysiques. &lt;/p&gt; &lt;p&gt; Il a marqué l'histoire de la pensée économique en introduisant des méthodes mathématiques rigoureuses et ses travaux sur le duopole, les monopoles et l'équilibre économique restent des références essentielles dans l'étude de la concurrence et des marchés. &lt;/p&gt; </t>
         </is>
       </c>
       <c r="F9" s="57" t="inlineStr">
@@ -1491,7 +1487,7 @@
       </c>
       <c r="E11" s="59" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Pierre-Joseph_Proudhon"  title=" Wikipedia"&gt;Joseph PROUDHON&lt;/a&gt; est un philosophe, économiste, sociologue et théoricien politique français, souvent considéré comme le premier à se revendiquer &lt;a href="https://www.youtube.com/watch?v=fe-De7lUIEc&amp;t=22s&amp;pp=ygUPSm9zZXBoIFBST1VESE9O"  title="Cet homme est le PLUS GRAND ANARCHISTE - Pierre Joseph PROUDHON par Draw my economy"&gt;anarchiste&lt;/a&gt;. Il s'engage dans le débat public, critiquant à la fois le capitalisme et le communisme autoritaire. En 1848, il participe à la Révolution française et est élu député à l'Assemblée constituante. &lt;/p&gt; &lt;p&gt; Il distingue la propriété (qui permet l'exploitation) de la possession (usage personnel).  Sa phrase célèbre, &lt;a href="https://blogs.mediapart.fr/alexis-paquet/blog/300123/la-propriete-cest-le-vol-analyse-critique-de-quest-ce-que-la-propriete" title="La propriété c'est le vol par DMediapart"&gt;« La propriété, c'est le vol ! »&lt;/a&gt;, vise à dénoncer l'accumulation de richesses par une minorité au détriment de la majorité. Il prône une société sans État, organisée autour de l'autogestion et de la mutualité et rejette à la fois le capitalisme et le communisme autoritaire, cherchant une troisième voie basée sur la liberté individuelle et la coopération volontaire. &lt;/p&gt; &lt;p&gt; Il défend un système politique fédéraliste, où les communautés locales s'auto-organisent et se fédèrent librement, sans autorité centrale coercitive. Il rejette toute forme d'autorité imposée, qu'elle soit politique, religieuse ou économique. Il croit en la capacité des individus à s'organiser de manière égalitaire et juste. &lt;/p&gt; &lt;p&gt; Ses oeuvres majeures:  - Qu'est-ce que la propriété ? : Texte où il développe sa critique de la propriété privée.  - Système des contradictions économiques ou  &lt;a href="https://www.youtube.com/watch?v=SvXqY7DuT9M" title="pierre Joseph Proudhon par Lecture a domicile"&gt;Philosophie de la misère&lt;/a&gt; : Analyse des contradictions du capitalisme.  - Idée générale de la révolution : Présentation de sa vision anarchiste et fédéraliste.  - De la justice dans la Révolution et dans l'Église : Réflexion sur la justice sociale et la morale. &lt;/p&gt; &lt;p&gt; Il a influencé de nombreux penseurs et mouvements, notamment l'anarchisme, le syndicalisme révolutionnaire et le socialisme libertaire. Il reste une référence pour ceux qui cherchent à concilier liberté individuelle et justice sociale. &lt;/p&gt;  &lt;audio controls title=" Pierre-Joseph Proudhon, précuseur de l'anarchisme par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/13915-17.01.2025-ITEMA_23998650-2024C3372E0473-21.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;  </t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Pierre-Joseph_Proudhon"  title=" Wikipedia"&gt;Joseph PROUDHON&lt;/a&gt; est un philosophe, économiste, sociologue et théoricien politique français, souvent considéré comme le premier à se revendiquer &lt;a href="https://www.youtube.com/watch?v=fe-De7lUIEc&amp;t=22s&amp;pp=ygUPSm9zZXBoIFBST1VESE9O"  title="Cet homme est le PLUS GRAND ANARCHISTE - Pierre Joseph PROUDHON par Draw my economy"&gt;anarchiste&lt;/a&gt;. Il s'engage dans le débat public, critiquant à la fois le capitalisme et le communisme autoritaire. En 1848, il participe à la Révolution française et est élu député à l'Assemblée constituante. &lt;/p&gt; &lt;p&gt; Il distingue la propriété (qui permet l'exploitation) de la possession (usage personnel).  Sa phrase célèbre, &lt;a href="https://blogs.mediapart.fr/alexis-paquet/blog/300123/la-propriete-cest-le-vol-analyse-critique-de-quest-ce-que-la-propriete" title="La propriété c'est le vol par DMediapart"&gt;« La propriété, c'est le vol ! »&lt;/a&gt;, vise à dénoncer l'accumulation de richesses par une minorité au détriment de la majorité. Il prône une société sans État, organisée autour de l'autogestion et de la mutualité et rejette à la fois le capitalisme et le communisme autoritaire, cherchant une troisième voie basée sur la liberté individuelle et la coopération volontaire. &lt;/p&gt; &lt;p&gt; Il défend un système politique fédéraliste, où les communautés locales s'auto-organisent et se fédèrent librement, sans autorité centrale coercitive. Il rejette toute forme d'autorité imposée, qu'elle soit politique, religieuse ou économique. Il croit en la capacité des individus à s'organiser de manière égalitaire et juste. &lt;/p&gt; &lt;p&gt; Ses oeuvres majeures: Qu'est-ce que la propriété ? : Texte où il développe sa critique de la propriété privée. Système des contradictions économiques ou  &lt;a href="https://www.youtube.com/watch?v=SvXqY7DuT9M" title="pierre Joseph Proudhon par Lecture a domicile"&gt;Philosophie de la misère&lt;/a&gt; : Analyse des contradictions du capitalisme. Idée générale de la révolution : Présentation de sa vision anarchiste et fédéraliste. De la justice dans la Révolution et dans l'Église : Réflexion sur la justice sociale et la morale. &lt;/p&gt; &lt;p&gt; Il a influencé de nombreux penseurs et mouvements, notamment l'anarchisme, le syndicalisme révolutionnaire et le socialisme libertaire. Il reste une référence pour ceux qui cherchent à concilier liberté individuelle et justice sociale. &lt;/p&gt;  &lt;audio controls title=" Pierre-Joseph Proudhon, précuseur de l'anarchisme par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/13915-17.01.2025-ITEMA_23998650-2024C3372E0473-21.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;  </t>
         </is>
       </c>
       <c r="F11" s="57" t="inlineStr">
@@ -4127,7 +4123,7 @@
       </c>
       <c r="E55" s="78" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Louis_Lavelle"  title=" Wikipedia"&gt;Louis MASSIGNON&lt;/a&gt; était un philosophe,  islamologue, orientaliste et intellectuel catholique français, considéré comme l’un des fondateurs de l’islamologie moderne et un pionnier du dialogue islamo-chrétien. Son œuvre mêle érudition philologique et historique sur l’islam, intérêt profond pour le soufisme, et engagement spirituel et politique en faveur d’une réconciliation des religions abrahamiques. &lt;/p&gt; &lt;p&gt; Il  est &lt;a href="https://louismassignon.fr/"&gt;surtout célèbre &lt;/a&gt;  pour son étude monumentale du mystique soufi al-Ḥallāj (mort en 922), qu’il considère comme un paradigme de la sainteté en islam et comme une figure de martyr spirituel. Il montre l’origine coranique du soufisme, analyse en détail le vocabulaire mystique musulman, et contribue à faire entrer l’étude de la mystique islamique dans le champ académique occidental. Son interprétation est marquée par sa propre spiritualité : il valorise une mystique d’ascèse et de souffrance, et se méfie des développements plus spéculatifs (comme chez Ibn ʿArabī). &lt;/p&gt; &lt;p&gt; Il développe une vision œcuménique centrée sur la figure d’Abraham, père commun du judaïsme, du christianisme et de l’islam, et travaille à faire reconnaître l’islam comme religion abrahamique par les catholiques. En 1934, avec l’Égyptienne Mary Kahil, il fonde la Badaliya (« substitution »), un groupe de prière où des chrétiens s’offrent spirituellement « en otage » pour les musulmans, dans une logique de solidarité et d’intercession. Ordonné prêtre de rite catholique melkite en 1950, il incarne une forme de catholicisme ouvert à l’islam, tout en restant fidèle à l’Église. &lt;/p&gt; &lt;p&gt; Il intervient aussi comme expert sur les  &lt;a href="https://www.youtube.com/watch?v=JabzLnmm8PM" title="les arts de l’islam avec luois Massignonpar Coscience Soufie"&gt;questions musulmanes &lt;/a&gt; dans l’Empire français, tout en défendant une politique non violente et une meilleure compréhension du monde arabe. Il influence profondément l’islamologie française, la théologie catholique du dialogue interreligieux, et prépare en partie l’ouverture de Vatican II envers l’islam. &lt;/p&gt; 
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Louis_Massignon"  title=" Wikipedia"&gt;Louis MASSIGNON&lt;/a&gt; était un philosophe,  islamologue, orientaliste et intellectuel catholique français, considéré comme l’un des fondateurs de l’islamologie moderne et un pionnier du dialogue islamo-chrétien. Son œuvre mêle érudition philologique et historique sur l’islam, intérêt profond pour le soufisme, et engagement spirituel et politique en faveur d’une réconciliation des religions abrahamiques. &lt;/p&gt; &lt;p&gt; Il  est &lt;a href="https://louismassignon.fr/"&gt;surtout célèbre &lt;/a&gt;  pour son étude monumentale du mystique soufi al-Ḥallāj (mort en 922), qu’il considère comme un paradigme de la sainteté en islam et comme une figure de martyr spirituel. Il montre l’origine coranique du soufisme, analyse en détail le vocabulaire mystique musulman, et contribue à faire entrer l’étude de la mystique islamique dans le champ académique occidental. Son interprétation est marquée par sa propre spiritualité : il valorise une mystique d’ascèse et de souffrance, et se méfie des développements plus spéculatifs (comme chez Ibn ʿArabī). &lt;/p&gt; &lt;p&gt; Il développe une vision œcuménique centrée sur la figure d’Abraham, père commun du judaïsme, du christianisme et de l’islam, et travaille à faire reconnaître l’islam comme religion abrahamique par les catholiques. En 1934, avec l’Égyptienne Mary Kahil, il fonde la Badaliya (« substitution »), un groupe de prière où des chrétiens s’offrent spirituellement « en otage » pour les musulmans, dans une logique de solidarité et d’intercession. Ordonné prêtre de rite catholique melkite en 1950, il incarne une forme de catholicisme ouvert à l’islam, tout en restant fidèle à l’Église. &lt;/p&gt; &lt;p&gt; Il intervient aussi comme expert sur les  &lt;a href="https://www.youtube.com/watch?v=JabzLnmm8PM" title="les arts de l’islam avec luois Massignonpar Coscience Soufie"&gt;questions musulmanes &lt;/a&gt; dans l’Empire français, tout en défendant une politique non violente et une meilleure compréhension du monde arabe. Il influence profondément l’islamologie française, la théologie catholique du dialogue interreligieux, et prépare en partie l’ouverture de Vatican II envers l’islam. &lt;/p&gt; 
 </t>
         </is>
       </c>
@@ -4906,8 +4902,7 @@
       </c>
       <c r="E68" s="59" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Henry_Corbin"   title=" Wikipedia"&gt;Henry CORBIN&lt;/a&gt; était un philosophe, théologien, iranologue et &lt;a href="https://www.persee.fr/doc/rhpr_0035-2403_1979_num_59_2_4477" title=" Un missionnaire protestant par Persée"&gt;orientaliste français&lt;/a&gt; qui a profondément renouvelé la compréhension occidentale de la philosophie islamique, en particulier de ses courants chiites et &lt;a href="https://www.youtube.com/watch?v=1MKjvaSpu3s&amp;t=17s" style="color:#88A1E9" title=" Henry Corbin - L'Imagination créatrice dans le Soufisme d'Ibn Arabi par On the Top of Damavand for ever"&gt;soufis&lt;/a&gt;, ainsi que de la pensée iranienne. &lt;a href="https://www.persee.fr/doc/ephe_0000-0002_1978_num_91_87_15381"  title=" Henry Corbin par Persée"&gt;Son œuvre&lt;/a&gt; se caractérise par une quête philosophique personnelle, un "pèlerinage vers l'Orient des Lumières" quil a mis en lumière : &lt;/p&gt; 
-&lt;p&gt; - La philosophie illuminative de Sohrawardî : Il a joué un rôle crucial dans la &lt;a href="https://www.youtube.com/watch?v=LDRVfRaiS7I"  title=" Sohravardî, L’Archange empourpré, par Henry Corbin par Conscience Soufie"&gt;redécouverte de ce philosophe persan&lt;/a&gt;, fondateur de l'école de l'Illumination, qui combine la logique aristotélicienne avec une métaphysique de la lumière d'inspiration platonicienne et zoroastrienne. &lt;/p&gt; &lt;p&gt; - Le concept du "monde imaginal" : Concepts centraux de sa pensée, il s'agit d'un monde intermédiaire, ontologiquement réel, entre le monde sensible et le monde purement intelligible, lieu des visions prophétiques, des événements de l'âme après la mort, et de l'imagination créatrice. Essentiel pour comprendre l'herméneutique spirituelle des textes sacrés. &lt;/p&gt; &lt;p&gt; - L'importance de la gnose chiite et de l'ismaélisme : Il a profondément exploré les dimensions ésotériques du chiisme, notamment duodécimain et ismaélien, en mettant en avant des figures comme Haydar Amoli et en soulignant le rôle central de l'Imâm comme guide spirituel et manifestation du divin. &lt;/p&gt;  &lt;p&gt; - La philosophie prophétique et l'angélologie : Il a mis en évidence le rôle des prophètes et des anges dans la cosmologie islamiques, soulignant la continuité entre la philosophie et la révélation. &lt;/p&gt;  &lt;audio controls title="Henry Corbin raconté par Tom Cheetham par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/10073-06.12.2015-ITEMA_20857956-2015C6125E0167-21.mp3" type="audio/mpeg" align="center"&gt;&lt;/audio&gt;  </t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Henry_Corbin"   title=" Wikipedia"&gt;Henry CORBIN&lt;/a&gt; était un philosophe, théologien, iranologue et &lt;a href="https://www.persee.fr/doc/rhpr_0035-2403_1979_num_59_2_4477" title=" Un missionnaire protestant par Persée"&gt;orientaliste français&lt;/a&gt; qui a profondément renouvelé la compréhension occidentale de la philosophie islamique, en particulier de ses courants chiites et &lt;a href="https://www.youtube.com/watch?v=1MKjvaSpu3s&amp;t=17s" style="color:#88A1E9" title=" Henry Corbin - L'Imagination créatrice dans le Soufisme d'Ibn Arabi par On the Top of Damavand for ever"&gt;soufis&lt;/a&gt;, ainsi que de la pensée iranienne. &lt;a href="https://www.persee.fr/doc/ephe_0000-0002_1978_num_91_87_15381"  title=" Henry Corbin par Persée"&gt;Son œuvre&lt;/a&gt; se caractérise par une quête philosophique personnelle, un "pèlerinage vers l'Orient des Lumières" quil a mis en lumière : &lt;/p&gt; &lt;p&gt;La philosophie illuminative de Sohrawardî : Il a joué un rôle crucial dans la &lt;a href="https://www.youtube.com/watch?v=LDRVfRaiS7I"  title=" Sohravardî, L’Archange empourpré, par Henry Corbin par Conscience Soufie"&gt;redécouverte de ce philosophe persan&lt;/a&gt;, fondateur de l'école de l'Illumination, qui combine la logique aristotélicienne avec une métaphysique de la lumière d'inspiration platonicienne et zoroastrienne. &lt;/p&gt; &lt;p&gt;Le concept du "monde imaginal" : Concepts centraux de sa pensée, il s'agit d'un monde intermédiaire, ontologiquement réel, entre le monde sensible et le monde purement intelligible, lieu des visions prophétiques, des événements de l'âme après la mort, et de l'imagination créatrice. Essentiel pour comprendre l'herméneutique spirituelle des textes sacrés. &lt;/p&gt; &lt;p&gt;L'importance de la gnose chiite et de l'ismaélisme : Il a profondément exploré les dimensions ésotériques du chiisme, notamment duodécimain et ismaélien, en mettant en avant des figures comme Haydar Amoli et en soulignant le rôle central de l'Imâm comme guide spirituel et manifestation du divin. &lt;/p&gt; &lt;p&gt;La philosophie prophétique et l'angélologie : Il a mis en évidence le rôle des prophètes et des anges dans la cosmologie islamiques, soulignant la continuité entre la philosophie et la révélation. &lt;/p&gt;  &lt;audio controls title="Henry Corbin raconté par Tom Cheetham par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/10073-06.12.2015-ITEMA_20857956-2015C6125E0167-21.mp3" type="audio/mpeg" align="center"&gt;&lt;/audio&gt;  </t>
         </is>
       </c>
       <c r="F68" s="57" t="inlineStr">
@@ -4967,8 +4962,7 @@
       </c>
       <c r="E69" s="56" t="inlineStr">
         <is>
-          <t>&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Jean_Cavaill%C3%A8s"    title=" Wikipedia"&gt;Jean CAVAILLES&lt;/a&gt;  était un philosophe français des sciences et un des &lt;a href="https://cavailles.hypotheses.org/jean-cavailles/vie-de-jean-cavailles" title="Les Amis de Jean Cavaillès par Hypotheses"&gt;héros intellectuels &lt;/a&gt; de la Résistance, fusillé par les nazis à l’âge de quarante ans. Normalien et officier de réserve, il est marqué par l’effondrement de la République de Weimar, la montée du nazisme et les débats religieux et politiques de l’entre‑deux‑guerres. &lt;/p&gt; &lt;p&gt; Il se spécialise en &lt;a href="https://www.youtube.com/watch?v=zfr9wq-kYTo" style="color:#88A1E9" title="Sur la philosophie de Jean cavaillès par Hypotheses"&gt;philosophie des mathématiques &lt;/a&gt; et de la logique, en particulier sur l’histoire et la structure des théories axiomatiques. En 1938, il soutient sa grande thèse "Méthode axiomatique et formalisme", et une thèse complémentaire "Remarques sur la formation de la théorie abstraite des ensembles" qui étudient l’essor de la théorie des ensembles et la dynamique interne des mathématiques modernes. Pour lui, les mathématiques ne sont pas un système figé fondé sur des essences éternelles, mais un processus en devenir, structuré par des problèmes et des prolongements internes des théories. &lt;/p&gt; &lt;p&gt; Il critique l’idéalisme qui ramène les mathématiques à la conscience ou à des intuitions subjectives, et défend une "dialectique du concept" où les contenus mathématiques se transforment par couches successives, sans recours à un sujet fondateur. &lt;/p&gt; &lt;p&gt; Formé auprès de Léon Brunschvicg, il s’en détache en critiquant l’arrière‑plan idéaliste et en se rapprochant d’un spinozisme rationaliste et athée, inspiré par la rigueur de l’Éthique et son mos geometricus. &lt;a href="https://www.youtube.com/watch?v=2QYkjVoqsoI" style="color:#88A1E9" title="Philosophies - Héroïsme, Georges Ganguilhem et Jean Cavailles avec Blandine Kriegel par Radio J"&gt;Sa réflexion &lt;/a&gt; articule des influences venant de Frege et Bolzano (objectivité logique) et de Hegel et Husserl (dimension historique et intentionnelle), pour élaborer une logique "sans sujet", centrée sur les structures et leurs transformations. &lt;/p&gt; 
-&lt;p&gt; &lt;/p&gt; &lt;p&gt;  &lt;audio controls title="Jean Cavaillès, un philosophe dans la Résistance par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/13915-17.05.2025-ITEMA_24138144-2023C3372E0374-NET_MFC_35F98764-59B9-45DA-98A2-EC760D00C7A0-21-2cc2ee029f69376f6533a7a090eb6a3c.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;</t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Jean_Cavaill%C3%A8s"    title=" Wikipedia"&gt;Jean CAVAILLES&lt;/a&gt;  était un philosophe français des sciences et un des &lt;a href="https://cavailles.hypotheses.org/jean-cavailles/vie-de-jean-cavailles" title="Les Amis de Jean Cavaillès par Hypotheses"&gt;héros intellectuels &lt;/a&gt; de la Résistance, fusillé par les nazis à l’âge de quarante ans. Normalien et officier de réserve, il est marqué par l’effondrement de la République de Weimar, la montée du nazisme et les débats religieux et politiques de l’entre‑deux‑guerres. &lt;/p&gt; &lt;p&gt; Il se spécialise en &lt;a href="https://www.youtube.com/watch?v=zfr9wq-kYTo" style="color:#88A1E9" title="Sur la philosophie de Jean cavaillès par Hypotheses"&gt;philosophie des mathématiques &lt;/a&gt; et de la logique, en particulier sur l’histoire et la structure des théories axiomatiques. En 1938, il soutient sa grande thèse "Méthode axiomatique et formalisme", et une thèse complémentaire "Remarques sur la formation de la théorie abstraite des ensembles" qui étudient l’essor de la théorie des ensembles et la dynamique interne des mathématiques modernes. Pour lui, les mathématiques ne sont pas un système figé fondé sur des essences éternelles, mais un processus en devenir, structuré par des problèmes et des prolongements internes des théories. &lt;/p&gt; &lt;p&gt; Il critique l’idéalisme qui ramène les mathématiques à la conscience ou à des intuitions subjectives, et défend une "dialectique du concept" où les contenus mathématiques se transforment par couches successives, sans recours à un sujet fondateur. &lt;/p&gt; &lt;p&gt; Formé auprès de Léon Brunschvicg, il s’en détache en critiquant l’arrière‑plan idéaliste et en se rapprochant d’un spinozisme rationaliste et athée, inspiré par la rigueur de l’Éthique et son mos geometricus. &lt;a href="https://www.youtube.com/watch?v=2QYkjVoqsoI" style="color:#88A1E9" title="Philosophies - Héroïsme, Georges Ganguilhem et Jean Cavailles avec Blandine Kriegel par Radio J"&gt;Sa réflexion &lt;/a&gt; articule des influences venant de Frege et Bolzano (objectivité logique) et de Hegel et Husserl (dimension historique et intentionnelle), pour élaborer une logique "sans sujet", centrée sur les structures et leurs transformations. &lt;/p&gt; &lt;p&gt;  &lt;audio controls title="Jean Cavaillès, un philosophe dans la Résistance par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/13915-17.05.2025-ITEMA_24138144-2023C3372E0374-NET_MFC_35F98764-59B9-45DA-98A2-EC760D00C7A0-21-2cc2ee029f69376f6533a7a090eb6a3c.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;</t>
         </is>
       </c>
       <c r="F69" s="54" t="inlineStr">
@@ -5028,8 +5022,8 @@
       </c>
       <c r="E70" s="65" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Vladimir_Jank%C3%A9l%C3%A9vitch"   title=" Wikipedia"&gt;Vladimir JANKÉLÉVITCH&lt;/a&gt; était un philosophe français d'origine russe, influencé par Bergson, connu pour sa pensée originale &lt;a href="https://www.youtube.com/watch?v=498pItDm0vA" title=" Vladimir Jankélévitch : penser la morale, aimer le monde par Ina Culture"&gt;mêlant morale, &lt;/a&gt; temps, musique, souvent en marge des courants dominants. Il  cultive un style littéraire élégant, improvisé, centré sur l'expérience vécue, le cœur et l'ineffable, refusant les systèmes rigides. &lt;/p&gt; &lt;p&gt;  Pour lui, la morale prime sur tout : elle est hyperbolique, urgente, guidée par le cœur et l'instant de la décision, au-delà des devoirs rationnels ; elle rejoint la métaphysique.  Il conçoit &lt;a href="https://www.youtube.com/watch?v=G6hbXImCmJA" title="Vladimir Jankélévitch, penser la vie par LCP"&gt;la liberté &lt;/a&gt; comme dynamique, non statique  amenant à une prise de conscience en mouvement, vers un "au-delà de soi" ; l'homme libre agit authentiquement, sans dogmes. &lt;/p&gt; &lt;p&gt; &lt;a href="https://maitron.fr/jankelevitch-vladimir/" title=" Vladimir Jankélévitch par maitron.fr"&gt; Pour lui, &lt;/a&gt; la musique transcende l'esthétique pour devenir une expérience philosophique et métaphysique. Elle incarne l'irréversibilité du temps et l'instant fugace, reliant le sensible à l'intelligible sans jamais se réduire à une structure figée ou un algorithme. Elle exprime l'inexprimable : émotions, mystère de l'être, profondeur existentielle que le discours rationnel esquive. Le silence y joue un rôle clé, non comme absence, mais comme plénitude qui invite à l'introspection et à la transcendance. Il a consacré une douzaine d'ouvrages à la musique, comme Fauré et le Ineffable, Debussy et le Mystère ou Ravel, où philosophie et analyse musicale fusionnent en une prose poétique et improvisée.&lt;/p&gt; &lt;p&gt; Ses Œuvres majeures : -"Philosophie première" paru en 1954 : métaphysique vitaliste.  - Le &lt;a href="https://www.youtube.com/watch?v=KUUGJfgMoj0" title="Vladimir Jankélévitch en 1980, philosophe du Je-ne-sais-quoi et du Presque-rien? par Radio-Canada Archives"&gt;"Je-ne-sais-quoi et le Presque-rien" &lt;/a&gt; paru en 1957. - "La Mort" paru en 1967 et  -"L'Irréversible et la Nostalgie" en 1974. &lt;/p&gt; 
-&lt;p&gt; &lt;/p&gt;   &lt;audio controls title="Avoir raison avec... Vladimir Jankélévitch par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/17362-07.08.2017-ITEMA_21402275-2017C35448E0026-NET_FC_4ECDB095-2595-41D4-AA28-F4A95CC22729-21.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;  </t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Vladimir_Jank%C3%A9l%C3%A9vitch"   title=" Wikipedia"&gt;Vladimir JANKÉLÉVITCH&lt;/a&gt; était un philosophe français d'origine russe, influencé par Bergson, connu pour sa pensée originale &lt;a href="https://www.youtube.com/watch?v=498pItDm0vA" title=" Vladimir Jankélévitch : penser la morale, aimer le monde par Ina Culture"&gt;mêlant morale, &lt;/a&gt; temps, musique, souvent en marge des courants dominants. Il  cultive un style littéraire élégant, improvisé, centré sur l'expérience vécue, le cœur et l'ineffable, refusant les systèmes rigides. &lt;/p&gt; &lt;p&gt;  Pour lui, la morale prime sur tout : elle est hyperbolique, urgente, guidée par le cœur et l'instant de la décision, au-delà des devoirs rationnels ; elle rejoint la métaphysique.  Il conçoit &lt;a href="https://www.youtube.com/watch?v=G6hbXImCmJA" title="Vladimir Jankélévitch, penser la vie par LCP"&gt;la liberté &lt;/a&gt; comme dynamique, non statique  amenant à une prise de conscience en mouvement, vers un "au-delà de soi" ; l'homme libre agit authentiquement, sans dogmes. &lt;/p&gt; &lt;p&gt; &lt;a href="https://maitron.fr/jankelevitch-vladimir/" title=" Vladimir Jankélévitch par maitron.fr"&gt; Pour lui, &lt;/a&gt; la musique transcende l'esthétique pour devenir une expérience philosophique et métaphysique. Elle incarne l'irréversibilité du temps et l'instant fugace, reliant le sensible à l'intelligible sans jamais se réduire à une structure figée ou un algorithme. Elle exprime l'inexprimable : émotions, mystère de l'être, profondeur existentielle que le discours rationnel esquive. Le silence y joue un rôle clé, non comme absence, mais comme plénitude qui invite à l'introspection et à la transcendance. Il a consacré une douzaine d'ouvrages à la musique, comme Fauré et le Ineffable, Debussy et le Mystère ou Ravel, où philosophie et analyse musicale fusionnent en une prose poétique et improvisée.&lt;/p&gt; &lt;p&gt; Ses Œuvres majeures : -"Philosophie première" paru en 1954 : métaphysique vitaliste. Le &lt;a href="https://www.youtube.com/watch?v=KUUGJfgMoj0" title="Vladimir Jankélévitch en 1980, philosophe du Je-ne-sais-quoi et du Presque-rien? par Radio-Canada Archives"&gt;"Je-ne-sais-quoi et le Presque-rien" &lt;/a&gt; paru en 1957. "La Mort" paru en 1967 et  -"L'Irréversible et la Nostalgie" en 1974. &lt;/p&gt; 
+   &lt;audio controls title="Avoir raison avec... Vladimir Jankélévitch par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/17362-07.08.2017-ITEMA_21402275-2017C35448E0026-NET_FC_4ECDB095-2595-41D4-AA28-F4A95CC22729-21.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;  </t>
         </is>
       </c>
       <c r="F70" s="57" t="inlineStr">
@@ -5092,7 +5086,7 @@
       </c>
       <c r="E71" s="61" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Georges_Politzer"  title=" Wikipedia"&gt;Georges POLITZER&lt;/a&gt; était un philosophe et militant communiste français d'origine hongroise, connu à la fois pour sa critique précoce de la psychologie universitaire et pour son engagement dans la Résistance qui lui coûta la vie. Né à Nagyvárad en Autriche-Hongrie, il arriva en France en 1921 et s'engagea rapidement dans le mouvement communiste. Professeur dans plusieurs lycées parisiens, il fut aussi l'un des principaux animateurs des Universités ouvrières fondées par le Parti communiste français. &lt;/p&gt; &lt;p&gt; Sa contribution philosophique principale est une critique radicale de la psychologie idéaliste et introspective dans &lt;em&gt;Critique des fondements de la psychologie&lt;/em&gt; (1928). Plaidant pour une  &lt;a href="https://www.youtube.com/watch?v=XHo2z8xTIgA"  title="la psychologie concrète par tropics television"&gt;« psychologie concrète » &lt;/a&gt; fondée sur l'étude des comportements réels des êtres humains dans leurs situations historiques concrètes, il anticipe certains thèmes du béhaviorisme et de la psychologie sociale, tout en restant dans une perspective matérialiste marxiste. Cette œuvre, originale et polémique, fit sensation dans les milieux philosophiques de l'époque. &lt;/p&gt; &lt;p&gt; Ses &lt;em&gt;Principes élémentaires de philosophie&lt;/em&gt;, cours donnés dans le cadre des universités ouvrières et publiés posthumément, constituent longtemps le manuel le plus diffusé d'introduction au matérialisme dialectique dans les milieux ouvriers et militants français. Arrêté par la Gestapo en 1942, il fut torturé et fusillé au Mont-Valérien le 23 mai 1942, en même temps que son ami le physicien Jacques Solomon. Sa mort symbolise le sacrifice de nombreux  &lt;a href="https://www.youtube.com/watch?v=QV4VvYOU4xU"  title="hommage  du PRCF à Politzer par PRCF"&gt;intellectuels communistes &lt;/a&gt;  dans la Résistance française. Il reste un personnage emblématique de l'engagement philosophique au service de l'émancipation ouvrière. &lt;/p&gt; &lt;p&gt; &lt;/p&gt;&lt;audio controls title=Vie et destin de Georges Politzer par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/10467-04.06.2013-ITEMA_20487057-2013C12410E0158-NET_FC_BA6CA596-C63D-4530-800E-B3E0D71E7027-21.mp3" type="audio/mpeg" align="center"&gt;&lt;/audio&gt;  </t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Georges_Politzer"  title=" Wikipedia"&gt;Georges POLITZER&lt;/a&gt; était un philosophe et militant communiste français d'origine hongroise, connu à la fois pour sa critique précoce de la psychologie universitaire et pour son engagement dans la Résistance qui lui coûta la vie. Né à Nagyvárad en Autriche-Hongrie, il arriva en France en 1921 et s'engagea rapidement dans le mouvement communiste. Professeur dans plusieurs lycées parisiens, il fut aussi l'un des principaux animateurs des Universités ouvrières fondées par le Parti communiste français. &lt;/p&gt; &lt;p&gt; Sa contribution philosophique principale est une critique radicale de la psychologie idéaliste et introspective dans &lt;em&gt;Critique des fondements de la psychologie&lt;/em&gt; (1928). Plaidant pour une  &lt;a href="https://www.youtube.com/watch?v=XHo2z8xTIgA"  title="la psychologie concrète par tropics television"&gt;« psychologie concrète » &lt;/a&gt; fondée sur l'étude des comportements réels des êtres humains dans leurs situations historiques concrètes, il anticipe certains thèmes du béhaviorisme et de la psychologie sociale, tout en restant dans une perspective matérialiste marxiste. Cette œuvre, originale et polémique, fit sensation dans les milieux philosophiques de l'époque. &lt;/p&gt; &lt;p&gt; Ses &lt;em&gt;Principes élémentaires de philosophie&lt;/em&gt;, cours donnés dans le cadre des universités ouvrières et publiés posthumément, constituent longtemps le manuel le plus diffusé d'introduction au matérialisme dialectique dans les milieux ouvriers et militants français. Arrêté par la Gestapo en 1942, il fut torturé et fusillé au Mont-Valérien le 23 mai 1942, en même temps que son ami le physicien Jacques Solomon. Sa mort symbolise le sacrifice de nombreux  &lt;a href="https://www.youtube.com/watch?v=QV4VvYOU4xU"  title="hommage  du PRCF à Politzer par PRCF"&gt;intellectuels communistes &lt;/a&gt;  dans la Résistance française. Il reste un personnage emblématique de l'engagement philosophique au service de l'émancipation ouvrière. &lt;/p&gt; &lt;audio controls title=Vie et destin de Georges Politzer par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/10467-04.06.2013-ITEMA_20487057-2013C12410E0158-NET_FC_BA6CA596-C63D-4530-800E-B3E0D71E7027-21.mp3" type="audio/mpeg" align="center"&gt;&lt;/audio&gt;  </t>
         </is>
       </c>
       <c r="F71" s="60" t="inlineStr">
@@ -5283,7 +5277,7 @@
       </c>
       <c r="E74" s="56" t="inlineStr">
         <is>
-          <t>&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Raymond_Aron"  title=" Wikipedia"&gt;Raymond ARON&lt;/a&gt;  était un philosophe français, à la fois sociologue, politologue et journaliste, surtout connu comme grand représentant du libéralisme politique face aux totalitarismes. Agrégé de philosophie en 1928, il part à Berlin au début des années 1930, y observe la montée du nazisme, expérience décisive pour sa réflexion sur le régime. &lt;/p&gt; &lt;p&gt; Il développe un libéralisme qu’il qualifie lui‑même de &lt;a href="https://www.youtube.com/watch?v=I3briDR0HoM"  title="Raymond Aron : un philosophe face à Mai 68 et à la société industrielle par Ina Culture"&gt;"modérément immodéré": &lt;/a&gt; défense de la démocratie représentative, de l’économie mixte, refus des utopies révolutionnaires et des idéologies fermées. Il se veut réaliste: sa philosophie politique et sa sociologie s’ancrent dans &lt;a href="https://www.youtube.com/watch?v=WI4IeZq5JGo" title=" Raymond Aron - La société industrielle et la guerre par Artequieu"&gt;l’étude concrète &lt;/a&gt; des régimes, des conflits, de l’histoire, plutôt que dans de grands systèmes spéculatifs. &lt;/p&gt; &lt;p&gt; Ses oeuvres majeures : - "L’Opium des intellectuels" paru en1955, critique la fascination d’une partie des intellectuels français pour le marxisme et les régimes communistes, en inversant la formule de Marx sur la religion: pour lui, le marxisme est "l’opium des intellectuels". - "Paix et guerre entre les nations" paru en 1962 est un ouvrage clé de théorie des relations internationales, où il analyse le jeu des puissances, la logique des États et la coexistence entre guerre et paix dans le système international. &lt;/p&gt; &lt;p&gt; Longtemps isolé dans un paysage intellectuel dominé par la gauche sartrienne, il incarne une figure de l’intellectuel "anti‑idéologue", attaché à la rigueur empirique et à la prudence politique. Sa confrontation avec Sartre symbolise en France l’opposition entre un existentialisme révolutionnaire et un libéralisme réaliste soucieux des limites de l’action politique.  &lt;/p&gt; &lt;p&gt;Il  laisse une œuvre de référence en philosophie politique libérale, en sociologie de la modernité et en relations internationales, et il a formé ou influencé de nombreux chercheurs et éditorialistes. &lt;/p&gt;  &lt;audio controls title="Raymond Aron, penseur du 21e siècle ? par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/19489-13.04.2025-ITEMA_24101720-2025C33085S0103-NET_MFC_6A5A935A-A263-404D-BA44-E5609DCE1A79-21.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;</t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Raymond_Aron"  title=" Wikipedia"&gt;Raymond ARON&lt;/a&gt;  était un philosophe français, à la fois sociologue, politologue et journaliste, surtout connu comme grand représentant du libéralisme politique face aux totalitarismes. Agrégé de philosophie en 1928, il part à Berlin au début des années 1930, y observe la montée du nazisme, expérience décisive pour sa réflexion sur le régime. &lt;/p&gt; &lt;p&gt; Il développe un libéralisme qu’il qualifie lui‑même de &lt;a href="https://www.youtube.com/watch?v=I3briDR0HoM"  title="Raymond Aron : un philosophe face à Mai 68 et à la société industrielle par Ina Culture"&gt;"modérément immodéré": &lt;/a&gt; défense de la démocratie représentative, de l’économie mixte, refus des utopies révolutionnaires et des idéologies fermées. Il se veut réaliste: sa philosophie politique et sa sociologie s’ancrent dans &lt;a href="https://www.youtube.com/watch?v=WI4IeZq5JGo" title=" Raymond Aron - La société industrielle et la guerre par Artequieu"&gt;l’étude concrète &lt;/a&gt; des régimes, des conflits, de l’histoire, plutôt que dans de grands systèmes spéculatifs. &lt;/p&gt; &lt;p&gt; Ses oeuvres majeures : "L’Opium des intellectuels" paru en1955, critique la fascination d’une partie des intellectuels français pour le marxisme et les régimes communistes, en inversant la formule de Marx sur la religion: pour lui, le marxisme est "l’opium des intellectuels". "Paix et guerre entre les nations" paru en 1962 est un ouvrage clé de théorie des relations internationales, où il analyse le jeu des puissances, la logique des États et la coexistence entre guerre et paix dans le système international. &lt;/p&gt; &lt;p&gt; Longtemps isolé dans un paysage intellectuel dominé par la gauche sartrienne, il incarne une figure de l’intellectuel "anti‑idéologue", attaché à la rigueur empirique et à la prudence politique. Sa confrontation avec Sartre symbolise en France l’opposition entre un existentialisme révolutionnaire et un libéralisme réaliste soucieux des limites de l’action politique.  &lt;/p&gt; &lt;p&gt;Il  laisse une œuvre de référence en philosophie politique libérale, en sociologie de la modernité et en relations internationales, et il a formé ou influencé de nombreux chercheurs et éditorialistes. &lt;/p&gt;  &lt;audio controls title="Raymond Aron, penseur du 21e siècle ? par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/19489-13.04.2025-ITEMA_24101720-2025C33085S0103-NET_MFC_6A5A935A-A263-404D-BA44-E5609DCE1A79-21.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;</t>
         </is>
       </c>
       <c r="F74" s="54" t="inlineStr">
@@ -5408,7 +5402,7 @@
       <c r="E76" s="59" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Emmanuel_Levinas"  title=" Wikipedia"&gt;Emmanuel LEVINAS&lt;/a&gt; était un  philosophe français d'origine Lituanienne dont la pensée a profondément renouvelé la philosophie du XXᵉ siècle en plaçant l’éthique au cœur de la métaphysique. Il rompt avec la tradition occidentale qui faisait de l’ontologie (la science de l’être) la «philosophie première». Pour lui, c’est &lt;a href="https://www.youtube.com/watch?v=xTeGpHz6tWo" style="color:#88A1E9" title=" Emmanuel Lévinas - L'éthique du visage par La Piquire de Socrate"&gt;l’éthique&lt;/a&gt; qui doit être fondement de toute philosophie. L’humain n’est pas défini d’abord par son être ou sa conscience, mais par sa responsabilité infinie envers autrui. Il écrit que «le sujet est structuré comme autre dans le même» : autrui n’est jamais totalement réductible à moi, mais m’oblige moralement dès que je le rencontre. &lt;/p&gt; &lt;p&gt; Son concept central est celui &lt;a href="https://www.youtube.com/watch?v=1WO-UpY0Gm0" title=" Le Visage chez Emmanuel Lévinas par L'Acropole"&gt;du visage&lt;/a&gt; (le visage d’autrui), développé notamment dans "Totalité et infini" (1961). Le visage n’est pas ici un ensemble de traits physiques ; il est la présence de l’autre comme vulnérable et inviolable. Devant ce visage, je ressens l’injonction silencieuse : «Tu ne tueras point». &lt;a href="https://www.youtube.com/watch?v=KLA_RvU7yC0" title=" Emmanuel Lévinas – La responsabilité pour autrui par Andrea Cirla"&gt;Autrui me convoque&lt;/a&gt;, m’impose une responsabilité qui ne vient pas d’une loi rationnelle, mais du simple fait de sa présence. Ainsi, il s’éloigne du théocentrisme : Dieu n’est plus l’objet d’un savoir, mais la trace de ce qui m’oblige, visible dans la souveraineté du visage. &lt;/p&gt; &lt;p&gt; Il reconnaît que la pure éthique du face-à-face doit se penser dans la société concrète. Quand un &lt;a href="https://leverbe.com/articles/idees/lautre-est-un-exil-breve-introduction-a-la-pensee-demmanuel-levinas" title="L’autre est un exil : brève introduction à la pensée d’Emmanuel Levinas par LeVerbe"&gt;tiers apparaît&lt;/a&gt; — un autre "autre" —, apparaît la nécessité de justice : comment être juste entre plusieurs ? C’est dans ce passage que l’éthique se prolonge en politique et en droit, sans jamais perdre la priorité de la responsabilité individuelle envers autrui.  La philosophie lévinassienne affirme que la transcendance n’est pas dans un au-delà abstrait, mais dans le rapport humain lui-même. L’humain accomplit sa véritable essence en répondant à autrui, dans la paix et la non-violence. &lt;/p&gt; 
-&lt;p&gt; &lt;/p&gt;&lt;audio controls title=" Emmanuel Levinas, le judaïsme et la philosophie par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/13397-04.01.2025-ITEMA_23984657-2025C3397E0001-21.mp3" type="audio/mpeg" align="center"&gt;&lt;/audio&gt;  </t>
+&lt;audio controls title=" Emmanuel Levinas, le judaïsme et la philosophie par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/13397-04.01.2025-ITEMA_23984657-2025C3397E0001-21.mp3" type="audio/mpeg" align="center"&gt;&lt;/audio&gt;  </t>
         </is>
       </c>
       <c r="F76" s="57" t="inlineStr">
@@ -5771,8 +5765,7 @@
       </c>
       <c r="E82" s="65" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Maurice_Merleau-Ponty" title=" Wikipedia"&gt;Maurice MERLEAU-PONTY&lt;/a&gt; était un philosophe français connu pour ses contributions à la phénoménologie, à la philosophie de la perception et à l’existentialisme. Il  s’inspire de plusieurs courants et penseurs et  reprend l’idée d’une description des expériences vécues, mais critique l’idéalisme husserlien. Dans son oeurvre majeure &lt;a href="https://www.youtube.com/watch?v=RrD5SEiXr_A"  title=" La phénoménologie de Maurice Merleau-Ponty par Tes grands auteurs en petits morceaux"&gt;"Phénoménalogie de la perception"&lt;/a&gt; il  y développe une critique radicale des approches traditionnelles de la perception pour proposer une vision incarnée et existentielle de l’expérience humaine. Il rejette la séparation cartésienne entre le corps et l’esprit &lt;a href="https://classiques.uqam.ca/classiques/merleau_ponty_maurice/sens_et_non_sens/sens_et_non_sens.html"  title="  Maurice Merleau-Ponty sens et non sens  par UQAM"&gt;(sens et non sens)&lt;/a&gt;. Pour lui, le corps n’est pas un objet, mais un sujet percevant :  &lt;/p&gt; &lt;p&gt;
--  Le corps propre : C’est par lui que nous faisons l’expérience du monde. Il est à la fois sujet et objet, toujours déjà engagé dans un environnement. &lt;/p&gt; &lt;p&gt; - La perception comme ouverture au monde : &lt;a href="https://www.youtube.com/watch?v=yiHMPFMCUvo" title="MERLEAU-PONTY - L'OEIL ET L'ESPRIT par Kosmos"&gt;Percevoir&lt;/a&gt;, c’est être en dialogue avec le monde, pas simplement recevoir des données sensorielles. &lt;/p&gt;  &lt;p&gt;   Il  s’intéresse au langage comme geste corporel. Pour lui, la parole n’est pas un simple véhicule de la pensée, mais une incarnation du sens et l’art montre comment l’expression émerge de la perception. &lt;/p&gt; &lt;p&gt; Dans "Le Visible et l’invisible", il développe une  &lt;a href="https://www.youtube.com/watch?v=wZNUUGSZHMs"  title=" Maurice Merleau-Ponty - Entretien : Heure de culture française par Artesquieu "&gt;ontologie originale&lt;/a&gt; où le "chair" est ni matière ni esprit, c’est une substance sensible qui unit le corps et le monde.  Chiasme : Concept décrivant l’entrelacs du voyant et du visible, du touchant et du touché (ex. : quand je me touche la main, je suis à la fois sujet et objet).  L’invisible : Non pas l’absence de visible, mais ce qui le structure. &lt;/p&gt;   &lt;audio controls title="Maurice Merleau-Ponty : Partie 8/12- La crise de la pensée religieuse par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/13915-20.11.2014-ITEMA_20690515-2013C3372E0710-21.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;  </t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Maurice_Merleau-Ponty" title=" Wikipedia"&gt;Maurice MERLEAU-PONTY&lt;/a&gt; était un philosophe français connu pour ses contributions à la phénoménologie, à la philosophie de la perception et à l’existentialisme. Il  s’inspire de plusieurs courants et penseurs et  reprend l’idée d’une description des expériences vécues, mais critique l’idéalisme husserlien. Dans son oeurvre majeure &lt;a href="https://www.youtube.com/watch?v=RrD5SEiXr_A"  title=" La phénoménologie de Maurice Merleau-Ponty par Tes grands auteurs en petits morceaux"&gt;"Phénoménalogie de la perception"&lt;/a&gt; il  y développe une critique radicale des approches traditionnelles de la perception pour proposer une vision incarnée et existentielle de l’expérience humaine. Il rejette la séparation cartésienne entre le corps et l’esprit &lt;a href="https://classiques.uqam.ca/classiques/merleau_ponty_maurice/sens_et_non_sens/sens_et_non_sens.html"  title="  Maurice Merleau-Ponty sens et non sens  par UQAM"&gt;(sens et non sens)&lt;/a&gt;. Pour lui, le corps n’est pas un objet, mais un sujet percevant :  &lt;/p&gt; &lt;p&gt;Le corps propre : C’est par lui que nous faisons l’expérience du monde. Il est à la fois sujet et objet, toujours déjà engagé dans un environnement. &lt;/p&gt; &lt;p&gt;La perception comme ouverture au monde : &lt;a href="https://www.youtube.com/watch?v=yiHMPFMCUvo" title="MERLEAU-PONTY - L'OEIL ET L'ESPRIT par Kosmos"&gt;Percevoir&lt;/a&gt;, c’est être en dialogue avec le monde, pas simplement recevoir des données sensorielles. &lt;/p&gt; &lt;p&gt;   Il  s’intéresse au langage comme geste corporel. Pour lui, la parole n’est pas un simple véhicule de la pensée, mais une incarnation du sens et l’art montre comment l’expression émerge de la perception. &lt;/p&gt; &lt;p&gt; Dans "Le Visible et l’invisible", il développe une  &lt;a href="https://www.youtube.com/watch?v=wZNUUGSZHMs"  title=" Maurice Merleau-Ponty - Entretien : Heure de culture française par Artesquieu "&gt;ontologie originale&lt;/a&gt; où le "chair" est ni matière ni esprit, c’est une substance sensible qui unit le corps et le monde.  Chiasme : Concept décrivant l’entrelacs du voyant et du visible, du touchant et du touché (ex. : quand je me touche la main, je suis à la fois sujet et objet).  L’invisible : Non pas l’absence de visible, mais ce qui le structure. &lt;/p&gt;   &lt;audio controls title="Maurice Merleau-Ponty : Partie 8/12- La crise de la pensée religieuse par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/13915-20.11.2014-ITEMA_20690515-2013C3372E0710-21.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;  </t>
         </is>
       </c>
       <c r="F82" s="57" t="inlineStr">
@@ -6578,7 +6571,7 @@
       </c>
       <c r="E95" s="65" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Louis_Althusser"  title=" Wikipedia"&gt;Louis ALTHUSSER&lt;/a&gt; était un philosophe connu pour ses efforts de renouvellement de la pensée marxiste et ses concepts novateurs.  Parmi ses concepts clés, on peut citer : &lt;/p&gt;  &lt;p&gt; - La coupure épistémologique : Il soutient qu'il existe une rupture radicale entre les œuvres de jeunesse de Marx  et ses œuvres de la maturité (notamment Le Capital). Cette coupure marquerait le passage d'une idéologie humaniste à une science de l'histoire, le matérialisme historique. &lt;/p&gt; &lt;p&gt; - L'idéologie et les Appareils Idéologiques d'État &lt;a href="https://www.youtube.com/watch?v=ZtJjAs7kLpo"  title=" Louis Althusser AIE par Cinema culture"&gt;(AIE) &lt;/a&gt;: Il développe une théorie influente de l'idéologie avec un ensemble d'idées fausses, mais une "représentation du rapport imaginaire des individus à leurs conditions réelles d'existence". Elle fonctionne en "interpellant" les individus en sujets. Les AIE (comme l'école, l'Église, la famille, les médias) jouent un rôle crucial dans la reproduction des rapports de production capitalistes en diffusant l'idéologie dominante. &lt;/p&gt; &lt;p&gt; - La surdétermination : Emprunté à la psychanalyse, ce concept lui permet de penser la complexité des contradictions dans une société. Une contradiction principale entre les forces productives et les rapports de production est toujours surdéterminée par d'autres contradictions secondaires. &lt;/p&gt; &lt;p&gt; - Le procès sans sujet : Il critique l'idée que l'histoire serait le produit de l'action consciente d'un sujet et insiste sur le fait que l'histoire est un &lt;a href="https://www.youtube.com/watch?v=Syi7hOQcNUs"  title=" Louis Althusser sur la civilisation par Artesquieu"&gt;processus déterminé&lt;/a&gt; par des structures. &lt;/p&gt; &lt;p&gt;  - La philosophie comme "lutte de classes dans la théorie" : Il conçoit la philosophie non pas comme une quête de vérité absolue, mais comme une intervention politique dans le champ théorique, reflétant les luttes de classes. Il parle aussi de la "philosophie spontanée des savants" pour désigner les présupposés idéologiques inconscients qui peuvent influencer le travail scientifique. &lt;/p&gt; &lt;p&gt; Parmi ses publications les plus importantes, on peut mentionner : &lt;/p&gt; &lt;p&gt;- Montesquieu, la politique et l'histoire : Une analyse de la pensée politique de Montesquieu.  - Lénine et la philosophie : Développe sa conception de la philosophie comme pratique politique.  - L'avenir dure longtemps (suivi de Les Faits) (1992, posthume) : Une autobiographie où il revient sur sa vie, ses troubles psychiques et le meurtre de sa femme, Hélène Rytmann, en 1980. Cet événement tragique a conduit à son internement psychiatrique et a mis fin à sa carrière publique. &lt;/p&gt;  &lt;audio controls title=" Louis Althusser par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/11189-11.07.2011-ITEMA_20296434-2011C15000E0126-ITE_00044081_RSCE-21.mp3" type="audio/mpeg" align="center"&gt;&lt;/audio&gt; </t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Louis_Althusser"  title=" Wikipedia"&gt;Louis ALTHUSSER&lt;/a&gt; était un philosophe connu pour ses efforts de renouvellement de la pensée marxiste et ses concepts novateurs.  Parmi ses concepts clés, on peut citer : &lt;/p&gt; &lt;p&gt;La coupure épistémologique : Il soutient qu'il existe une rupture radicale entre les œuvres de jeunesse de Marx  et ses œuvres de la maturité (notamment Le Capital). Cette coupure marquerait le passage d'une idéologie humaniste à une science de l'histoire, le matérialisme historique. &lt;/p&gt; &lt;p&gt;L'idéologie et les Appareils Idéologiques d'État &lt;a href="https://www.youtube.com/watch?v=ZtJjAs7kLpo"  title=" Louis Althusser AIE par Cinema culture"&gt;(AIE) &lt;/a&gt;: Il développe une théorie influente de l'idéologie avec un ensemble d'idées fausses, mais une "représentation du rapport imaginaire des individus à leurs conditions réelles d'existence". Elle fonctionne en "interpellant" les individus en sujets. Les AIE (comme l'école, l'Église, la famille, les médias) jouent un rôle crucial dans la reproduction des rapports de production capitalistes en diffusant l'idéologie dominante. &lt;/p&gt; &lt;p&gt;La surdétermination : Emprunté à la psychanalyse, ce concept lui permet de penser la complexité des contradictions dans une société. Une contradiction principale entre les forces productives et les rapports de production est toujours surdéterminée par d'autres contradictions secondaires. &lt;/p&gt; &lt;p&gt;Le procès sans sujet : Il critique l'idée que l'histoire serait le produit de l'action consciente d'un sujet et insiste sur le fait que l'histoire est un &lt;a href="https://www.youtube.com/watch?v=Syi7hOQcNUs"  title=" Louis Althusser sur la civilisation par Artesquieu"&gt;processus déterminé&lt;/a&gt; par des structures. &lt;/p&gt; &lt;p&gt;La philosophie comme "lutte de classes dans la théorie" : Il conçoit la philosophie non pas comme une quête de vérité absolue, mais comme une intervention politique dans le champ théorique, reflétant les luttes de classes. Il parle aussi de la "philosophie spontanée des savants" pour désigner les présupposés idéologiques inconscients qui peuvent influencer le travail scientifique. &lt;/p&gt; &lt;p&gt; Parmi ses publications les plus importantes, on peut mentionner : &lt;/p&gt; &lt;p&gt;Montesquieu, la politique et l'histoire : Une analyse de la pensée politique de Montesquieu. Lénine et la philosophie : Développe sa conception de la philosophie comme pratique politique. L'avenir dure longtemps (suivi de Les Faits) (1992, posthume) : Une autobiographie où il revient sur sa vie, ses troubles psychiques et le meurtre de sa femme, Hélène Rytmann, en 1980. Cet événement tragique a conduit à son internement psychiatrique et a mis fin à sa carrière publique. &lt;/p&gt;  &lt;audio controls title=" Louis Althusser par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/11189-11.07.2011-ITEMA_20296434-2011C15000E0126-ITE_00044081_RSCE-21.mp3" type="audio/mpeg" align="center"&gt;&lt;/audio&gt; </t>
         </is>
       </c>
       <c r="F95" s="57" t="inlineStr">
@@ -6760,7 +6753,7 @@
       </c>
       <c r="E98" s="62" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Jules_Vuillemin"  title=" Wikipedia"&gt;Jules VUILLEMIN&lt;/a&gt;  était un philosophe français qui  s'est distingué par son travail en  &lt;a href="https://hal.science/hal-04409311v1/document" title="Jules Vuillemin, philosdophie analytique contrarié par hal"&gt;philosophie analytique&lt;/a&gt;, en épistémologie et en histoire de la philosophie.  Il diffuse en France les idées de Bertrand Russell, Rudolf Carnap et Willard Van Orman Quine, influençant des penseurs comme Jacques Bouveresse. Ses débuts touchent à  &lt;a href="https://lafrancebyzantine.blogspot.com/2016/09/jules-vuillemin-t-il-ete-existentialiste.html"  title="Jules Vuillemin at'il été existantialiste? par lafrancebyzantine"&gt;l'existentialisme &lt;/a&gt; et au marxisme, mais il évolue vers un rationalisme rigoureux, rejetant les excès de Sartre ou Heidegger. &lt;/p&gt; &lt;p&gt; Ses œuvres majeures : - "Nécessité ou contingence" paru en 1984, qui analyse les systèmes philosophiques par une approche logique et historique, et "La philosophie de l'algèbre" paru en 1962 ou il explore la nécessité, la contingence, la logique et les sciences, insistant sur la cohérence interne des systèmes selon l'héritage de Martial Gueroult. Épistémologue de premier plan avec Gilles Gaston Granger et René Thom, il défend une philosophie attentive aux mathématiques et à la physique. &lt;/p&gt; &lt;p&gt; Il s'intéresse à Kant, Descartes, la liberté et la métaphysique de la nature, tout en critiquant les réductions existentialistes au profit d'une raison objective. Ses archives sont conservées au Laboratoire de Philosophie et d'Histoire des Sciences à Nancy. Auteur de plus de vingt livres, il reste une figure de la rigueur philosophique française. &lt;/p&gt;</t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Jules_Vuillemin"  title=" Wikipedia"&gt;Jules VUILLEMIN&lt;/a&gt;  était un philosophe français qui  s'est distingué par son travail en  &lt;a href="https://hal.science/hal-04409311v1/document" title="Jules Vuillemin, philosdophie analytique contrarié par hal"&gt;philosophie analytique&lt;/a&gt;, en épistémologie et en histoire de la philosophie.  Il diffuse en France les idées de Bertrand Russell, Rudolf Carnap et Willard Van Orman Quine, influençant des penseurs comme Jacques Bouveresse. Ses débuts touchent à  &lt;a href="https://lafrancebyzantine.blogspot.com/2016/09/jules-vuillemin-t-il-ete-existentialiste.html"  title="Jules Vuillemin at'il été existantialiste? par lafrancebyzantine"&gt;l'existentialisme &lt;/a&gt; et au marxisme, mais il évolue vers un rationalisme rigoureux, rejetant les excès de Sartre ou Heidegger. &lt;/p&gt; &lt;p&gt; Ses œuvres majeures : "Nécessité ou contingence" paru en 1984, qui analyse les systèmes philosophiques par une approche logique et historique, et "La philosophie de l'algèbre" paru en 1962 ou il explore la nécessité, la contingence, la logique et les sciences, insistant sur la cohérence interne des systèmes selon l'héritage de Martial Gueroult. Épistémologue de premier plan avec Gilles Gaston Granger et René Thom, il défend une philosophie attentive aux mathématiques et à la physique. &lt;/p&gt; &lt;p&gt; Il s'intéresse à Kant, Descartes, la liberté et la métaphysique de la nature, tout en critiquant les réductions existentialistes au profit d'une raison objective. Ses archives sont conservées au Laboratoire de Philosophie et d'Histoire des Sciences à Nancy. Auteur de plus de vingt livres, il reste une figure de la rigueur philosophique française. &lt;/p&gt;</t>
         </is>
       </c>
       <c r="F98" s="54" t="inlineStr">
@@ -6821,7 +6814,7 @@
       <c r="E99" s="59" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Gilles_Gaston_Granger"   title=" Wikipedia"&gt;Gilles Gaston GRANGER&lt;/a&gt;  était un philosophe  et épistémologue français connu pour son travail sur l'épistémologie comparative et l'application des formes logico-mathématiques aux sciences humaines. Élève de l'École normale supérieure, agrégé de philosophie en 1943 et licencié en mathématiques, &lt;a href="https://www.persee.fr/authority/281588"title=" Gilles Gaston GRANGER par Persée"&gt; il enseigna &lt;/a&gt; au Brésil puis en France.  Il traduisit le "Tractatus logico-philosophicus" de Wittgenstein en français et fonda la revue L'Âge de la Science en 1968. &lt;/p&gt; &lt;p&gt; Il, &lt;a href="https://www.youtube.com/watch?v=koxZPXhxpt0&amp;t=699s" title="
-Rationalité et raisonnement — Gilles-Gaston Granger par Andrea Cirla"&gt;développa &lt;/a&gt; une épistémologie comparatiste, unifiant sciences de la nature et humaines sur une échelle commune, inspirée d'Aristote et d'un rationalisme pragmatique. Il rejeta le platonisme (formes abstraites) et le positivisme strict (lois universelles pour les faits humains), privilégiant les modèles sémantiques et probabilistes en économie ou linguistique.  La raison est pour lui un "travail" et un "style" évolutif, appliquant formes mathématiques à des contenus concrets via abstraction. &lt;/p&gt; &lt;p&gt; Ses Œuvres clés sont : -"Méthodologie économique" paru en 1955 et "La Mathématique sociale du marquis de Condorcet" en 1956 : analyses pionnières des sciences humaines. - "Pensée formelle et sciences de l'homme" paru en 1960 : montre comment modéliser l'individuel (économie, langage, histoire). &lt;/p&gt; Il enseigne à l’université de São Paulo de 1947 à 1953, avant d’occuper de 1986 à 1991 une chaire d’épistémologie comparative au Collège de France. Dans &lt;em&gt;Essai d’une philosophie du style&lt;/em&gt; (1968), il montre que même la science, en apparence impersonnelle, porte la marque d’un style, c’est-à-dire d’une manière singulière d’organiser une expérience.</t>
+Rationalité et raisonnement — Gilles-Gaston Granger par Andrea Cirla"&gt;développa &lt;/a&gt; une épistémologie comparatiste, unifiant sciences de la nature et humaines sur une échelle commune, inspirée d'Aristote et d'un rationalisme pragmatique. Il rejeta le platonisme (formes abstraites) et le positivisme strict (lois universelles pour les faits humains), privilégiant les modèles sémantiques et probabilistes en économie ou linguistique.  La raison est pour lui un "travail" et un "style" évolutif, appliquant formes mathématiques à des contenus concrets via abstraction. &lt;/p&gt; &lt;p&gt; Ses Œuvres clés sont : -"Méthodologie économique" paru en 1955 et "La Mathématique sociale du marquis de Condorcet" en 1956 : analyses pionnières des sciences humaines. "Pensée formelle et sciences de l'homme" paru en 1960 : montre comment modéliser l'individuel (économie, langage, histoire). &lt;/p&gt; Il enseigne à l’université de São Paulo de 1947 à 1953, avant d’occuper de 1986 à 1991 une chaire d’épistémologie comparative au Collège de France. Dans &lt;em&gt;Essai d’une philosophie du style&lt;/em&gt; (1968), il montre que même la science, en apparence impersonnelle, porte la marque d’un style, c’est-à-dire d’une manière singulière d’organiser une expérience.</t>
         </is>
       </c>
       <c r="F99" s="57" t="inlineStr">
@@ -7126,7 +7119,7 @@
       </c>
       <c r="E104" s="65" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Ren%C3%A9_Girard" title=" Wikipedia"&gt;René GIRARD&lt;/a&gt; était un philosophe, anthropologue et critique littéraire français dont la pensée, souvent qualifiée de "théorie mimétique", repose sur des concepts clés interdépendants qui expliquent la nature du désir humain, de la violence et du sacré. &lt;/p&gt; &lt;p&gt;Nous ne désirons pas intrinsèquement des objets ou des personnes, mais nous désirons ce que les autres désirent. Notre  &lt;a href="https://www.youtube.com/watch?v=9tn7RVVD_bA" title="Le désir mimétique par le Precepteur"&gt;désir est "triangulaire" &lt;/a&gt; : il y a un sujet (celui qui désire), un objet, et un modèle (celui dont le désir influence le sujet). Voici les 3 points clés : &lt;/p&gt; &lt;p&gt;- Le modèle comme médiateur : Le modèle n'est pas simplement une personne qui possède l'objet désiré, mais celui qui nous le révèle comme désirable. &lt;/p&gt; &lt;p&gt; - &lt;a href="https://www.youtube.com/watch?v=7scJjspwo9M" title="La rivalité mimétique par le Precepteur"&gt;La rivalité mimétique &lt;/a&gt; : Lorsque plusieurs personnes désirent le même objet, une rivalité mimétique émerge et elle peut devenir intense et se substituer à l'objet initial. &lt;/p&gt; &lt;p&gt; - Le désir métaphysique : Il distingue le désir des objets matériels du désir d'être, plus profond car il porte sur quelque chose d'insaisissable. &lt;/p&gt; &lt;p&gt; Dans son ouvrages "Mensonge romantique et vérité romanesque", il montre comment les grands romanciers ont intuitivement compris la nature mimétique du désir et les illusions "romantiques" qui le masquent. &lt;/p&gt; &lt;p&gt; Selon lui, les sociétés humaines ont développé un mécanisme archaïque pour résoudre ces crises mimétiques : le mécanisme du &lt;a href="https://www.youtube.com/watch?v=QYTKoHPrKxI" title=" La fabrique du bouc émissaire par le Parole de Philosophe"&gt;bouc émissaire&lt;/a&gt; dont voici les points clés : &lt;/p&gt; &lt;p&gt; - La désignation d'une victime : Au point culminant de la crise, l'attention de la communauté se focalise sur un individu ou un groupe particulier, accusé d'être la cause du désordre. &lt;/p&gt; &lt;p&gt; - L'unanimité contre la victime :  &lt;a href="https://www.dailymotion.com/video/xv8mim"  title=" René Girard, la violence et le sacré par le Parole de mySkreen"&gt;La violence mimétique&lt;/a&gt;, initialement diffuse, se canalise et se concentre sur ce bouc émissaire. L'expulsion ou la mort de la victime rétablit temporairement la paix. &lt;/p&gt; &lt;p&gt; - La sacralisation de la victime : après avoir été la source du mal, elle est souvent sacralisée. On lui attribue un pouvoir extraordinaire, capable à la fois de provoquer la crise et de la résoudre. &lt;/p&gt; &lt;p&gt; - Le rite et le mythe : Les rites sacrificiels et les mythes sont des tentatives de reproduire et de commémorer le meurtre fondateur du bouc émissaire. &lt;/p&gt; &lt;p&gt;Il reste une figure intellectuelle majeure, dont les idées continuent d'inspirer et de provoquer la réflexion sur la nature humaine, la culture et la religion. &lt;/p&gt; &lt;audio controls title="René Girard, des choses cachées depuis la fondation du monde" par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/13915-24.12.2023-ITEMA_23566825-2023C3372E0859-21.mp3" type="audio/mpeg" align="center"&gt;&lt;/audio&gt;  </t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Ren%C3%A9_Girard" title=" Wikipedia"&gt;René GIRARD&lt;/a&gt; était un philosophe, anthropologue et critique littéraire français dont la pensée, souvent qualifiée de "théorie mimétique", repose sur des concepts clés interdépendants qui expliquent la nature du désir humain, de la violence et du sacré. &lt;/p&gt; &lt;p&gt;Nous ne désirons pas intrinsèquement des objets ou des personnes, mais nous désirons ce que les autres désirent. Notre  &lt;a href="https://www.youtube.com/watch?v=9tn7RVVD_bA" title="Le désir mimétique par le Precepteur"&gt;désir est "triangulaire" &lt;/a&gt; : il y a un sujet (celui qui désire), un objet, et un modèle (celui dont le désir influence le sujet). &lt;/p&gt; &lt;p&gt;Le modèle comme médiateur : Le modèle n'est pas simplement une personne qui possède l'objet désiré, mais celui qui nous le révèle comme désirable. &lt;/p&gt; &lt;p&gt;&lt;a href="https://www.youtube.com/watch?v=7scJjspwo9M" title="La rivalité mimétique par le Precepteur"&gt;La rivalité mimétique &lt;/a&gt; : Lorsque plusieurs personnes désirent le même objet, une rivalité mimétique émerge et elle peut devenir intense et se substituer à l'objet initial. &lt;/p&gt; &lt;p&gt;Le désir métaphysique : Il distingue le désir des objets matériels du désir d'être, plus profond car il porte sur quelque chose d'insaisissable. &lt;/p&gt; &lt;p&gt; Dans son ouvrages "Mensonge romantique et vérité romanesque", il montre comment les grands romanciers ont intuitivement compris la nature mimétique du désir et les illusions "romantiques" qui le masquent. &lt;/p&gt; &lt;p&gt; Selon lui, les sociétés humaines ont développé un mécanisme archaïque pour résoudre ces crises mimétiques : le mécanisme du &lt;a href="https://www.youtube.com/watch?v=QYTKoHPrKxI" title=" La fabrique du bouc émissaire par le Parole de Philosophe"&gt;bouc émissaire&lt;/a&gt; dont voici les points clés : &lt;/p&gt; &lt;p&gt;La désignation d'une victime : Au point culminant de la crise, l'attention de la communauté se focalise sur un individu ou un groupe particulier, accusé d'être la cause du désordre. &lt;/p&gt; &lt;p&gt;L'unanimité contre la victime :  &lt;a href="https://www.dailymotion.com/video/xv8mim"  title=" René Girard, la violence et le sacré par le Parole de mySkreen"&gt;La violence mimétique&lt;/a&gt;, initialement diffuse, se canalise et se concentre sur ce bouc émissaire. L'expulsion ou la mort de la victime rétablit temporairement la paix. &lt;/p&gt; &lt;p&gt;La sacralisation de la victime : après avoir été la source du mal, elle est souvent sacralisée. On lui attribue un pouvoir extraordinaire, capable à la fois de provoquer la crise et de la résoudre. &lt;/p&gt; &lt;p&gt;Le rite et le mythe : Les rites sacrificiels et les mythes sont des tentatives de reproduire et de commémorer le meurtre fondateur du bouc émissaire. &lt;/p&gt; &lt;p&gt;Il reste une figure intellectuelle majeure, dont les idées continuent d'inspirer et de provoquer la réflexion sur la nature humaine, la culture et la religion. &lt;/p&gt; &lt;audio controls title="René Girard, des choses cachées depuis la fondation du monde" par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/13915-24.12.2023-ITEMA_23566825-2023C3372E0859-21.mp3" type="audio/mpeg" align="center"&gt;&lt;/audio&gt;  </t>
         </is>
       </c>
       <c r="F104" s="57" t="inlineStr">
@@ -7366,9 +7359,7 @@
       </c>
       <c r="E108" s="65" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Gilles_Deleuze" title=" Wikipedia"&gt;Gilles DELEUZE&lt;/a&gt; était un philosophe français qui a profondément marqué la pensée contemporaine dans une  &lt;a href="http://sos.philosophie.free.fr/deleuze.php" style="color:#88A1E9" title=" Gilles Deleuze  par SOS philo"&gt;critique radicale&lt;/a&gt;oeuvre foisonnante et complexe.  Au cœur de sa philosophie se trouve une  &lt;a href="https://www.youtube.com/watch?v=4ybvyj_Pk7M" title=" Gilles Deleuze : l'art et les sociétés de contrôle par lINTELLECT FOCUS"&gt;critique radicale&lt;/a&gt; de la pensée traditionnelle occidentale, qu'il accuse d'être dominée par une logique de la représentation, de l'identité et de la négation. &lt;/p&gt; &lt;p&gt; Il cherche à penser la différence en elle-même qui n'est pas secondaire ou dérivée, mais originaire.  Le monde n'est pas constitué d'entités fixes et identiques qui entreraient ensuite en relation, mais d'un flux incessant de différences, de variations et de devenirs. Il conçoit plutôt la pensée comme une force créatrice qui produit des concepts pour appréhender et transformer le réel qui n'est pas statique, mais un processus continu de transformation, d'hybridation et de métamorphose. Ses oeuvres principales sont : &lt;/p&gt; &lt;p&gt; - &lt;a href="https://www.youtube.com/watch?v=ia0FpHbHa_U"  title=" Différence et répétition de Gilles Deleuze (French Audiobook/Livre audio) 1 Avant propos par Chad A Haag Philosophy Channel"&gt;"Différence et Répétition"&lt;/a&gt; : Oeuvre métaphysique majeure, où il développe sa pensée de la différence et critique la conception traditionnelle de la répétition comme reproduction de l'identique. &lt;/p&gt; 
-&lt;p&gt; - "Logique du sens" : Une exploration des paradoxes du langage et du sens à travers une lecture originale de Lewis Carroll et des stoïciens. &lt;/p&gt; 
-&lt;p&gt; - "Qu'est-ce que la philosophie ?" (avec Félix Guattari) : Une réflexion sur la nature de la philosophie comme création de concepts, distincte de la science et de l'art. &lt;/p&gt; &lt;p&gt;  Sa rencontre avec Felix Guattari donne naissance à 2 ouvrages majeurs :&lt;a href="https://www.youtube.com/watch?v=JQE4_2ti_10&amp;t=78s" title=" La pensée politique de Deleuze et Guattari - Partie 1 / L'anti-Oedipe par Politikon"&gt;" L'Anti-Œdipe "&lt;/a&gt;  : Critique radicale de la psychanalyse et une exploration du désir comme force révolutionnaire et &lt;a href="https://www.youtube.com/watch?v=E01RyGu3Zac" title="La pensée politique de Deleuze et Guattari - Partie 2 / Mille Plateaux par Politikon"&gt;" Mille Plateaux "&lt;/a&gt;   : Une œuvre foisonnante qui explore une multitude de thèmes (le territoire, le devenir ) à travers le  &lt;a href="https://www.youtube.com/watch?v=RQ2rJWwXilw" title="The Rhizome - A Thousand Plateaus, Deleuze and Guattari par Then &amp; Now"&gt;concept de Rhizome&lt;/a&gt;. &lt;/p&gt; &lt;p&gt; Il  est un philosophe majeur qui a profondément transformé notre manière de  &lt;a href="https://diacritik.com/category/deleuze/" title=" Deleuze par Diacritik"&gt;penser la différence&lt;/a&gt;, la multiplicité, le devenir et la créativité. &lt;/p&gt; &lt;audio controls title="Gilles Deleuze, notre contemporain" par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/11189-19.11.2012-ITEMA_20421487-2012C15000E0183-ITE_00054426_RSCE-21.mp3" type="audio/mpeg" align="center"&gt;&lt;/audio&gt; </t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Gilles_Deleuze" title=" Wikipedia"&gt;Gilles DELEUZE&lt;/a&gt; était un philosophe français qui a profondément marqué la pensée contemporaine dans une  &lt;a href="http://sos.philosophie.free.fr/deleuze.php" style="color:#88A1E9" title=" Gilles Deleuze  par SOS philo"&gt;critique radicale&lt;/a&gt;oeuvre foisonnante et complexe.  Au cœur de sa philosophie se trouve une  &lt;a href="https://www.youtube.com/watch?v=4ybvyj_Pk7M" title=" Gilles Deleuze : l'art et les sociétés de contrôle par lINTELLECT FOCUS"&gt;critique radicale&lt;/a&gt; de la pensée traditionnelle occidentale, qu'il accuse d'être dominée par une logique de la représentation, de l'identité et de la négation. &lt;/p&gt; &lt;p&gt; Il cherche à penser la différence en elle-même qui n'est pas secondaire ou dérivée, mais originaire.  Le monde n'est pas constitué d'entités fixes et identiques qui entreraient ensuite en relation, mais d'un flux incessant de différences, de variations et de devenirs. Il conçoit plutôt la pensée comme une force créatrice qui produit des concepts pour appréhender et transformer le réel qui n'est pas statique, mais un processus continu de transformation, d'hybridation et de métamorphose. Ses oeuvres principales sont : &lt;/p&gt; &lt;p&gt;&lt;a href="https://www.youtube.com/watch?v=ia0FpHbHa_U"  title=" Différence et répétition de Gilles Deleuze (French Audiobook/Livre audio) 1 Avant propos par Chad A Haag Philosophy Channel"&gt;"Différence et Répétition"&lt;/a&gt; : Oeuvre métaphysique majeure, où il développe sa pensée de la différence et critique la conception traditionnelle de la répétition comme reproduction de l'identique. &lt;/p&gt; &lt;p&gt;"Logique du sens" : Une exploration des paradoxes du langage et du sens à travers une lecture originale de Lewis Carroll et des stoïciens. &lt;/p&gt; &lt;p&gt;"Qu'est-ce que la philosophie ?" (avec Félix Guattari) : Une réflexion sur la nature de la philosophie comme création de concepts, distincte de la science et de l'art. &lt;/p&gt; &lt;p&gt;  Sa rencontre avec Felix Guattari donne naissance à 2 ouvrages majeurs :&lt;a href="https://www.youtube.com/watch?v=JQE4_2ti_10&amp;t=78s" title=" La pensée politique de Deleuze et Guattari - Partie 1 / L'anti-Oedipe par Politikon"&gt;" L'Anti-Œdipe "&lt;/a&gt;  : Critique radicale de la psychanalyse et une exploration du désir comme force révolutionnaire et &lt;a href="https://www.youtube.com/watch?v=E01RyGu3Zac" title="La pensée politique de Deleuze et Guattari - Partie 2 / Mille Plateaux par Politikon"&gt;" Mille Plateaux "&lt;/a&gt;   : Une œuvre foisonnante qui explore une multitude de thèmes (le territoire, le devenir ) à travers le  &lt;a href="https://www.youtube.com/watch?v=RQ2rJWwXilw" title="The Rhizome - A Thousand Plateaus, Deleuze and Guattari par Then &amp; Now"&gt;concept de Rhizome&lt;/a&gt;. &lt;/p&gt; &lt;p&gt; Il  est un philosophe majeur qui a profondément transformé notre manière de  &lt;a href="https://diacritik.com/category/deleuze/" title=" Deleuze par Diacritik"&gt;penser la différence&lt;/a&gt;, la multiplicité, le devenir et la créativité. &lt;/p&gt; &lt;audio controls title="Gilles Deleuze, notre contemporain" par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/11189-19.11.2012-ITEMA_20421487-2012C15000E0183-ITE_00054426_RSCE-21.mp3" type="audio/mpeg" align="center"&gt;&lt;/audio&gt; </t>
         </is>
       </c>
       <c r="F108" s="57" t="inlineStr">
@@ -7489,7 +7480,7 @@
       </c>
       <c r="E110" s="89" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Fran%C3%A7ois_Wahl"  title=" Wikipedia"&gt;François WAHL&lt;/a&gt; était un philosophe et éditeur français, figure centrale de la vie intellectuelle française de la fin des années 1950 au début des années 1990, surtout connu pour avoir promu le structuralisme et la psychanalyse aux Éditions du Seuil. l a régné pendant trente ans sur le domaine des sciences humaines et la littérature italienne au Seuil, publiant Jacques Lacan, Françoise Dolto, Paul Ricœur, Roland Barthes, Philippe Sollers, Alain Badiou, Jean-Cla Milner, ainsi que des auteurs italiens comme Carlo Emilio Gadda et Italo Calvino. Il est décrit comme un « structuraliste dans l’âme », construisant son activité éditoriale comme une structure où chaque choix (acceptations, refus, retraductions) faisait système, appliquant la doctrine structuraliste à son métier d’éditeur. &lt;/p&gt; &lt;p&gt; Il est l’auteur de trois ouvrages majeurs :  &lt;a href="https://philosophie.ac-normandie.fr/spip.php?article148" title="qu’est ce que la philosophie par françois Wahl "&gt;Qu’est-ce que le structuralisme ? &lt;/a&gt; , Philosophie (1973), Introduction au discours du tableau (1996) et Le Perçu (2007). Dans Introduction au discours du tableau, il étudie les œuvres de Poussin, Memling ou Bellini pour montrer que le « visible » apparaît sous deux espèces : le paysage et le tableau, articulant ainsi esthétique et théorie du signe. Le Perçu propose une exploration critique des phénoménologies du XXᵉ siècle, en mobilisant les concepts de discours, sujet, désir et énoncé pour formaliser une analyse du « fait esthétique ». &lt;/p&gt; &lt;p&gt; La ligne directrice de sa pensée peut se résumer à un repérage du concept de sujet dans la philosophie contemporaine et son introduction dans le champ de l’esthétique. Il a écrit de nombreux articles discutant les œuvres d’auteurs comme Badiou, Bataille, Barthes, Foucault ou Lacan, et son dernier grand livre, La dissidence du sujet, rassemble ces réflexions sur le sujet, le désir et le discours dans la philosophie et l’art. &lt;/p&gt; &lt;audio controls title="les fluides d’Aristote /hommage à f Wahl par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/12003-17.09.2014-ITEMA_20670365-2014C18006S0260-21.mp3" type="audio/mpeg" align="center"&gt;&lt;/audio&gt;  </t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Fran%C3%A7ois_Wahl"  title=" Wikipedia"&gt;François WAHL&lt;/a&gt; était un philosophe et éditeur français, figure centrale de la vie intellectuelle française de la fin des années 1950 au début des années 1990, surtout connu pour avoir promu le structuralisme et la psychanalyse aux Éditions du Seuil. Il a régné pendant trente ans sur le domaine des sciences humaines et la littérature italienne au Seuil, publiant Jacques Lacan, Françoise Dolto, Paul Ricœur, Roland Barthes, Philippe Sollers, Alain Badiou, Jean-Claude Milner, ainsi que des auteurs italiens comme Carlo Emilio Gadda et Italo Calvino. Il est décrit comme un « structuraliste dans l’âme », construisant son activité éditoriale comme une structure où chaque choix (acceptations, refus, retraductions) faisait système, appliquant la doctrine structuraliste à son métier d’éditeur. &lt;/p&gt; &lt;p&gt; Il est l’auteur de trois ouvrages majeurs :  &lt;a href="https://philosophie.ac-normandie.fr/spip.php?article148" title="qu’est ce que la philosophie par françois Wahl "&gt;Qu’est-ce que le structuralisme ? &lt;/a&gt;, Philosophie (1973), Introduction au discours du tableau (1996) et Le Perçu (2007). Dans Introduction au discours du tableau, il étudie les œuvres de Poussin, Memling ou Bellini pour montrer que le « visible » apparaît sous deux espèces : le paysage et le tableau, articulant ainsi esthétique et théorie du signe. Le Perçu propose une exploration critique des phénoménologies du XXᵉ siècle, en mobilisant les concepts de discours, sujet, désir et énoncé pour formaliser une analyse du « fait esthétique ». &lt;/p&gt; &lt;p&gt; La ligne directrice de sa pensée peut se résumer à un repérage du concept de sujet dans la philosophie contemporaine et son introduction dans le champ de l’esthétique. Il a écrit de nombreux articles discutant les œuvres d’auteurs comme Badiou, Bataille, Barthes, Foucault ou Lacan, et son dernier grand livre, La dissidence du sujet, rassemble ces réflexions sur le sujet, le désir et le discours dans la philosophie et l’art. &lt;/p&gt; &lt;audio controls title="les fluides d’Aristote /hommage à f Wahl par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/12003-17.09.2014-ITEMA_20670365-2014C18006S0260-21.mp3" type="audio/mpeg" align="center"&gt;&lt;/audio&gt;  </t>
         </is>
       </c>
       <c r="F110" s="57" t="n"/>
@@ -7907,8 +7898,7 @@
       </c>
       <c r="E117" s="59" t="inlineStr">
         <is>
-          <t>&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Jacques_Derrida"  title=" Wikipedia"&gt;Jacques DERRIDA&lt;/a&gt; était un philosophe français, né en Algérie, connu pour avoir développé le  &lt;a href="https://www.youtube.com/watch?v=5-fZwLNIB9M" style="color:#88A1E9" title=" La Déconstruction - DERRIDA par EXHAL"&gt;Déconstructionnisme&lt;/a&gt;. C 'est une stratégie de lecture critique qui vise à déconstruire les oppositions binaires (par exemple, parole/écriture, homme/femme) qui structurent la pensée occidentale. Elle met en lumière l'instabilité et l'indécidabilité inhérentes au langage et aux textes. Elle révèle comment les textes contiennent en eux-mêmes les forces qui minent leurs propres affirmations et significations apparentes. Voici ses oeuvres majeures :&lt;/p&gt; &lt;p&gt; - De la grammatologie : Un texte fondamental où il critique le logocentrisme (la primauté accordée à la parole sur l'écriture dans la pensée occidentale). &lt;/p&gt; &lt;p&gt;
-- L'Écriture et la différence : Recueil d'essais appliquant la déconstruction à divers auteurs et concepts. &lt;/p&gt; &lt;p&gt; - La Voix et le phénomène : Une critique de la phénoménologie de Husserl. &lt;/p&gt; &lt;p&gt; - Marges de la philosophie : Un autre recueil d'essais explorant les marges de la philosophie. &lt;/p&gt; &lt;p&gt; - Glas : Une œuvre plus expérimentale juxtaposant des réflexions sur Hegel et Genet. &lt;/p&gt; &lt;p&gt;  -  &lt;a href="https://fr.wikipedia.org/wiki/Spectres_de_Marx"  title="Spectres de Marx par Wikipedia"&gt;Spectres de Marx&lt;/a&gt;  : Une réflexion sur l'héritage de Marx après la chute du mur de Berlin. &lt;/p&gt; &lt;p&gt; -  &lt;a href="https://www.youtube.com/watch?v=sIMjxDbFK7E" title=" Jacques Derrida - Entretiens à propos de ses livres "Apories" et "Résistance de la psychanalyse" par Artesquieu"&gt;Aporie&lt;/a&gt; : Essai aborde les questions que soulèvent aussi bien le projet d'une histoire culturelle ou d'une anthropologie de la mort. &lt;/p&gt; &lt;p&gt; Il a marqué la pensée contemporaine par sa déconstruction des concepts fondamentaux de la philosophie occidentale et son exploration de la complexité du langage et du sens. C'est une   &lt;a href="https://www.youtube.com/watch?v=n_JqaGhpZ7s" title=" décès de Jacques DERRDA par INA Politique"&gt;figure incontournable&lt;/a&gt; pour comprendre les développements intellectuels de la fin du XXe siècle. &lt;/p&gt;   &lt;audio controls title="Jacques Derrida, le déconstructionniste par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/10351-14.12.1998-ITEMA_23647145-1998C3500E0186-21.mp3" type="audio/mpeg" align="center"&gt;&lt;/audio&gt;  &lt;</t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Jacques_Derrida"  title=" Wikipedia"&gt;Jacques DERRIDA&lt;/a&gt; était un philosophe français, né en Algérie, connu pour avoir développé le  &lt;a href="https://www.youtube.com/watch?v=5-fZwLNIB9M" style="color:#88A1E9" title=" La Déconstruction - DERRIDA par EXHAL"&gt;Déconstructionnisme&lt;/a&gt;. C 'est une stratégie de lecture critique qui vise à déconstruire les oppositions binaires (par exemple, parole/écriture, homme/femme) qui structurent la pensée occidentale. Elle met en lumière l'instabilité et l'indécidabilité inhérentes au langage et aux textes. Elle révèle comment les textes contiennent en eux-mêmes les forces qui minent leurs propres affirmations et significations apparentes. &lt;/p&gt; &lt;p&gt;De la grammatologie : Un texte fondamental où il critique le logocentrisme (la primauté accordée à la parole sur l'écriture dans la pensée occidentale). &lt;/p&gt; &lt;p&gt;L'Écriture et la différence : Recueil d'essais appliquant la déconstruction à divers auteurs et concepts. &lt;/p&gt; &lt;p&gt;La Voix et le phénomène : Une critique de la phénoménologie de Husserl. &lt;/p&gt; &lt;p&gt;Marges de la philosophie : Un autre recueil d'essais explorant les marges de la philosophie. &lt;/p&gt; &lt;p&gt;Glas : Une œuvre plus expérimentale juxtaposant des réflexions sur Hegel et Genet. &lt;/p&gt; &lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Spectres_de_Marx"  title="Spectres de Marx par Wikipedia"&gt;Spectres de Marx&lt;/a&gt;  : Une réflexion sur l'héritage de Marx après la chute du mur de Berlin. &lt;/p&gt; &lt;p&gt;&lt;a href="https://www.youtube.com/watch?v=sIMjxDbFK7E" title=" Jacques Derrida - Entretiens à propos de ses livres "Apories" et "Résistance de la psychanalyse" par Artesquieu"&gt;Aporie&lt;/a&gt; : Essai aborde les questions que soulèvent aussi bien le projet d'une histoire culturelle ou d'une anthropologie de la mort. &lt;/p&gt; &lt;p&gt; Il a marqué la pensée contemporaine par sa déconstruction des concepts fondamentaux de la philosophie occidentale et son exploration de la complexité du langage et du sens. C'est une   &lt;a href="https://www.youtube.com/watch?v=n_JqaGhpZ7s" title=" décès de Jacques DERRDA par INA Politique"&gt;figure incontournable&lt;/a&gt; pour comprendre les développements intellectuels de la fin du XXe siècle. &lt;/p&gt;   &lt;audio controls title="Jacques Derrida, le déconstructionniste par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/10351-14.12.1998-ITEMA_23647145-1998C3500E0186-21.mp3" type="audio/mpeg" align="center"&gt;&lt;/audio&gt;  &lt;</t>
         </is>
       </c>
       <c r="F117" s="57" t="inlineStr">
@@ -7976,7 +7966,7 @@
       </c>
       <c r="E118" s="56" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Pierre_Bourdieu"  title=" Wikipedia"&gt;Pierre BOURDIEU&lt;/a&gt; était un philosophe et sociologue français  qui a développé un ensemble de concepts interdépendants pour analyser la structure sociale et les &lt;a href="https://www.youtube.com/watch?v=LQ6UeaV-VTs"  title=" BOURDIEU - La reproduction sociale par le Precepteur"&gt;pratiques des individus&lt;/a&gt;. Parmi les plus importants, on trouve : &lt;/p&gt;&lt;p&gt; -    - Le champ : Il s'agit d'un espace social structuré, doté de ses propres règles, enjeux et formes de capital spécifiques (champ politique, économique, artistique,  universitaire, etc). Les agents sociaux y luttent pour la domination et l'accumulation de capital. &lt;/p&gt; &lt;p&gt; - Le capital : Il distingue plusieurs formes de capital qui confèrent du pouvoir et des avantages (capital économique, culturel, social et symbolique). &lt;/p&gt; &lt;p&gt; - &lt;a href="https://www.youtube.com/watch?v=c67GEYsM2yA" title=" BOURDIEU - L'habitus par Cyrus North"&gt;L'habitus&lt;/a&gt; : C'est un système de dispositions durables et transposables, des manières de percevoir, de penser et d'agir que les individus acquièrent par leur socialisation, notamment au sein de leur classe sociale et de leur trajectoire.  &lt;/p&gt; &lt;p&gt; - La violence symbolique : C'est une forme de domination douce, invisible et souvent acceptée par les dominés. Elle s'exerce notamment par l'imposition de catégories de pensée et de perception légitimes qui favorisent les dominants. Un exemple classique est la domination masculine. &lt;/p&gt; &lt;p&gt; - &lt;a href="https://www.youtube.com/watch?v=9UPoOcMhE9g" title=" La Doxa par Philo1492"&gt;La doxa&lt;/a&gt; : Ensemble des croyances fondamentales, non questionnées, qui sont au fondement d'un champ social et qui apparaissent comme naturelles et évidentes pour les agents qui y évoluent. &lt;/p&gt; &lt;p&gt; Il a offert une critique novatrice des approches dualistes en sociologie (comme l'opposition entre l'individu et la société, ou entre la structure et l'agent). Sa théorie de l'habitus et du champ vise à dépasser ces oppositions en montrant comment les structures sociales sont incorporées par les individus et comment ces individus agissent au sein de ces structures. &lt;/p&gt; &lt;audio controls title="Qu'est-ce que Pierre Bourdieu a changé ? par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/22789-09.05.2022-ITEMA_23020195-2022C45516S0129-21.mp3" type="audio/mpeg" align="center"&gt;&lt;/audio&gt;  </t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Pierre_Bourdieu"  title=" Wikipedia"&gt;Pierre BOURDIEU&lt;/a&gt; était un philosophe et sociologue français  qui a développé un ensemble de concepts interdépendants pour analyser la structure sociale et les &lt;a href="https://www.youtube.com/watch?v=LQ6UeaV-VTs"  title=" BOURDIEU - La reproduction sociale par le Precepteur"&gt;pratiques des individus&lt;/a&gt;. Parmi les plus importants, on trouve : &lt;/p&gt;&lt;p&gt;Le champ : Il s'agit d'un espace social structuré, doté de ses propres règles, enjeux et formes de capital spécifiques (champ politique, économique, artistique,  universitaire, etc). Les agents sociaux y luttent pour la domination et l'accumulation de capital. &lt;/p&gt; &lt;p&gt;Le capital : Il distingue plusieurs formes de capital qui confèrent du pouvoir et des avantages (capital économique, culturel, social et symbolique). &lt;/p&gt; &lt;p&gt;&lt;a href="https://www.youtube.com/watch?v=c67GEYsM2yA" title=" BOURDIEU - L'habitus par Cyrus North"&gt;L'habitus&lt;/a&gt; : C'est un système de dispositions durables et transposables, des manières de percevoir, de penser et d'agir que les individus acquièrent par leur socialisation, notamment au sein de leur classe sociale et de leur trajectoire.  &lt;/p&gt; &lt;p&gt;La violence symbolique : C'est une forme de domination douce, invisible et souvent acceptée par les dominés. Elle s'exerce notamment par l'imposition de catégories de pensée et de perception légitimes qui favorisent les dominants. Un exemple classique est la domination masculine. &lt;/p&gt; &lt;p&gt;&lt;a href="https://www.youtube.com/watch?v=9UPoOcMhE9g" title=" La Doxa par Philo1492"&gt;La doxa&lt;/a&gt; : Ensemble des croyances fondamentales, non questionnées, qui sont au fondement d'un champ social et qui apparaissent comme naturelles et évidentes pour les agents qui y évoluent. &lt;/p&gt; &lt;p&gt; Il a offert une critique novatrice des approches dualistes en sociologie (comme l'opposition entre l'individu et la société, ou entre la structure et l'agent). Sa théorie de l'habitus et du champ vise à dépasser ces oppositions en montrant comment les structures sociales sont incorporées par les individus et comment ces individus agissent au sein de ces structures. &lt;/p&gt; &lt;audio controls title="Qu'est-ce que Pierre Bourdieu a changé ? par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/22789-09.05.2022-ITEMA_23020195-2022C45516S0129-21.mp3" type="audio/mpeg" align="center"&gt;&lt;/audio&gt;  </t>
         </is>
       </c>
       <c r="F118" s="54" t="inlineStr">
@@ -8522,7 +8512,7 @@
       </c>
       <c r="E127" s="48" t="inlineStr">
         <is>
-          <t xml:space="preserve"> &lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Michel_Hulin"  title=" Wikipedia"&gt;Michel HULIN&lt;/a&gt; était un philosophe français récemment décédé, grand spécialiste de la &lt;a href="https://www.youtube.com/watch?v=tJFic9y58Sc" title=" Aperçu de l’hindouisme avec Michel Hulin par Resonances "&gt;philosophie indienne &lt;/a&gt; et de la comparaison entre pensée européenne et pensée asiatique, notamment de l’Advaïta Vedānta, le courant « non‑dualiste » du vedānta. Longtemps professeur de philosophie indienne et comparée à l’université Paris‑Sorbonne, il a joué un rôle central dans la diffusion en France des grandes écoles de pensée de l’Inde. Sa carrière s’est accompagnée d’un important travail de traduction du sanskrit et de vulgarisation, accessible à un public non spécialiste. &lt;/p&gt; &lt;p&gt; Ses recherches portent d’une part sur  &lt;a href="https://www.youtube.com/watch?v=kaJP8yDwHeY" title=" For intérieur par Resonnances "&gt;la pensée indienne classique &lt;/a&gt;  (notion d’ahamkāra, textes vedāntins et shivaïtes d’inspiration tantrique), d’autre part sur les questions épistémologiques et métaphysiques que soulève la rencontre entre les traditions européennes et asiatiques. Dans sa thèse, Le Principe de l’ego dans la pensée indienne classique, il analyse la notion de « faux moi » et montre comment elle éclaire notre expérience ordinaire de la conscience. Il s’intéresse également à la question du temps, de l’éternité et des expériences dites mystiques, qu’il relie à des vécus très concrets. &lt;/p&gt; &lt;p&gt; Dans des ouvrages comme La Face cachée du temps, La Mystique sauvage, Hegel et l’Orient, Shankara et la non‑dualité ou encore l’anthologie L’Inde des sages, il  conjugue une érudition très précise et un style volontairement clair. Il montre comment des interrogations métaphysiques complexes – sur le moi, le temps, l’au‑delà ou l’expérience spirituelle – touchent directement la vie intérieure de chacun. Par son enseignement et ses livres, il a contribué à installer durablement en France une philosophie comparée attentive au dialogue entre Europe et Inde. &lt;p&gt; &lt;/p&gt;&lt;audio controls title="  Philosophies indiennes (1/4) : Upanishads, les textes fondateurs ?  par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/10467-16.12.2013-ITEMA_20562153-2013C12410S0350-NET_FC_A092AF0E-5BC1-49EE-A72F-E62BB6A2A8B1-21.mp3" type="audio/mpeg" align="center"&gt;&lt;/audio&gt;  &lt;p&gt;  &lt;/p&gt;
+          <t xml:space="preserve"> &lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Michel_Hulin"  title=" Wikipedia"&gt;Michel HULIN&lt;/a&gt; était un philosophe français récemment décédé, grand spécialiste de la &lt;a href="https://www.youtube.com/watch?v=tJFic9y58Sc" title=" Aperçu de l’hindouisme avec Michel Hulin par Resonances "&gt;philosophie indienne &lt;/a&gt; et de la comparaison entre pensée européenne et pensée asiatique, notamment de l’Advaïta Vedānta, le courant « non‑dualiste » du vedānta. Longtemps professeur de philosophie indienne et comparée à l’université Paris‑Sorbonne, il a joué un rôle central dans la diffusion en France des grandes écoles de pensée de l’Inde. Sa carrière s’est accompagnée d’un important travail de traduction du sanskrit et de vulgarisation, accessible à un public non spécialiste. &lt;/p&gt; &lt;p&gt; Ses recherches portent d’une part sur  &lt;a href="https://www.youtube.com/watch?v=kaJP8yDwHeY" title=" For intérieur par Resonnances "&gt;la pensée indienne classique &lt;/a&gt;  (notion d’ahamkāra, textes vedāntins et shivaïtes d’inspiration tantrique), d’autre part sur les questions épistémologiques et métaphysiques que soulève la rencontre entre les traditions européennes et asiatiques. Dans sa thèse, Le Principe de l’ego dans la pensée indienne classique, il analyse la notion de « faux moi » et montre comment elle éclaire notre expérience ordinaire de la conscience. Il s’intéresse également à la question du temps, de l’éternité et des expériences dites mystiques, qu’il relie à des vécus très concrets. &lt;/p&gt; &lt;p&gt; Dans des ouvrages comme La Face cachée du temps, La Mystique sauvage, Hegel et l’Orient, Shankara et la non‑dualité ou encore l’anthologie L’Inde des sages, il  conjugue une érudition très précise et un style volontairement clair. Il montre comment des interrogations métaphysiques complexes – sur le moi, le temps, l’au‑delà ou l’expérience spirituelle – touchent directement la vie intérieure de chacun. Par son enseignement et ses livres, il a contribué à installer durablement en France une philosophie comparée attentive au dialogue entre Europe et Inde. &lt;audio controls title="  Philosophies indiennes (1/4) : Upanishads, les textes fondateurs ?  par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/10467-16.12.2013-ITEMA_20562153-2013C12410S0350-NET_FC_A092AF0E-5BC1-49EE-A72F-E62BB6A2A8B1-21.mp3" type="audio/mpeg" align="center"&gt;&lt;/audio&gt;  
 </t>
         </is>
       </c>
@@ -8643,7 +8633,7 @@
       </c>
       <c r="E129" s="62" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Cl%C3%A9ment_Rosset" title=" Wikipedia"&gt;Clément ROSSET&lt;/a&gt; était un philosophe français connu pour sa pensée radicale et son style d'écriture d'une grande clarté. Son œuvre est principalement centrée sur le concept du  &lt;a href="https://www.youtube.com/watch?v=I50Jbj6uQEU" title="Clément Rosset : la réalité ne convient pas ! par Kosmos"&gt;"réel"&lt;/a&gt;  et l'incapacité ou la difficulté de l'homme à l'accepter dans sa singularité et souvent sa cruauté. Voici les points essentiels concernant sa philosophie : &lt;/p&gt; &lt;p&gt; - &lt;a href="https://www.youtube.com/watch?v=8m_kXVBdtwg"  title=" Le réel et son double, Clément Rosset, 2.2 avant-propos par Thibault BELZACQ"&gt;Le Réel sans double&lt;/a&gt; : Son idée maîtresse est que le réel est unique, singulier et dépourvu de tout "double". Il n'y a pas d'arrière-monde, pas de sens caché, pas de consolation ou d'illusion qui puisse atténuer sa nature brute. Le réel est simplement ce qui est, dans son évidence la plus nue. &lt;/p&gt; &lt;p&gt; - Le Refus du double et de l'illusion : Une grande partie de son travail consiste à traquer les différentes formes d'illusions et de doubles que l'humanité crée pour  &lt;a href="https://philitt.fr/2023/09/12/clement-rosset-tout-est-sans-raison/"  title="Clément Rosset : tout est sans raison par Phillitt"&gt;échapper à la confrontation&lt;/a&gt; directe avec le réel. Ces doubles peuvent être d'ordre métaphysique, moral, psychologique, ou même esthétique.&lt;/p&gt; &lt;p&gt; - &lt;a href="https://www.youtube.com/watch?v=JDcudFE_uBQ"  title="Entretien avec Pierre Dumayet (1961) par Archives"&gt;Philosophie tragique&lt;/a&gt; et Joie : Bien que sa pensée puisse sembler sombre en insistant sur la cruauté et l'absurdité du réel, il développe une philosophie que l'on qualifie souvent de "tragique" au sens nietzschéen du terme. Il ne s'agit pas de désespoir, mais plutôt de l'affirmation de la vie et du réel tels qu'ils sont, y compris dans leurs aspects les plus difficiles. &lt;/p&gt; &lt;p&gt; Il est également remarquable par son style d'écriture. Loin du jargon philosophique abscons, il privilégie une langue simple, directe et percutante. Cette clarté formelle est au service de la clarté de sa pensée, cherchant à énoncer le réel avec le moins d'interférences possible. Son œuvre, bien que parfois restée en marge des courants universitaires dominants, a marqué par sa radicalité, sa lucidité et sa défense d'une confrontation sans fard avec le réel.  &lt;/p&gt; &lt;audio controls title="Clément Rosset par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/10080-20.12.2013-ITEMA_20564152-2013C3403E0215-21.mp3" type="audio/mpeg" align="center"&gt;&lt;/audio&gt;  </t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Cl%C3%A9ment_Rosset" title=" Wikipedia"&gt;Clément ROSSET&lt;/a&gt; était un philosophe français connu pour sa pensée radicale et son style d'écriture d'une grande clarté. Son œuvre est principalement centrée sur le concept du  &lt;a href="https://www.youtube.com/watch?v=I50Jbj6uQEU" title="Clément Rosset : la réalité ne convient pas ! par Kosmos"&gt;"réel"&lt;/a&gt;  et l'incapacité ou la difficulté de l'homme à l'accepter dans sa singularité et souvent sa cruauté. &lt;/p&gt; &lt;p&gt;&lt;a href="https://www.youtube.com/watch?v=8m_kXVBdtwg"  title=" Le réel et son double, Clément Rosset, 2.2 avant-propos par Thibault BELZACQ"&gt;Le Réel sans double&lt;/a&gt; : Son idée maîtresse est que le réel est unique, singulier et dépourvu de tout "double". Il n'y a pas d'arrière-monde, pas de sens caché, pas de consolation ou d'illusion qui puisse atténuer sa nature brute. Le réel est simplement ce qui est, dans son évidence la plus nue. &lt;/p&gt; &lt;p&gt;Le Refus du double et de l'illusion : Une grande partie de son travail consiste à traquer les différentes formes d'illusions et de doubles que l'humanité crée pour  &lt;a href="https://philitt.fr/2023/09/12/clement-rosset-tout-est-sans-raison/"  title="Clément Rosset : tout est sans raison par Phillitt"&gt;échapper à la confrontation&lt;/a&gt; directe avec le réel. Ces doubles peuvent être d'ordre métaphysique, moral, psychologique, ou même esthétique.&lt;/p&gt; &lt;p&gt;&lt;a href="https://www.youtube.com/watch?v=JDcudFE_uBQ"  title="Entretien avec Pierre Dumayet (1961) par Archives"&gt;Philosophie tragique&lt;/a&gt; et Joie : Bien que sa pensée puisse sembler sombre en insistant sur la cruauté et l'absurdité du réel, il développe une philosophie que l'on qualifie souvent de "tragique" au sens nietzschéen du terme. Il ne s'agit pas de désespoir, mais plutôt de l'affirmation de la vie et du réel tels qu'ils sont, y compris dans leurs aspects les plus difficiles. &lt;/p&gt; &lt;p&gt; Il est également remarquable par son style d'écriture. Loin du jargon philosophique abscons, il privilégie une langue simple, directe et percutante. Cette clarté formelle est au service de la clarté de sa pensée, cherchant à énoncer le réel avec le moins d'interférences possible. Son œuvre, bien que parfois restée en marge des courants universitaires dominants, a marqué par sa radicalité, sa lucidité et sa défense d'une confrontation sans fard avec le réel.  &lt;/p&gt; &lt;audio controls title="Clément Rosset par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/10080-20.12.2013-ITEMA_20564152-2013C3403E0215-21.mp3" type="audio/mpeg" align="center"&gt;&lt;/audio&gt;  </t>
         </is>
       </c>
       <c r="F129" s="54" t="inlineStr">
@@ -8821,7 +8811,7 @@
       </c>
       <c r="E132" s="62" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Philippe_Lacoue-Labarthe"  title=" Wikipedia"&gt;Philippe LACOUE-LABARTHE&lt;/a&gt; était un philosophe, critique littéraire, traducteur et théoricien français né à Tours et connu pour ses travaux sur la mimésis, le romantisme allemand, Hölderlin, Heidegger, Derrida et la relation entre esthétique et politique. Il a aussi beaucoup compté dans le milieu intellectuel de Strasbourg, où il a enseigné longtemps et travaillé avec Jean-Luc Nancy. &lt;/p&gt; &lt;p&gt; Son  &lt;a href="https://maitron.fr/lacoue-labarthe-philippe/"  title=" lacoue-labarthe par le maitron"&gt;œuvre interroge &lt;/a&gt; la façon dont l’art, la philosophie et la politique s’entrecroisent, notamment à travers la notion de mimésis et la critique de l’“esthétisation du politique”. Il a aussi travaillé sur le romantisme allemand et sur la réception de Hölderlin, qu’il considérait comme une figure majeure. &lt;/p&gt; &lt;p&gt; Parmi les livres souvent cités, on trouve Le Titre de la lettre avec Jean-Luc Nancy, L’Absolu littéraire, L’Imitation des modernes, La Fiction du politique et Heidegger, la politique du poème. Il a également traduit plusieurs auteurs allemands majeurs, dont Heidegger, Hölderlin, Nietzsche, Benjamin et Celan. &lt;/p&gt; &lt;p&gt; Sa pensée tourne autour de trois idées principales : - La représentation n’est jamais transparente : ce que nous montrons, racontons ou jouons n’est jamais la réalité elle-même, mais une forme, un masque, une imitation. - La littérature et le théâtre sont essentiels pour comprendre la philosophie, parce qu’ils révèlent ce que les concepts cachent ou simplifient.popups. - Le lien entre esthétique et politique est dangereux : il a beaucoup réfléchi à la manière dont l’art, les mythes et les images peuvent servir le politique, y compris dans des formes fascisantes. &lt;/p&gt; 
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Philippe_Lacoue-Labarthe"  title=" Wikipedia"&gt;Philippe LACOUE-LABARTHE&lt;/a&gt; était un philosophe, critique littéraire, traducteur et théoricien français né à Tours et connu pour ses travaux sur la mimésis, le romantisme allemand, Hölderlin, Heidegger, Derrida et la relation entre esthétique et politique. Il a aussi beaucoup compté dans le milieu intellectuel de Strasbourg, où il a enseigné longtemps et travaillé avec Jean-Luc Nancy. &lt;/p&gt; &lt;p&gt; Son  &lt;a href="https://maitron.fr/lacoue-labarthe-philippe/"  title=" lacoue-labarthe par le maitron"&gt;œuvre interroge &lt;/a&gt; la façon dont l’art, la philosophie et la politique s’entrecroisent, notamment à travers la notion de mimésis et la critique de l’“esthétisation du politique”. Il a aussi travaillé sur le romantisme allemand et sur la réception de Hölderlin, qu’il considérait comme une figure majeure. &lt;/p&gt; &lt;p&gt; Parmi les livres souvent cités, on trouve Le Titre de la lettre avec Jean-Luc Nancy, L’Absolu littéraire, L’Imitation des modernes, La Fiction du politique et Heidegger, la politique du poème. Il a également traduit plusieurs auteurs allemands majeurs, dont Heidegger, Hölderlin, Nietzsche, Benjamin et Celan. &lt;/p&gt; &lt;p&gt; Sa pensée tourne autour de trois idées principales : La représentation n’est jamais transparente : ce que nous montrons, racontons ou jouons n’est jamais la réalité elle-même, mais une forme, un masque, une imitation. La littérature et le théâtre sont essentiels pour comprendre la philosophie, parce qu’ils révèlent ce que les concepts cachent ou simplifient.popups. Le lien entre esthétique et politique est dangereux : il a beaucoup réfléchi à la manière dont l’art, les mythes et les images peuvent servir le politique, y compris dans des formes fascisantes. &lt;/p&gt; 
  &lt;audio controls title="les versions de philippe lacoue labarthe par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/16409-16.03.2007-ITEMA_20062386-2007C6409S0011-MEM_000036772_RF-21.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;  </t>
         </is>
       </c>
@@ -8942,7 +8932,7 @@
       </c>
       <c r="E134" s="63" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Dominique_Lecourt" title=" Wikipedia"&gt;Dominique LECOURT&lt;/a&gt; était un philosophe français connu pour ses travaux en philosophie des sciences et pour avoir prolongé, de manière originale, l’héritage de Gaston Bachelard et de Georges Canguilhem. Sa philosophie se déploie autour de la philosophie des sciences, des rapports entre savoir et pouvoir, et d’une réflexion éthique et politique sur la technoscience. &lt;/p&gt; &lt;p&gt; Disciple de Bachelard, il défend un "rationalisme appliqué" : la raison scientifique n’est pas une abstraction pure, mais une activité qui se confronte à des obstacles, des erreurs, des idéologies, et qui progresse en les surmontant. Dans cet esprit, il insiste sur le rôle des   &lt;a href="https://www.youtube.com/watch?v=YyntmVUC1wE"  title=" D Lecourt par booksmag"&gt;"obstacles épistémologiques" &lt;/a&gt;  qui déroutent la recherche et qu’il faut analyser pour comprendre les progrès de la science. Il montre aussi que l’imagination n’est pas l’ennemie de la science : elle est indispensable à l’invention scientifique autant qu’à la rigueur des démonstrations. &lt;/p&gt; &lt;p&gt; Il cherche à contrer à la fois  l’"arrogance du scientisme"  et la technophobie ou le catastrophisme qui voient dans la technique uniquement une menace. Pour lui, la philosophie des sciences doit donner les moyens de penser la puissance des technosciences sans la sacraliser ni la diaboliser. Cela implique un dialogue étroit avec les scientifiques, mais aussi avec les juristes, médecins, sociologues, responsables politiques, pour éclairer les choix collectifs. &lt;/p&gt; &lt;p&gt; Il développe une conception de la liberté qui refuse aussi bien l’individualisme égoïste que le "moralisme libertaire". La liberté, pour lui, se joue dans le rapport aux savoirs et aux techniques : il s’agit d’en faire des instruments d’émancipation plutôt que de domination.&lt;/p&gt; &lt;p&gt; Parmi ses nombreux livres (plus d’une trentaine), on peut citer : -"Lyssenko, histoire réelle d’une "science prolétarienne" : analyse de la manipulation politique de la biologie en URSS.  - "L’Amérique entre la Bible et Darwin" : sur les tensions entre science et religion aux États‑Unis. - "Contre la peur" : proposition d’une éthique de la recherche qui affirme la valeur de l’esprit critique face aux discours alarmistes. -  &lt;a href="https://www.youtube.com/watch?v=3e2K5Ogywl4"  title=" De quoi le transhumanisme est-il le nom ? par Editions M-Editer"&gt;"Humain post‑humain" &lt;/a&gt;  : réflexion sur les promesses et les dangers du transhumanisme. &lt;/p&gt;   &lt;audio controls title="L'age de la peur par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/10075-03.03.2010-ITEMA_20218172-2010C6608S0062-NET_E99ABA70-9EA1-4399-B0F4-9460EA040C60-21.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;  </t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Dominique_Lecourt" title=" Wikipedia"&gt;Dominique LECOURT&lt;/a&gt; était un philosophe français connu pour ses travaux en philosophie des sciences et pour avoir prolongé, de manière originale, l’héritage de Gaston Bachelard et de Georges Canguilhem. Sa philosophie se déploie autour de la philosophie des sciences, des rapports entre savoir et pouvoir, et d’une réflexion éthique et politique sur la technoscience. &lt;/p&gt; &lt;p&gt; Disciple de Bachelard, il défend un "rationalisme appliqué" : la raison scientifique n’est pas une abstraction pure, mais une activité qui se confronte à des obstacles, des erreurs, des idéologies, et qui progresse en les surmontant. Dans cet esprit, il insiste sur le rôle des   &lt;a href="https://www.youtube.com/watch?v=YyntmVUC1wE"  title=" D Lecourt par booksmag"&gt;"obstacles épistémologiques" &lt;/a&gt;  qui déroutent la recherche et qu’il faut analyser pour comprendre les progrès de la science. Il montre aussi que l’imagination n’est pas l’ennemie de la science : elle est indispensable à l’invention scientifique autant qu’à la rigueur des démonstrations. &lt;/p&gt; &lt;p&gt; Il cherche à contrer à la fois  l’"arrogance du scientisme"  et la technophobie ou le catastrophisme qui voient dans la technique uniquement une menace. Pour lui, la philosophie des sciences doit donner les moyens de penser la puissance des technosciences sans la sacraliser ni la diaboliser. Cela implique un dialogue étroit avec les scientifiques, mais aussi avec les juristes, médecins, sociologues, responsables politiques, pour éclairer les choix collectifs. &lt;/p&gt; &lt;p&gt; Il développe une conception de la liberté qui refuse aussi bien l’individualisme égoïste que le "moralisme libertaire". La liberté, pour lui, se joue dans le rapport aux savoirs et aux techniques : il s’agit d’en faire des instruments d’émancipation plutôt que de domination.&lt;/p&gt; &lt;p&gt; Parmi ses nombreux livres (plus d’une trentaine), on peut citer : -"Lyssenko, histoire réelle d’une "science prolétarienne" : analyse de la manipulation politique de la biologie en URSS. "L’Amérique entre la Bible et Darwin" : sur les tensions entre science et religion aux États‑Unis. "Contre la peur" : proposition d’une éthique de la recherche qui affirme la valeur de l’esprit critique face aux discours alarmistes. &lt;a href="https://www.youtube.com/watch?v=3e2K5Ogywl4"  title=" De quoi le transhumanisme est-il le nom ? par Editions M-Editer"&gt;"Humain post‑humain" &lt;/a&gt;  : réflexion sur les promesses et les dangers du transhumanisme. &lt;/p&gt;   &lt;audio controls title="L'age de la peur par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/10075-03.03.2010-ITEMA_20218172-2010C6608S0062-NET_E99ABA70-9EA1-4399-B0F4-9460EA040C60-21.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;  </t>
         </is>
       </c>
       <c r="F134" s="54" t="inlineStr">

--- a/data/frise-philosophes-france.xlsx
+++ b/data/frise-philosophes-france.xlsx
@@ -4363,7 +4363,7 @@
       <c r="E59" s="61" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Jean_Wahl"  title=" Wikipedia"&gt;Jean WAHL&lt;/a&gt; était un philosophe français,  professeur à la Sorbonne, il joua un rôle capital dans la réception des philosophies étrangères en France — Kierkegaard, Hegel, Heidegger, Whitehead, la philosophie américaine — et fonda en 1946 &lt;a href="https://www.en-attendant-nadeau.fr/2017/05/09/paris-philosophes-22-wahl/"  title="
-Paris des philosophes par en attendant nadeau"&gt;le Collège philosophique, &lt;/a&gt;  institution unique qui donna pendant trente ans une tribune aux philosophes du monde entier à Paris. &lt;/p&gt; &lt;p&gt; Sa thèse sur &lt;em&gt;Le Malheur de la conscience dans la philosophie de Hegel&lt;/em&gt; (1929) est un texte fondateur de la lecture existentialiste de Hegel en France : en mettant en lumière la dialectique de la conscience malheureuse dans la &lt;em&gt;Phénoménologie de l'Esprit&lt;/em&gt;, il  &lt;a href="https://www.youtube.com/watch?v=5lqhtfDxEQU/"  title="jean wahl god is the horizon of all conscious par spiritual quest "&gt;contribua décisivement &lt;/a&gt;  à orienter la réception française de Hegel vers les thématiques de l'existence, de la finitude et de la transcendance. Cette lecture influença profondément Sartre, Bataille et Merleau-Ponty. &lt;/p&gt; &lt;p&gt; Arrêté par les nazis en 1941 et interné à Drancy, il réussit à s'évader et à rejoindre les États-Unis où il enseigna jusqu'à la Libération. Cette expérience nourrit sa réflexion sur l'existence, la finitude et la transcendance. Dans sa &lt;em&gt;Traité de métaphysique&lt;/em&gt; (1953) et dans ses recueils poétiques — car il était aussi poète — il chercha à articuler l'expérience du tragique et de la joie dans une philosophie de la « trans-ascendance ». Homme de dialogue exceptionnel, il fut le passeur entre les grandes traditions philosophiques européenne et américaine. &lt;/p&gt;   &lt;audio controls title="le silence mystique est il à préserver par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/13915-16.02.2025-ITEMA_24030781-2025C3372E0048-NET_MFC_12794E2E-D0EA-4790-855D-484CC4309EF5-21-27aca72b8ab79e623b51c3b6c79e4d8f.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt; </t>
+Paris des philosophes par en attendant nadeau"&gt;le Collège philosophique, &lt;/a&gt;  institution unique qui donna pendant trente ans une tribune aux philosophes du monde entier à Paris. &lt;/p&gt; &lt;p&gt; Sa thèse sur &lt;em&gt;Le Malheur de la conscience dans la philosophie de Hegel&lt;/em&gt; (1929) est un texte fondateur de la lecture existentialiste de Hegel en France : en mettant en lumière la dialectique de la conscience malheureuse dans la &lt;em&gt;Phénoménologie de l'Esprit&lt;/em&gt;, il  &lt;a href="https://www.youtube.com/watch?v=5lqhtfDxEQU"  title="jean wahl god is the horizon of all conscious par spiritual quest "&gt;contribua décisivement &lt;/a&gt;  à orienter la réception française de Hegel vers les thématiques de l'existence, de la finitude et de la transcendance. Cette lecture influença profondément Sartre, Bataille et Merleau-Ponty. &lt;/p&gt; &lt;p&gt; Arrêté par les nazis en 1941 et interné à Drancy, il réussit à s'évader et à rejoindre les États-Unis où il enseigna jusqu'à la Libération. Cette expérience nourrit sa réflexion sur l'existence, la finitude et la transcendance. Dans sa &lt;em&gt;Traité de métaphysique&lt;/em&gt; (1953) et dans ses recueils poétiques — car il était aussi poète — il chercha à articuler l'expérience du tragique et de la joie dans une philosophie de la « trans-ascendance ». Homme de dialogue exceptionnel, il fut le passeur entre les grandes traditions philosophiques européenne et américaine. &lt;/p&gt;   &lt;audio controls title="le silence mystique est il à préserver par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/13915-16.02.2025-ITEMA_24030781-2025C3372E0048-NET_MFC_12794E2E-D0EA-4790-855D-484CC4309EF5-21-27aca72b8ab79e623b51c3b6c79e4d8f.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt; </t>
         </is>
       </c>
       <c r="F59" s="60" t="inlineStr">
@@ -6753,7 +6753,7 @@
       </c>
       <c r="E98" s="62" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Jules_Vuillemin"  title=" Wikipedia"&gt;Jules VUILLEMIN&lt;/a&gt;  était un philosophe français qui  s'est distingué par son travail en  &lt;a href="https://hal.science/hal-04409311v1/document" title="Jules Vuillemin, philosdophie analytique contrarié par hal"&gt;philosophie analytique&lt;/a&gt;, en épistémologie et en histoire de la philosophie.  Il diffuse en France les idées de Bertrand Russell, Rudolf Carnap et Willard Van Orman Quine, influençant des penseurs comme Jacques Bouveresse. Ses débuts touchent à  &lt;a href="https://lafrancebyzantine.blogspot.com/2016/09/jules-vuillemin-t-il-ete-existentialiste.html"  title="Jules Vuillemin at'il été existantialiste? par lafrancebyzantine"&gt;l'existentialisme &lt;/a&gt; et au marxisme, mais il évolue vers un rationalisme rigoureux, rejetant les excès de Sartre ou Heidegger. &lt;/p&gt; &lt;p&gt; Ses œuvres majeures : "Nécessité ou contingence" paru en 1984, qui analyse les systèmes philosophiques par une approche logique et historique, et "La philosophie de l'algèbre" paru en 1962 ou il explore la nécessité, la contingence, la logique et les sciences, insistant sur la cohérence interne des systèmes selon l'héritage de Martial Gueroult. Épistémologue de premier plan avec Gilles Gaston Granger et René Thom, il défend une philosophie attentive aux mathématiques et à la physique. &lt;/p&gt; &lt;p&gt; Il s'intéresse à Kant, Descartes, la liberté et la métaphysique de la nature, tout en critiquant les réductions existentialistes au profit d'une raison objective. Ses archives sont conservées au Laboratoire de Philosophie et d'Histoire des Sciences à Nancy. Auteur de plus de vingt livres, il reste une figure de la rigueur philosophique française. &lt;/p&gt;</t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Jules_Vuillemin"  title=" Wikipedia"&gt;Jules VUILLEMIN&lt;/a&gt; (1920-2001) est un philosophe français, l’un de ceux qui ont fait connaître en France la &lt;a href="https://hal.science/hal-04409311v1/document" title="Jules Vuillemin, philosdophie analytique contrarié par hal"&gt;philosophie analytique&lt;/a&gt;, en particulier les œuvres de Bertrand Russell, Rudolf Carnap et Willard Van Orman Quine. Ancien élève de l’École normale supérieure, il enseigne à l’université de Clermont-Ferrand, où il fait venir Michel Foucault, puis il est élu en 1962 au Collège de France, à la chaire de philosophie de la connaissance, qu’il occupe jusqu’en 1990.&lt;/p&gt; &lt;p&gt;Ses débuts touchent à &lt;a href="https://lafrancebyzantine.blogspot.com/2016/09/jules-vuillemin-t-il-ete-existentialiste.html"  title="Jules Vuillemin at'il été existantialiste? par lafrancebyzantine"&gt;l’existentialisme&lt;/a&gt; et au marxisme, avec un &lt;em&gt;Essai sur la signification de la mort&lt;/em&gt; (1948), mais il évolue vers un rationalisme rigoureux, attentif aux mathématiques et à la physique. Héritier de Martial Gueroult, il étudie les grands systèmes dans leur cohérence interne : &lt;em&gt;Physique et métaphysique kantiennes&lt;/em&gt; (1955), &lt;em&gt;Mathématiques et métaphysique chez Descartes&lt;/em&gt; (1960), puis &lt;em&gt;La Philosophie de l’algèbre&lt;/em&gt; (1962), qui montre comment les progrès de l’algèbre ont transformé la philosophie.&lt;/p&gt; &lt;p&gt;Dans &lt;em&gt;Nécessité ou contingence&lt;/em&gt; (1984), il part d’une énigme antique de Diodore Cronos sur le possible, et montre que chaque grand système philosophique y répond en renonçant à l’une de ses prémisses, ce qui permet de classer les philosophies. Épistémologue de premier plan, comme Gilles Gaston Granger, il a marqué des penseurs comme Jacques Bouveresse. Ses archives sont conservées au Laboratoire de philosophie et d’histoire des sciences, à Nancy.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="F98" s="54" t="inlineStr">
@@ -7776,7 +7776,7 @@
       </c>
       <c r="E115" s="83" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Bernard_Bourgeois"  title=" Wikipedia"&gt;Bernard BOURGEOIS&lt;/a&gt; était un philosophes français connu comme le grand traducteur et interprète de Hegel en langue française. Ancien élève de l’École normale supérieure, agrégé de philosophie, il a enseigné à Lyon puis à Paris I–Sorbonne, avant d’être élu à l’Académie des sciences morales et politiques, qu’il a présidée en 2014. &lt;/p&gt; &lt;p&gt; Sa philosophie se définit d’abord par un  &lt;a href="https://academiesciencesmoralesetpolitiques.fr/membres-titulaires/section-i-philosophie-2/bernard-bourgeois/" title="bernard bourgeois carrière et travaux académique par académie des sciences"&gt;travail historique et philologique &lt;/a&gt;  monumental sur l’idéalisme allemand, de Kant à Marx, avec un centre de gravité hégélien. Il a traduit et annoté des milliers de pages de Hegel (Phénoménologie de l’esprit, Encyclopédie des sciences philosophiques, Science de la logique, écrits de droit naturel, textes pédagogiques), en s’efforçant de restituer la rigueur conceptuelle et la cohérence systématique de la pensée hégélienne. &lt;/p&gt; &lt;p&gt; Au-delà de la traduction, il défend une lecture de Hegel comme philosophe de la liberté et de la raison dans l’histoire. Pour lui, Hegel ne célèbre pas un destin aveugle ni une fin dogmatique de l’histoire, mais pense l’historicité de l’Esprit comme déploiement de formes de rationalité et d’institutions où la liberté devient concrète (droit, État, vie éthique). Cette orientation se retrouve dans ses communications à l’Académie, par exemple sur &lt;a href="https://www.youtube.com/watch?v=YRErwGZWBqc/" title="bernard bourgeois , hegel et le droit par pkpdlm"&gt;« Hegel et le droit » &lt;/a&gt;  ou « La fin de l’histoire selon Hegel », où il montre comment la philosophie hégélienne éclaire les problèmes politiques et juridiques modernes. &lt;/p&gt; &lt;p&gt; Sa propre philosophie n’est pas un système indépendant de type hégélien, mais une méditation exigeante sur les conditions de la rationalité spéculative et sur la manière dont la philosophie peut habiter son époque. Il insiste sur la nécessité de « relire constamment » Hegel plutôt que de le lire une fois pour toutes, parce que la pensée spéculative demande un travail continu de reprise et d’approfondissement. En ce sens, sa philosophie est une pratique de la raison qui se forme au contact des textes, des concepts et des problèmes que Hegel a portés à leur plus haute expression. &lt;/p&gt; 
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Bernard_Bourgeois"  title=" Wikipedia"&gt;Bernard BOURGEOIS&lt;/a&gt; était un philosophes français connu comme le grand traducteur et interprète de Hegel en langue française. Ancien élève de l’École normale supérieure, agrégé de philosophie, il a enseigné à Lyon puis à Paris I–Sorbonne, avant d’être élu à l’Académie des sciences morales et politiques, qu’il a présidée en 2014. &lt;/p&gt; &lt;p&gt; Sa philosophie se définit d’abord par un  &lt;a href="https://academiesciencesmoralesetpolitiques.fr/membres-titulaires/section-i-philosophie-2/bernard-bourgeois/" title="bernard bourgeois carrière et travaux académique par académie des sciences"&gt;travail historique et philologique &lt;/a&gt;  monumental sur l’idéalisme allemand, de Kant à Marx, avec un centre de gravité hégélien. Il a traduit et annoté des milliers de pages de Hegel (Phénoménologie de l’esprit, Encyclopédie des sciences philosophiques, Science de la logique, écrits de droit naturel, textes pédagogiques), en s’efforçant de restituer la rigueur conceptuelle et la cohérence systématique de la pensée hégélienne. &lt;/p&gt; &lt;p&gt; Au-delà de la traduction, il défend une lecture de Hegel comme philosophe de la liberté et de la raison dans l’histoire. Pour lui, Hegel ne célèbre pas un destin aveugle ni une fin dogmatique de l’histoire, mais pense l’historicité de l’Esprit comme déploiement de formes de rationalité et d’institutions où la liberté devient concrète (droit, État, vie éthique). Cette orientation se retrouve dans ses communications à l’Académie, par exemple sur &lt;a href="https://www.youtube.com/watch?v=YRErwGZWBqc" title="bernard bourgeois , hegel et le droit par pkpdlm"&gt;« Hegel et le droit » &lt;/a&gt;  ou « La fin de l’histoire selon Hegel », où il montre comment la philosophie hégélienne éclaire les problèmes politiques et juridiques modernes. &lt;/p&gt; &lt;p&gt; Sa propre philosophie n’est pas un système indépendant de type hégélien, mais une méditation exigeante sur les conditions de la rationalité spéculative et sur la manière dont la philosophie peut habiter son époque. Il insiste sur la nécessité de « relire constamment » Hegel plutôt que de le lire une fois pour toutes, parce que la pensée spéculative demande un travail continu de reprise et d’approfondissement. En ce sens, sa philosophie est une pratique de la raison qui se forme au contact des textes, des concepts et des problèmes que Hegel a portés à leur plus haute expression. &lt;/p&gt; 
 </t>
         </is>
       </c>
@@ -8206,7 +8206,7 @@
       </c>
       <c r="E122" s="59" t="inlineStr">
         <is>
-          <t>&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/G%C3%A9rard_Granel"  title=" Wikipedia"&gt;Gérard GRANEL&lt;/a&gt; était un philosophe français, connu pour ses traductions et commentaires des œuvres de Husserl et Heidegger, et pour ses réflexions originales sur le capitalisme contemporain et l'enseignement philosophique. Agrégé de philosophie et professeur à l'Université de Toulouse-le Mirail, il fut l'une des &lt;a href="//www.gerardgranel.com"  title=" gerard granel"&gt;figures les plus singulières &lt;/a&gt;  de la philosophie française de la seconde moitié du XXe siècle, associant une rigueur herméneutique exigeante à un engagement politique radical. &lt;/p&gt; &lt;p&gt; Ses traductions de textes fondamentaux de Husserl — notamment les &lt;em&gt;Leçons pour une phénoménologie de la conscience intime du temps&lt;/em&gt; (1964) — et de Heidegger — &lt;em&gt;Être et Temps&lt;/em&gt; (1986), traduction très discutée mais d'une grande rigueur herméneutique — constituent des apports décisifs à la diffusion de la phénoménologie en France. Dans son essai &lt;em&gt;L'Équivoque ontologique de la pensée kantienne&lt;/em&gt; (1970), il offre une interprétation originale de Kant à la lumière de la phénoménologie. &lt;/p&gt; &lt;p&gt; Dans &lt;a href="https://www.youtube.com/watch?v=DBGFMdmXgik"  title=" gerard granel apolis par Politproductions"&gt;ses essais tardifs, &lt;/a&gt; réunis notamment dans &lt;em&gt;De l'Université&lt;/em&gt; (1982) et &lt;em&gt;Traditionis traditio&lt;/em&gt; (1972), il développe une réflexion acérée sur la crise de l'université et de la transmission du savoir philosophique à l'ère capitaliste. Sa critique des formes contemporaines de la domination économique et culturelle, menée à partir des outils de la phénoménologie et du marxisme, est l'une des contributions les plus originales de sa pensée à la compréhension de la modernité. Penseur exigeant et inclassable, il garde aujourd'hui une audience fidèle parmi les philosophes français. &lt;/p&gt;</t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/G%C3%A9rard_Granel"  title=" Wikipedia"&gt;Gérard GRANEL&lt;/a&gt; était un philosophe français, connu pour ses traductions et commentaires des œuvres de Husserl et Heidegger, et pour ses réflexions originales sur le capitalisme contemporain et l'enseignement philosophique. Agrégé de philosophie et professeur à l'Université de Toulouse-le Mirail, il fut l'une des &lt;a href="https://www.gerardgranel.com"  title=" gerard granel"&gt;figures les plus singulières &lt;/a&gt;  de la philosophie française de la seconde moitié du XXe siècle, associant une rigueur herméneutique exigeante à un engagement politique radical. &lt;/p&gt; &lt;p&gt; Ses traductions de textes fondamentaux de Husserl — notamment les &lt;em&gt;Leçons pour une phénoménologie de la conscience intime du temps&lt;/em&gt; (1964) — et de Heidegger — &lt;em&gt;Être et Temps&lt;/em&gt; (1986), traduction très discutée mais d'une grande rigueur herméneutique — constituent des apports décisifs à la diffusion de la phénoménologie en France. Dans son essai &lt;em&gt;L'Équivoque ontologique de la pensée kantienne&lt;/em&gt; (1970), il offre une interprétation originale de Kant à la lumière de la phénoménologie. &lt;/p&gt; &lt;p&gt; Dans &lt;a href="https://www.youtube.com/watch?v=DBGFMdmXgik"  title=" gerard granel apolis par Politproductions"&gt;ses essais tardifs, &lt;/a&gt; réunis notamment dans &lt;em&gt;De l'Université&lt;/em&gt; (1982) et &lt;em&gt;Traditionis traditio&lt;/em&gt; (1972), il développe une réflexion acérée sur la crise de l'université et de la transmission du savoir philosophique à l'ère capitaliste. Sa critique des formes contemporaines de la domination économique et culturelle, menée à partir des outils de la phénoménologie et du marxisme, est l'une des contributions les plus originales de sa pensée à la compréhension de la modernité. Penseur exigeant et inclassable, il garde aujourd'hui une audience fidèle parmi les philosophes français. &lt;/p&gt;</t>
         </is>
       </c>
       <c r="F122" s="57" t="inlineStr">

--- a/data/frise-philosophes-france.xlsx
+++ b/data/frise-philosophes-france.xlsx
@@ -3818,8 +3818,7 @@
       </c>
       <c r="E50" s="77" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Jacques_Chevalier_(philosophe)"  title=" Wikipedia"&gt;Jacques CHEVALIER&lt;/a&gt; était un philosophe français catholique et un historien de la philosophie connu pour son travail sur Platon, Pascal et Bergson ainsi que pour son engagement public dans l’entre-deux-guerres et pendant la Seconde Guerre mondiale. &lt;/p&gt; &lt;p&gt; Sur &lt;a href="https://www.persee.fr/doc/ahess_0395-2649_1957_num_12_4_2697_t1_0674_0000_1"  title=" histoire de la pensée   par persée"&gt;le plan philosophique,&lt;/a&gt;  il s’inscrit dans un courant spiritualiste et catholique influencé par Bergson : il défend une conception de la personne et de la vie intérieure opposée au matérialisme scientifique, tout en restant un historien et un commentateur rigoureux des textes classiques. &lt;/p&gt; &lt;p&gt; Politiquement, il fut actif : après 1940 il occupa des fonctions au sein de l’administration de Vichy (ministre de l’Instruction publique en 1941, puis secrétaire d’État à la Famille et à la Santé) et tenta d’introduire un &lt;a href="https://monbourbonnais.com/chevalier-jacques-ecrivain-philosophe/"  title=" chevalier jacques par mon bourbonnais"&gt;enseignement du devoir &lt;/a&gt; envers Dieu dans les programmes scolaires, réforme vivement contestée et finalement annulée après-guerre; il connut ensuite des poursuites mais fut finalement réhabilité partiellement. &lt;/p&gt; &lt;p&gt; Son œuvre laisse le souvenir d’un intellectuel engagé qui a cherché à réconcilier foi et culture, érudition et action publique : on retient chez lui la combinaison d’un solide travail d’édition et d’interprétation (ouvrages sur Platon, Pascal, Bergson) et d’un engagement pour une renaissance de la pensée catholique en France. &lt;/p&gt; 
-</t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Jacques_Chevalier_(philosophe)"  title=" Wikipedia"&gt;Jacques CHEVALIER&lt;/a&gt; (1882-1962) est un philosophe catholique français, historien de la philosophie et disciple d’Henri Bergson. Né à Cérilly, dans l’Allier, normalien et agrégé de philosophie, il enseigne à l’université de Grenoble. Il est l’auteur d’études sur Descartes, Pascal et Bergson, et d’une vaste &lt;em&gt;Histoire de la pensée&lt;/em&gt;. Son &lt;em&gt;Pascal&lt;/em&gt; (1922) et son &lt;em&gt;Bergson&lt;/em&gt; (1926) sont longtemps restés des ouvrages de référence, et il compte Emmanuel Mounier parmi ses étudiants.&lt;/p&gt; &lt;p&gt;Sur &lt;a href="https://www.persee.fr/doc/ahess_0395-2649_1957_num_12_4_2697_t1_0674_0000_1"  title=" histoire de la pensée   par persée"&gt;le plan philosophique&lt;/a&gt;, il s’inscrit dans un courant spiritualiste et catholique : il défend une conception de la personne et de la vie intérieure opposée au matérialisme scientifique, et voit dans la philosophie de Bergson un chemin vers la foi. Ses &lt;em&gt;Entretiens avec Bergson&lt;/em&gt; (1959), notes de conversations tenues pendant de longues années, sont un document précieux sur la pensée de son maître.&lt;/p&gt; &lt;p&gt;Proche du maréchal Pétain, ami de son père, il rejoint le régime de Vichy. Secrétaire d’État à l’Instruction publique à la fin de 1940, il fait inscrire l’&lt;a href="https://monbourbonnais.com/chevalier-jacques-ecrivain-philosophe/"  title=" chevalier jacques par mon bourbonnais"&gt;enseignement des devoirs&lt;/a&gt; envers Dieu dans les programmes de l’école primaire, mesure contestée et abandonnée dès 1941 par son successeur Jérôme Carcopino. Secrétaire d’État à la Famille et à la Santé en 1941, il soutient ensuite la Milice et dénonce des résistants, dont plusieurs sont exécutés. Après la Libération, il est condamné à vingt ans de prison et à l’indignité nationale, puis gracié en 1947 pour raisons de santé.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="F50" s="60" t="inlineStr">
@@ -6322,8 +6321,7 @@
       </c>
       <c r="E91" s="65" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt; &lt;a href="https://fr.wikipedia.org/wiki/Albert_Camus"  title=" Wikipedia"&gt;Albert CAMUS&lt;/a&gt; était un philosophe et écrivain français dont le courant de pensée est l'Existentialisme. Il a abordé de nombreux sujets philosophiques, notamment &lt;a href="https://www.youtube.com/watch?v=kAm_I8nwjnc&amp;t=498s&amp;ab_channel=LePr%C3%A9cepteur"   title="L'absure par le Précepteur"&gt;l'absurdité de la vie&lt;/a&gt;, la liberté individuelle, la révolte, l'amour.&lt;/p&gt; &lt;p&gt;Il a écrit plusieurs ouvrage comme  &lt;a href="https://www.youtube.com/watch?v=vpzwD2cqqII&amp;ab_channel=LePr%C3%A9cepteur"  title="L'étranger par le Précepteur"&gt;"l'Étranger"&lt;/a&gt;  ou "Le Mythe de Sisyphe" où il  a développé l'idée que la vie est fondamentalement absurde, car elle ne contient pas de sens intrinsèque ou de finalité. Il a expliqué que l'homme est confronté à un monde qui ne lui donne pas de réponses claires ou satisfaisantes à ses questions sur l'existence et que, par conséquent, il doit créer son propre sens de la vie. &lt;/p&gt; &lt;p&gt;Camus a également écrit sur la liberté individuelle et la révolte contre l'oppression avec son livre &lt;a href="https://www.youtube.com/watch?v=XLbXH2kVOJ8"  title="La Peste par le France Culture"&gt;" la Peste"&lt;/a&gt; sortie en 1947 où Il défend la position selon laquelle l'individu doit être libre de poursuivre ses propres intérêts et passions, et que la tyrannie et l'oppression sont des forces qui doivent être combattues. Après le cycle de l'absurde, il entame le cycle de la &lt;a href="https://www.youtube.com/watch?v=pkRWhuO0wX0&amp;ab_channel=AlainBajom%C3%A9er" title="La Révolte par Alain Bajomée"&gt;révolte.&lt;/a&gt; &lt;/p&gt; &lt;p&gt;Enfin, il a écrit sur l'amour et l'amitié, explorant la façon dont ces sentiments peuvent apporter de la signification et de la valeur à la vie et a réfléchi sur la solitude et l'isolement, soulignant que ces expériences peuvent être à la fois douloureuses et enrichissantes. &lt;/p&gt;   &lt;audio controls title="Albert Camus par France Culture"&gt; &lt;source src="https://cdn.radiofrance.fr/s3/cruiser-production/static/inter/sons/2011/07/s27/NET_2f8a9ed7-086a-40ee-9d75-b184f9e5f99a.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt; 
-</t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Albert_Camus"  title=" Wikipedia"&gt;Albert CAMUS&lt;/a&gt; (1913-1960) est un écrivain et philosophe français, né à Mondovi, en Algérie, dans une famille pauvre : son père meurt à la guerre en 1914, et sa mère, presque sourde, l’élève à Alger. Journaliste, résistant, rédacteur en chef du journal &lt;em&gt;Combat&lt;/em&gt; à la Libération, il reçoit le prix Nobel de littérature en 1957 et meurt dans un accident de voiture en 1960. On le range souvent parmi les existentialistes, une étiquette qu’il refusait.&lt;/p&gt; &lt;p&gt;Sa pensée part de &lt;a href="https://www.youtube.com/watch?v=kAm_I8nwjnc&amp;t=498s&amp;ab_channel=LePr%C3%A9cepteur"   title="L'absure par le Précepteur"&gt;l’absurde&lt;/a&gt; : l’homme réclame un sens et une clarté que le monde lui refuse. Le « cycle de l’absurde » réunit le roman &lt;a href="https://www.youtube.com/watch?v=vpzwD2cqqII&amp;ab_channel=LePr%C3%A9cepteur"  title="L'étranger par le Précepteur"&gt;&lt;em&gt;L’Étranger&lt;/em&gt;&lt;/a&gt; (1942), dont le héros, Meursault, traverse sa propre vie en étranger, et l’essai &lt;em&gt;Le Mythe de Sisyphe&lt;/em&gt; (1942). Camus y refuse aussi bien le suicide que l’espoir religieux : il faut vivre l’absurde en pleine lucidité, comme Sisyphe roulant éternellement son rocher. « Il faut imaginer Sisyphe heureux. »&lt;/p&gt; &lt;p&gt;Vient ensuite le cycle de la &lt;a href="https://www.youtube.com/watch?v=pkRWhuO0wX0&amp;ab_channel=AlainBajom%C3%A9er" title="La Révolte par Alain Bajomée"&gt;révolte&lt;/a&gt;. Dans &lt;a href="https://www.youtube.com/watch?v=XLbXH2kVOJ8"  title="La Peste par le France Culture"&gt;&lt;em&gt;La Peste&lt;/em&gt;&lt;/a&gt; (1947), allégorie de l’Occupation, des hommes luttent ensemble contre l’épidémie, sans héroïsme ni espoir de salut. &lt;em&gt;L’Homme révolté&lt;/em&gt; (1951) affirme : « Je me révolte, donc nous sommes » ; la révolte crée une solidarité et pose une limite, que les révolutions trahissent quand elles justifient le meurtre au nom de l’histoire. Le livre provoque sa rupture avec Sartre, en 1952. Ses pièces, comme &lt;em&gt;Caligula&lt;/em&gt; ou &lt;em&gt;Les Justes&lt;/em&gt;, prolongent cette réflexion sur la mesure et la dignité humaine.&lt;/p&gt;  &lt;audio controls title="Albert Camus par France Culture"&gt; &lt;source src="https://cdn.radiofrance.fr/s3/cruiser-production/static/inter/sons/2011/07/s27/NET_2f8a9ed7-086a-40ee-9d75-b184f9e5f99a.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;</t>
         </is>
       </c>
       <c r="F91" s="57" t="inlineStr">

--- a/data/frise-philosophes-france.xlsx
+++ b/data/frise-philosophes-france.xlsx
@@ -2147,7 +2147,7 @@
       </c>
       <c r="E22" s="56" t="inlineStr">
         <is>
-          <t>&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Georges_Sorel" title=" Wikipedia"&gt;Georges SOREL&lt;/a&gt; était un  philosophe et sociologue français,  principalement connu pour sa théorie du &lt;a href="https://www.youtube.com/watch?v=Lj0Ikd0X9mI&amp;t=173s"  title="Revolutionary Syndicalism: Moving Beyond Capitalism &amp; Communism par TheJayLino"&gt;"syndicalisme révolutionnaire" &lt;/a&gt; et sa réflexion originale sur le rôle du mythe et de la violence dans l’histoire sociale. Il est particulièrement célèbre pour son ouvrage "Réflexions sur la violence" paru en 1908, où il défend l’idée que la grève générale et &lt;a href="https://www.youtube.com/watch?v=ez4-qzm2BmY&amp;t=46s"  title="Georges Sorel -Le pessimisme et l'action par Ego Non"&gt;l’action directe&lt;/a&gt; sont des moyens essentiels pour l’émancipation ouvrière. Pour lui, la grève n’est pas seulement un moyen de revendication matérielle mais un acte fondateur, un mythe mobilisateur capable de forger une conscience collective et un esprit de combat chez les travailleurs. &lt;/p&gt; &lt;p&gt; Il distingue radicalement la notion de mythe de celle d’utopie. Le mythe a, selon lui, une force mobilisatrice concrète qui pousse à l’action, tandis que l’utopie a tendance à rigidifier l’histoire. Il considère le mythe comme une force morale et créatrice permettant de surmonter &lt;a href="https://www.persee.fr/doc/mcm_0755-8287_1983_num_1_1_862"  title="Georges Sorel et le fascisme. Éléments d'explication d'une légende tenace par Persée"&gt;la crise des valeurs &lt;/a&gt; de la société contemporaine.&lt;/p&gt; &lt;p&gt;  À la fin de sa vie, il s’éloigne du socialisme classique et se rapproche de mouvements intellectuels conservateurs et monarchistes, tout en affichant un certain malaise face à ces rapprochements. Son œuvre reste marquée par de nombreuses tensions : fidélité au marxisme, intérêt pour la morale, scepticisme envers le parlementarisme et critique de l’intellectualisme. &lt;/p&gt;</t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Georges_Sorel" title=" Wikipedia"&gt;Georges SOREL&lt;/a&gt; était un  philosophe et sociologue français,  principalement connu pour sa théorie du &lt;a href="https://www.youtube.com/watch?v=Lj0Ikd0X9mI&amp;t=173s"  title="Revolutionary Syndicalism: Moving Beyond Capitalism &amp; Communism par TheJayLino"&gt;"syndicalisme révolutionnaire" &lt;/a&gt; et sa réflexion originale sur le rôle du mythe et de la violence dans l’histoire sociale. Il est particulièrement célèbre pour son ouvrage "Réflexions sur la violence" paru en 1908, où il défend l’idée que la grève générale et &lt;a href="https://www.youtube.com/watch?v=ez4-qzm2BmY&amp;t=46s"  title="Georges Sorel -Le pessimisme et l'action par Ego Non"&gt;l’action directe&lt;/a&gt; sont des moyens essentiels pour l’émancipation ouvrière. Pour lui, la grève n’est pas seulement un moyen de revendication matérielle mais un acte fondateur, un mythe mobilisateur capable de forger une conscience collective et un esprit de combat chez les travailleurs. Ancien polytechnicien, ingénieur des Ponts et Chaussées, il abandonne son métier en 1892 pour se consacrer à l’étude et à l’écriture. &lt;/p&gt; &lt;p&gt; Il distingue radicalement la notion de mythe de celle d’utopie. Le mythe a, selon lui, une force mobilisatrice concrète qui pousse à l’action, tandis que l’utopie a tendance à rigidifier l’histoire. Il considère le mythe comme une force morale et créatrice permettant de surmonter &lt;a href="https://www.persee.fr/doc/mcm_0755-8287_1983_num_1_1_862"  title="Georges Sorel et le fascisme. Éléments d'explication d'une légende tenace par Persée"&gt;la crise des valeurs &lt;/a&gt; de la société contemporaine.&lt;/p&gt; &lt;p&gt;  À la fin de sa vie, il s’éloigne du socialisme classique et se rapproche de mouvements intellectuels conservateurs et monarchistes, tout en affichant un certain malaise face à ces rapprochements. Son œuvre reste marquée par de nombreuses tensions : fidélité au marxisme, intérêt pour la morale, scepticisme envers le parlementarisme et critique de l’intellectualisme. Après sa mort, Mussolini se réclamera de lui, ce qui a nourri une légende tenace. &lt;/p&gt;</t>
         </is>
       </c>
       <c r="F22" s="54" t="inlineStr">
@@ -3280,7 +3280,7 @@
       </c>
       <c r="E41" s="62" t="inlineStr">
         <is>
-          <t>&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/L%C3%A9on_Brunschvicg" title=" Wikipedia"&gt;Léon BRUNSCHVICG&lt;/a&gt; était un philosophe idéaliste français issus d’une famille juive cultivée, normalien et agrégé de philosophie, il enseigna à la Sorbonne de 1909 à 1940 et domina une grande partie de la vie philosophique française de l'entre-deux-guerres. &lt;/p&gt; &lt;p&gt; Sa philosophie, qualifiée d'« idéalisme critique » ou d'« idéalisme spiritualiste », part de la conviction que la réalité n'est accessible qu'à travers l'activité de l'esprit. &lt;a href="https://www.persee.fr/doc/inrp_0298-5632_1986_ant_2_2_2708" title="Brunschvicg par persée"&gt;Dans son œuvre &lt;/a&gt; maîtresse, &lt;em&gt;Les Étapes de la philosophie mathématique&lt;/em&gt; (1912), il montre que l'histoire des mathématiques révèle les progrès de la conscience spirituelle : chaque grande révolution mathématique — de l'arithmétique grecque à la géométrie non euclidienne — correspond à un approfondissement de la compréhension que l'esprit a de lui-même et du monde. &lt;/p&gt; &lt;p&gt; Dans &lt;em&gt;L'Expérience humaine et la causalité physique&lt;/em&gt; (1922) et &lt;em&gt;Le Progrès de la conscience dans la philosophie occidentale&lt;/em&gt; (1927), il approfondit cette vision d'une histoire de la pensée comme progrès de l'esprit vers lui-même. Sa philosophie religieuse, exposée dans &lt;em&gt;La Raison et la Religion&lt;/em&gt; (1939), défend un spiritualisme laïc et rationnel, proche de l'héritage de Spinoza. Il influença profondément les générations de philosophes français qui s'imposèrent après lui, notamment Jean-Paul Sartre et Maurice Merleau-Ponty, même si ce fut parfois par réaction contre son idéalisme. &lt;/p&gt;</t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/L%C3%A9on_Brunschvicg" title=" Wikipedia"&gt;Léon BRUNSCHVICG&lt;/a&gt; était un philosophe idéaliste français issu d’une famille juive cultivée, normalien et agrégé de philosophie, il enseigna à la Sorbonne de 1909 à 1940 et domina une grande partie de la vie philosophique française de l'entre-deux-guerres. Cofondateur en 1893 de la &lt;em&gt;Revue de métaphysique et de morale&lt;/em&gt;, il donne aussi des &lt;em&gt;Pensées&lt;/em&gt; de Pascal une édition restée célèbre. Juif, il doit quitter Paris sous l’Occupation et meurt en 1944 à Aix-les-Bains. &lt;/p&gt; &lt;p&gt; Sa philosophie, qualifiée d'« idéalisme critique » ou d'« idéalisme spiritualiste », part de la conviction que la réalité n'est accessible qu'à travers l'activité de l'esprit. &lt;a href="https://www.persee.fr/doc/inrp_0298-5632_1986_ant_2_2_2708" title="Brunschvicg par persée"&gt;Dans son œuvre &lt;/a&gt; maîtresse, &lt;em&gt;Les Étapes de la philosophie mathématique&lt;/em&gt; (1912), il montre que l'histoire des mathématiques révèle les progrès de la conscience spirituelle : chaque grande révolution mathématique — de l'arithmétique grecque à la géométrie non euclidienne — correspond à un approfondissement de la compréhension que l'esprit a de lui-même et du monde. &lt;/p&gt; &lt;p&gt; Dans &lt;em&gt;L'Expérience humaine et la causalité physique&lt;/em&gt; (1922) et &lt;em&gt;Le Progrès de la conscience dans la philosophie occidentale&lt;/em&gt; (1927), il approfondit cette vision d'une histoire de la pensée comme progrès de l'esprit vers lui-même. Sa philosophie religieuse, exposée dans &lt;em&gt;La Raison et la Religion&lt;/em&gt; (1939), défend un spiritualisme laïc et rationnel, proche de l'héritage de Spinoza. Il influença profondément les générations de philosophes français qui s'imposèrent après lui, notamment Jean-Paul Sartre et Maurice Merleau-Ponty, même si ce fut parfois par réaction contre son idéalisme. &lt;/p&gt;</t>
         </is>
       </c>
       <c r="F41" s="54" t="inlineStr">
@@ -6200,7 +6200,7 @@
       </c>
       <c r="E89" s="59" t="inlineStr">
         <is>
-          <t>&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Jacques_Ellul"  title=" Wikipedia"&gt;Jacques ELLUL&lt;/a&gt; était un philosophe,sociologue, historien du droit et théologien protestant français, célèbre pour sa critique radicale de la technique moderne et de ses  &lt;a href="https://www.youtube.com/watch?v=SfUEFANIm5s"  title=" Jacques Ellul : Comprendre la propagande infiltrés dans la société par Multivers philosophique"&gt;effets aliénants &lt;/a&gt; sur la société et la liberté humaine. Anarchiste chrétien, il oppose révolte authentique et révolution mythique, valorisant la non-violence et la résistance locale face à la massification.  Penseur inclassable mêlant marxisme critique, anarchisme chrétien et écologie avant l'heure, il a produit une &lt;a href="https://www.persee.fr/doc/colan_0336-1500_1995_num_106_1_2633"  title="Les leçons de Jacques Ellul  par Persée "&gt;œuvre prolifique &lt;/a&gt; dépassant les 50 livres, traduits dans de nombreuses langues. &lt;/p&gt; &lt;p&gt; Dans son livre "La Technique ou l'Enjeu du siècle" paru en 1954, il décrit son "efficience absolue" qui aliène l'homme, le rendant dépendant d'un milieu technique auto-entretenu, avec des notions clés comme le "milieu technique déterminé" et la "nécessité technique".  Il  définit la  &lt;a href="https://www.youtube.com/watch?v=DGsN8Ssf5oo"  title=" 
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Jacques_Ellul"  title=" Wikipedia"&gt;Jacques ELLUL&lt;/a&gt; était un philosophe, sociologue, historien du droit et théologien protestant français, célèbre pour sa critique radicale de la technique moderne et de ses  &lt;a href="https://www.youtube.com/watch?v=SfUEFANIm5s"  title=" Jacques Ellul : Comprendre la propagande infiltrés dans la société par Multivers philosophique"&gt;effets aliénants &lt;/a&gt; sur la société et la liberté humaine. Anarchiste chrétien, il oppose révolte authentique et révolution mythique, valorisant la non-violence et la résistance locale face à la massification.  Penseur inclassable mêlant marxisme critique, anarchisme chrétien et écologie avant l'heure, il a produit une &lt;a href="https://www.persee.fr/doc/colan_0336-1500_1995_num_106_1_2633"  title="Les leçons de Jacques Ellul  par Persée "&gt;œuvre prolifique &lt;/a&gt; dépassant les 50 livres, traduits dans de nombreuses langues. Né à Bordeaux, professeur à l’université de cette ville, résistant pendant la guerre, il est reconnu en 2001 « Juste parmi les nations » pour avoir caché des Juifs. &lt;/p&gt; &lt;p&gt; Dans son livre "La Technique ou l'Enjeu du siècle" paru en 1954, il décrit son "efficience absolue" qui aliène l'homme, le rendant dépendant d'un milieu technique auto-entretenu, avec des notions clés comme le "milieu technique déterminé" et la "nécessité technique".  Il  définit la  &lt;a href="https://www.youtube.com/watch?v=DGsN8Ssf5oo"  title=" 
 Jacques Ellul, premier critique de la technologie par France Culture"&gt;"technique" &lt;/a&gt; non comme un outil, mais comme un système autonome et totalisant de méthodes rationnelles efficaces, envahissant tous les domaines humains (économie, politique, éducation). &lt;/p&gt; &lt;p&gt; &lt;a href="https://www.jacques-ellul.org/"  title=" Jacques Ellul "&gt;Précurseur écologique, &lt;/a&gt; il dénonce la production illimitée qui domine les besoins humains et appelle à une "profanation" de cette sacralisation technique. Son legs visionnaire influence l'écologie politique, la décroissance et les réflexions sur le numérique, voyant dans la technique un "système technicien" préfigurant nos crises actuelles. &lt;/p&gt;  &lt;audio controls title="Avoir raison avec... Jacques Ellul par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/17362-11.08.2025-ITEMA_24214885-2025C35448E0031-ITE_00152537_RSCE-21.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;</t>
         </is>
       </c>
@@ -7835,7 +7835,7 @@
       </c>
       <c r="E116" s="56" t="inlineStr">
         <is>
-          <t>&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Jean_Baudrillard"  title=" Wikipedia"&gt;Jean BAUDRILLARD&lt;/a&gt;  était un philosophe français du courant dit "postmoderne", connu pour ses analyses de la société de consommation, des médias et des simulacres, ainsi que pour les notions  &lt;a href="https://www.youtube.com/watch?v=kiHpGAjA33E" title="Baudrillard - La Disparition Du Monde Réel par Mornhugss"&gt;d'hyperréalité &lt;/a&gt; et de "désert du réel". &lt;/p&gt; &lt;p&gt; Penseur inclassable, il se décrit lui‑même comme "pataphysicien à 20 ans, situationniste à 30, utopiste à 40, transversal à 50, viral et métaleptique à 60". &lt;/p&gt; &lt;p&gt; Il est associé à quelques idées devenues classiques pour penser la modernité tardive. Pour lui, dans les sociétés dominées par les médias, la publicité et les images, les signes ne renvoient plus à une réalité préexistante, mais se renvoient les uns aux autres, produisant un monde "plus vrai que vrai" qu’il appelle hyperréel.  Les simulations (images télévisuelles, flux financiers, modèles informatiques) ont remplacé leurs référents, de sorte qu’il ne reste que le &lt;a href="https://www.lemonde.fr/culture/article/2017/03/02/dix-ans-apres-sa-mort-baudrillard-fait-toujours-penser_5088278_3246.html" title="Dix ans après sa mort, Baudrillard fait toujours penser par Le Monde"&gt;désert du réel  &lt;/a&gt; derrière la prolifération des signes. La société se dissout dans une masse silencieuse de spectateurs qui cherchent le spectacle plutôt que le sens, ce qui fait  "imploser" les catégories classiques de classe, sujet politique ou opinion publique. &lt;p&gt; &lt;p&gt; Héritier critique du marxisme : ses premiers travaux combinent économie politique et sémiologie, mais il rompt ensuite avec l’idéologie de la production, qu’il considère elle‑même comme partie prenante du système qu’elle prétend critiquer.  &lt;/p&gt; &lt;audio controls title="Penser le monde avec Jean Baudrillard par France Culture"&gt; &lt;source src="https://cdn.radiofrance.fr/s3/cruiser-production/2019/09/4e5722ea-569d-4069-8321-69b5e27ba665/flyvonnetok.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;</t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Jean_Baudrillard"  title=" Wikipedia"&gt;Jean BAUDRILLARD&lt;/a&gt;  était un philosophe français du courant dit "postmoderne", connu pour ses analyses de la société de consommation, des médias et des simulacres, ainsi que pour les notions  &lt;a href="https://www.youtube.com/watch?v=kiHpGAjA33E" title="Baudrillard - La Disparition Du Monde Réel par Mornhugss"&gt;d'hyperréalité &lt;/a&gt; et de "désert du réel". &lt;/p&gt; &lt;p&gt; Penseur inclassable, il se décrit lui‑même comme "pataphysicien à 20 ans, situationniste à 30, utopiste à 40, transversal à 50, viral et métaleptique à 60". Né à Reims, il enseigne la sociologie à l’université de Nanterre. Ses livres, de &lt;em&gt;La Société de consommation&lt;/em&gt; (1970) à &lt;em&gt;Simulacres et Simulation&lt;/em&gt; (1981), que l’on aperçoit dans le film &lt;em&gt;Matrix&lt;/em&gt;, ont eu un écho mondial. &lt;/p&gt; &lt;p&gt; Il est associé à quelques idées devenues classiques pour penser la modernité tardive. Pour lui, dans les sociétés dominées par les médias, la publicité et les images, les signes ne renvoient plus à une réalité préexistante, mais se renvoient les uns aux autres, produisant un monde "plus vrai que vrai" qu’il appelle hyperréel.  Les simulations (images télévisuelles, flux financiers, modèles informatiques) ont remplacé leurs référents, de sorte qu’il ne reste que le &lt;a href="https://www.lemonde.fr/culture/article/2017/03/02/dix-ans-apres-sa-mort-baudrillard-fait-toujours-penser_5088278_3246.html" title="Dix ans après sa mort, Baudrillard fait toujours penser par Le Monde"&gt;désert du réel  &lt;/a&gt; derrière la prolifération des signes. La société se dissout dans une masse silencieuse de spectateurs qui cherchent le spectacle plutôt que le sens, ce qui fait  "imploser" les catégories classiques de classe, sujet politique ou opinion publique. &lt;/p&gt; &lt;p&gt; Héritier critique du marxisme : ses premiers travaux combinent économie politique et sémiologie, mais il rompt ensuite avec l’idéologie de la production, qu’il considère elle‑même comme partie prenante du système qu’elle prétend critiquer.  &lt;/p&gt; &lt;audio controls title="Penser le monde avec Jean Baudrillard par France Culture"&gt; &lt;source src="https://cdn.radiofrance.fr/s3/cruiser-production/2019/09/4e5722ea-569d-4069-8321-69b5e27ba665/flyvonnetok.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;</t>
         </is>
       </c>
       <c r="F116" s="54" t="inlineStr">

--- a/data/frise-philosophes-france.xlsx
+++ b/data/frise-philosophes-france.xlsx
@@ -2739,7 +2739,7 @@
       </c>
       <c r="E32" s="62" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Henri_Bergson"  title=" Wikipedia"&gt;Henri BERGSON&lt;/a&gt; (1859-1941) est un philosophe français, l’un des plus célèbres de son temps. Normalien, professeur de lycée puis au Collège de France à partir de 1900, il attire à ses cours une foule cultivée. Élu à l’Académie française en 1914, il reçoit en 1927 le prix Nobel de littérature.&lt;/p&gt; &lt;p&gt;Sa thèse, l’&lt;em&gt;Essai sur les données immédiates de la conscience&lt;/em&gt; (1889), oppose deux temps. Le temps des horloges et des sciences est mesuré, fait d’instants juxtaposés comme des points sur une ligne. &lt;a  href="https://www.youtube.com/watch?v=SWgNY2E40y4&amp;ab_channel=LePr%C3%A9cepteur" style="color:#88A1E9"  title="Le Temps par le Précepteur"&gt;Le temps vécu&lt;/a&gt;, la « durée », est au contraire continu : nos états de &lt;a  href="https://www.youtube.com/watch?v=E-v2eO_m_Fg&amp;ab_channel=Kosmos"  title="La Conscience par Kosmos"&gt;conscience&lt;/a&gt; se fondent les uns dans les autres comme les notes d’une mélodie, et nous sommes libres quand nos actes jaillissent de notre personnalité tout entière. L’intelligence, faite pour agir sur la matière, découpe le réel et le fige, comme le fait &lt;a  href="https://www.youtube.com/watch?v=M6-L2M_7ysk&amp;ab_channel=LePr%C3%A9cepteur"  title="Les limites du langage par Le Précepteur"&gt;le langage&lt;/a&gt; avec ses mots généraux ; seule l’intuition saisit le mouvement de la vie. Dans &lt;em&gt;Matière et mémoire&lt;/em&gt; (1896), il montre que le souvenir n’est pas stocké dans le cerveau, qui sert surtout à l’action. Dans &lt;a  href="https://philosophie.cegeptr.qc.ca/wp-content/documents/L%C3%A9volution-cr%C3%A9atrice.pdf" title="L'évolution créatrice par Philo cegeptr"&gt;&lt;em&gt;L’Évolution créatrice&lt;/em&gt;&lt;/a&gt; (1907), il décrit la vie comme un « élan vital » qui invente sans cesse des formes nouvelles. Son essai sur &lt;a  href="https://www.youtube.com/watch?v=RptdiM_WZrU&amp;ab_channel=LePr%C3%A9cepteur"  title="Le rire par Le Précepteur"&gt;le rire&lt;/a&gt; y voit « du mécanique plaqué sur du vivant ». Enfin, &lt;a  href="https://www.youtube.com/watch?v=E6MNRoeU9Ak&amp;ab_channel=Kosmos"  title="La Conscience par Kosmos"&gt;&lt;em&gt;Les Deux Sources de la morale et de la religion&lt;/em&gt;&lt;/a&gt; (1932) opposent la morale close des sociétés à la morale ouverte des mystiques, qui s’adresse à l’humanité entière.&lt;/p&gt; &lt;p&gt;Il voit dans &lt;a  href="https://www.youtube.com/watch?v=s9SwcAMCPrM&amp;ab_channel=FranceCulture" title="l'unique archive audio de sa voix par France Culture"&gt;l’art&lt;/a&gt; un moyen de percevoir le réel au-delà de nos habitudes. Proche du catholicisme, il refuse de se convertir par solidarité avec les juifs persécutés, et meurt dans Paris occupé en 1941.&lt;/p&gt;  &lt;audio controls title="Le possible et le réel par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/10467-20.06.2017-ITEMA_21363346-2.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;</t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Henri_Bergson"  title=" Wikipedia"&gt;Henri BERGSON&lt;/a&gt; (1859-1941) est un philosophe français, l’un des plus célèbres de son temps. Normalien, professeur de lycée puis au Collège de France à partir de 1900, il attire à ses cours une foule cultivée. Élu à l’Académie française en 1914, il reçoit en 1927 le prix Nobel de littérature.&lt;/p&gt; &lt;p&gt;Sa thèse, l’&lt;em&gt;Essai sur les données immédiates de la conscience&lt;/em&gt; (1889), oppose deux temps. Le temps des horloges et des sciences est mesuré, fait d’instants juxtaposés comme des points sur une ligne. &lt;a  href="https://www.youtube.com/watch?v=SWgNY2E40y4&amp;ab_channel=LePr%C3%A9cepteur" style="color:#88A1E9"  title="Le Temps par le Précepteur"&gt;Le temps vécu&lt;/a&gt;, la « durée », est au contraire continu : nos états de &lt;a  href="https://www.youtube.com/watch?v=E-v2eO_m_Fg&amp;ab_channel=Kosmos"  title="La Conscience par Kosmos"&gt;conscience&lt;/a&gt; se fondent les uns dans les autres comme les notes d’une mélodie, et nous sommes libres quand nos actes jaillissent de notre personnalité tout entière. L’intelligence, faite pour agir sur la matière, découpe le réel et le fige, comme le fait &lt;a  href="https://www.youtube.com/watch?v=M6-L2M_7ysk&amp;ab_channel=LePr%C3%A9cepteur"  title="Les limites du langage par Le Précepteur"&gt;le langage&lt;/a&gt; avec ses mots généraux ; seule l’intuition saisit le mouvement de la vie. Dans &lt;em&gt;Matière et mémoire&lt;/em&gt; (1896), il montre que le souvenir n’est pas stocké dans le cerveau, qui sert surtout à l’action. Dans &lt;em&gt;L’Évolution créatrice&lt;/em&gt; (1907), il décrit la vie comme un « élan vital » qui invente sans cesse des formes nouvelles. Son essai sur &lt;a  href="https://www.youtube.com/watch?v=RptdiM_WZrU&amp;ab_channel=LePr%C3%A9cepteur"  title="Le rire par Le Précepteur"&gt;le rire&lt;/a&gt; y voit « du mécanique plaqué sur du vivant ». Enfin, &lt;a  href="https://www.youtube.com/watch?v=E6MNRoeU9Ak&amp;ab_channel=Kosmos"  title="La Conscience par Kosmos"&gt;&lt;em&gt;Les Deux Sources de la morale et de la religion&lt;/em&gt;&lt;/a&gt; (1932) opposent la morale close des sociétés à la morale ouverte des mystiques, qui s’adresse à l’humanité entière.&lt;/p&gt; &lt;p&gt;Il voit dans &lt;a  href="https://www.youtube.com/watch?v=s9SwcAMCPrM&amp;ab_channel=FranceCulture" title="l'unique archive audio de sa voix par France Culture"&gt;l’art&lt;/a&gt; un moyen de percevoir le réel au-delà de nos habitudes. Proche du catholicisme, il refuse de se convertir par solidarité avec les juifs persécutés, et meurt dans Paris occupé en 1941.&lt;/p&gt;  &lt;audio controls title="Le possible et le réel par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/10467-20.06.2017-ITEMA_21363346-2.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;</t>
         </is>
       </c>
       <c r="F32" s="54" t="inlineStr">
@@ -6085,7 +6085,7 @@
       </c>
       <c r="E87" s="56" t="inlineStr">
         <is>
-          <t>&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Bernard_Charbonneau"  title=" Wikipedia"&gt;Bernard CHARBONNEAU&lt;/a&gt; était un penseur français, pionnier de la critique écologique et de la réflexion sur la technique et la liberté, souvent qualifié de « père méconnu » de l'écologie politique française. Né à Bordeaux,  &lt;a href="https://www.jacques-ellul.org/compagnonnage/bernard-charbonneau"  title="ami de Jacques Ellul  "&gt;ami intime de Jacques Ellul &lt;/a&gt; avec lequel il partagea une amitié intellectuelle de plus de soixante ans, il développa dès les années 1930 une pensée radicalement critique de la modernité technicienne et des formes contemporaines d'organisation sociale, bien avant que ces thèmes ne deviennent des enjeux politiques majeurs. &lt;/p&gt; &lt;p&gt; Dès 1937, dans un texte prophétique intitulé « Directives pour un personnalisme » rédigé avec Jacques Ellul, il posait les bases d'une critique du totalitarisme — qu'il identifiait non seulement au fascisme et au stalinisme, mais aussi à la démocratie de masse — fondée sur la défense irréductible de la liberté individuelle et de la &lt;a href="https://www.socialter.fr/article/bernard-charbonneau-objecteur-de-croissance-decroissance"  title="chardonneau 1er objecteur de conscience par socialter  "&gt;relation à la nature. &lt;/a&gt; Dans &lt;em&gt;Le Jardin de Babylone&lt;/em&gt; (1969), il montre comment la modernité a transformé la nature en décor consommable, détruisant ce rapport authentique à la terre et aux saisons qui constituait le fond de la liberté paysanne. &lt;/p&gt; &lt;p&gt; Son œuvre la plus ambitieuse, &lt;em&gt;Le Feu vert&lt;/em&gt; (1980) et &lt;em&gt;L'Etat&lt;/em&gt; (1987), développe une &lt;a href="https://www.youtube.com/watch?v=U6WXSBX8Ldg"  title="bernard Chardonneau par Sylvain Theriault  "&gt;critique radicale de l'État &lt;/a&gt; bureaucratique et technicien et de sa tendance à absorber toutes les formes de vie sociale. Il défendait un « anarchisme chrétien » ancré dans l'expérience concrète du Béarn où il choisit de vivre. Redécouvert dans les années 2000 par les mouvements écologistes et décroissants, il est aujourd'hui reconnu comme l'un des penseurs les plus originaux et les plus lucides du XXe siècle français. &lt;/p&gt;</t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Bernard_Charbonneau"  title=" Wikipedia"&gt;Bernard CHARBONNEAU&lt;/a&gt; était un penseur français, pionnier de la critique écologique et de la réflexion sur la technique et la liberté, souvent qualifié de « père méconnu » de l'écologie politique française. Né à Bordeaux,  &lt;a href="https://www.jacques-ellul.org/compagnonnage/bernard-charbonneau"  title="ami de Jacques Ellul  "&gt;ami intime de Jacques Ellul &lt;/a&gt; avec lequel il partagea une amitié intellectuelle de plus de soixante ans, il développa dès les années 1930 une pensée radicalement critique de la modernité technicienne et des formes contemporaines d'organisation sociale, bien avant que ces thèmes ne deviennent des enjeux politiques majeurs. &lt;/p&gt; &lt;p&gt; Dès 1937, dans un texte prophétique intitulé « Directives pour un personnalisme » rédigé avec Jacques Ellul, il posait les bases d'une critique du totalitarisme — qu'il identifiait non seulement au fascisme et au stalinisme, mais aussi à la démocratie de masse — fondée sur la défense irréductible de la liberté individuelle et de la relation à la nature.  Dans &lt;em&gt;Le Jardin de Babylone&lt;/em&gt; (1969), il montre comment la modernité a transformé la nature en décor consommable, détruisant ce rapport authentique à la terre et aux saisons qui constituait le fond de la liberté paysanne. &lt;/p&gt; &lt;p&gt; Son œuvre la plus ambitieuse, &lt;em&gt;Le Feu vert&lt;/em&gt; (1980) et &lt;em&gt;L'Etat&lt;/em&gt; (1987), développe une &lt;a href="https://www.youtube.com/watch?v=U6WXSBX8Ldg"  title="bernard Chardonneau par Sylvain Theriault  "&gt;critique radicale de l'État &lt;/a&gt; bureaucratique et technicien et de sa tendance à absorber toutes les formes de vie sociale. Il défendait un « anarchisme chrétien » ancré dans l'expérience concrète du Béarn où il choisit de vivre. Redécouvert dans les années 2000 par les mouvements écologistes et décroissants, il est aujourd'hui reconnu comme l'un des penseurs les plus originaux et les plus lucides du XXe siècle français. &lt;/p&gt;</t>
         </is>
       </c>
       <c r="F87" s="54" t="inlineStr">
@@ -7357,7 +7357,7 @@
       </c>
       <c r="E108" s="65" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Gilles_Deleuze" title=" Wikipedia"&gt;Gilles DELEUZE&lt;/a&gt; était un philosophe français qui a profondément marqué la pensée contemporaine dans une  &lt;a href="http://sos.philosophie.free.fr/deleuze.php" style="color:#88A1E9" title=" Gilles Deleuze  par SOS philo"&gt;critique radicale&lt;/a&gt;oeuvre foisonnante et complexe.  Au cœur de sa philosophie se trouve une  &lt;a href="https://www.youtube.com/watch?v=4ybvyj_Pk7M" title=" Gilles Deleuze : l'art et les sociétés de contrôle par lINTELLECT FOCUS"&gt;critique radicale&lt;/a&gt; de la pensée traditionnelle occidentale, qu'il accuse d'être dominée par une logique de la représentation, de l'identité et de la négation. &lt;/p&gt; &lt;p&gt; Il cherche à penser la différence en elle-même qui n'est pas secondaire ou dérivée, mais originaire.  Le monde n'est pas constitué d'entités fixes et identiques qui entreraient ensuite en relation, mais d'un flux incessant de différences, de variations et de devenirs. Il conçoit plutôt la pensée comme une force créatrice qui produit des concepts pour appréhender et transformer le réel qui n'est pas statique, mais un processus continu de transformation, d'hybridation et de métamorphose. Ses oeuvres principales sont : &lt;/p&gt; &lt;p&gt;&lt;a href="https://www.youtube.com/watch?v=ia0FpHbHa_U"  title=" Différence et répétition de Gilles Deleuze (French Audiobook/Livre audio) 1 Avant propos par Chad A Haag Philosophy Channel"&gt;"Différence et Répétition"&lt;/a&gt; : Oeuvre métaphysique majeure, où il développe sa pensée de la différence et critique la conception traditionnelle de la répétition comme reproduction de l'identique. &lt;/p&gt; &lt;p&gt;"Logique du sens" : Une exploration des paradoxes du langage et du sens à travers une lecture originale de Lewis Carroll et des stoïciens. &lt;/p&gt; &lt;p&gt;"Qu'est-ce que la philosophie ?" (avec Félix Guattari) : Une réflexion sur la nature de la philosophie comme création de concepts, distincte de la science et de l'art. &lt;/p&gt; &lt;p&gt;  Sa rencontre avec Felix Guattari donne naissance à 2 ouvrages majeurs :&lt;a href="https://www.youtube.com/watch?v=JQE4_2ti_10&amp;t=78s" title=" La pensée politique de Deleuze et Guattari - Partie 1 / L'anti-Oedipe par Politikon"&gt;" L'Anti-Œdipe "&lt;/a&gt;  : Critique radicale de la psychanalyse et une exploration du désir comme force révolutionnaire et &lt;a href="https://www.youtube.com/watch?v=E01RyGu3Zac" title="La pensée politique de Deleuze et Guattari - Partie 2 / Mille Plateaux par Politikon"&gt;" Mille Plateaux "&lt;/a&gt;   : Une œuvre foisonnante qui explore une multitude de thèmes (le territoire, le devenir ) à travers le  &lt;a href="https://www.youtube.com/watch?v=RQ2rJWwXilw" title="The Rhizome - A Thousand Plateaus, Deleuze and Guattari par Then &amp; Now"&gt;concept de Rhizome&lt;/a&gt;. &lt;/p&gt; &lt;p&gt; Il  est un philosophe majeur qui a profondément transformé notre manière de  &lt;a href="https://diacritik.com/category/deleuze/" title=" Deleuze par Diacritik"&gt;penser la différence&lt;/a&gt;, la multiplicité, le devenir et la créativité. &lt;/p&gt; &lt;audio controls title="Gilles Deleuze, notre contemporain" par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/11189-19.11.2012-ITEMA_20421487-2012C15000E0183-ITE_00054426_RSCE-21.mp3" type="audio/mpeg" align="center"&gt;&lt;/audio&gt; </t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Gilles_Deleuze" title=" Wikipedia"&gt;Gilles DELEUZE&lt;/a&gt; était un philosophe français qui a profondément marqué la pensée contemporaine dans une  &lt;a href="http://sos.philosophie.free.fr/deleuze.php" style="color:#88A1E9" title=" Gilles Deleuze  par SOS philo"&gt;critique radicale&lt;/a&gt;oeuvre foisonnante et complexe.  Au cœur de sa philosophie se trouve une  &lt;a href="https://www.youtube.com/watch?v=4ybvyj_Pk7M" title=" Gilles Deleuze : l'art et les sociétés de contrôle par lINTELLECT FOCUS"&gt;critique radicale&lt;/a&gt; de la pensée traditionnelle occidentale, qu'il accuse d'être dominée par une logique de la représentation, de l'identité et de la négation. &lt;/p&gt; &lt;p&gt; Il cherche à penser la différence en elle-même qui n'est pas secondaire ou dérivée, mais originaire.  Le monde n'est pas constitué d'entités fixes et identiques qui entreraient ensuite en relation, mais d'un flux incessant de différences, de variations et de devenirs. Il conçoit plutôt la pensée comme une force créatrice qui produit des concepts pour appréhender et transformer le réel qui n'est pas statique, mais un processus continu de transformation, d'hybridation et de métamorphose. Ses oeuvres principales sont : &lt;/p&gt; &lt;p&gt;"Différence et Répétition" : Oeuvre métaphysique majeure, où il développe sa pensée de la différence et critique la conception traditionnelle de la répétition comme reproduction de l'identique. &lt;/p&gt; &lt;p&gt;"Logique du sens" : Une exploration des paradoxes du langage et du sens à travers une lecture originale de Lewis Carroll et des stoïciens. &lt;/p&gt; &lt;p&gt;"Qu'est-ce que la philosophie ?" (avec Félix Guattari) : Une réflexion sur la nature de la philosophie comme création de concepts, distincte de la science et de l'art. &lt;/p&gt; &lt;p&gt;  Sa rencontre avec Felix Guattari donne naissance à 2 ouvrages majeurs :&lt;a href="https://www.youtube.com/watch?v=JQE4_2ti_10&amp;t=78s" title=" La pensée politique de Deleuze et Guattari - Partie 1 / L'anti-Oedipe par Politikon"&gt;" L'Anti-Œdipe "&lt;/a&gt;  : Critique radicale de la psychanalyse et une exploration du désir comme force révolutionnaire et &lt;a href="https://www.youtube.com/watch?v=E01RyGu3Zac" title="La pensée politique de Deleuze et Guattari - Partie 2 / Mille Plateaux par Politikon"&gt;" Mille Plateaux "&lt;/a&gt;   : Une œuvre foisonnante qui explore une multitude de thèmes (le territoire, le devenir ) à travers le  &lt;a href="https://www.youtube.com/watch?v=RQ2rJWwXilw" title="The Rhizome - A Thousand Plateaus, Deleuze and Guattari par Then &amp; Now"&gt;concept de Rhizome&lt;/a&gt;. &lt;/p&gt; &lt;p&gt; Il  est un philosophe majeur qui a profondément transformé notre manière de  &lt;a href="https://diacritik.com/category/deleuze/" title=" Deleuze par Diacritik"&gt;penser la différence&lt;/a&gt;, la multiplicité, le devenir et la créativité. &lt;/p&gt; &lt;audio controls title="Gilles Deleuze, notre contemporain" par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/11189-19.11.2012-ITEMA_20421487-2012C15000E0183-ITE_00054426_RSCE-21.mp3" type="audio/mpeg" align="center"&gt;&lt;/audio&gt; </t>
         </is>
       </c>
       <c r="F108" s="57" t="inlineStr">

--- a/data/frise-philosophes-france.xlsx
+++ b/data/frise-philosophes-france.xlsx
@@ -938,7 +938,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:O153"/>
+  <dimension ref="A1:O154"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="4.59" customWidth="1" style="47" min="1" max="1"/>
@@ -6125,15 +6125,15 @@
       </c>
     </row>
     <row r="88" ht="162" customHeight="1" s="49">
-      <c r="A88" s="57" t="n">
+      <c r="A88" s="57">
         <v>1910</v>
       </c>
-      <c r="B88" s="57" t="n">
-        <v>1999</v>
+      <c r="B88" s="57">
+        <v>1993</v>
       </c>
       <c r="C88" s="60" t="inlineStr">
         <is>
-          <t>1910 – 1999</t>
+          <t xml:space="preserve">1910 – 1993</t>
         </is>
       </c>
       <c r="D88" s="60" t="inlineStr">
@@ -10036,6 +10036,65 @@
         </is>
       </c>
       <c r="O153"/>
+    </row>
+    <row r="154" ht="176.25" customHeight="1" s="49">
+      <c r="A154" s="47">
+        <v>1937</v>
+      </c>
+      <c r="B154" s="47">
+        <v>2026</v>
+      </c>
+      <c r="C154" s="47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1937 – 2026</t>
+        </is>
+      </c>
+      <c r="D154" s="47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Éliane ESCOUBAS</t>
+        </is>
+      </c>
+      <c r="E154" s="85" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/%C3%89liane_Escoubas"  style="color:#6A142A"  title=" Wikipedia"&gt;Éliane ESCOUBAS&lt;/a&gt;  est une philosophe française, historienne de la philosophie et traductrice. Elle se rattache à l’école phénoménologique et travaille principalement sur la philosophie allemande, la phénoménologie de l’art et la psychiatrie phénoménologique, dite Daseinsanalyse. Après une formation marquée par les cours de Gérard Granel sur Husserl, Kant et Hegel à Toulouse, elle enseigne dans le secondaire puis devient maître de conférences, puis professeur de philosophie, tout en menant des recherches au CNRS et en participant à la création du Collège international de Philosophie. &lt;/p&gt; &lt;p&gt; Elle met au centre la phénoménologie de l’expérience sensible, en particulier la manière dont le monde et le sujet adviennent à travers le sentir, l’affect et la perception. Elle montre que la phénoménologie fournit un prisme particulièrement adapté pour penser l’esthétique, car l’œuvre d’art apparaît comme un mode privilégié pour saisir comment le sujet et le monde se co‑constituent dans une expérience sensible et existentielle. &lt;/p&gt; &lt;p&gt; Une grande partie de son œuvre est consacrée à une « esthétique du sentir » où l’art n’est pas seulement une illustration de la philosophie, mais un mode de connaissance autonome. Dans ses travaux comme Imago mundi. Topologie de l’art ou L’invention de l’art, elle montre que l’image et l’œuvre picturale ne se réduisent pas à « représentation » ou « signe », mais relèvent d’une apparition du monde lui‑même, d’une spatialité et d’une temporalité qui précèdent les catégories classiques de l’objet. &lt;/p&gt; &lt;p&gt; Sa philosophie s’ouvre aussi à la phénoménologie clinique et à la psychiatrie, notamment à travers la Daseinsanalyse et la place de l’affect et de l’affectivité dans la constitution du sujet. En explorant les affectivités dans la modernité et la phénoménologie, Escoubas prolonge ainsi une réflexion sur la manière dont le vécu, le corps et la subjectivité forment un champ de savoir propre, à la fois esthétique, analytique et existentiel. Elle meurt à Paris le 18 juillet 2026. &lt;/p&gt;  &lt;audio controls title="Alain BADIOU par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/10080-25.11.2011-ITEMA_20320112-2011C3403E0190-ITE_00047070_RSCE-21.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt; 
+</t>
+        </is>
+      </c>
+      <c r="H154" s="48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/eescoubas-mini.webp</t>
+        </is>
+      </c>
+      <c r="I154" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://laphilo.fr/photo/escoubas.webp</t>
+        </is>
+      </c>
+      <c r="J154" s="48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">esthetique ; epistemologie</t>
+        </is>
+      </c>
+      <c r="K154" s="48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Phénoménologie</t>
+        </is>
+      </c>
+      <c r="L154" s="48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">philosophe française, historienne de la philosophie et traductrice.</t>
+        </is>
+      </c>
+      <c r="M154" t="inlineStr">
+        <is>
+          <t xml:space="preserve">femme</t>
+        </is>
+      </c>
+      <c r="N154" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="1048566" ht="12.75" customHeight="1" s="49"/>
     <row r="1048567" ht="12.75" customHeight="1" s="49"/>

--- a/data/frise-philosophes-france.xlsx
+++ b/data/frise-philosophes-france.xlsx
@@ -8550,1016 +8550,1021 @@
         </is>
       </c>
     </row>
-    <row r="128" ht="185.25" customHeight="1" s="49">
-      <c r="A128" s="57" t="n">
+    <row r="128" ht="176.25" customHeight="1" s="49">
+      <c r="A128" s="47">
+        <v>1937</v>
+      </c>
+      <c r="B128" s="47">
+        <v>2026</v>
+      </c>
+      <c r="C128" s="47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1937 – 2026</t>
+        </is>
+      </c>
+      <c r="D128" s="47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Éliane ESCOUBAS</t>
+        </is>
+      </c>
+      <c r="E128" s="85" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/%C3%89liane_Escoubas"  style="color:#6A142A"  title=" Wikipedia"&gt;Éliane ESCOUBAS&lt;/a&gt;  est une philosophe française, historienne de la philosophie et traductrice. Elle se rattache à l’école phénoménologique et travaille principalement sur la philosophie allemande, la phénoménologie de l’art et la psychiatrie phénoménologique, dite Daseinsanalyse. Après une formation marquée par les cours de Gérard Granel sur Husserl, Kant et Hegel à Toulouse, elle enseigne dans le secondaire puis devient maître de conférences, puis professeur de philosophie, tout en menant des recherches au CNRS et en participant à la création du Collège international de Philosophie. &lt;/p&gt; &lt;p&gt; Elle met au centre la phénoménologie de l’expérience sensible, en particulier la manière dont le monde et le sujet adviennent à travers le sentir, l’affect et la perception. Elle montre que la phénoménologie fournit un prisme particulièrement adapté pour penser l’esthétique, car l’œuvre d’art apparaît comme un mode privilégié pour saisir comment le sujet et le monde se co‑constituent dans une expérience sensible et existentielle. &lt;/p&gt; &lt;p&gt; Une grande partie de son œuvre est consacrée à une « esthétique du sentir » où l’art n’est pas seulement une illustration de la philosophie, mais un mode de connaissance autonome. Dans ses travaux comme Imago mundi. Topologie de l’art ou L’invention de l’art, elle montre que l’image et l’œuvre picturale ne se réduisent pas à « représentation » ou « signe », mais relèvent d’une apparition du monde lui‑même, d’une spatialité et d’une temporalité qui précèdent les catégories classiques de l’objet. &lt;/p&gt; &lt;p&gt; Sa philosophie s’ouvre aussi à la phénoménologie clinique et à la psychiatrie, notamment à travers la Daseinsanalyse et la place de l’affect et de l’affectivité dans la constitution du sujet. En explorant les affectivités dans la modernité et la phénoménologie, Escoubas prolonge ainsi une réflexion sur la manière dont le vécu, le corps et la subjectivité forment un champ de savoir propre, à la fois esthétique, analytique et existentiel. Elle meurt à Paris le 18 juillet 2026. &lt;/p&gt;  &lt;audio controls title="Eliane ESCOUBAS par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/10080-25.11.2011-ITEMA_20320112-2011C3403E0190-ITE_00047070_RSCE-21.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;</t>
+        </is>
+      </c>
+      <c r="H128" s="48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/eescoubas-mini.webp</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://laphilo.fr/photo/escoubas.webp</t>
+        </is>
+      </c>
+      <c r="J128" s="48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">esthetique ; epistemologie</t>
+        </is>
+      </c>
+      <c r="K128" s="48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Phénoménologie</t>
+        </is>
+      </c>
+      <c r="L128" s="48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">philosophe française, historienne de la philosophie et traductrice.</t>
+        </is>
+      </c>
+      <c r="M128" t="inlineStr">
+        <is>
+          <t xml:space="preserve">femme</t>
+        </is>
+      </c>
+      <c r="N128" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+    </row>
+    <row r="129" ht="185.25" customHeight="1" s="49">
+      <c r="A129" s="57" t="n">
         <v>1938</v>
       </c>
-      <c r="B128" s="57" t="inlineStr">
+      <c r="B129" s="57" t="inlineStr">
         <is>
           <t>2017</t>
         </is>
       </c>
-      <c r="C128" s="57" t="inlineStr">
+      <c r="C129" s="57" t="inlineStr">
         <is>
           <t>1938 – 2017</t>
         </is>
       </c>
-      <c r="D128" s="58" t="inlineStr">
+      <c r="D129" s="58" t="inlineStr">
         <is>
           <t>Jean-François MARQUET</t>
         </is>
       </c>
-      <c r="E128" s="59" t="inlineStr">
+      <c r="E129" s="59" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Jean-Fran%C3%A7ois_Marquet"  title=" Wikipedia"&gt;Jean-François MARQUET&lt;/a&gt; était un philosophe français spécialiste de l'idéalisme allemand et de la mystique, connu pour ses travaux sur Schelling, Hegel, Böhme et &lt;a href="https://fr.wikipedia.org/wiki/N%C3%A9oplatonisme"  title=" neoplatonisme par Wikipedia"&gt;le néoplatonisme. &lt;/a&gt; Agrégé de philosophie et professeur à l'Université Paris-Sorbonne, il fut l'un des meilleurs connaisseurs français de Schelling et l'un des rares philosophes à s'être intéressé aux connexions entre la philosophie spéculative allemande et les traditions mystiques occidentales. &lt;/p&gt; &lt;p&gt; Sa thèse principale, &lt;em&gt;Liberté et Existence. Étude sur la formation de la philosophie de Schelling&lt;/em&gt; (1973), est une analyse rigoureuse et pénétrante du développement de la pensée de Schelling, depuis les premiers textes influencés par Fichte jusqu'à la philosophie tardive de la liberté et de la mythologie. Il y montre la cohérence profonde d'une pensée souvent jugée dispersée, en la centrant sur la problématique de la liberté comme indifférence originaire de l'être. &lt;/p&gt; &lt;p&gt; Dans &lt;em&gt;Miroirs de l'identité. La Littérature hantée par la philosophie&lt;/em&gt; (1996), il explore les relations entre philosophie et littérature à travers des auteurs comme Novalis, Kleist, Hoffmann et Nerval. Ses études sur Jakob Böhme et les thiosophes germaniques contribuèrent à ouvrir la philosophie française à des courants méconnus mais essentiels pour comprendre l'émergence de l'idéalisme allemand. Il représente un philosophe  &lt;a href="https://www.persee.fr/doc/abpo_0399-0826_1976_num_83_2_2819"  title=" les calendriers positivistes par persée"&gt;d'une rare érudition, &lt;/a&gt; capable de naviguer entre la rigueur conceptuelle et l'ouverture aux dimensions poétiques et spirituelles de la pensée. &lt;/p&gt;  &lt;audio controls title="Les strategies du secret par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/10194-14.02.2007-ITEMA_20058582-2007C3035S0033-MEM_000035816_RF-21.mp3" type="audio/mpeg" align="center"&gt;&lt;/audio&gt;  </t>
         </is>
       </c>
-      <c r="F128" s="57" t="inlineStr">
+      <c r="F129" s="57" t="inlineStr">
         <is>
           <t>W1PdYExCQRY</t>
         </is>
       </c>
-      <c r="G128" s="59" t="inlineStr">
+      <c r="G129" s="59" t="inlineStr">
         <is>
           <t>"JEAN FRANCOIS MARQUET" par Didier Doc Pilot</t>
         </is>
       </c>
-      <c r="H128" s="65" t="inlineStr">
+      <c r="H129" s="65" t="inlineStr">
         <is>
           <t>https://www.laphilo.fr/pho/jfmarquet-mini.webp</t>
         </is>
       </c>
-      <c r="J128" s="48" t="inlineStr">
+      <c r="J129" s="48" t="inlineStr">
         <is>
           <t>metaphysique</t>
         </is>
       </c>
-      <c r="K128" s="48" t="inlineStr">
+      <c r="K129" s="48" t="inlineStr">
         <is>
           <t>Phénoménologie</t>
         </is>
       </c>
-      <c r="L128" s="48" t="inlineStr">
+      <c r="L129" s="48" t="inlineStr">
         <is>
           <t>philosophe français spécialiste de l'idéalisme allemand et de la mystique.</t>
         </is>
       </c>
-      <c r="N128" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-    </row>
-    <row r="129" ht="216.75" customHeight="1" s="49">
-      <c r="A129" s="54" t="n">
+      <c r="N129" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+    </row>
+    <row r="130" ht="216.75" customHeight="1" s="49">
+      <c r="A130" s="54" t="n">
         <v>1939</v>
       </c>
-      <c r="B129" s="54" t="inlineStr">
+      <c r="B130" s="54" t="inlineStr">
         <is>
           <t>2018</t>
         </is>
       </c>
-      <c r="C129" s="54" t="inlineStr">
+      <c r="C130" s="54" t="inlineStr">
         <is>
           <t>1939 – 2018</t>
         </is>
       </c>
-      <c r="D129" s="55" t="inlineStr">
+      <c r="D130" s="55" t="inlineStr">
         <is>
           <t>Clément ROSSET</t>
         </is>
       </c>
-      <c r="E129" s="62" t="inlineStr">
+      <c r="E130" s="62" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Cl%C3%A9ment_Rosset" title=" Wikipedia"&gt;Clément ROSSET&lt;/a&gt; était un philosophe français connu pour sa pensée radicale et son style d'écriture d'une grande clarté. Son œuvre est principalement centrée sur le concept du  &lt;a href="https://www.youtube.com/watch?v=I50Jbj6uQEU" title="Clément Rosset : la réalité ne convient pas ! par Kosmos"&gt;"réel"&lt;/a&gt;  et l'incapacité ou la difficulté de l'homme à l'accepter dans sa singularité et souvent sa cruauté. &lt;/p&gt; &lt;p&gt;&lt;a href="https://www.youtube.com/watch?v=8m_kXVBdtwg"  title=" Le réel et son double, Clément Rosset, 2.2 avant-propos par Thibault BELZACQ"&gt;Le Réel sans double&lt;/a&gt; : Son idée maîtresse est que le réel est unique, singulier et dépourvu de tout "double". Il n'y a pas d'arrière-monde, pas de sens caché, pas de consolation ou d'illusion qui puisse atténuer sa nature brute. Le réel est simplement ce qui est, dans son évidence la plus nue. &lt;/p&gt; &lt;p&gt;Le Refus du double et de l'illusion : Une grande partie de son travail consiste à traquer les différentes formes d'illusions et de doubles que l'humanité crée pour  &lt;a href="https://philitt.fr/2023/09/12/clement-rosset-tout-est-sans-raison/"  title="Clément Rosset : tout est sans raison par Phillitt"&gt;échapper à la confrontation&lt;/a&gt; directe avec le réel. Ces doubles peuvent être d'ordre métaphysique, moral, psychologique, ou même esthétique.&lt;/p&gt; &lt;p&gt;&lt;a href="https://www.youtube.com/watch?v=JDcudFE_uBQ"  title="Entretien avec Pierre Dumayet (1961) par Archives"&gt;Philosophie tragique&lt;/a&gt; et Joie : Bien que sa pensée puisse sembler sombre en insistant sur la cruauté et l'absurdité du réel, il développe une philosophie que l'on qualifie souvent de "tragique" au sens nietzschéen du terme. Il ne s'agit pas de désespoir, mais plutôt de l'affirmation de la vie et du réel tels qu'ils sont, y compris dans leurs aspects les plus difficiles. &lt;/p&gt; &lt;p&gt; Il est également remarquable par son style d'écriture. Loin du jargon philosophique abscons, il privilégie une langue simple, directe et percutante. Cette clarté formelle est au service de la clarté de sa pensée, cherchant à énoncer le réel avec le moins d'interférences possible. Son œuvre, bien que parfois restée en marge des courants universitaires dominants, a marqué par sa radicalité, sa lucidité et sa défense d'une confrontation sans fard avec le réel.  &lt;/p&gt; &lt;audio controls title="Clément Rosset par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/10080-20.12.2013-ITEMA_20564152-2013C3403E0215-21.mp3" type="audio/mpeg" align="center"&gt;&lt;/audio&gt;  </t>
         </is>
       </c>
-      <c r="F129" s="54" t="inlineStr">
+      <c r="F130" s="54" t="inlineStr">
         <is>
           <t>9m6CPt4pRlw</t>
         </is>
       </c>
-      <c r="G129" s="56" t="inlineStr">
+      <c r="G130" s="56" t="inlineStr">
         <is>
           <t>"Clément Rosset (1): Heureux, malgré tout" par Camille Tassel</t>
         </is>
       </c>
-      <c r="H129" s="62" t="inlineStr">
+      <c r="H130" s="62" t="inlineStr">
         <is>
           <t>https://www.laphilo.fr/pho/rosset-mini.webp</t>
         </is>
       </c>
-      <c r="J129" s="48" t="inlineStr">
+      <c r="J130" s="48" t="inlineStr">
         <is>
           <t>metaphysique ; ethique</t>
         </is>
       </c>
-      <c r="K129" s="48" t="inlineStr">
+      <c r="K130" s="48" t="inlineStr">
         <is>
           <t>Naturalisme</t>
         </is>
       </c>
-      <c r="L129" s="48" t="inlineStr">
+      <c r="L130" s="48" t="inlineStr">
         <is>
           <t>philosophe français du tragique et de la théorie du réel.</t>
         </is>
       </c>
-      <c r="N129" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-    </row>
-    <row r="130" ht="199.5" customHeight="1" s="49">
-      <c r="A130" s="57" t="n">
+      <c r="N130" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+    </row>
+    <row r="131" ht="199.5" customHeight="1" s="49">
+      <c r="A131" s="57" t="n">
         <v>1940</v>
       </c>
-      <c r="B130" s="57" t="inlineStr">
+      <c r="B131" s="57" t="inlineStr">
         <is>
           <t>2021</t>
         </is>
       </c>
-      <c r="C130" s="57" t="inlineStr">
+      <c r="C131" s="57" t="inlineStr">
         <is>
           <t>1940 – 2021</t>
         </is>
       </c>
-      <c r="D130" s="58" t="inlineStr">
+      <c r="D131" s="58" t="inlineStr">
         <is>
           <t>Jacques BOUVERESSE</t>
         </is>
       </c>
-      <c r="E130" s="65" t="inlineStr">
+      <c r="E131" s="65" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Jacques_Bouveresse"  title=" Wikipedia"&gt;Jacques BOUVERESSE&lt;/a&gt; était un philosophe français du courant analytique, connu pour son rationalisme exigeant, son &lt;a href="https://www.youtube.com/watch?v=mfGM00nmj20"  title=" Wittgenstein et l'intériorité 一 Jacques Bouveresse par Andrea Cirla "&gt;travail sur Wittgenstein &lt;/a&gt; et sa critique des dérives du milieu intellectuel français. Il a largement contribué à introduire et stabiliser en France une philosophie soucieuse de vérité, de clarté et d’argumentation rigoureuse. &lt;/p&gt; &lt;p&gt; Ses domaines privilégiés sont la philosophie de la connaissance, des sciences, des mathématiques, de la logique, du langage, ainsi qu’une philosophie de la culture attentive à la littérature et à la critique sociale.  Il se réclame du rationalisme des Lumières et s’inspire fortement de la philosophie analytique, du Cercle de Vienne, de Frege, de Gödel et de la tradition d’Europe centrale. Wittgenstein, qu’il contribue à faire connaître en France, est l’une de ses références centrales. &lt;/p&gt; &lt;p&gt; Il défend une position rationaliste dont le prolongement éthique est ce qu’il appelle la  &lt;a href="https://www.persee.fr/doc/lgge_0458-726x_1971_num_6_21_2079" title="Langage ordinaire et philosophie par Persée "&gt;"modestie intellectuelle" &lt;/a&gt; : ne pas exagérer ce que la philosophie peut faire, refuser le pathos et le prestige facile. Il combat le relativisme, l’historicisme radical et les remises en cause globales de la notion de vérité, notamment chez certains auteurs français, tout en reconnaissant par ailleurs leur importance. &lt;/p&gt; &lt;p&gt; Sa grande thèse, "Le Mythe de l’intériorité", porte sur Wittgenstein, le langage privé, l’expérience et la signification, et a joué un rôle clé dans la réception française de Wittgenstein. Il consacre de nombreux travaux à Robert Musil et Karl Kraus, qu’il lit comme des alliés dans un combat pour l’exactitude, la critique de la bêtise et des illusions de la culture moderne. &lt;/p&gt;  &lt;audio controls title="Jacques Bouveresse, à la recherche de la clarté par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/10351-11.05.2021-ITEMA_23961779-2000C3500E0287-21.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;</t>
         </is>
       </c>
-      <c r="F130" s="57" t="inlineStr">
+      <c r="F131" s="57" t="inlineStr">
         <is>
           <t>72_NdVNiFbg</t>
         </is>
       </c>
-      <c r="G130" s="59" t="inlineStr">
+      <c r="G131" s="59" t="inlineStr">
         <is>
           <t xml:space="preserve">"Jacques Bouveresse, Prodiges et vertiges de l'analogie" par Philosophie Analytique</t>
         </is>
       </c>
-      <c r="H130" s="65" t="inlineStr">
+      <c r="H131" s="65" t="inlineStr">
         <is>
           <t>https://www.laphilo.fr/pho/bouveresse-mini.webp</t>
         </is>
       </c>
-      <c r="J130" s="48" t="inlineStr">
+      <c r="J131" s="48" t="inlineStr">
         <is>
           <t>epistemologie ; logique</t>
         </is>
       </c>
-      <c r="K130" s="48" t="inlineStr">
+      <c r="K131" s="48" t="inlineStr">
         <is>
           <t>Analytique</t>
         </is>
       </c>
-      <c r="L130" s="48" t="inlineStr">
+      <c r="L131" s="48" t="inlineStr">
         <is>
           <t>philosophe français du courant analytique d'un rationalisme exigeant.</t>
         </is>
       </c>
-      <c r="N130" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-    </row>
-    <row r="131" ht="164.25" customHeight="1" s="49">
-      <c r="A131" s="54" t="n">
-        <v>1940</v>
-      </c>
-      <c r="B131" s="54" t="inlineStr">
-        <is>
-          <t>2021</t>
-        </is>
-      </c>
-      <c r="C131" s="54" t="inlineStr">
-        <is>
-          <t>1940 – 2021</t>
-        </is>
-      </c>
-      <c r="D131" s="55" t="inlineStr">
-        <is>
-          <t>Jean-Luc NANCY</t>
-        </is>
-      </c>
-      <c r="E131" s="62" t="inlineStr">
-        <is>
-          <t>&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Jean-Luc_Nancy"  title=" Wikipedia"&gt;Jean-Luc NANCY&lt;/a&gt; était un philosophe français, agrégé de philosophie, il fut professeur à l'Université de Strasbourg jusqu'à sa retraite. Sa pensée, en dialogue constant avec Heidegger, Derrida et Lacoue-Labarthe — avec lequel il collabora étroitement — porte sur le « sens du monde », la communauté, le corps et le toucher. &lt;/p&gt; &lt;p&gt; Son œuvre est marquée par le questionnement du « with » (avec), du « being-with » heideggerien. Dans &lt;em&gt;La Communauté désoeuvrée&lt;/em&gt; (1986), il développe une pensée de la communauté qui refuse toute forme d'immanentisme ou de fusion : la communauté véritable n'est pas une substance commune, mais  &lt;a href="https://www.youtube.com/watch?v=fZK6pEAPxEw"  title="jean luc Nancy par Institut Humanités "&gt;l'exposition partagée &lt;/a&gt; de la singularité de chacun. Cette réflexion, en dialogue critique avec Blanchot et Bataille, a eu un retentissement considérable dans les débats contemporains sur la politique, la communauté et l'identité. &lt;/p&gt; &lt;p&gt; Dans &lt;em&gt;Corpus&lt;/em&gt; (1992) et &lt;em&gt;Noli me tangere&lt;/em&gt; (2003), il explore  &lt;a href="https://www.youtube.com/watch?v=1kCExw6Wp9k"  title="jean luc Nancy par Lacan TV "&gt;la philosophie du corps &lt;/a&gt; et du toucher comme modes fondamentaux de l'être-au-monde. Son essai sur le sens — &lt;em&gt;Le Sens du monde&lt;/em&gt; (1993) — aborde la question de la possibilité du sens dans un monde déserté par les transcendances. &lt;em&gt;L'Intrus&lt;/em&gt; (2000), bref récit autobiographique sur sa transplantation cardiaque, mêle réflexion philosophique et expérience personnelle de la maladie et de l'altérité. Son œuvre, immense et diverse, témoigne d'une pensée vivante et rigoureuse toujours en dialogue avec la littérature, l'art et la politique. &lt;/p&gt;  &lt;audio controls title="Jean luc Nancy par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/11472-06.02.2011-ITEMA_20267545-2011C16153E0003-ITE_00040439_RSCE-21.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;</t>
-        </is>
-      </c>
-      <c r="F131" s="54" t="inlineStr">
-        <is>
-          <t>0ONnn-EL0BA</t>
-        </is>
-      </c>
-      <c r="G131" s="56" t="inlineStr">
-        <is>
-          <t>"Jean-Luc Nancy, philosophe à l'intelligence sensible" par France Culture</t>
-        </is>
-      </c>
-      <c r="H131" s="62" t="inlineStr">
-        <is>
-          <t>https://www.laphilo.fr/pho/jlnancy-mini.webp</t>
-        </is>
-      </c>
-      <c r="J131" s="48" t="inlineStr">
-        <is>
-          <t>metaphysique ; politique</t>
-        </is>
-      </c>
-      <c r="K131" s="48" t="inlineStr">
-        <is>
-          <t>Post-structuralisme</t>
-        </is>
-      </c>
-      <c r="L131" s="48" t="inlineStr">
-        <is>
-          <t>philosophe français qui porta le « sens du monde », la communauté, le corps et le toucher.</t>
-        </is>
-      </c>
       <c r="N131" t="inlineStr">
         <is>
           <t xml:space="preserve">occident</t>
         </is>
       </c>
     </row>
-    <row r="132" ht="201" customHeight="1" s="49">
+    <row r="132" ht="164.25" customHeight="1" s="49">
       <c r="A132" s="54" t="n">
         <v>1940</v>
       </c>
-      <c r="B132" s="54" t="n">
+      <c r="B132" s="54" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="C132" s="54" t="inlineStr">
+        <is>
+          <t>1940 – 2021</t>
+        </is>
+      </c>
+      <c r="D132" s="55" t="inlineStr">
+        <is>
+          <t>Jean-Luc NANCY</t>
+        </is>
+      </c>
+      <c r="E132" s="62" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Jean-Luc_Nancy"  title=" Wikipedia"&gt;Jean-Luc NANCY&lt;/a&gt; était un philosophe français, agrégé de philosophie, il fut professeur à l'Université de Strasbourg jusqu'à sa retraite. Sa pensée, en dialogue constant avec Heidegger, Derrida et Lacoue-Labarthe — avec lequel il collabora étroitement — porte sur le « sens du monde », la communauté, le corps et le toucher. &lt;/p&gt; &lt;p&gt; Son œuvre est marquée par le questionnement du « with » (avec), du « being-with » heideggerien. Dans &lt;em&gt;La Communauté désoeuvrée&lt;/em&gt; (1986), il développe une pensée de la communauté qui refuse toute forme d'immanentisme ou de fusion : la communauté véritable n'est pas une substance commune, mais  &lt;a href="https://www.youtube.com/watch?v=fZK6pEAPxEw"  title="jean luc Nancy par Institut Humanités "&gt;l'exposition partagée &lt;/a&gt; de la singularité de chacun. Cette réflexion, en dialogue critique avec Blanchot et Bataille, a eu un retentissement considérable dans les débats contemporains sur la politique, la communauté et l'identité. &lt;/p&gt; &lt;p&gt; Dans &lt;em&gt;Corpus&lt;/em&gt; (1992) et &lt;em&gt;Noli me tangere&lt;/em&gt; (2003), il explore  &lt;a href="https://www.youtube.com/watch?v=1kCExw6Wp9k"  title="jean luc Nancy par Lacan TV "&gt;la philosophie du corps &lt;/a&gt; et du toucher comme modes fondamentaux de l'être-au-monde. Son essai sur le sens — &lt;em&gt;Le Sens du monde&lt;/em&gt; (1993) — aborde la question de la possibilité du sens dans un monde déserté par les transcendances. &lt;em&gt;L'Intrus&lt;/em&gt; (2000), bref récit autobiographique sur sa transplantation cardiaque, mêle réflexion philosophique et expérience personnelle de la maladie et de l'altérité. Son œuvre, immense et diverse, témoigne d'une pensée vivante et rigoureuse toujours en dialogue avec la littérature, l'art et la politique. &lt;/p&gt;  &lt;audio controls title="Jean luc Nancy par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/11472-06.02.2011-ITEMA_20267545-2011C16153E0003-ITE_00040439_RSCE-21.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;</t>
+        </is>
+      </c>
+      <c r="F132" s="54" t="inlineStr">
+        <is>
+          <t>0ONnn-EL0BA</t>
+        </is>
+      </c>
+      <c r="G132" s="56" t="inlineStr">
+        <is>
+          <t>"Jean-Luc Nancy, philosophe à l'intelligence sensible" par France Culture</t>
+        </is>
+      </c>
+      <c r="H132" s="62" t="inlineStr">
+        <is>
+          <t>https://www.laphilo.fr/pho/jlnancy-mini.webp</t>
+        </is>
+      </c>
+      <c r="J132" s="48" t="inlineStr">
+        <is>
+          <t>metaphysique ; politique</t>
+        </is>
+      </c>
+      <c r="K132" s="48" t="inlineStr">
+        <is>
+          <t>Post-structuralisme</t>
+        </is>
+      </c>
+      <c r="L132" s="48" t="inlineStr">
+        <is>
+          <t>philosophe français qui porta le « sens du monde », la communauté, le corps et le toucher.</t>
+        </is>
+      </c>
+      <c r="N132" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+    </row>
+    <row r="133" ht="201" customHeight="1" s="49">
+      <c r="A133" s="54" t="n">
+        <v>1940</v>
+      </c>
+      <c r="B133" s="54" t="n">
         <v>2007</v>
       </c>
-      <c r="C132" s="54" t="inlineStr">
+      <c r="C133" s="54" t="inlineStr">
         <is>
           <t>1940 – 2007</t>
         </is>
       </c>
-      <c r="D132" s="55" t="inlineStr">
+      <c r="D133" s="55" t="inlineStr">
         <is>
           <t>Philippe LACOUE-LABARTHE</t>
         </is>
       </c>
-      <c r="E132" s="62" t="inlineStr">
+      <c r="E133" s="62" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Philippe_Lacoue-Labarthe"  title=" Wikipedia"&gt;Philippe LACOUE-LABARTHE&lt;/a&gt; était un philosophe, critique littéraire, traducteur et théoricien français né à Tours et connu pour ses travaux sur la mimésis, le romantisme allemand, Hölderlin, Heidegger, Derrida et la relation entre esthétique et politique. Il a aussi beaucoup compté dans le milieu intellectuel de Strasbourg, où il a enseigné longtemps et travaillé avec Jean-Luc Nancy. &lt;/p&gt; &lt;p&gt; Son  &lt;a href="https://maitron.fr/lacoue-labarthe-philippe/"  title=" lacoue-labarthe par le maitron"&gt;œuvre interroge &lt;/a&gt; la façon dont l’art, la philosophie et la politique s’entrecroisent, notamment à travers la notion de mimésis et la critique de l’“esthétisation du politique”. Il a aussi travaillé sur le romantisme allemand et sur la réception de Hölderlin, qu’il considérait comme une figure majeure. &lt;/p&gt; &lt;p&gt; Parmi les livres souvent cités, on trouve Le Titre de la lettre avec Jean-Luc Nancy, L’Absolu littéraire, L’Imitation des modernes, La Fiction du politique et Heidegger, la politique du poème. Il a également traduit plusieurs auteurs allemands majeurs, dont Heidegger, Hölderlin, Nietzsche, Benjamin et Celan. &lt;/p&gt; &lt;p&gt; Sa pensée tourne autour de trois idées principales : La représentation n’est jamais transparente : ce que nous montrons, racontons ou jouons n’est jamais la réalité elle-même, mais une forme, un masque, une imitation. La littérature et le théâtre sont essentiels pour comprendre la philosophie, parce qu’ils révèlent ce que les concepts cachent ou simplifient.popups. Le lien entre esthétique et politique est dangereux : il a beaucoup réfléchi à la manière dont l’art, les mythes et les images peuvent servir le politique, y compris dans des formes fascisantes. &lt;/p&gt; 
  &lt;audio controls title="les versions de philippe lacoue labarthe par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/16409-16.03.2007-ITEMA_20062386-2007C6409S0011-MEM_000036772_RF-21.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;  </t>
         </is>
       </c>
-      <c r="F132" s="54" t="inlineStr">
+      <c r="F133" s="54" t="inlineStr">
         <is>
           <t>CI6zYPSwsoY</t>
         </is>
       </c>
-      <c r="G132" s="56" t="inlineStr">
+      <c r="G133" s="56" t="inlineStr">
         <is>
           <t>voyage a tubingen par capuseen</t>
         </is>
       </c>
-      <c r="H132" s="62" t="inlineStr">
+      <c r="H133" s="62" t="inlineStr">
         <is>
           <t>https://www.laphilo.fr/pho/pllabarthe-mini.webp</t>
         </is>
       </c>
-      <c r="J132" s="48" t="inlineStr">
+      <c r="J133" s="48" t="inlineStr">
         <is>
           <t>politique ; epistemologie</t>
         </is>
       </c>
-      <c r="K132" s="48" t="inlineStr">
+      <c r="K133" s="48" t="inlineStr">
         <is>
           <t>Déconstructionnisme</t>
         </is>
       </c>
-      <c r="L132" s="85" t="inlineStr">
+      <c r="L133" s="85" t="inlineStr">
         <is>
           <t xml:space="preserve"> philosophe et théoricien français connu pour ses travaux sur la mimésis et le romantisme allemand.</t>
         </is>
       </c>
-      <c r="N132" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-    </row>
-    <row r="133" ht="209.25" customHeight="1" s="49">
-      <c r="A133" s="57" t="n">
+      <c r="N133" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+    </row>
+    <row r="134" ht="209.25" customHeight="1" s="49">
+      <c r="A134" s="57" t="n">
         <v>1941</v>
       </c>
-      <c r="B133" s="57" t="inlineStr">
+      <c r="B134" s="57" t="inlineStr">
         <is>
           <t>2019</t>
         </is>
       </c>
-      <c r="C133" s="57" t="inlineStr">
+      <c r="C134" s="57" t="inlineStr">
         <is>
           <t>1941 – 2019</t>
         </is>
       </c>
-      <c r="D133" s="58" t="inlineStr">
+      <c r="D134" s="58" t="inlineStr">
         <is>
           <t>François DELAPORTE</t>
         </is>
       </c>
-      <c r="E133" s="59" t="inlineStr">
+      <c r="E134" s="59" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Fran%C3%A7ois_Delaporte"  title=" Wikipedia"&gt;François DELAPORTE&lt;/a&gt; était un philosophe français spécialiste d'histoire et de philosophie des sciences médicales et biologiques, connu notamment pour ses travaux sur l'histoire des maladies et la philosophie de Georges Canguilhem. Professeur à l'Université de Picardie, il fut l'un des continuateurs de la tradition canguilhémienne d'histoire et philosophie des sciences en France, appliquant cette approche à l'histoire de la médecine et de la biologie. &lt;/p&gt; &lt;p&gt; Son œuvre la plus importante, &lt;em&gt;   &lt;a href="https://www.persee.fr/doc/bec_0373-6237_1993_num_151_2_450700_t1_0415_0000_001"  title=" le savoir sur la maladie par persée"&gt;Le Savoir de la maladie. &lt;/a&gt; Essai sur le choléra de 1832 à Paris&lt;/em&gt; (1990), est une analyse philosophique de l'épidémie de choléra qui ravagea Paris en 1832. Suivant la méthode de Canguilhem et Foucault, il montre comment la compréhension d'une maladie est toujours insérée dans un réseau de savoirs, de pratiques et de pouvoirs qui configurent sa signification médicale et sociale. Cette étude est un modèle du genre pour l'articulation entre histoire des sciences et analyse philosophique. &lt;/p&gt; &lt;p&gt; Il contribua également à faire connaître la pensée de Canguilhem, notamment à travers des études sur &lt;em&gt;Le Normal et le Pathologique&lt;/em&gt; et sur la philosophie biologique canguilhémienne. Ses travaux sur l'histoire des figures du visage, réunis dans &lt;em&gt;Figures de la médecine&lt;/em&gt; (2009), constituent une autre contribution originale à l'intersection de l'histoire de l'art médical et de la philosophie du corps. Delaporte incarne une tradition française de philosophie de la médecine d'une grande rigueur et d'une réelle originalité. &lt;/p&gt;   &lt;audio controls title="François Laporte le vie monastique, pensée en mouvement  par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/11983-19.12.2013-ITEMA_20563752-2013C18137S0353-25.m4a" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;  </t>
         </is>
       </c>
-      <c r="F133" s="57" t="inlineStr">
+      <c r="F134" s="57" t="inlineStr">
         <is>
           <t>Y3FnglRhPxs</t>
         </is>
       </c>
-      <c r="G133" s="59" t="inlineStr">
+      <c r="G134" s="59" t="inlineStr">
         <is>
           <t>"François DELAPORTE 2014" par Colin Guillaume</t>
         </is>
       </c>
-      <c r="H133" s="65" t="inlineStr">
+      <c r="H134" s="65" t="inlineStr">
         <is>
           <t>https://www.laphilo.fr/pho/fdelaporte-mini.webp</t>
         </is>
       </c>
-      <c r="J133" s="48" t="inlineStr">
+      <c r="J134" s="48" t="inlineStr">
         <is>
           <t>epistemologie</t>
         </is>
       </c>
-      <c r="K133" s="48" t="inlineStr">
+      <c r="K134" s="48" t="inlineStr">
         <is>
           <t>Constructivisme</t>
         </is>
       </c>
-      <c r="L133" s="48" t="inlineStr">
+      <c r="L134" s="48" t="inlineStr">
         <is>
           <t>philosophe français spécialiste de philosophie des sciences médicales et biologiques.</t>
         </is>
       </c>
-      <c r="N133" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-    </row>
-    <row r="134" ht="218.25" customHeight="1" s="49">
-      <c r="A134" s="54" t="n">
+      <c r="N134" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+    </row>
+    <row r="135" ht="218.25" customHeight="1" s="49">
+      <c r="A135" s="54" t="n">
         <v>1944</v>
       </c>
-      <c r="B134" s="54" t="inlineStr">
+      <c r="B135" s="54" t="inlineStr">
         <is>
           <t>2022</t>
         </is>
       </c>
-      <c r="C134" s="54" t="inlineStr">
+      <c r="C135" s="54" t="inlineStr">
         <is>
           <t>1944 – 2022</t>
         </is>
       </c>
-      <c r="D134" s="55" t="inlineStr">
+      <c r="D135" s="55" t="inlineStr">
         <is>
           <t>Dominique LECOURT</t>
         </is>
       </c>
-      <c r="E134" s="63" t="inlineStr">
+      <c r="E135" s="63" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Dominique_Lecourt" title=" Wikipedia"&gt;Dominique LECOURT&lt;/a&gt; était un philosophe français connu pour ses travaux en philosophie des sciences et pour avoir prolongé, de manière originale, l’héritage de Gaston Bachelard et de Georges Canguilhem. Sa philosophie se déploie autour de la philosophie des sciences, des rapports entre savoir et pouvoir, et d’une réflexion éthique et politique sur la technoscience. &lt;/p&gt; &lt;p&gt; Disciple de Bachelard, il défend un "rationalisme appliqué" : la raison scientifique n’est pas une abstraction pure, mais une activité qui se confronte à des obstacles, des erreurs, des idéologies, et qui progresse en les surmontant. Dans cet esprit, il insiste sur le rôle des   &lt;a href="https://www.youtube.com/watch?v=YyntmVUC1wE"  title=" D Lecourt par booksmag"&gt;"obstacles épistémologiques" &lt;/a&gt;  qui déroutent la recherche et qu’il faut analyser pour comprendre les progrès de la science. Il montre aussi que l’imagination n’est pas l’ennemie de la science : elle est indispensable à l’invention scientifique autant qu’à la rigueur des démonstrations. &lt;/p&gt; &lt;p&gt; Il cherche à contrer à la fois  l’"arrogance du scientisme"  et la technophobie ou le catastrophisme qui voient dans la technique uniquement une menace. Pour lui, la philosophie des sciences doit donner les moyens de penser la puissance des technosciences sans la sacraliser ni la diaboliser. Cela implique un dialogue étroit avec les scientifiques, mais aussi avec les juristes, médecins, sociologues, responsables politiques, pour éclairer les choix collectifs. &lt;/p&gt; &lt;p&gt; Il développe une conception de la liberté qui refuse aussi bien l’individualisme égoïste que le "moralisme libertaire". La liberté, pour lui, se joue dans le rapport aux savoirs et aux techniques : il s’agit d’en faire des instruments d’émancipation plutôt que de domination.&lt;/p&gt; &lt;p&gt; Parmi ses nombreux livres (plus d’une trentaine), on peut citer : -"Lyssenko, histoire réelle d’une "science prolétarienne" : analyse de la manipulation politique de la biologie en URSS. "L’Amérique entre la Bible et Darwin" : sur les tensions entre science et religion aux États‑Unis. "Contre la peur" : proposition d’une éthique de la recherche qui affirme la valeur de l’esprit critique face aux discours alarmistes. &lt;a href="https://www.youtube.com/watch?v=3e2K5Ogywl4"  title=" De quoi le transhumanisme est-il le nom ? par Editions M-Editer"&gt;"Humain post‑humain" &lt;/a&gt;  : réflexion sur les promesses et les dangers du transhumanisme. &lt;/p&gt;   &lt;audio controls title="L'age de la peur par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/10075-03.03.2010-ITEMA_20218172-2010C6608S0062-NET_E99ABA70-9EA1-4399-B0F4-9460EA040C60-21.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;  </t>
         </is>
       </c>
-      <c r="F134" s="54" t="inlineStr">
+      <c r="F135" s="54" t="inlineStr">
         <is>
           <t>YyntmVUC1wE</t>
         </is>
       </c>
-      <c r="G134" s="56" t="inlineStr">
+      <c r="G135" s="56" t="inlineStr">
         <is>
           <t>"D Lecourt" par Booksmag</t>
         </is>
       </c>
-      <c r="H134" s="62" t="inlineStr">
+      <c r="H135" s="62" t="inlineStr">
         <is>
           <t>https://www.laphilo.fr/pho/lecourt-mini.webp</t>
         </is>
       </c>
-      <c r="J134" s="48" t="inlineStr">
+      <c r="J135" s="48" t="inlineStr">
         <is>
           <t>epistemologie</t>
         </is>
       </c>
-      <c r="K134" s="48" t="inlineStr">
+      <c r="K135" s="48" t="inlineStr">
         <is>
           <t>Marxisme ; Constructivisme</t>
         </is>
       </c>
-      <c r="L134" s="48" t="inlineStr">
+      <c r="L135" s="48" t="inlineStr">
         <is>
           <t>philosophe français connu pour ses travaux en philosophie des sciences.</t>
         </is>
       </c>
-      <c r="N134" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-    </row>
-    <row r="135" ht="157.5" customHeight="1" s="49">
-      <c r="A135" s="57" t="n">
+      <c r="N135" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+    </row>
+    <row r="136" ht="157.5" customHeight="1" s="49">
+      <c r="A136" s="57" t="n">
         <v>1945</v>
       </c>
-      <c r="B135" s="57" t="inlineStr">
+      <c r="B136" s="57" t="inlineStr">
         <is>
           <t>2006</t>
         </is>
       </c>
-      <c r="C135" s="57" t="inlineStr">
+      <c r="C136" s="57" t="inlineStr">
         <is>
           <t>1945 – 2006</t>
         </is>
       </c>
-      <c r="D135" s="58" t="inlineStr">
+      <c r="D136" s="58" t="inlineStr">
         <is>
           <t>Jean-Michel BERTHELOT</t>
         </is>
       </c>
-      <c r="E135" s="65" t="inlineStr">
+      <c r="E136" s="65" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Jean-Michel_Berthelot"  title=" Wikipedia"&gt;Jean-Michel BERTHELOT&lt;/a&gt; était un philosophe et sociologue français spécialiste d'épistémologie des sciences sociales. Professeur à l'Université de Paris IV-Sorbonne et à l'Université du Québec à Montréal, il contribua de manière décisive à la réflexion philosophique sur les fondements et les méthodes des sciences humaines et sociales. Son œuvre joint la rigueur épistémologique à une large culture philosophique et sociologique. &lt;/p&gt; &lt;p&gt; Son ouvrage principal, &lt;em&gt; &lt;a href="https://www.persee.fr/doc/sotra_0038-0296_1992_num_34_3_2605_t1_0388_0000_3"  title="l’intelligence du social par persée "&gt; L'Intelligence du social&lt;/a&gt; &lt;/em&gt; (1990), est une analyse approfondie des schèmes d'intelligibilité que les sciences sociales utilisent pour rendre compte de la réalité sociale : le schème causal, le schème fonctionnel, le schème structural, le schème herméneutique et d'autres modes d'explication. Berthelot montre que chaque paradigme sociologique privilégie un mode d'intelligibilité particulier, ce qui permet de comprendre à la fois leurs apports spécifiques et leurs limites. Ce livre constitue l'une des contributions les plus claires et les plus systématiques à la philosophie des sciences sociales en langue française. &lt;/p&gt; &lt;p&gt; Dans &lt;em&gt;Epistémologie des sciences sociales&lt;/em&gt; (2001, ouvrage collectif qu'il dirigea), il offrit un panorama complet des questions épistémologiques fondamentales que posent les sciences humaines et sociales : la causalité, la compréhension, la mesure, la modélisation, la réflexivité et les rapports entre science et valeurs. Ses travaux contribuèrent à établir l'épistémologie des sciences sociales comme une discipline à part entière dans le paysage universitaire français, en dialogue constant avec la philosophie des sciences anglophones et continentale. &lt;/p&gt;</t>
         </is>
       </c>
-      <c r="F135" s="57" t="inlineStr">
+      <c r="F136" s="57" t="inlineStr">
         <is>
           <t>032-iGqk37A</t>
         </is>
       </c>
-      <c r="G135" s="59" t="inlineStr">
+      <c r="G136" s="59" t="inlineStr">
         <is>
           <t>"JM BERTHELOT" par SFCR</t>
         </is>
       </c>
-      <c r="H135" s="65" t="inlineStr">
+      <c r="H136" s="65" t="inlineStr">
         <is>
           <t>https://www.laphilo.fr/pho/jmberthelot-mini.webp</t>
         </is>
       </c>
-      <c r="J135" s="48" t="inlineStr">
+      <c r="J136" s="48" t="inlineStr">
         <is>
           <t>epistemologie</t>
         </is>
       </c>
-      <c r="K135" s="48" t="inlineStr">
+      <c r="K136" s="48" t="inlineStr">
         <is>
           <t>Constructivisme</t>
         </is>
       </c>
-      <c r="L135" s="48" t="inlineStr">
+      <c r="L136" s="48" t="inlineStr">
         <is>
           <t>philosophe et sociologue français spécialiste d'épistémologie des sciences sociales.</t>
         </is>
       </c>
-      <c r="N135" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-    </row>
-    <row r="136" ht="166.5" customHeight="1" s="49">
-      <c r="A136" s="54" t="n">
+      <c r="N136" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+    </row>
+    <row r="137" ht="166.5" customHeight="1" s="49">
+      <c r="A137" s="54" t="n">
         <v>1946</v>
       </c>
-      <c r="B136" s="54" t="inlineStr">
+      <c r="B137" s="54" t="inlineStr">
         <is>
           <t>2010</t>
         </is>
       </c>
-      <c r="C136" s="54" t="inlineStr">
+      <c r="C137" s="54" t="inlineStr">
         <is>
           <t>1946 – 2010</t>
         </is>
       </c>
-      <c r="D136" s="55" t="inlineStr">
+      <c r="D137" s="55" t="inlineStr">
         <is>
           <t>Daniel BENSAÏD</t>
         </is>
       </c>
-      <c r="E136" s="62" t="inlineStr">
+      <c r="E137" s="62" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Daniel_Bensa%C3%AFd"  title=" Wikipedia"&gt;Daniel BENSAÏD&lt;/a&gt; était un philosophe français marxiste, l'un des intellectuels les plus importants de la gauche radicale française de son époque. Né à Paris dans une famille juive d'origine algérienne, il fut l'un des leaders de la révolte étudiante de mai 1968 à Paris-Nanterre aux côtés de Daniel Cohn-Bendit. Professeur de philosophie à l'Université Paris VIII-Saint-Denis, il fut membre dirigeant de la Ligue communiste révolutionnaire (LCR) et de son successeur le Nouveau Parti Anticapitaliste (NPA). &lt;/p&gt; &lt;p&gt; Sa pensée philosophique chercha à renouveler le marxisme en le débarrassant des &lt;a href="https://www.youtube.com/watch?v=uxBvxfRI2CE"  title="la privatisation du monde par bibou11slalala "&gt; simplifications téléologiques &lt;/a&gt; et en l'ouvrant à des problématiques nouvelles. Dans &lt;em&gt;Marx l'intempestif&lt;/em&gt; (1995), il défend un Marx débarrassé du déterminisme historique et de la philosophie du progrès, un Marx « intempestif » qui pense la politique comme art du possible et de l'impossible, en dialogue avec Blaise Pascal et Walter Benjamin. Ce livre renouvela profondément la  &lt;a href="https://www.youtube.com/watch?v=is8Ya038-Q4"  title="l’héritage de Marx par socialtram "&gt; lecture de Marx &lt;/a&gt; dans la gauche française. &lt;/p&gt; &lt;p&gt; Dans &lt;em&gt;Le Pari mélancolique&lt;/em&gt; (1997) et &lt;em&gt;Résistances&lt;/em&gt; (2001), il développe une philosophie de l'engagement politique nourrie par la mélancolie des défaites mais portée par une fidélité irréductible à l'émancipation. Sa réflexion sur les rapports entre philosophie et politique, entre utopie et stratégie, constitue l'une des contributions les plus originales à la pensée marxiste contemporaine. Polémiste redoutable et pédagogue exigeant, il laissa une empreinte profonde sur plusieurs générations de militants et d'intellectuels de gauche. &lt;/p&gt;  &lt;audio controls title="Daniel Bensaid  par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/10075-11.12.2006-ITEMA_20049670-2006C6608S0221-MEM_000033324_RF-21.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt; </t>
         </is>
       </c>
-      <c r="F136" s="54" t="inlineStr">
+      <c r="F137" s="54" t="inlineStr">
         <is>
           <t>xFJLPfAwApo</t>
         </is>
       </c>
-      <c r="G136" s="56" t="inlineStr">
+      <c r="G137" s="56" t="inlineStr">
         <is>
           <t>"Daniel Bensaïd sur l'idée du communisme" par Videos Politiques</t>
         </is>
       </c>
-      <c r="H136" s="62" t="inlineStr">
+      <c r="H137" s="62" t="inlineStr">
         <is>
           <t>https://www.laphilo.fr/pho/bensaid-mini.webp</t>
         </is>
       </c>
-      <c r="J136" s="48" t="inlineStr">
+      <c r="J137" s="48" t="inlineStr">
         <is>
           <t>politique</t>
         </is>
       </c>
-      <c r="K136" s="48" t="inlineStr">
+      <c r="K137" s="48" t="inlineStr">
         <is>
           <t>Marxisme</t>
         </is>
       </c>
-      <c r="L136" s="48" t="inlineStr">
+      <c r="L137" s="48" t="inlineStr">
         <is>
           <t>philosophe français marxiste, intellectuel important de la gauche radicale française.</t>
         </is>
       </c>
-      <c r="M136" t="inlineStr">
+      <c r="M137" t="inlineStr">
         <is>
           <t xml:space="preserve">juive</t>
         </is>
       </c>
-      <c r="N136" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-    </row>
-    <row r="137" ht="210" customHeight="1" s="49">
-      <c r="A137" s="57" t="n">
+      <c r="N137" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+    </row>
+    <row r="138" ht="210" customHeight="1" s="49">
+      <c r="A138" s="57" t="n">
         <v>1947</v>
       </c>
-      <c r="B137" s="57" t="inlineStr">
+      <c r="B138" s="57" t="inlineStr">
         <is>
           <t>2022</t>
         </is>
       </c>
-      <c r="C137" s="57" t="inlineStr">
+      <c r="C138" s="57" t="inlineStr">
         <is>
           <t>1947 - 2022</t>
         </is>
       </c>
-      <c r="D137" s="58" t="inlineStr">
+      <c r="D138" s="58" t="inlineStr">
         <is>
           <t>Bruno LATOUR</t>
         </is>
       </c>
-      <c r="E137" s="59" t="inlineStr">
+      <c r="E138" s="59" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Bruno_Latour"  title=" Wikipedia"&gt;Bruno LATOUR&lt;/a&gt;  est un sociologue, anthropologue et philosophe français connu pour ses travaux sur la sociologie des sciences, la philosophie des sciences et l'anthropologie des modernes.&lt;/p&gt; &lt;p&gt; L'un des concepts clés développés par Latour est celui de l'acteur-réseau, également connu sous le nom de &lt;a href="https://fr.wikipedia.org/wiki/Th%C3%A9orie_de_l%27acteur-r%C3%A9seau"  title="Théorie de l'acteur-réseau par Wikipedia "&gt; théorie de l'acteur-réseau (ANT)&lt;/a&gt;. Selon cette approche, les acteurs humains et non humains sont considérés comme des "actants" qui agissent en collaboration pour produire des réalités sociales complexes. L'ANT remet en question la distinction traditionnelle entre les sujets humains et les objets inanimés, soulignant plutôt les relations et les interactions entre eux. &lt;/p&gt; &lt;p&gt; Il s'est  intéressé aux enjeux environnementaux et a contribué au développement de l'écologie politique. Il a souligné l'importance de prendre en compte les dimensions politiques et sociales dans la compréhension des questions écologiques et climatiques. Son livre &lt;a href="http://www.bruno-latour.fr/sites/default/files/uploads/TELERAMA.pdf"  title="Nous n'avons jamais été moderne par Bruno-Latour "&gt; "Nous n'avons jamais été modernes" &lt;/a&gt; (1991) remet en question la distinction entre nature et culture, mettant en lumière les façons dont les sciences et les technologies façonnent notre compréhension du monde. &lt;/p&gt; &lt;p&gt; En plus de ses travaux académiques, Bruno Latour a également participé à des &lt;a href="https://profondeurdechamps.com/2012/10/19/entretien-avec-bruno-latour-12-lart-et-la-science/"  title="L'art et la science par Profondeurdechamps "&gt; projets artistiques &lt;/a&gt; et curatoriaux. Il a collaboré avec des artistes contemporains et a contribué à des expositions d'art qui explorent les thèmes de la science, de la technologie et de l'environnement.&lt;/p&gt; &lt;audio controls title="Introduction à la pensée de Bruno LATOUR par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/22676-06.05.2022-ITEMA_23017705-2022F45096S0126-22.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt; </t>
         </is>
       </c>
-      <c r="F137" s="57" t="inlineStr">
+      <c r="F138" s="57" t="inlineStr">
         <is>
           <t>BqM-sk_ZLeU</t>
         </is>
       </c>
-      <c r="G137" s="65" t="inlineStr">
+      <c r="G138" s="65" t="inlineStr">
         <is>
           <t>"Ce virus est là pour nous préparer au nouveau régime climatique" par France Culture</t>
         </is>
       </c>
-      <c r="H137" s="65" t="inlineStr">
+      <c r="H138" s="65" t="inlineStr">
         <is>
           <t>https://www.laphilo.fr/pho/latour-mini.webp</t>
         </is>
       </c>
-      <c r="J137" s="48" t="inlineStr">
+      <c r="J138" s="48" t="inlineStr">
         <is>
           <t>epistemologie ; politique</t>
         </is>
       </c>
-      <c r="K137" s="48" t="inlineStr">
+      <c r="K138" s="48" t="inlineStr">
         <is>
           <t>Constructivisme</t>
         </is>
       </c>
-      <c r="L137" s="48" t="inlineStr">
+      <c r="L138" s="48" t="inlineStr">
         <is>
           <t>philosophe français inscrit dans le mouvement du Nouveau Réalisme.</t>
         </is>
       </c>
-      <c r="N137" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-    </row>
-    <row r="138" ht="166.5" customHeight="1" s="49">
-      <c r="A138" s="54" t="n">
+      <c r="N138" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+    </row>
+    <row r="139" ht="166.5" customHeight="1" s="49">
+      <c r="A139" s="54" t="n">
         <v>1949</v>
       </c>
-      <c r="B138" s="54" t="inlineStr">
+      <c r="B139" s="54" t="inlineStr">
         <is>
           <t>2017</t>
         </is>
       </c>
-      <c r="C138" s="54" t="inlineStr">
+      <c r="C139" s="54" t="inlineStr">
         <is>
           <t>1949 – 2017</t>
         </is>
       </c>
-      <c r="D138" s="55" t="inlineStr">
+      <c r="D139" s="55" t="inlineStr">
         <is>
           <t>Robert DAMIEN</t>
         </is>
       </c>
-      <c r="E138" s="56" t="inlineStr">
+      <c r="E139" s="56" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Robert_Damien"  title=" Wikipedia"&gt;Robert DAMIEN&lt;/a&gt;   était un philosophe français  spécialiste de l'autorité politique et des tensions démocratiques, connu pour sa réhabilitation éthique de l'autorité comme principe d'élévation collective. Il incarna un rationalisme républicain franc et dialogique. &lt;/p&gt; &lt;p&gt; Il réfléchit aux tensions indépassables de la démocratie : décision vs connaissance, immanence vs autorité, pluralisme vs unité. L'autorité n'est pas abus ou force, mais "augmentation" (étymologiquement) : réciproque, fraternelle, légitime si elle élève sans domination, en rendant des comptes publics. Il prône un "pluralisme cohérent" (inspiré de Bachelard), un cogito relationnel et un État stratège sous souverainetés plurielles, face au déclin des absolus. &lt;/p&gt; &lt;p&gt; Joueur et &lt;a href="https://www.dailymotion.com/video/x18br7c" title="Robert Damien : de la figure de l'entraîneur à celle de Mandela par mediapart"&gt;entraîneur de rugby &lt;/a&gt; au CS Lons-le-Saunier, il intégrait le sport comme modèle philosophique du collectif et de l'autorité républicaine. Le rugby incarne pour lui une coopération interdépendante où la diversité des talents (puissants et habiles) fusionne en "Nous" : circulation du ballon prime sur l'individualisme, reliant partenaires contre adversaire. Pas de "joueurs isolés", mais des équipes où le "jeu sans ballon" (replacements, soutiens obscurs) assure continuité, révélant un "Moi nouveau" via le collectif. Dans "Activité physique et exercices spirituels" paru en 2005, le sport n'est pas idéologique mais matrice de fraternité : effort charnel révèle puissances collectives, appliquées à politique et bibliothèques (pluralité ordonnée). &lt;/p&gt;</t>
         </is>
       </c>
-      <c r="F138" s="54" t="inlineStr">
+      <c r="F139" s="54" t="inlineStr">
         <is>
           <t>iBriZ4Lhzfg</t>
         </is>
       </c>
-      <c r="G138" s="56" t="inlineStr">
+      <c r="G139" s="56" t="inlineStr">
         <is>
           <t>"robert damien les trois qualites de l autorite" par Sylvie Formero</t>
         </is>
       </c>
-      <c r="H138" s="62" t="inlineStr">
+      <c r="H139" s="62" t="inlineStr">
         <is>
           <t>https://www.laphilo.fr/pho/rdamien-mini.webp</t>
         </is>
       </c>
-      <c r="J138" s="48" t="inlineStr">
+      <c r="J139" s="48" t="inlineStr">
         <is>
           <t>politique ; epistemologie</t>
         </is>
       </c>
-      <c r="K138" s="48" t="inlineStr">
+      <c r="K139" s="48" t="inlineStr">
         <is>
           <t>Herméneutique</t>
         </is>
       </c>
-      <c r="L138" s="48" t="inlineStr">
+      <c r="L139" s="48" t="inlineStr">
         <is>
           <t>religieux français spécialiste de l'autorité politique &amp; des tensions démocratiques.</t>
         </is>
       </c>
-      <c r="N138" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-    </row>
-    <row r="139" ht="210.75" customHeight="1" s="49">
-      <c r="A139" s="57" t="n">
+      <c r="N139" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+    </row>
+    <row r="140" ht="210.75" customHeight="1" s="49">
+      <c r="A140" s="57" t="n">
         <v>1950</v>
       </c>
-      <c r="B139" s="57" t="inlineStr">
+      <c r="B140" s="57" t="inlineStr">
         <is>
           <t>2022</t>
         </is>
       </c>
-      <c r="C139" s="57" t="inlineStr">
+      <c r="C140" s="57" t="inlineStr">
         <is>
           <t>1950 – 2022</t>
         </is>
       </c>
-      <c r="D139" s="58" t="inlineStr">
+      <c r="D140" s="58" t="inlineStr">
         <is>
           <t>Catherine COLLIOT-THELENE</t>
         </is>
       </c>
-      <c r="E139" s="65" t="inlineStr">
+      <c r="E140" s="65" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Catherine_Colliot-Th%C3%A9l%C3%A8ne" title=" Wikipedia"&gt;Catherine COLLIOT-THELENE&lt;/a&gt; était une philosophe française  majeure de la philosophie politique contemporaine, spécialiste de Max Weber et penseuse des droits, de la démocratie et de la propriété dans un cadre cosmopolitique. Membre de l’Institut universitaire de France, elle est reconnue comme une référence internationale des études wébériennes. &lt;/p&gt; &lt;p&gt; Son travail se situe au croisement de la philosophie politique et des sciences sociales, avec trois pôles principaux :  &lt;a href="https://www.youtube.com/watch?v=krUYFtq9Jww" title="Max Weber et la violence légitime de l’état par France Culture"&gt;Max Weber, la démocratie et les droits, &lt;/a&gt;  la propriété et le cosmopolitisme.  Elle traduit et commente plusieurs textes de Weber, notamment Le Savant et le politique et Les Communautés, en montrant en détail ses concepts de rationalisation, de désenchantement et de domination. &lt;/p&gt; &lt;p&gt; À partir des années 2000, elle se concentre sur les droits subjectifs, leur articulation avec l’individualisme contemporain et la transformation des rapports entre pouvoirs politiques et économiques. Elle insiste sur la nécessité de penser la normativité (ce qui doit être) à partir d’une analyse précise des structures sociales réelles, d’où son dialogue constant avec le droit, l’histoire et la sociologie. &lt;/p&gt; &lt;p&gt; Dans "La Démocratie sans “demos”  paru en 2011, elle remet en question l’identification classique entre "peuple" et "démocratie". Elle critique la superposition entre souveraineté du peuple et souveraineté territoriale de l’État, qui conduit selon elle à des versions exclusives de la démocratie. &lt;a href="https://www.youtube.com/watch?v=ps2ixtEpgYI" title="la democratie c’est le droit de resistance par Journal l’Humanitét"&gt;Sa philosophie cherche &lt;/a&gt;  une démocratie fondée sur des droits universalisables et sur la participation de tous les sujets, plutôt que sur l’appartenance à une communauté nationale préconstituée. &lt;/p&gt; &lt;p&gt; Elle refuse la séparation entre théorie pure et monde social : pour elle, la philosophie politique doit dialoguer avec les sciences sociales pour produire une critique efficace des institutions et des inégalités. Elle a accompagné, sans posture militante classique mais avec une forte implication intellectuelle, les luttes pour les droits des femmes, des exclus et des étrangers, en cherchant à fournir des outils conceptuels pour penser l’égalité aujourd’hui. &lt;/p&gt; 
  &lt;audio controls title="Les défis juridiques de la migration : existe-t-il un droit à la libre circulation ? par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/21447-09.02.2022-ITEMA_22927630-2022C27677S0040-21.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;</t>
         </is>
       </c>
-      <c r="F139" s="57" t="inlineStr">
+      <c r="F140" s="57" t="inlineStr">
         <is>
           <t>g_YhgkqNE98</t>
         </is>
       </c>
-      <c r="G139" s="59" t="inlineStr">
+      <c r="G140" s="59" t="inlineStr">
         <is>
           <t>"La démocratie des droits : de Weber à Kant", entretien avec Catherine Colliot-Thélène" par Politika</t>
         </is>
       </c>
-      <c r="H139" s="65" t="inlineStr">
+      <c r="H140" s="65" t="inlineStr">
         <is>
           <t>https://www.laphilo.fr/pho/thelene-mini.webp</t>
         </is>
       </c>
-      <c r="J139" s="48" t="inlineStr">
+      <c r="J140" s="48" t="inlineStr">
         <is>
           <t>politique</t>
         </is>
       </c>
-      <c r="K139" s="48" t="inlineStr">
+      <c r="K140" s="48" t="inlineStr">
         <is>
           <t>Libéralisme</t>
         </is>
       </c>
-      <c r="L139" s="48" t="inlineStr">
+      <c r="L140" s="48" t="inlineStr">
         <is>
           <t>philosophe française majeure de la philosophie politique contemporaine.</t>
         </is>
       </c>
-      <c r="M139" t="inlineStr">
+      <c r="M140" t="inlineStr">
         <is>
           <t xml:space="preserve">femme</t>
         </is>
       </c>
-      <c r="N139" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-    </row>
-    <row r="140" ht="171.75" customHeight="1" s="49">
-      <c r="A140" s="54" t="n">
+      <c r="N140" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+    </row>
+    <row r="141" ht="171.75" customHeight="1" s="49">
+      <c r="A141" s="54" t="n">
         <v>1952</v>
       </c>
-      <c r="B140" s="54" t="inlineStr">
+      <c r="B141" s="54" t="inlineStr">
         <is>
           <t>2020</t>
         </is>
       </c>
-      <c r="C140" s="54" t="inlineStr">
+      <c r="C141" s="54" t="inlineStr">
         <is>
           <t>1952 – 2020</t>
         </is>
       </c>
-      <c r="D140" s="55" t="inlineStr">
+      <c r="D141" s="55" t="inlineStr">
         <is>
           <t xml:space="preserve">Bernard STIEGLER</t>
         </is>
       </c>
-      <c r="E140" s="56" t="inlineStr">
+      <c r="E141" s="56" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Bernard_Stiegler"  title=" Wikipedia"&gt;Bernard STIEGLER&lt;/a&gt; était un philosophe français, l'une des figures les plus originales et les plus influentes de la philosophie française. Né à Villebon-sur-Yvette, son parcours intellectuel fut marqué par une expérience singulière : il prépara sa thèse en philosophie pendant les cinq années qu'il passa en prison (1978-1983), condamné pour braquages. Docteur en philosophie sous la direction de Jacques Derrida, il fut directeur du département du développement culturel du Centre Pompidou puis directeur de l'Institut de Recherche et d'Innovation (IRI). &lt;/p&gt; &lt;p&gt; Son œuvre maîtresse, la trilogie &lt;em&gt;&lt;a href="https://www.youtube.com/watch?v=nwmOFXzCJUg" title="Bernard Stiegler a propos de la technique par Adrien Payet"&gt;La Technique et le Temps&lt;/a&gt; &lt;/em&gt; (1994-2001), constitue l'une des analyses philosophiques les plus ambitieuses de la technique et de ses effets sur la temporalité humaine. S'appuyant sur Simondon, Derrida et Heidegger, il y défend la thèse que l'être humain est fondamentalement un être technique : c'est par la technique — les « rétentions tertiaires », les objets qui externalisent la mémoire — que l'humain se constitue comme tel. La technique n'est pas un simple outil mais la condition même de la temporalité humaine et de la transmission culturelle. &lt;/p&gt; &lt;p&gt; Dans ses ouvrages ultérieurs — &lt;em&gt;De la misère symbolique&lt;/em&gt; (2004), &lt;em&gt;Prendre soin&lt;/em&gt; (2008), &lt;em&gt;États de choc&lt;/em&gt; (2012) — il  &lt;a href="https://www.youtube.com/watch?v=IOei5Kb1cQI" title="Bernard Stiegler par France 24"&gt;développa une critique &lt;/a&gt;  de l'économie de l'attention et du capitalisme des plateformes numériques, montrant comment ceux-ci détruisent les « savoirs faire » et « savoirs vivre » qui constituent le tissu de l'existence humaine. Sa pensée, nourrie d'une profonde inquiétude sur les effets destructeurs des industries culturelles et numériques, propose une pharmacologie de la technique : la technique est un pharmakon, à la fois poison et remède. &lt;/p&gt;  &lt;audio controls title="Bernard Stiegler : je reflechis au rapport entre technique et le mal  par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/13915-05.11.2017-ITEMA_21460251-5.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;</t>
         </is>
       </c>
-      <c r="F140" s="54" t="inlineStr">
+      <c r="F141" s="54" t="inlineStr">
         <is>
           <t>Q10Ski-xusk</t>
         </is>
       </c>
-      <c r="G140" s="56" t="inlineStr">
+      <c r="G141" s="56" t="inlineStr">
         <is>
           <t>"Mémoire et personnalité - Bernard Stiegler" par Obserbatoire B2V des Mémoires</t>
         </is>
       </c>
-      <c r="H140" s="62" t="inlineStr">
+      <c r="H141" s="62" t="inlineStr">
         <is>
           <t>https://www.laphilo.fr/pho/bstiegler-mini.webp</t>
         </is>
       </c>
-      <c r="J140" s="48" t="inlineStr">
+      <c r="J141" s="48" t="inlineStr">
         <is>
           <t>politique ; epistemologie</t>
         </is>
       </c>
-      <c r="K140" s="48" t="inlineStr">
+      <c r="K141" s="48" t="inlineStr">
         <is>
           <t>Post-structuralisme</t>
         </is>
       </c>
-      <c r="L140" s="48" t="inlineStr">
+      <c r="L141" s="48" t="inlineStr">
         <is>
           <t>philosophe français qui fit une analyse ambitieuse de la technique et de ses effets.</t>
         </is>
       </c>
-      <c r="N140" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-    </row>
-    <row r="141" ht="135.75" customHeight="1" s="49">
-      <c r="A141" s="57" t="n">
+      <c r="N141" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+    </row>
+    <row r="142" ht="135.75" customHeight="1" s="49">
+      <c r="A142" s="57" t="n">
         <v>1959</v>
       </c>
-      <c r="B141" s="57" t="inlineStr">
+      <c r="B142" s="57" t="inlineStr">
         <is>
           <t>2014</t>
         </is>
       </c>
-      <c r="C141" s="57" t="inlineStr">
+      <c r="C142" s="57" t="inlineStr">
         <is>
           <t>1959 – 2014</t>
         </is>
       </c>
-      <c r="D141" s="58" t="inlineStr">
+      <c r="D142" s="58" t="inlineStr">
         <is>
           <t>Bernard MABILLE</t>
         </is>
       </c>
-      <c r="E141" s="65" t="inlineStr">
+      <c r="E142" s="65" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Bernard_Mabille_(philosophe)"  style="color:#6A142A"  title=" Wikipedia"&gt;Bernard MABILLE&lt;/a&gt; était un philosophe français spécialiste de dialectique et de philosophie hégélienne, ainsi que de métaphysique contemporaine. Agrégé de philosophie et professeur à l'Université Paris IV-Sorbonne, il fut l'un des meilleurs connaisseurs français de Hegel et contribua de manière significative au renouvellement des études hégéliennes en France dans les dernières décennies du XXe siècle. &lt;/p&gt; &lt;p&gt; Sa thèse principale, &lt;em&gt;Hegel : l'épreuve de la contingence&lt;/em&gt; (1999), est une lecture originale de la philosophie hégélienne à la lumière de la problématique de la contingence. Contre les lectures qui réduisent Hegel à un penseur du nécessaire et du rationnel, Mabille montre que la contingence est au cœur même du système hégélien et que la dialectique est précisément la méthode qui permet de penser le passage du contingent au nécessaire sans l'éliminer. Cette relecture contribua à ouvrir la philosophie hégélienne à des problématiques contemporaines. &lt;/p&gt; &lt;p&gt; Dans ses travaux sur la métaphysique et la dialectique, Mabille s'intéressa également aux rapports entre la philosophie hégélienne et la phénoménologie française, notamment Merleau-Ponty et Henry. Son enseignement à la Sorbonne forma plusieurs générations d'étudiants à la rigueur de la pensée dialectique. Sa disparition prématurée priva la philosophie française d'un penseur rigoureux dont l'œuvre, bien que de volume limité, témoigne d'une lecture profonde et originale de l'idéalisme allemand et de ses prolongements contemporains. &lt;/p&gt;</t>
         </is>
       </c>
-      <c r="F141" s="57" t="inlineStr">
+      <c r="F142" s="57" t="inlineStr">
         <is>
           <t>2ZxXXD2lk_Q</t>
         </is>
       </c>
-      <c r="G141" s="59" t="inlineStr">
+      <c r="G142" s="59" t="inlineStr">
         <is>
           <t>Bernard MABILLE par La Compagnie des indes TV</t>
         </is>
       </c>
-      <c r="H141" s="65" t="inlineStr">
+      <c r="H142" s="65" t="inlineStr">
         <is>
           <t>https://www.laphilo.fr/pho/bnabille-mini.webp</t>
         </is>
       </c>
-      <c r="J141" s="48" t="inlineStr">
+      <c r="J142" s="48" t="inlineStr">
         <is>
           <t>metaphysique</t>
         </is>
       </c>
-      <c r="K141" s="48" t="inlineStr">
+      <c r="K142" s="48" t="inlineStr">
         <is>
           <t>Idéalisme allemand</t>
         </is>
       </c>
-      <c r="L141" s="48" t="inlineStr">
+      <c r="L142" s="48" t="inlineStr">
         <is>
           <t>philosophe français spécialiste de dialectique et de philosophie hégélienne.</t>
         </is>
       </c>
-      <c r="N141" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-    </row>
-    <row r="142" ht="176.25" customHeight="1" s="49">
-      <c r="A142" s="47" t="n">
+      <c r="N142" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+    </row>
+    <row r="143" ht="176.25" customHeight="1" s="49">
+      <c r="A143" s="47" t="n">
         <v>1964</v>
       </c>
-      <c r="B142" s="47" t="n">
+      <c r="B143" s="47" t="n">
         <v>2017</v>
       </c>
-      <c r="C142" s="47" t="inlineStr">
+      <c r="C143" s="47" t="inlineStr">
         <is>
           <t>1964 – 2017</t>
         </is>
       </c>
-      <c r="D142" s="47" t="inlineStr">
+      <c r="D143" s="47" t="inlineStr">
         <is>
           <t>Anne DUFOURMANTELLE</t>
         </is>
       </c>
-      <c r="E142" s="85" t="inlineStr">
+      <c r="E143" s="85" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Anne_Dufourmantelle"  title=" Wikipedia"&gt;Anne DUFOURMANTELLE&lt;/a&gt; était une philosophe et psychanalyste française dont l’œuvre, marquée par une grande finesse d’analyse, explore la vulnérabilité humaine, le risque, le secret et l’hospitalité. Bien qu’elle ne soit pas une théoricienne du &lt;a href="https://fr.wikipedia.org/wiki/Constructivisme_(%C3%A9pist%C3%A9mologie)"  title="Constructivisme par Wikipedia"&gt;« constructivisme »&lt;/a&gt;  au sens politique ou académique strict, sa pensée entre en résonance avec une réflexion sur la manière dont nous bâtissons notre rapport au monde et à l’autre. &lt;/p&gt; &lt;p&gt; Son concept d'&lt;a href="https://www.umc.org/fr/content/what-is-radical-hospitality"  title="Qu’est ce que l’hospitalité radicale par umc"&gt;« hospitalité radicale », &lt;/a&gt; nourri de ses travaux avec Jacques Derrida, propose d'accueillir l'inconnu sans conditions, voyant dans cette ouverture une forme de résistance à la fermeture du monde. Elle invite à une éthique de la rencontre où la vulnérabilité n'est pas un défaut, mais un espace de croissance mutuelle qui défie les normes sociales établies. &lt;/p&gt; &lt;p&gt; '&lt;a href="https://www.youtube.com/watch?v=QAlsJD3IAs0"  title="L’envers du feu par Librairie mollat"&gt;Dans des ouvrages &lt;/a&gt; comme Éloge du risque, elle explore la tension entre la sécurité et l'aventure de vivre, encourageant une liberté de penser et d'aimer qui dépasse les discours ambiants. Elle percevait la psychanalyse et la philosophie comme des outils pour « traquer » les mutations invisibles de notre époque et redonner du sens à nos vies intérieures. &lt;/p&gt; &lt;p&gt; Sa disparition brutale en 2017, alors qu'elle portait secours à des enfants en mer, a été perçue comme l'incarnation ultime de son engagement philosophique : une éthique en actes où le souci de l'autre devient une responsabilité immédiate. Son héritage intellectuel reste une source d'inspiration pour ceux qui cherchent à penser la douceur, l'enfance et la résistance dans un monde en mutation. &lt;/p&gt; 
 &lt;audio controls title="Anne Dufourmantelle par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/11189-07.11.2011-ITEMA_20320628-2011C15000E0211-ITE_00045291_RSCE-21.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;
 </t>
         </is>
       </c>
-      <c r="F142" s="47" t="inlineStr">
+      <c r="F143" s="47" t="inlineStr">
         <is>
           <t>PCCcMUiurLo</t>
         </is>
       </c>
-      <c r="G142" s="48" t="inlineStr">
+      <c r="G143" s="48" t="inlineStr">
         <is>
           <t>Hommage à Anne DUFOURMANTELLE par PhiloCloud</t>
         </is>
       </c>
-      <c r="H142" s="48" t="inlineStr">
+      <c r="H143" s="48" t="inlineStr">
         <is>
           <t>https://www.laphilo.fr/pho/adufourmantelle-mini.webp</t>
         </is>
       </c>
-      <c r="J142" s="48" t="inlineStr">
+      <c r="J143" s="48" t="inlineStr">
         <is>
           <t>ethique ; esthetique</t>
         </is>
       </c>
-      <c r="K142" s="48" t="inlineStr">
+      <c r="K143" s="48" t="inlineStr">
         <is>
           <t>Phénoménologie</t>
         </is>
       </c>
-      <c r="L142" s="48" t="inlineStr">
+      <c r="L143" s="48" t="inlineStr">
         <is>
           <t>philosophe et psychanalyste française fine analyste, qui explore la vulnérabilité humaine.</t>
         </is>
       </c>
-      <c r="M142" t="inlineStr">
+      <c r="M143" t="inlineStr">
         <is>
           <t xml:space="preserve">femme</t>
         </is>
       </c>
-      <c r="N142" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-    </row>
-    <row r="143" ht="176.25" customHeight="1" s="49">
-      <c r="A143" s="47">
-        <v>1881</v>
-      </c>
-      <c r="B143" s="47" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1955</t>
-        </is>
-      </c>
-      <c r="C143" s="47" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1881 – 1955</t>
-        </is>
-      </c>
-      <c r="D143" s="47" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Pierre TEILHARD DE CHARDIN</t>
-        </is>
-      </c>
-      <c r="E143" s="85" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Pierre_Teilhard_de_Chardin" title=" Wikipedia"&gt;Pierre TEILHARD DE CHARDIN&lt;/a&gt; est un prêtre jésuite, paléontologue et philosophe français, qui a voulu réconcilier la foi chrétienne et la théorie de l’évolution. Né en Auvergne, il entre chez les jésuites et devient un spécialiste reconnu de la &lt;a href="https://fr.wikipedia.org/wiki/Pal%C3%A9ontologie" title=" Wikipedia"&gt;paléontologie&lt;/a&gt;. Brancardier pendant la Première Guerre mondiale, il passe ensuite plus de vingt ans en Chine, où il participe aux recherches sur l’&lt;a href="https://fr.wikipedia.org/wiki/Homme_de_P%C3%A9kin" title=" Wikipedia"&gt;Homme de Pékin&lt;/a&gt;, l’un des plus anciens fossiles humains connus, et prend part en 1931-1932 à la &lt;a href="https://fr.wikipedia.org/wiki/Croisi%C3%A8re_jaune" title=" Wikipedia"&gt;Croisière jaune&lt;/a&gt;, grande expédition à travers l’Asie centrale.&lt;/p&gt; &lt;p&gt;Dans &lt;em&gt;Le Phénomène humain&lt;/em&gt;, écrit dans les années 1930 et publié après sa mort, il décrit l’univers comme un grand mouvement d’évolution, de la matière à la vie, puis de la vie à la pensée. À mesure que la matière se complexifie, la conscience grandit : c’est la « loi de complexité-conscience ». Avec l’homme apparaît une nouvelle couche de la Terre, la &lt;a href="https://fr.wikipedia.org/wiki/Noosph%C3%A8re" title=" Wikipedia"&gt;noosphère&lt;/a&gt;, la sphère de la pensée, qui relie peu à peu tous les esprits.&lt;/p&gt; &lt;p&gt;Cette évolution est selon lui orientée vers un point de convergence final, le &lt;a href="https://fr.wikipedia.org/wiki/Point_Om%C3%A9ga" title=" Wikipedia"&gt;point Oméga&lt;/a&gt;, qu’il identifie au Christ cosmique, où l’humanité s’unira sans perdre la personnalité de chacun. Son autre grand texte, &lt;em&gt;Le Milieu divin&lt;/em&gt;, médite sur la présence de Dieu dans toutes les activités humaines. Ses idées inquiètent Rome, qui lui interdit de publier ses écrits philosophiques et l’éloigne de France. Il meurt à New York en 1955. Publiée après sa mort, son œuvre connaît un succès mondial, et l’on voit parfois dans la noosphère une anticipation d’Internet.&lt;/p&gt;</t>
-        </is>
-      </c>
-      <c r="H143" s="48" t="inlineStr">
-        <is>
-          <t xml:space="preserve">https://www.laphilo.fr/pho/teilhard-mini.webp</t>
-        </is>
-      </c>
-      <c r="J143" s="48" t="inlineStr">
-        <is>
-          <t xml:space="preserve">metaphysique ; spiritualite</t>
-        </is>
-      </c>
-      <c r="K143" s="48" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Spiritualisme ; Panenthéisme</t>
-        </is>
-      </c>
-      <c r="L143" s="48" t="inlineStr">
-        <is>
-          <t xml:space="preserve">jésuite et paléontologue français, penseur d’une évolution cosmique orientée vers la conscience et l’esprit.</t>
-        </is>
-      </c>
       <c r="N143" t="inlineStr">
         <is>
           <t xml:space="preserve">occident</t>
         </is>
-      </c>
-      <c r="O143">
-        <v>2</v>
       </c>
     </row>
     <row r="144" ht="176.25" customHeight="1" s="49">
       <c r="A144" s="47">
-        <v>1868</v>
+        <v>1881</v>
       </c>
       <c r="B144" s="47" t="inlineStr">
         <is>
-          <t xml:space="preserve">1952</t>
+          <t xml:space="preserve">1955</t>
         </is>
       </c>
       <c r="C144" s="47" t="inlineStr">
         <is>
-          <t xml:space="preserve">1868 – 1952</t>
+          <t xml:space="preserve">1881 – 1955</t>
         </is>
       </c>
       <c r="D144" s="47" t="inlineStr">
         <is>
-          <t xml:space="preserve">Charles MAURRAS</t>
+          <t xml:space="preserve">Pierre TEILHARD DE CHARDIN</t>
         </is>
       </c>
       <c r="E144" s="85" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Charles_Maurras" title=" Wikipedia"&gt;Charles MAURRAS&lt;/a&gt; est un écrivain, journaliste et théoricien politique français, le maître à penser de l’&lt;a href="https://fr.wikipedia.org/wiki/Action_fran%C3%A7aise" title=" Wikipedia"&gt;Action française&lt;/a&gt;. Né en 1868 à Martigues, en Provence, il devient sourd vers quatorze ans, perd la foi, et monte à Paris, où il se fait connaître comme critique littéraire et poète, défenseur d’un classicisme inspiré de la Grèce contre le romantisme, qu’il juge source de désordre. L’affaire Dreyfus le jette dans la politique : en 1898, il justifie le faux du colonel Henry au nom de l’intérêt de l’armée et de l’État.&lt;/p&gt; &lt;p&gt;Avec son &lt;em&gt;Enquête sur la monarchie&lt;/em&gt; (1900), il convertit l’Action française à la royauté. Sa doctrine, le « nationalisme intégral », place la nation au-dessus de tout : seule une monarchie héréditaire, antiparlementaire et décentralisée pourrait garantir l’ordre et la durée que la République, gouvernement des partis et de l’opinion, détruirait. Agnostique, il défend pourtant l’Église catholique comme une force d’ordre. Il appelle sa méthode l’« empirisme organisateur » : tirer de l’histoire les lois du bon gouvernement. Il dénonce les « quatre États confédérés » qui, selon lui, rongent la France : les juifs, les protestants, les francs-maçons et les « métèques ». Cet antisémitisme d’État est au cœur de sa pensée.&lt;/p&gt; &lt;p&gt;Son quotidien, &lt;em&gt;L’Action française&lt;/em&gt;, exerce une influence considérable sur la droite et sur une partie de la jeunesse intellectuelle, malgré la condamnation du mouvement par le pape Pie XI en 1926. Maurras entre à l’Académie française en 1938. Hostile à l’Allemagne, il soutient pourtant en 1940 le maréchal Pétain, dont l’arrivée au pouvoir est pour lui une « divine surprise ». Condamné en 1945 à la réclusion à perpétuité et à la dégradation nationale pour intelligence avec l’ennemi, il s’écrie : « C’est la revanche de Dreyfus ! » Gracié pour raison de santé, il meurt en 1952. Sa pensée a durablement marqué l’extrême droite française.&lt;/p&gt;</t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Pierre_Teilhard_de_Chardin" title=" Wikipedia"&gt;Pierre TEILHARD DE CHARDIN&lt;/a&gt; est un prêtre jésuite, paléontologue et philosophe français, qui a voulu réconcilier la foi chrétienne et la théorie de l’évolution. Né en Auvergne, il entre chez les jésuites et devient un spécialiste reconnu de la &lt;a href="https://fr.wikipedia.org/wiki/Pal%C3%A9ontologie" title=" Wikipedia"&gt;paléontologie&lt;/a&gt;. Brancardier pendant la Première Guerre mondiale, il passe ensuite plus de vingt ans en Chine, où il participe aux recherches sur l’&lt;a href="https://fr.wikipedia.org/wiki/Homme_de_P%C3%A9kin" title=" Wikipedia"&gt;Homme de Pékin&lt;/a&gt;, l’un des plus anciens fossiles humains connus, et prend part en 1931-1932 à la &lt;a href="https://fr.wikipedia.org/wiki/Croisi%C3%A8re_jaune" title=" Wikipedia"&gt;Croisière jaune&lt;/a&gt;, grande expédition à travers l’Asie centrale.&lt;/p&gt; &lt;p&gt;Dans &lt;em&gt;Le Phénomène humain&lt;/em&gt;, écrit dans les années 1930 et publié après sa mort, il décrit l’univers comme un grand mouvement d’évolution, de la matière à la vie, puis de la vie à la pensée. À mesure que la matière se complexifie, la conscience grandit : c’est la « loi de complexité-conscience ». Avec l’homme apparaît une nouvelle couche de la Terre, la &lt;a href="https://fr.wikipedia.org/wiki/Noosph%C3%A8re" title=" Wikipedia"&gt;noosphère&lt;/a&gt;, la sphère de la pensée, qui relie peu à peu tous les esprits.&lt;/p&gt; &lt;p&gt;Cette évolution est selon lui orientée vers un point de convergence final, le &lt;a href="https://fr.wikipedia.org/wiki/Point_Om%C3%A9ga" title=" Wikipedia"&gt;point Oméga&lt;/a&gt;, qu’il identifie au Christ cosmique, où l’humanité s’unira sans perdre la personnalité de chacun. Son autre grand texte, &lt;em&gt;Le Milieu divin&lt;/em&gt;, médite sur la présence de Dieu dans toutes les activités humaines. Ses idées inquiètent Rome, qui lui interdit de publier ses écrits philosophiques et l’éloigne de France. Il meurt à New York en 1955. Publiée après sa mort, son œuvre connaît un succès mondial, et l’on voit parfois dans la noosphère une anticipation d’Internet.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H144" s="48" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.laphilo.fr/pho/maurras-mini.webp</t>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/teilhard-mini.webp</t>
         </is>
       </c>
       <c r="J144" s="48" t="inlineStr">
         <is>
-          <t xml:space="preserve">politique</t>
+          <t xml:space="preserve">metaphysique ; spiritualite</t>
         </is>
       </c>
       <c r="K144" s="48" t="inlineStr">
         <is>
-          <t xml:space="preserve">Maurrassisme ; Conservatisme</t>
+          <t xml:space="preserve">Spiritualisme ; Panenthéisme</t>
         </is>
       </c>
       <c r="L144" s="48" t="inlineStr">
         <is>
-          <t xml:space="preserve">écrivain et théoricien politique français, chef de l’Action française et du « nationalisme intégral ».</t>
+          <t xml:space="preserve">jésuite et paléontologue français, penseur d’une évolution cosmique orientée vers la conscience et l’esprit.</t>
         </is>
       </c>
       <c r="N144" t="inlineStr">
@@ -9567,50 +9572,52 @@
           <t xml:space="preserve">occident</t>
         </is>
       </c>
-      <c r="O144"/>
+      <c r="O144">
+        <v>2</v>
+      </c>
     </row>
     <row r="145" ht="176.25" customHeight="1" s="49">
       <c r="A145" s="47">
-        <v>1827</v>
+        <v>1868</v>
       </c>
       <c r="B145" s="47" t="inlineStr">
         <is>
-          <t xml:space="preserve">1907</t>
+          <t xml:space="preserve">1952</t>
         </is>
       </c>
       <c r="C145" s="47" t="inlineStr">
         <is>
-          <t xml:space="preserve">1827 – 1907</t>
+          <t xml:space="preserve">1868 – 1952</t>
         </is>
       </c>
       <c r="D145" s="47" t="inlineStr">
         <is>
-          <t xml:space="preserve">Marcellin BERTHELOT</t>
+          <t xml:space="preserve">Charles MAURRAS</t>
         </is>
       </c>
       <c r="E145" s="85" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Marcellin_Berthelot" title=" Wikipedia"&gt;Marcellin BERTHELOT&lt;/a&gt; est un chimiste, historien des sciences et homme politique français, l’une des figures les plus représentatives du &lt;a href="https://fr.wikipedia.org/wiki/Scientisme" title=" Wikipedia"&gt;scientisme&lt;/a&gt;. Né à Paris en 1827, fils d’un médecin, il devient l’un des fondateurs de la chimie organique de synthèse : il montre qu’on peut fabriquer en laboratoire, à partir des éléments, des corps jusque-là produits seulement par les êtres vivants, comme l’acétylène, le méthane ou l’alcool. Il en tire une leçon philosophique : il n’existe pas de « force vitale » mystérieuse, la vie obéit aux mêmes lois que la matière.&lt;/p&gt; &lt;p&gt;Pour Berthelot, la science expérimentale est la seule voie vers la vérité, et elle doit aussi fonder la morale et la politique. « Le monde est aujourd’hui sans mystère », écrit-il en 1885 : ce que la science ne sait pas encore, elle le saura demain. Ami de &lt;a href="https://fr.wikipedia.org/wiki/Ernest_Renan" title=" Wikipedia"&gt;Ernest Renan&lt;/a&gt;, avec qui il partage la foi dans l’avenir de la science, il expose ses idées dans &lt;em&gt;Science et morale&lt;/em&gt; (1897). En 1895, quand le critique Ferdinand Brunetière proclame la « faillite de la science », qui n’aurait pas tenu ses promesses morales, Berthelot devient le porte-parole de la réplique républicaine et laïque.&lt;/p&gt; &lt;p&gt;Sénateur inamovible, il est ministre de l’Instruction publique (1886-1887) puis des Affaires étrangères (1895-1896), et défend une école laïque fondée sur les sciences. Professeur au Collège de France, secrétaire perpétuel de l’Académie des sciences, il s’oppose aussi à la théorie atomique, qu’il juge trop hypothétique. Il meurt en 1907 le même jour que sa femme, et tous deux sont inhumés au Panthéon.&lt;/p&gt;</t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Charles_Maurras" title=" Wikipedia"&gt;Charles MAURRAS&lt;/a&gt; est un écrivain, journaliste et théoricien politique français, le maître à penser de l’&lt;a href="https://fr.wikipedia.org/wiki/Action_fran%C3%A7aise" title=" Wikipedia"&gt;Action française&lt;/a&gt;. Né en 1868 à Martigues, en Provence, il devient sourd vers quatorze ans, perd la foi, et monte à Paris, où il se fait connaître comme critique littéraire et poète, défenseur d’un classicisme inspiré de la Grèce contre le romantisme, qu’il juge source de désordre. L’affaire Dreyfus le jette dans la politique : en 1898, il justifie le faux du colonel Henry au nom de l’intérêt de l’armée et de l’État.&lt;/p&gt; &lt;p&gt;Avec son &lt;em&gt;Enquête sur la monarchie&lt;/em&gt; (1900), il convertit l’Action française à la royauté. Sa doctrine, le « nationalisme intégral », place la nation au-dessus de tout : seule une monarchie héréditaire, antiparlementaire et décentralisée pourrait garantir l’ordre et la durée que la République, gouvernement des partis et de l’opinion, détruirait. Agnostique, il défend pourtant l’Église catholique comme une force d’ordre. Il appelle sa méthode l’« empirisme organisateur » : tirer de l’histoire les lois du bon gouvernement. Il dénonce les « quatre États confédérés » qui, selon lui, rongent la France : les juifs, les protestants, les francs-maçons et les « métèques ». Cet antisémitisme d’État est au cœur de sa pensée.&lt;/p&gt; &lt;p&gt;Son quotidien, &lt;em&gt;L’Action française&lt;/em&gt;, exerce une influence considérable sur la droite et sur une partie de la jeunesse intellectuelle, malgré la condamnation du mouvement par le pape Pie XI en 1926. Maurras entre à l’Académie française en 1938. Hostile à l’Allemagne, il soutient pourtant en 1940 le maréchal Pétain, dont l’arrivée au pouvoir est pour lui une « divine surprise ». Condamné en 1945 à la réclusion à perpétuité et à la dégradation nationale pour intelligence avec l’ennemi, il s’écrie : « C’est la revanche de Dreyfus ! » Gracié pour raison de santé, il meurt en 1952. Sa pensée a durablement marqué l’extrême droite française.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H145" s="48" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.laphilo.fr/pho/berthelot-mini.webp</t>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/maurras-mini.webp</t>
         </is>
       </c>
       <c r="J145" s="48" t="inlineStr">
         <is>
-          <t xml:space="preserve">epistemologie ; politique</t>
+          <t xml:space="preserve">politique</t>
         </is>
       </c>
       <c r="K145" s="48" t="inlineStr">
         <is>
-          <t xml:space="preserve">Scientisme ; Positivisme</t>
+          <t xml:space="preserve">Maurrassisme ; Conservatisme</t>
         </is>
       </c>
       <c r="L145" s="48" t="inlineStr">
         <is>
-          <t xml:space="preserve">chimiste et homme politique français, figure emblématique du scientisme.</t>
+          <t xml:space="preserve">écrivain et théoricien politique français, chef de l’Action française et du « nationalisme intégral ».</t>
         </is>
       </c>
       <c r="N145" t="inlineStr">
@@ -9622,46 +9629,46 @@
     </row>
     <row r="146" ht="176.25" customHeight="1" s="49">
       <c r="A146" s="47">
-        <v>1861</v>
+        <v>1827</v>
       </c>
       <c r="B146" s="47" t="inlineStr">
         <is>
-          <t xml:space="preserve">1916</t>
+          <t xml:space="preserve">1907</t>
         </is>
       </c>
       <c r="C146" s="47" t="inlineStr">
         <is>
-          <t xml:space="preserve">1861 – 1916</t>
+          <t xml:space="preserve">1827 – 1907</t>
         </is>
       </c>
       <c r="D146" s="47" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pierre DUHEM</t>
+          <t xml:space="preserve">Marcellin BERTHELOT</t>
         </is>
       </c>
       <c r="E146" s="85" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Pierre_Duhem" title=" Wikipedia"&gt;Pierre DUHEM&lt;/a&gt; est un physicien, philosophe et historien des sciences français. Né à Paris en 1861, brillant élève de l’École normale supérieure, il consacre ses travaux de physique à la thermodynamique. Une thèse où il critique les idées du chimiste Marcellin Berthelot est refusée ; Berthelot, très puissant, l’empêche ensuite d’obtenir un poste à Paris, et Duhem, catholique convaincu, fait sa carrière en province, à Lille, à Rennes, puis à Bordeaux.&lt;/p&gt; &lt;p&gt;Dans &lt;em&gt;La Théorie physique, son objet, sa structure&lt;/em&gt; (1906), il soutient qu’une théorie physique n’explique pas la réalité cachée des choses, ce qui relève de la métaphysique : elle est un système de propositions mathématiques qui représente et classe le plus simplement possible les lois expérimentales. Il faut, comme disaient les astronomes grecs, « sauver les phénomènes ». Surtout, une expérience ne peut jamais réfuter une hypothèse isolée : elle met en jeu tout un ensemble de théories et d’instruments, et si la prédiction échoue, on ne sait pas laquelle des hypothèses est fausse. Il n’y a donc pas d’« expérience cruciale ». Cette idée, reprise par Quine, est connue comme la &lt;a href="https://fr.wikipedia.org/wiki/Th%C3%A8se_de_Duhem-Quine" title=" Wikipedia"&gt;thèse de Duhem-Quine&lt;/a&gt;.&lt;/p&gt; &lt;p&gt;Duhem est aussi un grand historien des sciences. Dans les dix volumes du &lt;em&gt;Système du monde&lt;/em&gt;, il redécouvre la physique du Moyen Âge, celle de Jean Buridan et de Nicole Oresme, et montre que la science moderne ne naît pas d’une rupture brutale avec les siècles « obscurs », mais les prolonge. Il meurt en 1916. Son instrumentalisme et son holisme ont profondément marqué la philosophie des sciences du XXe siècle.&lt;/p&gt;</t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Marcellin_Berthelot" title=" Wikipedia"&gt;Marcellin BERTHELOT&lt;/a&gt; est un chimiste, historien des sciences et homme politique français, l’une des figures les plus représentatives du &lt;a href="https://fr.wikipedia.org/wiki/Scientisme" title=" Wikipedia"&gt;scientisme&lt;/a&gt;. Né à Paris en 1827, fils d’un médecin, il devient l’un des fondateurs de la chimie organique de synthèse : il montre qu’on peut fabriquer en laboratoire, à partir des éléments, des corps jusque-là produits seulement par les êtres vivants, comme l’acétylène, le méthane ou l’alcool. Il en tire une leçon philosophique : il n’existe pas de « force vitale » mystérieuse, la vie obéit aux mêmes lois que la matière.&lt;/p&gt; &lt;p&gt;Pour Berthelot, la science expérimentale est la seule voie vers la vérité, et elle doit aussi fonder la morale et la politique. « Le monde est aujourd’hui sans mystère », écrit-il en 1885 : ce que la science ne sait pas encore, elle le saura demain. Ami de &lt;a href="https://fr.wikipedia.org/wiki/Ernest_Renan" title=" Wikipedia"&gt;Ernest Renan&lt;/a&gt;, avec qui il partage la foi dans l’avenir de la science, il expose ses idées dans &lt;em&gt;Science et morale&lt;/em&gt; (1897). En 1895, quand le critique Ferdinand Brunetière proclame la « faillite de la science », qui n’aurait pas tenu ses promesses morales, Berthelot devient le porte-parole de la réplique républicaine et laïque.&lt;/p&gt; &lt;p&gt;Sénateur inamovible, il est ministre de l’Instruction publique (1886-1887) puis des Affaires étrangères (1895-1896), et défend une école laïque fondée sur les sciences. Professeur au Collège de France, secrétaire perpétuel de l’Académie des sciences, il s’oppose aussi à la théorie atomique, qu’il juge trop hypothétique. Il meurt en 1907 le même jour que sa femme, et tous deux sont inhumés au Panthéon.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H146" s="48" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.laphilo.fr/pho/duhem-mini.webp</t>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/berthelot-mini.webp</t>
         </is>
       </c>
       <c r="J146" s="48" t="inlineStr">
         <is>
-          <t xml:space="preserve">epistemologie</t>
+          <t xml:space="preserve">epistemologie ; politique</t>
         </is>
       </c>
       <c r="K146" s="48" t="inlineStr">
         <is>
-          <t xml:space="preserve">Instrumentalisme ; Holisme</t>
+          <t xml:space="preserve">Scientisme ; Positivisme</t>
         </is>
       </c>
       <c r="L146" s="48" t="inlineStr">
         <is>
-          <t xml:space="preserve">physicien et philosophe des sciences français, pour qui une hypothèse n’est jamais testée seule.</t>
+          <t xml:space="preserve">chimiste et homme politique français, figure emblématique du scientisme.</t>
         </is>
       </c>
       <c r="N146" t="inlineStr">
@@ -9673,46 +9680,46 @@
     </row>
     <row r="147" ht="176.25" customHeight="1" s="49">
       <c r="A147" s="47">
-        <v>1854</v>
+        <v>1861</v>
       </c>
       <c r="B147" s="47" t="inlineStr">
         <is>
-          <t xml:space="preserve">1912</t>
+          <t xml:space="preserve">1916</t>
         </is>
       </c>
       <c r="C147" s="47" t="inlineStr">
         <is>
-          <t xml:space="preserve">1854 – 1912</t>
+          <t xml:space="preserve">1861 – 1916</t>
         </is>
       </c>
       <c r="D147" s="47" t="inlineStr">
         <is>
-          <t xml:space="preserve">Henri POINCARÉ</t>
+          <t xml:space="preserve">Pierre DUHEM</t>
         </is>
       </c>
       <c r="E147" s="85" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Henri_Poincar%C3%A9" title=" Wikipedia"&gt;Henri POINCARÉ&lt;/a&gt; est un mathématicien, physicien et philosophe des sciences français, l’un des derniers savants universels. Né à Nancy en 1854, polytechnicien et ingénieur des mines, il enseigne à la Sorbonne à partir de 1881. Il renouvelle presque toutes les branches des mathématiques : il fonde la topologie, découvre en étudiant le mouvement de trois corps célestes les comportements imprévisibles qu’on appellera « chaos », et pose en 1905, en même temps qu’Einstein, les bases mathématiques de la relativité restreinte.&lt;/p&gt; &lt;p&gt;Dans &lt;em&gt;La Science et l’Hypothèse&lt;/em&gt; (1902), il défend le &lt;a href="https://fr.wikipedia.org/wiki/Conventionnalisme" title=" Wikipedia"&gt;conventionnalisme&lt;/a&gt; : certains principes de la science ne sont ni des vérités a priori ni des faits d’expérience, mais des conventions. Ainsi, aucune expérience ne peut dire si l’espace est euclidien ou non : nous choisissons la géométrie d’Euclide parce qu’elle est la plus commode. Ces conventions ne sont pas arbitraires, car l’expérience nous guide, mais elles ne peuvent être ni vraies ni fausses. La science ne connaît pas les choses elles-mêmes, mais les rapports entre les choses.&lt;/p&gt; &lt;p&gt;Dans &lt;em&gt;La Valeur de la science&lt;/em&gt; (1905) et &lt;em&gt;Science et méthode&lt;/em&gt; (1908), il s’oppose aussi aux logiciens, comme Russell, qui veulent réduire les mathématiques à la logique : pour lui, le raisonnement mathématique repose sur une intuition. Il décrit le rôle de l’inconscient dans la découverte, à partir de ses propres illuminations soudaines, comme celle qui lui vint en montant dans un omnibus. Élu à l’Académie française en 1908, il meurt à Paris en 1912.&lt;/p&gt;</t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Pierre_Duhem" title=" Wikipedia"&gt;Pierre DUHEM&lt;/a&gt; est un physicien, philosophe et historien des sciences français. Né à Paris en 1861, brillant élève de l’École normale supérieure, il consacre ses travaux de physique à la thermodynamique. Une thèse où il critique les idées du chimiste Marcellin Berthelot est refusée ; Berthelot, très puissant, l’empêche ensuite d’obtenir un poste à Paris, et Duhem, catholique convaincu, fait sa carrière en province, à Lille, à Rennes, puis à Bordeaux.&lt;/p&gt; &lt;p&gt;Dans &lt;em&gt;La Théorie physique, son objet, sa structure&lt;/em&gt; (1906), il soutient qu’une théorie physique n’explique pas la réalité cachée des choses, ce qui relève de la métaphysique : elle est un système de propositions mathématiques qui représente et classe le plus simplement possible les lois expérimentales. Il faut, comme disaient les astronomes grecs, « sauver les phénomènes ». Surtout, une expérience ne peut jamais réfuter une hypothèse isolée : elle met en jeu tout un ensemble de théories et d’instruments, et si la prédiction échoue, on ne sait pas laquelle des hypothèses est fausse. Il n’y a donc pas d’« expérience cruciale ». Cette idée, reprise par Quine, est connue comme la &lt;a href="https://fr.wikipedia.org/wiki/Th%C3%A8se_de_Duhem-Quine" title=" Wikipedia"&gt;thèse de Duhem-Quine&lt;/a&gt;.&lt;/p&gt; &lt;p&gt;Duhem est aussi un grand historien des sciences. Dans les dix volumes du &lt;em&gt;Système du monde&lt;/em&gt;, il redécouvre la physique du Moyen Âge, celle de Jean Buridan et de Nicole Oresme, et montre que la science moderne ne naît pas d’une rupture brutale avec les siècles « obscurs », mais les prolonge. Il meurt en 1916. Son instrumentalisme et son holisme ont profondément marqué la philosophie des sciences du XXe siècle.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H147" s="48" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.laphilo.fr/pho/poincare-mini.webp</t>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/duhem-mini.webp</t>
         </is>
       </c>
       <c r="J147" s="48" t="inlineStr">
         <is>
-          <t xml:space="preserve">epistemologie ; logique</t>
+          <t xml:space="preserve">epistemologie</t>
         </is>
       </c>
       <c r="K147" s="48" t="inlineStr">
         <is>
-          <t xml:space="preserve">Conventionnalisme</t>
+          <t xml:space="preserve">Instrumentalisme ; Holisme</t>
         </is>
       </c>
       <c r="L147" s="48" t="inlineStr">
         <is>
-          <t xml:space="preserve">mathématicien et physicien français, philosophe des sciences et fondateur du conventionnalisme.</t>
+          <t xml:space="preserve">physicien et philosophe des sciences français, pour qui une hypothèse n’est jamais testée seule.</t>
         </is>
       </c>
       <c r="N147" t="inlineStr">
@@ -9720,52 +9727,50 @@
           <t xml:space="preserve">occident</t>
         </is>
       </c>
-      <c r="O147">
-        <v>2</v>
-      </c>
+      <c r="O147"/>
     </row>
     <row r="148" ht="176.25" customHeight="1" s="49">
       <c r="A148" s="47">
-        <v>1866</v>
+        <v>1854</v>
       </c>
       <c r="B148" s="47" t="inlineStr">
         <is>
-          <t xml:space="preserve">1947</t>
+          <t xml:space="preserve">1912</t>
         </is>
       </c>
       <c r="C148" s="47" t="inlineStr">
         <is>
-          <t xml:space="preserve">1866 – 1947</t>
+          <t xml:space="preserve">1854 – 1912</t>
         </is>
       </c>
       <c r="D148" s="47" t="inlineStr">
         <is>
-          <t xml:space="preserve">Léon ROBIN</t>
+          <t xml:space="preserve">Henri POINCARÉ</t>
         </is>
       </c>
       <c r="E148" s="85" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/L%C3%A9on_Robin" title=" Wikipedia"&gt;Léon ROBIN&lt;/a&gt; est un philosophe et historien français de la philosophie, l’un des grands spécialistes de la pensée grecque. Né à Nantes en 1866, fils de marchand, il est reçu à l’agrégation de philosophie en 1891 et enseigne longtemps dans les lycées, à Compiègne, Vendôme et Angers. Élève et disciple d’Octave Hamelin, il publie après la mort de celui-ci son cours sur &lt;em&gt;Le Système d’Aristote&lt;/em&gt;. Il enseigne ensuite à Caen, puis à la Sorbonne de 1913 à 1937, où il occupe à partir de 1924 la chaire d’histoire de la philosophie antique.&lt;/p&gt; &lt;p&gt;Sa thèse, &lt;em&gt;La Théorie platonicienne des Idées et des nombres d’après Aristote&lt;/em&gt; (1908), s’appuie sur les témoignages d’Aristote pour reconstituer l’enseignement oral de &lt;a href="https://fr.wikipedia.org/wiki/Platon" title=" Wikipedia"&gt;Platon&lt;/a&gt; à l’Académie, où les Idées sont rattachées à des principes mathématiques, l’Un et la Dyade. Dans &lt;em&gt;La Pensée grecque et les origines de l’esprit scientifique&lt;/em&gt; (1923), il retrace la naissance de la raison grecque, des premiers physiciens d’Ionie jusqu’aux écoles hellénistiques. Il consacre aussi des livres à la morale antique, à Platon et au scepticisme de Pyrrhon, toujours appuyés sur une lecture rigoureuse des textes grecs.&lt;/p&gt; &lt;p&gt;Son œuvre la plus durable est la traduction des œuvres complètes de Platon pour la Bibliothèque de la Pléiade, qu’il dirige et dont il traduit lui-même la plus grande partie : précise et élégante, elle a fait lire Platon à des générations de lecteurs français. Il dirige aussi l’Institut international de philosophie. Il meurt à Paris en 1947. Pierre-Maxime Schuhl lui a succédé à la Sorbonne.&lt;/p&gt;</t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Henri_Poincar%C3%A9" title=" Wikipedia"&gt;Henri POINCARÉ&lt;/a&gt; est un mathématicien, physicien et philosophe des sciences français, l’un des derniers savants universels. Né à Nancy en 1854, polytechnicien et ingénieur des mines, il enseigne à la Sorbonne à partir de 1881. Il renouvelle presque toutes les branches des mathématiques : il fonde la topologie, découvre en étudiant le mouvement de trois corps célestes les comportements imprévisibles qu’on appellera « chaos », et pose en 1905, en même temps qu’Einstein, les bases mathématiques de la relativité restreinte.&lt;/p&gt; &lt;p&gt;Dans &lt;em&gt;La Science et l’Hypothèse&lt;/em&gt; (1902), il défend le &lt;a href="https://fr.wikipedia.org/wiki/Conventionnalisme" title=" Wikipedia"&gt;conventionnalisme&lt;/a&gt; : certains principes de la science ne sont ni des vérités a priori ni des faits d’expérience, mais des conventions. Ainsi, aucune expérience ne peut dire si l’espace est euclidien ou non : nous choisissons la géométrie d’Euclide parce qu’elle est la plus commode. Ces conventions ne sont pas arbitraires, car l’expérience nous guide, mais elles ne peuvent être ni vraies ni fausses. La science ne connaît pas les choses elles-mêmes, mais les rapports entre les choses.&lt;/p&gt; &lt;p&gt;Dans &lt;em&gt;La Valeur de la science&lt;/em&gt; (1905) et &lt;em&gt;Science et méthode&lt;/em&gt; (1908), il s’oppose aussi aux logiciens, comme Russell, qui veulent réduire les mathématiques à la logique : pour lui, le raisonnement mathématique repose sur une intuition. Il décrit le rôle de l’inconscient dans la découverte, à partir de ses propres illuminations soudaines, comme celle qui lui vint en montant dans un omnibus. Élu à l’Académie française en 1908, il meurt à Paris en 1912.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H148" s="48" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.laphilo.fr/pho/leonrobin-mini.webp</t>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/poincare-mini.webp</t>
         </is>
       </c>
       <c r="J148" s="48" t="inlineStr">
         <is>
-          <t xml:space="preserve">metaphysique ; epistemologie</t>
+          <t xml:space="preserve">epistemologie ; logique</t>
         </is>
       </c>
       <c r="K148" s="48" t="inlineStr">
         <is>
-          <t xml:space="preserve">Platonisme</t>
+          <t xml:space="preserve">Conventionnalisme</t>
         </is>
       </c>
       <c r="L148" s="48" t="inlineStr">
         <is>
-          <t xml:space="preserve">historien français de la philosophie grecque, grand interprète et traducteur de Platon.</t>
+          <t xml:space="preserve">mathématicien et physicien français, philosophe des sciences et fondateur du conventionnalisme.</t>
         </is>
       </c>
       <c r="N148" t="inlineStr">
@@ -9773,50 +9778,52 @@
           <t xml:space="preserve">occident</t>
         </is>
       </c>
-      <c r="O148"/>
+      <c r="O148">
+        <v>2</v>
+      </c>
     </row>
     <row r="149" ht="176.25" customHeight="1" s="49">
       <c r="A149" s="47">
-        <v>1898</v>
+        <v>1866</v>
       </c>
       <c r="B149" s="47" t="inlineStr">
         <is>
-          <t xml:space="preserve">1994</t>
+          <t xml:space="preserve">1947</t>
         </is>
       </c>
       <c r="C149" s="47" t="inlineStr">
         <is>
-          <t xml:space="preserve">1898 – 1994</t>
+          <t xml:space="preserve">1866 – 1947</t>
         </is>
       </c>
       <c r="D149" s="47" t="inlineStr">
         <is>
-          <t xml:space="preserve">Henri GOUHIER</t>
+          <t xml:space="preserve">Léon ROBIN</t>
         </is>
       </c>
       <c r="E149" s="85" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Henri_Gouhier" title=" Wikipedia"&gt;Henri GOUHIER&lt;/a&gt; est un philosophe, historien de la philosophie et critique de théâtre français. Né à Auxerre en 1898, fils d’un clerc de notaire et d’une modiste, il entre à l’École normale supérieure en 1919 et est reçu premier à l’agrégation de philosophie en 1921. Élève d’&lt;a href="https://fr.wikipedia.org/wiki/%C3%89tienne_Gilson" title=" Wikipedia"&gt;Étienne Gilson&lt;/a&gt;, qui lui demande de faire pour la pensée française moderne ce qu’il fait lui-même pour le Moyen Âge, il enseigne à Lille, à Bordeaux, puis à la Sorbonne de 1941 à 1968, dans la chaire d’histoire de la pensée religieuse en France.&lt;/p&gt; &lt;p&gt;Il consacre sa vie à la philosophie française de Descartes à Bergson, qu’il lit en historien attentif aux convictions religieuses des auteurs. Il étudie la pensée religieuse de Descartes, Malebranche, Pascal, et surtout, dans trois volumes, la jeunesse d’Auguste Comte et la naissance du positivisme. Il montre comment le fondateur de la religion de l’Humanité a remplacé Dieu par l’humanité. Ces travaux inspirent le théologien Henri de Lubac pour &lt;em&gt;Le Drame de l’humanisme athée&lt;/em&gt; (1944). Il écrit aussi sur les conversions de Maine de Biran, sur Rousseau et sur Bergson, et défend l’idée d’une philosophie chrétienne.&lt;/p&gt; &lt;p&gt;Passionné de théâtre, il est pendant des décennies critique dramatique et publie &lt;em&gt;L’Essence du théâtre&lt;/em&gt; (1943), où il voit dans la représentation une présence réelle, une action vivante et non un simple texte. Membre de l’Académie des sciences morales et politiques, il est élu en 1979 à l’Académie française, au fauteuil de son maître Gilson. Il meurt à Paris en 1994.&lt;/p&gt;</t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/L%C3%A9on_Robin" title=" Wikipedia"&gt;Léon ROBIN&lt;/a&gt; est un philosophe et historien français de la philosophie, l’un des grands spécialistes de la pensée grecque. Né à Nantes en 1866, fils de marchand, il est reçu à l’agrégation de philosophie en 1891 et enseigne longtemps dans les lycées, à Compiègne, Vendôme et Angers. Élève et disciple d’Octave Hamelin, il publie après la mort de celui-ci son cours sur &lt;em&gt;Le Système d’Aristote&lt;/em&gt;. Il enseigne ensuite à Caen, puis à la Sorbonne de 1913 à 1937, où il occupe à partir de 1924 la chaire d’histoire de la philosophie antique.&lt;/p&gt; &lt;p&gt;Sa thèse, &lt;em&gt;La Théorie platonicienne des Idées et des nombres d’après Aristote&lt;/em&gt; (1908), s’appuie sur les témoignages d’Aristote pour reconstituer l’enseignement oral de &lt;a href="https://fr.wikipedia.org/wiki/Platon" title=" Wikipedia"&gt;Platon&lt;/a&gt; à l’Académie, où les Idées sont rattachées à des principes mathématiques, l’Un et la Dyade. Dans &lt;em&gt;La Pensée grecque et les origines de l’esprit scientifique&lt;/em&gt; (1923), il retrace la naissance de la raison grecque, des premiers physiciens d’Ionie jusqu’aux écoles hellénistiques. Il consacre aussi des livres à la morale antique, à Platon et au scepticisme de Pyrrhon, toujours appuyés sur une lecture rigoureuse des textes grecs.&lt;/p&gt; &lt;p&gt;Son œuvre la plus durable est la traduction des œuvres complètes de Platon pour la Bibliothèque de la Pléiade, qu’il dirige et dont il traduit lui-même la plus grande partie : précise et élégante, elle a fait lire Platon à des générations de lecteurs français. Il dirige aussi l’Institut international de philosophie. Il meurt à Paris en 1947. Pierre-Maxime Schuhl lui a succédé à la Sorbonne.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H149" s="48" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.laphilo.fr/pho/gouhier-mini.webp</t>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/leonrobin-mini.webp</t>
         </is>
       </c>
       <c r="J149" s="48" t="inlineStr">
         <is>
-          <t xml:space="preserve">metaphysique ; spiritualite ; esthetique</t>
+          <t xml:space="preserve">metaphysique ; epistemologie</t>
         </is>
       </c>
       <c r="K149" s="48" t="inlineStr">
         <is>
-          <t xml:space="preserve">Spiritualisme ; Cartésianisme</t>
+          <t xml:space="preserve">Platonisme</t>
         </is>
       </c>
       <c r="L149" s="48" t="inlineStr">
         <is>
-          <t xml:space="preserve">historien français de la philosophie, de Descartes à Bergson, et critique dramatique.</t>
+          <t xml:space="preserve">historien français de la philosophie grecque, grand interprète et traducteur de Platon.</t>
         </is>
       </c>
       <c r="N149" t="inlineStr">
@@ -9828,46 +9835,46 @@
     </row>
     <row r="150" ht="176.25" customHeight="1" s="49">
       <c r="A150" s="47">
-        <v>1918</v>
+        <v>1898</v>
       </c>
       <c r="B150" s="47" t="inlineStr">
         <is>
-          <t xml:space="preserve">1990</t>
+          <t xml:space="preserve">1994</t>
         </is>
       </c>
       <c r="C150" s="47" t="inlineStr">
         <is>
-          <t xml:space="preserve">1918 – 1990</t>
+          <t xml:space="preserve">1898 – 1994</t>
         </is>
       </c>
       <c r="D150" s="47" t="inlineStr">
         <is>
-          <t xml:space="preserve">Henri BIRAULT</t>
+          <t xml:space="preserve">Henri GOUHIER</t>
         </is>
       </c>
       <c r="E150" s="85" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Henri_Birault" title=" Wikipedia"&gt;Henri BIRAULT&lt;/a&gt; est un philosophe français. Né à Paris en 1918, il entre à l’École normale supérieure en 1939, dans la même promotion que Louis Althusser et Jules Vuillemin, et est reçu deuxième à l’agrégation de philosophie en 1945. Élève de Louis Lavelle et de Jean Nabert, il découvre ensuite l’œuvre de &lt;a href="https://fr.wikipedia.org/wiki/Martin_Heidegger" title=" Wikipedia"&gt;Martin Heidegger&lt;/a&gt;, dont il devient, avec Jean Beaufret, l’un des grands commentateurs français. Il enseigne en khâgne au lycée Henri-IV, puis à la Sorbonne.&lt;/p&gt; &lt;p&gt;Professeur admiré, il marque plusieurs générations d’étudiants par ses lectures lentes et minutieuses des textes, qu’il lit dans leur langue d’origine, en grec, en latin, en allemand. Sa réflexion, nourrie de Pascal, de Kant, de Nietzsche et de Heidegger, porte sur la question de l’être et sur la finitude humaine. Avec Heidegger, il cherche à comprendre ce que veut dire penser, au-delà de la métaphysique qui a réduit l’être à un objet disponible pour la science et la technique. Il en tire &lt;em&gt;Heidegger et l’expérience de la pensée&lt;/em&gt; (1978), qui reste l’une des grandes introductions françaises à cette œuvre difficile.&lt;/p&gt; &lt;p&gt;Sa contribution la plus célèbre, « De la béatitude chez Nietzsche », présentée en 1964 au colloque de Royaumont, montre que Nietzsche n’est pas seulement le penseur de la volonté de puissance et de la mort de Dieu, mais aussi celui d’une joie, d’une approbation sans réserve de la vie, de l’« amour du destin ». Respecté par Deleuze et ses contemporains, il publie peu et réécrit sans cesse. Il meurt en 1990. &lt;em&gt;De l’Être, du divin et des dieux&lt;/em&gt; paraît en 2005.&lt;/p&gt;</t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Henri_Gouhier" title=" Wikipedia"&gt;Henri GOUHIER&lt;/a&gt; est un philosophe, historien de la philosophie et critique de théâtre français. Né à Auxerre en 1898, fils d’un clerc de notaire et d’une modiste, il entre à l’École normale supérieure en 1919 et est reçu premier à l’agrégation de philosophie en 1921. Élève d’&lt;a href="https://fr.wikipedia.org/wiki/%C3%89tienne_Gilson" title=" Wikipedia"&gt;Étienne Gilson&lt;/a&gt;, qui lui demande de faire pour la pensée française moderne ce qu’il fait lui-même pour le Moyen Âge, il enseigne à Lille, à Bordeaux, puis à la Sorbonne de 1941 à 1968, dans la chaire d’histoire de la pensée religieuse en France.&lt;/p&gt; &lt;p&gt;Il consacre sa vie à la philosophie française de Descartes à Bergson, qu’il lit en historien attentif aux convictions religieuses des auteurs. Il étudie la pensée religieuse de Descartes, Malebranche, Pascal, et surtout, dans trois volumes, la jeunesse d’Auguste Comte et la naissance du positivisme. Il montre comment le fondateur de la religion de l’Humanité a remplacé Dieu par l’humanité. Ces travaux inspirent le théologien Henri de Lubac pour &lt;em&gt;Le Drame de l’humanisme athée&lt;/em&gt; (1944). Il écrit aussi sur les conversions de Maine de Biran, sur Rousseau et sur Bergson, et défend l’idée d’une philosophie chrétienne.&lt;/p&gt; &lt;p&gt;Passionné de théâtre, il est pendant des décennies critique dramatique et publie &lt;em&gt;L’Essence du théâtre&lt;/em&gt; (1943), où il voit dans la représentation une présence réelle, une action vivante et non un simple texte. Membre de l’Académie des sciences morales et politiques, il est élu en 1979 à l’Académie française, au fauteuil de son maître Gilson. Il meurt à Paris en 1994.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H150" s="48" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.laphilo.fr/pho/birault-mini.webp</t>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/gouhier-mini.webp</t>
         </is>
       </c>
       <c r="J150" s="48" t="inlineStr">
         <is>
-          <t xml:space="preserve">metaphysique ; spiritualite</t>
+          <t xml:space="preserve">metaphysique ; spiritualite ; esthetique</t>
         </is>
       </c>
       <c r="K150" s="48" t="inlineStr">
         <is>
-          <t xml:space="preserve">Phénoménologie</t>
+          <t xml:space="preserve">Spiritualisme ; Cartésianisme</t>
         </is>
       </c>
       <c r="L150" s="48" t="inlineStr">
         <is>
-          <t xml:space="preserve">philosophe français, grand lecteur de Heidegger, de Nietzsche et de Pascal.</t>
+          <t xml:space="preserve">historien français de la philosophie, de Descartes à Bergson, et critique dramatique.</t>
         </is>
       </c>
       <c r="N150" t="inlineStr">
@@ -9879,51 +9886,46 @@
     </row>
     <row r="151" ht="176.25" customHeight="1" s="49">
       <c r="A151" s="47">
-        <v>1923</v>
+        <v>1918</v>
       </c>
       <c r="B151" s="47" t="inlineStr">
         <is>
-          <t xml:space="preserve">2007</t>
+          <t xml:space="preserve">1990</t>
         </is>
       </c>
       <c r="C151" s="47" t="inlineStr">
         <is>
-          <t xml:space="preserve">1923 – 2007</t>
+          <t xml:space="preserve">1918 – 1990</t>
         </is>
       </c>
       <c r="D151" s="47" t="inlineStr">
         <is>
-          <t xml:space="preserve">André GORZ</t>
+          <t xml:space="preserve">Henri BIRAULT</t>
         </is>
       </c>
       <c r="E151" s="85" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Andr%C3%A9_Gorz" title=" Wikipedia"&gt;André GORZ&lt;/a&gt; est un philosophe et journaliste français d’origine autrichienne, l’un des fondateurs de l’écologie politique. Né Gerhart Hirsch à Vienne en 1923, d’un père juif et d’une mère catholique, il est envoyé en Suisse en 1939 pour échapper à la guerre et y devient ingénieur chimiste. En 1946, il rencontre &lt;a href="https://fr.wikipedia.org/wiki/Jean-Paul_Sartre" title=" Wikipedia"&gt;Jean-Paul Sartre&lt;/a&gt;, qui le marque profondément. Installé à Paris en 1949, il écrit sous le nom de Michel Bosquet pour &lt;em&gt;L’Express&lt;/em&gt;, puis participe en 1964 à la fondation du &lt;em&gt;Nouvel Observateur&lt;/em&gt;.&lt;/p&gt; &lt;p&gt;Dans &lt;em&gt;Le Traître&lt;/em&gt; (1958), préfacé par Sartre, il analyse sa propre vie en existentialiste. Penseur du marxisme critique, il s’intéresse ensuite au travail : dans &lt;em&gt;Adieux au prolétariat&lt;/em&gt; (1980), il affirme que la classe ouvrière n’est plus le sujet de l’émancipation, et que la libération passe par la réduction du temps de travail. L’automatisation permettrait de travailler beaucoup moins, et de développer les activités libres, choisies pour elles-mêmes, plutôt que de produire et consommer toujours plus.&lt;/p&gt; &lt;p&gt;Dès &lt;em&gt;Écologie et politique&lt;/em&gt; (1975), il relie la crise écologique au capitalisme : la croissance infinie détruit la nature et les liens humains. L’écologie doit être une politique de l’autonomie, qui permette de « produire moins, vivre mieux ». Il défendra plus tard un revenu d’existence versé à tous, indépendamment de l’emploi. Dans &lt;em&gt;Lettre à D.&lt;/em&gt; (2006), il écrit un émouvant livre d’amour à sa femme Dorine, gravement malade. Ils se donnent la mort ensemble en 2007, dans leur maison de Vosnon, dans l’Aube.&lt;/p&gt;</t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Henri_Birault" title=" Wikipedia"&gt;Henri BIRAULT&lt;/a&gt; est un philosophe français. Né à Paris en 1918, il entre à l’École normale supérieure en 1939, dans la même promotion que Louis Althusser et Jules Vuillemin, et est reçu deuxième à l’agrégation de philosophie en 1945. Élève de Louis Lavelle et de Jean Nabert, il découvre ensuite l’œuvre de &lt;a href="https://fr.wikipedia.org/wiki/Martin_Heidegger" title=" Wikipedia"&gt;Martin Heidegger&lt;/a&gt;, dont il devient, avec Jean Beaufret, l’un des grands commentateurs français. Il enseigne en khâgne au lycée Henri-IV, puis à la Sorbonne.&lt;/p&gt; &lt;p&gt;Professeur admiré, il marque plusieurs générations d’étudiants par ses lectures lentes et minutieuses des textes, qu’il lit dans leur langue d’origine, en grec, en latin, en allemand. Sa réflexion, nourrie de Pascal, de Kant, de Nietzsche et de Heidegger, porte sur la question de l’être et sur la finitude humaine. Avec Heidegger, il cherche à comprendre ce que veut dire penser, au-delà de la métaphysique qui a réduit l’être à un objet disponible pour la science et la technique. Il en tire &lt;em&gt;Heidegger et l’expérience de la pensée&lt;/em&gt; (1978), qui reste l’une des grandes introductions françaises à cette œuvre difficile.&lt;/p&gt; &lt;p&gt;Sa contribution la plus célèbre, « De la béatitude chez Nietzsche », présentée en 1964 au colloque de Royaumont, montre que Nietzsche n’est pas seulement le penseur de la volonté de puissance et de la mort de Dieu, mais aussi celui d’une joie, d’une approbation sans réserve de la vie, de l’« amour du destin ». Respecté par Deleuze et ses contemporains, il publie peu et réécrit sans cesse. Il meurt en 1990. &lt;em&gt;De l’Être, du divin et des dieux&lt;/em&gt; paraît en 2005.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H151" s="48" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.laphilo.fr/pho/gorz-mini.webp</t>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/birault-mini.webp</t>
         </is>
       </c>
       <c r="J151" s="48" t="inlineStr">
         <is>
-          <t xml:space="preserve">politique ; ethique</t>
+          <t xml:space="preserve">metaphysique ; spiritualite</t>
         </is>
       </c>
       <c r="K151" s="48" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ecologisme ; Marxisme</t>
+          <t xml:space="preserve">Phénoménologie</t>
         </is>
       </c>
       <c r="L151" s="48" t="inlineStr">
         <is>
-          <t xml:space="preserve">philosophe et journaliste français, l’un des fondateurs de l’écologie politique.</t>
-        </is>
-      </c>
-      <c r="M151" t="inlineStr">
-        <is>
-          <t xml:space="preserve">juive</t>
+          <t xml:space="preserve">philosophe français, grand lecteur de Heidegger, de Nietzsche et de Pascal.</t>
         </is>
       </c>
       <c r="N151" t="inlineStr">
@@ -9931,52 +9933,55 @@
           <t xml:space="preserve">occident</t>
         </is>
       </c>
-      <c r="O151">
-        <v>2</v>
-      </c>
+      <c r="O151"/>
     </row>
     <row r="152" ht="176.25" customHeight="1" s="49">
       <c r="A152" s="47">
-        <v>1936</v>
+        <v>1923</v>
       </c>
       <c r="B152" s="47" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025</t>
+          <t xml:space="preserve">2007</t>
         </is>
       </c>
       <c r="C152" s="47" t="inlineStr">
         <is>
-          <t xml:space="preserve">1936 – 2025</t>
+          <t xml:space="preserve">1923 – 2007</t>
         </is>
       </c>
       <c r="D152" s="47" t="inlineStr">
         <is>
-          <t xml:space="preserve">Alain ROGER</t>
+          <t xml:space="preserve">André GORZ</t>
         </is>
       </c>
       <c r="E152" s="85" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Alain_Roger" title=" Wikipedia"&gt;Alain ROGER&lt;/a&gt; est un philosophe et écrivain français. Né à Mirecourt, dans les Vosges, en 1936, ancien élève de l’École normale supérieure, agrégé de philosophie et élève de &lt;a href="https://fr.wikipedia.org/wiki/Gilles_Deleuze" title=" Wikipedia"&gt;Gilles Deleuze&lt;/a&gt;, il enseigne l’esthétique à l’université de Clermont-Ferrand. Romancier, il publie notamment &lt;em&gt;La Travestie&lt;/em&gt; (1987), adaptée au cinéma par Yves Boisset. Mais il est surtout connu comme le grand théoricien français du &lt;a href="https://fr.wikipedia.org/wiki/Paysage" title=" Wikipedia"&gt;paysage&lt;/a&gt;, auquel il consacre l’essentiel de son œuvre de philosophe.&lt;/p&gt; &lt;p&gt;Dans &lt;em&gt;Nus et paysages&lt;/em&gt; (1978) puis dans le &lt;em&gt;Court traité du paysage&lt;/em&gt; (1997), il soutient que la beauté de la nature n’est pas naturelle : nous voyons le monde à travers les œuvres d’art. Il reprend à Montaigne le mot « artialisation » pour désigner cette transformation de la nature par l’art. Elle peut être directe, « in situ », quand on façonne un jardin ou un corps, ou indirecte, « in visu », quand la peinture, la poésie ou la photographie éduquent notre regard. Le paysage naît ainsi au XVe siècle dans la peinture flamande, par la « fenêtre » ouverte au fond des tableaux.&lt;/p&gt; &lt;p&gt;Il montre que des lieux longtemps jugés affreux, comme la montagne ou le bord de mer, ne sont devenus beaux qu’au XVIIIe siècle, grâce aux écrivains et aux peintres. Ses travaux inspirent paysagistes et aménageurs, et il enseigne à l’école d’architecture de Paris-La Villette. Il est aussi l’auteur d’un &lt;em&gt;Bréviaire de la bêtise&lt;/em&gt; (2008), recueil d’aphorismes sur la sottise et ses formes les plus savantes. Il meurt à Belley, dans l’Ain, le 7 octobre 2025.&lt;/p&gt;</t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Andr%C3%A9_Gorz" title=" Wikipedia"&gt;André GORZ&lt;/a&gt; est un philosophe et journaliste français d’origine autrichienne, l’un des fondateurs de l’écologie politique. Né Gerhart Hirsch à Vienne en 1923, d’un père juif et d’une mère catholique, il est envoyé en Suisse en 1939 pour échapper à la guerre et y devient ingénieur chimiste. En 1946, il rencontre &lt;a href="https://fr.wikipedia.org/wiki/Jean-Paul_Sartre" title=" Wikipedia"&gt;Jean-Paul Sartre&lt;/a&gt;, qui le marque profondément. Installé à Paris en 1949, il écrit sous le nom de Michel Bosquet pour &lt;em&gt;L’Express&lt;/em&gt;, puis participe en 1964 à la fondation du &lt;em&gt;Nouvel Observateur&lt;/em&gt;.&lt;/p&gt; &lt;p&gt;Dans &lt;em&gt;Le Traître&lt;/em&gt; (1958), préfacé par Sartre, il analyse sa propre vie en existentialiste. Penseur du marxisme critique, il s’intéresse ensuite au travail : dans &lt;em&gt;Adieux au prolétariat&lt;/em&gt; (1980), il affirme que la classe ouvrière n’est plus le sujet de l’émancipation, et que la libération passe par la réduction du temps de travail. L’automatisation permettrait de travailler beaucoup moins, et de développer les activités libres, choisies pour elles-mêmes, plutôt que de produire et consommer toujours plus.&lt;/p&gt; &lt;p&gt;Dès &lt;em&gt;Écologie et politique&lt;/em&gt; (1975), il relie la crise écologique au capitalisme : la croissance infinie détruit la nature et les liens humains. L’écologie doit être une politique de l’autonomie, qui permette de « produire moins, vivre mieux ». Il défendra plus tard un revenu d’existence versé à tous, indépendamment de l’emploi. Dans &lt;em&gt;Lettre à D.&lt;/em&gt; (2006), il écrit un émouvant livre d’amour à sa femme Dorine, gravement malade. Ils se donnent la mort ensemble en 2007, dans leur maison de Vosnon, dans l’Aube.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H152" s="48" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.laphilo.fr/pho/alainroger-mini.webp</t>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/gorz-mini.webp</t>
         </is>
       </c>
       <c r="J152" s="48" t="inlineStr">
         <is>
-          <t xml:space="preserve">esthetique</t>
+          <t xml:space="preserve">politique ; ethique</t>
         </is>
       </c>
       <c r="K152" s="48" t="inlineStr">
         <is>
-          <t xml:space="preserve">Constructivisme</t>
+          <t xml:space="preserve">Ecologisme ; Marxisme</t>
         </is>
       </c>
       <c r="L152" s="48" t="inlineStr">
         <is>
-          <t xml:space="preserve">philosophe et romancier français, théoricien de l’« artialisation » et de l’invention du paysage.</t>
+          <t xml:space="preserve">philosophe et journaliste français, l’un des fondateurs de l’écologie politique.</t>
+        </is>
+      </c>
+      <c r="M152" t="inlineStr">
+        <is>
+          <t xml:space="preserve">juive</t>
         </is>
       </c>
       <c r="N152" t="inlineStr">
@@ -9984,50 +9989,52 @@
           <t xml:space="preserve">occident</t>
         </is>
       </c>
-      <c r="O152"/>
+      <c r="O152">
+        <v>2</v>
+      </c>
     </row>
     <row r="153" ht="176.25" customHeight="1" s="49">
       <c r="A153" s="47">
-        <v>1938</v>
+        <v>1936</v>
       </c>
       <c r="B153" s="47" t="inlineStr">
         <is>
-          <t xml:space="preserve">2021</t>
+          <t xml:space="preserve">2025</t>
         </is>
       </c>
       <c r="C153" s="47" t="inlineStr">
         <is>
-          <t xml:space="preserve">1938 – 2021</t>
+          <t xml:space="preserve">1936 – 2025</t>
         </is>
       </c>
       <c r="D153" s="47" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pierre RABHI</t>
+          <t xml:space="preserve">Alain ROGER</t>
         </is>
       </c>
       <c r="E153" s="85" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Pierre_Rabhi" title=" Wikipedia"&gt;Pierre RABHI&lt;/a&gt; est un agriculteur, essayiste et militant français, l’une des figures de l’&lt;a href="https://fr.wikipedia.org/wiki/%C3%89cologisme" title=" Wikipedia"&gt;écologie&lt;/a&gt; en France. Né Rabah Rabhi en 1938 à Kenadsa, une oasis du sud de l’Algérie, il perd sa mère très jeune et est confié à un couple de Français d’Oran ; il se convertit au catholicisme et prend le prénom de Pierre. Venu à Paris, il travaille comme ouvrier, puis s’installe en 1961 avec sa femme Michèle dans les Cévennes ardéchoises, où il devient paysan et pratique une agriculture sans produits chimiques.&lt;/p&gt; &lt;p&gt;À partir de 1981, il forme des paysans au Burkina Faso, puis dans d’autres pays d’Afrique, à l’« agroécologie », une agriculture qui respecte les sols et rend les communautés autonomes. Dans ses livres, comme &lt;em&gt;Vers la sobriété heureuse&lt;/em&gt; (2010), il critique la société de consommation et l’idéologie de la croissance : il faut apprendre à vivre avec moins pour être plus heureux. En 2007, il fonde le mouvement Colibris, d’après une légende amérindienne : pendant un incendie de forêt, le colibri apporte des gouttes d’eau dans son bec, car il « fait sa part ».&lt;/p&gt; &lt;p&gt;Très populaire, il est candidat à l’élection présidentielle de 2002, sans réunir les signatures nécessaires. Son discours spirituel, sa proximité avec l’anthroposophie et son peu d’intérêt pour les combats politiques lui valent aussi des critiques, notamment de journalistes et de scientifiques qui contestent certaines de ses affirmations sur l’agriculture. Il meurt à Lyon en 2021. Son appel à une « insurrection des consciences » a inspiré de nombreuses initiatives locales d’écologie.&lt;/p&gt;</t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Alain_Roger" title=" Wikipedia"&gt;Alain ROGER&lt;/a&gt; est un philosophe et écrivain français. Né à Mirecourt, dans les Vosges, en 1936, ancien élève de l’École normale supérieure, agrégé de philosophie et élève de &lt;a href="https://fr.wikipedia.org/wiki/Gilles_Deleuze" title=" Wikipedia"&gt;Gilles Deleuze&lt;/a&gt;, il enseigne l’esthétique à l’université de Clermont-Ferrand. Romancier, il publie notamment &lt;em&gt;La Travestie&lt;/em&gt; (1987), adaptée au cinéma par Yves Boisset. Mais il est surtout connu comme le grand théoricien français du &lt;a href="https://fr.wikipedia.org/wiki/Paysage" title=" Wikipedia"&gt;paysage&lt;/a&gt;, auquel il consacre l’essentiel de son œuvre de philosophe.&lt;/p&gt; &lt;p&gt;Dans &lt;em&gt;Nus et paysages&lt;/em&gt; (1978) puis dans le &lt;em&gt;Court traité du paysage&lt;/em&gt; (1997), il soutient que la beauté de la nature n’est pas naturelle : nous voyons le monde à travers les œuvres d’art. Il reprend à Montaigne le mot « artialisation » pour désigner cette transformation de la nature par l’art. Elle peut être directe, « in situ », quand on façonne un jardin ou un corps, ou indirecte, « in visu », quand la peinture, la poésie ou la photographie éduquent notre regard. Le paysage naît ainsi au XVe siècle dans la peinture flamande, par la « fenêtre » ouverte au fond des tableaux.&lt;/p&gt; &lt;p&gt;Il montre que des lieux longtemps jugés affreux, comme la montagne ou le bord de mer, ne sont devenus beaux qu’au XVIIIe siècle, grâce aux écrivains et aux peintres. Ses travaux inspirent paysagistes et aménageurs, et il enseigne à l’école d’architecture de Paris-La Villette. Il est aussi l’auteur d’un &lt;em&gt;Bréviaire de la bêtise&lt;/em&gt; (2008), recueil d’aphorismes sur la sottise et ses formes les plus savantes. Il meurt à Belley, dans l’Ain, le 7 octobre 2025.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H153" s="48" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.laphilo.fr/pho/rabhi-mini.webp</t>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/alainroger-mini.webp</t>
         </is>
       </c>
       <c r="J153" s="48" t="inlineStr">
         <is>
-          <t xml:space="preserve">ethique ; politique ; spiritualite</t>
+          <t xml:space="preserve">esthetique</t>
         </is>
       </c>
       <c r="K153" s="48" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ecologisme</t>
+          <t xml:space="preserve">Constructivisme</t>
         </is>
       </c>
       <c r="L153" s="48" t="inlineStr">
         <is>
-          <t xml:space="preserve">agriculteur et essayiste français, pionnier de l’agroécologie et chantre de la « sobriété heureuse ».</t>
+          <t xml:space="preserve">philosophe et romancier français, théoricien de l’« artialisation » et de l’invention du paysage.</t>
         </is>
       </c>
       <c r="N153" t="inlineStr">
@@ -10039,55 +10046,46 @@
     </row>
     <row r="154" ht="176.25" customHeight="1" s="49">
       <c r="A154" s="47">
-        <v>1937</v>
-      </c>
-      <c r="B154" s="47">
-        <v>2026</v>
+        <v>1938</v>
+      </c>
+      <c r="B154" s="47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2021</t>
+        </is>
       </c>
       <c r="C154" s="47" t="inlineStr">
         <is>
-          <t xml:space="preserve">1937 – 2026</t>
+          <t xml:space="preserve">1938 – 2021</t>
         </is>
       </c>
       <c r="D154" s="47" t="inlineStr">
         <is>
-          <t xml:space="preserve">Éliane ESCOUBAS</t>
+          <t xml:space="preserve">Pierre RABHI</t>
         </is>
       </c>
       <c r="E154" s="85" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/%C3%89liane_Escoubas"  style="color:#6A142A"  title=" Wikipedia"&gt;Éliane ESCOUBAS&lt;/a&gt;  est une philosophe française, historienne de la philosophie et traductrice. Elle se rattache à l’école phénoménologique et travaille principalement sur la philosophie allemande, la phénoménologie de l’art et la psychiatrie phénoménologique, dite Daseinsanalyse. Après une formation marquée par les cours de Gérard Granel sur Husserl, Kant et Hegel à Toulouse, elle enseigne dans le secondaire puis devient maître de conférences, puis professeur de philosophie, tout en menant des recherches au CNRS et en participant à la création du Collège international de Philosophie. &lt;/p&gt; &lt;p&gt; Elle met au centre la phénoménologie de l’expérience sensible, en particulier la manière dont le monde et le sujet adviennent à travers le sentir, l’affect et la perception. Elle montre que la phénoménologie fournit un prisme particulièrement adapté pour penser l’esthétique, car l’œuvre d’art apparaît comme un mode privilégié pour saisir comment le sujet et le monde se co‑constituent dans une expérience sensible et existentielle. &lt;/p&gt; &lt;p&gt; Une grande partie de son œuvre est consacrée à une « esthétique du sentir » où l’art n’est pas seulement une illustration de la philosophie, mais un mode de connaissance autonome. Dans ses travaux comme Imago mundi. Topologie de l’art ou L’invention de l’art, elle montre que l’image et l’œuvre picturale ne se réduisent pas à « représentation » ou « signe », mais relèvent d’une apparition du monde lui‑même, d’une spatialité et d’une temporalité qui précèdent les catégories classiques de l’objet. &lt;/p&gt; &lt;p&gt; Sa philosophie s’ouvre aussi à la phénoménologie clinique et à la psychiatrie, notamment à travers la Daseinsanalyse et la place de l’affect et de l’affectivité dans la constitution du sujet. En explorant les affectivités dans la modernité et la phénoménologie, Escoubas prolonge ainsi une réflexion sur la manière dont le vécu, le corps et la subjectivité forment un champ de savoir propre, à la fois esthétique, analytique et existentiel. Elle meurt à Paris le 18 juillet 2026. &lt;/p&gt;  &lt;audio controls title="Alain BADIOU par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/10080-25.11.2011-ITEMA_20320112-2011C3403E0190-ITE_00047070_RSCE-21.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt; 
-</t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Pierre_Rabhi" title=" Wikipedia"&gt;Pierre RABHI&lt;/a&gt; est un agriculteur, essayiste et militant français, l’une des figures de l’&lt;a href="https://fr.wikipedia.org/wiki/%C3%89cologisme" title=" Wikipedia"&gt;écologie&lt;/a&gt; en France. Né Rabah Rabhi en 1938 à Kenadsa, une oasis du sud de l’Algérie, il perd sa mère très jeune et est confié à un couple de Français d’Oran ; il se convertit au catholicisme et prend le prénom de Pierre. Venu à Paris, il travaille comme ouvrier, puis s’installe en 1961 avec sa femme Michèle dans les Cévennes ardéchoises, où il devient paysan et pratique une agriculture sans produits chimiques.&lt;/p&gt; &lt;p&gt;À partir de 1981, il forme des paysans au Burkina Faso, puis dans d’autres pays d’Afrique, à l’« agroécologie », une agriculture qui respecte les sols et rend les communautés autonomes. Dans ses livres, comme &lt;em&gt;Vers la sobriété heureuse&lt;/em&gt; (2010), il critique la société de consommation et l’idéologie de la croissance : il faut apprendre à vivre avec moins pour être plus heureux. En 2007, il fonde le mouvement Colibris, d’après une légende amérindienne : pendant un incendie de forêt, le colibri apporte des gouttes d’eau dans son bec, car il « fait sa part ».&lt;/p&gt; &lt;p&gt;Très populaire, il est candidat à l’élection présidentielle de 2002, sans réunir les signatures nécessaires. Son discours spirituel, sa proximité avec l’anthroposophie et son peu d’intérêt pour les combats politiques lui valent aussi des critiques, notamment de journalistes et de scientifiques qui contestent certaines de ses affirmations sur l’agriculture. Il meurt à Lyon en 2021. Son appel à une « insurrection des consciences » a inspiré de nombreuses initiatives locales d’écologie.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H154" s="48" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.laphilo.fr/pho/eescoubas-mini.webp</t>
-        </is>
-      </c>
-      <c r="I154" t="inlineStr">
-        <is>
-          <t xml:space="preserve">https://laphilo.fr/photo/escoubas.webp</t>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/rabhi-mini.webp</t>
         </is>
       </c>
       <c r="J154" s="48" t="inlineStr">
         <is>
-          <t xml:space="preserve">esthetique ; epistemologie</t>
+          <t xml:space="preserve">ethique ; politique ; spiritualite</t>
         </is>
       </c>
       <c r="K154" s="48" t="inlineStr">
         <is>
-          <t xml:space="preserve">Phénoménologie</t>
+          <t xml:space="preserve">Ecologisme</t>
         </is>
       </c>
       <c r="L154" s="48" t="inlineStr">
         <is>
-          <t xml:space="preserve">philosophe française, historienne de la philosophie et traductrice.</t>
-        </is>
-      </c>
-      <c r="M154" t="inlineStr">
-        <is>
-          <t xml:space="preserve">femme</t>
+          <t xml:space="preserve">agriculteur et essayiste français, pionnier de l’agroécologie et chantre de la « sobriété heureuse ».</t>
         </is>
       </c>
       <c r="N154" t="inlineStr">
@@ -10095,6 +10093,7 @@
           <t xml:space="preserve">occident</t>
         </is>
       </c>
+      <c r="O154"/>
     </row>
     <row r="1048566" ht="12.75" customHeight="1" s="49"/>
     <row r="1048567" ht="12.75" customHeight="1" s="49"/>
@@ -10195,30 +10194,30 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H126" display="https://www.laphilo.fr/pho/mwittig-mini.webp" r:id="rId79"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E127" display=" &lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Michel_Hulin&quot;  title=&quot; Wikipedia&quot;&gt;Michel HULIN&lt;/a&gt; était un philosophe français récemment décédé, grand spécialiste de la &lt;a href=&quot;https://www.youtube.com/watch?v=tJFic9y58Sc&quot; title=&quot; Aperçu de l’hindouisme avec Michel Hulin par Resonances &quot;&gt;philosophie indienne &lt;/a&gt; et de la comparaison entre pensée européenne et pensée asiatique, notamment de l’Advaïta Vedānta, le courant « non‑dualiste » du vedānta. Longtemps professeur de philosophie indienne et comparée à l’université Paris‑Sorbonne, il a joué un rôle central dans la diffusion en France des grandes écoles de pensée de l’Inde. Sa carrière s’est accompagnée d’un important travail de traduction du sanskrit et de vulgarisation, accessible à un public non spécialiste. &lt;/p&gt; &lt;p&gt; Ses recherches portent d’une part sur  &lt;a href=&quot;https://www.youtube.com/watch?v=kaJP8yDwHeY&quot; title=&quot; For intérieur par Resonnances &quot;&gt;la pensée indienne classique &lt;/a&gt;  (notion d’ahamkāra, textes vedāntins et shivaïtes d’inspiration tantrique), d’autre part sur les questions épistémologiques et métaphysiques que soulève la rencontre entre les traditions européennes et asiatiques. Dans sa thèse, Le Principe de l’ego dans la pensée indienne classique, il analyse la notion de « faux moi » et montre comment elle éclaire notre expérience ordinaire de la conscience. Il s’intéresse également à la question du temps, de l’éternité et des expériences dites mystiques, qu’il relie à des vécus très concrets. &lt;/p&gt; &lt;p&gt; Dans des ouvrages comme La Face cachée du temps, La Mystique sauvage, Hegel et l’Orient, Shankara et la non‑dualité ou encore l’anthologie L’Inde des sages, il  conjugue une érudition très précise et un style volontairement clair. Il montre comment des interrogations métaphysiques complexes – sur le moi, le temps, l’au‑delà ou l’expérience spirituelle – touchent directement la vie intérieure de chacun. Par son enseignement et ses livres, il a contribué à installer durablement en France une philosophie comparée attentive au dialogue entre Europe et Inde. &lt;p&gt; &lt;/p&gt;&lt;audio controls title=&quot;  Philosophies indiennes (1/4) : Upanishads, les textes fondateurs ?  par France Culture&quot;&gt; &lt;source src=&quot;https://media.radiofrance-podcast.net/podcast09/10467-16.12.2013-ITEMA_20562153-2013C12410S0350-NET_FC_A092AF0E-5BC1-49EE-A72F-E62BB6A2A8B1-21.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt;&lt;/audio&gt;  &lt;p&gt;  &lt;/p&gt;&#10;" r:id="rId80"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H127" display="https://www.laphilo.fr/pho/mhulin-mini.webp" r:id="rId81"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H128" display="https://www.laphilo.fr/pho/jfmarquet-mini.webp" r:id="rId82"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E129" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Cl%C3%A9ment_Rosset&quot; title=&quot; Wikipedia&quot;&gt;Clément ROSSET&lt;/a&gt; était un philosophe français connu pour sa pensée radicale et son style d'écriture d'une grande clarté. Son œuvre est principalement centrée sur le concept du  &lt;a href=&quot;https://www.youtube.com/watch?v=I50Jbj6uQEU&quot; title=&quot;Clément Rosset : la réalité ne convient pas ! par Kosmos&quot;&gt;&quot;réel&quot;&lt;/a&gt;  et l'incapacité ou la difficulté de l'homme à l'accepter dans sa singularité et souvent sa cruauté. Voici les points essentiels concernant sa philosophie : &lt;/p&gt; &lt;p&gt; - &lt;a href=&quot;https://www.youtube.com/watch?v=8m_kXVBdtwg&quot;  title=&quot; Le réel et son double, Clément Rosset, 2.2 avant-propos par Thibault BELZACQ&quot;&gt;Le Réel sans double&lt;/a&gt; : Son idée maîtresse est que le réel est unique, singulier et dépourvu de tout &quot;double&quot;. Il n'y a pas d'arrière-monde, pas de sens caché, pas de consolation ou d'illusion qui puisse atténuer sa nature brute. Le réel est simplement ce qui est, dans son évidence la plus nue. &lt;/p&gt; &lt;p&gt; - Le Refus du double et de l'illusion : Une grande partie de son travail consiste à traquer les différentes formes d'illusions et de doubles que l'humanité crée pour  &lt;a href=&quot;https://philitt.fr/2023/09/12/clement-rosset-tout-est-sans-raison/&quot;  title=&quot;Clément Rosset : tout est sans raison par Phillitt&quot;&gt;échapper à la confrontation&lt;/a&gt; directe avec le réel. Ces doubles peuvent être d'ordre métaphysique, moral, psychologique, ou même esthétique.&lt;/p&gt; &lt;p&gt; - &lt;a href=&quot;https://www.youtube.com/watch?v=JDcudFE_uBQ&quot;  title=&quot;Entretien avec Pierre Dumayet (1961) par Archives&quot;&gt;Philosophie tragique&lt;/a&gt; et Joie : Bien que sa pensée puisse sembler sombre en insistant sur la cruauté et l'absurdité du réel, il développe une philosophie que l'on qualifie souvent de &quot;tragique&quot; au sens nietzschéen du terme. Il ne s'agit pas de désespoir, mais plutôt de l'affirmation de la vie et du réel tels qu'ils sont, y compris dans leurs aspects les plus difficiles. &lt;/p&gt; &lt;p&gt; Il est également remarquable par son style d'écriture. Loin du jargon philosophique abscons, il privilégie une langue simple, directe et percutante. Cette clarté formelle est au service de la clarté de sa pensée, cherchant à énoncer le réel avec le moins d'interférences possible. Son œuvre, bien que parfois restée en marge des courants universitaires dominants, a marqué par sa radicalité, sa lucidité et sa défense d'une confrontation sans fard avec le réel.  &lt;/p&gt; &lt;audio controls title=&quot;Clément Rosset par France Culture&quot;&gt; &lt;source src=&quot;https://media.radiofrance-podcast.net/podcast09/10080-20.12.2013-ITEMA_20564152-2013C3403E0215-21.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt;&lt;/audio&gt;  " r:id="rId83"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H129" display="https://www.laphilo.fr/pho/rosset-mini.webp" r:id="rId84"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E130" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Jacques_Bouveresse&quot;  title=&quot; Wikipedia&quot;&gt;Jacques BOUVERESSE&lt;/a&gt; était un philosophe français du courant analytique, connu pour son rationalisme exigeant, son &lt;a href=&quot;https://www.youtube.com/watch?v=mfGM00nmj20&quot;  title=&quot; Wittgenstein et l'intériorité 一 Jacques Bouveresse par Andrea Cirla &quot;&gt;travail sur Wittgenstein &lt;/a&gt; et sa critique des dérives du milieu intellectuel français. Il a largement contribué à introduire et stabiliser en France une philosophie soucieuse de vérité, de clarté et d’argumentation rigoureuse. &lt;/p&gt; &lt;p&gt; Ses domaines privilégiés sont la philosophie de la connaissance, des sciences, des mathématiques, de la logique, du langage, ainsi qu’une philosophie de la culture attentive à la littérature et à la critique sociale.  Il se réclame du rationalisme des Lumières et s’inspire fortement de la philosophie analytique, du Cercle de Vienne, de Frege, de Gödel et de la tradition d’Europe centrale. Wittgenstein, qu’il contribue à faire connaître en France, est l’une de ses références centrales. &lt;/p&gt; &lt;p&gt; Il défend une position rationaliste dont le prolongement éthique est ce qu’il appelle la  &lt;a href=&quot;https://www.persee.fr/doc/lgge_0458-726x_1971_num_6_21_2079&quot; title=&quot;Langage ordinaire et philosophie par Persée &quot;&gt;&quot;modestie intellectuelle&quot; &lt;/a&gt; : ne pas exagérer ce que la philosophie peut faire, refuser le pathos et le prestige facile. Il combat le relativisme, l’historicisme radical et les remises en cause globales de la notion de vérité, notamment chez certains auteurs français, tout en reconnaissant par ailleurs leur importance. &lt;/p&gt; &lt;p&gt; Sa grande thèse, &quot;Le Mythe de l’intériorité&quot;, porte sur Wittgenstein, le langage privé, l’expérience et la signification, et a joué un rôle clé dans la réception française de Wittgenstein. Il consacre de nombreux travaux à Robert Musil et Karl Kraus, qu’il lit comme des alliés dans un combat pour l’exactitude, la critique de la bêtise et des illusions de la culture moderne. &lt;/p&gt;  &lt;audio controls title=&quot;Jacques Bouveresse, à la recherche de la clarté par France Culture&quot;&gt; &lt;source src=&quot;https://media.radiofrance-podcast.net/podcast09/10351-11.05.2021-ITEMA_23961779-2000C3500E0287-21.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt;" r:id="rId85"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H130" display="https://www.laphilo.fr/pho/bouveresse-mini.webp" r:id="rId86"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E131" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Jean-Luc_Nancy&quot;  title=&quot; Wikipedia&quot;&gt;Jean-Luc NANCY&lt;/a&gt; était un philosophe français, agrégé de philosophie, il fut professeur à l'Université de Strasbourg jusqu'à sa retraite. Sa pensée, en dialogue constant avec Heidegger, Derrida et Lacoue-Labarthe — avec lequel il collabora étroitement — porte sur le « sens du monde », la communauté, le corps et le toucher. &lt;/p&gt; &lt;p&gt; Son œuvre est marquée par le questionnement du « with » (avec), du « being-with » heideggerien. Dans &lt;em&gt;La Communauté désoeuvrée&lt;/em&gt; (1986), il développe une pensée de la communauté qui refuse toute forme d'immanentisme ou de fusion : la communauté véritable n'est pas une substance commune, mais  &lt;a href=&quot;https://www.youtube.com/watch?v=fZK6pEAPxEw&quot;  title=&quot;jean luc Nancy par Institut Humanités &quot;&gt;l'exposition partagée &lt;/a&gt; de la singularité de chacun. Cette réflexion, en dialogue critique avec Blanchot et Bataille, a eu un retentissement considérable dans les débats contemporains sur la politique, la communauté et l'identité. &lt;/p&gt; &lt;p&gt; Dans &lt;em&gt;Corpus&lt;/em&gt; (1992) et &lt;em&gt;Noli me tangere&lt;/em&gt; (2003), il explore  &lt;a href=&quot;https://www.youtube.com/watch?v=1kCExw6Wp9k&quot;  title=&quot;jean luc Nancy par Lacan TV &quot;&gt;la philosophie du corps &lt;/a&gt; et du toucher comme modes fondamentaux de l'être-au-monde. Son essai sur le sens — &lt;em&gt;Le Sens du monde&lt;/em&gt; (1993) — aborde la question de la possibilité du sens dans un monde déserté par les transcendances. &lt;em&gt;L'Intrus&lt;/em&gt; (2000), bref récit autobiographique sur sa transplantation cardiaque, mêle réflexion philosophique et expérience personnelle de la maladie et de l'altérité. Son œuvre, immense et diverse, témoigne d'une pensée vivante et rigoureuse toujours en dialogue avec la littérature, l'art et la politique. &lt;/p&gt;  &lt;audio controls title=&quot;Jean luc Nancy par France Culture&quot;&gt; &lt;source src=&quot;https://media.radiofrance-podcast.net/podcast09/11472-06.02.2011-ITEMA_20267545-2011C16153E0003-ITE_00040439_RSCE-21.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt;" r:id="rId87"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H131" display="https://www.laphilo.fr/pho/jlnancy-mini.webp" r:id="rId88"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E132" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Philippe_Lacoue-Labarthe&quot;  title=&quot; Wikipedia&quot;&gt;Philippe LACOUE-LABARTHE&lt;/a&gt; était un philosophe, critique littéraire, traducteur et théoricien français né à Tours et connu pour ses travaux sur la mimésis, le romantisme allemand, Hölderlin, Heidegger, Derrida et la relation entre esthétique et politique. Il a aussi beaucoup compté dans le milieu intellectuel de Strasbourg, où il a enseigné longtemps et travaillé avec Jean-Luc Nancy. &lt;/p&gt; &lt;p&gt; Son  &lt;a href=&quot;https://maitron.fr/lacoue-labarthe-philippe/&quot;  title=&quot; lacoue-labarthe par le maitron&quot;&gt;œuvre interroge &lt;/a&gt; la façon dont l’art, la philosophie et la politique s’entrecroisent, notamment à travers la notion de mimésis et la critique de l’“esthétisation du politique”. Il a aussi travaillé sur le romantisme allemand et sur la réception de Hölderlin, qu’il considérait comme une figure majeure. &lt;/p&gt; &lt;p&gt; Parmi les livres souvent cités, on trouve Le Titre de la lettre avec Jean-Luc Nancy, L’Absolu littéraire, L’Imitation des modernes, La Fiction du politique et Heidegger, la politique du poème. Il a également traduit plusieurs auteurs allemands majeurs, dont Heidegger, Hölderlin, Nietzsche, Benjamin et Celan. &lt;/p&gt; &lt;p&gt; Sa pensée tourne autour de trois idées principales : - La représentation n’est jamais transparente : ce que nous montrons, racontons ou jouons n’est jamais la réalité elle-même, mais une forme, un masque, une imitation. - La littérature et le théâtre sont essentiels pour comprendre la philosophie, parce qu’ils révèlent ce que les concepts cachent ou simplifient.popups. - Le lien entre esthétique et politique est dangereux : il a beaucoup réfléchi à la manière dont l’art, les mythes et les images peuvent servir le politique, y compris dans des formes fascisantes. &lt;/p&gt; &#10; &lt;audio controls title=&quot;les versions de philippe lacoue labarthe par France Culture&quot;&gt; &lt;source src=&quot;https://media.radiofrance-podcast.net/podcast09/16409-16.03.2007-ITEMA_20062386-2007C6409S0011-MEM_000036772_RF-21.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt;  " r:id="rId89"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H132" display="https://www.laphilo.fr/pho/pllabarthe-mini.webp" r:id="rId90"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H133" display="https://www.laphilo.fr/pho/fdelaporte-mini.webp" r:id="rId91"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H134" display="https://www.laphilo.fr/pho/lecourt-mini.webp" r:id="rId92"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E135" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Jean-Michel_Berthelot&quot;  title=&quot; Wikipedia&quot;&gt;Jean-Michel BERTHELOT&lt;/a&gt; était un philosophe et sociologue français spécialiste d'épistémologie des sciences sociales. Professeur à l'Université de Paris IV-Sorbonne et à l'Université du Québec à Montréal, il contribua de manière décisive à la réflexion philosophique sur les fondements et les méthodes des sciences humaines et sociales. Son œuvre joint la rigueur épistémologique à une large culture philosophique et sociologique. &lt;/p&gt; &lt;p&gt; Son ouvrage principal, &lt;em&gt; &lt;a href=&quot;https://www.persee.fr/doc/sotra_0038-0296_1992_num_34_3_2605_t1_0388_0000_3&quot;  title=&quot;l’intelligence du social par persée &quot;&gt; L'Intelligence du social&lt;/a&gt; &lt;/em&gt; (1990), est une analyse approfondie des schèmes d'intelligibilité que les sciences sociales utilisent pour rendre compte de la réalité sociale : le schème causal, le schème fonctionnel, le schème structural, le schème herméneutique et d'autres modes d'explication. Berthelot montre que chaque paradigme sociologique privilégie un mode d'intelligibilité particulier, ce qui permet de comprendre à la fois leurs apports spécifiques et leurs limites. Ce livre constitue l'une des contributions les plus claires et les plus systématiques à la philosophie des sciences sociales en langue française. &lt;/p&gt; &lt;p&gt; Dans &lt;em&gt;Epistémologie des sciences sociales&lt;/em&gt; (2001, ouvrage collectif qu'il dirigea), il offrit un panorama complet des questions épistémologiques fondamentales que posent les sciences humaines et sociales : la causalité, la compréhension, la mesure, la modélisation, la réflexivité et les rapports entre science et valeurs. Ses travaux contribuèrent à établir l'épistémologie des sciences sociales comme une discipline à part entière dans le paysage universitaire français, en dialogue constant avec la philosophie des sciences anglophones et continentale. &lt;/p&gt;" r:id="rId93"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H135" display="https://www.laphilo.fr/pho/jmberthelot-mini.webp" r:id="rId94"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E136" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Daniel_Bensa%C3%AFd&quot;  title=&quot; Wikipedia&quot;&gt;Daniel BENSAÏD&lt;/a&gt; était un philosophe français marxiste, l'un des intellectuels les plus importants de la gauche radicale française de son époque. Né à Paris dans une famille juive d'origine algérienne, il fut l'un des leaders de la révolte étudiante de mai 1968 à Paris-Nanterre aux côtés de Daniel Cohn-Bendit. Professeur de philosophie à l'Université Paris VIII-Saint-Denis, il fut membre dirigeant de la Ligue communiste révolutionnaire (LCR) et de son successeur le Nouveau Parti Anticapitaliste (NPA). &lt;/p&gt; &lt;p&gt; Sa pensée philosophique chercha à renouveler le marxisme en le débarrassant des &lt;a href=&quot;https://www.youtube.com/watch?v=uxBvxfRI2CE&quot;  title=&quot;la privatisation du monde par bibou11slalala &quot;&gt; simplifications téléologiques &lt;/a&gt; et en l'ouvrant à des problématiques nouvelles. Dans &lt;em&gt;Marx l'intempestif&lt;/em&gt; (1995), il défend un Marx débarrassé du déterminisme historique et de la philosophie du progrès, un Marx « intempestif » qui pense la politique comme art du possible et de l'impossible, en dialogue avec Blaise Pascal et Walter Benjamin. Ce livre renouvela profondément la  &lt;a href=&quot;https://www.youtube.com/watch?v=is8Ya038-Q4&quot;  title=&quot;l’héritage de Marx par socialtram &quot;&gt; lecture de Marx &lt;/a&gt; dans la gauche française. &lt;/p&gt; &lt;p&gt; Dans &lt;em&gt;Le Pari mélancolique&lt;/em&gt; (1997) et &lt;em&gt;Résistances&lt;/em&gt; (2001), il développe une philosophie de l'engagement politique nourrie par la mélancolie des défaites mais portée par une fidélité irréductible à l'émancipation. Sa réflexion sur les rapports entre philosophie et politique, entre utopie et stratégie, constitue l'une des contributions les plus originales à la pensée marxiste contemporaine. Polémiste redoutable et pédagogue exigeant, il laissa une empreinte profonde sur plusieurs générations de militants et d'intellectuels de gauche. &lt;/p&gt;  &lt;audio controls title=&quot;Daniel Bensaid  par France Culture&quot;&gt; &lt;source src=&quot;https://media.radiofrance-podcast.net/podcast09/10075-11.12.2006-ITEMA_20049670-2006C6608S0221-MEM_000033324_RF-21.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt; " r:id="rId95"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H136" display="https://www.laphilo.fr/pho/bensaid-mini.webp" r:id="rId96"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G137" display="&quot;Ce virus est là pour nous préparer au nouveau régime climatique&quot; par France Culture" r:id="rId97"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H137" display="https://www.laphilo.fr/pho/latour-mini.webp" r:id="rId98"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H138" display="https://www.laphilo.fr/pho/rdamien-mini.webp" r:id="rId99"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E139" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Catherine_Colliot-Th%C3%A9l%C3%A8ne&quot; title=&quot; Wikipedia&quot;&gt;Catherine COLLIOT-THELENE&lt;/a&gt; était une philosophe française  majeure de la philosophie politique contemporaine, spécialiste de Max Weber et penseuse des droits, de la démocratie et de la propriété dans un cadre cosmopolitique. Membre de l’Institut universitaire de France, elle est reconnue comme une référence internationale des études wébériennes. &lt;/p&gt; &lt;p&gt; Son travail se situe au croisement de la philosophie politique et des sciences sociales, avec trois pôles principaux :  &lt;a href=&quot;https://www.youtube.com/watch?v=krUYFtq9Jww&quot; title=&quot;Max Weber et la violence légitime de l’état par France Culture&quot;&gt;Max Weber, la démocratie et les droits, &lt;/a&gt;  la propriété et le cosmopolitisme.  Elle traduit et commente plusieurs textes de Weber, notamment Le Savant et le politique et Les Communautés, en montrant en détail ses concepts de rationalisation, de désenchantement et de domination. &lt;/p&gt; &lt;p&gt; À partir des années 2000, elle se concentre sur les droits subjectifs, leur articulation avec l’individualisme contemporain et la transformation des rapports entre pouvoirs politiques et économiques. Elle insiste sur la nécessité de penser la normativité (ce qui doit être) à partir d’une analyse précise des structures sociales réelles, d’où son dialogue constant avec le droit, l’histoire et la sociologie. &lt;/p&gt; &lt;p&gt; Dans &quot;La Démocratie sans “demos”  paru en 2011, elle remet en question l’identification classique entre &quot;peuple&quot; et &quot;démocratie&quot;. Elle critique la superposition entre souveraineté du peuple et souveraineté territoriale de l’État, qui conduit selon elle à des versions exclusives de la démocratie. &lt;a href=&quot;https://www.youtube.com/watch?v=ps2ixtEpgYI&quot; title=&quot;la democratie c’est le droit de resistance par Journal l’Humanitét&quot;&gt;Sa philosophie cherche &lt;/a&gt;  une démocratie fondée sur des droits universalisables et sur la participation de tous les sujets, plutôt que sur l’appartenance à une communauté nationale préconstituée. &lt;/p&gt; &lt;p&gt; Elle refuse la séparation entre théorie pure et monde social : pour elle, la philosophie politique doit dialoguer avec les sciences sociales pour produire une critique efficace des institutions et des inégalités. Elle a accompagné, sans posture militante classique mais avec une forte implication intellectuelle, les luttes pour les droits des femmes, des exclus et des étrangers, en cherchant à fournir des outils conceptuels pour penser l’égalité aujourd’hui. &lt;/p&gt; &#10; &lt;audio controls title=&quot;Les défis juridiques de la migration : existe-t-il un droit à la libre circulation ? par France Culture&quot;&gt; &lt;source src=&quot;https://media.radiofrance-podcast.net/podcast09/21447-09.02.2022-ITEMA_22927630-2022C27677S0040-21.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt;" r:id="rId100"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H139" display="https://www.laphilo.fr/pho/thelene-mini.webp" r:id="rId101"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H140" display="https://www.laphilo.fr/pho/bstiegler-mini.webp" r:id="rId102"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E141" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Bernard_Mabille_(philosophe)&quot;  style=&quot;color:#6A142A&quot;  title=&quot; Wikipedia&quot;&gt;Bernard MABILLE&lt;/a&gt; était un philosophe français spécialiste de dialectique et de philosophie hégélienne, ainsi que de métaphysique contemporaine. Agrégé de philosophie et professeur à l'Université Paris IV-Sorbonne, il fut l'un des meilleurs connaisseurs français de Hegel et contribua de manière significative au renouvellement des études hégéliennes en France dans les dernières décennies du XXe siècle. &lt;/p&gt; &lt;p&gt; Sa thèse principale, &lt;em&gt;Hegel : l'épreuve de la contingence&lt;/em&gt; (1999), est une lecture originale de la philosophie hégélienne à la lumière de la problématique de la contingence. Contre les lectures qui réduisent Hegel à un penseur du nécessaire et du rationnel, Mabille montre que la contingence est au cœur même du système hégélien et que la dialectique est précisément la méthode qui permet de penser le passage du contingent au nécessaire sans l'éliminer. Cette relecture contribua à ouvrir la philosophie hégélienne à des problématiques contemporaines. &lt;/p&gt; &lt;p&gt; Dans ses travaux sur la métaphysique et la dialectique, Mabille s'intéressa également aux rapports entre la philosophie hégélienne et la phénoménologie française, notamment Merleau-Ponty et Henry. Son enseignement à la Sorbonne forma plusieurs générations d'étudiants à la rigueur de la pensée dialectique. Sa disparition prématurée priva la philosophie française d'un penseur rigoureux dont l'œuvre, bien que de volume limité, témoigne d'une lecture profonde et originale de l'idéalisme allemand et de ses prolongements contemporains. &lt;/p&gt;" r:id="rId103"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H141" display="https://www.laphilo.fr/pho/bnabille-mini.webp" r:id="rId104"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H142" display="https://www.laphilo.fr/pho/adufourmantelle-mini.webp" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H129" display="https://www.laphilo.fr/pho/jfmarquet-mini.webp" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E130" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Cl%C3%A9ment_Rosset&quot; title=&quot; Wikipedia&quot;&gt;Clément ROSSET&lt;/a&gt; était un philosophe français connu pour sa pensée radicale et son style d'écriture d'une grande clarté. Son œuvre est principalement centrée sur le concept du  &lt;a href=&quot;https://www.youtube.com/watch?v=I50Jbj6uQEU&quot; title=&quot;Clément Rosset : la réalité ne convient pas ! par Kosmos&quot;&gt;&quot;réel&quot;&lt;/a&gt;  et l'incapacité ou la difficulté de l'homme à l'accepter dans sa singularité et souvent sa cruauté. Voici les points essentiels concernant sa philosophie : &lt;/p&gt; &lt;p&gt; - &lt;a href=&quot;https://www.youtube.com/watch?v=8m_kXVBdtwg&quot;  title=&quot; Le réel et son double, Clément Rosset, 2.2 avant-propos par Thibault BELZACQ&quot;&gt;Le Réel sans double&lt;/a&gt; : Son idée maîtresse est que le réel est unique, singulier et dépourvu de tout &quot;double&quot;. Il n'y a pas d'arrière-monde, pas de sens caché, pas de consolation ou d'illusion qui puisse atténuer sa nature brute. Le réel est simplement ce qui est, dans son évidence la plus nue. &lt;/p&gt; &lt;p&gt; - Le Refus du double et de l'illusion : Une grande partie de son travail consiste à traquer les différentes formes d'illusions et de doubles que l'humanité crée pour  &lt;a href=&quot;https://philitt.fr/2023/09/12/clement-rosset-tout-est-sans-raison/&quot;  title=&quot;Clément Rosset : tout est sans raison par Phillitt&quot;&gt;échapper à la confrontation&lt;/a&gt; directe avec le réel. Ces doubles peuvent être d'ordre métaphysique, moral, psychologique, ou même esthétique.&lt;/p&gt; &lt;p&gt; - &lt;a href=&quot;https://www.youtube.com/watch?v=JDcudFE_uBQ&quot;  title=&quot;Entretien avec Pierre Dumayet (1961) par Archives&quot;&gt;Philosophie tragique&lt;/a&gt; et Joie : Bien que sa pensée puisse sembler sombre en insistant sur la cruauté et l'absurdité du réel, il développe une philosophie que l'on qualifie souvent de &quot;tragique&quot; au sens nietzschéen du terme. Il ne s'agit pas de désespoir, mais plutôt de l'affirmation de la vie et du réel tels qu'ils sont, y compris dans leurs aspects les plus difficiles. &lt;/p&gt; &lt;p&gt; Il est également remarquable par son style d'écriture. Loin du jargon philosophique abscons, il privilégie une langue simple, directe et percutante. Cette clarté formelle est au service de la clarté de sa pensée, cherchant à énoncer le réel avec le moins d'interférences possible. Son œuvre, bien que parfois restée en marge des courants universitaires dominants, a marqué par sa radicalité, sa lucidité et sa défense d'une confrontation sans fard avec le réel.  &lt;/p&gt; &lt;audio controls title=&quot;Clément Rosset par France Culture&quot;&gt; &lt;source src=&quot;https://media.radiofrance-podcast.net/podcast09/10080-20.12.2013-ITEMA_20564152-2013C3403E0215-21.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt;&lt;/audio&gt;  " r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H130" display="https://www.laphilo.fr/pho/rosset-mini.webp" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E131" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Jacques_Bouveresse&quot;  title=&quot; Wikipedia&quot;&gt;Jacques BOUVERESSE&lt;/a&gt; était un philosophe français du courant analytique, connu pour son rationalisme exigeant, son &lt;a href=&quot;https://www.youtube.com/watch?v=mfGM00nmj20&quot;  title=&quot; Wittgenstein et l'intériorité 一 Jacques Bouveresse par Andrea Cirla &quot;&gt;travail sur Wittgenstein &lt;/a&gt; et sa critique des dérives du milieu intellectuel français. Il a largement contribué à introduire et stabiliser en France une philosophie soucieuse de vérité, de clarté et d’argumentation rigoureuse. &lt;/p&gt; &lt;p&gt; Ses domaines privilégiés sont la philosophie de la connaissance, des sciences, des mathématiques, de la logique, du langage, ainsi qu’une philosophie de la culture attentive à la littérature et à la critique sociale.  Il se réclame du rationalisme des Lumières et s’inspire fortement de la philosophie analytique, du Cercle de Vienne, de Frege, de Gödel et de la tradition d’Europe centrale. Wittgenstein, qu’il contribue à faire connaître en France, est l’une de ses références centrales. &lt;/p&gt; &lt;p&gt; Il défend une position rationaliste dont le prolongement éthique est ce qu’il appelle la  &lt;a href=&quot;https://www.persee.fr/doc/lgge_0458-726x_1971_num_6_21_2079&quot; title=&quot;Langage ordinaire et philosophie par Persée &quot;&gt;&quot;modestie intellectuelle&quot; &lt;/a&gt; : ne pas exagérer ce que la philosophie peut faire, refuser le pathos et le prestige facile. Il combat le relativisme, l’historicisme radical et les remises en cause globales de la notion de vérité, notamment chez certains auteurs français, tout en reconnaissant par ailleurs leur importance. &lt;/p&gt; &lt;p&gt; Sa grande thèse, &quot;Le Mythe de l’intériorité&quot;, porte sur Wittgenstein, le langage privé, l’expérience et la signification, et a joué un rôle clé dans la réception française de Wittgenstein. Il consacre de nombreux travaux à Robert Musil et Karl Kraus, qu’il lit comme des alliés dans un combat pour l’exactitude, la critique de la bêtise et des illusions de la culture moderne. &lt;/p&gt;  &lt;audio controls title=&quot;Jacques Bouveresse, à la recherche de la clarté par France Culture&quot;&gt; &lt;source src=&quot;https://media.radiofrance-podcast.net/podcast09/10351-11.05.2021-ITEMA_23961779-2000C3500E0287-21.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt;" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H131" display="https://www.laphilo.fr/pho/bouveresse-mini.webp" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E132" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Jean-Luc_Nancy&quot;  title=&quot; Wikipedia&quot;&gt;Jean-Luc NANCY&lt;/a&gt; était un philosophe français, agrégé de philosophie, il fut professeur à l'Université de Strasbourg jusqu'à sa retraite. Sa pensée, en dialogue constant avec Heidegger, Derrida et Lacoue-Labarthe — avec lequel il collabora étroitement — porte sur le « sens du monde », la communauté, le corps et le toucher. &lt;/p&gt; &lt;p&gt; Son œuvre est marquée par le questionnement du « with » (avec), du « being-with » heideggerien. Dans &lt;em&gt;La Communauté désoeuvrée&lt;/em&gt; (1986), il développe une pensée de la communauté qui refuse toute forme d'immanentisme ou de fusion : la communauté véritable n'est pas une substance commune, mais  &lt;a href=&quot;https://www.youtube.com/watch?v=fZK6pEAPxEw&quot;  title=&quot;jean luc Nancy par Institut Humanités &quot;&gt;l'exposition partagée &lt;/a&gt; de la singularité de chacun. Cette réflexion, en dialogue critique avec Blanchot et Bataille, a eu un retentissement considérable dans les débats contemporains sur la politique, la communauté et l'identité. &lt;/p&gt; &lt;p&gt; Dans &lt;em&gt;Corpus&lt;/em&gt; (1992) et &lt;em&gt;Noli me tangere&lt;/em&gt; (2003), il explore  &lt;a href=&quot;https://www.youtube.com/watch?v=1kCExw6Wp9k&quot;  title=&quot;jean luc Nancy par Lacan TV &quot;&gt;la philosophie du corps &lt;/a&gt; et du toucher comme modes fondamentaux de l'être-au-monde. Son essai sur le sens — &lt;em&gt;Le Sens du monde&lt;/em&gt; (1993) — aborde la question de la possibilité du sens dans un monde déserté par les transcendances. &lt;em&gt;L'Intrus&lt;/em&gt; (2000), bref récit autobiographique sur sa transplantation cardiaque, mêle réflexion philosophique et expérience personnelle de la maladie et de l'altérité. Son œuvre, immense et diverse, témoigne d'une pensée vivante et rigoureuse toujours en dialogue avec la littérature, l'art et la politique. &lt;/p&gt;  &lt;audio controls title=&quot;Jean luc Nancy par France Culture&quot;&gt; &lt;source src=&quot;https://media.radiofrance-podcast.net/podcast09/11472-06.02.2011-ITEMA_20267545-2011C16153E0003-ITE_00040439_RSCE-21.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt;" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H132" display="https://www.laphilo.fr/pho/jlnancy-mini.webp" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E133" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Philippe_Lacoue-Labarthe&quot;  title=&quot; Wikipedia&quot;&gt;Philippe LACOUE-LABARTHE&lt;/a&gt; était un philosophe, critique littéraire, traducteur et théoricien français né à Tours et connu pour ses travaux sur la mimésis, le romantisme allemand, Hölderlin, Heidegger, Derrida et la relation entre esthétique et politique. Il a aussi beaucoup compté dans le milieu intellectuel de Strasbourg, où il a enseigné longtemps et travaillé avec Jean-Luc Nancy. &lt;/p&gt; &lt;p&gt; Son  &lt;a href=&quot;https://maitron.fr/lacoue-labarthe-philippe/&quot;  title=&quot; lacoue-labarthe par le maitron&quot;&gt;œuvre interroge &lt;/a&gt; la façon dont l’art, la philosophie et la politique s’entrecroisent, notamment à travers la notion de mimésis et la critique de l’“esthétisation du politique”. Il a aussi travaillé sur le romantisme allemand et sur la réception de Hölderlin, qu’il considérait comme une figure majeure. &lt;/p&gt; &lt;p&gt; Parmi les livres souvent cités, on trouve Le Titre de la lettre avec Jean-Luc Nancy, L’Absolu littéraire, L’Imitation des modernes, La Fiction du politique et Heidegger, la politique du poème. Il a également traduit plusieurs auteurs allemands majeurs, dont Heidegger, Hölderlin, Nietzsche, Benjamin et Celan. &lt;/p&gt; &lt;p&gt; Sa pensée tourne autour de trois idées principales : - La représentation n’est jamais transparente : ce que nous montrons, racontons ou jouons n’est jamais la réalité elle-même, mais une forme, un masque, une imitation. - La littérature et le théâtre sont essentiels pour comprendre la philosophie, parce qu’ils révèlent ce que les concepts cachent ou simplifient.popups. - Le lien entre esthétique et politique est dangereux : il a beaucoup réfléchi à la manière dont l’art, les mythes et les images peuvent servir le politique, y compris dans des formes fascisantes. &lt;/p&gt; &#10; &lt;audio controls title=&quot;les versions de philippe lacoue labarthe par France Culture&quot;&gt; &lt;source src=&quot;https://media.radiofrance-podcast.net/podcast09/16409-16.03.2007-ITEMA_20062386-2007C6409S0011-MEM_000036772_RF-21.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt;  " r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H133" display="https://www.laphilo.fr/pho/pllabarthe-mini.webp" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H134" display="https://www.laphilo.fr/pho/fdelaporte-mini.webp" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H135" display="https://www.laphilo.fr/pho/lecourt-mini.webp" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E136" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Jean-Michel_Berthelot&quot;  title=&quot; Wikipedia&quot;&gt;Jean-Michel BERTHELOT&lt;/a&gt; était un philosophe et sociologue français spécialiste d'épistémologie des sciences sociales. Professeur à l'Université de Paris IV-Sorbonne et à l'Université du Québec à Montréal, il contribua de manière décisive à la réflexion philosophique sur les fondements et les méthodes des sciences humaines et sociales. Son œuvre joint la rigueur épistémologique à une large culture philosophique et sociologique. &lt;/p&gt; &lt;p&gt; Son ouvrage principal, &lt;em&gt; &lt;a href=&quot;https://www.persee.fr/doc/sotra_0038-0296_1992_num_34_3_2605_t1_0388_0000_3&quot;  title=&quot;l’intelligence du social par persée &quot;&gt; L'Intelligence du social&lt;/a&gt; &lt;/em&gt; (1990), est une analyse approfondie des schèmes d'intelligibilité que les sciences sociales utilisent pour rendre compte de la réalité sociale : le schème causal, le schème fonctionnel, le schème structural, le schème herméneutique et d'autres modes d'explication. Berthelot montre que chaque paradigme sociologique privilégie un mode d'intelligibilité particulier, ce qui permet de comprendre à la fois leurs apports spécifiques et leurs limites. Ce livre constitue l'une des contributions les plus claires et les plus systématiques à la philosophie des sciences sociales en langue française. &lt;/p&gt; &lt;p&gt; Dans &lt;em&gt;Epistémologie des sciences sociales&lt;/em&gt; (2001, ouvrage collectif qu'il dirigea), il offrit un panorama complet des questions épistémologiques fondamentales que posent les sciences humaines et sociales : la causalité, la compréhension, la mesure, la modélisation, la réflexivité et les rapports entre science et valeurs. Ses travaux contribuèrent à établir l'épistémologie des sciences sociales comme une discipline à part entière dans le paysage universitaire français, en dialogue constant avec la philosophie des sciences anglophones et continentale. &lt;/p&gt;" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H136" display="https://www.laphilo.fr/pho/jmberthelot-mini.webp" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E137" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Daniel_Bensa%C3%AFd&quot;  title=&quot; Wikipedia&quot;&gt;Daniel BENSAÏD&lt;/a&gt; était un philosophe français marxiste, l'un des intellectuels les plus importants de la gauche radicale française de son époque. Né à Paris dans une famille juive d'origine algérienne, il fut l'un des leaders de la révolte étudiante de mai 1968 à Paris-Nanterre aux côtés de Daniel Cohn-Bendit. Professeur de philosophie à l'Université Paris VIII-Saint-Denis, il fut membre dirigeant de la Ligue communiste révolutionnaire (LCR) et de son successeur le Nouveau Parti Anticapitaliste (NPA). &lt;/p&gt; &lt;p&gt; Sa pensée philosophique chercha à renouveler le marxisme en le débarrassant des &lt;a href=&quot;https://www.youtube.com/watch?v=uxBvxfRI2CE&quot;  title=&quot;la privatisation du monde par bibou11slalala &quot;&gt; simplifications téléologiques &lt;/a&gt; et en l'ouvrant à des problématiques nouvelles. Dans &lt;em&gt;Marx l'intempestif&lt;/em&gt; (1995), il défend un Marx débarrassé du déterminisme historique et de la philosophie du progrès, un Marx « intempestif » qui pense la politique comme art du possible et de l'impossible, en dialogue avec Blaise Pascal et Walter Benjamin. Ce livre renouvela profondément la  &lt;a href=&quot;https://www.youtube.com/watch?v=is8Ya038-Q4&quot;  title=&quot;l’héritage de Marx par socialtram &quot;&gt; lecture de Marx &lt;/a&gt; dans la gauche française. &lt;/p&gt; &lt;p&gt; Dans &lt;em&gt;Le Pari mélancolique&lt;/em&gt; (1997) et &lt;em&gt;Résistances&lt;/em&gt; (2001), il développe une philosophie de l'engagement politique nourrie par la mélancolie des défaites mais portée par une fidélité irréductible à l'émancipation. Sa réflexion sur les rapports entre philosophie et politique, entre utopie et stratégie, constitue l'une des contributions les plus originales à la pensée marxiste contemporaine. Polémiste redoutable et pédagogue exigeant, il laissa une empreinte profonde sur plusieurs générations de militants et d'intellectuels de gauche. &lt;/p&gt;  &lt;audio controls title=&quot;Daniel Bensaid  par France Culture&quot;&gt; &lt;source src=&quot;https://media.radiofrance-podcast.net/podcast09/10075-11.12.2006-ITEMA_20049670-2006C6608S0221-MEM_000033324_RF-21.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt; " r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H137" display="https://www.laphilo.fr/pho/bensaid-mini.webp" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G138" display="&quot;Ce virus est là pour nous préparer au nouveau régime climatique&quot; par France Culture" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H138" display="https://www.laphilo.fr/pho/latour-mini.webp" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H139" display="https://www.laphilo.fr/pho/rdamien-mini.webp" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E140" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Catherine_Colliot-Th%C3%A9l%C3%A8ne&quot; title=&quot; Wikipedia&quot;&gt;Catherine COLLIOT-THELENE&lt;/a&gt; était une philosophe française  majeure de la philosophie politique contemporaine, spécialiste de Max Weber et penseuse des droits, de la démocratie et de la propriété dans un cadre cosmopolitique. Membre de l’Institut universitaire de France, elle est reconnue comme une référence internationale des études wébériennes. &lt;/p&gt; &lt;p&gt; Son travail se situe au croisement de la philosophie politique et des sciences sociales, avec trois pôles principaux :  &lt;a href=&quot;https://www.youtube.com/watch?v=krUYFtq9Jww&quot; title=&quot;Max Weber et la violence légitime de l’état par France Culture&quot;&gt;Max Weber, la démocratie et les droits, &lt;/a&gt;  la propriété et le cosmopolitisme.  Elle traduit et commente plusieurs textes de Weber, notamment Le Savant et le politique et Les Communautés, en montrant en détail ses concepts de rationalisation, de désenchantement et de domination. &lt;/p&gt; &lt;p&gt; À partir des années 2000, elle se concentre sur les droits subjectifs, leur articulation avec l’individualisme contemporain et la transformation des rapports entre pouvoirs politiques et économiques. Elle insiste sur la nécessité de penser la normativité (ce qui doit être) à partir d’une analyse précise des structures sociales réelles, d’où son dialogue constant avec le droit, l’histoire et la sociologie. &lt;/p&gt; &lt;p&gt; Dans &quot;La Démocratie sans “demos”  paru en 2011, elle remet en question l’identification classique entre &quot;peuple&quot; et &quot;démocratie&quot;. Elle critique la superposition entre souveraineté du peuple et souveraineté territoriale de l’État, qui conduit selon elle à des versions exclusives de la démocratie. &lt;a href=&quot;https://www.youtube.com/watch?v=ps2ixtEpgYI&quot; title=&quot;la democratie c’est le droit de resistance par Journal l’Humanitét&quot;&gt;Sa philosophie cherche &lt;/a&gt;  une démocratie fondée sur des droits universalisables et sur la participation de tous les sujets, plutôt que sur l’appartenance à une communauté nationale préconstituée. &lt;/p&gt; &lt;p&gt; Elle refuse la séparation entre théorie pure et monde social : pour elle, la philosophie politique doit dialoguer avec les sciences sociales pour produire une critique efficace des institutions et des inégalités. Elle a accompagné, sans posture militante classique mais avec une forte implication intellectuelle, les luttes pour les droits des femmes, des exclus et des étrangers, en cherchant à fournir des outils conceptuels pour penser l’égalité aujourd’hui. &lt;/p&gt; &#10; &lt;audio controls title=&quot;Les défis juridiques de la migration : existe-t-il un droit à la libre circulation ? par France Culture&quot;&gt; &lt;source src=&quot;https://media.radiofrance-podcast.net/podcast09/21447-09.02.2022-ITEMA_22927630-2022C27677S0040-21.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt;" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H140" display="https://www.laphilo.fr/pho/thelene-mini.webp" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H141" display="https://www.laphilo.fr/pho/bstiegler-mini.webp" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E142" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Bernard_Mabille_(philosophe)&quot;  style=&quot;color:#6A142A&quot;  title=&quot; Wikipedia&quot;&gt;Bernard MABILLE&lt;/a&gt; était un philosophe français spécialiste de dialectique et de philosophie hégélienne, ainsi que de métaphysique contemporaine. Agrégé de philosophie et professeur à l'Université Paris IV-Sorbonne, il fut l'un des meilleurs connaisseurs français de Hegel et contribua de manière significative au renouvellement des études hégéliennes en France dans les dernières décennies du XXe siècle. &lt;/p&gt; &lt;p&gt; Sa thèse principale, &lt;em&gt;Hegel : l'épreuve de la contingence&lt;/em&gt; (1999), est une lecture originale de la philosophie hégélienne à la lumière de la problématique de la contingence. Contre les lectures qui réduisent Hegel à un penseur du nécessaire et du rationnel, Mabille montre que la contingence est au cœur même du système hégélien et que la dialectique est précisément la méthode qui permet de penser le passage du contingent au nécessaire sans l'éliminer. Cette relecture contribua à ouvrir la philosophie hégélienne à des problématiques contemporaines. &lt;/p&gt; &lt;p&gt; Dans ses travaux sur la métaphysique et la dialectique, Mabille s'intéressa également aux rapports entre la philosophie hégélienne et la phénoménologie française, notamment Merleau-Ponty et Henry. Son enseignement à la Sorbonne forma plusieurs générations d'étudiants à la rigueur de la pensée dialectique. Sa disparition prématurée priva la philosophie française d'un penseur rigoureux dont l'œuvre, bien que de volume limité, témoigne d'une lecture profonde et originale de l'idéalisme allemand et de ses prolongements contemporains. &lt;/p&gt;" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H142" display="https://www.laphilo.fr/pho/bnabille-mini.webp" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H143" display="https://www.laphilo.fr/pho/adufourmantelle-mini.webp" r:id="rId105"/>
   </hyperlinks>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>

--- a/data/frise-philosophes-france.xlsx
+++ b/data/frise-philosophes-france.xlsx
@@ -3799,56 +3799,58 @@
         </is>
       </c>
     </row>
-    <row r="50" ht="266.25" customHeight="1" s="49">
-      <c r="A50" s="57" t="n">
-        <v>1882</v>
-      </c>
-      <c r="B50" s="57" t="n">
-        <v>1962</v>
-      </c>
-      <c r="C50" s="60" t="inlineStr">
-        <is>
-          <t>1882 – 1962</t>
-        </is>
-      </c>
-      <c r="D50" s="60" t="inlineStr">
-        <is>
-          <t>Jacques CHEVALIER</t>
-        </is>
-      </c>
-      <c r="E50" s="77" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Jacques_Chevalier_(philosophe)"  title=" Wikipedia"&gt;Jacques CHEVALIER&lt;/a&gt; (1882-1962) est un philosophe catholique français, historien de la philosophie et disciple d’Henri Bergson. Né à Cérilly, dans l’Allier, normalien et agrégé de philosophie, il enseigne à l’université de Grenoble. Il est l’auteur d’études sur Descartes, Pascal et Bergson, et d’une vaste &lt;em&gt;Histoire de la pensée&lt;/em&gt;. Son &lt;em&gt;Pascal&lt;/em&gt; (1922) et son &lt;em&gt;Bergson&lt;/em&gt; (1926) sont longtemps restés des ouvrages de référence, et il compte Emmanuel Mounier parmi ses étudiants.&lt;/p&gt; &lt;p&gt;Sur &lt;a href="https://www.persee.fr/doc/ahess_0395-2649_1957_num_12_4_2697_t1_0674_0000_1"  title=" histoire de la pensée   par persée"&gt;le plan philosophique&lt;/a&gt;, il s’inscrit dans un courant spiritualiste et catholique : il défend une conception de la personne et de la vie intérieure opposée au matérialisme scientifique, et voit dans la philosophie de Bergson un chemin vers la foi. Ses &lt;em&gt;Entretiens avec Bergson&lt;/em&gt; (1959), notes de conversations tenues pendant de longues années, sont un document précieux sur la pensée de son maître.&lt;/p&gt; &lt;p&gt;Proche du maréchal Pétain, ami de son père, il rejoint le régime de Vichy. Secrétaire d’État à l’Instruction publique à la fin de 1940, il fait inscrire l’&lt;a href="https://monbourbonnais.com/chevalier-jacques-ecrivain-philosophe/"  title=" chevalier jacques par mon bourbonnais"&gt;enseignement des devoirs&lt;/a&gt; envers Dieu dans les programmes de l’école primaire, mesure contestée et abandonnée dès 1941 par son successeur Jérôme Carcopino. Secrétaire d’État à la Famille et à la Santé en 1941, il soutient ensuite la Milice et dénonce des résistants, dont plusieurs sont exécutés. Après la Libération, il est condamné à vingt ans de prison et à l’indignité nationale, puis gracié en 1947 pour raisons de santé.&lt;/p&gt;</t>
-        </is>
-      </c>
-      <c r="F50" s="60" t="inlineStr">
-        <is>
-          <t>l4Mlgo9flWk</t>
-        </is>
-      </c>
-      <c r="G50" s="66" t="inlineStr">
-        <is>
-          <t>enracinement de jacques chevalier en bourbannais</t>
-        </is>
-      </c>
-      <c r="H50" s="61" t="inlineStr">
-        <is>
-          <t>https://www.laphilo.fr/pho/jchevalier-mini.webp</t>
+    <row r="50" ht="176.25" customHeight="1" s="49">
+      <c r="A50" s="47">
+        <v>1881</v>
+      </c>
+      <c r="B50" s="47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1955</t>
+        </is>
+      </c>
+      <c r="C50" s="47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1881 – 1955</t>
+        </is>
+      </c>
+      <c r="D50" s="47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pierre TEILHARD DE CHARDIN</t>
+        </is>
+      </c>
+      <c r="E50" s="85" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Pierre_Teilhard_de_Chardin" title=" Wikipedia"&gt;Pierre TEILHARD DE CHARDIN&lt;/a&gt; est un prêtre jésuite, paléontologue et philosophe français, qui a voulu réconcilier la foi chrétienne et la théorie de l’évolution. Né en Auvergne, il entre chez les jésuites et devient un spécialiste reconnu de la &lt;a href="https://fr.wikipedia.org/wiki/Pal%C3%A9ontologie" title=" Wikipedia"&gt;paléontologie&lt;/a&gt;. Brancardier pendant la Première Guerre mondiale, il passe ensuite plus de vingt ans en Chine, où il participe aux recherches sur l’&lt;a href="https://fr.wikipedia.org/wiki/Homme_de_P%C3%A9kin" title=" Wikipedia"&gt;Homme de Pékin&lt;/a&gt;, l’un des plus anciens fossiles humains connus, et prend part en 1931-1932 à la &lt;a href="https://fr.wikipedia.org/wiki/Croisi%C3%A8re_jaune" title=" Wikipedia"&gt;Croisière jaune&lt;/a&gt;, grande expédition à travers l’Asie centrale.&lt;/p&gt; &lt;p&gt;Dans&lt;a href="https://www.youtube.com/watch?v=3lnH0IsSosY" title="L'Univers s'éveille à travers nous : Le Phénomène Humain de Pierre Teilhard de Chardin - Résumé par Résumons Ça "&gt; &lt;em&gt;Le Phénomène humain&lt;/em&gt;&lt;/a&gt;, écrit dans les années 1930 et publié après sa mort,&lt;a href="https://www.lavie.fr/idees/histoire/teilhard-de-chardin-pourquoi-il-fascine-encore-98833.php" title="Teilhard de Chardin : pourquoi il fascine encore par lavie"&gt; il décrit l’univers&lt;/a&gt; comme un grand mouvement d’évolution, de la matière à la vie, puis de la vie à la pensée. À mesure que la matière se complexifie, la conscience grandit : c’est la « loi de complexité-conscience ». Avec l’homme apparaît une nouvelle couche de la Terre, la &lt;a href="https://fr.wikipedia.org/wiki/Noosph%C3%A8re" title=" Wikipedia"&gt;noosphère&lt;/a&gt;, la sphère de la pensée, qui relie peu à peu tous les esprits.&lt;/p&gt; &lt;p&gt;Cette évolution est selon lui orientée vers un point de convergence final, le &lt;a href="https://fr.wikipedia.org/wiki/Point_Om%C3%A9ga" title=" Wikipedia"&gt;point Oméga&lt;/a&gt;, qu’il identifie au Christ cosmique, où l’humanité s’unira sans perdre la personnalité de chacun. Son autre grand texte, &lt;em&gt;Le Milieu divin&lt;/em&gt;, médite sur la présence de Dieu dans toutes les activités humaines. Ses idées inquiètent Rome, qui lui interdit de publier ses écrits philosophiques et l’éloigne de France. Il meurt à New York en 1955. Publiée après sa mort, son œuvre connaît un succès mondial, et l’on voit parfois dans la noosphère une anticipation d’Internet.&lt;/p&gt;  &lt;audio controls title="Les religions - Pierre Teilhard de Chardin par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/14864-28.03.2005-ITEMA_24411051-2005F4864E0041-NET_MFI_B0010B53-6856-4882-ACA1-A6B9A05AEAF6-27-88fce0fc98f25b5a9ea3195cc6fcc643.m4a" type="audio/mp4" align="center"&gt; &lt;/audio&gt;</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ga3Se2oq9X4</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"LE MILIEU DIVIN - Pierre Teilhard De Chardin : Vos larmes et votre fatigue ont un sens divin." par Résumons Ça</t>
+        </is>
+      </c>
+      <c r="H50" s="48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/teilhard-mini.webp</t>
         </is>
       </c>
       <c r="J50" s="48" t="inlineStr">
         <is>
-          <t>metaphysique</t>
+          <t xml:space="preserve">metaphysique ; spiritualite</t>
         </is>
       </c>
       <c r="K50" s="48" t="inlineStr">
         <is>
-          <t>Spiritualisme</t>
+          <t xml:space="preserve">Spiritualisme ; Panenthéisme</t>
         </is>
       </c>
       <c r="L50" s="48" t="inlineStr">
         <is>
-          <t>philosophe français qui s’inscrit dans un courant spiritualiste et catholique influencé par Bergson.</t>
+          <t xml:space="preserve">jésuite et paléontologue français, penseur d’une évolution cosmique orientée vers la conscience et l’esprit.</t>
         </is>
       </c>
       <c r="N50" t="inlineStr">
@@ -3856,2068 +3858,2066 @@
           <t xml:space="preserve">occident</t>
         </is>
       </c>
-    </row>
-    <row r="51" ht="198" customHeight="1" s="49">
+      <c r="O50">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="51" ht="266.25" customHeight="1" s="49">
       <c r="A51" s="57" t="n">
         <v>1882</v>
       </c>
-      <c r="B51" s="57" t="inlineStr">
+      <c r="B51" s="57" t="n">
+        <v>1962</v>
+      </c>
+      <c r="C51" s="60" t="inlineStr">
+        <is>
+          <t>1882 – 1962</t>
+        </is>
+      </c>
+      <c r="D51" s="60" t="inlineStr">
+        <is>
+          <t>Jacques CHEVALIER</t>
+        </is>
+      </c>
+      <c r="E51" s="77" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Jacques_Chevalier_(philosophe)"  title=" Wikipedia"&gt;Jacques CHEVALIER&lt;/a&gt; (1882-1962) est un philosophe catholique français, historien de la philosophie et disciple d’Henri Bergson. Né à Cérilly, dans l’Allier, normalien et agrégé de philosophie, il enseigne à l’université de Grenoble. Il est l’auteur d’études sur Descartes, Pascal et Bergson, et d’une vaste &lt;em&gt;Histoire de la pensée&lt;/em&gt;. Son &lt;em&gt;Pascal&lt;/em&gt; (1922) et son &lt;em&gt;Bergson&lt;/em&gt; (1926) sont longtemps restés des ouvrages de référence, et il compte Emmanuel Mounier parmi ses étudiants.&lt;/p&gt; &lt;p&gt;Sur &lt;a href="https://www.persee.fr/doc/ahess_0395-2649_1957_num_12_4_2697_t1_0674_0000_1"  title=" histoire de la pensée   par persée"&gt;le plan philosophique&lt;/a&gt;, il s’inscrit dans un courant spiritualiste et catholique : il défend une conception de la personne et de la vie intérieure opposée au matérialisme scientifique, et voit dans la philosophie de Bergson un chemin vers la foi. Ses &lt;em&gt;Entretiens avec Bergson&lt;/em&gt; (1959), notes de conversations tenues pendant de longues années, sont un document précieux sur la pensée de son maître.&lt;/p&gt; &lt;p&gt;Proche du maréchal Pétain, ami de son père, il rejoint le régime de Vichy. Secrétaire d’État à l’Instruction publique à la fin de 1940, il fait inscrire l’&lt;a href="https://monbourbonnais.com/chevalier-jacques-ecrivain-philosophe/"  title=" chevalier jacques par mon bourbonnais"&gt;enseignement des devoirs&lt;/a&gt; envers Dieu dans les programmes de l’école primaire, mesure contestée et abandonnée dès 1941 par son successeur Jérôme Carcopino. Secrétaire d’État à la Famille et à la Santé en 1941, il soutient ensuite la Milice et dénonce des résistants, dont plusieurs sont exécutés. Après la Libération, il est condamné à vingt ans de prison et à l’indignité nationale, puis gracié en 1947 pour raisons de santé.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="F51" s="60" t="inlineStr">
+        <is>
+          <t>l4Mlgo9flWk</t>
+        </is>
+      </c>
+      <c r="G51" s="66" t="inlineStr">
+        <is>
+          <t>enracinement de jacques chevalier en bourbannais</t>
+        </is>
+      </c>
+      <c r="H51" s="61" t="inlineStr">
+        <is>
+          <t>https://www.laphilo.fr/pho/jchevalier-mini.webp</t>
+        </is>
+      </c>
+      <c r="J51" s="48" t="inlineStr">
+        <is>
+          <t>metaphysique</t>
+        </is>
+      </c>
+      <c r="K51" s="48" t="inlineStr">
+        <is>
+          <t>Spiritualisme</t>
+        </is>
+      </c>
+      <c r="L51" s="48" t="inlineStr">
+        <is>
+          <t>philosophe français qui s’inscrit dans un courant spiritualiste et catholique influencé par Bergson.</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="198" customHeight="1" s="49">
+      <c r="A52" s="57" t="n">
+        <v>1882</v>
+      </c>
+      <c r="B52" s="57" t="inlineStr">
         <is>
           <t>1973</t>
         </is>
       </c>
-      <c r="C51" s="57" t="inlineStr">
+      <c r="C52" s="57" t="inlineStr">
         <is>
           <t>1882 – 1973</t>
         </is>
       </c>
-      <c r="D51" s="58" t="inlineStr">
+      <c r="D52" s="58" t="inlineStr">
         <is>
           <t>Jacques MARITAIN</t>
         </is>
       </c>
-      <c r="E51" s="59" t="inlineStr">
+      <c r="E52" s="59" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Jacques_Maritain"  title=" Wikipedia"&gt;Jacques MARITAIN&lt;/a&gt; était un philosophe français catholique, l'une des figures les plus importantes du renouveau thomiste au XXe siècle. Né à Paris dans une famille protestante, converti au catholicisme en 1906 sous l'influence de Léon Bloy, il devint le principal représentant du &lt;a href="https://fr.wikipedia.org/wiki/N%C3%A9othomisme"  title=" Néothomisme par wikipedia"&gt;« néo-thomisme » &lt;/a&gt;  ou philosophie chrétienne inspirée de saint Thomas d'Aquin. Professeur dans plusieurs universités françaises, puis à Princeton et à Toronto après son exil aux États-Unis pendant la Seconde Guerre mondiale, il joua un rôle important dans la rédaction de la Déclaration universelle des droits de l'homme (1948) sous l'égide de l'UNESCO. &lt;/p&gt; &lt;p&gt; Sa &lt;a href="https://www.youtube.com/watch?v=Z08aZPDIIA4"  title=" La philosophie de Maritain par Radio Coutousie"&gt;pensée philosophique &lt;/a&gt; se développe à partir d'une relecture créatrice de Thomas d'Aquin, qu'il cherche à mettre en dialogue avec la modernité. Dans &lt;em&gt;Distinguer pour unir ou les Degrés du savoir&lt;/em&gt; (1932), son œuvre théorétique majeure, il développe une épistémologie hiérarchique distinguant les différents niveaux de la connaissance, de la science empirique à la philosophie et à la théologie mystique. Il défend la possibilité d'une métaphysique réaliste face à l'idéalisme kantien et au positivisme. &lt;/p&gt; &lt;p&gt; En philosophie politique, Maritain élabora une doctrine de l'humanisme intégral et de la démocratie chrétienne qui influença profondément les partis démocrates-chrétiens européens et latino-américains. Ses œuvres &lt;em&gt;Humanisme intégral&lt;/em&gt; (1936) et &lt;em&gt;La Personne et le bien commun&lt;/em&gt; (1947) défendent une vision personnaliste de la société où la dignité de la personne humaine est le fondement de tout ordre politique juste. Il influença notamment les fondateurs de la démocratie chrétienne en France, en Italie et en Amérique latine. &lt;/p&gt;   &lt;audio controls title=Jacques MARITAIN par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/13915-28.04.2023-ITEMA_23362289-2016C3372E1388-21.mp3" type="audio/mpeg" align="center"&gt;&lt;/audio&gt;</t>
         </is>
       </c>
-      <c r="F51" s="57" t="inlineStr">
+      <c r="F52" s="57" t="inlineStr">
         <is>
           <t>5n4lKn5lnGs</t>
         </is>
       </c>
-      <c r="G51" s="59" t="inlineStr">
+      <c r="G52" s="59" t="inlineStr">
         <is>
           <t>"Jacques Maritain, par VIS PHILO</t>
         </is>
       </c>
-      <c r="H51" s="59" t="inlineStr">
+      <c r="H52" s="59" t="inlineStr">
         <is>
           <t>https://www.laphilo.fr/pho/jmaritain-mini.webp</t>
         </is>
       </c>
-      <c r="J51" s="48" t="inlineStr">
+      <c r="J52" s="48" t="inlineStr">
         <is>
           <t xml:space="preserve">metaphysique </t>
         </is>
       </c>
-      <c r="K51" s="48" t="inlineStr">
+      <c r="K52" s="48" t="inlineStr">
         <is>
           <t>Néothomisme</t>
         </is>
       </c>
-      <c r="L51" s="76" t="inlineStr">
+      <c r="L52" s="76" t="inlineStr">
         <is>
           <t xml:space="preserve">philosophe thomiste chrétien qui renouvela la pensée de saint Thomas d’Aquin. </t>
         </is>
       </c>
-      <c r="N51" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-    </row>
-    <row r="52" ht="158.25" customHeight="1" s="49">
-      <c r="A52" s="54" t="n">
+      <c r="N52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="158.25" customHeight="1" s="49">
+      <c r="A53" s="54" t="n">
         <v>1882</v>
       </c>
-      <c r="B52" s="54" t="inlineStr">
+      <c r="B53" s="54" t="inlineStr">
         <is>
           <t>1954</t>
         </is>
       </c>
-      <c r="C52" s="54" t="inlineStr">
+      <c r="C53" s="54" t="inlineStr">
         <is>
           <t>1882 – 1954</t>
         </is>
       </c>
-      <c r="D52" s="55" t="inlineStr">
+      <c r="D53" s="55" t="inlineStr">
         <is>
           <t>René le SENNE</t>
         </is>
       </c>
-      <c r="E52" s="62" t="inlineStr">
+      <c r="E53" s="62" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Ren%C3%A9_Le_Senne" title=" Wikipedia"&gt;René le SENNE&lt;/a&gt; était un philosophe français, cofondateur avec Louis Lavelle du mouvement dit de « La Philosophie de l'Esprit » ou « philosophie de la valeur », l'une des réponses spécifiquement françaises aux courants existentialistes et phénoménologiques qui se développaient en Europe dans la première moitié du XXe siècle. &lt;/p&gt; &lt;p&gt; Sa pensée s'organise autour du concept de valeur et d'obstacle. Dans son œuvre principale, &lt;em&gt;Obstacle et Valeur&lt;/em&gt; (1934), il développe &lt;a href="https://www.persee.fr/doc/phlou_0035-3841_1955_num_53_37_4532"  title=" René de Senne par persée"&gt;une philosophie de l'épreuve &lt;/a&gt; : c'est dans la rencontre avec l'obstacle, dans la résistance que le réel oppose à nos désirs et à nos projets, que l'esprit se découvre lui-même et prend conscience de sa vocation à réaliser des valeurs. La valeur n'est pas donnée mais conquise à travers la lutte, et c'est dans cette tension permanente entre l'Etre et la conscience que réside la vie spirituelle. &lt;/p&gt; &lt;p&gt; Il est aussi l'auteur d'un &lt;em&gt;Traité de caractérologie&lt;/em&gt; (1945), ouvrage qui connut un large succès et qui cherche à établir une science rigoureuse des types de caractère humain. Distinguant plusieurs dimensions du caractère (émotivité, activité, résonance), il proposa une taxinomie des tempéraments qui eut une influence durable dans la psychologie et la pédagogie françaises. Cette double orientation, métaphysique et psychologique, fait de Le Senne un penseur original qui tenta de réconcilier la rigueur de l'analyse avec la profondeur de la réflexion sur l'existence humaine. &lt;/p&gt;</t>
         </is>
       </c>
-      <c r="F52" s="54" t="inlineStr">
+      <c r="F53" s="54" t="inlineStr">
         <is>
           <t>E4ogrcU9_1I</t>
         </is>
       </c>
-      <c r="G52" s="64" t="inlineStr">
+      <c r="G53" s="64" t="inlineStr">
         <is>
           <t xml:space="preserve">
 La caractérologie - Le Senne (8 types) par lucoluc59</t>
         </is>
       </c>
-      <c r="H52" s="56" t="inlineStr">
+      <c r="H53" s="56" t="inlineStr">
         <is>
           <t>https://www.laphilo.fr/pho/rsenne-mini.webp</t>
         </is>
       </c>
-      <c r="J52" s="48" t="inlineStr">
+      <c r="J53" s="48" t="inlineStr">
         <is>
           <t>metaphysique ; ethique</t>
         </is>
       </c>
-      <c r="K52" s="48" t="inlineStr">
+      <c r="K53" s="48" t="inlineStr">
         <is>
           <t>Spiritualisme</t>
         </is>
       </c>
-      <c r="L52" s="76" t="inlineStr">
+      <c r="L53" s="76" t="inlineStr">
         <is>
           <t xml:space="preserve">philosophe français spiritualiste, connu pour sa philosophie des valeurs et ses travaux de morale. </t>
         </is>
       </c>
-      <c r="N52" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-    </row>
-    <row r="53" ht="185.8" customHeight="1" s="49">
-      <c r="A53" s="57" t="n">
+      <c r="N53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="185.8" customHeight="1" s="49">
+      <c r="A54" s="57" t="n">
         <v>1883</v>
       </c>
-      <c r="B53" s="57" t="inlineStr">
+      <c r="B54" s="57" t="inlineStr">
         <is>
           <t>1960</t>
         </is>
       </c>
-      <c r="C53" s="57" t="inlineStr">
+      <c r="C54" s="57" t="inlineStr">
         <is>
           <t>1883 – 1960</t>
         </is>
       </c>
-      <c r="D53" s="58" t="inlineStr">
+      <c r="D54" s="58" t="inlineStr">
         <is>
           <t>Raïssa MARITAIN</t>
         </is>
       </c>
-      <c r="E53" s="65" t="inlineStr">
+      <c r="E54" s="65" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Ra%C3%AFssa_Maritain"  title=" Wikipedia"&gt;Raïssa MARITAIN&lt;/a&gt; était une philosophe, poétesse et mystique franco-russe. Née dans une famille juive, elle émigra en France avec sa famille dans l'enfance, étudia à la Sorbonne où elle rencontra Jacques Maritain, et se convertit avec lui au catholicisme en 1906 sous l'influence de Léon Bloy. Ensemble, ils formèrent l'un des &lt;a href="https://www.lavie.fr/idees/histoire/jacques-et-raissa-maritain-est-deux-88033.php" title="jacques e traîssa par lavie,fr"&gt;couples intellectuels &lt;/a&gt; les plus féconds de cette époque. &lt;/p&gt; &lt;p&gt; Elle apporta une contribution originale et irremplaçable à l'œuvre commune du couple. Poétesse d'une grande sensibilité, elle exprima dans des recueils comme &lt;em&gt;La Vie donnée&lt;/em&gt; (1935) une expérience mystique intense nourrie par la tradition juive et la spiritualité chrétienne. Ses &lt;em&gt;&lt;a href="https://www.youtube.com/watch?v=aKqCOZIq198" title="la vérité par l’amitié par le verbe medias"&gt;Grandes Amitiés &lt;/a&gt; &lt;/em&gt; (1941-1944), mémoires en deux volumes, constituent un témoignage exceptionnel sur la vie intellectuelle et spirituelle de l'entre-deux-guerres, évoquant ses rencontres avec Léon Bloy, Henri Bergson, Ernest Psichari, Jean Cocteau et de nombreux &lt;a href="http://palimpsestes.fr/metaphysique/textes/rmaritain_angoisse.html" title="raissa maritain les grandes amitiés par palimpsestes.fr"&gt;autres artistes et penseurs. &lt;/a&gt; &lt;/p&gt; &lt;p&gt; Elle contribua également aux travaux philosophiques de son mari, notamment aux réflexions sur la poésie et la connaissance poétique exposées dans &lt;em&gt;Situation de la poésie&lt;/em&gt; (1938), ouvrage qu'ils rédigèrent ensemble. Sa pensée sur le rapport entre expérience mystique, création artistique et connaissance philosophique constitue un apport original à la philosophie catholique française. Figure de la conversion et de l'engagement intellectuel au service de la foi, elle incarne une manière particulièrement intensément vécue de la vie de l'esprit. &lt;/p&gt;</t>
         </is>
       </c>
-      <c r="F53" s="57" t="inlineStr">
+      <c r="F54" s="57" t="inlineStr">
         <is>
           <t>nDmAJHqFKS0</t>
         </is>
       </c>
-      <c r="G53" s="59" t="inlineStr">
+      <c r="G54" s="59" t="inlineStr">
         <is>
           <t>Raïssa Maritain - Nous avons été amis (extrait) | Livres audio de Catholic Culture</t>
         </is>
       </c>
-      <c r="H53" s="59" t="inlineStr">
+      <c r="H54" s="59" t="inlineStr">
         <is>
           <t>https://www.laphilo.fr/pho/rmaritain-mini.webp</t>
         </is>
       </c>
-      <c r="J53" s="48" t="inlineStr">
+      <c r="J54" s="48" t="inlineStr">
         <is>
           <t>metaphysique ; spiritualite</t>
         </is>
       </c>
-      <c r="K53" s="48" t="inlineStr">
+      <c r="K54" s="48" t="inlineStr">
         <is>
           <t>Néothomisme ; Spiritualisme</t>
         </is>
       </c>
-      <c r="L53" s="48" t="inlineStr">
+      <c r="L54" s="48" t="inlineStr">
         <is>
           <t>philosophe, poétesse et mystique franco-russe de tradition juive.</t>
         </is>
       </c>
-      <c r="M53" t="inlineStr">
+      <c r="M54" t="inlineStr">
         <is>
           <t xml:space="preserve">juive;femme</t>
         </is>
       </c>
-      <c r="N53" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-    </row>
-    <row r="54" ht="238.05" customHeight="1" s="49">
-      <c r="A54" s="54" t="n">
-        <v>1883</v>
-      </c>
-      <c r="B54" s="54" t="inlineStr">
-        <is>
-          <t>1951</t>
-        </is>
-      </c>
-      <c r="C54" s="54" t="inlineStr">
-        <is>
-          <t>1883 – 1951</t>
-        </is>
-      </c>
-      <c r="D54" s="55" t="inlineStr">
-        <is>
-          <t>Louis LAVELLE</t>
-        </is>
-      </c>
-      <c r="E54" s="56" t="inlineStr">
-        <is>
-          <t>&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Louis_Lavelle"  title=" Wikipedia"&gt;Louis LAVELLE&lt;/a&gt; était un philosophe français, cofondateur avec René Le Senne du mouvement philosophique dit « La Philosophie de l'Esprit ». Il fut professeur au Collège de France (chaire de philosophie morale et métaphysique) et membre de l'Académie des sciences morales et politiques. Son œuvre monumentale constitue l'une des synthèses métaphysiques les plus ambitieuses de la philosophie française du XXe siècle. &lt;/p&gt; &lt;p&gt; &lt;a href="https://classiques.uqam.ca/classiques/lavelle_louis/carnets_de_guerre_1915_18/carnets_intro.html" title="carnet de guerre Lavelle par classiques-uqam"&gt;Sa pensée s'articule &lt;/a&gt;  autour du concept d'Être, qu'il conçoit comme une présence totale et infinie dont toute conscience particulière participe. Sa philosophie, exposée dans la grande trilogie &lt;em&gt;La Dialectique du monde sensible&lt;/em&gt; (1921), &lt;em&gt;La Présence totale&lt;/em&gt; (1934) et &lt;em&gt;De l'Être&lt;/em&gt; (1928), est une ontologie de la participation : l'être humain ne possède pas l'être, mais y participe librement et activement, et c'est dans cet acte de participation que réside la vie spirituelle. Cette métaphysique est indissociable d'une éthique et &lt;a href="https://www.youtube.com/watch?v=Ud1UWWhN-tw" title="de la philosophie lavellienne par spiritual quest"&gt;d'une spiritualité vécue. &lt;/a&gt; &lt;/p&gt; &lt;p&gt; Il développa également une philosophie de l'intériorité et du temps dans des ouvrages comme &lt;em&gt;Du Temps et de l'éternité&lt;/em&gt; (1945) et une réflexion sur les valeurs dans son &lt;em&gt;Traité des valeurs&lt;/em&gt; (2 volumes, 1951-1955). Sa pensée, nourrie de Plotin, de Descartes et de Maine de Biran, offre une alternative spiritualiste à la fois à l'existentialisme sartriens et au positivisme logique. Par la profondeur de son inspiration et l'ampleur de son œuvre, il représente l'une des grandes figures du spiritualisme chrétien dans la philosophie française du XXe siècle. &lt;/p&gt;</t>
-        </is>
-      </c>
-      <c r="F54" s="54" t="inlineStr">
-        <is>
-          <t>zUNlTsK6nXM</t>
-        </is>
-      </c>
-      <c r="G54" s="56" t="inlineStr">
-        <is>
-          <t>"La voix de Louis Lavelle" par sebastien robert</t>
-        </is>
-      </c>
-      <c r="H54" s="56" t="inlineStr">
-        <is>
-          <t>https://www.laphilo.fr/pho/llavelle-mini.webp</t>
-        </is>
-      </c>
-      <c r="J54" s="48" t="inlineStr">
-        <is>
-          <t>metaphysique ; spiritualite</t>
-        </is>
-      </c>
-      <c r="K54" s="48" t="inlineStr">
-        <is>
-          <t>Spiritualisme</t>
-        </is>
-      </c>
-      <c r="L54" s="48" t="inlineStr">
-        <is>
-          <t>philosophe français cofondateur du mouvement philosophique dit "La Philosophie de l'Esprit".</t>
-        </is>
-      </c>
       <c r="N54" t="inlineStr">
         <is>
           <t xml:space="preserve">occident</t>
         </is>
       </c>
     </row>
-    <row r="55" ht="421.6" customHeight="1" s="49">
+    <row r="55" ht="238.05" customHeight="1" s="49">
       <c r="A55" s="54" t="n">
         <v>1883</v>
       </c>
-      <c r="B55" s="54" t="n">
+      <c r="B55" s="54" t="inlineStr">
+        <is>
+          <t>1951</t>
+        </is>
+      </c>
+      <c r="C55" s="54" t="inlineStr">
+        <is>
+          <t>1883 – 1951</t>
+        </is>
+      </c>
+      <c r="D55" s="55" t="inlineStr">
+        <is>
+          <t>Louis LAVELLE</t>
+        </is>
+      </c>
+      <c r="E55" s="56" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Louis_Lavelle"  title=" Wikipedia"&gt;Louis LAVELLE&lt;/a&gt; était un philosophe français, cofondateur avec René Le Senne du mouvement philosophique dit « La Philosophie de l'Esprit ». Il fut professeur au Collège de France (chaire de philosophie morale et métaphysique) et membre de l'Académie des sciences morales et politiques. Son œuvre monumentale constitue l'une des synthèses métaphysiques les plus ambitieuses de la philosophie française du XXe siècle. &lt;/p&gt; &lt;p&gt; &lt;a href="https://classiques.uqam.ca/classiques/lavelle_louis/carnets_de_guerre_1915_18/carnets_intro.html" title="carnet de guerre Lavelle par classiques-uqam"&gt;Sa pensée s'articule &lt;/a&gt;  autour du concept d'Être, qu'il conçoit comme une présence totale et infinie dont toute conscience particulière participe. Sa philosophie, exposée dans la grande trilogie &lt;em&gt;La Dialectique du monde sensible&lt;/em&gt; (1921), &lt;em&gt;La Présence totale&lt;/em&gt; (1934) et &lt;em&gt;De l'Être&lt;/em&gt; (1928), est une ontologie de la participation : l'être humain ne possède pas l'être, mais y participe librement et activement, et c'est dans cet acte de participation que réside la vie spirituelle. Cette métaphysique est indissociable d'une éthique et &lt;a href="https://www.youtube.com/watch?v=Ud1UWWhN-tw" title="de la philosophie lavellienne par spiritual quest"&gt;d'une spiritualité vécue. &lt;/a&gt; &lt;/p&gt; &lt;p&gt; Il développa également une philosophie de l'intériorité et du temps dans des ouvrages comme &lt;em&gt;Du Temps et de l'éternité&lt;/em&gt; (1945) et une réflexion sur les valeurs dans son &lt;em&gt;Traité des valeurs&lt;/em&gt; (2 volumes, 1951-1955). Sa pensée, nourrie de Plotin, de Descartes et de Maine de Biran, offre une alternative spiritualiste à la fois à l'existentialisme sartriens et au positivisme logique. Par la profondeur de son inspiration et l'ampleur de son œuvre, il représente l'une des grandes figures du spiritualisme chrétien dans la philosophie française du XXe siècle. &lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="F55" s="54" t="inlineStr">
+        <is>
+          <t>zUNlTsK6nXM</t>
+        </is>
+      </c>
+      <c r="G55" s="56" t="inlineStr">
+        <is>
+          <t>"La voix de Louis Lavelle" par sebastien robert</t>
+        </is>
+      </c>
+      <c r="H55" s="56" t="inlineStr">
+        <is>
+          <t>https://www.laphilo.fr/pho/llavelle-mini.webp</t>
+        </is>
+      </c>
+      <c r="J55" s="48" t="inlineStr">
+        <is>
+          <t>metaphysique ; spiritualite</t>
+        </is>
+      </c>
+      <c r="K55" s="48" t="inlineStr">
+        <is>
+          <t>Spiritualisme</t>
+        </is>
+      </c>
+      <c r="L55" s="48" t="inlineStr">
+        <is>
+          <t>philosophe français cofondateur du mouvement philosophique dit "La Philosophie de l'Esprit".</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="421.6" customHeight="1" s="49">
+      <c r="A56" s="54" t="n">
+        <v>1883</v>
+      </c>
+      <c r="B56" s="54" t="n">
         <v>1962</v>
       </c>
-      <c r="C55" s="54" t="inlineStr">
+      <c r="C56" s="54" t="inlineStr">
         <is>
           <t>1883 – 1962</t>
         </is>
       </c>
-      <c r="D55" s="55" t="inlineStr">
+      <c r="D56" s="55" t="inlineStr">
         <is>
           <t>Louis MASSIGNON</t>
         </is>
       </c>
-      <c r="E55" s="78" t="inlineStr">
+      <c r="E56" s="78" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Louis_Massignon"  title=" Wikipedia"&gt;Louis MASSIGNON&lt;/a&gt; était un philosophe,  islamologue, orientaliste et intellectuel catholique français, considéré comme l’un des fondateurs de l’islamologie moderne et un pionnier du dialogue islamo-chrétien. Son œuvre mêle érudition philologique et historique sur l’islam, intérêt profond pour le soufisme, et engagement spirituel et politique en faveur d’une réconciliation des religions abrahamiques. &lt;/p&gt; &lt;p&gt; Il  est &lt;a href="https://louismassignon.fr/"&gt;surtout célèbre &lt;/a&gt;  pour son étude monumentale du mystique soufi al-Ḥallāj (mort en 922), qu’il considère comme un paradigme de la sainteté en islam et comme une figure de martyr spirituel. Il montre l’origine coranique du soufisme, analyse en détail le vocabulaire mystique musulman, et contribue à faire entrer l’étude de la mystique islamique dans le champ académique occidental. Son interprétation est marquée par sa propre spiritualité : il valorise une mystique d’ascèse et de souffrance, et se méfie des développements plus spéculatifs (comme chez Ibn ʿArabī). &lt;/p&gt; &lt;p&gt; Il développe une vision œcuménique centrée sur la figure d’Abraham, père commun du judaïsme, du christianisme et de l’islam, et travaille à faire reconnaître l’islam comme religion abrahamique par les catholiques. En 1934, avec l’Égyptienne Mary Kahil, il fonde la Badaliya (« substitution »), un groupe de prière où des chrétiens s’offrent spirituellement « en otage » pour les musulmans, dans une logique de solidarité et d’intercession. Ordonné prêtre de rite catholique melkite en 1950, il incarne une forme de catholicisme ouvert à l’islam, tout en restant fidèle à l’Église. &lt;/p&gt; &lt;p&gt; Il intervient aussi comme expert sur les  &lt;a href="https://www.youtube.com/watch?v=JabzLnmm8PM" title="les arts de l’islam avec luois Massignonpar Coscience Soufie"&gt;questions musulmanes &lt;/a&gt; dans l’Empire français, tout en défendant une politique non violente et une meilleure compréhension du monde arabe. Il influence profondément l’islamologie française, la théologie catholique du dialogue interreligieux, et prépare en partie l’ouverture de Vatican II envers l’islam. &lt;/p&gt; 
 </t>
         </is>
       </c>
-      <c r="F55" s="54" t="inlineStr">
+      <c r="F56" s="54" t="inlineStr">
         <is>
           <t>C5aym32gy2w</t>
         </is>
       </c>
-      <c r="G55" s="56" t="inlineStr">
+      <c r="G56" s="56" t="inlineStr">
         <is>
           <t>Louis Massignon et la tombe d’al-Hallâj par conscience Soufie</t>
         </is>
       </c>
-      <c r="H55" s="79" t="inlineStr">
+      <c r="H56" s="79" t="inlineStr">
         <is>
           <t>https://www.laphilo.fr/pho/lmassignon-mini.webp</t>
         </is>
       </c>
-      <c r="J55" s="48" t="inlineStr">
+      <c r="J56" s="48" t="inlineStr">
         <is>
           <t xml:space="preserve">spiritualite </t>
         </is>
       </c>
-      <c r="K55" s="48" t="inlineStr">
+      <c r="K56" s="48" t="inlineStr">
         <is>
           <t xml:space="preserve">Soufisme ; Orientalisme</t>
         </is>
       </c>
-      <c r="L55" s="80" t="inlineStr">
+      <c r="L56" s="80" t="inlineStr">
         <is>
           <t>Philosophe français, considéré comme l’un des fondateurs de l’islamologie moderne et un pionnier du dialogue islamo-chrétien.</t>
         </is>
       </c>
-      <c r="N55" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-    </row>
-    <row r="56" ht="273" customHeight="1" s="49">
-      <c r="A56" s="57" t="n">
+      <c r="N56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="273" customHeight="1" s="49">
+      <c r="A57" s="57" t="n">
         <v>1884</v>
       </c>
-      <c r="B56" s="57" t="inlineStr">
+      <c r="B57" s="57" t="inlineStr">
         <is>
           <t>1962</t>
         </is>
       </c>
-      <c r="C56" s="57" t="inlineStr">
+      <c r="C57" s="57" t="inlineStr">
         <is>
           <t>1884 - 1962</t>
         </is>
       </c>
-      <c r="D56" s="58" t="inlineStr">
+      <c r="D57" s="58" t="inlineStr">
         <is>
           <t>Gaston BACHELARD</t>
         </is>
       </c>
-      <c r="E56" s="59" t="inlineStr">
+      <c r="E57" s="59" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Gaston_Bachelard"  title=" Wikipedia"&gt;Gaston BACHELARD&lt;/a&gt; était un  philosophe français des sciences et de la poésie et  resta la figure emblématique majeure de l’épistémologie française. Il mena de front une réflexion sur la raison scientifique et sur l'imagination poétique, qu'il considérait comme deux activités distinctes de l'esprit humain.  &lt;a href="https://www.youtube.com/watch?v=UY6EZsKqb8w" title="Une Vie, une œuvre : Gaston Bachelard, une enfance parmi les eaux par Rien ne veut rien dire"&gt;Sa philosophie&lt;/a&gt; peut être abordée selon deux axes principaux, souvent appelés "le diurne" (la raison, la science) et "le nocturne" (le rêve, la poésie). &lt;/p&gt; &lt;p&gt;  Il  a révolutionné l'épistémologie en insistant sur le fait que la science moderne (la physique quantique, la relativité) n'est pas une simple continuation ou un perfectionnement de la connaissance ordinaire, mais une rupture radicale avec elle. Pour comprendre le monde tel que le révèlent Einstein ou Bohr, il faut briser ("rompre") avec les intuitions, les préjugés et les images sensibles qui structurent notre expérience commune du monde. L'objet scientifique (un atome, un électron) n'est pas un "petit caillou" ; il est une construction mathématique qui défie l'imagination.  Ce qui empêche cette rupture, ce sont les "obstacles" ancrés dans notre esprit : l'expérience première, l'opinion (doxa), les métaphores trop faciles. Le travail du scientifique est un combat contre ces obstacles pour laisser place à une raison abstraite et rigoureuse.&lt;/p&gt; &lt;p&gt;  Il montre que le progrès scientifique se fait souvent par la négation des théories anciennes. Une nouvelle théorie ne complète pas l'ancienne ; elle la contredit et la dépasse.  &lt;a href="https://www.persee.fr/doc/phlou_0035-3841_1963_num_61_72_5231"title="Psychanalyse de la raison chez Gaston Bachelard par Persée"&gt; La raison scientifique&lt;/a&gt;   doit donc être "ouverte", dialectique, capable de se réformer en permanence ("rationalisme appliqué" ou "matérialisme technique"). &lt;/p&gt; &lt;p&gt; Parallèlement à son  &lt;a href="https://www.youtube.com/watch?v=HlrsFGSneh4" title="Gaston Bachelard, philosophe français des sciences par Mathieu"&gt;travail sur la science&lt;/a&gt;, il a développé une philosophie de l'imagination matérielle et de la poésie, peut-être même plus célèbre aujourd'hui. Il ne s'intéresse pas aux images comme copies du réel, mais comme forces productrices. Il étudie comment  &lt;a href="https://www.youtube.com/watch?v=X05w-ggXXQM" title="Gaston Bachelard s'exprime sur le dormeur éveillé par l'élan du savoir"&gt; l'esprit rêveur&lt;/a&gt; entre en communion avec les éléments matériels primordiaux (le feu, &lt;a href="https://www.youtube.com/watch?v=Z65E177AEHc" title="Gaston Bachelard La poésie et l'eau éveillé par Résonances"&gt;  l'eau&lt;/a&gt;, l'air, la terre). Chaque élément inspire un réseau d'images et de sentiments spécifiques. Il distingue la rêverie (état de conscience poétique, heureux, dirigé vers le monde) du rêve nocturne (inconscient, souvent perturbé). La rêverie est une activité créatrice et solitaire qui nous reconnecte à l'enfance et au bonheur d'imaginer. &lt;/p&gt; &lt;p&gt; Il nous invite ainsi à une vie intellectuelle complète : à être rigoureux dans notre quête de vérité scientifique et à cultiver, par la poésie, une âme rêveuse et émerveillée par le monde. &lt;/p&gt; &lt;audio controls title="Gaston Bachelard : "Nous sommes des dormeurs éveillés, des rêveurs lucides" par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/24554-19.01.2024-ITEMA_23620023-2016C3372E0751-21.mp3" type="audio/mpeg" align="center"&gt;&lt;/audio&gt;  </t>
         </is>
       </c>
-      <c r="F56" s="57" t="inlineStr">
+      <c r="F57" s="57" t="inlineStr">
         <is>
           <t>fn_775MMIhE</t>
         </is>
       </c>
-      <c r="G56" s="59" t="inlineStr">
+      <c r="G57" s="59" t="inlineStr">
         <is>
           <t xml:space="preserve">"Gaston Bachelard, philosophe français des sciences" par Radio-Canada Archives</t>
         </is>
       </c>
-      <c r="H56" s="59" t="inlineStr">
+      <c r="H57" s="59" t="inlineStr">
         <is>
           <t>https://www.laphilo.fr/pho/bachelard-mini.webp</t>
         </is>
       </c>
-      <c r="J56" s="48" t="inlineStr">
+      <c r="J57" s="48" t="inlineStr">
         <is>
           <t>epistemologie ; esthetique</t>
         </is>
       </c>
-      <c r="K56" s="48" t="inlineStr">
+      <c r="K57" s="48" t="inlineStr">
         <is>
           <t>Rationalisme ; Constructivisme</t>
         </is>
       </c>
-      <c r="L56" s="48" t="inlineStr">
+      <c r="L57" s="48" t="inlineStr">
         <is>
           <t>philosophe français des sciences et de la poésie, représentant de l'épistémologie historique.</t>
         </is>
       </c>
-      <c r="N56" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-    </row>
-    <row r="57" ht="222" customHeight="1" s="49">
-      <c r="A57" s="54" t="n">
+      <c r="N57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="222" customHeight="1" s="49">
+      <c r="A58" s="54" t="n">
         <v>1884</v>
       </c>
-      <c r="B57" s="54" t="inlineStr">
+      <c r="B58" s="54" t="inlineStr">
         <is>
           <t>1978</t>
         </is>
       </c>
-      <c r="C57" s="54" t="inlineStr">
+      <c r="C58" s="54" t="inlineStr">
         <is>
           <t>1884 – 1978</t>
         </is>
       </c>
-      <c r="D57" s="55" t="inlineStr">
+      <c r="D58" s="55" t="inlineStr">
         <is>
           <t>Etienne GILSON</t>
         </is>
       </c>
-      <c r="E57" s="56" t="inlineStr">
+      <c r="E58" s="56" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/%C3%89tienne_Gilson" title=" Wikipedia"&gt;Etienne GILSON&lt;/a&gt; était un philosophe et historien  français reconnu pour ses   &lt;a href="https://www.en-attendant-nadeau.fr/2023/04/12/gilson-philosophe-cite/"  title="Un Alcuin du vingtième siècle par EAN"&gt;travaux consacré&lt;/a&gt; à la philosophie médiévale et en particulier au &lt;a href="https://www.youtube.com/watch?v=cVFGGJ-vHos"  title="SAINT THOMAS D'AQUIN - Réconcilier théologie et philosophie par Therence carvalho"&gt; Thomisme &lt;/a&gt; ( pensée de Thomas d’Aquin).  Il fut membre de l’Académie française et joua un rôle de premier plan dans la redécouverte et la valorisation de la philosophie du Moyen Âge, en combattant l’idée reçue selon laquelle cette période n’aurait pas produit de véritable pensée philosophique. Son magistère académique influença plusieurs générations de spécialistes. &lt;/p&gt; &lt;p&gt; Il  défend le réalisme philosophique en s’appuyant sur les œuvres de Thomas d’Aquin. Il est une des grandes figures du néothomisme, mouvement qui propose un renouvellement de la philosophie sur la base du thomisme catholique. Son ouvrage "L’Être et l’essence" a marqué le débat sur la métaphysique en France en repositionnant la doctrine thomiste comme une réponse originale à la crise de la &lt;a href="https://www.youtube.com/watch?v=Dl6FvYX6X7E" title="Etienne Gilson provocateur par Baglis tv"&gt;métaphysique moderne&lt;/a&gt;. Il a analysé la contribution du christianisme à la philosophie, interrogé la notion de « philosophie chrétienne » et montré comment la révélation a enrichi le champ rationnel de la philosophie médiévale. &lt;/p&gt; &lt;p&gt; Il fut également actif dans le débat intellectuel et religieux, défendant une conception chrétienne et réaliste de la culture et de la philosophie, tout en gardant une profonde sensibilité historique. Il joua un rôle dans l’animation du mouvement européen après la Seconde Guerre mondiale et dans le renouveau des études médiévales en France et au Canada.​ Son œuvre reste aujourd’hui une &lt;a href="https://www.persee.fr/doc/phlou_0035-3841_1978_num_76_32_6007"  title="n memoriam Étienne Gilson par Persée"&gt;référence incontournable&lt;/a&gt; pour l’étude de la pensée médiévale et la compréhension du dialogue entre philosophie et théologie. &lt;/p&gt; &lt;audio controls title="Étienne Gilson : une biographie intellectuelle et politiquer France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/18143-07.03.2018-ITEMA_21609308-2018C29703S0066-21.mp3" type="audio/mpeg" align="center"&gt;&lt;/audio&gt; </t>
         </is>
       </c>
-      <c r="F57" s="54" t="inlineStr">
+      <c r="F58" s="54" t="inlineStr">
         <is>
           <t>U52mO5rFZ1I</t>
         </is>
       </c>
-      <c r="G57" s="56" t="inlineStr">
+      <c r="G58" s="56" t="inlineStr">
         <is>
           <t>" En 1960, une conférence d'Étienne Gilson sur la tolérance et le dogmatisme par Radio-Canada Archives</t>
         </is>
       </c>
-      <c r="H57" s="56" t="inlineStr">
+      <c r="H58" s="56" t="inlineStr">
         <is>
           <t>https://www.laphilo.fr/pho/gilson-mini.webp</t>
         </is>
       </c>
-      <c r="J57" s="48" t="inlineStr">
+      <c r="J58" s="48" t="inlineStr">
         <is>
           <t>metaphysique ; spiritualite</t>
         </is>
       </c>
-      <c r="K57" s="48" t="inlineStr">
+      <c r="K58" s="48" t="inlineStr">
         <is>
           <t>Néothomisme</t>
         </is>
       </c>
-      <c r="L57" s="48" t="inlineStr">
+      <c r="L58" s="48" t="inlineStr">
         <is>
           <t>philosophe français spécialiste en histoire de la philosophie médiévale.</t>
         </is>
       </c>
-      <c r="N57" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-    </row>
-    <row r="58" ht="220.5" customHeight="1" s="49">
-      <c r="A58" s="57" t="n">
+      <c r="N58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="220.5" customHeight="1" s="49">
+      <c r="A59" s="57" t="n">
         <v>1886</v>
       </c>
-      <c r="B58" s="57" t="inlineStr">
+      <c r="B59" s="57" t="inlineStr">
         <is>
           <t>1951</t>
         </is>
       </c>
-      <c r="C58" s="57" t="inlineStr">
+      <c r="C59" s="57" t="inlineStr">
         <is>
           <t>1886 - 1951</t>
         </is>
       </c>
-      <c r="D58" s="58" t="inlineStr">
+      <c r="D59" s="58" t="inlineStr">
         <is>
           <t>René GUENON</t>
         </is>
       </c>
-      <c r="E58" s="81" t="inlineStr">
+      <c r="E59" s="81" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Ren%C3%A9_Gu%C3%A9non"   title=" Wikipedia"&gt;René GUENON&lt;/a&gt; était un philosophe et métaphysicien Français, connu surtout pour sa critique radicale de la modernité et pour son attachement à la métaphysique traditionnelle. Il est souvent rangé parmi les grands auteurs du traditionalisme. Il s'est rapidement tourné vers des sujets tels que l'alchimie, l'astrologie et la métaphysique et son travail est caractérisé par une connaissance profonde des &lt;a  href="https://www.youtube.com/watch?v=87R2WP0ZCkc"   title="le mystère du devenir postume guénon par il solitario"&gt;traditions ésotériques &lt;/a&gt; et mystiques de diverses cultures, notamment l'hindouisme, le bouddhisme, le taoïsme et le soufisme.&lt;/p&gt; &lt;p&gt; Son idée centrale est qu’il existe une sagesse traditionnelle commune à plusieurs civilisations, au-delà des différences religieuses de surface. Pour lui, les grandes traditions spirituelles conservent des vérités profondes, alors que le monde moderne a tendance à les oublier. L'un de ses concepts les plus influents est celui de la &lt;a  href="https://www.youtube.com/watch?v=qlgHNpzlCR4&amp;ab_channel=Revue%C3%A9l%C3%A9ments"   title="La Tradition Primordiale par Revue éléments"&gt;"tradition primordiale"&lt;/a&gt;, qu'il considérait comme une connaissance spirituelle universelle et intemporelle présente dans toutes les cultures et religions. &lt;/p&gt; &lt;p&gt; Il s’oppose fortement au matérialisme, à l’individualisme et à ce qu’il voit comme la domination de la quantité sur la qualité. Dans ses livres, il explique que la modernité privilégie la technique, l’utilité et le calcul, au détriment du sens spirituel. Son travail a été très influent dans le développement du mouvement &lt;a  href="https://fr.wikipedia.org/wiki/La_Tradition_selon_la_perspective_de_Ren%C3%A9_Gu%C3%A9non"   title="La Tradition selon guénon par wikipedia"&gt;"Traditionaliste",&lt;/a&gt;  qui cherche à préserver et à promouvoir les valeurs spirituelles et culturelles traditionnelles dans le monde moderne. &lt;/p&gt; &lt;p&gt;  Ses écrits ont également eu un impact significatif sur un certain nombre d'autres domaines, notamment la &lt;a  href="https://www.youtube.com/watch?v=TXhXCrYOq0A&amp;ab_channel=LaTraditionPrimordiale"  title="L'illusion de la vie moderne par La Tradition Primordiale"&gt;l'illusion de la vie ordinaire&lt;/a&gt;, la crise du monde moderne, la religion et l'art.&lt;/p&gt; &lt;p&gt;  Son traditionalisme s'oppose à la vision progressiste et matérialiste de la modernité, en affirmant que la société doit revenir aux valeurs et aux principes spirituels qui ont été transmis à travers les âges.&lt;/p&gt;   &lt;audio controls title="L'oeuvre de René Guenon par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/13915-07.11.2019-ITEMA_22196740-2019C3372E0405-21.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt; </t>
         </is>
       </c>
-      <c r="F58" s="57" t="inlineStr">
+      <c r="F59" s="57" t="inlineStr">
         <is>
           <t>CYbrdHqnWfo</t>
         </is>
       </c>
-      <c r="G58" s="59" t="inlineStr">
+      <c r="G59" s="59" t="inlineStr">
         <is>
           <t xml:space="preserve">La fin des temps par Le Précepteur</t>
         </is>
       </c>
-      <c r="H58" s="59" t="inlineStr">
+      <c r="H59" s="59" t="inlineStr">
         <is>
           <t>https://www.laphilo.fr/pho/guenon-mini.webp</t>
         </is>
       </c>
-      <c r="J58" s="48" t="inlineStr">
+      <c r="J59" s="48" t="inlineStr">
         <is>
           <t>metaphysique ; spiritualite</t>
         </is>
       </c>
-      <c r="K58" s="48" t="inlineStr">
+      <c r="K59" s="48" t="inlineStr">
         <is>
           <t>Pérennialisme</t>
         </is>
       </c>
-      <c r="L58" s="48" t="inlineStr">
+      <c r="L59" s="48" t="inlineStr">
         <is>
           <t>philosophe et métaphysicien français qui prône le retour du traditionalisme.</t>
         </is>
       </c>
-      <c r="N58" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-    </row>
-    <row r="59" ht="229.5" customHeight="1" s="49">
-      <c r="A59" s="57" t="n">
+      <c r="N59" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="229.5" customHeight="1" s="49">
+      <c r="A60" s="57" t="n">
         <v>1888</v>
       </c>
-      <c r="B59" s="57" t="n">
+      <c r="B60" s="57" t="n">
         <v>1974</v>
       </c>
-      <c r="C59" s="60" t="inlineStr">
+      <c r="C60" s="60" t="inlineStr">
         <is>
           <t>1888 – 1974</t>
         </is>
       </c>
-      <c r="D59" s="60" t="inlineStr">
+      <c r="D60" s="60" t="inlineStr">
         <is>
           <t>Jean WAHL</t>
         </is>
       </c>
-      <c r="E59" s="61" t="inlineStr">
+      <c r="E60" s="61" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Jean_Wahl"  title=" Wikipedia"&gt;Jean WAHL&lt;/a&gt; était un philosophe français,  professeur à la Sorbonne, il joua un rôle capital dans la réception des philosophies étrangères en France — Kierkegaard, Hegel, Heidegger, Whitehead, la philosophie américaine — et fonda en 1946 &lt;a href="https://www.en-attendant-nadeau.fr/2017/05/09/paris-philosophes-22-wahl/"  title="
 Paris des philosophes par en attendant nadeau"&gt;le Collège philosophique, &lt;/a&gt;  institution unique qui donna pendant trente ans une tribune aux philosophes du monde entier à Paris. &lt;/p&gt; &lt;p&gt; Sa thèse sur &lt;em&gt;Le Malheur de la conscience dans la philosophie de Hegel&lt;/em&gt; (1929) est un texte fondateur de la lecture existentialiste de Hegel en France : en mettant en lumière la dialectique de la conscience malheureuse dans la &lt;em&gt;Phénoménologie de l'Esprit&lt;/em&gt;, il  &lt;a href="https://www.youtube.com/watch?v=5lqhtfDxEQU"  title="jean wahl god is the horizon of all conscious par spiritual quest "&gt;contribua décisivement &lt;/a&gt;  à orienter la réception française de Hegel vers les thématiques de l'existence, de la finitude et de la transcendance. Cette lecture influença profondément Sartre, Bataille et Merleau-Ponty. &lt;/p&gt; &lt;p&gt; Arrêté par les nazis en 1941 et interné à Drancy, il réussit à s'évader et à rejoindre les États-Unis où il enseigna jusqu'à la Libération. Cette expérience nourrit sa réflexion sur l'existence, la finitude et la transcendance. Dans sa &lt;em&gt;Traité de métaphysique&lt;/em&gt; (1953) et dans ses recueils poétiques — car il était aussi poète — il chercha à articuler l'expérience du tragique et de la joie dans une philosophie de la « trans-ascendance ». Homme de dialogue exceptionnel, il fut le passeur entre les grandes traditions philosophiques européenne et américaine. &lt;/p&gt;   &lt;audio controls title="le silence mystique est il à préserver par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/13915-16.02.2025-ITEMA_24030781-2025C3372E0048-NET_MFC_12794E2E-D0EA-4790-855D-484CC4309EF5-21-27aca72b8ab79e623b51c3b6c79e4d8f.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt; </t>
         </is>
       </c>
-      <c r="F59" s="60" t="inlineStr">
+      <c r="F60" s="60" t="inlineStr">
         <is>
           <t>g0UJRl_TKQE</t>
         </is>
       </c>
-      <c r="G59" s="61" t="inlineStr">
+      <c r="G60" s="61" t="inlineStr">
         <is>
           <t xml:space="preserve"> Jean Wahl parle de philosophie en tant que poète et de poésie en tant que philosophe
 </t>
         </is>
       </c>
-      <c r="H59" s="61" t="inlineStr">
+      <c r="H60" s="61" t="inlineStr">
         <is>
           <t>https://www.laphilo.fr/pho/jwahl-mini.webp</t>
         </is>
       </c>
-      <c r="J59" s="48" t="inlineStr">
+      <c r="J60" s="48" t="inlineStr">
         <is>
           <t>metaphysique ; epistemologie</t>
         </is>
       </c>
-      <c r="K59" s="48" t="inlineStr">
+      <c r="K60" s="48" t="inlineStr">
         <is>
           <t>Existentialisme</t>
         </is>
       </c>
-      <c r="L59" s="48" t="inlineStr">
+      <c r="L60" s="48" t="inlineStr">
         <is>
           <t>philosophe français capital dans la réception des philosophies étrangères en France.</t>
         </is>
       </c>
-      <c r="M59" t="inlineStr">
+      <c r="M60" t="inlineStr">
         <is>
           <t xml:space="preserve">juive</t>
         </is>
       </c>
-      <c r="N59" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-    </row>
-    <row r="60" ht="284.25" customHeight="1" s="49">
-      <c r="A60" s="57" t="n">
+      <c r="N60" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="284.25" customHeight="1" s="49">
+      <c r="A61" s="57" t="n">
         <v>1889</v>
       </c>
-      <c r="B60" s="57" t="n">
+      <c r="B61" s="57" t="n">
         <v>1973</v>
       </c>
-      <c r="C60" s="60" t="inlineStr">
+      <c r="C61" s="60" t="inlineStr">
         <is>
           <t>1889 – 1973</t>
         </is>
       </c>
-      <c r="D60" s="60" t="inlineStr">
+      <c r="D61" s="60" t="inlineStr">
         <is>
           <t>Gabriel MARCEL</t>
         </is>
       </c>
-      <c r="E60" s="77" t="inlineStr">
+      <c r="E61" s="77" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://en.wikipedia.org/wiki/Gabriel_Marcel"  title=" Wikipedia"&gt;Gabriel MARCEL&lt;/a&gt; était un philosophe et dramaturge  français, généralement classé parmi les représentants majeurs de l’existentialisme chrétien et du personnalisme. Il préférait toutefois se définir comme un penseur « néo-socratique » ou comme un philosophe de l’existence, car il se méfiait de &lt;a href="https://www.persee.fr/doc/phlou_0035-3841_1955_num_53_37_4535"  title=" un exposé de la philosophie de Gabriel Marcel par persée"&gt;l’étiquette existentialiste, &lt;/a&gt; notamment en raison de son opposition à Sartre parce qu’il ne considère pas l’existence comme abandonnée à l’absurde : pour lui, la fidélité, l’amour et l’espérance ouvrent l’être humain à une dimension transcendante.&lt;/p&gt; &lt;p&gt; Le point de départ de sa pensée est l’existence concrète, vécue par une personne  &lt;a href="https://www.youtube.com/watch?v=8JcdDv7F7zI"  title=" l’espérance qui nous pousse par développement personnel"&gt;située dans une histoire, &lt;/a&gt; un corps et des relations. Il refuse de traiter l’être humain comme un objet que l’on pourrait analyser de manière entièrement extérieure : nous sommes toujours engagés dans le monde et impliqués dans les situations que nous cherchons à comprendre. &lt;/p&gt; &lt;p&gt; Il distingue le problème du mystère. Un problème est extérieur à moi et peut être résolu par une méthode technique ; un mystère, au contraire, m’implique intérieurement et ne peut être réduit à une simple explication. L’amour, la fidélité, la souffrance, la mort et l’espérance relèvent ainsi du mystère de l’existence plutôt que d’un problème à résoudre. &lt;/p&gt; &lt;p&gt; Il accorde une grande importance à la présence, à la disponibilité, à la fidélité et à l’espérance. La personne se réalise dans la rencontre avec autrui, et non dans l’isolement d’une conscience individuelle ; cette relation humaine trouve finalement son accomplissement dans la relation à Dieu, conçu comme le « Toi absolu ». &lt;/p&gt;
 </t>
         </is>
       </c>
-      <c r="F60" s="60" t="inlineStr">
+      <c r="F61" s="60" t="inlineStr">
         <is>
           <t>snNPlT8fx84</t>
         </is>
       </c>
-      <c r="G60" s="61" t="inlineStr">
+      <c r="G61" s="61" t="inlineStr">
         <is>
           <t>gabriel marcel par yoann diot</t>
         </is>
       </c>
-      <c r="H60" s="61" t="inlineStr">
+      <c r="H61" s="61" t="inlineStr">
         <is>
           <t>https://www.laphilo.fr/pho/gmarcel-mini.webp</t>
         </is>
       </c>
-      <c r="J60" s="48" t="inlineStr">
+      <c r="J61" s="48" t="inlineStr">
         <is>
           <t>metaphysique</t>
         </is>
       </c>
-      <c r="K60" s="48" t="inlineStr">
+      <c r="K61" s="48" t="inlineStr">
         <is>
           <t>Existentialisme ; Personnalisme ; Spiritualisme</t>
         </is>
       </c>
-      <c r="L60" s="76" t="inlineStr">
+      <c r="L61" s="76" t="inlineStr">
         <is>
           <t>philosophe et dramaturge français  représentant  de l’existentialisme chrétien et du personnalisme.</t>
         </is>
       </c>
-      <c r="N60" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-    </row>
-    <row r="61" ht="201.75" customHeight="1" s="49">
-      <c r="A61" s="54" t="n">
+      <c r="N61" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="201.75" customHeight="1" s="49">
+      <c r="A62" s="54" t="n">
         <v>1891</v>
       </c>
-      <c r="B61" s="54" t="inlineStr">
+      <c r="B62" s="54" t="inlineStr">
         <is>
           <t>1976</t>
         </is>
       </c>
-      <c r="C61" s="54" t="inlineStr">
+      <c r="C62" s="54" t="inlineStr">
         <is>
           <t>1891 – 1976</t>
         </is>
       </c>
-      <c r="D61" s="55" t="inlineStr">
+      <c r="D62" s="55" t="inlineStr">
         <is>
           <t>Martial GUEROULT</t>
         </is>
       </c>
-      <c r="E61" s="56" t="inlineStr">
+      <c r="E62" s="56" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Martial_Gueroult"  title=" Wikipedia"&gt;Martial GUEROULT&lt;/a&gt; était un philosophe français, l'un des représentants les plus importants de la méthode d'histoire de la philosophie par analyse interne des textes. Né à Saint-Quentin, normalien et agrégé de philosophie, il fut professeur à la Sorbonne puis au Collège de France, où il occupa la chaire d'histoire et technologie des systèmes philosophiques. Ses travaux sur Descartes, Fichte, Leibniz et Spinoza constituent des monuments de l'érudition philosophique française. &lt;/p&gt; &lt;p&gt;   &lt;a href="https://fr.scribd.com/document/264871906/Gueroult-methode"  title=" Gueroult méthode par scribd"&gt;La méthode de Gueroult, &lt;/a&gt; qu'il développa et défendit tout au long de sa carrière, consiste à lire les grands textes philosophiques de l'intérieur, en suivant rigoureusement la logique propre de chaque système. Pour lui, tout grand philosophe a construit un système cohérent dont chaque élément est solidaire des autres, et la tâche de l'historien de la philosophie est de reconstituer cette architecture interne avec la même rigueur que celle du mathématicien étudiant un théorème. Cette approche s'oppose à la fois à l'histoire externe (contextualiste) et à la lecture éclectique des textes. &lt;/p&gt; &lt;p&gt; Son œuvre maîtresse, &lt;em&gt;Descartes selon l'ordre des raisons&lt;/em&gt; (2 volumes, 1953), est une analyse minutieuse et magistrale de l'enchaînement des arguments dans les &lt;em&gt;Méditations métaphysiques&lt;/em&gt; de Descartes. Ses études sur Spinoza (&lt;em&gt;Spinoza&lt;/em&gt;, 2 volumes publiés de 1968 à 1974) sont également des références incontournables. Dans &lt;em&gt;Dianoématique&lt;/em&gt;, son projet inachevé, il cherchait à établir une théorie générale des systèmes philosophiques. Il a profondément &lt;a href="https://www.persee.fr/doc/barb_0001-4133_1976_num_62_1_60408"  title="Hommage à martial Gueroult par persée"&gt;marqué l'histoire de la philosophie &lt;/a&gt; française et sa méthode continue d'influencer les études cartésiennes et spinozistes. &lt;/p&gt;</t>
         </is>
       </c>
-      <c r="F61" s="54" t="n"/>
-      <c r="G61" s="56" t="n"/>
-      <c r="H61" s="56" t="inlineStr">
+      <c r="F62" s="54" t="n"/>
+      <c r="G62" s="56" t="n"/>
+      <c r="H62" s="56" t="inlineStr">
         <is>
           <t>https://www.laphilo.fr/pho/gueroult-mini.webp</t>
         </is>
       </c>
-      <c r="I61" s="48" t="inlineStr">
+      <c r="I62" s="48" t="inlineStr">
         <is>
           <t>https://laphilo.fr/photo/mgueroult.webp</t>
         </is>
       </c>
-      <c r="J61" s="48" t="inlineStr">
+      <c r="J62" s="48" t="inlineStr">
         <is>
           <t>epistemologie</t>
         </is>
       </c>
-      <c r="K61" s="48" t="inlineStr">
+      <c r="K62" s="48" t="inlineStr">
         <is>
           <t>Rationalisme</t>
         </is>
       </c>
-      <c r="L61" s="48" t="inlineStr">
+      <c r="L62" s="48" t="inlineStr">
         <is>
           <t>philosophe français de la méthode d'histoire de la philosophie par analyse interne des textes.</t>
         </is>
       </c>
-      <c r="N61" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-    </row>
-    <row r="62" ht="161.25" customHeight="1" s="49">
-      <c r="A62" s="57" t="n">
+      <c r="N62" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="161.25" customHeight="1" s="49">
+      <c r="A63" s="57" t="n">
         <v>1892</v>
       </c>
-      <c r="B62" s="57" t="n">
+      <c r="B63" s="57" t="n">
         <v>1964</v>
       </c>
-      <c r="C62" s="60" t="inlineStr">
+      <c r="C63" s="60" t="inlineStr">
         <is>
           <t>1892 – 1964</t>
         </is>
       </c>
-      <c r="D62" s="60" t="inlineStr">
+      <c r="D63" s="60" t="inlineStr">
         <is>
           <t>Alexandre KOYRÉ</t>
         </is>
       </c>
-      <c r="E62" s="61" t="inlineStr">
+      <c r="E63" s="61" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Alexandre_Koyr%C3%A9"  title=" Wikipedia"&gt;Alexandre KOYRÉ&lt;/a&gt; était un philosophe et historien des sciences français d'origine russe, l'un des fondateurs de l'histoire des sciences modernes et un penseur dont l'influence sur l'historiographie scientifique mondiale fut décisive. Né à Taganrog en Russie, il étudia à Göttingen auprès de Husserl et de Hilbert avant de s'établir à Paris où il devint directeur d'études à l'École pratique des hautes études. Après la guerre, il partagea sa carrière entre Paris et Princeton. &lt;/p&gt; &lt;p&gt; Son œuvre maîtresse, &lt;em&gt;Études galiléennes&lt;/em&gt; (1939), est une révolution dans l'histoire des sciences. Contre la vision positiviste d'une science qui progresse par accumulation de faits expérimentaux, Koyré montre que la révolution scientifique du XVIIe siècle constitua une transformation radicale de la structure conceptuelle par laquelle les hommes pensaient la nature : le passage du cosmos aristotélicien, fini et ordonné, à l'univers infini et homogène de la physique classique. Cette thèse centrale, que l'histoire des sciences est d'abord une histoire des structures intellectuelles et non une simple accumulation de données, renouvela entièrement la discipline. &lt;/p&gt; &lt;p&gt; Dans &lt;em&gt;Du Monde clos à l'univers infini&lt;/em&gt; (1957), il approfondit cette thèse en retraçant la mutation cosmologique du XVIe au XVIIe siècle de Copernic à Newton. Ses travaux sur Descartes, Boyle et Newton sont également des contributions majeures. Son influence sur Thomas Kuhn — qui lui rendit hommage dans &lt;em&gt;La Structure des révolutions scientifiques&lt;/em&gt; — témoigne de la portée internationale de son travail. Koyré représente le modèle du philosophe-historien dont la rigueur intellectuelle a transformé durablement la compréhension du développement de la pensée scientifique. &lt;/p&gt;</t>
         </is>
       </c>
-      <c r="F62" s="60" t="inlineStr">
+      <c r="F63" s="60" t="inlineStr">
         <is>
           <t>m-60JVKKvbA</t>
         </is>
       </c>
-      <c r="G62" s="61" t="inlineStr">
+      <c r="G63" s="61" t="inlineStr">
         <is>
           <t>Alexandre KOYRÉ par Christopher Santos Côté</t>
         </is>
       </c>
-      <c r="H62" s="61" t="inlineStr">
+      <c r="H63" s="61" t="inlineStr">
         <is>
           <t>https://www.laphilo.fr/pho/koyre-mini.webp</t>
         </is>
       </c>
-      <c r="J62" s="48" t="inlineStr">
+      <c r="J63" s="48" t="inlineStr">
         <is>
           <t>epistemologie</t>
         </is>
       </c>
-      <c r="K62" s="48" t="inlineStr">
+      <c r="K63" s="48" t="inlineStr">
         <is>
           <t>Rationalisme</t>
         </is>
       </c>
-      <c r="L62" s="48" t="inlineStr">
+      <c r="L63" s="48" t="inlineStr">
         <is>
           <t>philosophe français et un des fondateurs de l'histoire des sciences modernes.</t>
         </is>
       </c>
-      <c r="M62" t="inlineStr">
+      <c r="M63" t="inlineStr">
         <is>
           <t xml:space="preserve">juive;russe</t>
         </is>
       </c>
-      <c r="N62" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-    </row>
-    <row r="63" ht="300.75" customHeight="1" s="49">
-      <c r="A63" s="57" t="n">
+      <c r="N63" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="300.75" customHeight="1" s="49">
+      <c r="A64" s="57" t="n">
         <v>1895</v>
       </c>
-      <c r="B63" s="57" t="n">
+      <c r="B64" s="57" t="n">
         <v>1958</v>
       </c>
-      <c r="C63" s="60" t="inlineStr">
+      <c r="C64" s="60" t="inlineStr">
         <is>
           <t>1895 – 1958</t>
         </is>
       </c>
-      <c r="D63" s="60" t="inlineStr">
+      <c r="D64" s="60" t="inlineStr">
         <is>
           <t>Gabriel MADINIER</t>
         </is>
       </c>
-      <c r="E63" s="66" t="inlineStr">
+      <c r="E64" s="66" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Gabriel_Madinier"  title=" Wikipedia"&gt;Gabriel MADINIER&lt;/a&gt; était un philosophe français de tradition spiritualiste et réflexive, professeur à l’Université de Lyon, connu surtout pour sa « trilogie » sur la conscience (Conscience et mouvement, Conscience et amour, Conscience et signification) et pour son analyse de la conscience morale. Sa pensée s’inscrit dans le sillage de la philosophie de l’esprit française et vise à fonder une métaphysique et une éthique à partir de l’acte même par lequel la conscience se pose. &lt;/p&gt; &lt;p&gt; Fidèle à la méthode réflexive héritée de Lagneau et de Maine de Biran, il cherche à saisir le moi non comme un objet, mais dans l’acte même par lequel il se pose. Dans &lt;a href="https://www.persee.fr/doc/phlou_0776-555x_1940_num_43_67_4030_t1_0292_0000_2"  title="gabriel madinier , conscience et mouvement par persée"&gt;Conscience et mouvement &lt;/a&gt;  (1938), il montre que la conscience n’est pas séparable de la motricité : le geste, l’effort, le mouvement sont des manifestations concrètes à travers lesquelles la conscience s’éprouve et se constitue. Cette « conscience motrice » lui permet de dépasser les impasses du parallélisme et de l’objectivisme en ancrant la vie spirituelle dans l’expérience vécue du sujet agissant. &lt;/p&gt; &lt;p&gt; Dans Conscience et amour (1938), il prolonge cette enquête en explorant les conditions « surdéterminantes » de l’acte du moi, c’est-à-dire ce qui l’oriente vers autrui et vers la valeur. Le « Nous » n’est pas une simple donnée sociologique, mais une structure de la conscience où l’amour apparaît comme catégorie suprême de la raison, capable à la fois de distinguer et d’unir. Il y dessine une métaphysique du lien : au-delà du plan empirique des relations, l’amour se développe par la médiation de la justice et ouvre sur une dimension religieuse (rapport à Dieu) sans quitter le terrain de la psychologie réflexive. &lt;/p&gt; &lt;p&gt; Avec Conscience et signification (1953), il achève sa trilogie en proposant une véritable « métaphysique du signe » : la conscience est essentiellement productrice de sens, et c’est dans le Cogito que la conscience morale prend son origine. Il en tire, dans La conscience morale (1954), les conséquences éthiques : un rationalisme à la fois métaphysique et moral, d’inspiration très française, qui voit dans la raison la source des plus hautes exigences et dans l’amour (dont le christianisme révèle la signification universelle) l’explication ultime du réel. Pour lui, « ou le monde est absurde, ou l’amour explique tout », formule qui résume son option pour un spiritualisme rationnel ouvert à la transcendance. &lt;/p&gt; &lt;p&gt; Longtemps moins célèbre que d’autres représentants du spiritualisme français, il est reconnu par ses pairs comme un métaphysicien du signe et un penseur exigeant de la conscience et de l’amour. Ses ouvrages, réédités et parfois préfacés (notamment par Henri Gouhier et Aimé Forest), continuent d’intéresser ceux qui cherchent une philosophie réflexive, ancrée dans l’expérience concrète, mais capable de déboucher sur une éthique et une métaphysique intégrales. En ce sens, il prolonge et approfondit la tradition biranienne en lui donnant une tournure à la fois psychologique, morale et religieuse. &lt;/p&gt; 
 </t>
         </is>
       </c>
-      <c r="F63" s="60" t="n"/>
-      <c r="G63" s="61" t="n"/>
-      <c r="H63" s="61" t="inlineStr">
+      <c r="F64" s="60" t="n"/>
+      <c r="G64" s="61" t="n"/>
+      <c r="H64" s="61" t="inlineStr">
         <is>
           <t>https://www.laphilo.fr/pho/gmadinier-mini.webp</t>
         </is>
       </c>
-      <c r="I63" s="48" t="inlineStr">
+      <c r="I64" s="48" t="inlineStr">
         <is>
           <t>https://www.laphilo.fr/photo/gmadinier.webp</t>
         </is>
       </c>
-      <c r="J63" s="48" t="inlineStr">
+      <c r="J64" s="48" t="inlineStr">
         <is>
           <t xml:space="preserve">spiritualite </t>
         </is>
       </c>
-      <c r="K63" s="48" t="inlineStr">
+      <c r="K64" s="48" t="inlineStr">
         <is>
           <t>Spiritualisme</t>
         </is>
       </c>
-      <c r="L63" s="82" t="inlineStr">
+      <c r="L64" s="82" t="inlineStr">
         <is>
           <t xml:space="preserve"> philosophe spiritualiste français connu surtout pour sa « trilogie » sur la conscience.</t>
         </is>
       </c>
-      <c r="N63" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-    </row>
-    <row r="64" ht="156.75" customHeight="1" s="49">
-      <c r="A64" s="57" t="n">
+      <c r="N64" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="156.75" customHeight="1" s="49">
+      <c r="A65" s="57" t="n">
         <v>1896</v>
       </c>
-      <c r="B64" s="57" t="inlineStr">
+      <c r="B65" s="57" t="inlineStr">
         <is>
           <t>1960</t>
         </is>
       </c>
-      <c r="C64" s="57" t="inlineStr">
+      <c r="C65" s="57" t="inlineStr">
         <is>
           <t>1896 – 1960</t>
         </is>
       </c>
-      <c r="D64" s="58" t="inlineStr">
+      <c r="D65" s="58" t="inlineStr">
         <is>
           <t>Gaston BERGER</t>
         </is>
       </c>
-      <c r="E64" s="65" t="inlineStr">
+      <c r="E65" s="65" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Gaston_Berger"  title=" Wikipedia"&gt;Gaston BERGER&lt;/a&gt; était un philosophe, chef d’entreprise et haut fonctionnaire français connu pour avoir développé la notion de prospective et pour ses travaux sur la phénoménologie de Husserl. Il a cherché toute sa vie à articuler réflexion philosophique et action concrète, aussi bien dans l’industrie que dans l’administration de l’enseignement supérieur. Il fonde en 1925 la Société &lt;a href="https://www.youtube.com/watch?v=gChPu0ENNxI" title=" Centre Gaston Berger par Insa toulouse"&gt;d’études philosophiques &lt;/a&gt; et la revue Études philosophiques, qui deviendront des lieux importants de la réflexion française.
  &lt;/p&gt; &lt;p&gt; Fondateur du mouvement de “prospective”, qu’il définit comme une science de l’“homme à venir”, vise à comprendre l’avenir possible pour mieux participer à sa réalisation, en réfléchissant aux besoins futurs tant culturels et moraux que techniques et matériels. Il crée le Centre international de prospective afin de favoriser des réflexions interdisciplinaires sur les futurs souhaitables et les responsabilités collectives.  &lt;/p&gt; &lt;p&gt;Il est l’un des principaux introducteurs de la phénoménologie d’Edmund Husserl en France, à laquelle il consacre sa thèse. Il propose la “théorétique”, conçue comme une science de la compréhension, qui vise à donner des outils conceptuels pour mieux saisir le réel et guider l’action.
  &lt;/p&gt; &lt;p&gt;Sa recherche se centre sur la conscience: valeur de la connaissance, présence de l’être, situation du moi, engagement, dialogue, amour, temps, courage. Il esquisse une phénoménologie de la mémoire où le devenir est une donnée concrète et le temps une construction ou un “mythe collectif” permettant aux hommes d’espérer et d’agir ensemble &lt;/p&gt; &lt;p&gt;  Il  incarne une figure de “philosophe‑administrateur”: il voit dans l’organisation et l’administration d’abord des problèmes humains avant d’être techniques. Son œuvre défend l’idée que la connaissance gratuite est à la fois facteur d’épanouissement personnel et condition d’une démocratie vivante. &lt;/p&gt;</t>
         </is>
       </c>
-      <c r="F64" s="57" t="inlineStr">
+      <c r="F65" s="57" t="inlineStr">
         <is>
           <t>uk28nuiT-js</t>
         </is>
       </c>
-      <c r="G64" s="59" t="inlineStr">
+      <c r="G65" s="59" t="inlineStr">
         <is>
           <t>"Connaissez-vous le modèle INSA ?" par groupeinsa</t>
         </is>
       </c>
-      <c r="H64" s="59" t="inlineStr">
+      <c r="H65" s="59" t="inlineStr">
         <is>
           <t>https://www.laphilo.fr/pho/berger-mini.webp</t>
         </is>
       </c>
-      <c r="J64" s="48" t="inlineStr">
+      <c r="J65" s="48" t="inlineStr">
         <is>
           <t>metaphysique ; ethique</t>
         </is>
       </c>
-      <c r="K64" s="48" t="inlineStr">
+      <c r="K65" s="48" t="inlineStr">
         <is>
           <t>Phénoménologie</t>
         </is>
       </c>
-      <c r="L64" s="48" t="inlineStr">
+      <c r="L65" s="48" t="inlineStr">
         <is>
           <t>philosophe français connu pour avoir développé la notion de Prospective.</t>
         </is>
       </c>
-      <c r="N64" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-    </row>
-    <row r="65" ht="294" customHeight="1" s="49">
-      <c r="A65" s="57" t="n">
+      <c r="N65" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="294" customHeight="1" s="49">
+      <c r="A66" s="57" t="n">
         <v>1897</v>
       </c>
-      <c r="B65" s="57" t="n">
+      <c r="B66" s="57" t="n">
         <v>1962</v>
       </c>
-      <c r="C65" s="57" t="inlineStr">
+      <c r="C66" s="57" t="inlineStr">
         <is>
           <t>1897 – 1962</t>
         </is>
       </c>
-      <c r="D65" s="58" t="inlineStr">
+      <c r="D66" s="58" t="inlineStr">
         <is>
           <t>Georges BATAILLE</t>
         </is>
       </c>
-      <c r="E65" s="83" t="inlineStr">
+      <c r="E66" s="83" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Georges_Bataille" title=" Wikipedia"&gt;George BATAILLE&lt;/a&gt;  est un écrivain, philosophe, anthropologue et sociologue français, souvent qualifié de metaphysicien du mal pour son intérêt pour le sexe, la mort, la dégradation et le pouvoir de l'obscène. Il fut bibliothécaire, fondateur du Collège de Sociologie en 1937, et membre du journal Acéphale. Largement ignoré durant sa vie, il est aujourd'hui une figure centrale  &lt;a href="https://www.youtube.com/watch?v=ub2Ucoxs5fk"  title="une vie, une œuvre par rien ne veut rien dire"&gt;de l'intelligence française &lt;/a&gt; et a influencé des penseurs comme Foucault, Derrida ou Deleuze. &lt;/p&gt; &lt;p&gt; Sa philosophie se centre sur l'expérience intérieure, décrite comme un « voyage au bout du possible de l'homme », une extase ou ravissement qui nous porte au-delà des limites. Cette expérience s'atteint dans l'ivresse, l'érotisme, le rire, l'effusion poétique —  &lt;a href="https://blogs.mediapart.fr/amadouba19gmailcom/blog/150125/georges-bataille-1897-1962-mystique-transgressif-amadou-bal-ba"  title="Georges Bataille mystique transgressif par blogs mediapart"&gt;sans révélation divine, &lt;/a&gt;  dans un athéisme féroce. L'expérience intérieure est une plongée dans l'abîme où les repères s'effondrent, le savoir est aboli, la pensée défaite : « je saisis en sombrant que la seule vérité de l'homme, enfin entrevue, est d'être une supplication sans réponse ». &lt;/p&gt; &lt;p&gt; Il  est le penseur du mal, de l'excès, du négatif et de l'érotisme, considérés comme autant d'expériences intérieures. Il fut attiré par la violence et la disruption qu'elle pourrait causer au capitalisme et aux valeurs bourgeoises. Il explore les &lt;a href="https://www.persee.fr/doc/litt_0047-4800_1985_num_58_2_1389"  title="Georges Bataille et la mort par persee"&gt;« expériences limites » &lt;/a&gt; corporelles : cruauté, érotisme, transgression, subversion, sacrifice et excès, qui transcendent la pensée rationnelle. Ces expériences sont des voies pour acquérir une souveraineté personnelle, où la rationalité est suspendue lorsqu'on s'abandonne aux objets de ses désirs. &lt;/p&gt; &lt;p&gt; Parmi ses concepts clés, on trouve la sovereaneté (la liberté comme « seul miracle profane : impossible et pourtant là »), le sperpero ou dépense (déploiement inutile), et la partie maudite. La partie maudite exprime notre rapport à la mort, la violence et l'érotisme — la part sauvagement excessive de l'énergie qui ne peut être intégrée au système. Le sacré et l'abjection s'épousent chez lui sous une forme de dépassement des antinomies : le sacré est « à la fois saint et maudit, pur et impur, blanc et noir ». &lt;/p&gt; &lt;p&gt; Son œuvre Sur Nietzsche offre une nouvelle vision révolutionnaire du philosophe allemand, qui influença significativement Foucault, Derrida, Barthes et autres. Ses conceptions de la souveraineté, du sperpero et du sacrifice auront une grande influence sur les philosophes du XXe siècle, et ses idées sont reprises par Derrida, Kristeva et Sollers. &lt;/p&gt; 
  &lt;audio controls title="Georges Bataille par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/13915-21.02.2024-ITEMA_23655177-2023C3372E0061-NET_MFC_CC62CF01-3F56-460F-B780-97916C17B0D7-21-7d903e2b8ecc4f9a64f0bed40bc4f642.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt; 
 </t>
         </is>
       </c>
-      <c r="F65" s="57" t="inlineStr">
+      <c r="F66" s="57" t="inlineStr">
         <is>
           <t>tpFSXAdlEYY</t>
         </is>
       </c>
-      <c r="G65" s="59" t="inlineStr">
+      <c r="G66" s="59" t="inlineStr">
         <is>
           <t>Georges BATAILLE le littérature et le mal par Mr Sigma</t>
         </is>
       </c>
-      <c r="H65" s="65" t="inlineStr">
+      <c r="H66" s="65" t="inlineStr">
         <is>
           <t>https://www.laphilo.fr/pho/gbataille-mini.webp</t>
         </is>
       </c>
-      <c r="J65" s="48" t="inlineStr">
+      <c r="J66" s="48" t="inlineStr">
         <is>
           <t>epistemologie ; ethique</t>
         </is>
       </c>
-      <c r="K65" s="48" t="inlineStr">
+      <c r="K66" s="48" t="inlineStr">
         <is>
           <t>Matérialisme</t>
         </is>
       </c>
-      <c r="L65" s="48" t="inlineStr">
+      <c r="L66" s="48" t="inlineStr">
         <is>
           <t>philosophe et écrivain français qualifié de métaphysicien du mal pour son intérêt pour le sexe, à la mort, la dégradation et le pouvoir de l'obscène.</t>
         </is>
       </c>
-      <c r="N65" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-    </row>
-    <row r="66" ht="323.25" customHeight="1" s="49">
-      <c r="A66" s="57" t="n">
+      <c r="N66" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="323.25" customHeight="1" s="49">
+      <c r="A67" s="57" t="n">
         <v>1898</v>
       </c>
-      <c r="B66" s="57" t="n">
+      <c r="B67" s="57" t="n">
         <v>1983</v>
       </c>
-      <c r="C66" s="57" t="inlineStr">
+      <c r="C67" s="57" t="inlineStr">
         <is>
           <t>1898 – 1983</t>
         </is>
       </c>
-      <c r="D66" s="58" t="inlineStr">
+      <c r="D67" s="58" t="inlineStr">
         <is>
           <t>Aimé FOREST</t>
         </is>
       </c>
-      <c r="E66" s="84" t="inlineStr">
+      <c r="E67" s="84" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Aim%C3%A9_Forest" title=" Wikipedia"&gt;Aimé FOREST&lt;/a&gt; était t un philosophe français spiritualiste, à la fois historien de la philosophie médiévale et métaphysicien d’inspiration thomiste et augustinienne. Sa pensée, souvent qualifiée de « philosophie du consentement », vise à articuler réalisme métaphysique, intériorité et sagesse chrétienne dans une démarche à la fois contemplative et concrète. &lt;/p&gt; &lt;p&gt; Né à Rancon (Haute-Vienne), agrégé de philosophie en 1921, il enseigne d’abord dans le secondaire avant de soutenir, en 1931, une thèse majeure sur La structure métaphysique du concret selon saint Thomas d’Aquin. Il occupe ensuite des chaires universitaires à Grenoble puis à Montpellier (1943–1968), où il forme plusieurs générations d’étudiants tout en publiant une œuvre abondante, jalonnée par des ouvrages comme Du consentement à l’être (1935), Consentement et création (1943), L’Avènement de l’âme (1973) ou Nos promesses encloses (1985). &lt;/p&gt; &lt;p&gt; Le titre même de son ouvrage phare indique l’axe central de sa philosophie : l’être ne se conquiert pas par la seule maîtrise conceptuelle, mais se reçoit dans un acte de consentement. Contre un idéalisme abstrait, Forest insiste sur la réalité concrète de l’existence et sur la nécessité, pour la pensée, de s’ouvrir à ce qui la précède et la soutient. Ce consentement n’est pas passivité, mais disposition active de l’intelligence à accueillir la vérité de l’être, vérité qui se dévoile davantage dans l’expérience intérieure que dans la construction systématique. &lt;/p&gt; &lt;p&gt; Influencé par Pascal, Maine de Biran, Louis Lavelle et Blondel, il développe une philosophie de l’intériorité où l’esprit découvre sa vocation sapientielle. L’âme n’est pas un objet parmi d’autres, mais le lieu où se noue le rapport à l’être et où se manifeste un « lien spirituel » qui unit les personnes entre elles et à la transcendance. Des titres comme L’Avènement de l’âme ou Essai sur les formes du lien spirituel montrent que sa métaphysique débouche sur une anthropologie spirituelle attentive à l’amour, à la promesse et à la communauté des esprits. &lt;/p&gt; &lt;p&gt;  Il assume explicitement la figure du « philosophe chrétien » : pour lui, la raison trouve son élan naturel dans le consentement au soutien de la foi, qui ne la supprime pas mais l’élève et l’assure. Sa démarche intègre thomisme et augustinisme dans une « sagesse plus haute que le thomisme », où métaphysique, mystique et amour convergent vers une sagesse intégrale. Cette orientation le place en marge des grands courants dominants du XXᵉ siècle (phénoménologie, existentialisme, pensée allemande), au profit d’une voie spirituelle, réaliste et universelle. &lt;/p&gt; &lt;p&gt; Longtemps peu connu hors des cercles spécialisés, il fait l’objet d’un regain d’attention grâce à des études (Michel Mahé, Philippe-Marie Margelidon, etc.) qui mettent en lumière la cohérence de son itinéraire. Son œuvre intéresse aujourd’hui ceux qui cherchent une métaphysique non dogmatique, ancrée dans l’expérience concrète et l’intériorité, tout en restant ouverte à la dimension religieuse. En ce sens, il propose moins un système clos qu’un chemin de sagesse : apprendre à consentir à l’être, à habiter son intériorité et à reconnaître, dans l’amour et la promesse, les formes vivantes du lien spirituel.&lt;/p&gt; 
 </t>
         </is>
       </c>
-      <c r="F66" s="57" t="n"/>
-      <c r="G66" s="59" t="n"/>
-      <c r="H66" s="65" t="inlineStr">
+      <c r="F67" s="57" t="n"/>
+      <c r="G67" s="59" t="n"/>
+      <c r="H67" s="65" t="inlineStr">
         <is>
           <t>https://www.laphilo.fr/pho/aforest-mini.webp</t>
         </is>
       </c>
-      <c r="I66" s="48" t="inlineStr">
+      <c r="I67" s="48" t="inlineStr">
         <is>
           <t>https://www.laphilo.fr/photo/aforest.webp</t>
         </is>
       </c>
-      <c r="J66" s="48" t="inlineStr">
+      <c r="J67" s="48" t="inlineStr">
         <is>
           <t xml:space="preserve">spiritualite </t>
         </is>
       </c>
-      <c r="K66" s="48" t="inlineStr">
+      <c r="K67" s="48" t="inlineStr">
         <is>
           <t>Augustinisme ; Thomisme</t>
         </is>
       </c>
-      <c r="L66" s="85" t="inlineStr">
+      <c r="L67" s="85" t="inlineStr">
         <is>
           <t>philosophe français spiritualiste, historien de la philosophie médiévale et métaphysicien d’inspiration thomiste et augustinienne.</t>
         </is>
       </c>
-      <c r="N66" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-    </row>
-    <row r="67" ht="188.25" customHeight="1" s="49">
-      <c r="A67" s="54" t="n">
+      <c r="N67" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="188.25" customHeight="1" s="49">
+      <c r="A68" s="54" t="n">
         <v>1901</v>
       </c>
-      <c r="B67" s="54" t="inlineStr">
+      <c r="B68" s="54" t="inlineStr">
         <is>
           <t>1999</t>
         </is>
       </c>
-      <c r="C67" s="54" t="inlineStr">
+      <c r="C68" s="54" t="inlineStr">
         <is>
           <t>1901 – 1999</t>
         </is>
       </c>
-      <c r="D67" s="55" t="inlineStr">
+      <c r="D68" s="55" t="inlineStr">
         <is>
           <t>Jean GUITTON</t>
         </is>
       </c>
-      <c r="E67" s="56" t="inlineStr">
+      <c r="E68" s="56" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Jean_Guitton" title=" Wikipedia"&gt;Jean GUITTON&lt;/a&gt; était un philosophe, écrivain et académicien français, figure majeure de la pensée catholique car sa pensée est profondément ancrée dans le catholicisme. Il a cherché à réconcilier la foi et la raison, le christianisme et les questionnements contemporains. Il s'est intéressé aux convergences entre la science la plus récente (notamment la physique quantique) et le christianisme, comme en témoigne son livre  &lt;a href="https://www.youtube.com/watch?v=QuHD0eMvmkc"  title="Jean Guitton, Igor et Grichka Bogdanoff "Dieu et la science" par Ina Sciences"&gt;"Dieu et la science"&lt;/a&gt; co-écrit avec les frères Bogdanov. &lt;/p&gt; &lt;p&gt;  Ses œuvres abordent des sujets fondamentaux tels que le temps et l'éternité (sa thèse portait sur Plotin et Saint Augustin), l'amour humain et divin, le problème de Jésus, et la question du sens de l'existence.  Il était connu pour sa capacité au dialogue et à la réflexion ouverte. Il fut notamment le seul laïc autorisé par le Pape à siéger au Concile Vatican II, ce qui souligne son rôle important dans la vie intellectuelle et religieuse de son temps. &lt;/p&gt; &lt;p&gt; Il  a laissé une œuvre considérable et variée, comprenant des essais philosophiques, des critiques religieuses, des biographies et des écrits plus personnels. Parmi ses titres notables, on peut citer "La philosophie de Newman", "Le Problème de Jésus", "L'Amour humain",   &lt;a href="https://www.persee.fr/doc/phlou_0035-3841_1952_num_50_25_7895_t1_0187_0000_2"  title="Jean Guitton, Le travail intellectuel. Conseils à ceux qui étudient et à ceux qui écrivent par Persée"&gt;"Le Travail intellectuel"&lt;/a&gt;, "Dialogues avec Paul VI", "Profils parallèles", et "La pensée et la guerre". &lt;/p&gt; &lt;p&gt; Il fut une figure intellectuelle  marquante dont la philosophie cherchait à unir la profondeur de la foi catholique avec les exigences de la raison et les évolutions du monde moderne. &lt;/p&gt;</t>
         </is>
       </c>
-      <c r="F67" s="54" t="inlineStr">
+      <c r="F68" s="54" t="inlineStr">
         <is>
           <t>7_fOAe03h18</t>
         </is>
       </c>
-      <c r="G67" s="56" t="inlineStr">
+      <c r="G68" s="56" t="inlineStr">
         <is>
           <t>"Jean GUITTON" par Jean Khoury</t>
         </is>
       </c>
-      <c r="H67" s="56" t="inlineStr">
+      <c r="H68" s="56" t="inlineStr">
         <is>
           <t>https://www.laphilo.fr/pho/guitton-mini.webp</t>
         </is>
       </c>
-      <c r="J67" s="48" t="inlineStr">
+      <c r="J68" s="48" t="inlineStr">
         <is>
           <t>metaphysique ; spiritualite</t>
         </is>
       </c>
-      <c r="K67" s="48" t="inlineStr">
+      <c r="K68" s="48" t="inlineStr">
         <is>
           <t>Spiritualisme</t>
         </is>
       </c>
-      <c r="L67" s="48" t="inlineStr">
+      <c r="L68" s="48" t="inlineStr">
         <is>
           <t>philosophe français qui chercha à réconcilier la foi et la raison au XXème.</t>
         </is>
       </c>
-      <c r="N67" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-    </row>
-    <row r="68" ht="217.5" customHeight="1" s="49">
-      <c r="A68" s="57" t="n">
+      <c r="N68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" ht="217.5" customHeight="1" s="49">
+      <c r="A69" s="57" t="n">
         <v>1903</v>
       </c>
-      <c r="B68" s="57" t="inlineStr">
+      <c r="B69" s="57" t="inlineStr">
         <is>
           <t>1978</t>
         </is>
       </c>
-      <c r="C68" s="57" t="inlineStr">
+      <c r="C69" s="57" t="inlineStr">
         <is>
           <t>1903 – 1978</t>
         </is>
       </c>
-      <c r="D68" s="58" t="inlineStr">
+      <c r="D69" s="58" t="inlineStr">
         <is>
           <t>Henry CORBIN</t>
         </is>
       </c>
-      <c r="E68" s="59" t="inlineStr">
+      <c r="E69" s="59" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Henry_Corbin"   title=" Wikipedia"&gt;Henry CORBIN&lt;/a&gt; était un philosophe, théologien, iranologue et &lt;a href="https://www.persee.fr/doc/rhpr_0035-2403_1979_num_59_2_4477" title=" Un missionnaire protestant par Persée"&gt;orientaliste français&lt;/a&gt; qui a profondément renouvelé la compréhension occidentale de la philosophie islamique, en particulier de ses courants chiites et &lt;a href="https://www.youtube.com/watch?v=1MKjvaSpu3s&amp;t=17s" style="color:#88A1E9" title=" Henry Corbin - L'Imagination créatrice dans le Soufisme d'Ibn Arabi par On the Top of Damavand for ever"&gt;soufis&lt;/a&gt;, ainsi que de la pensée iranienne. &lt;a href="https://www.persee.fr/doc/ephe_0000-0002_1978_num_91_87_15381"  title=" Henry Corbin par Persée"&gt;Son œuvre&lt;/a&gt; se caractérise par une quête philosophique personnelle, un "pèlerinage vers l'Orient des Lumières" quil a mis en lumière : &lt;/p&gt; &lt;p&gt;La philosophie illuminative de Sohrawardî : Il a joué un rôle crucial dans la &lt;a href="https://www.youtube.com/watch?v=LDRVfRaiS7I"  title=" Sohravardî, L’Archange empourpré, par Henry Corbin par Conscience Soufie"&gt;redécouverte de ce philosophe persan&lt;/a&gt;, fondateur de l'école de l'Illumination, qui combine la logique aristotélicienne avec une métaphysique de la lumière d'inspiration platonicienne et zoroastrienne. &lt;/p&gt; &lt;p&gt;Le concept du "monde imaginal" : Concepts centraux de sa pensée, il s'agit d'un monde intermédiaire, ontologiquement réel, entre le monde sensible et le monde purement intelligible, lieu des visions prophétiques, des événements de l'âme après la mort, et de l'imagination créatrice. Essentiel pour comprendre l'herméneutique spirituelle des textes sacrés. &lt;/p&gt; &lt;p&gt;L'importance de la gnose chiite et de l'ismaélisme : Il a profondément exploré les dimensions ésotériques du chiisme, notamment duodécimain et ismaélien, en mettant en avant des figures comme Haydar Amoli et en soulignant le rôle central de l'Imâm comme guide spirituel et manifestation du divin. &lt;/p&gt; &lt;p&gt;La philosophie prophétique et l'angélologie : Il a mis en évidence le rôle des prophètes et des anges dans la cosmologie islamiques, soulignant la continuité entre la philosophie et la révélation. &lt;/p&gt;  &lt;audio controls title="Henry Corbin raconté par Tom Cheetham par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/10073-06.12.2015-ITEMA_20857956-2015C6125E0167-21.mp3" type="audio/mpeg" align="center"&gt;&lt;/audio&gt;  </t>
         </is>
       </c>
-      <c r="F68" s="57" t="inlineStr">
+      <c r="F69" s="57" t="inlineStr">
         <is>
           <t>AeOiYf5CwwQ</t>
         </is>
       </c>
-      <c r="G68" s="59" t="inlineStr">
+      <c r="G69" s="59" t="inlineStr">
         <is>
           <t>"Dr. Henry Corbin | L'Imam investi d'une fonction cosmique" par Sciences &amp; Conscience</t>
         </is>
       </c>
-      <c r="H68" s="59" t="inlineStr">
+      <c r="H69" s="59" t="inlineStr">
         <is>
           <t>https://www.laphilo.fr/pho/corbin-mini.webp</t>
         </is>
       </c>
-      <c r="J68" s="48" t="inlineStr">
+      <c r="J69" s="48" t="inlineStr">
         <is>
           <t>spiritualite ; metaphysique</t>
         </is>
       </c>
-      <c r="K68" s="48" t="inlineStr">
+      <c r="K69" s="48" t="inlineStr">
         <is>
           <t xml:space="preserve">Ishraqisme ; Herméneutique ; Orientalisme</t>
         </is>
       </c>
-      <c r="L68" s="48" t="inlineStr">
+      <c r="L69" s="48" t="inlineStr">
         <is>
           <t>philosophe français qui renouvela la compréhension de la philosophie islamique.</t>
         </is>
       </c>
-      <c r="N68" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-    </row>
-    <row r="69" ht="225" customHeight="1" s="49">
-      <c r="A69" s="54" t="n">
+      <c r="N69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" ht="225" customHeight="1" s="49">
+      <c r="A70" s="54" t="n">
         <v>1903</v>
       </c>
-      <c r="B69" s="54" t="inlineStr">
+      <c r="B70" s="54" t="inlineStr">
         <is>
           <t>1944</t>
         </is>
       </c>
-      <c r="C69" s="54" t="inlineStr">
+      <c r="C70" s="54" t="inlineStr">
         <is>
           <t>1903 – 1944</t>
         </is>
       </c>
-      <c r="D69" s="55" t="inlineStr">
+      <c r="D70" s="55" t="inlineStr">
         <is>
           <t>Jean CAVAILLES</t>
         </is>
       </c>
-      <c r="E69" s="56" t="inlineStr">
+      <c r="E70" s="56" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Jean_Cavaill%C3%A8s"    title=" Wikipedia"&gt;Jean CAVAILLES&lt;/a&gt;  était un philosophe français des sciences et un des &lt;a href="https://cavailles.hypotheses.org/jean-cavailles/vie-de-jean-cavailles" title="Les Amis de Jean Cavaillès par Hypotheses"&gt;héros intellectuels &lt;/a&gt; de la Résistance, fusillé par les nazis à l’âge de quarante ans. Normalien et officier de réserve, il est marqué par l’effondrement de la République de Weimar, la montée du nazisme et les débats religieux et politiques de l’entre‑deux‑guerres. &lt;/p&gt; &lt;p&gt; Il se spécialise en &lt;a href="https://www.youtube.com/watch?v=zfr9wq-kYTo" style="color:#88A1E9" title="Sur la philosophie de Jean cavaillès par Hypotheses"&gt;philosophie des mathématiques &lt;/a&gt; et de la logique, en particulier sur l’histoire et la structure des théories axiomatiques. En 1938, il soutient sa grande thèse "Méthode axiomatique et formalisme", et une thèse complémentaire "Remarques sur la formation de la théorie abstraite des ensembles" qui étudient l’essor de la théorie des ensembles et la dynamique interne des mathématiques modernes. Pour lui, les mathématiques ne sont pas un système figé fondé sur des essences éternelles, mais un processus en devenir, structuré par des problèmes et des prolongements internes des théories. &lt;/p&gt; &lt;p&gt; Il critique l’idéalisme qui ramène les mathématiques à la conscience ou à des intuitions subjectives, et défend une "dialectique du concept" où les contenus mathématiques se transforment par couches successives, sans recours à un sujet fondateur. &lt;/p&gt; &lt;p&gt; Formé auprès de Léon Brunschvicg, il s’en détache en critiquant l’arrière‑plan idéaliste et en se rapprochant d’un spinozisme rationaliste et athée, inspiré par la rigueur de l’Éthique et son mos geometricus. &lt;a href="https://www.youtube.com/watch?v=2QYkjVoqsoI" style="color:#88A1E9" title="Philosophies - Héroïsme, Georges Ganguilhem et Jean Cavailles avec Blandine Kriegel par Radio J"&gt;Sa réflexion &lt;/a&gt; articule des influences venant de Frege et Bolzano (objectivité logique) et de Hegel et Husserl (dimension historique et intentionnelle), pour élaborer une logique "sans sujet", centrée sur les structures et leurs transformations. &lt;/p&gt; &lt;p&gt;  &lt;audio controls title="Jean Cavaillès, un philosophe dans la Résistance par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/13915-17.05.2025-ITEMA_24138144-2023C3372E0374-NET_MFC_35F98764-59B9-45DA-98A2-EC760D00C7A0-21-2cc2ee029f69376f6533a7a090eb6a3c.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;</t>
         </is>
       </c>
-      <c r="F69" s="54" t="inlineStr">
+      <c r="F70" s="54" t="inlineStr">
         <is>
           <t>xbVwzWdJgok</t>
         </is>
       </c>
-      <c r="G69" s="56" t="inlineStr">
+      <c r="G70" s="56" t="inlineStr">
         <is>
           <t>"Philosophie du combattant - Jean Cavaillès, mathématicien dynamiteur" par Monos</t>
         </is>
       </c>
-      <c r="H69" s="56" t="inlineStr">
+      <c r="H70" s="56" t="inlineStr">
         <is>
           <t>https://www.laphilo.fr/pho/cavailles-mini.webp</t>
         </is>
       </c>
-      <c r="J69" s="48" t="inlineStr">
+      <c r="J70" s="48" t="inlineStr">
         <is>
           <t>epistemologie ; logique</t>
         </is>
       </c>
-      <c r="K69" s="48" t="inlineStr">
+      <c r="K70" s="48" t="inlineStr">
         <is>
           <t>Rationalisme</t>
         </is>
       </c>
-      <c r="L69" s="48" t="inlineStr">
+      <c r="L70" s="48" t="inlineStr">
         <is>
           <t>philosophe français des mathématiques et héros intellectuel de la Résistance.</t>
         </is>
       </c>
-      <c r="N69" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-    </row>
-    <row r="70" ht="194.25" customHeight="1" s="49">
-      <c r="A70" s="57" t="n">
+      <c r="N70" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+    </row>
+    <row r="71" ht="194.25" customHeight="1" s="49">
+      <c r="A71" s="57" t="n">
         <v>1903</v>
       </c>
-      <c r="B70" s="57" t="inlineStr">
+      <c r="B71" s="57" t="inlineStr">
         <is>
           <t>1985</t>
         </is>
       </c>
-      <c r="C70" s="57" t="inlineStr">
+      <c r="C71" s="57" t="inlineStr">
         <is>
           <t>1903 – 1985</t>
         </is>
       </c>
-      <c r="D70" s="58" t="inlineStr">
+      <c r="D71" s="58" t="inlineStr">
         <is>
           <t>Vladimir JANKÉLÉVITCH</t>
         </is>
       </c>
-      <c r="E70" s="65" t="inlineStr">
+      <c r="E71" s="65" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Vladimir_Jank%C3%A9l%C3%A9vitch"   title=" Wikipedia"&gt;Vladimir JANKÉLÉVITCH&lt;/a&gt; était un philosophe français d'origine russe, influencé par Bergson, connu pour sa pensée originale &lt;a href="https://www.youtube.com/watch?v=498pItDm0vA" title=" Vladimir Jankélévitch : penser la morale, aimer le monde par Ina Culture"&gt;mêlant morale, &lt;/a&gt; temps, musique, souvent en marge des courants dominants. Il  cultive un style littéraire élégant, improvisé, centré sur l'expérience vécue, le cœur et l'ineffable, refusant les systèmes rigides. &lt;/p&gt; &lt;p&gt;  Pour lui, la morale prime sur tout : elle est hyperbolique, urgente, guidée par le cœur et l'instant de la décision, au-delà des devoirs rationnels ; elle rejoint la métaphysique.  Il conçoit &lt;a href="https://www.youtube.com/watch?v=G6hbXImCmJA" title="Vladimir Jankélévitch, penser la vie par LCP"&gt;la liberté &lt;/a&gt; comme dynamique, non statique  amenant à une prise de conscience en mouvement, vers un "au-delà de soi" ; l'homme libre agit authentiquement, sans dogmes. &lt;/p&gt; &lt;p&gt; &lt;a href="https://maitron.fr/jankelevitch-vladimir/" title=" Vladimir Jankélévitch par maitron.fr"&gt; Pour lui, &lt;/a&gt; la musique transcende l'esthétique pour devenir une expérience philosophique et métaphysique. Elle incarne l'irréversibilité du temps et l'instant fugace, reliant le sensible à l'intelligible sans jamais se réduire à une structure figée ou un algorithme. Elle exprime l'inexprimable : émotions, mystère de l'être, profondeur existentielle que le discours rationnel esquive. Le silence y joue un rôle clé, non comme absence, mais comme plénitude qui invite à l'introspection et à la transcendance. Il a consacré une douzaine d'ouvrages à la musique, comme Fauré et le Ineffable, Debussy et le Mystère ou Ravel, où philosophie et analyse musicale fusionnent en une prose poétique et improvisée.&lt;/p&gt; &lt;p&gt; Ses Œuvres majeures : -"Philosophie première" paru en 1954 : métaphysique vitaliste. Le &lt;a href="https://www.youtube.com/watch?v=KUUGJfgMoj0" title="Vladimir Jankélévitch en 1980, philosophe du Je-ne-sais-quoi et du Presque-rien? par Radio-Canada Archives"&gt;"Je-ne-sais-quoi et le Presque-rien" &lt;/a&gt; paru en 1957. "La Mort" paru en 1967 et  -"L'Irréversible et la Nostalgie" en 1974. &lt;/p&gt; 
    &lt;audio controls title="Avoir raison avec... Vladimir Jankélévitch par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/17362-07.08.2017-ITEMA_21402275-2017C35448E0026-NET_FC_4ECDB095-2595-41D4-AA28-F4A95CC22729-21.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;  </t>
         </is>
       </c>
-      <c r="F70" s="57" t="inlineStr">
+      <c r="F71" s="57" t="inlineStr">
         <is>
           <t>e-0PYNveM00</t>
         </is>
       </c>
-      <c r="G70" s="59" t="inlineStr">
+      <c r="G71" s="59" t="inlineStr">
         <is>
           <t>"Jankélévitch : la musique est "presque-rien" - Culture prime" par France Musique</t>
         </is>
       </c>
-      <c r="H70" s="59" t="inlineStr">
+      <c r="H71" s="59" t="inlineStr">
         <is>
           <t>https://www.laphilo.fr/pho/jankelevitch-mini.webp</t>
         </is>
       </c>
-      <c r="J70" s="48" t="inlineStr">
+      <c r="J71" s="48" t="inlineStr">
         <is>
           <t>ethique ; metaphysique</t>
         </is>
       </c>
-      <c r="K70" s="48" t="inlineStr">
+      <c r="K71" s="48" t="inlineStr">
         <is>
           <t>Existentialisme</t>
         </is>
       </c>
-      <c r="L70" s="48" t="inlineStr">
+      <c r="L71" s="48" t="inlineStr">
         <is>
           <t>philosophe &amp; musicologue français connu pour sa pensée mêlant morale, temps et musique.</t>
         </is>
       </c>
-      <c r="M70" t="inlineStr">
+      <c r="M71" t="inlineStr">
         <is>
           <t xml:space="preserve">juive</t>
         </is>
       </c>
-      <c r="N70" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-    </row>
-    <row r="71" ht="198" customHeight="1" s="49">
-      <c r="A71" s="57" t="n">
+      <c r="N71" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+    </row>
+    <row r="72" ht="198" customHeight="1" s="49">
+      <c r="A72" s="57" t="n">
         <v>1903</v>
       </c>
-      <c r="B71" s="57" t="n">
+      <c r="B72" s="57" t="n">
         <v>1942</v>
       </c>
-      <c r="C71" s="60" t="inlineStr">
+      <c r="C72" s="60" t="inlineStr">
         <is>
           <t>1903 – 1942</t>
         </is>
       </c>
-      <c r="D71" s="60" t="inlineStr">
+      <c r="D72" s="60" t="inlineStr">
         <is>
           <t>Georges POLITZER</t>
         </is>
       </c>
-      <c r="E71" s="61" t="inlineStr">
+      <c r="E72" s="61" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Georges_Politzer"  title=" Wikipedia"&gt;Georges POLITZER&lt;/a&gt; était un philosophe et militant communiste français d'origine hongroise, connu à la fois pour sa critique précoce de la psychologie universitaire et pour son engagement dans la Résistance qui lui coûta la vie. Né à Nagyvárad en Autriche-Hongrie, il arriva en France en 1921 et s'engagea rapidement dans le mouvement communiste. Professeur dans plusieurs lycées parisiens, il fut aussi l'un des principaux animateurs des Universités ouvrières fondées par le Parti communiste français. &lt;/p&gt; &lt;p&gt; Sa contribution philosophique principale est une critique radicale de la psychologie idéaliste et introspective dans &lt;em&gt;Critique des fondements de la psychologie&lt;/em&gt; (1928). Plaidant pour une  &lt;a href="https://www.youtube.com/watch?v=XHo2z8xTIgA"  title="la psychologie concrète par tropics television"&gt;« psychologie concrète » &lt;/a&gt; fondée sur l'étude des comportements réels des êtres humains dans leurs situations historiques concrètes, il anticipe certains thèmes du béhaviorisme et de la psychologie sociale, tout en restant dans une perspective matérialiste marxiste. Cette œuvre, originale et polémique, fit sensation dans les milieux philosophiques de l'époque. &lt;/p&gt; &lt;p&gt; Ses &lt;em&gt;Principes élémentaires de philosophie&lt;/em&gt;, cours donnés dans le cadre des universités ouvrières et publiés posthumément, constituent longtemps le manuel le plus diffusé d'introduction au matérialisme dialectique dans les milieux ouvriers et militants français. Arrêté par la Gestapo en 1942, il fut torturé et fusillé au Mont-Valérien le 23 mai 1942, en même temps que son ami le physicien Jacques Solomon. Sa mort symbolise le sacrifice de nombreux  &lt;a href="https://www.youtube.com/watch?v=QV4VvYOU4xU"  title="hommage  du PRCF à Politzer par PRCF"&gt;intellectuels communistes &lt;/a&gt;  dans la Résistance française. Il reste un personnage emblématique de l'engagement philosophique au service de l'émancipation ouvrière. &lt;/p&gt; &lt;audio controls title=Vie et destin de Georges Politzer par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/10467-04.06.2013-ITEMA_20487057-2013C12410E0158-NET_FC_BA6CA596-C63D-4530-800E-B3E0D71E7027-21.mp3" type="audio/mpeg" align="center"&gt;&lt;/audio&gt;  </t>
         </is>
       </c>
-      <c r="F71" s="60" t="inlineStr">
+      <c r="F72" s="60" t="inlineStr">
         <is>
           <t>wXAW8KsabAA</t>
         </is>
       </c>
-      <c r="G71" s="66" t="inlineStr">
+      <c r="G72" s="66" t="inlineStr">
         <is>
           <t xml:space="preserve">
 La méthode Politzer par Pages Rouges</t>
         </is>
       </c>
-      <c r="H71" s="61" t="inlineStr">
+      <c r="H72" s="61" t="inlineStr">
         <is>
           <t>https://www.laphilo.fr/pho/politzer-mini.webp</t>
         </is>
       </c>
-      <c r="J71" s="48" t="inlineStr">
+      <c r="J72" s="48" t="inlineStr">
         <is>
           <t>politique ; epistemologie</t>
         </is>
       </c>
-      <c r="K71" s="48" t="inlineStr">
+      <c r="K72" s="48" t="inlineStr">
         <is>
           <t>Marxisme ; Béhaviorisme</t>
         </is>
       </c>
-      <c r="L71" s="48" t="inlineStr">
+      <c r="L72" s="48" t="inlineStr">
         <is>
           <t>philosophe français communiste connu pour sa critique précoce de la psychologie universitaire.</t>
         </is>
       </c>
-      <c r="M71" t="inlineStr">
+      <c r="M72" t="inlineStr">
         <is>
           <t xml:space="preserve">juive</t>
         </is>
       </c>
-      <c r="N71" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-    </row>
-    <row r="72" ht="192" customHeight="1" s="49">
-      <c r="A72" s="54" t="n">
+      <c r="N72" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+    </row>
+    <row r="73" ht="192" customHeight="1" s="49">
+      <c r="A73" s="54" t="n">
         <v>1904</v>
       </c>
-      <c r="B72" s="54" t="inlineStr">
+      <c r="B73" s="54" t="inlineStr">
         <is>
           <t>1995</t>
         </is>
       </c>
-      <c r="C72" s="54" t="inlineStr">
+      <c r="C73" s="54" t="inlineStr">
         <is>
           <t>1904 – 1995</t>
         </is>
       </c>
-      <c r="D72" s="55" t="inlineStr">
+      <c r="D73" s="55" t="inlineStr">
         <is>
           <t>Georges CANGUILHEM</t>
         </is>
       </c>
-      <c r="E72" s="56" t="inlineStr">
+      <c r="E73" s="56" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Georges_Canguilhem"  title=" Wikipedia"&gt;Georges CANGUILHEM&lt;/a&gt; était un philosophe français,   historien des sciences et résistant, connu pour ses travaux en   &lt;a href="https://www.youtube.com/watch?v=SKBNSabxhUA"  title="
 Philosophie et sciences - Interview de Canguilhem par Badiou par Normezmoi"&gt;épistémologie des sciences &lt;/a&gt; du vivant. Normalien agrégé de philosophie et docteur en médecine sans exercer, il succéda à Gaston Bachelard à la direction de l'IHPST et influença profondément Foucault et Bourdieu. Élève de l'ENS avec Sartre et Nizan, il enseigna la philosophie avant de rejoindre la Résistance en 1940 sous le pseudonyme Lafont. &lt;/p&gt; &lt;p&gt; Il  refuse la réduction physico-chimique ou mécaniste de la vie, défendant sa spécificité organique et normative contre le scientisme. Dans "Le Normal et le Pathologique" paru en 1943, il montre que le pathologique n'est pas une simple négation quantitative du normal, mais une altération qualitative de la vie, rendant la norme contextuelle et historique. &lt;/p&gt; &lt;p&gt; Son historicisme épistémologique, nourri de Cavaillès et Marx, analyse les ruptures scientifiques comme des réponses vitales aux obstacles, valorisant une connaissance active et créatrice plutôt que positiviste. &lt;a href="https://www.persee.fr/doc/phlou_0035-3841_1966_num_64_82_5347"  title="Georges Canguilhem, La connaissance de la vie  par persée"&gt;"La Connaissance de la vie" &lt;/a&gt; paru en 1952 critique le réductionnisme biologique, affirmant que la vie excède les mécanismes pour inclure l'action et l'environnement. Pour lui, être en bonne santé, ce n’est pas seulement être conforme à une moyenne : c’est pouvoir créer de nouvelles normes de vie et faire face aux changements du milieu, alors que la maladie réduit cette capacité. Il a renouvelé l’histoire des sciences en étudiant la formation des concepts. Il a dirigé la thèse de Michel Foucault sur l’histoire de la folie et marqué toute une génération de philosophes. &lt;/p&gt;   &lt;audio controls title="Georges Canguilhem par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/10200-07.09.2006-ITEMA_20037357-2006C10589S0002-MEM_000030679_RF-21.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;  </t>
         </is>
       </c>
-      <c r="F72" s="54" t="inlineStr">
+      <c r="F73" s="54" t="inlineStr">
         <is>
           <t>BnFHd5azTmc</t>
         </is>
       </c>
-      <c r="G72" s="56" t="inlineStr">
+      <c r="G73" s="56" t="inlineStr">
         <is>
           <t>"
 Entretien de Georges Canguilhem avec François Dagognet sur le vivant" par NormezMoi</t>
         </is>
       </c>
-      <c r="H72" s="56" t="inlineStr">
+      <c r="H73" s="56" t="inlineStr">
         <is>
           <t>https://www.laphilo.fr/pho/canguilhem-mini.webp</t>
         </is>
       </c>
-      <c r="J72" s="48" t="inlineStr">
+      <c r="J73" s="48" t="inlineStr">
         <is>
           <t>epistemologie</t>
         </is>
       </c>
-      <c r="K72" s="48" t="inlineStr">
+      <c r="K73" s="48" t="inlineStr">
         <is>
           <t xml:space="preserve">Rationalisme</t>
         </is>
       </c>
-      <c r="L72" s="48" t="inlineStr">
+      <c r="L73" s="48" t="inlineStr">
         <is>
           <t>philosophe &amp; résistant français épistémologiste des sciences du vivant.</t>
         </is>
       </c>
-      <c r="N72" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-    </row>
-    <row r="73" ht="182.25" customHeight="1" s="49">
-      <c r="A73" s="57" t="n">
+      <c r="N73" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+    </row>
+    <row r="74" ht="182.25" customHeight="1" s="49">
+      <c r="A74" s="57" t="n">
         <v>1905</v>
       </c>
-      <c r="B73" s="57" t="inlineStr">
+      <c r="B74" s="57" t="inlineStr">
         <is>
           <t>1980</t>
         </is>
       </c>
-      <c r="C73" s="57" t="inlineStr">
+      <c r="C74" s="57" t="inlineStr">
         <is>
           <t>1905 - 1980</t>
         </is>
       </c>
-      <c r="D73" s="58" t="inlineStr">
+      <c r="D74" s="58" t="inlineStr">
         <is>
           <t>Jean Paul SARTRE</t>
         </is>
       </c>
-      <c r="E73" s="59" t="inlineStr">
+      <c r="E74" s="59" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Jean-Paul_Sartre"   title=" Wikipedia"&gt;Jean-Paul SARTRE&lt;/a&gt; (1905-1980) est un philosophe, romancier et dramaturge français, la grande figure de l’&lt;a href="https://www.youtube.com/watch?v=kX3saEPOG-g&amp;t=51s&amp;ab_channel=Coursitout" title="Nous sommes condamnés à être libre par Yapi Florent AKICHI"&gt;existentialisme&lt;/a&gt;. Normalien, agrégé de philosophie en 1929, il découvre la phénoménologie de Husserl à Berlin en 1933, puis publie &lt;em&gt;La Nausée&lt;/em&gt; (1938), roman de l’absurdité d’exister. Prisonnier de guerre en 1940, il fait paraître en 1943 son grand traité, &lt;em&gt;L’Être et le Néant&lt;/em&gt;.&lt;/p&gt; &lt;p&gt;Pour Sartre, chez l’homme, « l’existence précède l’essence » : il n’y a pas de nature humaine fixée d’avance, chacun se définit par ses actes. La conscience n’est pas une chose, mais un néant, une ouverture qui ne coïncide jamais avec elle-même. L’homme est donc &lt;a href="https://www.youtube.com/watch?v=xN0ysLkGiP8&amp;ab_channel=LePr%C3%A9cepteur"   title="Nous sommes condamnés à être libre par le Précepteur"&gt;libre&lt;/a&gt;, et même « condamné à être libre » : il ne peut pas ne pas choisir, et il est responsable de ce qu’il fait de lui-même. Beaucoup fuient cette angoisse dans la « mauvaise foi », comme le garçon de café qui joue à être garçon de café pour se donner l’existence d’une chose. Sous &lt;a href="https://www.youtube.com/watch?v=BJIM41TnDHI&amp;ab_channel=LePr%C3%A9cepteur"  title="Le regard des autres par le Précepteur"&gt;le regard d’autrui&lt;/a&gt;, je deviens un objet, figé dans une image que je ne maîtrise pas, d’où la réplique de &lt;em&gt;Huis clos&lt;/em&gt; (1944) : « l’enfer, c’est les autres ». Après la guerre, Sartre fonde la revue &lt;em&gt;Les Temps modernes&lt;/em&gt; et défend l’engagement de l’écrivain. Il se rapproche du marxisme, qu’il veut concilier avec la liberté dans la &lt;em&gt;Critique de la raison dialectique&lt;/em&gt; (1960), et prend parti dans les luttes de son temps, contre la guerre d’Algérie, puis en Mai 68.&lt;/p&gt; &lt;p&gt;En 1964, il refuse le prix Nobel de littérature. Il partage sa vie avec Simone de Beauvoir dans une &lt;a href="https://www.youtube.com/watch?v=5BCjCYimqlc&amp;ab_channel=LePr%C3%A9cepteur"  title="L'amour par le Précepteur"&gt;relation libre&lt;/a&gt;, et ses funérailles, en 1980, rassemblent des dizaines de milliers de personnes.&lt;/p&gt;  &lt;audio controls title="Le roman comme expérience par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/22054-28.03.2021-ITEMA_22624288-2017C24632S0115.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;</t>
         </is>
       </c>
-      <c r="F73" s="57" t="inlineStr">
+      <c r="F74" s="57" t="inlineStr">
         <is>
           <t>3bQsZxDQgzU</t>
         </is>
       </c>
-      <c r="G73" s="59" t="inlineStr">
+      <c r="G74" s="59" t="inlineStr">
         <is>
           <t xml:space="preserve">Sartre par The School of Life</t>
         </is>
       </c>
-      <c r="H73" s="59" t="inlineStr">
+      <c r="H74" s="59" t="inlineStr">
         <is>
           <t>https://www.laphilo.fr/pho/sartre-mini.webp</t>
         </is>
       </c>
-      <c r="J73" s="48" t="inlineStr">
+      <c r="J74" s="48" t="inlineStr">
         <is>
           <t>metaphysique ; politique</t>
         </is>
       </c>
-      <c r="K73" s="48" t="inlineStr">
+      <c r="K74" s="48" t="inlineStr">
         <is>
           <t xml:space="preserve">Existentialisme ; Marxisme ; Athéisme ; Absurde</t>
         </is>
       </c>
-      <c r="L73" s="48" t="inlineStr">
+      <c r="L74" s="48" t="inlineStr">
         <is>
           <t>philosophe français qui développa la théorie de l'Existentialisme.</t>
         </is>
       </c>
-      <c r="N73" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-      <c r="O73">
+      <c r="N74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+      <c r="O74">
         <v>3</v>
       </c>
     </row>
-    <row r="74" ht="212.25" customHeight="1" s="49">
-      <c r="A74" s="54" t="n">
-        <v>1905</v>
-      </c>
-      <c r="B74" s="54" t="inlineStr">
-        <is>
-          <t>1983</t>
-        </is>
-      </c>
-      <c r="C74" s="54" t="inlineStr">
-        <is>
-          <t>1905 – 1983</t>
-        </is>
-      </c>
-      <c r="D74" s="55" t="inlineStr">
-        <is>
-          <t>Raymond ARON</t>
-        </is>
-      </c>
-      <c r="E74" s="56" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Raymond_Aron"  title=" Wikipedia"&gt;Raymond ARON&lt;/a&gt;  était un philosophe français, à la fois sociologue, politologue et journaliste, surtout connu comme grand représentant du libéralisme politique face aux totalitarismes. Agrégé de philosophie en 1928, il part à Berlin au début des années 1930, y observe la montée du nazisme, expérience décisive pour sa réflexion sur le régime. &lt;/p&gt; &lt;p&gt; Il développe un libéralisme qu’il qualifie lui‑même de &lt;a href="https://www.youtube.com/watch?v=I3briDR0HoM"  title="Raymond Aron : un philosophe face à Mai 68 et à la société industrielle par Ina Culture"&gt;"modérément immodéré": &lt;/a&gt; défense de la démocratie représentative, de l’économie mixte, refus des utopies révolutionnaires et des idéologies fermées. Il se veut réaliste: sa philosophie politique et sa sociologie s’ancrent dans &lt;a href="https://www.youtube.com/watch?v=WI4IeZq5JGo" title=" Raymond Aron - La société industrielle et la guerre par Artequieu"&gt;l’étude concrète &lt;/a&gt; des régimes, des conflits, de l’histoire, plutôt que dans de grands systèmes spéculatifs. &lt;/p&gt; &lt;p&gt; Ses oeuvres majeures : "L’Opium des intellectuels" paru en1955, critique la fascination d’une partie des intellectuels français pour le marxisme et les régimes communistes, en inversant la formule de Marx sur la religion: pour lui, le marxisme est "l’opium des intellectuels". "Paix et guerre entre les nations" paru en 1962 est un ouvrage clé de théorie des relations internationales, où il analyse le jeu des puissances, la logique des États et la coexistence entre guerre et paix dans le système international. &lt;/p&gt; &lt;p&gt; Longtemps isolé dans un paysage intellectuel dominé par la gauche sartrienne, il incarne une figure de l’intellectuel "anti‑idéologue", attaché à la rigueur empirique et à la prudence politique. Sa confrontation avec Sartre symbolise en France l’opposition entre un existentialisme révolutionnaire et un libéralisme réaliste soucieux des limites de l’action politique.  &lt;/p&gt; &lt;p&gt;Il  laisse une œuvre de référence en philosophie politique libérale, en sociologie de la modernité et en relations internationales, et il a formé ou influencé de nombreux chercheurs et éditorialistes. &lt;/p&gt;  &lt;audio controls title="Raymond Aron, penseur du 21e siècle ? par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/19489-13.04.2025-ITEMA_24101720-2025C33085S0103-NET_MFC_6A5A935A-A263-404D-BA44-E5609DCE1A79-21.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;</t>
-        </is>
-      </c>
-      <c r="F74" s="54" t="inlineStr">
-        <is>
-          <t>gkEsjYGsGM0</t>
-        </is>
-      </c>
-      <c r="G74" s="56" t="inlineStr">
-        <is>
-          <t>"Entrevue en 1979 avec Raymond Aron, philosophe et sociologue français" par Radio-Canada Archives</t>
-        </is>
-      </c>
-      <c r="H74" s="56" t="inlineStr">
-        <is>
-          <t>https://www.laphilo.fr/pho/aron-mini.webp</t>
-        </is>
-      </c>
-      <c r="J74" s="48" t="inlineStr">
-        <is>
-          <t>politique ; epistemologie</t>
-        </is>
-      </c>
-      <c r="K74" s="48" t="inlineStr">
-        <is>
-          <t>Libéralisme</t>
-        </is>
-      </c>
-      <c r="L74" s="48" t="inlineStr">
-        <is>
-          <t>philosophe français représentant du libéralisme politique face aux totalitarismes.</t>
-        </is>
-      </c>
-      <c r="M74" t="inlineStr">
-        <is>
-          <t xml:space="preserve">juive</t>
-        </is>
-      </c>
-      <c r="N74" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-    </row>
-    <row r="75" ht="251.25" customHeight="1" s="49">
+    <row r="75" ht="212.25" customHeight="1" s="49">
       <c r="A75" s="54" t="n">
         <v>1905</v>
       </c>
-      <c r="B75" s="54" t="n">
+      <c r="B75" s="54" t="inlineStr">
+        <is>
+          <t>1983</t>
+        </is>
+      </c>
+      <c r="C75" s="54" t="inlineStr">
+        <is>
+          <t>1905 – 1983</t>
+        </is>
+      </c>
+      <c r="D75" s="55" t="inlineStr">
+        <is>
+          <t>Raymond ARON</t>
+        </is>
+      </c>
+      <c r="E75" s="56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Raymond_Aron"  title=" Wikipedia"&gt;Raymond ARON&lt;/a&gt;  était un philosophe français, à la fois sociologue, politologue et journaliste, surtout connu comme grand représentant du libéralisme politique face aux totalitarismes. Agrégé de philosophie en 1928, il part à Berlin au début des années 1930, y observe la montée du nazisme, expérience décisive pour sa réflexion sur le régime. &lt;/p&gt; &lt;p&gt; Il développe un libéralisme qu’il qualifie lui‑même de &lt;a href="https://www.youtube.com/watch?v=I3briDR0HoM"  title="Raymond Aron : un philosophe face à Mai 68 et à la société industrielle par Ina Culture"&gt;"modérément immodéré": &lt;/a&gt; défense de la démocratie représentative, de l’économie mixte, refus des utopies révolutionnaires et des idéologies fermées. Il se veut réaliste: sa philosophie politique et sa sociologie s’ancrent dans &lt;a href="https://www.youtube.com/watch?v=WI4IeZq5JGo" title=" Raymond Aron - La société industrielle et la guerre par Artequieu"&gt;l’étude concrète &lt;/a&gt; des régimes, des conflits, de l’histoire, plutôt que dans de grands systèmes spéculatifs. &lt;/p&gt; &lt;p&gt; Ses oeuvres majeures : "L’Opium des intellectuels" paru en1955, critique la fascination d’une partie des intellectuels français pour le marxisme et les régimes communistes, en inversant la formule de Marx sur la religion: pour lui, le marxisme est "l’opium des intellectuels". "Paix et guerre entre les nations" paru en 1962 est un ouvrage clé de théorie des relations internationales, où il analyse le jeu des puissances, la logique des États et la coexistence entre guerre et paix dans le système international. &lt;/p&gt; &lt;p&gt; Longtemps isolé dans un paysage intellectuel dominé par la gauche sartrienne, il incarne une figure de l’intellectuel "anti‑idéologue", attaché à la rigueur empirique et à la prudence politique. Sa confrontation avec Sartre symbolise en France l’opposition entre un existentialisme révolutionnaire et un libéralisme réaliste soucieux des limites de l’action politique.  &lt;/p&gt; &lt;p&gt;Il  laisse une œuvre de référence en philosophie politique libérale, en sociologie de la modernité et en relations internationales, et il a formé ou influencé de nombreux chercheurs et éditorialistes. &lt;/p&gt;  &lt;audio controls title="Raymond Aron, penseur du 21e siècle ? par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/19489-13.04.2025-ITEMA_24101720-2025C33085S0103-NET_MFC_6A5A935A-A263-404D-BA44-E5609DCE1A79-21.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;</t>
+        </is>
+      </c>
+      <c r="F75" s="54" t="inlineStr">
+        <is>
+          <t>gkEsjYGsGM0</t>
+        </is>
+      </c>
+      <c r="G75" s="56" t="inlineStr">
+        <is>
+          <t>"Entrevue en 1979 avec Raymond Aron, philosophe et sociologue français" par Radio-Canada Archives</t>
+        </is>
+      </c>
+      <c r="H75" s="56" t="inlineStr">
+        <is>
+          <t>https://www.laphilo.fr/pho/aron-mini.webp</t>
+        </is>
+      </c>
+      <c r="J75" s="48" t="inlineStr">
+        <is>
+          <t>politique ; epistemologie</t>
+        </is>
+      </c>
+      <c r="K75" s="48" t="inlineStr">
+        <is>
+          <t>Libéralisme</t>
+        </is>
+      </c>
+      <c r="L75" s="48" t="inlineStr">
+        <is>
+          <t>philosophe français représentant du libéralisme politique face aux totalitarismes.</t>
+        </is>
+      </c>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t xml:space="preserve">juive</t>
+        </is>
+      </c>
+      <c r="N75" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+    </row>
+    <row r="76" ht="251.25" customHeight="1" s="49">
+      <c r="A76" s="54" t="n">
+        <v>1905</v>
+      </c>
+      <c r="B76" s="54" t="n">
         <v>1950</v>
       </c>
-      <c r="C75" s="54" t="inlineStr">
+      <c r="C76" s="54" t="inlineStr">
         <is>
           <t>1905 – 1950</t>
         </is>
       </c>
-      <c r="D75" s="55" t="inlineStr">
+      <c r="D76" s="55" t="inlineStr">
         <is>
           <t>Emmanuel MOUNIER</t>
         </is>
       </c>
-      <c r="E75" s="75" t="inlineStr">
+      <c r="E76" s="75" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Emmanuel_Mounier"  title=" Wikipedia"&gt;Emmanuel MOUNIER&lt;/a&gt; était un philosophe français connu comme le fondateur du personnalisme, un courant qui veut remettre la personne humaine au centre de la pensée et de la vie sociale. &lt;/p&gt; &lt;p&gt; Sa philosophie naît dans un contexte de crise : montée du capitalisme, du fascisme, du marxisme et sentiment que l’homme est écrasé par des systèmes trop abstraits. Il refuse à la fois l’individualisme, qui isole l’être humain, et le collectivisme, qui le dissout dans le groupe. &lt;/p&gt; &lt;p&gt; Pour lui, la personne n’est pas seulement un individu biologique ou social.  &lt;a href="https://www.youtube.com/watch?v=T8tZ7E0D49k"  title="emmanuel mounier par kto tv"&gt;"C’est un être libre, &lt;/a&gt; responsable, ouvert aux autres et appelé à se construire dans l’engagement, la relation et la vie communautaire. Cette idée donne à sa pensée une dimension à la fois morale, politique et spirituelle. &lt;/p&gt; &lt;p&gt; Il est aussi profondément chrétien, mais un chrétien engagé dans le monde. Avec  &lt;a href="https://maitron.fr/mounier-emmanuel-hippolyte-henri/"  title="emmanuel mounier par maitron"&gt;la revue Esprit, &lt;/a&gt; qu’il fonde en 1932, il cherche à faire dialoguer la foi, la réflexion philosophique et les grands problèmes de son époque, comme la guerre, la démocratie ou la justice sociale. Il défend une forme de « révolution spirituelle », c’est-à-dire une transformation intérieure et sociale de l’homme et des institutions. &lt;/p&gt; &lt;p&gt; La philosophie de Mounier propose une vision exigeante de l’humain : la personne doit être respectée dans sa dignité, sa liberté et sa vocation relationnelle. Son influence a été importante sur la pensée chrétienne, la philosophie sociale et les débats sur la démocratie au XXe siècle. &lt;/p&gt; &lt;audio controls title="Les murs blancs revue esprit par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/17473-14.03.2021-ITEMA_22602800-2021B20595S0073.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt; 
 </t>
         </is>
       </c>
-      <c r="F75" s="54" t="inlineStr">
+      <c r="F76" s="54" t="inlineStr">
         <is>
           <t>pGarT6jKqv8</t>
         </is>
       </c>
-      <c r="G75" s="56" t="inlineStr">
+      <c r="G76" s="56" t="inlineStr">
         <is>
           <t xml:space="preserve">emmanuel mounier par Regards protestants</t>
         </is>
       </c>
-      <c r="H75" s="62" t="inlineStr">
+      <c r="H76" s="62" t="inlineStr">
         <is>
           <t>https://www.laphilo.fr/pho/emounier-mini.webp</t>
         </is>
       </c>
-      <c r="J75" s="48" t="inlineStr">
+      <c r="J76" s="48" t="inlineStr">
         <is>
           <t>politique</t>
         </is>
       </c>
-      <c r="K75" s="48" t="inlineStr">
+      <c r="K76" s="48" t="inlineStr">
         <is>
           <t>Personnalisme</t>
         </is>
       </c>
-      <c r="L75" s="85" t="inlineStr">
+      <c r="L76" s="85" t="inlineStr">
         <is>
           <t>philosophe français connu comme le fondateur du personnalisme.</t>
         </is>
       </c>
-      <c r="N75" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-    </row>
-    <row r="76" ht="217.5" customHeight="1" s="49">
-      <c r="A76" s="57" t="n">
+      <c r="N76" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+    </row>
+    <row r="77" ht="217.5" customHeight="1" s="49">
+      <c r="A77" s="57" t="n">
         <v>1906</v>
       </c>
-      <c r="B76" s="57" t="inlineStr">
+      <c r="B77" s="57" t="inlineStr">
         <is>
           <t>1995</t>
         </is>
       </c>
-      <c r="C76" s="57" t="inlineStr">
+      <c r="C77" s="57" t="inlineStr">
         <is>
           <t>1906 – 1995</t>
         </is>
       </c>
-      <c r="D76" s="58" t="inlineStr">
+      <c r="D77" s="58" t="inlineStr">
         <is>
           <t>Emmanuel LEVINAS</t>
         </is>
       </c>
-      <c r="E76" s="59" t="inlineStr">
+      <c r="E77" s="59" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Emmanuel_Levinas"  title=" Wikipedia"&gt;Emmanuel LEVINAS&lt;/a&gt; était un  philosophe français d'origine Lituanienne dont la pensée a profondément renouvelé la philosophie du XXᵉ siècle en plaçant l’éthique au cœur de la métaphysique. Il rompt avec la tradition occidentale qui faisait de l’ontologie (la science de l’être) la «philosophie première». Pour lui, c’est &lt;a href="https://www.youtube.com/watch?v=xTeGpHz6tWo" style="color:#88A1E9" title=" Emmanuel Lévinas - L'éthique du visage par La Piquire de Socrate"&gt;l’éthique&lt;/a&gt; qui doit être fondement de toute philosophie. L’humain n’est pas défini d’abord par son être ou sa conscience, mais par sa responsabilité infinie envers autrui. Il écrit que «le sujet est structuré comme autre dans le même» : autrui n’est jamais totalement réductible à moi, mais m’oblige moralement dès que je le rencontre. &lt;/p&gt; &lt;p&gt; Son concept central est celui &lt;a href="https://www.youtube.com/watch?v=1WO-UpY0Gm0" title=" Le Visage chez Emmanuel Lévinas par L'Acropole"&gt;du visage&lt;/a&gt; (le visage d’autrui), développé notamment dans "Totalité et infini" (1961). Le visage n’est pas ici un ensemble de traits physiques ; il est la présence de l’autre comme vulnérable et inviolable. Devant ce visage, je ressens l’injonction silencieuse : «Tu ne tueras point». &lt;a href="https://www.youtube.com/watch?v=KLA_RvU7yC0" title=" Emmanuel Lévinas – La responsabilité pour autrui par Andrea Cirla"&gt;Autrui me convoque&lt;/a&gt;, m’impose une responsabilité qui ne vient pas d’une loi rationnelle, mais du simple fait de sa présence. Ainsi, il s’éloigne du théocentrisme : Dieu n’est plus l’objet d’un savoir, mais la trace de ce qui m’oblige, visible dans la souveraineté du visage. &lt;/p&gt; &lt;p&gt; Il reconnaît que la pure éthique du face-à-face doit se penser dans la société concrète. Quand un &lt;a href="https://leverbe.com/articles/idees/lautre-est-un-exil-breve-introduction-a-la-pensee-demmanuel-levinas" title="L’autre est un exil : brève introduction à la pensée d’Emmanuel Levinas par LeVerbe"&gt;tiers apparaît&lt;/a&gt; — un autre "autre" —, apparaît la nécessité de justice : comment être juste entre plusieurs ? C’est dans ce passage que l’éthique se prolonge en politique et en droit, sans jamais perdre la priorité de la responsabilité individuelle envers autrui.  La philosophie lévinassienne affirme que la transcendance n’est pas dans un au-delà abstrait, mais dans le rapport humain lui-même. L’humain accomplit sa véritable essence en répondant à autrui, dans la paix et la non-violence. &lt;/p&gt; 
 &lt;audio controls title=" Emmanuel Levinas, le judaïsme et la philosophie par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/13397-04.01.2025-ITEMA_23984657-2025C3397E0001-21.mp3" type="audio/mpeg" align="center"&gt;&lt;/audio&gt;  </t>
         </is>
       </c>
-      <c r="F76" s="57" t="inlineStr">
+      <c r="F77" s="57" t="inlineStr">
         <is>
           <t>kXIMsLzaAVo</t>
         </is>
       </c>
-      <c r="G76" s="59" t="inlineStr">
+      <c r="G77" s="59" t="inlineStr">
         <is>
           <t>"Entrevue en 1981 avec Emmanuel Levinas philosophe" par Radio-Canada Archives</t>
         </is>
       </c>
-      <c r="H76" s="59" t="inlineStr">
+      <c r="H77" s="59" t="inlineStr">
         <is>
           <t>https://www.laphilo.fr/pho/levinas-mini.webp</t>
         </is>
       </c>
-      <c r="J76" s="48" t="inlineStr">
+      <c r="J77" s="48" t="inlineStr">
         <is>
           <t>ethique ; metaphysique</t>
         </is>
       </c>
-      <c r="K76" s="48" t="inlineStr">
+      <c r="K77" s="48" t="inlineStr">
         <is>
           <t>Phénoménologie ; Herméneutique</t>
         </is>
       </c>
-      <c r="L76" s="48" t="inlineStr">
+      <c r="L77" s="48" t="inlineStr">
         <is>
           <t>philosophe français centré sur la question éthique et métaphysique d'autrui.</t>
         </is>
       </c>
-      <c r="M76" t="inlineStr">
+      <c r="M77" t="inlineStr">
         <is>
           <t xml:space="preserve">juive</t>
         </is>
       </c>
-      <c r="N76" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-      <c r="O76">
+      <c r="N77" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+      <c r="O77">
         <v>3</v>
       </c>
     </row>
-    <row r="77" ht="132.75" customHeight="1" s="49">
-      <c r="A77" s="54" t="n">
+    <row r="78" ht="132.75" customHeight="1" s="49">
+      <c r="A78" s="54" t="n">
         <v>1906</v>
       </c>
-      <c r="B77" s="54" t="inlineStr">
+      <c r="B78" s="54" t="inlineStr">
         <is>
           <t>2006</t>
         </is>
       </c>
-      <c r="C77" s="54" t="inlineStr">
+      <c r="C78" s="54" t="inlineStr">
         <is>
           <t>1906 – 2006</t>
         </is>
       </c>
-      <c r="D77" s="55" t="inlineStr">
+      <c r="D78" s="55" t="inlineStr">
         <is>
           <t>Maurice de GANDILLAC</t>
         </is>
       </c>
-      <c r="E77" s="56" t="inlineStr">
+      <c r="E78" s="56" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Maurice_de_Gandillac"  title=" Wikipedia"&gt;Maurice de GANDILLAC&lt;/a&gt;  était un philosophe français spécialiste de la pensée médiévale et de la Renaissance, connu pour son ouverture d'esprit et son &lt;a href="https://www.youtube.com/watch?v=wMU50jMSLdo"  title=" Maurice de Gandillac et les décades de Pontigny (1926-1938) par adriano meis"&gt;rôle de passeur &lt;/a&gt; entre traditions philosophiques. Professeur à la Sorbonne pendant trois décennies, il a influencé des générations d'étudiants et traduit des auteurs majeurs comme Nicolas de Cues, Walter Benjamin et Nietzsche. Catholique initialement proche de Maritain et Mounier, il s'engage dans des revues comme Esprit et Dieu vivant, et préside les rencontres de Cerisy de 1954 à 1999. &lt;/p&gt; &lt;p&gt;  Sa thèse de 1941 (La Philosophie de Nicolas de Cues) et de multiples traductions (dont De docta ignorantia) en font l'un des principaux introducteurs du Cusain en France, explorant l'infini, la "docte ignorance" et l'unité des contraires. Premier à traduire Walter Benjamin en français, ainsi que Novalis, Hegel, Nietzsche (avec Deleuze), Ernst Bloch et Dante (Divine Comédie). &lt;/p&gt; &lt;p&gt; Il incarne un &lt;a href="https://www.persee.fr/doc/homso_0018-4306_1999_num_131_1_3626"  title="Maurice de Gandillac, Le siècle traversé. Souvenirs de neuf décennies, Paris, Albin Michel, 1998 par Persée"&gt;humanisme érudit&lt;/a&gt;, liant Moyen Âge, Renaissance et modernité, avec un souci des silences et opacités de la pensée face à l'indicible. Son œuvre, mêlant histoire philosophique, poésie (Bestiaire latéral, 1974) et dialogues interdisciplinaires, reste une référence pour l'étude des marges de la rationalité. Né en Algérie en 1906, normalien, il a enseigné à la Sorbonne de 1946 à 1977, où il a dirigé ou accompagné les travaux de nombreux philosophes, de Gilles Deleuze à Jacques Derrida. Il a raconté ce parcours dans &lt;em&gt;Le Siècle traversé&lt;/em&gt; (1998). Mort en 2006 à près de cent ans, il reste le modèle d’un philosophe généreux et curieux de tout. &lt;/p&gt;</t>
         </is>
       </c>
-      <c r="F77" s="54" t="inlineStr">
+      <c r="F78" s="54" t="inlineStr">
         <is>
           <t>wMU50jMSLdo</t>
         </is>
       </c>
-      <c r="G77" s="56" t="inlineStr">
+      <c r="G78" s="56" t="inlineStr">
         <is>
           <t>"Maurice de Gandillac et les décades de Pontigny" par adriano meis</t>
         </is>
       </c>
-      <c r="H77" s="56" t="inlineStr">
+      <c r="H78" s="56" t="inlineStr">
         <is>
           <t>https://www.laphilo.fr/pho/gandillac-mini.webp</t>
         </is>
       </c>
-      <c r="J77" s="48" t="inlineStr">
+      <c r="J78" s="48" t="inlineStr">
         <is>
           <t>epistemologie</t>
         </is>
       </c>
-      <c r="K77" s="48" t="inlineStr">
+      <c r="K78" s="48" t="inlineStr">
         <is>
           <t>Herméneutique</t>
         </is>
       </c>
-      <c r="L77" s="48" t="inlineStr">
+      <c r="L78" s="48" t="inlineStr">
         <is>
           <t>philosophe français connu pour son rôle de passeur entre traditions philosophiques.</t>
         </is>
       </c>
-      <c r="N77" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-    </row>
-    <row r="78" ht="174.75" customHeight="1" s="49">
-      <c r="A78" s="57" t="n">
+      <c r="N78" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+    </row>
+    <row r="79" ht="174.75" customHeight="1" s="49">
+      <c r="A79" s="57" t="n">
         <v>1906</v>
       </c>
-      <c r="B78" s="57" t="n">
+      <c r="B79" s="57" t="n">
         <v>1985</v>
       </c>
-      <c r="C78" s="60" t="inlineStr">
+      <c r="C79" s="60" t="inlineStr">
         <is>
           <t>1906 –  1985</t>
         </is>
       </c>
-      <c r="D78" s="60" t="inlineStr">
+      <c r="D79" s="60" t="inlineStr">
         <is>
           <t>Ferdinand ALQUIÉ</t>
         </is>
       </c>
-      <c r="E78" s="86" t="inlineStr">
+      <c r="E79" s="86" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Ferdinand_Alqui%C3%A9" title=" Wikipedia"&gt;Ferdinand ALQUIÉ&lt;/a&gt; était un philosophe français, l'un des plus grands spécialistes de Descartes et du cartésianisme, et figure importante du surréalisme philosophique. Né à Carcassonne, normalien et agrégé de philosophie, il fut professeur à la Sorbonne et membre de l'Académie des sciences morales et politiques. Sa double appartenance à la tradition du rationalisme cartésien et à la sensibilité surréaliste fait de lui un philosophe original et inclassable. &lt;/p&gt; &lt;p&gt;&lt;a href="https://www.persee.fr/doc/phlou_0035-3841_1971_num_69_4_5640_t1_0599_0000_1"  title=" Ferdinand Alquié signification de la philosophie par persée"&gt; Son œuvre cartésienne &lt;/a&gt; est considérable. Dans &lt;em&gt;La Découverte métaphysique de l'homme chez Descartes&lt;/em&gt; (1950) et dans sa grande édition commentée des &lt;em&gt;Œuvres philosophiques de Descartes&lt;/em&gt; (3 volumes, 1963-1973), il développe une interprétation existentielle et spiritualiste du cartésianisme qui insiste sur la dimension humaine de la découverte du cogito et sur la signification métaphysique de la démonstration de l'existence de Dieu. Cette lecture s'opposait à celle, plus formaliste et rationaliste, de Gueroult. &lt;/p&gt; &lt;p&gt; Son intérêt pour le surréalisme se manifesta dans &lt;em&gt;&lt;a href="https://www.puf.com/ferdinand-alquie"  title=" Ferdinand Alquié "&gt; Philosophie du surréalisme &lt;/a&gt; &lt;/em&gt; (1955), où il montra comment le mouvement surréaliste, malgré ses apparences irrationnelles, était habité par une quête authentique d'une réalité plus vraie, d'un « surréel » qui dépasse les limites du réel ordinaire. Cette dimension philosophique du surréalisme — sa relation au désir, au rêve et à l'amour comme voies d'accès à l'être — rapproche Breton de certaines intuitions de la métaphysique traditionnelle. Alquié représente ainsi une forme particulièrement riche de la philosophie française : rigoureuse et ouverte à la fois aux enjeux existentiels et poétiques de l'existence. &lt;/p&gt;    &lt;audio controls title="Le surréalisme après le surréalisme Ferdinand Alquié par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/13915-17.04.2022-ITEMA_22998020-2022C3372E0143-NET_MFC_F58A9676-97B8-4856-8F45-E151171B9161-21-e84cbcaee9155c0217a400e083995116.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;  </t>
         </is>
       </c>
-      <c r="F78" s="60" t="inlineStr">
+      <c r="F79" s="60" t="inlineStr">
         <is>
           <t>qBblW_rhpJ4</t>
         </is>
       </c>
-      <c r="G78" s="77" t="inlineStr">
+      <c r="G79" s="77" t="inlineStr">
         <is>
           <t>Ferdinand Alquié: Leçons sur Kant. La morale de Kant. Par Jgrandtour</t>
         </is>
       </c>
-      <c r="H78" s="86" t="inlineStr">
+      <c r="H79" s="86" t="inlineStr">
         <is>
           <t>https://www.laphilo.fr/pho/falquie-mini.webp</t>
         </is>
       </c>
-      <c r="J78" s="48" t="inlineStr">
+      <c r="J79" s="48" t="inlineStr">
         <is>
           <t>metaphysique ; epistemologie</t>
         </is>
       </c>
-      <c r="K78" s="48" t="inlineStr">
+      <c r="K79" s="48" t="inlineStr">
         <is>
           <t>Rationalisme</t>
         </is>
       </c>
-      <c r="L78" s="48" t="inlineStr">
+      <c r="L79" s="48" t="inlineStr">
         <is>
           <t>philosophe français spécialiste de Descartes et du cartésianisme.</t>
         </is>
       </c>
-      <c r="N78" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-    </row>
-    <row r="79" ht="150" customHeight="1" s="49">
-      <c r="A79" s="57" t="n">
+      <c r="N79" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+    </row>
+    <row r="80" ht="150" customHeight="1" s="49">
+      <c r="A80" s="57" t="n">
         <v>1907</v>
       </c>
-      <c r="B79" s="57" t="inlineStr">
+      <c r="B80" s="57" t="inlineStr">
         <is>
           <t>1968</t>
         </is>
       </c>
-      <c r="C79" s="57" t="inlineStr">
+      <c r="C80" s="57" t="inlineStr">
         <is>
           <t>1907 – 1968</t>
         </is>
       </c>
-      <c r="D79" s="58" t="inlineStr">
+      <c r="D80" s="58" t="inlineStr">
         <is>
           <t>Jean HYPPOLITE</t>
         </is>
       </c>
-      <c r="E79" s="59" t="inlineStr">
+      <c r="E80" s="59" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Jean_Hyppolite"  title=" Wikipedia"&gt;Jean HYPPOLITE&lt;/a&gt; était un philosophe français, l'un des grands introducteurs de Hegel en France au XXe siècle. Normalien et agrégé de philosophie, il enseigna dans plusieurs lycées et universités avant d'accéder à la chaire d'histoire de la philosophie au Collège de France en 1963. Il fut le maître de nombreux philosophes qui allaient marquer la pensée française de la seconde moitié du XXe siècle, dont Louis Althusser, Michel Foucault, Gilles Deleuze et Alain Badiou. &lt;/p&gt; &lt;p&gt; Son œuvre principale, la traduction et le commentaire de la &lt;em&gt;&lt;a href="https://www.persee.fr/doc/rscir_0035-2217_1947_num_21_3_1844_t1_0273_0000_2"  title=" jean hyppolite structure et phenomenologie de l’esprit par persée"&gt;Phénoménologie de l'Esprit &lt;/a&gt; &lt;/em&gt; de Hegel (&lt;em&gt;Genèse et structure de la Phénoménologie de l'Esprit de Hegel&lt;/em&gt;, 1946), est une contribution décisive à la connaissance de Hegel en France. Cette traduction, qui fit autorité pendant des décennies, et le vaste commentaire qui l'accompagnait rendirent accessible au public français une œuvre dont la complexité avait longtemps limité la diffusion. Il y montra la profondeur et l'actualité de la dialectique hégélienne comme philosophie de l'expérience et de l'histoire. &lt;/p&gt; &lt;p&gt; Dans &lt;em&gt;Logique et Existence&lt;/em&gt; (1953), &lt;a href="https://www.youtube.com/watch?v=tDBb946eDQs"  title=" jean hyppolite et alain badiou par benjamin Barbe"&gt;il tenta une interprétation &lt;/a&gt; ontologique de la &lt;em&gt;Science de la logique&lt;/em&gt; de Hegel, en dialogue avec Heidegger et la phénoménologie. Ses &lt;em&gt;Études sur Marx et Hegel&lt;/em&gt; (1955) contribuèrent à renouveler la lecture du marxisme en le confrontant à ses sources hégéliennes. Il incarnait une conception de la philosophie comme lecture rigoureuse des textes et comme méditation sur l'histoire de l'esprit, laissant une empreinte durable sur plusieurs générations de philosophes français. &lt;/p&gt;</t>
         </is>
       </c>
-      <c r="F79" s="57" t="inlineStr">
+      <c r="F80" s="57" t="inlineStr">
         <is>
           <t>Ws_ixU18OWg</t>
         </is>
       </c>
-      <c r="G79" s="59" t="inlineStr">
+      <c r="G80" s="59" t="inlineStr">
         <is>
           <t>"Qu'est-ce que l'histoire de la philosophie ? Entretien Jean Hyppolite-Alain Badiou" par NormezMoi</t>
         </is>
       </c>
-      <c r="H79" s="59" t="inlineStr">
+      <c r="H80" s="59" t="inlineStr">
         <is>
           <t>https://www.laphilo.fr/pho/jhyppolite-mini.webp</t>
         </is>
       </c>
-      <c r="J79" s="48" t="inlineStr">
+      <c r="J80" s="48" t="inlineStr">
         <is>
           <t>metaphysique ; epistemologie</t>
         </is>
       </c>
-      <c r="K79" s="48" t="inlineStr">
+      <c r="K80" s="48" t="inlineStr">
         <is>
           <t>Idéalisme allemand ; Marxisme</t>
         </is>
       </c>
-      <c r="L79" s="48" t="inlineStr">
+      <c r="L80" s="48" t="inlineStr">
         <is>
           <t>philosophe français qui introduisit Hegel en France au XXe siècle.</t>
         </is>
       </c>
-      <c r="N79" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-    </row>
-    <row r="80" ht="155.25" customHeight="1" s="49">
-      <c r="A80" s="54" t="n">
+      <c r="N80" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+    </row>
+    <row r="81" ht="155.25" customHeight="1" s="49">
+      <c r="A81" s="54" t="n">
         <v>1907</v>
       </c>
-      <c r="B80" s="54" t="inlineStr">
+      <c r="B81" s="54" t="inlineStr">
         <is>
           <t>2003</t>
         </is>
       </c>
-      <c r="C80" s="54" t="inlineStr">
+      <c r="C81" s="54" t="inlineStr">
         <is>
           <t>1907 – 2003</t>
         </is>
       </c>
-      <c r="D80" s="55" t="inlineStr">
+      <c r="D81" s="55" t="inlineStr">
         <is>
           <t>Maurice BLANCHOT</t>
         </is>
       </c>
-      <c r="E80" s="56" t="inlineStr">
+      <c r="E81" s="56" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Maurice_Blanchot" title=" Wikipedia"&gt;Maurice BLANCHOT&lt;/a&gt; était un philosophe, critique littéraire et écrivain français. Né à Quain en Saône-et-Loire, il étudia la philosophie et l'allemand à Strasbourg avant de s'orienter vers le journalisme et la critique littéraire. Après avoir flirté avec l'extrême-droite dans sa jeunesse, il rompit définitivement avec tout engagement politique direct après la guerre pour se consacrer entièrement à l'écriture et à la pensée. &lt;/p&gt; &lt;p&gt; Sa pensée oscille de manière caractéristique entre récit littéraire et réflexion philosophique, entre écriture et pensée de l'écriture. Dans ses essais critiques — &lt;em&gt;Faux Pas&lt;/em&gt; (1943), &lt;em&gt;La Part du Feu&lt;/em&gt; (1949), &lt;em&gt;&lt;a href="https://blanchot.fr/"  title=" maurice Blanchot"&gt;L'Espace littéraire &lt;/a&gt; &lt;/em&gt; (1955), &lt;em&gt;Le Livre à venir&lt;/em&gt; (1959) — il développe  &lt;a href="https://www.youtube.com/watch?v=5ag2XtoZN5E"  title=" maurice Blanchot par philovibre"&gt; une méditation originale &lt;/a&gt;  sur la littérature comme expérience de l'impossible, comme rapport à ce qu'il nomme le « neutre » ou le « dehors ». Pour lui, écrire c'est s'approcher de cette zone limite où le langage touche à son propre effacement. &lt;/p&gt; &lt;p&gt; Ses récits littéraires — &lt;em&gt;Thomas l'Obscur&lt;/em&gt; (1941, 1950), &lt;em&gt;Aminadab&lt;/em&gt; (1942), &lt;em&gt;Au Moment voulu&lt;/em&gt; (1951), &lt;em&gt;L'Attente l'Oubli&lt;/em&gt; (1962) — mettent en œuvre cette pensée de la limite, de l'absence et de la mort. Blanchot fut en dialogue constant avec Heidegger, Levinas, Kafka et Mallarmé. &lt;a href="https://www.youtube.com/watch?v=jiXPmq5LRfM"  title="levinas on maurice Blanchot par Eidos84"&gt; Son amitié avec Emmanuel Levinas &lt;/a&gt; fut l'une des plus fécondes de la philosophie française. L'influence de sa pensée sur le poststructuralisme et les théories de la littérature est considérable. &lt;/p&gt;   &lt;audio controls title="La vie secrète des philosophes par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/10467-22.05.2018-ITEMA_21686813-2018C12410E0142-21.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;  </t>
         </is>
       </c>
-      <c r="F80" s="54" t="inlineStr">
+      <c r="F81" s="54" t="inlineStr">
         <is>
           <t>Mzw9MF4JmBs</t>
         </is>
       </c>
-      <c r="G80" s="56" t="inlineStr">
+      <c r="G81" s="56" t="inlineStr">
         <is>
           <t>"MAURICE BLANCHOT – Les Vendredis de la philosophie" par Rien ne veut rien dire</t>
         </is>
       </c>
-      <c r="H80" s="56" t="inlineStr">
+      <c r="H81" s="56" t="inlineStr">
         <is>
           <t>https://www.laphilo.fr/pho/mblanchot-mini.webp</t>
         </is>
       </c>
-      <c r="J80" s="48" t="inlineStr">
+      <c r="J81" s="48" t="inlineStr">
         <is>
           <t>esthetique ; metaphysique</t>
         </is>
       </c>
-      <c r="K80" s="48" t="inlineStr">
+      <c r="K81" s="48" t="inlineStr">
         <is>
           <t>Post-structuralisme</t>
         </is>
       </c>
-      <c r="L80" s="48" t="inlineStr">
+      <c r="L81" s="48" t="inlineStr">
         <is>
           <t>philosophe français figure singulière et influente de la pensée française du XXe siècle.</t>
         </is>
       </c>
-      <c r="N80" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-    </row>
-    <row r="81" ht="175.5" customHeight="1" s="49">
-      <c r="A81" s="57" t="n">
+      <c r="N81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+    </row>
+    <row r="82" ht="175.5" customHeight="1" s="49">
+      <c r="A82" s="57" t="n">
         <v>1907</v>
       </c>
-      <c r="B81" s="57" t="inlineStr">
+      <c r="B82" s="57" t="inlineStr">
         <is>
           <t>1982</t>
         </is>
       </c>
-      <c r="C81" s="57" t="inlineStr">
+      <c r="C82" s="57" t="inlineStr">
         <is>
           <t>1907 – 1982</t>
         </is>
       </c>
-      <c r="D81" s="58" t="inlineStr">
+      <c r="D82" s="58" t="inlineStr">
         <is>
           <t>Jean BEAUFRET</t>
         </is>
       </c>
-      <c r="E81" s="59" t="inlineStr">
+      <c r="E82" s="59" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Jean_Beaufret"   title=" Wikipedia"&gt;Jean BEAUFRET&lt;/a&gt; était un philosophe français, connu principalement comme le principal introducteur et interprète de la philosophie de Martin Heidegger en France. Normalien et agrégé de philosophie, il enseigna dans plusieurs lycées parisiens et consacra l'essentiel de sa réflexion à la pensée heideggerienne, dont il fut à la fois le traducteur, le commentateur et le défenseur. La célèbre &lt;em&gt;Lettre sur l'humanisme&lt;/em&gt; de Heidegger (1946) fut écrite en réponse à des questions que Beaufret lui avait posées, témoignant de l'importance de ce dialogue franco-allemand. &lt;/p&gt; &lt;p&gt; Sa &lt;a href="https://www.persee.fr/doc/phlou_0035-3841_1983_num_81_50_6250"  title="in memory jean Beaufret par persée"&gt; contribution principale &lt;/a&gt; consiste dans l'introduction et la diffusion de la pensée de Heidegger dans le contexte philosophique français d'après-guerre, dominé par l'existentialisme de Sartre. Il soulignait la différence fondamentale entre la question heideggerienne de l'être et l'existentialisme sartrien, défendant la singularité de la « question de l'être » comme horizon ultime de toute philosophie. Ses cours et séminaires attirèrent de&lt;a href="https://www.youtube.com/watch?v=R9YGK09L2_Q"  title="jeanbeaufret par Michel Onfray"&gt; nombreux philosophes, &lt;/a&gt; parmi lesquels François Fédier, qui poursuivit son travail de traduction et d'interprétation. &lt;/p&gt; &lt;p&gt; Parmi ses publications, le &lt;em&gt;Dialogue avec Heidegger&lt;/em&gt; (4 volumes, 1973-1985) rassemble ses principaux essais et analyses de la pensée heideggerienne, couvrant la philosophie grecque, la modernité et la pensée contemporaine. Ces textes constituent un commentaire exigeant et pénétrant de l'œuvre de Heidegger, même si son rapport exclusif à cette unique source a parfois été critiqué. Son rôle dans la réception française de Heidegger, pour le meilleur et pour le pire — compte tenu de la controverse née de ses positions négationnistes à la fin de sa vie — reste incontournable. &lt;/p&gt; &lt;audio controls title="La vie absolument par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/15537-21.05.2018-ITEMA_21686393-1.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt; </t>
         </is>
       </c>
-      <c r="F81" s="57" t="n"/>
-      <c r="G81" s="59" t="n"/>
-      <c r="H81" s="59" t="inlineStr">
+      <c r="F82" s="57" t="n"/>
+      <c r="G82" s="59" t="n"/>
+      <c r="H82" s="59" t="inlineStr">
         <is>
           <t>https://www.laphilo.fr/pho/jbeaufret-mini.webp</t>
         </is>
       </c>
-      <c r="I81" s="48" t="inlineStr">
+      <c r="I82" s="48" t="inlineStr">
         <is>
           <t>https://www.laphilo.fr/photo/jbeaufret.webp</t>
         </is>
       </c>
-      <c r="J81" s="48" t="inlineStr">
+      <c r="J82" s="48" t="inlineStr">
         <is>
           <t>metaphysique</t>
         </is>
       </c>
-      <c r="K81" s="48" t="inlineStr">
+      <c r="K82" s="48" t="inlineStr">
         <is>
           <t>Phénoménologie</t>
         </is>
       </c>
-      <c r="L81" s="48" t="inlineStr">
+      <c r="L82" s="48" t="inlineStr">
         <is>
           <t>philosophe français introducteur et interprète de la philosophie de Martin Heidegger.</t>
         </is>
       </c>
-      <c r="N81" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-    </row>
-    <row r="82" ht="204" customHeight="1" s="49">
-      <c r="A82" s="57" t="n">
+      <c r="N82" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+    </row>
+    <row r="83" ht="204" customHeight="1" s="49">
+      <c r="A83" s="57" t="n">
         <v>1908</v>
       </c>
-      <c r="B82" s="57" t="inlineStr">
+      <c r="B83" s="57" t="inlineStr">
         <is>
           <t>1961</t>
         </is>
       </c>
-      <c r="C82" s="57" t="inlineStr">
+      <c r="C83" s="57" t="inlineStr">
         <is>
           <t>1908 – 1961</t>
         </is>
       </c>
-      <c r="D82" s="58" t="inlineStr">
+      <c r="D83" s="58" t="inlineStr">
         <is>
           <t>Maurice MERLEAU-PONTY</t>
         </is>
       </c>
-      <c r="E82" s="65" t="inlineStr">
+      <c r="E83" s="65" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Maurice_Merleau-Ponty" title=" Wikipedia"&gt;Maurice MERLEAU-PONTY&lt;/a&gt; était un philosophe français connu pour ses contributions à la phénoménologie, à la philosophie de la perception et à l’existentialisme. Il  s’inspire de plusieurs courants et penseurs et  reprend l’idée d’une description des expériences vécues, mais critique l’idéalisme husserlien. Dans son oeurvre majeure &lt;a href="https://www.youtube.com/watch?v=RrD5SEiXr_A"  title=" La phénoménologie de Maurice Merleau-Ponty par Tes grands auteurs en petits morceaux"&gt;"Phénoménalogie de la perception"&lt;/a&gt; il  y développe une critique radicale des approches traditionnelles de la perception pour proposer une vision incarnée et existentielle de l’expérience humaine. Il rejette la séparation cartésienne entre le corps et l’esprit &lt;a href="https://classiques.uqam.ca/classiques/merleau_ponty_maurice/sens_et_non_sens/sens_et_non_sens.html"  title="  Maurice Merleau-Ponty sens et non sens  par UQAM"&gt;(sens et non sens)&lt;/a&gt;. Pour lui, le corps n’est pas un objet, mais un sujet percevant :  &lt;/p&gt; &lt;p&gt;Le corps propre : C’est par lui que nous faisons l’expérience du monde. Il est à la fois sujet et objet, toujours déjà engagé dans un environnement. &lt;/p&gt; &lt;p&gt;La perception comme ouverture au monde : &lt;a href="https://www.youtube.com/watch?v=yiHMPFMCUvo" title="MERLEAU-PONTY - L'OEIL ET L'ESPRIT par Kosmos"&gt;Percevoir&lt;/a&gt;, c’est être en dialogue avec le monde, pas simplement recevoir des données sensorielles. &lt;/p&gt; &lt;p&gt;   Il  s’intéresse au langage comme geste corporel. Pour lui, la parole n’est pas un simple véhicule de la pensée, mais une incarnation du sens et l’art montre comment l’expression émerge de la perception. &lt;/p&gt; &lt;p&gt; Dans "Le Visible et l’invisible", il développe une  &lt;a href="https://www.youtube.com/watch?v=wZNUUGSZHMs"  title=" Maurice Merleau-Ponty - Entretien : Heure de culture française par Artesquieu "&gt;ontologie originale&lt;/a&gt; où le "chair" est ni matière ni esprit, c’est une substance sensible qui unit le corps et le monde.  Chiasme : Concept décrivant l’entrelacs du voyant et du visible, du touchant et du touché (ex. : quand je me touche la main, je suis à la fois sujet et objet).  L’invisible : Non pas l’absence de visible, mais ce qui le structure. &lt;/p&gt;   &lt;audio controls title="Maurice Merleau-Ponty : Partie 8/12- La crise de la pensée religieuse par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/13915-20.11.2014-ITEMA_20690515-2013C3372E0710-21.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;  </t>
         </is>
       </c>
-      <c r="F82" s="57" t="inlineStr">
+      <c r="F83" s="57" t="inlineStr">
         <is>
           <t>yiHMPFMCUvo</t>
         </is>
       </c>
-      <c r="G82" s="59" t="inlineStr">
+      <c r="G83" s="59" t="inlineStr">
         <is>
           <t>"MERLEAU-PONTY - L'OEIL ET L'ESPRIT" par Kosmos</t>
         </is>
       </c>
-      <c r="H82" s="59" t="inlineStr">
+      <c r="H83" s="59" t="inlineStr">
         <is>
           <t>https://www.laphilo.fr/pho/ponty-mini.webp</t>
         </is>
       </c>
-      <c r="J82" s="48" t="inlineStr">
+      <c r="J83" s="48" t="inlineStr">
         <is>
           <t>epistemologie ; metaphysique</t>
         </is>
       </c>
-      <c r="K82" s="48" t="inlineStr">
+      <c r="K83" s="48" t="inlineStr">
         <is>
           <t>Phénoménologie</t>
         </is>
       </c>
-      <c r="L82" s="48" t="inlineStr">
+      <c r="L83" s="48" t="inlineStr">
         <is>
           <t>philosophe français connu pour ses contributions à la phénoménologie.</t>
         </is>
       </c>
-      <c r="N82" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-    </row>
-    <row r="83" ht="210" customHeight="1" s="49">
-      <c r="A83" s="54" t="n">
-        <v>1908</v>
-      </c>
-      <c r="B83" s="54" t="inlineStr">
-        <is>
-          <t>1944</t>
-        </is>
-      </c>
-      <c r="C83" s="54" t="inlineStr">
-        <is>
-          <t>1908 – 1944</t>
-        </is>
-      </c>
-      <c r="D83" s="55" t="inlineStr">
-        <is>
-          <t>Albert LAUTMAN</t>
-        </is>
-      </c>
-      <c r="E83" s="56" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Albert_Lautman" title=" Wikipedia"&gt;Albert LAUTMAN&lt;/a&gt; était un philosophe français des mathématiques, dont l'œuvre courte mais d'une originalité remarquable a exercé une influence durable sur la philosophie française des sciences et des mathématiques. Né à Paris dans une famille juive, normalien et agrégé de philosophie, il fut mobilisé en 1939 et, après l'armistice, rejoignit la Résistance. Arrêté par la Gestapo en 1944, il fut fusillé à Mont-de-Marsan le 1er août de la même année, à l'âge de 35 ans, laissant une œuvre inachevée mais fondamentale. &lt;/p&gt; &lt;p&gt; &lt;a href="https://www.youtube.com/watch?v=aBr6djRSCiE"  title=" Albert Lautman et le platonisme dynamique par Hamda Mlika"&gt;Sa philosophie &lt;/a&gt; s'articule autour d'une réflexion originale sur les rapports entre mathématiques et philosophie. Dans ses thèses et ses essais — réunis sous le titre posthume &lt;em&gt;Essai sur l'unité des mathématiques et divers écrits&lt;/em&gt; (1977) — il soutient que les grandes théories mathématiques  (topologie, algèbre abstraite, géométrie différentielle) ne sont pas de simples constructions formelles, mais réalisent dans leur domaine propre des structures dialectiques qui constituent des problèmes philosophiques fondamentaux, tels que la relation entre le local et le global, le continu et le discret, l'un et le multiple. &lt;/p&gt; &lt;p&gt; Cette thèse fait de lui un penseur singulier à l'intersection de la philosophie platonicienne — il voit dans les mathématiques une participation à des idées dialectiques — et de la philosophie des sciences modernes. Gilles Deleuze reconnut en lui un précurseur de sa propre théorie du problème et de la différence. Fernando Zalamea a contribué à renouveler l'intérêt pour sa pensée dans les débats contemporains sur la philosophie des mathématiques. &lt;/p&gt;  &lt;audio controls title="Pourquoi les philosophes mathématiciens se sont fait fusiller  par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/13957-15.01.2022-ITEMA_22900988-2022C22785S0015-NET_MFC_0B385814-1D52-4706-8B44-2A8E4B2A1FAF-21-a970caaf0dead3c1677f6dad167bee92.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;  </t>
-        </is>
-      </c>
-      <c r="F83" s="54" t="inlineStr">
-        <is>
-          <t>abLPmODCgA4</t>
-        </is>
-      </c>
-      <c r="G83" s="56" t="inlineStr">
-        <is>
-          <t>"1908 - 1944 | Albert Lautman | Philosopher of Mathematical Reality" par Essai</t>
-        </is>
-      </c>
-      <c r="H83" s="56" t="inlineStr">
-        <is>
-          <t>https://www.laphilo.fr/pho/lautman-mini.webp</t>
-        </is>
-      </c>
-      <c r="J83" s="48" t="inlineStr">
-        <is>
-          <t>epistemologie</t>
-        </is>
-      </c>
-      <c r="K83" s="48" t="inlineStr">
-        <is>
-          <t>Rationalisme</t>
-        </is>
-      </c>
-      <c r="L83" s="48" t="inlineStr">
-        <is>
-          <t>philosophe français des mathématiques et résistant arrêté.</t>
-        </is>
-      </c>
-      <c r="M83" t="inlineStr">
-        <is>
-          <t xml:space="preserve">juive</t>
-        </is>
-      </c>
       <c r="N83" t="inlineStr">
         <is>
           <t xml:space="preserve">occident</t>
         </is>
       </c>
     </row>
-    <row r="84" ht="330.75" customHeight="1" s="49">
+    <row r="84" ht="210" customHeight="1" s="49">
       <c r="A84" s="54" t="n">
         <v>1908</v>
       </c>
-      <c r="B84" s="54" t="n">
-        <v>2009</v>
+      <c r="B84" s="54" t="inlineStr">
+        <is>
+          <t>1944</t>
+        </is>
       </c>
       <c r="C84" s="54" t="inlineStr">
         <is>
-          <t>1908 – 2009</t>
+          <t>1908 – 1944</t>
         </is>
       </c>
       <c r="D84" s="55" t="inlineStr">
         <is>
-          <t>Claude LEVI-STRAUSS</t>
-        </is>
-      </c>
-      <c r="E84" s="87" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;p&gt; &lt;a href="https://fr.wikipedia.org/wiki/Claude_L%C3%A9vi-Strauss"  title=" Wikipedia"&gt;Claude LEVI-STRAUSS&lt;/a&gt; était un anthropologue et ethnologue français, considéré comme l’une des grandes figures intellectuelles du XXᵉ siècle. Après des études de droit puis de philosophie, il se tourne vers l’ethnologie et commence ses premières missions de terrain au Brésil dans les années 1930, auprès de peuples amérindiens du Mato Grosso et de l’Amazonie. De ces expériences, il tirera notamment le livre Tristes tropiques, qui le rend célèbre auprès d’un public plus large en mêlant récit de voyage, &lt;a href="https://www.youtube.com/watch?v=Fk7du0Avh7U" title="peuples amerindiens levi-strauss par ina culture"&gt; réflexion sur les sociétés &lt;/a&gt; dites « primitives » et critique de l’ethnocentrisme occidental. &lt;/p&gt; &lt;p&gt; Il est connu pour avoir fondé l’anthropologie structurale, une manière d’étudier les cultures qui cherche les structures profondes, souvent inconscientes, qui organisent les systèmes de parenté, les mythes, les rites et plus largement les formes de vie sociales. Inspiré par la linguistique structurale, il considère que les faits culturels sont comme des langages : ce qui compte, ce sont les relations entre les éléments, plutôt que les éléments pris isolément. Sa méthode vise à réduire la diversité apparente des cultures à des ensembles de relations et d’oppositions formelles, par exemple des oppositions binaires (nature/culture, cru/cuit, vie/mort) qui structurent l’imaginaire. &lt;/p&gt; &lt;p&gt; Une partie centrale de son œuvre concerne les systèmes de parenté et l’alliance matrimoniale, qu’il étudie en détail dans Les structures élémentaires de la parenté, publié en 1949. Il y développe la théorie de l’alliance, selon laquelle les liens de parenté ne sont pas seulement des liens de sang, mais aussi des échanges de femmes entre groupes qui créent des solidarités et des obligations réciproques. Le mariage devient ainsi un mécanisme de communication sociale, une manière d’établir des réseaux d’alliance qui rendent possible la cohésion de la société. &lt;/p&gt; &lt;p&gt; Un autre volet majeur de sa pensée est son travail sur les mythes, en particulier dans les quatre volumes des Mythologiques, où il cherche à montrer que les mythes des différentes cultures, malgré leur grande diversité, obéissent à des schémas de transformation et à des structures communes. Pour lui, le mythe n’est pas une simple histoire, mais un système logique qui met en scène des oppositions et des médiations  pour résoudre symboliquement des tensions fondamentales. En analysant les mythes comme des ensembles de relations, il soutient que  &lt;a href="https://www.youtube.com/watch?v=fC0HUuXknHk" title="etre pessimiste pour l’avenir par ina culture"&gt;l’esprit humain fonctionne &lt;/a&gt;  partout selon des structures universelles, même si le contenu des récits varie. &lt;/p&gt; &lt;p&gt; Il développa une réflexion plus générale sur la diversité culturelle et les effets du colonialisme et de la modernité, notamment dans Tristes tropiques où il critique la tendance du monde moderne à homogénéiser et à détruire les différences culturelles. Il affirme l’idée que toutes les cultures sont égales en dignité et que la diversité des formes de vie humaines représente une richesse qu’il faut préserver, plutôt qu’un obstacle à dépasser. Son œuvre, reconnue par de nombreuses distinctions (médaille d’or du CNRS, élection à l’Académie française, prix Érasme, etc.), a contribué à transformer notre manière de penser le rapport entre l’Occident et les autres sociétés, ainsi que les fondements mêmes des sciences sociales. &lt;/p&gt;    &lt;audio controls title="sur les pas de claude levi-dtrausspar France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/13019-03.08.2022-ITEMA_23099095-2022F20970S0215-22.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;  </t>
+          <t>Albert LAUTMAN</t>
+        </is>
+      </c>
+      <c r="E84" s="56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Albert_Lautman" title=" Wikipedia"&gt;Albert LAUTMAN&lt;/a&gt; était un philosophe français des mathématiques, dont l'œuvre courte mais d'une originalité remarquable a exercé une influence durable sur la philosophie française des sciences et des mathématiques. Né à Paris dans une famille juive, normalien et agrégé de philosophie, il fut mobilisé en 1939 et, après l'armistice, rejoignit la Résistance. Arrêté par la Gestapo en 1944, il fut fusillé à Mont-de-Marsan le 1er août de la même année, à l'âge de 35 ans, laissant une œuvre inachevée mais fondamentale. &lt;/p&gt; &lt;p&gt; &lt;a href="https://www.youtube.com/watch?v=aBr6djRSCiE"  title=" Albert Lautman et le platonisme dynamique par Hamda Mlika"&gt;Sa philosophie &lt;/a&gt; s'articule autour d'une réflexion originale sur les rapports entre mathématiques et philosophie. Dans ses thèses et ses essais — réunis sous le titre posthume &lt;em&gt;Essai sur l'unité des mathématiques et divers écrits&lt;/em&gt; (1977) — il soutient que les grandes théories mathématiques  (topologie, algèbre abstraite, géométrie différentielle) ne sont pas de simples constructions formelles, mais réalisent dans leur domaine propre des structures dialectiques qui constituent des problèmes philosophiques fondamentaux, tels que la relation entre le local et le global, le continu et le discret, l'un et le multiple. &lt;/p&gt; &lt;p&gt; Cette thèse fait de lui un penseur singulier à l'intersection de la philosophie platonicienne — il voit dans les mathématiques une participation à des idées dialectiques — et de la philosophie des sciences modernes. Gilles Deleuze reconnut en lui un précurseur de sa propre théorie du problème et de la différence. Fernando Zalamea a contribué à renouveler l'intérêt pour sa pensée dans les débats contemporains sur la philosophie des mathématiques. &lt;/p&gt;  &lt;audio controls title="Pourquoi les philosophes mathématiciens se sont fait fusiller  par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/13957-15.01.2022-ITEMA_22900988-2022C22785S0015-NET_MFC_0B385814-1D52-4706-8B44-2A8E4B2A1FAF-21-a970caaf0dead3c1677f6dad167bee92.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;  </t>
         </is>
       </c>
       <c r="F84" s="54" t="inlineStr">
         <is>
-          <t>EPebdq4ZAsQ</t>
+          <t>abLPmODCgA4</t>
         </is>
       </c>
       <c r="G84" s="56" t="inlineStr">
         <is>
-          <t xml:space="preserve">claude levi-strauss le structuralisme par Ina Culture</t>
-        </is>
-      </c>
-      <c r="H84" s="62" t="inlineStr">
-        <is>
-          <t>https://www.laphilo.fr/pho/clstrauss-mini.webp</t>
+          <t>"1908 - 1944 | Albert Lautman | Philosopher of Mathematical Reality" par Essai</t>
+        </is>
+      </c>
+      <c r="H84" s="56" t="inlineStr">
+        <is>
+          <t>https://www.laphilo.fr/pho/lautman-mini.webp</t>
         </is>
       </c>
       <c r="J84" s="48" t="inlineStr">
         <is>
-          <t>ethique</t>
+          <t>epistemologie</t>
         </is>
       </c>
       <c r="K84" s="48" t="inlineStr">
         <is>
-          <t xml:space="preserve">Structuralisme ; Totémisme </t>
+          <t>Rationalisme</t>
         </is>
       </c>
       <c r="L84" s="48" t="inlineStr">
         <is>
-          <t>philosophe et anthropologue français qui  fonda l’anthropologie structurale.</t>
+          <t>philosophe français des mathématiques et résistant arrêté.</t>
         </is>
       </c>
       <c r="M84" t="inlineStr">
@@ -5931,1526 +5931,1526 @@
         </is>
       </c>
     </row>
-    <row r="85" ht="156" customHeight="1" s="49">
+    <row r="85" ht="330.75" customHeight="1" s="49">
       <c r="A85" s="54" t="n">
         <v>1908</v>
       </c>
-      <c r="B85" s="54" t="inlineStr">
+      <c r="B85" s="54" t="n">
+        <v>2009</v>
+      </c>
+      <c r="C85" s="54" t="inlineStr">
+        <is>
+          <t>1908 – 2009</t>
+        </is>
+      </c>
+      <c r="D85" s="55" t="inlineStr">
+        <is>
+          <t>Claude LEVI-STRAUSS</t>
+        </is>
+      </c>
+      <c r="E85" s="87" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt; &lt;a href="https://fr.wikipedia.org/wiki/Claude_L%C3%A9vi-Strauss"  title=" Wikipedia"&gt;Claude LEVI-STRAUSS&lt;/a&gt; était un anthropologue et ethnologue français, considéré comme l’une des grandes figures intellectuelles du XXᵉ siècle. Après des études de droit puis de philosophie, il se tourne vers l’ethnologie et commence ses premières missions de terrain au Brésil dans les années 1930, auprès de peuples amérindiens du Mato Grosso et de l’Amazonie. De ces expériences, il tirera notamment le livre Tristes tropiques, qui le rend célèbre auprès d’un public plus large en mêlant récit de voyage, &lt;a href="https://www.youtube.com/watch?v=Fk7du0Avh7U" title="peuples amerindiens levi-strauss par ina culture"&gt; réflexion sur les sociétés &lt;/a&gt; dites « primitives » et critique de l’ethnocentrisme occidental. &lt;/p&gt; &lt;p&gt; Il est connu pour avoir fondé l’anthropologie structurale, une manière d’étudier les cultures qui cherche les structures profondes, souvent inconscientes, qui organisent les systèmes de parenté, les mythes, les rites et plus largement les formes de vie sociales. Inspiré par la linguistique structurale, il considère que les faits culturels sont comme des langages : ce qui compte, ce sont les relations entre les éléments, plutôt que les éléments pris isolément. Sa méthode vise à réduire la diversité apparente des cultures à des ensembles de relations et d’oppositions formelles, par exemple des oppositions binaires (nature/culture, cru/cuit, vie/mort) qui structurent l’imaginaire. &lt;/p&gt; &lt;p&gt; Une partie centrale de son œuvre concerne les systèmes de parenté et l’alliance matrimoniale, qu’il étudie en détail dans Les structures élémentaires de la parenté, publié en 1949. Il y développe la théorie de l’alliance, selon laquelle les liens de parenté ne sont pas seulement des liens de sang, mais aussi des échanges de femmes entre groupes qui créent des solidarités et des obligations réciproques. Le mariage devient ainsi un mécanisme de communication sociale, une manière d’établir des réseaux d’alliance qui rendent possible la cohésion de la société. &lt;/p&gt; &lt;p&gt; Un autre volet majeur de sa pensée est son travail sur les mythes, en particulier dans les quatre volumes des Mythologiques, où il cherche à montrer que les mythes des différentes cultures, malgré leur grande diversité, obéissent à des schémas de transformation et à des structures communes. Pour lui, le mythe n’est pas une simple histoire, mais un système logique qui met en scène des oppositions et des médiations  pour résoudre symboliquement des tensions fondamentales. En analysant les mythes comme des ensembles de relations, il soutient que  &lt;a href="https://www.youtube.com/watch?v=fC0HUuXknHk" title="etre pessimiste pour l’avenir par ina culture"&gt;l’esprit humain fonctionne &lt;/a&gt;  partout selon des structures universelles, même si le contenu des récits varie. &lt;/p&gt; &lt;p&gt; Il développa une réflexion plus générale sur la diversité culturelle et les effets du colonialisme et de la modernité, notamment dans Tristes tropiques où il critique la tendance du monde moderne à homogénéiser et à détruire les différences culturelles. Il affirme l’idée que toutes les cultures sont égales en dignité et que la diversité des formes de vie humaines représente une richesse qu’il faut préserver, plutôt qu’un obstacle à dépasser. Son œuvre, reconnue par de nombreuses distinctions (médaille d’or du CNRS, élection à l’Académie française, prix Érasme, etc.), a contribué à transformer notre manière de penser le rapport entre l’Occident et les autres sociétés, ainsi que les fondements mêmes des sciences sociales. &lt;/p&gt;    &lt;audio controls title="sur les pas de claude levi-dtrausspar France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/13019-03.08.2022-ITEMA_23099095-2022F20970S0215-22.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;  </t>
+        </is>
+      </c>
+      <c r="F85" s="54" t="inlineStr">
+        <is>
+          <t>EPebdq4ZAsQ</t>
+        </is>
+      </c>
+      <c r="G85" s="56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">claude levi-strauss le structuralisme par Ina Culture</t>
+        </is>
+      </c>
+      <c r="H85" s="62" t="inlineStr">
+        <is>
+          <t>https://www.laphilo.fr/pho/clstrauss-mini.webp</t>
+        </is>
+      </c>
+      <c r="J85" s="48" t="inlineStr">
+        <is>
+          <t>ethique</t>
+        </is>
+      </c>
+      <c r="K85" s="48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Structuralisme ; Totémisme </t>
+        </is>
+      </c>
+      <c r="L85" s="48" t="inlineStr">
+        <is>
+          <t>philosophe et anthropologue français qui  fonda l’anthropologie structurale.</t>
+        </is>
+      </c>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t xml:space="preserve">juive</t>
+        </is>
+      </c>
+      <c r="N85" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+    </row>
+    <row r="86" ht="156" customHeight="1" s="49">
+      <c r="A86" s="54" t="n">
+        <v>1908</v>
+      </c>
+      <c r="B86" s="54" t="inlineStr">
         <is>
           <t>1986</t>
         </is>
       </c>
-      <c r="C85" s="54" t="inlineStr">
+      <c r="C86" s="54" t="inlineStr">
         <is>
           <t>1908 - 1986</t>
         </is>
       </c>
-      <c r="D85" s="55" t="inlineStr">
+      <c r="D86" s="55" t="inlineStr">
         <is>
           <t>Simone de BEAUVOIR</t>
         </is>
       </c>
-      <c r="E85" s="56" t="inlineStr">
+      <c r="E86" s="56" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Simone_de_Beauvoir"  title=" Wikipedia"&gt;Simone de BEAUVOIR&lt;/a&gt; (1908-1986) est une philosophe et romancière française, l’une des grandes figures de l’existentialisme et du féminisme du XXe siècle. Née à Paris dans une famille bourgeoise et catholique, elle rompt avec ce milieu, réussit en 1929 l’agrégation de philosophie, où elle rencontre Jean-Paul Sartre, et enseigne dans plusieurs lycées. Ils resteront liés toute leur vie, sans se marier ni vivre ensemble.&lt;/p&gt; &lt;p&gt;Dans &lt;em&gt;Pour une morale de l’ambiguïté&lt;/em&gt; (1947), elle prolonge la pensée de Sartre : l’homme est libre, mais sa liberté n’a de sens que si elle veut aussi celle des autres. Elle en tire un &lt;a href="https://www.youtube.com/watch?v=J3AW5eQEs68&amp;ab_channel=LePr%C3%A9cepteur"  title="Le Féminisme Existentialiste par le Précepteur"&gt;féminisme existentialiste&lt;/a&gt;. Dans &lt;a href="https://www.youtube.com/watch?v=QsnELrcARYU"  title="Le Deuxième Sexe de Simone de BEAUVOIR"&gt;&lt;em&gt;Le Deuxième Sexe&lt;/em&gt;&lt;/a&gt; (1949), elle montre que l’humanité a été pensée au masculin, et que la femme a été définie comme « l’Autre » de l’homme. Ni la biologie, ni la psychanalyse, ni l’histoire ne justifient cette situation : elle résulte de l’éducation, des mythes et des institutions qui enferment les femmes dans les rôles d’épouse et de mère. &lt;a href="https://fr.wikipedia.org/wiki/Le_Deuxi%C3%A8me_Sexe"  title=" Le deuxième sexe par wikipedia"&gt;« On ne naît pas femme : on le devient »&lt;/a&gt;. L’émancipation passe par la liberté de choisir sa vie, et d’abord par le travail et l’indépendance économique. Le livre fait scandale, puis devient une référence du féminisme dans le monde entier.&lt;/p&gt; &lt;p&gt;Romancière, elle reçoit le prix Goncourt en 1954 pour &lt;em&gt;Les Mandarins&lt;/em&gt; et raconte sa jeunesse dans les &lt;em&gt;Mémoires d’une jeune fille rangée&lt;/em&gt;. Engagée, elle signe en 1971 le manifeste des 343 femmes déclarant avoir avorté. Elle étudie aussi le sort des personnes âgées dans &lt;em&gt;La Vieillesse&lt;/em&gt; (1970).&lt;/p&gt;  &lt;audio controls title="Les féministes contemporaines se réclament-elles toujours de Simone de Beauvoir par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/10175-14.04.2026-ITEMA_24475616-2026C53458S0104-NET_MFC_D6B88A9C-001A-4EAF-84CB-D43E021E8A90-21-89a773555bc6a04e1bca98fa20edba08.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;</t>
         </is>
       </c>
-      <c r="F85" s="54" t="inlineStr">
+      <c r="F86" s="54" t="inlineStr">
         <is>
           <t>PY3Ie8Mnw9E</t>
         </is>
       </c>
-      <c r="G85" s="56" t="inlineStr">
+      <c r="G86" s="56" t="inlineStr">
         <is>
           <t>Simone de Beauvoir par Brut</t>
         </is>
       </c>
-      <c r="H85" s="56" t="inlineStr">
+      <c r="H86" s="56" t="inlineStr">
         <is>
           <t>https://www.laphilo.fr/pho/beauvoir-mini.webp</t>
         </is>
       </c>
-      <c r="J85" s="48" t="inlineStr">
+      <c r="J86" s="48" t="inlineStr">
         <is>
           <t>ethique ; politique</t>
         </is>
       </c>
-      <c r="K85" s="48" t="inlineStr">
+      <c r="K86" s="48" t="inlineStr">
         <is>
           <t>Existentialisme ; Féminisme</t>
         </is>
       </c>
-      <c r="L85" s="48" t="inlineStr">
+      <c r="L86" s="48" t="inlineStr">
         <is>
           <t>philosophe française et intellectuelle anticonformiste figure de l'existentialisme.</t>
         </is>
       </c>
-      <c r="M85" t="inlineStr">
+      <c r="M86" t="inlineStr">
         <is>
           <t xml:space="preserve">femme</t>
         </is>
       </c>
-      <c r="N85" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-      <c r="O85">
+      <c r="N86" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+      <c r="O86">
         <v>3</v>
       </c>
     </row>
-    <row r="86" ht="242.25" customHeight="1" s="49">
-      <c r="A86" s="57" t="n">
+    <row r="87" ht="242.25" customHeight="1" s="49">
+      <c r="A87" s="57" t="n">
         <v>1909</v>
       </c>
-      <c r="B86" s="57" t="inlineStr">
+      <c r="B87" s="57" t="inlineStr">
         <is>
           <t>1943</t>
         </is>
       </c>
-      <c r="C86" s="57" t="inlineStr">
+      <c r="C87" s="57" t="inlineStr">
         <is>
           <t>1909 - 1943</t>
         </is>
       </c>
-      <c r="D86" s="58" t="inlineStr">
+      <c r="D87" s="58" t="inlineStr">
         <is>
           <t>Simone WEIL</t>
         </is>
       </c>
-      <c r="E86" s="59" t="inlineStr">
+      <c r="E87" s="59" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Simone_Weil"  title=" Wikipedia"&gt;Simone WEIL&lt;/a&gt; (1909-1943) est une philosophe française, dont l’œuvre unit la réflexion politique, l’expérience du travail et la recherche spirituelle. Élève du philosophe Alain, normalienne, agrégée de philosophie, elle enseigne dans plusieurs lycées et milite auprès des syndicats ouvriers. En 1934-1935, elle quitte l’enseignement pour travailler comme ouvrière dans des usines, chez Alsthom puis chez Renault, afin de connaître de l’intérieur l’oppression du travail à la chaîne : ses notes formeront &lt;em&gt;La Condition ouvrière&lt;/em&gt;.&lt;/p&gt; &lt;p&gt;En 1936, elle rejoint en Espagne une colonne anarchiste pendant la guerre civile, mais doit rentrer après un accident. À la fin des années 1930, elle vit une expérience mystique et se tourne vers le christianisme, sans jamais demander le baptême, par solidarité avec ceux qui restent hors de l’Église. Réfugiée à Marseille en 1941, elle travaille aux vendanges chez le philosophe paysan Gustave Thibon, qui publiera après sa mort des extraits de ses carnets, &lt;em&gt;La Pesanteur et la grâce&lt;/em&gt;. Elle y médite sur le malheur, sur l’attention, qui est « la forme la plus rare et la plus pure de la générosité », et sur la nécessité de se détacher de soi. En 1942, elle rejoint la France libre à Londres. Elle y écrit &lt;a href="https://www.youtube.com/watch?v=6CR2PcTPvCk&amp;ab_channel=Al%C3%A8theiar" title="Les besoins de l'âme par Alèteia"&gt;&lt;em&gt;L’Enracinement&lt;/em&gt;&lt;/a&gt;, où elle décrit les « besoins de l’âme » et la nécessité pour chacun d’avoir des racines. Dans sa &lt;em&gt;Note sur la &lt;a href="https://www.youtube.com/watch?v=Pg0qv0kIaKo&amp;ab_channel=LePr%C3%A9cepteur"  style="color:#88A1E9"  title="Supprimer les parties politiques par le Précepteur"&gt;suppression générale des partis politiques&lt;/a&gt;&lt;/em&gt;, elle accuse les partis de fabriquer de la passion collective et d’étouffer la pensée.&lt;/p&gt; &lt;p&gt;Épuisée, refusant de manger plus que les rations de la France occupée, elle meurt à trente-quatre ans en Angleterre.&lt;/p&gt;  &lt;audio controls title="Une intellectuelle à l'usine par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/21936-01.01.2021-ITEMA_22534096-2019C12410E0194.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;</t>
         </is>
       </c>
-      <c r="F86" s="57" t="inlineStr">
+      <c r="F87" s="57" t="inlineStr">
         <is>
           <t>2ZJCrhkDuC4</t>
         </is>
       </c>
-      <c r="G86" s="59" t="inlineStr">
+      <c r="G87" s="59" t="inlineStr">
         <is>
           <t>"Pourquoi il faut lire Simone Weil" par France Culture</t>
         </is>
       </c>
-      <c r="H86" s="59" t="inlineStr">
+      <c r="H87" s="59" t="inlineStr">
         <is>
           <t>https://www.laphilo.fr/pho/weil-mini.webp</t>
         </is>
       </c>
-      <c r="J86" s="48" t="inlineStr">
+      <c r="J87" s="48" t="inlineStr">
         <is>
           <t>ethique ; spiritualite</t>
         </is>
       </c>
-      <c r="K86" s="48" t="inlineStr">
+      <c r="K87" s="48" t="inlineStr">
         <is>
           <t>Spiritualisme ; Existentialisme</t>
         </is>
       </c>
-      <c r="L86" s="48" t="inlineStr">
+      <c r="L87" s="48" t="inlineStr">
         <is>
           <t>philosophe française humaniste et profondément spirituelle.</t>
         </is>
       </c>
-      <c r="M86" t="inlineStr">
+      <c r="M87" t="inlineStr">
         <is>
           <t xml:space="preserve">juive;femme</t>
         </is>
       </c>
-      <c r="N86" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-    </row>
-    <row r="87" ht="227.25" customHeight="1" s="49">
-      <c r="A87" s="54" t="n">
+      <c r="N87" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+    </row>
+    <row r="88" ht="227.25" customHeight="1" s="49">
+      <c r="A88" s="54" t="n">
         <v>1910</v>
       </c>
-      <c r="B87" s="54" t="inlineStr">
+      <c r="B88" s="54" t="inlineStr">
         <is>
           <t>1996</t>
         </is>
       </c>
-      <c r="C87" s="54" t="inlineStr">
+      <c r="C88" s="54" t="inlineStr">
         <is>
           <t>1910 – 1996</t>
         </is>
       </c>
-      <c r="D87" s="55" t="inlineStr">
+      <c r="D88" s="55" t="inlineStr">
         <is>
           <t>Bernard CHARBONNEAU</t>
         </is>
       </c>
-      <c r="E87" s="56" t="inlineStr">
+      <c r="E88" s="56" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Bernard_Charbonneau"  title=" Wikipedia"&gt;Bernard CHARBONNEAU&lt;/a&gt; était un penseur français, pionnier de la critique écologique et de la réflexion sur la technique et la liberté, souvent qualifié de « père méconnu » de l'écologie politique française. Né à Bordeaux,  &lt;a href="https://www.jacques-ellul.org/compagnonnage/bernard-charbonneau"  title="ami de Jacques Ellul  "&gt;ami intime de Jacques Ellul &lt;/a&gt; avec lequel il partagea une amitié intellectuelle de plus de soixante ans, il développa dès les années 1930 une pensée radicalement critique de la modernité technicienne et des formes contemporaines d'organisation sociale, bien avant que ces thèmes ne deviennent des enjeux politiques majeurs. &lt;/p&gt; &lt;p&gt; Dès 1937, dans un texte prophétique intitulé « Directives pour un personnalisme » rédigé avec Jacques Ellul, il posait les bases d'une critique du totalitarisme — qu'il identifiait non seulement au fascisme et au stalinisme, mais aussi à la démocratie de masse — fondée sur la défense irréductible de la liberté individuelle et de la relation à la nature.  Dans &lt;em&gt;Le Jardin de Babylone&lt;/em&gt; (1969), il montre comment la modernité a transformé la nature en décor consommable, détruisant ce rapport authentique à la terre et aux saisons qui constituait le fond de la liberté paysanne. &lt;/p&gt; &lt;p&gt; Son œuvre la plus ambitieuse, &lt;em&gt;Le Feu vert&lt;/em&gt; (1980) et &lt;em&gt;L'Etat&lt;/em&gt; (1987), développe une &lt;a href="https://www.youtube.com/watch?v=U6WXSBX8Ldg"  title="bernard Chardonneau par Sylvain Theriault  "&gt;critique radicale de l'État &lt;/a&gt; bureaucratique et technicien et de sa tendance à absorber toutes les formes de vie sociale. Il défendait un « anarchisme chrétien » ancré dans l'expérience concrète du Béarn où il choisit de vivre. Redécouvert dans les années 2000 par les mouvements écologistes et décroissants, il est aujourd'hui reconnu comme l'un des penseurs les plus originaux et les plus lucides du XXe siècle français. &lt;/p&gt;</t>
         </is>
       </c>
-      <c r="F87" s="54" t="inlineStr">
+      <c r="F88" s="54" t="inlineStr">
         <is>
           <t>hJKaFSyjNqo</t>
         </is>
       </c>
-      <c r="G87" s="56" t="inlineStr">
+      <c r="G88" s="56" t="inlineStr">
         <is>
           <t>"Bernard Charbonneau, la liberté pour boussole" par Regards propestants</t>
         </is>
       </c>
-      <c r="H87" s="56" t="inlineStr">
+      <c r="H88" s="56" t="inlineStr">
         <is>
           <t>https://www.laphilo.fr/pho/charbonneau-mini.webp</t>
         </is>
       </c>
-      <c r="J87" s="48" t="inlineStr">
+      <c r="J88" s="48" t="inlineStr">
         <is>
           <t>politique ; ethique</t>
         </is>
       </c>
-      <c r="K87" s="48" t="inlineStr">
+      <c r="K88" s="48" t="inlineStr">
         <is>
           <t>Ecologisme</t>
         </is>
       </c>
-      <c r="L87" s="48" t="inlineStr">
+      <c r="L88" s="48" t="inlineStr">
         <is>
           <t>philosophe français pionnier de la critique écologique.</t>
         </is>
       </c>
-      <c r="N87" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-    </row>
-    <row r="88" ht="162" customHeight="1" s="49">
-      <c r="A88" s="57">
+      <c r="N88" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+    </row>
+    <row r="89" ht="162" customHeight="1" s="49">
+      <c r="A89" s="57">
         <v>1910</v>
       </c>
-      <c r="B88" s="57">
+      <c r="B89" s="57">
         <v>1993</v>
       </c>
-      <c r="C88" s="60" t="inlineStr">
+      <c r="C89" s="60" t="inlineStr">
         <is>
           <t xml:space="preserve">1910 – 1993</t>
         </is>
       </c>
-      <c r="D88" s="60" t="inlineStr">
+      <c r="D89" s="60" t="inlineStr">
         <is>
           <t>Édouard MOROT-SIR</t>
         </is>
       </c>
-      <c r="E88" s="61" t="inlineStr">
+      <c r="E89" s="61" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/%C3%89douard_Morot-Sir"   title=" Wikipedia"&gt;Édouard MOROT-SIR&lt;/a&gt; était un philosophe français, connu pour sa longue carrière universitaire en France et aux États-Unis, où il joua un rôle de passeur essentiel entre les cultures philosophiques française et américaine. Agrégé de philosophie, il fut conseiller culturel de l'ambassade de France aux États-Unis, professeur dans plusieurs universités américaines — notamment à l'Université de Caroline du Nord à Chapel Hill — et contribua à diffuser la philosophie française outre-Atlantique pendant les décennies de l'après-guerre. &lt;/p&gt; &lt;p&gt; Sa philosophie s'articule autour d'une réflexion sur le langage, la pensée et l'existence. Dans &lt;em&gt;La Pensée française d'aujourd'hui&lt;/em&gt; (1971) et dans &lt;a href="https://www.persee.fr/doc/rfea_0397-7870_1987_num_34_1_1293"  title=" reflexion sur l’expérience littéraire et le pouvoir critique aus USA par persée"&gt;plusieurs ouvrages &lt;/a&gt; consacrés à la linguistique philosophique, il défend une conception du langage comme acte de présence au monde, irréductible à une simple description de données objectives. Sa réflexion sur les rapports entre pensée, langage et expérience intérieure le situe dans la continuité de la tradition réflexive française tout en intégrant les apports de&lt;a href="https://fr.wikipedia.org/wiki/Philosophie_analytique"  title=" philosophie analytique par wikipedia"&gt; la philosophie analytique &lt;/a&gt; anglo-saxonne. &lt;/p&gt; &lt;p&gt; Ses travaux sur la rhétorique et la logique naturelle du langage, développés notamment dans &lt;em&gt;Rhétorique et stylistique de la fiction&lt;/em&gt; (1988), témoignent d'un intérêt constant pour les modes d'expression et d'argumentation propres à la littérature et à la philosophie. Enseignant d'une grande qualité pédagogique, il forma des générations d'étudiants américains à la philosophie française. Sa longue carrière à l'intersection de deux cultures intellectuelles fait de lui une figure originale et importante pour l'internationalisation de la philosophie française. &lt;/p&gt;</t>
         </is>
       </c>
-      <c r="F88" s="60" t="n"/>
-      <c r="G88" s="61" t="n"/>
-      <c r="H88" s="61" t="inlineStr">
+      <c r="F89" s="60" t="n"/>
+      <c r="G89" s="61" t="n"/>
+      <c r="H89" s="61" t="inlineStr">
         <is>
           <t>https://www.laphilo.fr/pho/morotsir-mini.webp</t>
         </is>
       </c>
-      <c r="I88" s="48" t="inlineStr">
+      <c r="I89" s="48" t="inlineStr">
         <is>
           <t>https://www.laphilo.fr/photo/morotsir.webp</t>
         </is>
       </c>
-      <c r="J88" s="48" t="inlineStr">
+      <c r="J89" s="48" t="inlineStr">
         <is>
           <t>metaphysique ; epistemologie</t>
         </is>
       </c>
-      <c r="K88" s="48" t="inlineStr">
+      <c r="K89" s="48" t="inlineStr">
         <is>
           <t>Spiritualisme</t>
         </is>
       </c>
-      <c r="L88" s="48" t="inlineStr">
+      <c r="L89" s="48" t="inlineStr">
         <is>
           <t>philosophe français passeur entre les cultures philosophiques française et américaine.</t>
         </is>
       </c>
-      <c r="N88" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-    </row>
-    <row r="89" ht="186" customHeight="1" s="49">
-      <c r="A89" s="57" t="n">
+      <c r="N89" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+    </row>
+    <row r="90" ht="186" customHeight="1" s="49">
+      <c r="A90" s="57" t="n">
         <v>1912</v>
       </c>
-      <c r="B89" s="57" t="inlineStr">
+      <c r="B90" s="57" t="inlineStr">
         <is>
           <t>1994</t>
         </is>
       </c>
-      <c r="C89" s="57" t="inlineStr">
+      <c r="C90" s="57" t="inlineStr">
         <is>
           <t>1912 – 1994</t>
         </is>
       </c>
-      <c r="D89" s="58" t="inlineStr">
+      <c r="D90" s="58" t="inlineStr">
         <is>
           <t>Jacques ELLUL</t>
         </is>
       </c>
-      <c r="E89" s="59" t="inlineStr">
+      <c r="E90" s="59" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Jacques_Ellul"  title=" Wikipedia"&gt;Jacques ELLUL&lt;/a&gt; était un philosophe, sociologue, historien du droit et théologien protestant français, célèbre pour sa critique radicale de la technique moderne et de ses  &lt;a href="https://www.youtube.com/watch?v=SfUEFANIm5s"  title=" Jacques Ellul : Comprendre la propagande infiltrés dans la société par Multivers philosophique"&gt;effets aliénants &lt;/a&gt; sur la société et la liberté humaine. Anarchiste chrétien, il oppose révolte authentique et révolution mythique, valorisant la non-violence et la résistance locale face à la massification.  Penseur inclassable mêlant marxisme critique, anarchisme chrétien et écologie avant l'heure, il a produit une &lt;a href="https://www.persee.fr/doc/colan_0336-1500_1995_num_106_1_2633"  title="Les leçons de Jacques Ellul  par Persée "&gt;œuvre prolifique &lt;/a&gt; dépassant les 50 livres, traduits dans de nombreuses langues. Né à Bordeaux, professeur à l’université de cette ville, résistant pendant la guerre, il est reconnu en 2001 « Juste parmi les nations » pour avoir caché des Juifs. &lt;/p&gt; &lt;p&gt; Dans son livre "La Technique ou l'Enjeu du siècle" paru en 1954, il décrit son "efficience absolue" qui aliène l'homme, le rendant dépendant d'un milieu technique auto-entretenu, avec des notions clés comme le "milieu technique déterminé" et la "nécessité technique".  Il  définit la  &lt;a href="https://www.youtube.com/watch?v=DGsN8Ssf5oo"  title=" 
 Jacques Ellul, premier critique de la technologie par France Culture"&gt;"technique" &lt;/a&gt; non comme un outil, mais comme un système autonome et totalisant de méthodes rationnelles efficaces, envahissant tous les domaines humains (économie, politique, éducation). &lt;/p&gt; &lt;p&gt; &lt;a href="https://www.jacques-ellul.org/"  title=" Jacques Ellul "&gt;Précurseur écologique, &lt;/a&gt; il dénonce la production illimitée qui domine les besoins humains et appelle à une "profanation" de cette sacralisation technique. Son legs visionnaire influence l'écologie politique, la décroissance et les réflexions sur le numérique, voyant dans la technique un "système technicien" préfigurant nos crises actuelles. &lt;/p&gt;  &lt;audio controls title="Avoir raison avec... Jacques Ellul par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/17362-11.08.2025-ITEMA_24214885-2025C35448E0031-ITE_00152537_RSCE-21.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;</t>
         </is>
       </c>
-      <c r="F89" s="57" t="inlineStr">
+      <c r="F90" s="57" t="inlineStr">
         <is>
           <t>-_ixXU1dmIU</t>
         </is>
       </c>
-      <c r="G89" s="59" t="inlineStr">
+      <c r="G90" s="59" t="inlineStr">
         <is>
           <t>"Jacques ELLUL - L'illusion de notre liberté" par Polis</t>
         </is>
       </c>
-      <c r="H89" s="59" t="inlineStr">
+      <c r="H90" s="59" t="inlineStr">
         <is>
           <t>https://www.laphilo.fr/pho/ellul-mini.webp</t>
         </is>
       </c>
-      <c r="J89" s="48" t="inlineStr">
+      <c r="J90" s="48" t="inlineStr">
         <is>
           <t>politique ; ethique</t>
         </is>
       </c>
-      <c r="K89" s="48" t="inlineStr">
+      <c r="K90" s="48" t="inlineStr">
         <is>
           <t>Ecologisme ; Conservatisme</t>
         </is>
       </c>
-      <c r="L89" s="48" t="inlineStr">
+      <c r="L90" s="48" t="inlineStr">
         <is>
           <t>philosophe français critique de la technique moderne &amp; des effets aliénants sur la société.</t>
         </is>
       </c>
-      <c r="N89" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-    </row>
-    <row r="90" ht="183.75" customHeight="1" s="49">
-      <c r="A90" s="54" t="n">
+      <c r="N90" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+    </row>
+    <row r="91" ht="183.75" customHeight="1" s="49">
+      <c r="A91" s="54" t="n">
         <v>1912</v>
       </c>
-      <c r="B90" s="54" t="inlineStr">
+      <c r="B91" s="54" t="inlineStr">
         <is>
           <t>2013</t>
         </is>
       </c>
-      <c r="C90" s="54" t="inlineStr">
+      <c r="C91" s="54" t="inlineStr">
         <is>
           <t>1912 – 2013</t>
         </is>
       </c>
-      <c r="D90" s="55" t="inlineStr">
+      <c r="D91" s="55" t="inlineStr">
         <is>
           <t>Henri MALDINEY</t>
         </is>
       </c>
-      <c r="E90" s="62" t="inlineStr">
+      <c r="E91" s="62" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Henri_Maldiney"  title=" Wikipedia"&gt;Henri MALDINEY&lt;/a&gt; était un philosophe français, l'une des figures les plus importantes de la phénoménologie française, connu pour sa réflexion originale sur l'art, la psychiatrie et l'existence. Né à Lyon, agrégé de philosophie, il enseigna à l'Université de Lyon pendant toute sa carrière. Sa pensée, &lt;a href="https://www.henri-maldiney.org/"  title="henri MALDINEY"&gt; d'une grande densité &lt;/a&gt; et d'un style exigeant, se développe à l'intersection de la phénoménologie husserlienne et heideggerienne, de la psychiatrie phénoménologique (notamment Binswanger) et d'une réflexion approfondie sur les arts plastiques et la musique. &lt;/p&gt; &lt;p&gt; Son œuvre maîtresse, &lt;em&gt;Regard, Parole, Espace&lt;/em&gt; (1973), est une méditation profonde sur la perception, le langage et l'espace à partir de l'analyse d'œuvres plastiques et poétiques.  &lt;a href="https://www.persee.fr/doc/chime_0986-6035_2001_num_44_1_2388/"  title="henri MALDINEY par persée "&gt; Il y développe &lt;/a&gt; une phénoménologie du pathique — du mode d'être fondamental par lequel nous sommes d'abord « touchés » par ce qui nous vient — par opposition au gnostique, qui serait le rapport détaché et objectivant à la réalité. Cette distinction lui permet d'analyser de manière originale la perception esthétique, l'expérience psychopathologique et la rencontre avec l'autre. &lt;/p&gt; &lt;p&gt; Dans &lt;em&gt;&lt;a href="https://fr.wikiversity.org/wiki/Penser_l%27homme_et_la_folie"  title="pensée l’homme et la folie  par wikipedia "&gt;Penser l'homme et la folie &lt;/a&gt; &lt;/em&gt; (1991) et &lt;em&gt;L'Art, l'éclair de l'être&lt;/em&gt; (1993), il approfondit sa réflexion sur les relations entre existence, folie et création artistique. Pour lui, l'art n'est pas un objet parmi d'autres mais une modalité d'existence, un surgissement de sens qui déborde toute représentation. Sa pensée, qui articule phénoménologie, psychiatrie et esthétique, a exercé une influence durable sur la psychiatrie phénoménologique française et sur les études d'esthétique philosophique. &lt;/p&gt;  &lt;audio controls title="hommage à Henri Maldiney par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/10080-14.12.2013-ITEMA_20561627-2013C3403E0239-21.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt; </t>
         </is>
       </c>
-      <c r="F90" s="54" t="inlineStr">
+      <c r="F91" s="54" t="inlineStr">
         <is>
           <t>hqRpB9RgYio</t>
         </is>
       </c>
-      <c r="G90" s="56" t="inlineStr">
+      <c r="G91" s="56" t="inlineStr">
         <is>
           <t>"Henri Maldiney Entretien par Connaitre Henri Maldiney</t>
         </is>
       </c>
-      <c r="H90" s="56" t="inlineStr">
+      <c r="H91" s="56" t="inlineStr">
         <is>
           <t>https://www.laphilo.fr/pho/hmaldiney-mini.webp</t>
         </is>
       </c>
-      <c r="J90" s="48" t="inlineStr">
+      <c r="J91" s="48" t="inlineStr">
         <is>
           <t>esthetique ; epistemologie</t>
         </is>
       </c>
-      <c r="K90" s="48" t="inlineStr">
+      <c r="K91" s="48" t="inlineStr">
         <is>
           <t>Phénoménologie</t>
         </is>
       </c>
-      <c r="L90" s="48" t="inlineStr">
+      <c r="L91" s="48" t="inlineStr">
         <is>
           <t>philosophe français figure importante de la phénoménologie française.</t>
         </is>
       </c>
-      <c r="N90" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-    </row>
-    <row r="91" ht="225.75" customHeight="1" s="49">
-      <c r="A91" s="57" t="n">
+      <c r="N91" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+    </row>
+    <row r="92" ht="225.75" customHeight="1" s="49">
+      <c r="A92" s="57" t="n">
         <v>1913</v>
       </c>
-      <c r="B91" s="57" t="inlineStr">
+      <c r="B92" s="57" t="inlineStr">
         <is>
           <t>1960</t>
         </is>
       </c>
-      <c r="C91" s="57" t="inlineStr">
+      <c r="C92" s="57" t="inlineStr">
         <is>
           <t>1913 - 1960</t>
         </is>
       </c>
-      <c r="D91" s="58" t="inlineStr">
+      <c r="D92" s="58" t="inlineStr">
         <is>
           <t>Albert CAMUS</t>
         </is>
       </c>
-      <c r="E91" s="65" t="inlineStr">
+      <c r="E92" s="65" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Albert_Camus"  title=" Wikipedia"&gt;Albert CAMUS&lt;/a&gt; (1913-1960) est un écrivain et philosophe français, né à Mondovi, en Algérie, dans une famille pauvre : son père meurt à la guerre en 1914, et sa mère, presque sourde, l’élève à Alger. Journaliste, résistant, rédacteur en chef du journal &lt;em&gt;Combat&lt;/em&gt; à la Libération, il reçoit le prix Nobel de littérature en 1957 et meurt dans un accident de voiture en 1960. On le range souvent parmi les existentialistes, une étiquette qu’il refusait.&lt;/p&gt; &lt;p&gt;Sa pensée part de &lt;a href="https://www.youtube.com/watch?v=kAm_I8nwjnc&amp;t=498s&amp;ab_channel=LePr%C3%A9cepteur"   title="L'absure par le Précepteur"&gt;l’absurde&lt;/a&gt; : l’homme réclame un sens et une clarté que le monde lui refuse. Le « cycle de l’absurde » réunit le roman &lt;a href="https://www.youtube.com/watch?v=vpzwD2cqqII&amp;ab_channel=LePr%C3%A9cepteur"  title="L'étranger par le Précepteur"&gt;&lt;em&gt;L’Étranger&lt;/em&gt;&lt;/a&gt; (1942), dont le héros, Meursault, traverse sa propre vie en étranger, et l’essai &lt;em&gt;Le Mythe de Sisyphe&lt;/em&gt; (1942). Camus y refuse aussi bien le suicide que l’espoir religieux : il faut vivre l’absurde en pleine lucidité, comme Sisyphe roulant éternellement son rocher. « Il faut imaginer Sisyphe heureux. »&lt;/p&gt; &lt;p&gt;Vient ensuite le cycle de la &lt;a href="https://www.youtube.com/watch?v=pkRWhuO0wX0&amp;ab_channel=AlainBajom%C3%A9er" title="La Révolte par Alain Bajomée"&gt;révolte&lt;/a&gt;. Dans &lt;a href="https://www.youtube.com/watch?v=XLbXH2kVOJ8"  title="La Peste par le France Culture"&gt;&lt;em&gt;La Peste&lt;/em&gt;&lt;/a&gt; (1947), allégorie de l’Occupation, des hommes luttent ensemble contre l’épidémie, sans héroïsme ni espoir de salut. &lt;em&gt;L’Homme révolté&lt;/em&gt; (1951) affirme : « Je me révolte, donc nous sommes » ; la révolte crée une solidarité et pose une limite, que les révolutions trahissent quand elles justifient le meurtre au nom de l’histoire. Le livre provoque sa rupture avec Sartre, en 1952. Ses pièces, comme &lt;em&gt;Caligula&lt;/em&gt; ou &lt;em&gt;Les Justes&lt;/em&gt;, prolongent cette réflexion sur la mesure et la dignité humaine.&lt;/p&gt;  &lt;audio controls title="Albert Camus par France Culture"&gt; &lt;source src="https://cdn.radiofrance.fr/s3/cruiser-production/static/inter/sons/2011/07/s27/NET_2f8a9ed7-086a-40ee-9d75-b184f9e5f99a.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;</t>
         </is>
       </c>
-      <c r="F91" s="57" t="inlineStr">
+      <c r="F92" s="57" t="inlineStr">
         <is>
           <t>q2m4kRO2yuw</t>
         </is>
       </c>
-      <c r="G91" s="59" t="inlineStr">
+      <c r="G92" s="59" t="inlineStr">
         <is>
           <t>"La VIE n'a pas de SENS" par Evolution Factory</t>
         </is>
       </c>
-      <c r="H91" s="59" t="inlineStr">
+      <c r="H92" s="59" t="inlineStr">
         <is>
           <t>https://www.laphilo.fr/pho/camus-mini.webp</t>
         </is>
       </c>
-      <c r="J91" s="48" t="inlineStr">
+      <c r="J92" s="48" t="inlineStr">
         <is>
           <t>ethique ; metaphysique</t>
         </is>
       </c>
-      <c r="K91" s="48" t="inlineStr">
+      <c r="K92" s="48" t="inlineStr">
         <is>
           <t>Existentialisme ; Absurde</t>
         </is>
       </c>
-      <c r="L91" s="48" t="inlineStr">
+      <c r="L92" s="48" t="inlineStr">
         <is>
           <t>philosophe et écrivain français existentialiste connu pour sa vision de l'absurde.</t>
         </is>
       </c>
-      <c r="N91" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-    </row>
-    <row r="92" ht="267" customHeight="1" s="49">
-      <c r="A92" s="54" t="n">
+      <c r="N92" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+    </row>
+    <row r="93" ht="267" customHeight="1" s="49">
+      <c r="A93" s="54" t="n">
         <v>1913</v>
       </c>
-      <c r="B92" s="54" t="inlineStr">
+      <c r="B93" s="54" t="inlineStr">
         <is>
           <t>2005</t>
         </is>
       </c>
-      <c r="C92" s="54" t="inlineStr">
+      <c r="C93" s="54" t="inlineStr">
         <is>
           <t>1913 – 2005</t>
         </is>
       </c>
-      <c r="D92" s="55" t="inlineStr">
+      <c r="D93" s="55" t="inlineStr">
         <is>
           <t>Paul RICOEUR</t>
         </is>
       </c>
-      <c r="E92" s="62" t="inlineStr">
+      <c r="E93" s="62" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Paul_Ric%C5%93ur"   title=" Wikipedia"&gt;Paul RICOEUR&lt;/a&gt; était un  philosophe français considéré comme le dernier &lt;a href="https://www.lemonde.fr/a-la-une/article/2005/05/21/paul-ricoeur-philosophe-de-tous-les-dialogues_652552_3208.html"  title="Paul Ricoeur, philosophe de tous les dialogues par Le Monde"&gt;"grands penseurs" &lt;/a&gt; à la croisée de la phénoménologie, de l’herméneutique, de la philosophie du langage et de l’éthique. &lt;/p&gt; &lt;p&gt; Dans “Le volontaire et l’involontaire” et “Finitude et culpabilité”, il analyse la volonté humaine comme toujours prise entre liberté et contraintes, capacité d’agir et fragilité, ce qui nourrit sa réflexion sur la faute et la responsabilité.  Ses travaux sur le symbole et l’interprétation montrent que l’être humain se comprend à travers  &lt;a href="https://www.youtube.com/watch?v=QLOwycKenCI" title="En 1965, le philosophe Paul Ricoeur commente la contre-culture beatnik par Radio-Canada"&gt; des symboles&lt;/a&gt;, des récits et des textes, dont le sens n’est jamais donné immédiatement mais demande un travail d’interprétation. Son projet est de tenir ensemble la compréhension “interprétative” et les approches critiques (psychanalyse, structuralisme), en assumant les “conflits d’interprétations” plutôt que de chercher une seule lecture définitive. &lt;/p&gt; &lt;p&gt; Il conçoit  &lt;a href="https://www.youtube.com/watch?v=uX76UVhBIqs"  title="Paul Ricoeur, l’herméneutique du soupçon par Baglis Tv"&gt; l’herméneutique&lt;/a&gt; comme une philosophie de l’interprétation qui assume la distance entre nous et les textes, les événements, les autres, et qui cherche une vérité située dans ce travail d’interprétation plutôt que dans une évidence immédiate.​ Il insiste sur le fait qu’il n’existe pas de philosophie “sans présuppositions” : toute compréhension passe par des pré-compréhensions, que la critique vient transformer, ce qui l’amène à articuler la lecture soupçonneuse (Marx, Nietzsche, Freud) et la lecture de confiance. &lt;/p&gt; &lt;p&gt; Il développe une éthique de la “vie bonne, avec et pour les autres, dans des institutions justes” (formule célèbre de “Soi-même comme un autre”), où l’éthique (visée de la vie bonne) précède la morale (règles, normes).​ 
 Il met au centre le “sujet capable” (capable de parler, agir, se raconter, se tenir pour responsable) mais toujours fragile, et pense la justice comme articulation entre la reconnaissance de la vulnérabilité des personnes et la nécessité d’institutions justes.​ &lt;/p&gt; &lt;p&gt; Ses analyses de la mémoire, de l’histoire et du pardon nourrissent aussi les débats contemporains sur le “devoir de mémoire”, les violences politiques et les possibilités de réconciliation. &lt;/p&gt;   &lt;audio controls title="La pensée de Paul Ricoeur par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/10467-18.11.2013-ITEMA_20550371-2013C12410S0322-NET_FC_66E918EC-2266-4DF5-B6E4-489E465FA68D-21.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;</t>
         </is>
       </c>
-      <c r="F92" s="54" t="inlineStr">
+      <c r="F93" s="54" t="inlineStr">
         <is>
           <t>2Dsxl0LJPsY</t>
         </is>
       </c>
-      <c r="G92" s="56" t="inlineStr">
+      <c r="G93" s="56" t="inlineStr">
         <is>
           <t>"C'EST QUOI UN PHILOSOPHE ? Pour le philosophe français Paul Ricoeur," par Ina</t>
         </is>
       </c>
-      <c r="H92" s="56" t="inlineStr">
+      <c r="H93" s="56" t="inlineStr">
         <is>
           <t>https://www.laphilo.fr/pho/ricoeur-mini.webp</t>
         </is>
       </c>
-      <c r="J92" s="48" t="inlineStr">
+      <c r="J93" s="48" t="inlineStr">
         <is>
           <t>epistemologie ; ethique</t>
         </is>
       </c>
-      <c r="K92" s="48" t="inlineStr">
+      <c r="K93" s="48" t="inlineStr">
         <is>
           <t>Herméneutique ; Phénoménologie</t>
         </is>
       </c>
-      <c r="L92" s="48" t="inlineStr">
+      <c r="L93" s="48" t="inlineStr">
         <is>
           <t>philosophe français s'inscrivant dans les courants phénoménologiques et herméneutiques.</t>
         </is>
       </c>
-      <c r="N92" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-    </row>
-    <row r="93" ht="404.25" customHeight="1" s="49">
-      <c r="A93" s="54" t="n">
+      <c r="N93" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+    </row>
+    <row r="94" ht="404.25" customHeight="1" s="49">
+      <c r="A94" s="54" t="n">
         <v>1913</v>
       </c>
-      <c r="B93" s="54" t="n">
+      <c r="B94" s="54" t="n">
         <v>1970</v>
       </c>
-      <c r="C93" s="54" t="inlineStr">
+      <c r="C94" s="54" t="inlineStr">
         <is>
           <t>1913 – 1970</t>
         </is>
       </c>
-      <c r="D93" s="55" t="inlineStr">
+      <c r="D94" s="55" t="inlineStr">
         <is>
           <t>Lucien GOLDMANN</t>
         </is>
       </c>
-      <c r="E93" s="88" t="inlineStr">
+      <c r="E94" s="88" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Lucien_Goldmann"  title=" Wikipedia"&gt;Lucien GOLDMANN&lt;/a&gt; était un philosophe et sociologue français d’origine roumaine, fortement marqué par Marx et par le jeune Georg Lukács. Il a enseigné à l’École pratique des hautes études et fut l’une des figures importantes du marxisme humaniste en France.  &lt;a href="https://maitron.fr/goldmann-lucien-serge/"  title="Goldmann Lucien par le Maitron"&gt;Sa pensée cherche à comprendre &lt;/a&gt;  les œuvres littéraires et philosophiques non comme de simples productions individuelles, mais comme l’expression organisée d’une expérience sociale et historique. &lt;/p&gt; &lt;p&gt; Son concept central est celui de &lt;a href="https://www.youtube.com/watch?v=cSDfwVq-LyU"  title="le concept de vision du monde selon Goldmann par Loic Chaigneau"&gt;« vision du monde ». &lt;/a&gt; Une vision du monde désigne l’ensemble cohérent d’idées, de sentiments et d’aspirations qu’un groupe social développe à partir de sa situation historique. L’écrivain ou le philosophe ne parle donc jamais entièrement en son nom propre : il donne une forme particulièrement élaborée à des préoccupations collectives. L’œuvre devient ainsi le lieu où une conscience sociale atteint un degré de cohérence qu’elle ne possédait pas nécessairement dans la vie quotidienne. &lt;/p&gt; &lt;p&gt; Pour étudier cette relation entre œuvre et société, il élabore le structuralisme génétique. Le terme « structuralisme » signifie qu’il faut analyser la cohérence interne d’une œuvre : ses personnages, ses thèmes, ses oppositions et sa forme. Le terme « génétique » rappelle qu’il faut aussi rechercher comment cette structure s’est constituée historiquement, en la mettant en rapport avec les groupes sociaux et les conflits de leur époque. Il refuse donc à la fois de réduire l’œuvre à un simple reflet mécanique de l’économie et de l’isoler complètement de la société. &lt;/p&gt; &lt;p&gt; Dans Le Dieu caché, son ouvrage majeur publié en 1956, il rapproche les Pensées de Pascal et le théâtre de Racine. Selon lui, ces œuvres expriment une même vision tragique du monde, liée à la situation historique  &lt;a href="https://fr.wikipedia.org/wiki/Jans%C3%A9nisme"  title="Jansénisme par wikipedia"&gt;du jansénisme : &lt;/a&gt;  l’homme aspire à une vérité et à une transcendance, mais il se heurte à l’absence apparente de Dieu et à l’impossibilité de résoudre pleinement ses contradictions. Il montre ainsi que l’analyse philosophique, religieuse et littéraire peut être réunie dans une interprétation sociologique et historique. &lt;/p&gt; &lt;p&gt; Dans Pour une sociologie du roman, il applique ensuite sa méthode au roman moderne. Il établit une homologie entre la forme romanesque, centrée sur la recherche individuelle de valeurs authentiques, et la société individualiste de l’économie marchande, où les relations humaines tendent à être médiatisées par les échanges et les objets. Sa philosophie est donc une théorie des rapports entre conscience, histoire et création culturelle : les œuvres ne sont ni de purs produits individuels ni de simples miroirs sociaux, mais des constructions qui donnent une expression cohérente aux tensions vécues par des groupes humains. &lt;/p&gt; </t>
         </is>
       </c>
-      <c r="F93" s="54" t="inlineStr">
+      <c r="F94" s="54" t="inlineStr">
         <is>
           <t>OIc0AWrxGFY</t>
         </is>
       </c>
-      <c r="G93" s="56" t="inlineStr">
+      <c r="G94" s="56" t="inlineStr">
         <is>
           <t>lisez lucien Goldmann c’est une bombe par paduTeam</t>
         </is>
       </c>
-      <c r="H93" s="62" t="inlineStr">
+      <c r="H94" s="62" t="inlineStr">
         <is>
           <t>https://www.laphilo.fr/pho/lgoldmann-mini.webp</t>
         </is>
       </c>
-      <c r="J93" s="48" t="inlineStr">
+      <c r="J94" s="48" t="inlineStr">
         <is>
           <t>politique</t>
         </is>
       </c>
-      <c r="K93" s="48" t="inlineStr">
+      <c r="K94" s="48" t="inlineStr">
         <is>
           <t>Marxisme ; Structuralisme</t>
         </is>
       </c>
-      <c r="L93" s="76" t="inlineStr">
+      <c r="L94" s="76" t="inlineStr">
         <is>
           <t xml:space="preserve"> philosophe et sociologue français d’origine roumaine, fortement marqué par Marx.</t>
         </is>
       </c>
-      <c r="M93" t="inlineStr">
+      <c r="M94" t="inlineStr">
         <is>
           <t xml:space="preserve">juive</t>
         </is>
       </c>
-      <c r="N93" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-    </row>
-    <row r="94" ht="249.75" customHeight="1" s="49">
-      <c r="A94" s="54" t="n">
+      <c r="N94" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+    </row>
+    <row r="95" ht="249.75" customHeight="1" s="49">
+      <c r="A95" s="54" t="n">
         <v>1914</v>
       </c>
-      <c r="B94" s="54" t="n">
+      <c r="B95" s="54" t="n">
         <v>1996</v>
       </c>
-      <c r="C94" s="54" t="inlineStr">
+      <c r="C95" s="54" t="inlineStr">
         <is>
           <t>1914 – 1996</t>
         </is>
       </c>
-      <c r="D94" s="55" t="inlineStr">
+      <c r="D95" s="55" t="inlineStr">
         <is>
           <t>Marguerite DURAS</t>
         </is>
       </c>
-      <c r="E94" s="88" t="inlineStr">
+      <c r="E95" s="88" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Marguerite_Duras"  title=" Wikipedia"&gt;Marguerite DURAS&lt;/a&gt; n’était pas une philosophe au sens académique, mais son œuvre littéraire, cinématographique et théâtrale déploie  &lt;a href="https://www.marguerite-duras.com/Biographie.php"  title="marguerite duras -biographie"&gt;une pensée originale, &lt;/a&gt; centrée sur l’écriture, le désir, la mémoire et la condition humaine. &lt;/p&gt; &lt;p&gt; Elle récuse le dualisme corps/esprit hérité de la tradition philosophique et religieuse occidentale, et propose plutôt un monisme matérialiste : l’être est fait d’une seule substance, la matière, et le corps y est réhabilité contre les représentations littéraires marquées par le péché originel. Cette vision s’enracine aussi dans son athéisme et dans l’influence de la philosophie orientale, vécue durant ses dix-huit premières années en Indochine. &lt;/p&gt; &lt;p&gt; Pour elle, écrire, c’est « donner corps au paradoxe » et signifier le désir : l’écriture est le lieu même de la « vérité du désir », souvent orientée vers un objet absent, inaccessible. Elle décrit l’écriture comme un acte de silence et de cri : « Écrire c’est ne pas parler. C’est se taire. C’est hurler sans bruit. », libérant un  &lt;a href="https://www.youtube.com/watch?v=KBum9zj-9p8"  title="marguerite duras -détruire pour mieux reconstruire par france culture"&gt;désir refoulé &lt;/a&gt; par la société. La mémoire est inséparable du désir et de l’écriture : elle n’est pas fiable, et c’est par l’affabulation et la réinscription dans le texte que les souvenirs acquièrent une existence réelle. L’écriture devient alors travail de mémoire et de deuil, une manière de faire durer la vie face à la mort, en traitant « la mémoire de l’oubli ». &lt;/p&gt; &lt;p&gt; Elle met en scène un sujet humain inconsistant, « fantomatique », essentiellement seul et dépourvu d’identité stable, s’opposant au « fantasme d’identité » de la philosophie occidentale. Tout en restant distante du militantisme féministe, son œuvre défend la cause des femmes et explore la liberté, la passivité et la dynamique masculin/féminin, notamment dans sa dernière période créatrice. &lt;/p&gt; &lt;p&gt; Bien qu’elle affirme ne pas écrire ex nihilo et reconnaisse des inspirations (Pascal, Diderot, Rousseau, Kierkegaard), elle s’en détache en déclarant avoir oublié ses lectures, marquant une relation paradoxale à la philosophie. Son rapport à la pensée se manifeste par des interrogations sur le temps, la matière et la souffrance, faisant de l’écriture le seul moyen d’exprimer des émotions fondamentales que le langage ordinaire ne peut porter. &lt;/p&gt; 
 &lt;audio controls title="Marguerite DURAS , je mets la musique au-dessus de tout par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/20333-02.01.2023-ITEMA_23242749-2022M36310E0193-25.m4a" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;  </t>
         </is>
       </c>
-      <c r="F94" s="54" t="inlineStr">
+      <c r="F95" s="54" t="inlineStr">
         <is>
           <t>DthxMnXQGB0</t>
         </is>
       </c>
-      <c r="G94" s="56" t="inlineStr">
+      <c r="G95" s="56" t="inlineStr">
         <is>
           <t xml:space="preserve">Une vie : Marguerite DURAS par Brut</t>
         </is>
       </c>
-      <c r="H94" s="62" t="inlineStr">
+      <c r="H95" s="62" t="inlineStr">
         <is>
           <t>https://www.laphilo.fr/pho/mduras-mini.webp</t>
         </is>
       </c>
-      <c r="J94" s="48" t="inlineStr">
+      <c r="J95" s="48" t="inlineStr">
         <is>
           <t xml:space="preserve">ethique ; </t>
         </is>
       </c>
-      <c r="K94" s="48" t="inlineStr">
+      <c r="K95" s="48" t="inlineStr">
         <is>
           <t xml:space="preserve">Existentialisme</t>
         </is>
       </c>
-      <c r="L94" s="76" t="inlineStr">
+      <c r="L95" s="76" t="inlineStr">
         <is>
           <t xml:space="preserve"> pas une philosophe au sens académique, mais son œuvre littéraire, cinématographique et théâtrale déploie une pensée originale, centrée sur l’écriture, le désir, la mémoire et la condition humaine.</t>
         </is>
       </c>
-      <c r="M94" t="inlineStr">
+      <c r="M95" t="inlineStr">
         <is>
           <t xml:space="preserve">femme</t>
         </is>
       </c>
-      <c r="N94" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-    </row>
-    <row r="95" ht="247.5" customHeight="1" s="49">
-      <c r="A95" s="57" t="n">
+      <c r="N95" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+    </row>
+    <row r="96" ht="247.5" customHeight="1" s="49">
+      <c r="A96" s="57" t="n">
         <v>1918</v>
       </c>
-      <c r="B95" s="57" t="inlineStr">
+      <c r="B96" s="57" t="inlineStr">
         <is>
           <t>1990</t>
         </is>
       </c>
-      <c r="C95" s="57" t="inlineStr">
+      <c r="C96" s="57" t="inlineStr">
         <is>
           <t>1918 – 1990</t>
         </is>
       </c>
-      <c r="D95" s="58" t="inlineStr">
+      <c r="D96" s="58" t="inlineStr">
         <is>
           <t>Louis ALTHUSSER</t>
         </is>
       </c>
-      <c r="E95" s="65" t="inlineStr">
+      <c r="E96" s="65" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Louis_Althusser"  title=" Wikipedia"&gt;Louis ALTHUSSER&lt;/a&gt; était un philosophe connu pour ses efforts de renouvellement de la pensée marxiste et ses concepts novateurs.  Parmi ses concepts clés, on peut citer : &lt;/p&gt; &lt;p&gt;La coupure épistémologique : Il soutient qu'il existe une rupture radicale entre les œuvres de jeunesse de Marx  et ses œuvres de la maturité (notamment Le Capital). Cette coupure marquerait le passage d'une idéologie humaniste à une science de l'histoire, le matérialisme historique. &lt;/p&gt; &lt;p&gt;L'idéologie et les Appareils Idéologiques d'État &lt;a href="https://www.youtube.com/watch?v=ZtJjAs7kLpo"  title=" Louis Althusser AIE par Cinema culture"&gt;(AIE) &lt;/a&gt;: Il développe une théorie influente de l'idéologie avec un ensemble d'idées fausses, mais une "représentation du rapport imaginaire des individus à leurs conditions réelles d'existence". Elle fonctionne en "interpellant" les individus en sujets. Les AIE (comme l'école, l'Église, la famille, les médias) jouent un rôle crucial dans la reproduction des rapports de production capitalistes en diffusant l'idéologie dominante. &lt;/p&gt; &lt;p&gt;La surdétermination : Emprunté à la psychanalyse, ce concept lui permet de penser la complexité des contradictions dans une société. Une contradiction principale entre les forces productives et les rapports de production est toujours surdéterminée par d'autres contradictions secondaires. &lt;/p&gt; &lt;p&gt;Le procès sans sujet : Il critique l'idée que l'histoire serait le produit de l'action consciente d'un sujet et insiste sur le fait que l'histoire est un &lt;a href="https://www.youtube.com/watch?v=Syi7hOQcNUs"  title=" Louis Althusser sur la civilisation par Artesquieu"&gt;processus déterminé&lt;/a&gt; par des structures. &lt;/p&gt; &lt;p&gt;La philosophie comme "lutte de classes dans la théorie" : Il conçoit la philosophie non pas comme une quête de vérité absolue, mais comme une intervention politique dans le champ théorique, reflétant les luttes de classes. Il parle aussi de la "philosophie spontanée des savants" pour désigner les présupposés idéologiques inconscients qui peuvent influencer le travail scientifique. &lt;/p&gt; &lt;p&gt; Parmi ses publications les plus importantes, on peut mentionner : &lt;/p&gt; &lt;p&gt;Montesquieu, la politique et l'histoire : Une analyse de la pensée politique de Montesquieu. Lénine et la philosophie : Développe sa conception de la philosophie comme pratique politique. L'avenir dure longtemps (suivi de Les Faits) (1992, posthume) : Une autobiographie où il revient sur sa vie, ses troubles psychiques et le meurtre de sa femme, Hélène Rytmann, en 1980. Cet événement tragique a conduit à son internement psychiatrique et a mis fin à sa carrière publique. &lt;/p&gt;  &lt;audio controls title=" Louis Althusser par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/11189-11.07.2011-ITEMA_20296434-2011C15000E0126-ITE_00044081_RSCE-21.mp3" type="audio/mpeg" align="center"&gt;&lt;/audio&gt; </t>
         </is>
       </c>
-      <c r="F95" s="57" t="inlineStr">
+      <c r="F96" s="57" t="inlineStr">
         <is>
           <t>n89Mtv1ovNQ</t>
         </is>
       </c>
-      <c r="G95" s="59" t="inlineStr">
+      <c r="G96" s="59" t="inlineStr">
         <is>
           <t>"Louis Althusser : Idéologie et appareils idéologiques d’État " par Cinema Culture</t>
         </is>
       </c>
-      <c r="H95" s="59" t="inlineStr">
+      <c r="H96" s="59" t="inlineStr">
         <is>
           <t>https://www.laphilo.fr/pho/althusser-mini.webp</t>
         </is>
       </c>
-      <c r="J95" s="48" t="inlineStr">
+      <c r="J96" s="48" t="inlineStr">
         <is>
           <t>politique ; epistemologie</t>
         </is>
       </c>
-      <c r="K95" s="48" t="inlineStr">
+      <c r="K96" s="48" t="inlineStr">
         <is>
           <t>Marxisme ; Structuralisme</t>
         </is>
       </c>
-      <c r="L95" s="48" t="inlineStr">
+      <c r="L96" s="48" t="inlineStr">
         <is>
           <t>philosophe français à l'origine d'un renouvellement de la pensée marxiste.</t>
         </is>
       </c>
-      <c r="N95" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-    </row>
-    <row r="96" ht="174.75" customHeight="1" s="49">
-      <c r="A96" s="54" t="n">
+      <c r="N96" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+    </row>
+    <row r="97" ht="174.75" customHeight="1" s="49">
+      <c r="A97" s="54" t="n">
         <v>1919</v>
       </c>
-      <c r="B96" s="54" t="inlineStr">
+      <c r="B97" s="54" t="inlineStr">
         <is>
           <t>1994</t>
         </is>
       </c>
-      <c r="C96" s="54" t="inlineStr">
+      <c r="C97" s="54" t="inlineStr">
         <is>
           <t>1919 – 1994</t>
         </is>
       </c>
-      <c r="D96" s="55" t="inlineStr">
+      <c r="D97" s="55" t="inlineStr">
         <is>
           <t>Jean BRUN</t>
         </is>
       </c>
-      <c r="E96" s="56" t="inlineStr">
+      <c r="E97" s="56" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Jean_Brun_(philosophe)"  title=" Wikipedia"&gt;Jean BRUN&lt;/a&gt; était un philosophe français spécialiste de philosophie antique, de philosophie des techniques et de pensée chrétienne. Né à Pont-à-Mousson, agrégé de philosophie et docteur ès lettres, il enseigna à l'Université de Dijon pendant toute sa carrière. Son œuvre étendue couvre l'histoire de la philosophie grecque, la philosophie de la technique et une réflexion théologique et anthropologique sur le destin de l'homme moderne. &lt;/p&gt; &lt;p&gt;   &lt;a href="https://www.persee.fr/doc/phlou_0035-3841_1989_num_87_76_6584_t1_0666_0000_2"  title=" jean brun 25 siècle de pensée occidentale par persée"&gt;Ses travaux &lt;/a&gt; sur la philosophie antique — notamment &lt;em&gt;Les Présocratiques&lt;/em&gt; (1968), &lt;em&gt;L'Épicurisme&lt;/em&gt; (1959), &lt;em&gt;Le Stoïcisme&lt;/em&gt; (1958), &lt;em&gt;Socrate&lt;/em&gt; (1960) — constituent des introductions claires et pénétrantes aux grandes écoles de la pensée grecque, qui ont initié des générations d'étudiants à la philosophie ancienne. Ces ouvrages publiés dans la collection « Que sais-je ? » ou chez des éditeurs universitaires se distinguent par leur lisibilité et la qualité de leur synthèse. &lt;/p&gt; &lt;p&gt; Dans &lt;em&gt;Le Retour de Dionysos&lt;/em&gt; (1969) et surtout dans &lt;em&gt;Les Vagabonds de l'Occident&lt;/em&gt; (1976), il développe une réflexion critique sur la modernité technique et ses effets sur l'existence humaine. Il voit dans la  &lt;a href="https://www.youtube.com/watch?v=LiVoSaLhWB8"  title=" jean brun conquete de l’homme par lamecaniqueunviverselle"&gt;domination technicienne &lt;/a&gt; une forme de hubris qui rompt le lien entre l'homme et le cosmos, et dans cette rupture la source des grands maux de la modernité. Sa pensée, nourrie de christianisme et de philosophie grecque, offre une vision prophétique des dangers de la technocratie. Il représente une forme originale de philosophie chrétienne engagée dans la critique culturelle. &lt;/p&gt;</t>
         </is>
       </c>
-      <c r="F96" s="54" t="inlineStr">
+      <c r="F97" s="54" t="inlineStr">
         <is>
           <t>vHpZx3DyWyE</t>
         </is>
       </c>
-      <c r="G96" s="56" t="inlineStr">
+      <c r="G97" s="56" t="inlineStr">
         <is>
           <t>"De Jean brun : les conquêtes de l'homme et la séparation ontologique. Nietzsche Chestov" par La MecaniqueUniverselle</t>
         </is>
       </c>
-      <c r="H96" s="56" t="inlineStr">
+      <c r="H97" s="56" t="inlineStr">
         <is>
           <t>https://www.laphilo.fr/pho/jbrun-mini.webp</t>
         </is>
       </c>
-      <c r="J96" s="48" t="inlineStr">
+      <c r="J97" s="48" t="inlineStr">
         <is>
           <t>metaphysique ; spiritualite</t>
         </is>
       </c>
-      <c r="K96" s="48" t="inlineStr">
+      <c r="K97" s="48" t="inlineStr">
         <is>
           <t>Spiritualisme</t>
         </is>
       </c>
-      <c r="L96" s="48" t="inlineStr">
+      <c r="L97" s="48" t="inlineStr">
         <is>
           <t>philosophe français spécialiste de philosophie antique et de pensée chrétienne.</t>
         </is>
       </c>
-      <c r="N96" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-    </row>
-    <row r="97" ht="159.75" customHeight="1" s="49">
-      <c r="A97" s="57" t="n">
+      <c r="N97" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+    </row>
+    <row r="98" ht="159.75" customHeight="1" s="49">
+      <c r="A98" s="57" t="n">
         <v>1919</v>
       </c>
-      <c r="B97" s="57" t="inlineStr">
+      <c r="B98" s="57" t="inlineStr">
         <is>
           <t>2007</t>
         </is>
       </c>
-      <c r="C97" s="57" t="inlineStr">
+      <c r="C98" s="57" t="inlineStr">
         <is>
           <t>1919 – 2007</t>
         </is>
       </c>
-      <c r="D97" s="58" t="inlineStr">
+      <c r="D98" s="58" t="inlineStr">
         <is>
           <t>Suzanne BACHELARD</t>
         </is>
       </c>
-      <c r="E97" s="65" t="inlineStr">
+      <c r="E98" s="65" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Suzanne_Bachelard" title=" Wikipedia"&gt;Suzanne BACHELARD&lt;/a&gt; était une philosophe française spécialiste de phénoménologie et de logique, fille du célèbre Gaston Bachelard. Agrégée de philosophie et docteur ès lettres, elle fut professeur à la Sorbonne et contribua de manière significative à la diffusion et à l'approfondissement de la &lt;a href="https://www.persee.fr/doc/phlou_0035-3841_1954_num_52_34_4491"  title="phénoménologie husserlienne et hegelienne par persée"&gt;phénoménologie husserlienne &lt;/a&gt;  en France. Son travail intellectuel, longtemps éclipsé par la stature de son père, mérite d'être apprécié pour lui-même. &lt;/p&gt; &lt;p&gt; Sa thèse principale, &lt;em&gt;&lt;a href="https://www.persee.fr/doc/phlou_0035-3841_1984_num_82_56_6315"  title="le problème de la logique pure par persée"&gt;La Logique de Husserl : &lt;/a&gt;  étude sur Logique formelle et Logique transcendantale&lt;/em&gt; (1957), est une analyse rigoureuse et pénétrante de la philosophie logique de Husserl, en particulier de la distinction entre logique formelle et logique transcendantale. Cette œuvre constitue une contribution importante à la réception française de la phénoménologie husserlienne et à la compréhension des rapports entre logique formelle et constitution transcendantale du sens. &lt;/p&gt; &lt;p&gt; Elle publia également des travaux sur la temporalité, notamment &lt;em&gt;Une étude sur la phénoménologie du temps de Husserl&lt;/em&gt; et contribua à faire connaître en France des aspects moins explorés de la phénoménologie, en particulier la théorie husserlienne de la conscience intime du temps. Professeur engagée et pédagogue de talent, elle forma plusieurs générations d'étudiants à la rigueur phénoménologique. Son œuvre illustre la richesse et la profondeur de la réception française de la phénoménologie husserlienne dans la seconde moitié du XXe siècle. &lt;/p&gt;</t>
         </is>
       </c>
-      <c r="F97" s="57" t="n"/>
-      <c r="G97" s="59" t="n"/>
-      <c r="H97" s="59" t="inlineStr">
+      <c r="F98" s="57" t="n"/>
+      <c r="G98" s="59" t="n"/>
+      <c r="H98" s="59" t="inlineStr">
         <is>
           <t>https://www.laphilo.fr/pho/sbachelard-mini.webp</t>
         </is>
       </c>
-      <c r="I97" s="48" t="inlineStr">
+      <c r="I98" s="48" t="inlineStr">
         <is>
           <t>https://www.laphilo.fr/photo/sbachelard.webp</t>
         </is>
       </c>
-      <c r="J97" s="48" t="inlineStr">
+      <c r="J98" s="48" t="inlineStr">
         <is>
           <t>epistemologie</t>
         </is>
       </c>
-      <c r="K97" s="48" t="inlineStr">
+      <c r="K98" s="48" t="inlineStr">
         <is>
           <t>Phénoménologie</t>
         </is>
       </c>
-      <c r="L97" s="48" t="inlineStr">
+      <c r="L98" s="48" t="inlineStr">
         <is>
           <t>philosophe française spécialiste de phénoménologie et de logique.</t>
         </is>
       </c>
-      <c r="M97" t="inlineStr">
+      <c r="M98" t="inlineStr">
         <is>
           <t xml:space="preserve">femme</t>
         </is>
       </c>
-      <c r="N97" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-    </row>
-    <row r="98" ht="129.75" customHeight="1" s="49">
-      <c r="A98" s="54" t="n">
+      <c r="N98" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+    </row>
+    <row r="99" ht="129.75" customHeight="1" s="49">
+      <c r="A99" s="54" t="n">
         <v>1920</v>
       </c>
-      <c r="B98" s="54" t="inlineStr">
+      <c r="B99" s="54" t="inlineStr">
         <is>
           <t>2001</t>
         </is>
       </c>
-      <c r="C98" s="54" t="inlineStr">
+      <c r="C99" s="54" t="inlineStr">
         <is>
           <t>1920 – 2001</t>
         </is>
       </c>
-      <c r="D98" s="55" t="inlineStr">
+      <c r="D99" s="55" t="inlineStr">
         <is>
           <t>Jules VUILLEMIN</t>
         </is>
       </c>
-      <c r="E98" s="62" t="inlineStr">
+      <c r="E99" s="62" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Jules_Vuillemin"  title=" Wikipedia"&gt;Jules VUILLEMIN&lt;/a&gt; (1920-2001) est un philosophe français, l’un de ceux qui ont fait connaître en France la &lt;a href="https://hal.science/hal-04409311v1/document" title="Jules Vuillemin, philosdophie analytique contrarié par hal"&gt;philosophie analytique&lt;/a&gt;, en particulier les œuvres de Bertrand Russell, Rudolf Carnap et Willard Van Orman Quine. Ancien élève de l’École normale supérieure, il enseigne à l’université de Clermont-Ferrand, où il fait venir Michel Foucault, puis il est élu en 1962 au Collège de France, à la chaire de philosophie de la connaissance, qu’il occupe jusqu’en 1990.&lt;/p&gt; &lt;p&gt;Ses débuts touchent à &lt;a href="https://lafrancebyzantine.blogspot.com/2016/09/jules-vuillemin-t-il-ete-existentialiste.html"  title="Jules Vuillemin at'il été existantialiste? par lafrancebyzantine"&gt;l’existentialisme&lt;/a&gt; et au marxisme, avec un &lt;em&gt;Essai sur la signification de la mort&lt;/em&gt; (1948), mais il évolue vers un rationalisme rigoureux, attentif aux mathématiques et à la physique. Héritier de Martial Gueroult, il étudie les grands systèmes dans leur cohérence interne : &lt;em&gt;Physique et métaphysique kantiennes&lt;/em&gt; (1955), &lt;em&gt;Mathématiques et métaphysique chez Descartes&lt;/em&gt; (1960), puis &lt;em&gt;La Philosophie de l’algèbre&lt;/em&gt; (1962), qui montre comment les progrès de l’algèbre ont transformé la philosophie.&lt;/p&gt; &lt;p&gt;Dans &lt;em&gt;Nécessité ou contingence&lt;/em&gt; (1984), il part d’une énigme antique de Diodore Cronos sur le possible, et montre que chaque grand système philosophique y répond en renonçant à l’une de ses prémisses, ce qui permet de classer les philosophies. Épistémologue de premier plan, comme Gilles Gaston Granger, il a marqué des penseurs comme Jacques Bouveresse. Ses archives sont conservées au Laboratoire de philosophie et d’histoire des sciences, à Nancy.&lt;/p&gt;</t>
         </is>
       </c>
-      <c r="F98" s="54" t="inlineStr">
+      <c r="F99" s="54" t="inlineStr">
         <is>
           <t>DxKSHJEWZAs</t>
         </is>
       </c>
-      <c r="G98" s="56" t="inlineStr">
+      <c r="G99" s="56" t="inlineStr">
         <is>
           <t>"La reconstruction de la raison (9) - Claudine Tiercelin" par Collège de France</t>
         </is>
       </c>
-      <c r="H98" s="56" t="inlineStr">
+      <c r="H99" s="56" t="inlineStr">
         <is>
           <t>https://www.laphilo.fr/pho/villemin-mini.webp</t>
         </is>
       </c>
-      <c r="J98" s="48" t="inlineStr">
+      <c r="J99" s="48" t="inlineStr">
         <is>
           <t>epistemologie ; logique</t>
         </is>
       </c>
-      <c r="K98" s="48" t="inlineStr">
+      <c r="K99" s="48" t="inlineStr">
         <is>
           <t>Analytique</t>
         </is>
       </c>
-      <c r="L98" s="48" t="inlineStr">
+      <c r="L99" s="48" t="inlineStr">
         <is>
           <t>philosophe français connu pour son travail en philosophie analytique &amp; en épistémologie.</t>
         </is>
       </c>
-      <c r="N98" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-    </row>
-    <row r="99" ht="132" customHeight="1" s="49">
-      <c r="A99" s="57" t="n">
+      <c r="N99" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+    </row>
+    <row r="100" ht="132" customHeight="1" s="49">
+      <c r="A100" s="57" t="n">
         <v>1920</v>
       </c>
-      <c r="B99" s="57" t="inlineStr">
+      <c r="B100" s="57" t="inlineStr">
         <is>
           <t>2016</t>
         </is>
       </c>
-      <c r="C99" s="57" t="inlineStr">
+      <c r="C100" s="57" t="inlineStr">
         <is>
           <t>1920 – 2016</t>
         </is>
       </c>
-      <c r="D99" s="58" t="inlineStr">
+      <c r="D100" s="58" t="inlineStr">
         <is>
           <t>Gilles Gaston GRANGER</t>
         </is>
       </c>
-      <c r="E99" s="59" t="inlineStr">
+      <c r="E100" s="59" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Gilles_Gaston_Granger"   title=" Wikipedia"&gt;Gilles Gaston GRANGER&lt;/a&gt;  était un philosophe  et épistémologue français connu pour son travail sur l'épistémologie comparative et l'application des formes logico-mathématiques aux sciences humaines. Élève de l'École normale supérieure, agrégé de philosophie en 1943 et licencié en mathématiques, &lt;a href="https://www.persee.fr/authority/281588"title=" Gilles Gaston GRANGER par Persée"&gt; il enseigna &lt;/a&gt; au Brésil puis en France.  Il traduisit le "Tractatus logico-philosophicus" de Wittgenstein en français et fonda la revue L'Âge de la Science en 1968. &lt;/p&gt; &lt;p&gt; Il, &lt;a href="https://www.youtube.com/watch?v=koxZPXhxpt0&amp;t=699s" title="
 Rationalité et raisonnement — Gilles-Gaston Granger par Andrea Cirla"&gt;développa &lt;/a&gt; une épistémologie comparatiste, unifiant sciences de la nature et humaines sur une échelle commune, inspirée d'Aristote et d'un rationalisme pragmatique. Il rejeta le platonisme (formes abstraites) et le positivisme strict (lois universelles pour les faits humains), privilégiant les modèles sémantiques et probabilistes en économie ou linguistique.  La raison est pour lui un "travail" et un "style" évolutif, appliquant formes mathématiques à des contenus concrets via abstraction. &lt;/p&gt; &lt;p&gt; Ses Œuvres clés sont : -"Méthodologie économique" paru en 1955 et "La Mathématique sociale du marquis de Condorcet" en 1956 : analyses pionnières des sciences humaines. "Pensée formelle et sciences de l'homme" paru en 1960 : montre comment modéliser l'individuel (économie, langage, histoire). &lt;/p&gt; Il enseigne à l’université de São Paulo de 1947 à 1953, avant d’occuper de 1986 à 1991 une chaire d’épistémologie comparative au Collège de France. Dans &lt;em&gt;Essai d’une philosophie du style&lt;/em&gt; (1968), il montre que même la science, en apparence impersonnelle, porte la marque d’un style, c’est-à-dire d’une manière singulière d’organiser une expérience.</t>
         </is>
       </c>
-      <c r="F99" s="57" t="inlineStr">
+      <c r="F100" s="57" t="inlineStr">
         <is>
           <t>koxZPXhxpt0</t>
         </is>
       </c>
-      <c r="G99" s="59" t="inlineStr">
+      <c r="G100" s="59" t="inlineStr">
         <is>
           <t>Rationalité et raisonnement par Andrea Cirla</t>
         </is>
       </c>
-      <c r="H99" s="59" t="inlineStr">
+      <c r="H100" s="59" t="inlineStr">
         <is>
           <t>https://www.laphilo.fr/pho/granger-mini.webp</t>
         </is>
       </c>
-      <c r="J99" s="48" t="inlineStr">
+      <c r="J100" s="48" t="inlineStr">
         <is>
           <t>epistemologie</t>
         </is>
       </c>
-      <c r="K99" s="48" t="inlineStr">
+      <c r="K100" s="48" t="inlineStr">
         <is>
           <t>Analytique</t>
         </is>
       </c>
-      <c r="L99" s="48" t="inlineStr">
+      <c r="L100" s="48" t="inlineStr">
         <is>
           <t>philosophe français connu pour son travail sur l'épistémologie comparative.</t>
         </is>
       </c>
-      <c r="N99" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-    </row>
-    <row r="100" ht="197.25" customHeight="1" s="49">
-      <c r="A100" s="54" t="n">
-        <v>1921</v>
-      </c>
-      <c r="B100" s="54" t="inlineStr">
-        <is>
-          <t>2011</t>
-        </is>
-      </c>
-      <c r="C100" s="54" t="inlineStr">
-        <is>
-          <t>1921 – 2011</t>
-        </is>
-      </c>
-      <c r="D100" s="55" t="inlineStr">
-        <is>
-          <t>Lucien JERPHAGNON</t>
-        </is>
-      </c>
-      <c r="E100" s="56" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Lucien_Jerphagnon"  title=" Wikipedia"&gt;Lucien JERPHAGNON&lt;/a&gt; était un philosophe français spécialiste de philosophie antique et de &lt;a href="https://fr.wikipedia.org/wiki/Patristique" title="patristique par Wikipediaon "&gt; patristique, &lt;/a&gt; dont les travaux allièrent toujours érudition rigoureuse et accessible pédagogie. Agrégé de philosophie et docteur ès lettres, il fut professeur à l'Université de Caen.  &lt;a href="https://www.youtube.com/watch?v=4i0E9DZQuXI" title="Lucien Jerphagnon par Resonnances"&gt; Sa passion pour le monde &lt;/a&gt;  antique tardif — Rome impériale, néoplatonisme et origines du christianisme — l'amena à produire une œuvre d'une remarquable richesse, à la fois scientifique et destinée au grand public. &lt;/p&gt; &lt;p&gt; Ses travaux académiques portent principalement sur Augustin d'Hippone et sur le néoplatonisme. Sa thèse sur Augustin, &lt;em&gt;Julien dit l'Apostat&lt;/em&gt; (1986), est une biographie intellectuelle et spirituelle de l'empereur qui tenta de restaurer le paganisme face à l'essor du christianisme. Ses études sur Plotin et les néoplatoniciens contribuèrent à renouveler la compréhension de ce courant fondamental pour la philosophie médiévale et moderne. &lt;/p&gt; &lt;p&gt; Mais il se distingua aussi par des ouvrages de haute vulgarisation d'un rare talent littéraire. Son &lt;em&gt;Histoire de la pensée : d'Homère à Jeanne d'Arc&lt;/em&gt; (2 volumes, 1989-1991, réédités plusieurs fois) présente avec vivacité et profondeur le cheminement de la pensée occidentale des origines jusqu'au Moyen Âge. Ses essais sur Augustin — notamment &lt;em&gt;Dieu en tous ses états&lt;/em&gt; et &lt;em&gt;Connais-toi toi-même : Antiquité, christianisme, Islam&lt;/em&gt; — atteignirent un large public cultivé.  &lt;a href="https://www.lucienjerphagnon.com/" title="Lucien Jerphagnon "&gt; Jovial, érudit et conteur &lt;/a&gt;  hors pair, il incarne un idéal rare du philosophe capable d'allier rigueur scientifique et plaisir de communiquer. &lt;/p&gt;  &lt;audio controls title="quelques part dans l’inachevé par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/13915-27.01.2019-ITEMA_21947423-5.mp3" type="audio/mpeg" align="center"&gt;&lt;/audio&gt;  </t>
-        </is>
-      </c>
-      <c r="F100" s="54" t="inlineStr">
-        <is>
-          <t>JsZmhKrSVnc</t>
-        </is>
-      </c>
-      <c r="G100" s="56" t="inlineStr">
-        <is>
-          <t>"Lucien Jerphagnon : les dieux ne sont jamais loin" par sciences humaines</t>
-        </is>
-      </c>
-      <c r="H100" s="56" t="inlineStr">
-        <is>
-          <t>https://www.laphilo.fr/pho/jerphagnon-mini.webp</t>
-        </is>
-      </c>
-      <c r="J100" s="48" t="inlineStr">
-        <is>
-          <t>epistemologie ; spiritualite</t>
-        </is>
-      </c>
-      <c r="K100" s="48" t="inlineStr">
-        <is>
-          <t>Humanisme</t>
-        </is>
-      </c>
-      <c r="L100" s="48" t="inlineStr">
-        <is>
-          <t>philosophe français spécialiste de philosophie antique et de patristique.</t>
-        </is>
-      </c>
       <c r="N100" t="inlineStr">
         <is>
           <t xml:space="preserve">occident</t>
         </is>
       </c>
     </row>
-    <row r="101" ht="342" customHeight="1" s="49">
+    <row r="101" ht="197.25" customHeight="1" s="49">
       <c r="A101" s="54" t="n">
         <v>1921</v>
       </c>
-      <c r="B101" s="54" t="n">
+      <c r="B101" s="54" t="inlineStr">
+        <is>
+          <t>2011</t>
+        </is>
+      </c>
+      <c r="C101" s="54" t="inlineStr">
+        <is>
+          <t>1921 – 2011</t>
+        </is>
+      </c>
+      <c r="D101" s="55" t="inlineStr">
+        <is>
+          <t>Lucien JERPHAGNON</t>
+        </is>
+      </c>
+      <c r="E101" s="56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Lucien_Jerphagnon"  title=" Wikipedia"&gt;Lucien JERPHAGNON&lt;/a&gt; était un philosophe français spécialiste de philosophie antique et de &lt;a href="https://fr.wikipedia.org/wiki/Patristique" title="patristique par Wikipediaon "&gt; patristique, &lt;/a&gt; dont les travaux allièrent toujours érudition rigoureuse et accessible pédagogie. Agrégé de philosophie et docteur ès lettres, il fut professeur à l'Université de Caen.  &lt;a href="https://www.youtube.com/watch?v=4i0E9DZQuXI" title="Lucien Jerphagnon par Resonnances"&gt; Sa passion pour le monde &lt;/a&gt;  antique tardif — Rome impériale, néoplatonisme et origines du christianisme — l'amena à produire une œuvre d'une remarquable richesse, à la fois scientifique et destinée au grand public. &lt;/p&gt; &lt;p&gt; Ses travaux académiques portent principalement sur Augustin d'Hippone et sur le néoplatonisme. Sa thèse sur Augustin, &lt;em&gt;Julien dit l'Apostat&lt;/em&gt; (1986), est une biographie intellectuelle et spirituelle de l'empereur qui tenta de restaurer le paganisme face à l'essor du christianisme. Ses études sur Plotin et les néoplatoniciens contribuèrent à renouveler la compréhension de ce courant fondamental pour la philosophie médiévale et moderne. &lt;/p&gt; &lt;p&gt; Mais il se distingua aussi par des ouvrages de haute vulgarisation d'un rare talent littéraire. Son &lt;em&gt;Histoire de la pensée : d'Homère à Jeanne d'Arc&lt;/em&gt; (2 volumes, 1989-1991, réédités plusieurs fois) présente avec vivacité et profondeur le cheminement de la pensée occidentale des origines jusqu'au Moyen Âge. Ses essais sur Augustin — notamment &lt;em&gt;Dieu en tous ses états&lt;/em&gt; et &lt;em&gt;Connais-toi toi-même : Antiquité, christianisme, Islam&lt;/em&gt; — atteignirent un large public cultivé.  &lt;a href="https://www.lucienjerphagnon.com/" title="Lucien Jerphagnon "&gt; Jovial, érudit et conteur &lt;/a&gt;  hors pair, il incarne un idéal rare du philosophe capable d'allier rigueur scientifique et plaisir de communiquer. &lt;/p&gt;  &lt;audio controls title="quelques part dans l’inachevé par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/13915-27.01.2019-ITEMA_21947423-5.mp3" type="audio/mpeg" align="center"&gt;&lt;/audio&gt;  </t>
+        </is>
+      </c>
+      <c r="F101" s="54" t="inlineStr">
+        <is>
+          <t>JsZmhKrSVnc</t>
+        </is>
+      </c>
+      <c r="G101" s="56" t="inlineStr">
+        <is>
+          <t>"Lucien Jerphagnon : les dieux ne sont jamais loin" par sciences humaines</t>
+        </is>
+      </c>
+      <c r="H101" s="56" t="inlineStr">
+        <is>
+          <t>https://www.laphilo.fr/pho/jerphagnon-mini.webp</t>
+        </is>
+      </c>
+      <c r="J101" s="48" t="inlineStr">
+        <is>
+          <t>epistemologie ; spiritualite</t>
+        </is>
+      </c>
+      <c r="K101" s="48" t="inlineStr">
+        <is>
+          <t>Humanisme</t>
+        </is>
+      </c>
+      <c r="L101" s="48" t="inlineStr">
+        <is>
+          <t>philosophe français spécialiste de philosophie antique et de patristique.</t>
+        </is>
+      </c>
+      <c r="N101" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+    </row>
+    <row r="102" ht="342" customHeight="1" s="49">
+      <c r="A102" s="54" t="n">
+        <v>1921</v>
+      </c>
+      <c r="B102" s="54" t="n">
         <v>2026</v>
       </c>
-      <c r="C101" s="54" t="inlineStr">
+      <c r="C102" s="54" t="inlineStr">
         <is>
           <t>1921 – 2026</t>
         </is>
       </c>
-      <c r="D101" s="55" t="inlineStr">
+      <c r="D102" s="55" t="inlineStr">
         <is>
           <t>Edgar MORIN</t>
         </is>
       </c>
-      <c r="E101" s="56" t="inlineStr">
+      <c r="E102" s="56" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Edgar_Morin"  title=" Wikipedia"&gt;Edgar MORIN&lt;/a&gt; était un philosophe et sociologue français, directeur de recherches émérite au CNRS et président de l'Association pour la pensée complexe. Ancien résistant de la Seconde Guerre mondiale, il a adhéré au Parti communiste français en 1941 avant d'en être exclu en 1951 pour son soutien trop marqué aux États-Unis, ce qui l'a conduit à développer une réflexion critique sur l'endoctrinement politique. &lt;/p&gt; &lt;p&gt; Sa pensée s'articule autour du concept de complexité, qu'il définit comme « ce qui est tissé ensemble », rejetant la pensée simplificatrice qui sépare les disciplines et réduit la réalité à ses éléments simples. Il propose une  &lt;a href="https://www.youtube.com/watch?v=hfcNgSvQygQ" title="Edgar Morin son approche inter-disciplinaire par radio-Canada "&gt;approche transdisciplinaire &lt;/a&gt;  qui relie les connaissances dans un tout englobant, respectant à la fois l'individuel, le singulier et leur contexte global. &lt;/p&gt; &lt;p&gt; Les trois principes fondamentaux de sa pensée complexe sont : le principe dialogique (qui unit deux notions antagonistes indissociables comme l'ordre et le désordre), le principe hologrammatique (la partie est dans le tout et le tout dans la partie), et le principe récursif (les effets produisent eux-mêmes ce qui les produit). Contrairement à la dialectique hégélienne qui cherche une synthèse, Morin maintient la tension entre les opposés dans leur simultanéité et leur interaction. &lt;/p&gt; &lt;p&gt; Son œuvre majeure,  &lt;a href="https://www.youtube.com/watch?v=9IkWz6gJziw" title="Edgar Morin la méthode par Acte Sud Editions "&gt; La Méthode, &lt;/a&gt;  comprend six volumes publiés entre 1977 et 2004 et constitue une véritable &lt;a href="https://fr.wikipedia.org/wiki/La_M%C3%A9thode_(Edgar_Morin)" title="Edgar Morin la Méthode par Wikipédia "&gt;encyclopédie de sa pensée, &lt;/a&gt;  couvrant la nature, la vie, la connaissance de la connaissance, les idées, l'humanité et l'éthique. Parmi ses autres ouvrages importants figurent Autocritique (1951), La Rumeur d'Orléans (1969), Le Paradigme perdu : la nature humaine (1973) et Science avec conscience (1982) où il formule pour la première fois sa notion de complexité. &lt;/p&gt; &lt;p&gt; Il  s'engage activement pour la paix et la conciliation, parrainant la Coordination française pour la décennie de la culture de la paix et de la non-violence créée en 2000, et continue d'analyser les crises contemporaines jusqu'à sa mort, notamment avec Changeons de voie. Les leçons du coronavirus publié en 2020. Son œuvre, traduite en vingt-sept langues dans quarante-deux pays, représente l'un des  &lt;a href="https://www.youtube.com/watch?v=vY3fNDP6KS4" title="Edgar Morin la pensée complexe par Culture Tube "&gt;efforts les plus ambitieux &lt;/a&gt; du XXe siècle pour réformer la pensée face à la complexité du monde. &lt;/p&gt; 
 &lt;audio controls title="Pour moi, le mystère n’est pas la mort, mais la vie par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/20904-26.06.2023-ITEMA_23422542-2023F26101S0177-NET_MFI_B9B6A9F2-D857-4B7A-8438-F7CDA3AE30A5-22-d8591eee606f5d536353797406969978.mp3" type="audio/mpeg" align="center"&gt;&lt;/audio&gt;  
 </t>
         </is>
       </c>
-      <c r="F101" s="54" t="inlineStr">
+      <c r="F102" s="54" t="inlineStr">
         <is>
           <t>U3GKdgvBsU4</t>
         </is>
       </c>
-      <c r="G101" s="56" t="inlineStr">
+      <c r="G102" s="56" t="inlineStr">
         <is>
           <t>Edgard Morin, philosophe à l’état sauvage par France Culture</t>
         </is>
       </c>
-      <c r="H101" s="62" t="inlineStr">
+      <c r="H102" s="62" t="inlineStr">
         <is>
           <t>https://www.laphilo.fr/pho/emorin-mini.webp</t>
         </is>
       </c>
-      <c r="J101" s="48" t="inlineStr">
+      <c r="J102" s="48" t="inlineStr">
         <is>
           <t>epistemologie ; politique ; ethique</t>
         </is>
       </c>
-      <c r="K101" s="48" t="inlineStr">
+      <c r="K102" s="48" t="inlineStr">
         <is>
           <t>Humanisme</t>
         </is>
       </c>
-      <c r="L101" s="48" t="inlineStr">
+      <c r="L102" s="48" t="inlineStr">
         <is>
           <t>philosophe français connu pour sa pensée complexe et son approche  transdisciplinaire.</t>
         </is>
       </c>
-      <c r="M101" t="inlineStr">
+      <c r="M102" t="inlineStr">
         <is>
           <t xml:space="preserve">juive</t>
         </is>
       </c>
-      <c r="N101" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-    </row>
-    <row r="102" ht="209.25" customHeight="1" s="49">
-      <c r="A102" s="57" t="n">
+      <c r="N102" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+    </row>
+    <row r="103" ht="209.25" customHeight="1" s="49">
+      <c r="A103" s="57" t="n">
         <v>1922</v>
       </c>
-      <c r="B102" s="57" t="inlineStr">
+      <c r="B103" s="57" t="inlineStr">
         <is>
           <t>2022</t>
         </is>
       </c>
-      <c r="C102" s="57" t="inlineStr">
+      <c r="C103" s="57" t="inlineStr">
         <is>
           <t>1922 – 2022</t>
         </is>
       </c>
-      <c r="D102" s="58" t="inlineStr">
+      <c r="D103" s="58" t="inlineStr">
         <is>
           <t>Marcel CONCHE</t>
         </is>
       </c>
-      <c r="E102" s="59" t="inlineStr">
+      <c r="E103" s="59" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Marcel_Conche"   title=" Wikipedia"&gt;Marcel CONCHE&lt;/a&gt;  était un philosophe français connu pour son athéisme radical, son naturalisme et son attachement à la philosophie grecque ancienne. Il a longtemps travaillé sur les présocratiques et sur la question du temps, de la mort, du hasard et de &lt;a href="https://www.youtube.com/watch?v=geBN-4kx5dw" title="Marcel CONCHE - Le destin de l'homme est-il celui de solitude ? par Edition M-Editer"&gt; la liberté.&lt;/a&gt; &lt;/p&gt; &lt;p&gt; Il  rejette très tôt toute croyance en Dieu, même s’il a été élevé dans le christianisme. Son argument central est moral : l’existence du mal, en particulier la souffrance des enfants, lui paraît absolument incompatible avec l’idée d’un Dieu bon et juste. Il insiste aussi sur un argument rationnel : la philosophie est l’œuvre de la raison humaine et "ne peut pas rencontrer Dieu" ; introduire Dieu, c’est réimporter une foi pré-donnée dans la réflexion. &lt;/p&gt; &lt;p&gt; Pour lui, l’"absolu", ce n’est pas Dieu mais la Nature, entendue comme réalité infinie, éternelle, englobante, incréée. Il parle  &lt;a href="https://www.youtube.com/watch?v=1m7Egbvphu0" title=" Recueil de pensées - Marcel CONCHE Philosophe naturaliste par PhiloCloud"&gt; d’un naturalisme  &lt;/a&gt; : "il n’existe rien en dehors de la Nature", mais refuse de réduire cela à un simple matérialisme car elle n’est pas seulement un mécanisme de causes et d’effets : &lt;a href="https://www.persee.fr/doc/raipr_0033-9075_2011_num_177_1_4291" title=" Marcel CONCHE Philosophe naturaliste par Persée"&gt; il la décrit &lt;/a&gt; comme improvisatrice, "poète", toujours créatrice et en devenir. &lt;/p&gt; &lt;p&gt; Il s’inspire de Pyrrhon et de Montaigne pour penser que nous n’avons affaire qu’aux apparences, ce qui l’amène à parler à un moment de "nihilisme ontologique". Plus tard, il distingue le "temps immense" de la nature et le temps humain "rétréci" : le devenir est éternel, la nature est éternelle, ce qui rapproche sa lecture d’Héraclite et de Parménide. &lt;/p&gt; &lt;p&gt; La question morale traverse toute son œuvre, notamment dans "Orientation philosophique" et "Le Fondement de la morale".  Il distingue la morale (ce qui vaut absolument, l’exigence d’universalité) de l’éthique (les manières de vivre singulières, les choix personnels). Sa morale reste compatible avec son naturalisme : l’homme est produit par la nature, mais il possède une capacité de liberté qui le rend responsable de ses choix et de ses obligations. &lt;/p&gt;  &lt;audio controls title="Marcel Conche : la philosophie comme pratique de la sagesse par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/11189-22.03.2010-ITEMA_20220693-2010C15000E0045-ITE_00033740_RSCE-21.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;  </t>
         </is>
       </c>
-      <c r="F102" s="57" t="inlineStr">
+      <c r="F103" s="57" t="inlineStr">
         <is>
           <t>VUZsLAcYZiU</t>
         </is>
       </c>
-      <c r="G102" s="59" t="inlineStr">
+      <c r="G103" s="59" t="inlineStr">
         <is>
           <t>"Petit Conseil du philosophe Marcel Conche" par Pierre Tochet</t>
         </is>
       </c>
-      <c r="H102" s="59" t="inlineStr">
+      <c r="H103" s="59" t="inlineStr">
         <is>
           <t>https://www.laphilo.fr/pho/conche-mini.webp</t>
         </is>
       </c>
-      <c r="J102" s="48" t="inlineStr">
+      <c r="J103" s="48" t="inlineStr">
         <is>
           <t>metaphysique ; ethique</t>
         </is>
       </c>
-      <c r="K102" s="48" t="inlineStr">
+      <c r="K103" s="48" t="inlineStr">
         <is>
           <t>Naturalisme</t>
         </is>
       </c>
-      <c r="L102" s="48" t="inlineStr">
+      <c r="L103" s="48" t="inlineStr">
         <is>
           <t>philosophe français connu pour son athéisme radical, son naturalisme.</t>
         </is>
       </c>
-      <c r="N102" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-    </row>
-    <row r="103" ht="171" customHeight="1" s="49">
-      <c r="A103" s="54" t="n">
+      <c r="N103" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+    </row>
+    <row r="104" ht="171" customHeight="1" s="49">
+      <c r="A104" s="54" t="n">
         <v>1922</v>
       </c>
-      <c r="B103" s="54" t="inlineStr">
+      <c r="B104" s="54" t="inlineStr">
         <is>
           <t>2010</t>
         </is>
       </c>
-      <c r="C103" s="54" t="inlineStr">
+      <c r="C104" s="54" t="inlineStr">
         <is>
           <t>1922 – 2010</t>
         </is>
       </c>
-      <c r="D103" s="55" t="inlineStr">
+      <c r="D104" s="55" t="inlineStr">
         <is>
           <t>Pierre HADOT</t>
         </is>
       </c>
-      <c r="E103" s="56" t="inlineStr">
+      <c r="E104" s="56" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Pierre_Hadot"  title=" Wikipedia"&gt;Pierre HADOT&lt;/a&gt; était un philosophe français spécialiste de philosophie antique, dont les travaux sur les « exercices spirituels » de l'Antiquité ont profondément renouvelé la compréhension de la philosophie grecque et romaine. Né à Paris, prêtre catholique puis laïcisé, il fut directeur d'études à l'École pratique des hautes études et professeur au Collège de France. Son œuvre, d'abord destinée aux spécialistes, toucha un large public à partir des années 1990 et influença profondément la réflexion contemporaine sur la philosophie comme art de vivre. &lt;/p&gt; &lt;p&gt; Sa thèse centrale, développée notamment dans &lt;em&gt;Exercices spirituels et philosophie antique&lt;/em&gt; (1981) et &lt;em&gt; &lt;a href="https://www.persee.fr/doc/raipr_0033-9075_1996_num_119_1_3361_t1_0150_0000_3" title="la philosophie antique par persée "&gt;Qu'est-ce que la philosophie antique ? &lt;/a&gt; &lt;/em&gt; (1995), est que la philosophie dans l'Antiquité n'était pas d'abord un discours théorique, mais une pratique transformatrice de soi : un ensemble d'exercices — méditation, dialogue, contemplation, examen de conscience — visant à transformer la façon de voir et de vivre du philosophe. Cette conception, qu'il nomme « philosophie comme manière de vivre », contrastait avec la philosophie universitaire moderne réduite à la production de discours. &lt;/p&gt; &lt;p&gt; Ses contributions à la compréhension du néoplatonisme, de Marc Aurèle et de Plotin sont également fondamentales. Dans &lt;em&gt;La Citadelle intérieure&lt;/em&gt; (1992), il offre une analyse magistrale des &lt;em&gt;Pensées&lt;/em&gt; de Marc Aurèle comme pratique spirituelle stoïcienne. Son influence sur la pensée de Michel Foucault, notamment sur la notion de « souci de soi », est documentée. Il a contribué à faire redécouvrir l'Antiquité non comme un objet d'érudition, mais comme une source vive pour la réflexion contemporaine sur le sens de l'existence. &lt;/p&gt;   &lt;audio controls title="commenrt pierre hadot reliait il l’art de lire et l’art de vivre " par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/22788-07.06.2023-ITEMA_23403099-2023C45539E0108-21.mp3" type="audio/mpeg" align="center"&gt;&lt;/audio&gt;  </t>
         </is>
       </c>
-      <c r="F103" s="54" t="inlineStr">
+      <c r="F104" s="54" t="inlineStr">
         <is>
           <t>L_KcOA3v5oU</t>
         </is>
       </c>
-      <c r="G103" s="56" t="inlineStr">
+      <c r="G104" s="56" t="inlineStr">
         <is>
           <t xml:space="preserve">"Pierre Hadot : La simplicité comme exercice spirituel" par Résonances</t>
         </is>
       </c>
-      <c r="H103" s="56" t="inlineStr">
+      <c r="H104" s="56" t="inlineStr">
         <is>
           <t>https://www.laphilo.fr/pho/hadot-mini.webp</t>
         </is>
       </c>
-      <c r="J103" s="48" t="inlineStr">
+      <c r="J104" s="48" t="inlineStr">
         <is>
           <t>metaphysique ; spiritualite</t>
         </is>
       </c>
-      <c r="K103" s="48" t="inlineStr">
+      <c r="K104" s="48" t="inlineStr">
         <is>
           <t>Stoïcisme ; Herméneutique</t>
         </is>
       </c>
-      <c r="L103" s="48" t="inlineStr">
+      <c r="L104" s="48" t="inlineStr">
         <is>
           <t>philosophe français spécialiste de philosophie antique.</t>
         </is>
       </c>
-      <c r="N103" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-    </row>
-    <row r="104" ht="257.25" customHeight="1" s="49">
-      <c r="A104" s="57" t="n">
+      <c r="N104" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+    </row>
+    <row r="105" ht="257.25" customHeight="1" s="49">
+      <c r="A105" s="57" t="n">
         <v>1923</v>
       </c>
-      <c r="B104" s="57" t="inlineStr">
+      <c r="B105" s="57" t="inlineStr">
         <is>
           <t>2015</t>
         </is>
       </c>
-      <c r="C104" s="57" t="inlineStr">
+      <c r="C105" s="57" t="inlineStr">
         <is>
           <t>1923 – 2015</t>
         </is>
       </c>
-      <c r="D104" s="58" t="inlineStr">
+      <c r="D105" s="58" t="inlineStr">
         <is>
           <t>René GIRARD</t>
         </is>
       </c>
-      <c r="E104" s="65" t="inlineStr">
+      <c r="E105" s="65" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Ren%C3%A9_Girard" title=" Wikipedia"&gt;René GIRARD&lt;/a&gt; était un philosophe, anthropologue et critique littéraire français dont la pensée, souvent qualifiée de "théorie mimétique", repose sur des concepts clés interdépendants qui expliquent la nature du désir humain, de la violence et du sacré. &lt;/p&gt; &lt;p&gt;Nous ne désirons pas intrinsèquement des objets ou des personnes, mais nous désirons ce que les autres désirent. Notre  &lt;a href="https://www.youtube.com/watch?v=9tn7RVVD_bA" title="Le désir mimétique par le Precepteur"&gt;désir est "triangulaire" &lt;/a&gt; : il y a un sujet (celui qui désire), un objet, et un modèle (celui dont le désir influence le sujet). &lt;/p&gt; &lt;p&gt;Le modèle comme médiateur : Le modèle n'est pas simplement une personne qui possède l'objet désiré, mais celui qui nous le révèle comme désirable. &lt;/p&gt; &lt;p&gt;&lt;a href="https://www.youtube.com/watch?v=7scJjspwo9M" title="La rivalité mimétique par le Precepteur"&gt;La rivalité mimétique &lt;/a&gt; : Lorsque plusieurs personnes désirent le même objet, une rivalité mimétique émerge et elle peut devenir intense et se substituer à l'objet initial. &lt;/p&gt; &lt;p&gt;Le désir métaphysique : Il distingue le désir des objets matériels du désir d'être, plus profond car il porte sur quelque chose d'insaisissable. &lt;/p&gt; &lt;p&gt; Dans son ouvrages "Mensonge romantique et vérité romanesque", il montre comment les grands romanciers ont intuitivement compris la nature mimétique du désir et les illusions "romantiques" qui le masquent. &lt;/p&gt; &lt;p&gt; Selon lui, les sociétés humaines ont développé un mécanisme archaïque pour résoudre ces crises mimétiques : le mécanisme du &lt;a href="https://www.youtube.com/watch?v=QYTKoHPrKxI" title=" La fabrique du bouc émissaire par le Parole de Philosophe"&gt;bouc émissaire&lt;/a&gt; dont voici les points clés : &lt;/p&gt; &lt;p&gt;La désignation d'une victime : Au point culminant de la crise, l'attention de la communauté se focalise sur un individu ou un groupe particulier, accusé d'être la cause du désordre. &lt;/p&gt; &lt;p&gt;L'unanimité contre la victime :  &lt;a href="https://www.dailymotion.com/video/xv8mim"  title=" René Girard, la violence et le sacré par le Parole de mySkreen"&gt;La violence mimétique&lt;/a&gt;, initialement diffuse, se canalise et se concentre sur ce bouc émissaire. L'expulsion ou la mort de la victime rétablit temporairement la paix. &lt;/p&gt; &lt;p&gt;La sacralisation de la victime : après avoir été la source du mal, elle est souvent sacralisée. On lui attribue un pouvoir extraordinaire, capable à la fois de provoquer la crise et de la résoudre. &lt;/p&gt; &lt;p&gt;Le rite et le mythe : Les rites sacrificiels et les mythes sont des tentatives de reproduire et de commémorer le meurtre fondateur du bouc émissaire. &lt;/p&gt; &lt;p&gt;Il reste une figure intellectuelle majeure, dont les idées continuent d'inspirer et de provoquer la réflexion sur la nature humaine, la culture et la religion. &lt;/p&gt; &lt;audio controls title="René Girard, des choses cachées depuis la fondation du monde" par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/13915-24.12.2023-ITEMA_23566825-2023C3372E0859-21.mp3" type="audio/mpeg" align="center"&gt;&lt;/audio&gt;  </t>
         </is>
       </c>
-      <c r="F104" s="57" t="inlineStr">
+      <c r="F105" s="57" t="inlineStr">
         <is>
           <t>d9z0BmMCBC4</t>
         </is>
       </c>
-      <c r="G104" s="59" t="inlineStr">
+      <c r="G105" s="59" t="inlineStr">
         <is>
           <t>"Présentation de la théorie mimétique" par Recherche mimétique</t>
         </is>
       </c>
-      <c r="H104" s="59" t="inlineStr">
+      <c r="H105" s="59" t="inlineStr">
         <is>
           <t>https://www.laphilo.fr/pho/girard-mini.webp</t>
         </is>
       </c>
-      <c r="J104" s="48" t="inlineStr">
+      <c r="J105" s="48" t="inlineStr">
         <is>
           <t>epistemologie ; esthetique</t>
         </is>
       </c>
-      <c r="K104" s="48" t="inlineStr">
+      <c r="K105" s="48" t="inlineStr">
         <is>
           <t>Herméneutique</t>
         </is>
       </c>
-      <c r="L104" s="48" t="inlineStr">
+      <c r="L105" s="48" t="inlineStr">
         <is>
           <t>philosophe et anthropologue français père de la "théorie mimétique".</t>
         </is>
       </c>
-      <c r="N104" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-    </row>
-    <row r="105" ht="167.25" customHeight="1" s="49">
-      <c r="A105" s="54" t="n">
+      <c r="N105" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+    </row>
+    <row r="106" ht="167.25" customHeight="1" s="49">
+      <c r="A106" s="54" t="n">
         <v>1923</v>
       </c>
-      <c r="B105" s="54" t="inlineStr">
+      <c r="B106" s="54" t="inlineStr">
         <is>
           <t>2013</t>
         </is>
       </c>
-      <c r="C105" s="54" t="inlineStr">
+      <c r="C106" s="54" t="inlineStr">
         <is>
           <t>1923 – 2013</t>
         </is>
       </c>
-      <c r="D105" s="55" t="inlineStr">
+      <c r="D106" s="55" t="inlineStr">
         <is>
           <t>Jean-Claude MARGOLIN</t>
         </is>
       </c>
-      <c r="E105" s="62" t="inlineStr">
+      <c r="E106" s="62" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Jean-Claude_Margolin"  title=" Wikipedia"&gt;Jean-Claude MARGOLIN&lt;/a&gt; était un philosophe et humaniste français, spécialiste reconnu de la pensée de la Renaissance et notamment d'Érasme de Rotterdam. Agrégé de philosophie et docteur ès lettres, il fut directeur de recherches au CNRS et l'un des fondateurs du Centre d'études supérieures de la Renaissance à Tours. Son œuvre immense, qui combine érudition philologique et analyse philosophique, constitue une contribution majeure à la connaissance de l'humanisme de la Renaissance. &lt;/p&gt; &lt;p&gt; Ses travaux sur Érasme — dont une biographie de référence, &lt;em&gt;&lt;a href="https://www.persee.fr/doc/rhren_0181-6799_1995_num_40_1_2825" title="jean claude Margolin Erasme precepteur par Persée "&gt;Érasme par lui-même&lt;/a&gt; &lt;/em&gt; (1965, réédité plusieurs fois), et de nombreuses éditions critiques et traductions d'œuvres érasmiennes — font de lui l'un des plus grands érasmistes du XXe siècle. Il contribua à montrer la cohérence et la profondeur de la pensée d'Érasme, souvent réduite à un simple « humanisme » de bon sens, en soulignant la rigueur de sa théologie chrétienne, la finesse de son anthropologie et la complexité de son rapport à la Réforme. &lt;/p&gt; &lt;p&gt; Il s'intéressa à l'ensemble de la culture philosophique et littéraire de la Renaissance : Rabelais, Montaigne, Vives, Thomas More, et aux grandes questions de cette époque comme la définition de l'humanisme, les rapports entre foi et raison, l'éducation et la rhétorique. Sa direction de la revue &lt;em&gt;&lt;a href="https://www.persee.fr/doc/rhren_1771-1347_2013_num_76_1_3288" title="jean claude Margolin humaniste par Persée "&gt;Bibliothèque d'Humanisme &lt;/a&gt; et Renaissance&lt;/em&gt; et ses nombreuses contributions collectives firent de lui un animateur central de la recherche internationale sur la Renaissance. Son œuvre témoigne d'une conception exigeante de l'histoire de la philosophie comme restitution vivante d'une pensée dans toute sa richesse. &lt;/p&gt;  &lt;audio controls title=La folie Erasme par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/10467-15.01.2010-ITEMA_20211948-2010C12410E0018-NET_6E4A59B9-E10B-4E2F-A507-FFDDA95137E9_FC-21.mp3" type="audio/mpeg" align="center"&gt;&lt;/audio&gt; </t>
         </is>
       </c>
-      <c r="F105" s="54" t="inlineStr">
+      <c r="F106" s="54" t="inlineStr">
         <is>
           <t>Q_q2-tleirw</t>
         </is>
       </c>
-      <c r="G105" s="56" t="inlineStr">
+      <c r="G106" s="56" t="inlineStr">
         <is>
           <t>"Autour des rébus de Picardie approche historique et anthropologique par Jean-Claude Margolin" par Agence régionale de la langue picarde</t>
         </is>
       </c>
-      <c r="H105" s="56" t="inlineStr">
+      <c r="H106" s="56" t="inlineStr">
         <is>
           <t>https://www.laphilo.fr/pho/margolin-mini.webp</t>
         </is>
       </c>
-      <c r="J105" s="48" t="inlineStr">
+      <c r="J106" s="48" t="inlineStr">
         <is>
           <t>epistemologie</t>
         </is>
       </c>
-      <c r="K105" s="48" t="inlineStr">
+      <c r="K106" s="48" t="inlineStr">
         <is>
           <t>Humanisme</t>
         </is>
       </c>
-      <c r="L105" s="48" t="inlineStr">
+      <c r="L106" s="48" t="inlineStr">
         <is>
           <t>philosophe et humaniste français spécialiste reconnu de la pensée de la Renaissance.</t>
         </is>
       </c>
-      <c r="N105" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-    </row>
-    <row r="106" ht="189.75" customHeight="1" s="49">
-      <c r="A106" s="57" t="n">
+      <c r="N106" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+    </row>
+    <row r="107" ht="189.75" customHeight="1" s="49">
+      <c r="A107" s="57" t="n">
         <v>1924</v>
       </c>
-      <c r="B106" s="57" t="inlineStr">
+      <c r="B107" s="57" t="inlineStr">
         <is>
           <t>1998</t>
         </is>
       </c>
-      <c r="C106" s="57" t="inlineStr">
+      <c r="C107" s="57" t="inlineStr">
         <is>
           <t>1924 – 1998</t>
         </is>
       </c>
-      <c r="D106" s="58" t="inlineStr">
+      <c r="D107" s="58" t="inlineStr">
         <is>
           <t>Jean-François LYOTARD</t>
         </is>
       </c>
-      <c r="E106" s="59" t="inlineStr">
+      <c r="E107" s="59" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Jean-Fran%C3%A7ois_Lyotard"  title=" Wikipedia"&gt;Jean-François LYOTARD&lt;/a&gt; était un philosophe français et figure du &lt;a href="https://fr.wikipedia.org/wiki/Postmodernisme" title="postmoderrnisme par Wikipedia"&gt;postmodernisme. &lt;/a&gt;  Professeur à l'Université de Paris VIII-Vincennes puis à Paris X-Nanterre, avant d'enseigner dans plusieurs universités américaines. Sa pensée embrassa successivement le marxisme critique, la phénoménologie, la philosophie du langage et l'esthétique, pour aboutir à une remise en cause radicale des &lt;a href="https://www.scienceshumaines.com/jean-francois-lyotard-1924-1998-la-fin-des-grands-recits_fr_21377.html" title="la fin des grands réciits par sciences humaines"&gt;« grands récits » &lt;/a&gt; de la modernité. &lt;/p&gt; &lt;p&gt; Son œuvre la plus influente, &lt;em&gt;La Condition postmoderne&lt;/em&gt; (1979), rédigée comme rapport sur le savoir pour le gouvernement du Québec, diagnostiqua avec une clarté saisissante l'épuisement des grands récits de légitimation de la modernité — le progrès, l'émancipation, la vérité — dans les sociétés post-industrielles. Cette « incrédulité envers les métarécits » définit pour lui la condition postmoderne : un monde de jeux de langage multiples et hétérogènes, sans fondement unificateur. Cette thèse, largement diffusée et âprement débattue, fit de lui l'un des théoriciens les plus discutés à l'échelle internationale. &lt;/p&gt; &lt;p&gt; Dans &lt;em&gt;&lt;a href="https://www.persee.fr/doc/homso_0018-4306_1984_num_73_1_2178" title="le Differend par Persée"&gt;Le Différend&lt;/a&gt;&lt;/em&gt; (1983), son œuvre philosophique la plus rigoureuse, il développa une philosophie du langage fondée sur l'hétérogénéité irréductible des régimes de phrases et des genres de discours. Le « différend » désigne la situation d'un tort qui ne peut trouver d'expression dans les règles d'un seul genre de discours. Cette réflexion, nourrie de Wittgenstein et de Kant, débouche sur une éthique de l'obligation de témoigner du différend. Son œuvre sur le sublime kantien, notamment &lt;em&gt;L'Inhumain&lt;/em&gt; (1988) et &lt;em&gt;Leçons sur l'Analytique du Sublime&lt;/em&gt;, est également d'une grande profondeur. &lt;/p&gt;   &lt;audio controls title="Jean François LYOTARD par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/16409-29.05.2009-ITEMA_20182818-2009C6409E0143-ITE_00027090_RSCE-21.mp3" type="audio/mpeg" align="center"&gt;&lt;/audio&gt;  </t>
         </is>
       </c>
-      <c r="F106" s="57" t="inlineStr">
+      <c r="F107" s="57" t="inlineStr">
         <is>
           <t>-P46ExQnBes</t>
         </is>
       </c>
-      <c r="G106" s="59" t="inlineStr">
+      <c r="G107" s="59" t="inlineStr">
         <is>
           <t>"1994 Jean François Lyotard" par gm maal</t>
         </is>
       </c>
-      <c r="H106" s="59" t="inlineStr">
+      <c r="H107" s="59" t="inlineStr">
         <is>
           <t>https://www.laphilo.fr/pho/lyotard-mini.webp</t>
         </is>
       </c>
-      <c r="J106" s="48" t="inlineStr">
+      <c r="J107" s="48" t="inlineStr">
         <is>
           <t>esthetique ; politique</t>
         </is>
       </c>
-      <c r="K106" s="48" t="inlineStr">
+      <c r="K107" s="48" t="inlineStr">
         <is>
           <t>Post Modernisme</t>
         </is>
       </c>
-      <c r="L106" s="48" t="inlineStr">
+      <c r="L107" s="48" t="inlineStr">
         <is>
           <t>philosophe français figure du postmodernisme qui aboutit à une remise en cause radicale.</t>
         </is>
       </c>
-      <c r="N106" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-    </row>
-    <row r="107" ht="185.25" customHeight="1" s="49">
-      <c r="A107" s="54" t="n">
+      <c r="N107" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+    </row>
+    <row r="108" ht="185.25" customHeight="1" s="49">
+      <c r="A108" s="54" t="n">
         <v>1924</v>
       </c>
-      <c r="B107" s="54" t="inlineStr">
+      <c r="B108" s="54" t="inlineStr">
         <is>
           <t>1989</t>
         </is>
       </c>
-      <c r="C107" s="54" t="inlineStr">
+      <c r="C108" s="54" t="inlineStr">
         <is>
           <t>1924 – 1989</t>
         </is>
       </c>
-      <c r="D107" s="55" t="inlineStr">
+      <c r="D108" s="55" t="inlineStr">
         <is>
           <t>Gilbert SIMONDON</t>
         </is>
       </c>
-      <c r="E107" s="56" t="inlineStr">
+      <c r="E108" s="56" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Gilbert_Simondon" title=" Wikipedia"&gt;Gilbert SIMONDON&lt;/a&gt; était un philosophe français, auteur d'une œuvre d'une originalité et d'une profondeur exceptionnelles sur l'individuation, la technique et la relation entre l'humain et la machine. Il fut professeur à l'Université René Descartes (Paris V) et l'un des esprits les plus inventifs de la philosophie française de son époque. Sa pensée, longtemps restée confidentielle, connaît depuis les années 1990 un regain d'intérêt considérable dans les domaines de la philosophie, des sciences humaines et des théories du numérique. &lt;/p&gt; &lt;p&gt; Sa thèse principale, &lt;em&gt; &lt;a href="https://fr.wikipedia.org/wiki/Individuation" title="Individuation par Wikipedia"&gt;L'individuation à la lumière&lt;/a&gt;  des notions de forme et d'information&lt;/em&gt; (soutenue en 1958, publiée dans son intégralité en 2005), est l'une des œuvres philosophiques les plus originales du XXe siècle. Il y développe une ontologie de l'individuation qui renverse la primauté traditionnellement accordée à l'individu constitué : ce n'est pas l'individu qui précède l'individuation, mais l'individuation qui engendre l'individu. Cette thèse, illustrée par des analyses de la physique, de la biologie et de la psychologie, débouche sur une philosophie originale de l'être comme système en déséquilibre permanent. &lt;/p&gt; &lt;p&gt; &lt;a href="https://gilbert.simondon.fr/" title=" gilbert Simonchon"&gt;Sa thèse complémentaire, &lt;/a&gt; &lt;em&gt;Du mode d'existence des objets techniques&lt;/em&gt; (1958), est une philosophie de la technique d'une rare profondeur. Contre la vision instrumentale qui réduit la machine à un simple outil, il montre que les objets techniques ont leur propre mode d'existence, leur propre « genèse » et leur propre « concrétisation ». Il plaide pour une &lt;a href="https://www.youtube.com/watch?v=8JyptY0N2Xc" title="gilles simondon interview on mechanology par Dennis Gordeychuk"&gt;culture technique &lt;/a&gt; qui reconnaîtrait la réalité propre des objets techniques et permettrait à l'homme de s'y rapporter de manière non aliénée. Cette œuvre a influencé des penseurs comme Gilles Deleuze, Bernard Stiegler et de nombreux théoriciens des nouvelles technologies. &lt;/p&gt;  &lt;audio controls title="une philosophie de l’individuation par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/10467-05.04.2016-ITEMA_20953616-2016C12410S0096-21.mp3" type="audio/mpeg" align="center"&gt;&lt;/audio&gt;  </t>
         </is>
       </c>
-      <c r="F107" s="54" t="inlineStr">
+      <c r="F108" s="54" t="inlineStr">
         <is>
           <t>HRqy9vttW-E</t>
         </is>
       </c>
-      <c r="G107" s="56" t="inlineStr">
+      <c r="G108" s="56" t="inlineStr">
         <is>
           <t>"Gilbert Simondon Entretien sur la mécanologie par PrNeix</t>
         </is>
       </c>
-      <c r="H107" s="56" t="inlineStr">
+      <c r="H108" s="56" t="inlineStr">
         <is>
           <t>https://www.laphilo.fr/pho/simondon-mini.webp</t>
         </is>
       </c>
-      <c r="J107" s="48" t="inlineStr">
+      <c r="J108" s="48" t="inlineStr">
         <is>
           <t>epistemologie</t>
         </is>
       </c>
-      <c r="K107" s="48" t="inlineStr">
+      <c r="K108" s="48" t="inlineStr">
         <is>
           <t>Constructivisme</t>
         </is>
       </c>
-      <c r="L107" s="48" t="inlineStr">
+      <c r="L108" s="48" t="inlineStr">
         <is>
           <t>philosophe français auteur d'une œuvre sur la relation entre l'humain et la machine.</t>
         </is>
       </c>
-      <c r="N107" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-    </row>
-    <row r="108" ht="223.5" customHeight="1" s="49">
-      <c r="A108" s="57" t="n">
-        <v>1925</v>
-      </c>
-      <c r="B108" s="57" t="inlineStr">
-        <is>
-          <t>1995</t>
-        </is>
-      </c>
-      <c r="C108" s="57" t="inlineStr">
-        <is>
-          <t>1925 – 1995</t>
-        </is>
-      </c>
-      <c r="D108" s="58" t="inlineStr">
-        <is>
-          <t>Gilles DELEUZE</t>
-        </is>
-      </c>
-      <c r="E108" s="65" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Gilles_Deleuze" title=" Wikipedia"&gt;Gilles DELEUZE&lt;/a&gt; était un philosophe français qui a profondément marqué la pensée contemporaine dans une  &lt;a href="http://sos.philosophie.free.fr/deleuze.php" style="color:#88A1E9" title=" Gilles Deleuze  par SOS philo"&gt;critique radicale&lt;/a&gt;oeuvre foisonnante et complexe.  Au cœur de sa philosophie se trouve une  &lt;a href="https://www.youtube.com/watch?v=4ybvyj_Pk7M" title=" Gilles Deleuze : l'art et les sociétés de contrôle par lINTELLECT FOCUS"&gt;critique radicale&lt;/a&gt; de la pensée traditionnelle occidentale, qu'il accuse d'être dominée par une logique de la représentation, de l'identité et de la négation. &lt;/p&gt; &lt;p&gt; Il cherche à penser la différence en elle-même qui n'est pas secondaire ou dérivée, mais originaire.  Le monde n'est pas constitué d'entités fixes et identiques qui entreraient ensuite en relation, mais d'un flux incessant de différences, de variations et de devenirs. Il conçoit plutôt la pensée comme une force créatrice qui produit des concepts pour appréhender et transformer le réel qui n'est pas statique, mais un processus continu de transformation, d'hybridation et de métamorphose. Ses oeuvres principales sont : &lt;/p&gt; &lt;p&gt;"Différence et Répétition" : Oeuvre métaphysique majeure, où il développe sa pensée de la différence et critique la conception traditionnelle de la répétition comme reproduction de l'identique. &lt;/p&gt; &lt;p&gt;"Logique du sens" : Une exploration des paradoxes du langage et du sens à travers une lecture originale de Lewis Carroll et des stoïciens. &lt;/p&gt; &lt;p&gt;"Qu'est-ce que la philosophie ?" (avec Félix Guattari) : Une réflexion sur la nature de la philosophie comme création de concepts, distincte de la science et de l'art. &lt;/p&gt; &lt;p&gt;  Sa rencontre avec Felix Guattari donne naissance à 2 ouvrages majeurs :&lt;a href="https://www.youtube.com/watch?v=JQE4_2ti_10&amp;t=78s" title=" La pensée politique de Deleuze et Guattari - Partie 1 / L'anti-Oedipe par Politikon"&gt;" L'Anti-Œdipe "&lt;/a&gt;  : Critique radicale de la psychanalyse et une exploration du désir comme force révolutionnaire et &lt;a href="https://www.youtube.com/watch?v=E01RyGu3Zac" title="La pensée politique de Deleuze et Guattari - Partie 2 / Mille Plateaux par Politikon"&gt;" Mille Plateaux "&lt;/a&gt;   : Une œuvre foisonnante qui explore une multitude de thèmes (le territoire, le devenir ) à travers le  &lt;a href="https://www.youtube.com/watch?v=RQ2rJWwXilw" title="The Rhizome - A Thousand Plateaus, Deleuze and Guattari par Then &amp; Now"&gt;concept de Rhizome&lt;/a&gt;. &lt;/p&gt; &lt;p&gt; Il  est un philosophe majeur qui a profondément transformé notre manière de  &lt;a href="https://diacritik.com/category/deleuze/" title=" Deleuze par Diacritik"&gt;penser la différence&lt;/a&gt;, la multiplicité, le devenir et la créativité. &lt;/p&gt; &lt;audio controls title="Gilles Deleuze, notre contemporain" par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/11189-19.11.2012-ITEMA_20421487-2012C15000E0183-ITE_00054426_RSCE-21.mp3" type="audio/mpeg" align="center"&gt;&lt;/audio&gt; </t>
-        </is>
-      </c>
-      <c r="F108" s="57" t="inlineStr">
-        <is>
-          <t>fZlv7iETh9Q</t>
-        </is>
-      </c>
-      <c r="G108" s="59" t="inlineStr">
-        <is>
-          <t>"Comprendre Gilles Deleuze en 3 minutes" par France Culture</t>
-        </is>
-      </c>
-      <c r="H108" s="59" t="inlineStr">
-        <is>
-          <t>https://www.laphilo.fr/pho/deleuze-mini.webp</t>
-        </is>
-      </c>
-      <c r="J108" s="48" t="inlineStr">
-        <is>
-          <t>metaphysique ; esthetique</t>
-        </is>
-      </c>
-      <c r="K108" s="48" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Post-structuralisme ; Accélérationnisme</t>
-        </is>
-      </c>
-      <c r="L108" s="48" t="inlineStr">
-        <is>
-          <t>philosophe français qui chercha à penser la différence en elle-même (French Theory).</t>
-        </is>
-      </c>
       <c r="N108" t="inlineStr">
         <is>
           <t xml:space="preserve">occident</t>
         </is>
       </c>
-      <c r="O108">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="109" ht="152.25" customHeight="1" s="49">
+    </row>
+    <row r="109" ht="223.5" customHeight="1" s="49">
       <c r="A109" s="57" t="n">
         <v>1925</v>
       </c>
       <c r="B109" s="57" t="inlineStr">
         <is>
-          <t>2018</t>
+          <t>1995</t>
         </is>
       </c>
       <c r="C109" s="57" t="inlineStr">
         <is>
-          <t>1925 – 2018</t>
+          <t>1925 – 1995</t>
         </is>
       </c>
       <c r="D109" s="58" t="inlineStr">
         <is>
-          <t>Jean JOLIVET</t>
-        </is>
-      </c>
-      <c r="E109" s="59" t="inlineStr">
-        <is>
-          <t>&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Jean_Jolivet"  title=" Wikipedia"&gt;Jean JOLIVET&lt;/a&gt; était un philosophe français, l'un des grands spécialistes de la philosophie médiévale arabe et latine. Directeur d'études à l'École pratique des hautes études, il consacra l'essentiel de sa carrière à l'étude de la pensée philosophique du Moyen Âge, en accordant une attention particulière aux traditions arabe et syrienne et à leurs interactions avec la philosophie latine. Ses travaux contribuèrent de manière décisive à renouveler la connaissance de cette période longtemps négligée par la philosophie française. &lt;/p&gt; &lt;p&gt; Ses travaux sur Abélard — notamment &lt;em&gt;Arts du langage et théologie chez Abélard&lt;/em&gt; (1969) — constituent une contribution majeure à la compréhension de la logique et de la théologie du XIIe siècle. Il s'intéressa également à la tradition arabe médiévale, notamment à &lt;a href="https://laphilo.fr/frise-philosophes-orientaux.html?p=AL-KINDI" title="Al-Kindi par laphilo "&gt;al-Kindi &lt;/a&gt;  et à la transmission de l'aristotélisme en arabe, contribuant à restituer la richesse et la complexité des échanges philosophiques entre l'Islam et la chrétienté médiévale. &lt;/p&gt; &lt;p&gt; Dans ses travaux sur la philosophie arabe et sur la tradition néoplatonicienne médiévale, il montra comment des penseurs comme al-Farabi, Avicenne et Averroès ne se contentèrent pas de transmettre la philosophie grecque mais la transformèrent et l'enrichirent de manière originale. Ses contributions à l'&lt;em&gt;Histoire de la philosophie&lt;/em&gt; de &lt;a href="https://fr.wikipedia.org/wiki/Pl%C3%A9iade_(XVIe_si%C3%A8cle)" title="Pléiade par wikipedia "&gt;la Pléiade &lt;/a&gt; et à de nombreux ouvrages collectifs firent de lui une référence indispensable pour tous ceux qui s'intéressent à la pensée médiévale. Son œuvre illustre l'importance d'une histoire de la philosophie véritablement comparative et transculturelle. &lt;/p&gt;</t>
+          <t>Gilles DELEUZE</t>
+        </is>
+      </c>
+      <c r="E109" s="65" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Gilles_Deleuze" title=" Wikipedia"&gt;Gilles DELEUZE&lt;/a&gt; était un philosophe français qui a profondément marqué la pensée contemporaine dans une  &lt;a href="http://sos.philosophie.free.fr/deleuze.php" style="color:#88A1E9" title=" Gilles Deleuze  par SOS philo"&gt;critique radicale&lt;/a&gt;oeuvre foisonnante et complexe.  Au cœur de sa philosophie se trouve une  &lt;a href="https://www.youtube.com/watch?v=4ybvyj_Pk7M" title=" Gilles Deleuze : l'art et les sociétés de contrôle par lINTELLECT FOCUS"&gt;critique radicale&lt;/a&gt; de la pensée traditionnelle occidentale, qu'il accuse d'être dominée par une logique de la représentation, de l'identité et de la négation. &lt;/p&gt; &lt;p&gt; Il cherche à penser la différence en elle-même qui n'est pas secondaire ou dérivée, mais originaire.  Le monde n'est pas constitué d'entités fixes et identiques qui entreraient ensuite en relation, mais d'un flux incessant de différences, de variations et de devenirs. Il conçoit plutôt la pensée comme une force créatrice qui produit des concepts pour appréhender et transformer le réel qui n'est pas statique, mais un processus continu de transformation, d'hybridation et de métamorphose. Ses oeuvres principales sont : &lt;/p&gt; &lt;p&gt;"Différence et Répétition" : Oeuvre métaphysique majeure, où il développe sa pensée de la différence et critique la conception traditionnelle de la répétition comme reproduction de l'identique. &lt;/p&gt; &lt;p&gt;"Logique du sens" : Une exploration des paradoxes du langage et du sens à travers une lecture originale de Lewis Carroll et des stoïciens. &lt;/p&gt; &lt;p&gt;"Qu'est-ce que la philosophie ?" (avec Félix Guattari) : Une réflexion sur la nature de la philosophie comme création de concepts, distincte de la science et de l'art. &lt;/p&gt; &lt;p&gt;  Sa rencontre avec Felix Guattari donne naissance à 2 ouvrages majeurs :&lt;a href="https://www.youtube.com/watch?v=JQE4_2ti_10&amp;t=78s" title=" La pensée politique de Deleuze et Guattari - Partie 1 / L'anti-Oedipe par Politikon"&gt;" L'Anti-Œdipe "&lt;/a&gt;  : Critique radicale de la psychanalyse et une exploration du désir comme force révolutionnaire et &lt;a href="https://www.youtube.com/watch?v=E01RyGu3Zac" title="La pensée politique de Deleuze et Guattari - Partie 2 / Mille Plateaux par Politikon"&gt;" Mille Plateaux "&lt;/a&gt;   : Une œuvre foisonnante qui explore une multitude de thèmes (le territoire, le devenir ) à travers le  &lt;a href="https://www.youtube.com/watch?v=RQ2rJWwXilw" title="The Rhizome - A Thousand Plateaus, Deleuze and Guattari par Then &amp; Now"&gt;concept de Rhizome&lt;/a&gt;. &lt;/p&gt; &lt;p&gt; Il  est un philosophe majeur qui a profondément transformé notre manière de  &lt;a href="https://diacritik.com/category/deleuze/" title=" Deleuze par Diacritik"&gt;penser la différence&lt;/a&gt;, la multiplicité, le devenir et la créativité. &lt;/p&gt; &lt;audio controls title="Gilles Deleuze, notre contemporain" par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/11189-19.11.2012-ITEMA_20421487-2012C15000E0183-ITE_00054426_RSCE-21.mp3" type="audio/mpeg" align="center"&gt;&lt;/audio&gt; </t>
         </is>
       </c>
       <c r="F109" s="57" t="inlineStr">
         <is>
-          <t>qP8sVHGvXQs</t>
+          <t>fZlv7iETh9Q</t>
         </is>
       </c>
       <c r="G109" s="59" t="inlineStr">
         <is>
-          <t>" Pierre Abélard avec J.Verger J.Jolivet G.Lobrichon (France Culture 1996)" par palacky</t>
+          <t>"Comprendre Gilles Deleuze en 3 minutes" par France Culture</t>
         </is>
       </c>
       <c r="H109" s="59" t="inlineStr">
         <is>
-          <t>https://www.laphilo.fr/pho/jolivet-mini.webp</t>
+          <t>https://www.laphilo.fr/pho/deleuze-mini.webp</t>
         </is>
       </c>
       <c r="J109" s="48" t="inlineStr">
         <is>
-          <t>metaphysique ; epistemologie</t>
+          <t>metaphysique ; esthetique</t>
         </is>
       </c>
       <c r="K109" s="48" t="inlineStr">
         <is>
-          <t>Herméneutique</t>
+          <t xml:space="preserve">Post-structuralisme ; Accélérationnisme</t>
         </is>
       </c>
       <c r="L109" s="48" t="inlineStr">
         <is>
-          <t>philosophe français spécialiste de la philosophie médiévale arabe et latine.</t>
+          <t>philosophe français qui chercha à penser la différence en elle-même (French Theory).</t>
         </is>
       </c>
       <c r="N109" t="inlineStr">
@@ -7458,1752 +7458,1751 @@
           <t xml:space="preserve">occident</t>
         </is>
       </c>
-    </row>
-    <row r="110" ht="205.5" customHeight="1" s="49">
+      <c r="O109">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="110" ht="152.25" customHeight="1" s="49">
       <c r="A110" s="57" t="n">
         <v>1925</v>
       </c>
-      <c r="B110" s="57" t="n">
+      <c r="B110" s="57" t="inlineStr">
+        <is>
+          <t>2018</t>
+        </is>
+      </c>
+      <c r="C110" s="57" t="inlineStr">
+        <is>
+          <t>1925 – 2018</t>
+        </is>
+      </c>
+      <c r="D110" s="58" t="inlineStr">
+        <is>
+          <t>Jean JOLIVET</t>
+        </is>
+      </c>
+      <c r="E110" s="59" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Jean_Jolivet"  title=" Wikipedia"&gt;Jean JOLIVET&lt;/a&gt; était un philosophe français, l'un des grands spécialistes de la philosophie médiévale arabe et latine. Directeur d'études à l'École pratique des hautes études, il consacra l'essentiel de sa carrière à l'étude de la pensée philosophique du Moyen Âge, en accordant une attention particulière aux traditions arabe et syrienne et à leurs interactions avec la philosophie latine. Ses travaux contribuèrent de manière décisive à renouveler la connaissance de cette période longtemps négligée par la philosophie française. &lt;/p&gt; &lt;p&gt; Ses travaux sur Abélard — notamment &lt;em&gt;Arts du langage et théologie chez Abélard&lt;/em&gt; (1969) — constituent une contribution majeure à la compréhension de la logique et de la théologie du XIIe siècle. Il s'intéressa également à la tradition arabe médiévale, notamment à &lt;a href="https://laphilo.fr/frise-philosophes-orientaux.html?p=AL-KINDI" title="Al-Kindi par laphilo "&gt;al-Kindi &lt;/a&gt;  et à la transmission de l'aristotélisme en arabe, contribuant à restituer la richesse et la complexité des échanges philosophiques entre l'Islam et la chrétienté médiévale. &lt;/p&gt; &lt;p&gt; Dans ses travaux sur la philosophie arabe et sur la tradition néoplatonicienne médiévale, il montra comment des penseurs comme al-Farabi, Avicenne et Averroès ne se contentèrent pas de transmettre la philosophie grecque mais la transformèrent et l'enrichirent de manière originale. Ses contributions à l'&lt;em&gt;Histoire de la philosophie&lt;/em&gt; de &lt;a href="https://fr.wikipedia.org/wiki/Pl%C3%A9iade_(XVIe_si%C3%A8cle)" title="Pléiade par wikipedia "&gt;la Pléiade &lt;/a&gt; et à de nombreux ouvrages collectifs firent de lui une référence indispensable pour tous ceux qui s'intéressent à la pensée médiévale. Son œuvre illustre l'importance d'une histoire de la philosophie véritablement comparative et transculturelle. &lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="F110" s="57" t="inlineStr">
+        <is>
+          <t>qP8sVHGvXQs</t>
+        </is>
+      </c>
+      <c r="G110" s="59" t="inlineStr">
+        <is>
+          <t>" Pierre Abélard avec J.Verger J.Jolivet G.Lobrichon (France Culture 1996)" par palacky</t>
+        </is>
+      </c>
+      <c r="H110" s="59" t="inlineStr">
+        <is>
+          <t>https://www.laphilo.fr/pho/jolivet-mini.webp</t>
+        </is>
+      </c>
+      <c r="J110" s="48" t="inlineStr">
+        <is>
+          <t>metaphysique ; epistemologie</t>
+        </is>
+      </c>
+      <c r="K110" s="48" t="inlineStr">
+        <is>
+          <t>Herméneutique</t>
+        </is>
+      </c>
+      <c r="L110" s="48" t="inlineStr">
+        <is>
+          <t>philosophe français spécialiste de la philosophie médiévale arabe et latine.</t>
+        </is>
+      </c>
+      <c r="N110" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+    </row>
+    <row r="111" ht="205.5" customHeight="1" s="49">
+      <c r="A111" s="57" t="n">
+        <v>1925</v>
+      </c>
+      <c r="B111" s="57" t="n">
         <v>2014</v>
       </c>
-      <c r="C110" s="57" t="inlineStr">
+      <c r="C111" s="57" t="inlineStr">
         <is>
           <t>1925 – 2014</t>
         </is>
       </c>
-      <c r="D110" s="58" t="inlineStr">
+      <c r="D111" s="58" t="inlineStr">
         <is>
           <t>François WAHL</t>
         </is>
       </c>
-      <c r="E110" s="89" t="inlineStr">
+      <c r="E111" s="89" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Fran%C3%A7ois_Wahl"  title=" Wikipedia"&gt;François WAHL&lt;/a&gt; était un philosophe et éditeur français, figure centrale de la vie intellectuelle française de la fin des années 1950 au début des années 1990, surtout connu pour avoir promu le structuralisme et la psychanalyse aux Éditions du Seuil. Il a régné pendant trente ans sur le domaine des sciences humaines et la littérature italienne au Seuil, publiant Jacques Lacan, Françoise Dolto, Paul Ricœur, Roland Barthes, Philippe Sollers, Alain Badiou, Jean-Claude Milner, ainsi que des auteurs italiens comme Carlo Emilio Gadda et Italo Calvino. Il est décrit comme un « structuraliste dans l’âme », construisant son activité éditoriale comme une structure où chaque choix (acceptations, refus, retraductions) faisait système, appliquant la doctrine structuraliste à son métier d’éditeur. &lt;/p&gt; &lt;p&gt; Il est l’auteur de trois ouvrages majeurs :  &lt;a href="https://philosophie.ac-normandie.fr/spip.php?article148" title="qu’est ce que la philosophie par françois Wahl "&gt;Qu’est-ce que le structuralisme ? &lt;/a&gt;, Philosophie (1973), Introduction au discours du tableau (1996) et Le Perçu (2007). Dans Introduction au discours du tableau, il étudie les œuvres de Poussin, Memling ou Bellini pour montrer que le « visible » apparaît sous deux espèces : le paysage et le tableau, articulant ainsi esthétique et théorie du signe. Le Perçu propose une exploration critique des phénoménologies du XXᵉ siècle, en mobilisant les concepts de discours, sujet, désir et énoncé pour formaliser une analyse du « fait esthétique ». &lt;/p&gt; &lt;p&gt; La ligne directrice de sa pensée peut se résumer à un repérage du concept de sujet dans la philosophie contemporaine et son introduction dans le champ de l’esthétique. Il a écrit de nombreux articles discutant les œuvres d’auteurs comme Badiou, Bataille, Barthes, Foucault ou Lacan, et son dernier grand livre, La dissidence du sujet, rassemble ces réflexions sur le sujet, le désir et le discours dans la philosophie et l’art. &lt;/p&gt; &lt;audio controls title="les fluides d’Aristote /hommage à f Wahl par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/12003-17.09.2014-ITEMA_20670365-2014C18006S0260-21.mp3" type="audio/mpeg" align="center"&gt;&lt;/audio&gt;  </t>
         </is>
       </c>
-      <c r="F110" s="57" t="n"/>
-      <c r="G110" s="59" t="n"/>
-      <c r="H110" s="65" t="inlineStr">
+      <c r="F111" s="57" t="n"/>
+      <c r="G111" s="59" t="n"/>
+      <c r="H111" s="65" t="inlineStr">
         <is>
           <t>https://www.laphilo.fr/pho/fwahl-mini.webp</t>
         </is>
       </c>
-      <c r="I110" s="48" t="inlineStr">
+      <c r="I111" s="48" t="inlineStr">
         <is>
           <t>https://www.laphilo.fr/photo/fwahl.webp</t>
         </is>
       </c>
-      <c r="J110" s="48" t="inlineStr">
+      <c r="J111" s="48" t="inlineStr">
         <is>
           <t>metaphysique ; esthetique</t>
         </is>
       </c>
-      <c r="K110" s="48" t="inlineStr">
+      <c r="K111" s="48" t="inlineStr">
         <is>
           <t>Structuralisme ; Phénoménologie</t>
         </is>
       </c>
-      <c r="L110" s="76" t="inlineStr">
+      <c r="L111" s="76" t="inlineStr">
         <is>
           <t xml:space="preserve"> philosophe et éditeur français connu pour avoir promu le structuralisme et la psychanalyse aux Éditions du Seuil.</t>
         </is>
       </c>
-      <c r="N110" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-    </row>
-    <row r="111" ht="246" customHeight="1" s="49">
-      <c r="A111" s="54" t="n">
+      <c r="N111" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+    </row>
+    <row r="112" ht="246" customHeight="1" s="49">
+      <c r="A112" s="54" t="n">
         <v>1926</v>
       </c>
-      <c r="B111" s="54" t="inlineStr">
+      <c r="B112" s="54" t="inlineStr">
         <is>
           <t>1984</t>
         </is>
       </c>
-      <c r="C111" s="54" t="inlineStr">
+      <c r="C112" s="54" t="inlineStr">
         <is>
           <t>1926 - 1984</t>
         </is>
       </c>
-      <c r="D111" s="55" t="inlineStr">
+      <c r="D112" s="55" t="inlineStr">
         <is>
           <t>Michel FOUCAULT</t>
         </is>
       </c>
-      <c r="E111" s="56" t="inlineStr">
+      <c r="E112" s="56" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;p&gt; &lt;a href="https://fr.wikipedia.org/wiki/Michel_Foucault"  title=" Wikipedia"&gt; Michel FOUCAULT&lt;/a&gt; était un philosophe français principalement connu pour son analyse du pouvoir et des mécanismes de contrôle social et sur la manière dont les institutions sociales et les discours produisent des formes spécifiques de savoir et de vérité. &lt;/p&gt; &lt;p&gt; L'une des contributions majeures de Foucault réside dans son concept de &lt;a href="https://fr.wikipedia.org/wiki/Biopolitique"  title=" biopolitique par Wikipedia"&gt;"biopolitique"&lt;/a&gt;. Selon lui, le pouvoir moderne se caractérise par sa capacité à réguler et à contrôler les populations à travers des mécanismes de surveillance et de normalisation. Il a étudié les institutions comme &lt;a href="https://www.youtube.com/watch?v=lhn53WDSDcQ&amp;ab_channel=FranceCulture" title="Histoire de la folie par France Culture "&gt;l'asile&lt;/a&gt;, la prison et &lt;a href="https://www.youtube.com/watch?v=VjsHyppHiZM&amp;ab_channel=AntoineThomas"  title="Michel Foucault à propos de l'école par Antoine Thomas "&gt;l'école&lt;/a&gt; pour comprendre comment le pouvoir s'exerce sur les individus et les groupes. &lt;/p&gt; &lt;p&gt;
 Foucault a également développé le concept &lt;a href="https://www.youtube.com/watch?v=iRlbHG-3oi4&amp;ab_channel=Artesquieu"  title="Michel Foucault- Archéologie du savoir par Artesquieu "&gt;d'"archéologie du savoir"&lt;/a&gt;, qui consiste à analyser les discours et les pratiques historiques pour comprendre comment ils façonnent le savoir et les subjectivités. Il s'est intéressé à l'histoire des sciences, de la médecine, de la psychiatrie et de la sexualité pour montrer comment les catégories de vérité sont produites et maintenues dans la société. Parmi les ouvrages les plus connus de Foucault, on peut citer &lt;a href="https://www.youtube.com/watch?v=H_KPwTTmurI"  title="Michel Foucault- Surveiller et punir par France Culture "&gt;"Surveiller et punir"&lt;/a&gt; (1975), où il explore l'évolution des systèmes de surveillance et de la discipline, et &lt;a href="https://www.youtube.com/watch?v=nfH4ZVmryvA"  title="Michel Foucault- Histoire de la sexualité par Rien ne veut rien dire "&gt;"Histoire de la sexualité" &lt;/a&gt;(1976), une série de livres dans lesquels il analyse la manière dont la sexualité est régulée et normalisée dans la société occidentale. &lt;/p&gt; &lt;p&gt; La pensée de Foucault a suscité de nombreuses critiques et interprétations mais son influence a dépassé les frontières de la France et a touché des intellectuels du monde entier. &lt;/p&gt;   &lt;audio controls title="Le discours philosophique par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/16740-13.05.2023-ITEMA_23377485-2023C49326S0133-21.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt; </t>
         </is>
       </c>
-      <c r="F111" s="54" t="inlineStr">
+      <c r="F112" s="54" t="inlineStr">
         <is>
           <t>pe5HpgZKQjs</t>
         </is>
       </c>
-      <c r="G111" s="56" t="inlineStr">
+      <c r="G112" s="56" t="inlineStr">
         <is>
           <t>"Foucault Interview 1981" par Philosophy Overdose</t>
         </is>
       </c>
-      <c r="H111" s="56" t="inlineStr">
+      <c r="H112" s="56" t="inlineStr">
         <is>
           <t>https://www.laphilo.fr/pho/foucault-mini.webp</t>
         </is>
       </c>
-      <c r="J111" s="48" t="inlineStr">
+      <c r="J112" s="48" t="inlineStr">
         <is>
           <t>politique ; epistemologie</t>
         </is>
       </c>
-      <c r="K111" s="48" t="inlineStr">
+      <c r="K112" s="48" t="inlineStr">
         <is>
           <t xml:space="preserve">Post-structuralisme ; Biopolitique ; Analogisme</t>
         </is>
       </c>
-      <c r="L111" s="48" t="inlineStr">
+      <c r="L112" s="48" t="inlineStr">
         <is>
           <t>philosophe français qui a exploré la folie, la prison et la sexualité.</t>
         </is>
       </c>
-      <c r="N111" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-      <c r="O111">
+      <c r="N112" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+      <c r="O112">
         <v>3</v>
       </c>
     </row>
-    <row r="112" ht="248.25" customHeight="1" s="49">
-      <c r="A112" s="47" t="n">
+    <row r="113" ht="248.25" customHeight="1" s="49">
+      <c r="A113" s="47" t="n">
         <v>1926</v>
       </c>
-      <c r="B112" s="47" t="n">
+      <c r="B113" s="47" t="n">
         <v>1992</v>
       </c>
-      <c r="C112" s="47" t="inlineStr">
+      <c r="C113" s="47" t="inlineStr">
         <is>
           <t>1926 – 1992</t>
         </is>
       </c>
-      <c r="D112" s="47" t="inlineStr">
+      <c r="D113" s="47" t="inlineStr">
         <is>
           <t>Jean MEYENDORFF</t>
         </is>
       </c>
-      <c r="E112" s="48" t="inlineStr">
+      <c r="E113" s="48" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Jean_Meyendorff" title=" Wikipedia"&gt;Jean MEYENDORFF&lt;/a&gt; était un théologien, historien et patrologue orthodoxe français,  figure de la patristique orthodoxe et de la théologie byzantine au XXe siècle. Né à Paris dans une famille russe exilée, formé à l'Institut Saint-Serge de Paris, il s'établit aux États-Unis où il enseigna au Séminaire Saint-Vladimir de New York, dont il fut le doyen, et à l'Université de Fordham et à l'Université de Princeton.&lt;/p&gt;&lt;p&gt;Sa contribution académique principale est l'étude historique et théologique du palamisme — la théologie de Grégoire Palamas sur la distinction entre l'essence et les énergies divines. Sa thèse de doctorat, &lt;em&gt;Introduction à l'étude de Grégoire Palamas&lt;/em&gt; (1959), suivie de sa traduction critique des œuvres de Palamas, constituent des &lt;a href="https://www.youtube.com/watch?v=gSvlrp9sYfU"  title="john meyendorff par the orhodox christian studies"&gt; contributions fondamentales &lt;/a&gt; à la connaissance de la théologie byzantine tardive. Dans son ouvrage &lt;em&gt;Byzantine Theology&lt;/em&gt; (1974), il offre une synthèse remarquable de la théologie byzantine du concile de Nicée au XVe siècle, devenue une référence indispensable pour les études byzantines.&lt;/p&gt;&lt;p&gt;Ses travaux sur le primat dans &lt;a href="https://orthodoxie.com/vient-de-paraitre-decouvrir-les-peres-de-leglise-nouveau-manuel-de-patristique/"  title="découvrir les pères de l’église par  orhodoxie"&gt;l'Église orthodoxe &lt;/a&gt; et sur le rapport entre papauté et orthodoxie constituent des contributions importantes au dialogue œcuménique. Sa réflexion théologique, toujours ancrée dans la tradition patristique byzantine, cherchait à en dégager la pertinence pour les questions contemporaines de l'Église et du monde. Il représente la tradition académique la plus rigoureuse de la patristique orthodoxe, alliant érudition historique et engagement théologique dans un dialogue permanent avec le monde occidental.&lt;/p&gt;   &lt;audio controls title="hommage au père Jean Meyendorff par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/10491-01.11.2013-ITEMA_20543654-2013C3184E0023-21.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt; </t>
         </is>
       </c>
-      <c r="F112" s="47" t="inlineStr">
+      <c r="F113" s="47" t="inlineStr">
         <is>
           <t>Sz_6z0H4aG4</t>
         </is>
       </c>
-      <c r="G112" s="48" t="inlineStr">
+      <c r="G113" s="48" t="inlineStr">
         <is>
           <t>Celebrating the legacy of john Meyendroff par st vladimir’s orthodox</t>
         </is>
       </c>
-      <c r="H112" s="48" t="inlineStr">
+      <c r="H113" s="48" t="inlineStr">
         <is>
           <t>https://www.laphilo.fr/pho/jmeyendorff-mini.webp</t>
         </is>
       </c>
-      <c r="J112" s="48" t="inlineStr">
+      <c r="J113" s="48" t="inlineStr">
         <is>
           <t>spiritualite ; metaphysique</t>
         </is>
       </c>
-      <c r="K112" s="48" t="inlineStr">
+      <c r="K113" s="48" t="inlineStr">
         <is>
           <t xml:space="preserve">Spiritualisme ; Hésychasme</t>
         </is>
       </c>
-      <c r="L112" s="48" t="inlineStr">
+      <c r="L113" s="48" t="inlineStr">
         <is>
           <t>théologien, historien et patrologue orthodoxe français figure de la patristique orthodoxe.</t>
         </is>
       </c>
-      <c r="N112" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-    </row>
-    <row r="113" ht="245.25" customHeight="1" s="49">
-      <c r="A113" s="57" t="n">
-        <v>1928</v>
-      </c>
-      <c r="B113" s="57" t="inlineStr">
-        <is>
-          <t>2009</t>
-        </is>
-      </c>
-      <c r="C113" s="57" t="inlineStr">
-        <is>
-          <t>1928 - 2009</t>
-        </is>
-      </c>
-      <c r="D113" s="58" t="inlineStr">
-        <is>
-          <t>Michel CLOUSCARD</t>
-        </is>
-      </c>
-      <c r="E113" s="59" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Michel_Clouscard"  title=" Wikipedia"&gt;Michel CLOUSCARD&lt;/a&gt; est un philosophe et sociologue français d'origine prolétarienne connu pour ses travaux sur la société de consommation et sa critique du capitalisme. &lt;/p&gt; &lt;p&gt; Il s'est intéressé à la philosophie politique et à la sociologie, en particulier à l'étude des idéologies, de la consommation et de la société de consommation. Il a été influencé par la pensée de Karl Marx et par le concept de l'aliénation, qu'il a cherché à appliquer à la société contemporaine. &lt;/p&gt; &lt;p&gt; Il publie en 1972, un livre quasi prophétique &lt;a href="http://projet.pcf.fr/82152"  title="La pensée de Clouscard, entretien de Aymeric Monville dans La revue du Progrès"&gt; "Néofascisme et idéologie du désir" &lt;/a&gt;  où il décode et décrit le parcours qui mène inexorablement de Cohn-Bendit à Le Pen et &lt;a href="https://www.youtube.com/watch?v=dhq5qHKge7g" title="Le capitalisme de la séduction "&gt; " Le capitalisme de la séduction " &lt;/a&gt; où il dénonce l'entrée forcée de notre époque dans la consommation de masse avec tous les effets néfastes que cela engendre sur l'individu et sur notre environnement. &lt;/p&gt; &lt;p&gt; Clouscard développe également une théorie du "clivage érotique" dans la société capitaliste, affirmant que les désirs et les pulsions sexuelles sont façonnés et manipulés par le système économique. Selon lui, la société capitaliste exploite l'érotisme pour maintenir le contrôle sur les individus et perpétuer le système de production. &lt;/p&gt; &lt;p&gt; En plus de ses travaux sur la société de consommation, Il s'est également intéressé à la politique, à la théorie du pouvoir et à la question de la démocratie. Il a notamment critiqué la notion de démocratie libérale, affirmant qu'elle masque les véritables mécanismes de pouvoir et renforce les inégalités sociales.&lt;/p&gt; &lt;audio controls title="La fin d'un cycle sous nos yeux par France Culture"&gt; &lt;source src="https://cdn.radiofrance.fr/s3/cruiser-production/static/culture/sons/2013/11/s46/NET_FC_b614bad9-f96f-46b2-bb81-af28f807ab54.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt; </t>
-        </is>
-      </c>
-      <c r="F113" s="57" t="inlineStr">
-        <is>
-          <t>iKl9bk8BQqY</t>
-        </is>
-      </c>
-      <c r="G113" s="59" t="inlineStr">
-        <is>
-          <t xml:space="preserve">"L'idéologie du désir par Le Précepteur</t>
-        </is>
-      </c>
-      <c r="H113" s="59" t="inlineStr">
-        <is>
-          <t>https://www.laphilo.fr/pho/clouscard-mini.webp</t>
-        </is>
-      </c>
-      <c r="J113" s="48" t="inlineStr">
-        <is>
-          <t>politique</t>
-        </is>
-      </c>
-      <c r="K113" s="48" t="inlineStr">
-        <is>
-          <t>Marxisme</t>
-        </is>
-      </c>
-      <c r="L113" s="48" t="inlineStr">
-        <is>
-          <t>philosophe français critique du libéralisme libertaire et du capitalisme.</t>
-        </is>
-      </c>
       <c r="N113" t="inlineStr">
         <is>
           <t xml:space="preserve">occident</t>
         </is>
       </c>
     </row>
-    <row r="114" ht="330.75" customHeight="1" s="49">
+    <row r="114" ht="245.25" customHeight="1" s="49">
       <c r="A114" s="57" t="n">
         <v>1928</v>
       </c>
-      <c r="B114" s="57" t="n">
+      <c r="B114" s="57" t="inlineStr">
+        <is>
+          <t>2009</t>
+        </is>
+      </c>
+      <c r="C114" s="57" t="inlineStr">
+        <is>
+          <t>1928 - 2009</t>
+        </is>
+      </c>
+      <c r="D114" s="58" t="inlineStr">
+        <is>
+          <t>Michel CLOUSCARD</t>
+        </is>
+      </c>
+      <c r="E114" s="59" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Michel_Clouscard"  title=" Wikipedia"&gt;Michel CLOUSCARD&lt;/a&gt; est un philosophe et sociologue français d'origine prolétarienne connu pour ses travaux sur la société de consommation et sa critique du capitalisme. &lt;/p&gt; &lt;p&gt; Il s'est intéressé à la philosophie politique et à la sociologie, en particulier à l'étude des idéologies, de la consommation et de la société de consommation. Il a été influencé par la pensée de Karl Marx et par le concept de l'aliénation, qu'il a cherché à appliquer à la société contemporaine. &lt;/p&gt; &lt;p&gt; Il publie en 1972, un livre quasi prophétique &lt;a href="http://projet.pcf.fr/82152"  title="La pensée de Clouscard, entretien de Aymeric Monville dans La revue du Progrès"&gt; "Néofascisme et idéologie du désir" &lt;/a&gt;  où il décode et décrit le parcours qui mène inexorablement de Cohn-Bendit à Le Pen et &lt;a href="https://www.youtube.com/watch?v=dhq5qHKge7g" title="Le capitalisme de la séduction "&gt; " Le capitalisme de la séduction " &lt;/a&gt; où il dénonce l'entrée forcée de notre époque dans la consommation de masse avec tous les effets néfastes que cela engendre sur l'individu et sur notre environnement. &lt;/p&gt; &lt;p&gt; Clouscard développe également une théorie du "clivage érotique" dans la société capitaliste, affirmant que les désirs et les pulsions sexuelles sont façonnés et manipulés par le système économique. Selon lui, la société capitaliste exploite l'érotisme pour maintenir le contrôle sur les individus et perpétuer le système de production. &lt;/p&gt; &lt;p&gt; En plus de ses travaux sur la société de consommation, Il s'est également intéressé à la politique, à la théorie du pouvoir et à la question de la démocratie. Il a notamment critiqué la notion de démocratie libérale, affirmant qu'elle masque les véritables mécanismes de pouvoir et renforce les inégalités sociales.&lt;/p&gt; &lt;audio controls title="La fin d'un cycle sous nos yeux par France Culture"&gt; &lt;source src="https://cdn.radiofrance.fr/s3/cruiser-production/static/culture/sons/2013/11/s46/NET_FC_b614bad9-f96f-46b2-bb81-af28f807ab54.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt; </t>
+        </is>
+      </c>
+      <c r="F114" s="57" t="inlineStr">
+        <is>
+          <t>iKl9bk8BQqY</t>
+        </is>
+      </c>
+      <c r="G114" s="59" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"L'idéologie du désir par Le Précepteur</t>
+        </is>
+      </c>
+      <c r="H114" s="59" t="inlineStr">
+        <is>
+          <t>https://www.laphilo.fr/pho/clouscard-mini.webp</t>
+        </is>
+      </c>
+      <c r="J114" s="48" t="inlineStr">
+        <is>
+          <t>politique</t>
+        </is>
+      </c>
+      <c r="K114" s="48" t="inlineStr">
+        <is>
+          <t>Marxisme</t>
+        </is>
+      </c>
+      <c r="L114" s="48" t="inlineStr">
+        <is>
+          <t>philosophe français critique du libéralisme libertaire et du capitalisme.</t>
+        </is>
+      </c>
+      <c r="N114" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+    </row>
+    <row r="115" ht="330.75" customHeight="1" s="49">
+      <c r="A115" s="57" t="n">
+        <v>1928</v>
+      </c>
+      <c r="B115" s="57" t="n">
         <v>2017</v>
       </c>
-      <c r="C114" s="57" t="inlineStr">
+      <c r="C115" s="57" t="inlineStr">
         <is>
           <t xml:space="preserve">1928 – 2017</t>
         </is>
       </c>
-      <c r="D114" s="58" t="inlineStr">
+      <c r="D115" s="58" t="inlineStr">
         <is>
           <t>Hubert DAMISCH</t>
         </is>
       </c>
-      <c r="E114" s="74" t="inlineStr">
+      <c r="E115" s="74" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Hubert_Damisch"  title=" Wikipedia"&gt;Hubert DAMISCH&lt;/a&gt; était un philosophe, historien et théoricien de l’art français, figure majeure de la pensée visuelle et de l’iconologie analytique. Il conçoit l’histoire de l’art comme une discipline philosophique, travaillant non pas sur les œuvres comme objets clos, mais avec elles, en tant qu’elles posent des  &lt;a href="https://www.persee.fr/doc/colan_0336-1500_1987_num_74_1_1016_t1_0126_0000_2" title="hubert Damisch l’origine de la perspective par persée"&gt;problèmes d’interprétation &lt;/a&gt; ouvrant des perspectives singulières sur les structures d’une culture. Il développe une « iconologie analytique », méthode qui cherche à déterminer non pas la signification des œuvres, mais leur force ostensive, en préservant leur résistance à l’interprétation. Cette approche s’enracine dans la sémiotique visuelle et l’attention aux caractéristiques plastiques du signe, au-delà des formes purement linguistiques.&lt;/p&gt; &lt;p&gt; Son ouvrage majeur, Théorie du /nuage/ (1972), est considéré comme révolutionnaire dans le champ de l’histoire de l’art et de la culture visuelle. Il y distingue le « nuage » (phénomène atmosphérique réel) du « /nuage/ » (représentation artistique du nuage dans la peinture), montrant comment cette figure déstabilise l’espace perspectif occidental et introduit une histoire discontinue, non linéaire, de la peinture. Ce livre dépasse la narration traditionnelle de l’histoire de l’art, révélant ses ruptures et sa matérialité signifiante. &lt;/p&gt; &lt;p&gt; Dans L’Origine de la perspective (1987/1992), il  propose une réflexion approfondie sur la perspective comme objet de connaissance et de pensée, du dispositif de Brunelleschi aux Ménines de Velázquez. Il montre que l’histoire de la perspective, constituée au Quattrocento, est plurielle et que la science y rencontre le théâtre, refusant tout récit linéaire et évolutionniste. Cet ouvrage est devenu un pilier des « perspective studies », même s’il ouvre aussi vers une philosophie où la pensée n’est plus monopolisée par la philosophie traditionnelle. &lt;/p&gt; &lt;p&gt; Il est reconnu comme un fondateur de la sémiotique visuelle et de l’histoire/théorie de l’art en France, avec une posture « omnivore et pérégrine » qui traverse peinture, architecture, photographie, cinéma et théâtre. Son manifeste « Histoire et/ou théorie de l’art » (1971) et ses travaux sur le Jugement de Pâris, Piero della Francesca, Goya ou la photographie ont durablement transformé la discipline, en insistant sur l’idée d’« atteindre des moments et des objets qui “font histoire” dans l’art » &lt;/p&gt; 
 &lt;audio controls title="Hubert DAMISCH par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/10080-03.07.2012-ITEMA_20320269-2012C3403E0116-ITE_00052122_RSCE-21.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt; </t>
         </is>
       </c>
-      <c r="F114" s="57" t="inlineStr">
+      <c r="F115" s="57" t="inlineStr">
         <is>
           <t>69h9xzbSHdo</t>
         </is>
       </c>
-      <c r="G114" s="59" t="inlineStr">
+      <c r="G115" s="59" t="inlineStr">
         <is>
           <t>hubert Damisch, déplacé par CRAL</t>
         </is>
       </c>
-      <c r="H114" s="65" t="inlineStr">
+      <c r="H115" s="65" t="inlineStr">
         <is>
           <t>https://www.laphilo.fr/pho/hdamisch-mini.webp</t>
         </is>
       </c>
-      <c r="J114" s="48" t="inlineStr">
+      <c r="J115" s="48" t="inlineStr">
         <is>
           <t xml:space="preserve">esthetique </t>
         </is>
       </c>
-      <c r="K114" s="48" t="inlineStr">
+      <c r="K115" s="48" t="inlineStr">
         <is>
           <t>Symbolisme</t>
         </is>
       </c>
-      <c r="L114" s="85" t="inlineStr">
+      <c r="L115" s="85" t="inlineStr">
         <is>
           <t>philosophe, historien et théoricien de l’art français, figure majeure de la pensée visuelle et de l’iconologie analytique.</t>
         </is>
       </c>
-      <c r="N114" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-    </row>
-    <row r="115" ht="228.75" customHeight="1" s="49">
-      <c r="A115" s="57" t="n">
+      <c r="N115" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+    </row>
+    <row r="116" ht="228.75" customHeight="1" s="49">
+      <c r="A116" s="57" t="n">
         <v>1929</v>
       </c>
-      <c r="B115" s="57" t="n">
+      <c r="B116" s="57" t="n">
         <v>2024</v>
       </c>
-      <c r="C115" s="57" t="inlineStr">
+      <c r="C116" s="57" t="inlineStr">
         <is>
           <t>1929 – 2024</t>
         </is>
       </c>
-      <c r="D115" s="58" t="inlineStr">
+      <c r="D116" s="58" t="inlineStr">
         <is>
           <t>Bernard BOURGEOIS</t>
         </is>
       </c>
-      <c r="E115" s="83" t="inlineStr">
+      <c r="E116" s="83" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Bernard_Bourgeois"  title=" Wikipedia"&gt;Bernard BOURGEOIS&lt;/a&gt; était un philosophes français connu comme le grand traducteur et interprète de Hegel en langue française. Ancien élève de l’École normale supérieure, agrégé de philosophie, il a enseigné à Lyon puis à Paris I–Sorbonne, avant d’être élu à l’Académie des sciences morales et politiques, qu’il a présidée en 2014. &lt;/p&gt; &lt;p&gt; Sa philosophie se définit d’abord par un  &lt;a href="https://academiesciencesmoralesetpolitiques.fr/membres-titulaires/section-i-philosophie-2/bernard-bourgeois/" title="bernard bourgeois carrière et travaux académique par académie des sciences"&gt;travail historique et philologique &lt;/a&gt;  monumental sur l’idéalisme allemand, de Kant à Marx, avec un centre de gravité hégélien. Il a traduit et annoté des milliers de pages de Hegel (Phénoménologie de l’esprit, Encyclopédie des sciences philosophiques, Science de la logique, écrits de droit naturel, textes pédagogiques), en s’efforçant de restituer la rigueur conceptuelle et la cohérence systématique de la pensée hégélienne. &lt;/p&gt; &lt;p&gt; Au-delà de la traduction, il défend une lecture de Hegel comme philosophe de la liberté et de la raison dans l’histoire. Pour lui, Hegel ne célèbre pas un destin aveugle ni une fin dogmatique de l’histoire, mais pense l’historicité de l’Esprit comme déploiement de formes de rationalité et d’institutions où la liberté devient concrète (droit, État, vie éthique). Cette orientation se retrouve dans ses communications à l’Académie, par exemple sur &lt;a href="https://www.youtube.com/watch?v=YRErwGZWBqc" title="bernard bourgeois , hegel et le droit par pkpdlm"&gt;« Hegel et le droit » &lt;/a&gt;  ou « La fin de l’histoire selon Hegel », où il montre comment la philosophie hégélienne éclaire les problèmes politiques et juridiques modernes. &lt;/p&gt; &lt;p&gt; Sa propre philosophie n’est pas un système indépendant de type hégélien, mais une méditation exigeante sur les conditions de la rationalité spéculative et sur la manière dont la philosophie peut habiter son époque. Il insiste sur la nécessité de « relire constamment » Hegel plutôt que de le lire une fois pour toutes, parce que la pensée spéculative demande un travail continu de reprise et d’approfondissement. En ce sens, sa philosophie est une pratique de la raison qui se forme au contact des textes, des concepts et des problèmes que Hegel a portés à leur plus haute expression. &lt;/p&gt; 
 </t>
         </is>
       </c>
-      <c r="F115" s="57" t="inlineStr">
+      <c r="F116" s="57" t="inlineStr">
         <is>
           <t>KKg1YV0Kviw</t>
         </is>
       </c>
-      <c r="G115" s="59" t="inlineStr">
+      <c r="G116" s="59" t="inlineStr">
         <is>
           <t>Bernard Bourgeois le concept par Librairie Tropiques</t>
         </is>
       </c>
-      <c r="H115" s="65" t="inlineStr">
+      <c r="H116" s="65" t="inlineStr">
         <is>
           <t>https://www.laphilo.fr/pho/bbourgeois-mini.webp</t>
         </is>
       </c>
-      <c r="J115" s="48" t="inlineStr">
+      <c r="J116" s="48" t="inlineStr">
         <is>
           <t>logique ; langage</t>
         </is>
       </c>
-      <c r="K115" s="48" t="inlineStr">
+      <c r="K116" s="48" t="inlineStr">
         <is>
           <t xml:space="preserve">Idéalisme allemand  </t>
         </is>
       </c>
-      <c r="L115" s="76" t="inlineStr">
+      <c r="L116" s="76" t="inlineStr">
         <is>
           <t xml:space="preserve">philosophe français connu comme le grand traducteur et interprète de Hegel en langue française. </t>
         </is>
       </c>
-      <c r="N115" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-    </row>
-    <row r="116" ht="216" customHeight="1" s="49">
-      <c r="A116" s="54" t="n">
+      <c r="N116" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+    </row>
+    <row r="117" ht="216" customHeight="1" s="49">
+      <c r="A117" s="54" t="n">
         <v>1929</v>
       </c>
-      <c r="B116" s="54" t="inlineStr">
+      <c r="B117" s="54" t="inlineStr">
         <is>
           <t>2007</t>
         </is>
       </c>
-      <c r="C116" s="54" t="inlineStr">
+      <c r="C117" s="54" t="inlineStr">
         <is>
           <t>1929 – 2007</t>
         </is>
       </c>
-      <c r="D116" s="55" t="inlineStr">
+      <c r="D117" s="55" t="inlineStr">
         <is>
           <t>Jean BAUDRILLARD</t>
         </is>
       </c>
-      <c r="E116" s="56" t="inlineStr">
+      <c r="E117" s="56" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Jean_Baudrillard"  title=" Wikipedia"&gt;Jean BAUDRILLARD&lt;/a&gt;  était un philosophe français du courant dit "postmoderne", connu pour ses analyses de la société de consommation, des médias et des simulacres, ainsi que pour les notions  &lt;a href="https://www.youtube.com/watch?v=kiHpGAjA33E" title="Baudrillard - La Disparition Du Monde Réel par Mornhugss"&gt;d'hyperréalité &lt;/a&gt; et de "désert du réel". &lt;/p&gt; &lt;p&gt; Penseur inclassable, il se décrit lui‑même comme "pataphysicien à 20 ans, situationniste à 30, utopiste à 40, transversal à 50, viral et métaleptique à 60". Né à Reims, il enseigne la sociologie à l’université de Nanterre. Ses livres, de &lt;em&gt;La Société de consommation&lt;/em&gt; (1970) à &lt;em&gt;Simulacres et Simulation&lt;/em&gt; (1981), que l’on aperçoit dans le film &lt;em&gt;Matrix&lt;/em&gt;, ont eu un écho mondial. &lt;/p&gt; &lt;p&gt; Il est associé à quelques idées devenues classiques pour penser la modernité tardive. Pour lui, dans les sociétés dominées par les médias, la publicité et les images, les signes ne renvoient plus à une réalité préexistante, mais se renvoient les uns aux autres, produisant un monde "plus vrai que vrai" qu’il appelle hyperréel.  Les simulations (images télévisuelles, flux financiers, modèles informatiques) ont remplacé leurs référents, de sorte qu’il ne reste que le &lt;a href="https://www.lemonde.fr/culture/article/2017/03/02/dix-ans-apres-sa-mort-baudrillard-fait-toujours-penser_5088278_3246.html" title="Dix ans après sa mort, Baudrillard fait toujours penser par Le Monde"&gt;désert du réel  &lt;/a&gt; derrière la prolifération des signes. La société se dissout dans une masse silencieuse de spectateurs qui cherchent le spectacle plutôt que le sens, ce qui fait  "imploser" les catégories classiques de classe, sujet politique ou opinion publique. &lt;/p&gt; &lt;p&gt; Héritier critique du marxisme : ses premiers travaux combinent économie politique et sémiologie, mais il rompt ensuite avec l’idéologie de la production, qu’il considère elle‑même comme partie prenante du système qu’elle prétend critiquer.  &lt;/p&gt; &lt;audio controls title="Penser le monde avec Jean Baudrillard par France Culture"&gt; &lt;source src="https://cdn.radiofrance.fr/s3/cruiser-production/2019/09/4e5722ea-569d-4069-8321-69b5e27ba665/flyvonnetok.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;</t>
         </is>
       </c>
-      <c r="F116" s="54" t="inlineStr">
+      <c r="F117" s="54" t="inlineStr">
         <is>
           <t>p7RykSyUywI</t>
         </is>
       </c>
-      <c r="G116" s="56" t="inlineStr">
+      <c r="G117" s="56" t="inlineStr">
         <is>
           <t>"
 Jean Baudrillard, entre philosophie et provocation chez Thierry Ardisson " par INA Arditube</t>
         </is>
       </c>
-      <c r="H116" s="62" t="inlineStr">
+      <c r="H117" s="62" t="inlineStr">
         <is>
           <t>https://www.laphilo.fr/pho/baudrillard-mini.webp</t>
         </is>
       </c>
-      <c r="J116" s="48" t="inlineStr">
+      <c r="J117" s="48" t="inlineStr">
         <is>
           <t>politique ; esthetique</t>
         </is>
       </c>
-      <c r="K116" s="48" t="inlineStr">
+      <c r="K117" s="48" t="inlineStr">
         <is>
           <t>Post Modernisme</t>
         </is>
       </c>
-      <c r="L116" s="48" t="inlineStr">
+      <c r="L117" s="48" t="inlineStr">
         <is>
           <t>philosophe français majeur du postmodernisme &amp; connu pour ses analyses.</t>
         </is>
       </c>
-      <c r="N116" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-    </row>
-    <row r="117" ht="201.75" customHeight="1" s="49">
-      <c r="A117" s="57" t="n">
+      <c r="N117" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+    </row>
+    <row r="118" ht="201.75" customHeight="1" s="49">
+      <c r="A118" s="57" t="n">
         <v>1930</v>
       </c>
-      <c r="B117" s="57" t="inlineStr">
+      <c r="B118" s="57" t="inlineStr">
         <is>
           <t>2004</t>
         </is>
       </c>
-      <c r="C117" s="57" t="inlineStr">
+      <c r="C118" s="57" t="inlineStr">
         <is>
           <t>1930 – 2004</t>
         </is>
       </c>
-      <c r="D117" s="58" t="inlineStr">
+      <c r="D118" s="58" t="inlineStr">
         <is>
           <t>Jacques DERRIDA</t>
         </is>
       </c>
-      <c r="E117" s="59" t="inlineStr">
+      <c r="E118" s="59" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Jacques_Derrida"  title=" Wikipedia"&gt;Jacques DERRIDA&lt;/a&gt; était un philosophe français, né en Algérie, connu pour avoir développé le  &lt;a href="https://www.youtube.com/watch?v=5-fZwLNIB9M" style="color:#88A1E9" title=" La Déconstruction - DERRIDA par EXHAL"&gt;Déconstructionnisme&lt;/a&gt;. C 'est une stratégie de lecture critique qui vise à déconstruire les oppositions binaires (par exemple, parole/écriture, homme/femme) qui structurent la pensée occidentale. Elle met en lumière l'instabilité et l'indécidabilité inhérentes au langage et aux textes. Elle révèle comment les textes contiennent en eux-mêmes les forces qui minent leurs propres affirmations et significations apparentes. &lt;/p&gt; &lt;p&gt;De la grammatologie : Un texte fondamental où il critique le logocentrisme (la primauté accordée à la parole sur l'écriture dans la pensée occidentale). &lt;/p&gt; &lt;p&gt;L'Écriture et la différence : Recueil d'essais appliquant la déconstruction à divers auteurs et concepts. &lt;/p&gt; &lt;p&gt;La Voix et le phénomène : Une critique de la phénoménologie de Husserl. &lt;/p&gt; &lt;p&gt;Marges de la philosophie : Un autre recueil d'essais explorant les marges de la philosophie. &lt;/p&gt; &lt;p&gt;Glas : Une œuvre plus expérimentale juxtaposant des réflexions sur Hegel et Genet. &lt;/p&gt; &lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Spectres_de_Marx"  title="Spectres de Marx par Wikipedia"&gt;Spectres de Marx&lt;/a&gt;  : Une réflexion sur l'héritage de Marx après la chute du mur de Berlin. &lt;/p&gt; &lt;p&gt;&lt;a href="https://www.youtube.com/watch?v=sIMjxDbFK7E" title=" Jacques Derrida - Entretiens à propos de ses livres "Apories" et "Résistance de la psychanalyse" par Artesquieu"&gt;Aporie&lt;/a&gt; : Essai aborde les questions que soulèvent aussi bien le projet d'une histoire culturelle ou d'une anthropologie de la mort. &lt;/p&gt; &lt;p&gt; Il a marqué la pensée contemporaine par sa déconstruction des concepts fondamentaux de la philosophie occidentale et son exploration de la complexité du langage et du sens. C'est une   &lt;a href="https://www.youtube.com/watch?v=n_JqaGhpZ7s" title=" décès de Jacques DERRDA par INA Politique"&gt;figure incontournable&lt;/a&gt; pour comprendre les développements intellectuels de la fin du XXe siècle. &lt;/p&gt;   &lt;audio controls title="Jacques Derrida, le déconstructionniste par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/10351-14.12.1998-ITEMA_23647145-1998C3500E0186-21.mp3" type="audio/mpeg" align="center"&gt;&lt;/audio&gt;  &lt;</t>
         </is>
       </c>
-      <c r="F117" s="57" t="inlineStr">
+      <c r="F118" s="57" t="inlineStr">
         <is>
           <t>bv_R2tpj_tY</t>
         </is>
       </c>
-      <c r="G117" s="59" t="inlineStr">
+      <c r="G118" s="59" t="inlineStr">
         <is>
           <t>"La déconstruction, ou penser autrement le monde selon Jacques Derrida" par Ina Culture</t>
         </is>
       </c>
-      <c r="H117" s="59" t="inlineStr">
+      <c r="H118" s="59" t="inlineStr">
         <is>
           <t>https://www.laphilo.fr/pho/derrida-mini.webp</t>
         </is>
       </c>
-      <c r="J117" s="48" t="inlineStr">
+      <c r="J118" s="48" t="inlineStr">
         <is>
           <t>epistemologie ; esthetique</t>
         </is>
       </c>
-      <c r="K117" s="48" t="inlineStr">
+      <c r="K118" s="48" t="inlineStr">
         <is>
           <t>Déconstructionnisme</t>
         </is>
       </c>
-      <c r="L117" s="48" t="inlineStr">
+      <c r="L118" s="48" t="inlineStr">
         <is>
           <t>philosophe français qui développa la pensée déconstructionniste.</t>
         </is>
       </c>
-      <c r="M117" t="inlineStr">
+      <c r="M118" t="inlineStr">
         <is>
           <t xml:space="preserve">juive</t>
         </is>
       </c>
-      <c r="N117" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-      <c r="O117">
+      <c r="N118" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+      <c r="O118">
         <v>3</v>
       </c>
     </row>
-    <row r="118" ht="226.5" customHeight="1" s="49">
-      <c r="A118" s="54" t="n">
-        <v>1930</v>
-      </c>
-      <c r="B118" s="54" t="inlineStr">
-        <is>
-          <t>2002</t>
-        </is>
-      </c>
-      <c r="C118" s="54" t="inlineStr">
-        <is>
-          <t>1930 – 2002</t>
-        </is>
-      </c>
-      <c r="D118" s="55" t="inlineStr">
-        <is>
-          <t>Pierre BOURDIEU</t>
-        </is>
-      </c>
-      <c r="E118" s="56" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Pierre_Bourdieu"  title=" Wikipedia"&gt;Pierre BOURDIEU&lt;/a&gt; était un philosophe et sociologue français  qui a développé un ensemble de concepts interdépendants pour analyser la structure sociale et les &lt;a href="https://www.youtube.com/watch?v=LQ6UeaV-VTs"  title=" BOURDIEU - La reproduction sociale par le Precepteur"&gt;pratiques des individus&lt;/a&gt;. Parmi les plus importants, on trouve : &lt;/p&gt;&lt;p&gt;Le champ : Il s'agit d'un espace social structuré, doté de ses propres règles, enjeux et formes de capital spécifiques (champ politique, économique, artistique,  universitaire, etc). Les agents sociaux y luttent pour la domination et l'accumulation de capital. &lt;/p&gt; &lt;p&gt;Le capital : Il distingue plusieurs formes de capital qui confèrent du pouvoir et des avantages (capital économique, culturel, social et symbolique). &lt;/p&gt; &lt;p&gt;&lt;a href="https://www.youtube.com/watch?v=c67GEYsM2yA" title=" BOURDIEU - L'habitus par Cyrus North"&gt;L'habitus&lt;/a&gt; : C'est un système de dispositions durables et transposables, des manières de percevoir, de penser et d'agir que les individus acquièrent par leur socialisation, notamment au sein de leur classe sociale et de leur trajectoire.  &lt;/p&gt; &lt;p&gt;La violence symbolique : C'est une forme de domination douce, invisible et souvent acceptée par les dominés. Elle s'exerce notamment par l'imposition de catégories de pensée et de perception légitimes qui favorisent les dominants. Un exemple classique est la domination masculine. &lt;/p&gt; &lt;p&gt;&lt;a href="https://www.youtube.com/watch?v=9UPoOcMhE9g" title=" La Doxa par Philo1492"&gt;La doxa&lt;/a&gt; : Ensemble des croyances fondamentales, non questionnées, qui sont au fondement d'un champ social et qui apparaissent comme naturelles et évidentes pour les agents qui y évoluent. &lt;/p&gt; &lt;p&gt; Il a offert une critique novatrice des approches dualistes en sociologie (comme l'opposition entre l'individu et la société, ou entre la structure et l'agent). Sa théorie de l'habitus et du champ vise à dépasser ces oppositions en montrant comment les structures sociales sont incorporées par les individus et comment ces individus agissent au sein de ces structures. &lt;/p&gt; &lt;audio controls title="Qu'est-ce que Pierre Bourdieu a changé ? par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/22789-09.05.2022-ITEMA_23020195-2022C45516S0129-21.mp3" type="audio/mpeg" align="center"&gt;&lt;/audio&gt;  </t>
-        </is>
-      </c>
-      <c r="F118" s="54" t="inlineStr">
-        <is>
-          <t>4EoJMOmKGZw</t>
-        </is>
-      </c>
-      <c r="G118" s="56" t="inlineStr">
-        <is>
-          <t>"La misère invisible : comprendre pour agir, l’analyse de Pierre Bourdieu" par Ina Culture</t>
-        </is>
-      </c>
-      <c r="H118" s="56" t="inlineStr">
-        <is>
-          <t>https://www.laphilo.fr/pho/bourdieu-mini.webp</t>
-        </is>
-      </c>
-      <c r="J118" s="48" t="inlineStr">
-        <is>
-          <t>politique ; epistemologie</t>
-        </is>
-      </c>
-      <c r="K118" s="48" t="inlineStr">
-        <is>
-          <t>Constructivisme ; Marxisme</t>
-        </is>
-      </c>
-      <c r="L118" s="48" t="inlineStr">
-        <is>
-          <t>philosophe, sociologue français et figure intellectuelle importante.</t>
-        </is>
-      </c>
-      <c r="N118" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-    </row>
-    <row r="119" ht="257.25" customHeight="1" s="49">
+    <row r="119" ht="226.5" customHeight="1" s="49">
       <c r="A119" s="54" t="n">
         <v>1930</v>
       </c>
-      <c r="B119" s="54" t="n">
+      <c r="B119" s="54" t="inlineStr">
+        <is>
+          <t>2002</t>
+        </is>
+      </c>
+      <c r="C119" s="54" t="inlineStr">
+        <is>
+          <t>1930 – 2002</t>
+        </is>
+      </c>
+      <c r="D119" s="55" t="inlineStr">
+        <is>
+          <t>Pierre BOURDIEU</t>
+        </is>
+      </c>
+      <c r="E119" s="56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Pierre_Bourdieu"  title=" Wikipedia"&gt;Pierre BOURDIEU&lt;/a&gt; était un philosophe et sociologue français  qui a développé un ensemble de concepts interdépendants pour analyser la structure sociale et les &lt;a href="https://www.youtube.com/watch?v=LQ6UeaV-VTs"  title=" BOURDIEU - La reproduction sociale par le Precepteur"&gt;pratiques des individus&lt;/a&gt;. Parmi les plus importants, on trouve : &lt;/p&gt;&lt;p&gt;Le champ : Il s'agit d'un espace social structuré, doté de ses propres règles, enjeux et formes de capital spécifiques (champ politique, économique, artistique,  universitaire, etc). Les agents sociaux y luttent pour la domination et l'accumulation de capital. &lt;/p&gt; &lt;p&gt;Le capital : Il distingue plusieurs formes de capital qui confèrent du pouvoir et des avantages (capital économique, culturel, social et symbolique). &lt;/p&gt; &lt;p&gt;&lt;a href="https://www.youtube.com/watch?v=c67GEYsM2yA" title=" BOURDIEU - L'habitus par Cyrus North"&gt;L'habitus&lt;/a&gt; : C'est un système de dispositions durables et transposables, des manières de percevoir, de penser et d'agir que les individus acquièrent par leur socialisation, notamment au sein de leur classe sociale et de leur trajectoire.  &lt;/p&gt; &lt;p&gt;La violence symbolique : C'est une forme de domination douce, invisible et souvent acceptée par les dominés. Elle s'exerce notamment par l'imposition de catégories de pensée et de perception légitimes qui favorisent les dominants. Un exemple classique est la domination masculine. &lt;/p&gt; &lt;p&gt;&lt;a href="https://www.youtube.com/watch?v=9UPoOcMhE9g" title=" La Doxa par Philo1492"&gt;La doxa&lt;/a&gt; : Ensemble des croyances fondamentales, non questionnées, qui sont au fondement d'un champ social et qui apparaissent comme naturelles et évidentes pour les agents qui y évoluent. &lt;/p&gt; &lt;p&gt; Il a offert une critique novatrice des approches dualistes en sociologie (comme l'opposition entre l'individu et la société, ou entre la structure et l'agent). Sa théorie de l'habitus et du champ vise à dépasser ces oppositions en montrant comment les structures sociales sont incorporées par les individus et comment ces individus agissent au sein de ces structures. &lt;/p&gt; &lt;audio controls title="Qu'est-ce que Pierre Bourdieu a changé ? par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/22789-09.05.2022-ITEMA_23020195-2022C45516S0129-21.mp3" type="audio/mpeg" align="center"&gt;&lt;/audio&gt;  </t>
+        </is>
+      </c>
+      <c r="F119" s="54" t="inlineStr">
+        <is>
+          <t>4EoJMOmKGZw</t>
+        </is>
+      </c>
+      <c r="G119" s="56" t="inlineStr">
+        <is>
+          <t>"La misère invisible : comprendre pour agir, l’analyse de Pierre Bourdieu" par Ina Culture</t>
+        </is>
+      </c>
+      <c r="H119" s="56" t="inlineStr">
+        <is>
+          <t>https://www.laphilo.fr/pho/bourdieu-mini.webp</t>
+        </is>
+      </c>
+      <c r="J119" s="48" t="inlineStr">
+        <is>
+          <t>politique ; epistemologie</t>
+        </is>
+      </c>
+      <c r="K119" s="48" t="inlineStr">
+        <is>
+          <t>Constructivisme ; Marxisme</t>
+        </is>
+      </c>
+      <c r="L119" s="48" t="inlineStr">
+        <is>
+          <t>philosophe, sociologue français et figure intellectuelle importante.</t>
+        </is>
+      </c>
+      <c r="N119" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+    </row>
+    <row r="120" ht="257.25" customHeight="1" s="49">
+      <c r="A120" s="54" t="n">
+        <v>1930</v>
+      </c>
+      <c r="B120" s="54" t="n">
         <v>1992</v>
       </c>
-      <c r="C119" s="54" t="inlineStr">
+      <c r="C120" s="54" t="inlineStr">
         <is>
           <t>1930 – 1992</t>
         </is>
       </c>
-      <c r="D119" s="55" t="inlineStr">
+      <c r="D120" s="55" t="inlineStr">
         <is>
           <t>Félix GUATTARI</t>
         </is>
       </c>
-      <c r="E119" s="62" t="inlineStr">
+      <c r="E120" s="62" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/F%C3%A9lix_Guattari"  title=" Wikipedia"&gt;Félix GUATTARI&lt;/a&gt; était un philosophe, psychanalyste et  &lt;a href="https://maitron.fr/guattari-felix/" title=" BOURDIEU - L'habitus par Cyrus North"&gt;militant intellectuel &lt;/a&gt; français connu pour sa collaboration avec Gilles Deleuze, mais il a aussi développé une pensée personnelle très originale. Sa philosophie se situe surtout dans le courant du post-structuralisme et de la pensée critique contemporaine. Elle s’oppose aux idées trop fixes de sujet, d’identité ou de structure, et insiste au contraire sur les processus, les relations et les transformations. &lt;/p&gt; &lt;p&gt; Un de ses apports centraux est la notion de subjectivité comme quelque chose de produit par des agencements multiples. Pour lui, la subjectivité n’est pas seulement intérieure ou individuelle : elle se fabrique aussi dans les institutions, les médias, la politique, la famille et les environnements techniques. &lt;/p&gt; &lt;p&gt; Il a aussi travaillé sur la psychanalyse, en critiquant ce qu’il voyait comme ses formes trop normatives, notamment autour du complexe d’Œdipe. Dans &lt;a href="https://enseignants.lumni.fr/fiche-media/00000001135/l-anti-oedipe-de-gilles-deleuze-et-felix-guattari.html" title=" anti-oedipe  deleuze et guattari par enseignants lumni"&gt;L’Anti-Œdipe &lt;/a&gt; et Mille Plateaux, il défend avec Deleuze une pensée des flux, des désirs, des « rhizomes » et des lignes de fuite, contre les modèles hiérarchiques et fermés. &lt;/p&gt; &lt;p&gt; On peut donc le placer à la croisée de plusieurs branches : philosophie politique, philosophie de la subjectivité, psychanalyse critique et théorie sociale. Sa pensée est souvent associée à des idées comme l’écologie mentale, la créativité collective et la transformation des formes de vie. &lt;/p&gt;  
  &lt;audio controls title="la fin du politique par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/13915-16.03.2022-ITEMA_22964487-2022C3372E0135-NET_MFC_B9CCC943-E790-4029-A9C3-4076BC2B331E-21-443183d5ed7da523138c0280fb088809.mp3" type="audio/mpeg" align="center"&gt;&lt;/audio&gt;  </t>
         </is>
       </c>
-      <c r="F119" s="54" t="inlineStr">
+      <c r="F120" s="54" t="inlineStr">
         <is>
           <t>uWwrNHpasY4</t>
         </is>
       </c>
-      <c r="G119" s="56" t="inlineStr">
+      <c r="G120" s="56" t="inlineStr">
         <is>
           <t>f guattari et la question de la drogue par adrian romero</t>
         </is>
       </c>
-      <c r="H119" s="62" t="inlineStr">
+      <c r="H120" s="62" t="inlineStr">
         <is>
           <t>https://www.laphilo.fr/pho/fguattari-mini.webp</t>
         </is>
       </c>
-      <c r="J119" s="48" t="inlineStr">
+      <c r="J120" s="48" t="inlineStr">
         <is>
           <t>politique ; metaphysique</t>
         </is>
       </c>
-      <c r="K119" s="48" t="inlineStr">
+      <c r="K120" s="48" t="inlineStr">
         <is>
           <t xml:space="preserve">Post-structuralisme ; </t>
         </is>
       </c>
-      <c r="L119" s="48" t="inlineStr">
+      <c r="L120" s="48" t="inlineStr">
         <is>
           <t>philosophe français du courant post-structuraliste et de la pensée critique.</t>
         </is>
       </c>
-      <c r="N119" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-    </row>
-    <row r="120" ht="150.75" customHeight="1" s="49">
-      <c r="A120" s="57" t="n">
+      <c r="N120" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+    </row>
+    <row r="121" ht="150.75" customHeight="1" s="49">
+      <c r="A121" s="57" t="n">
         <v>1930</v>
       </c>
-      <c r="B120" s="57" t="inlineStr">
+      <c r="B121" s="57" t="inlineStr">
         <is>
           <t>1999</t>
         </is>
       </c>
-      <c r="C120" s="57" t="inlineStr">
+      <c r="C121" s="57" t="inlineStr">
         <is>
           <t>1930 – 1999</t>
         </is>
       </c>
-      <c r="D120" s="58" t="inlineStr">
+      <c r="D121" s="58" t="inlineStr">
         <is>
           <t>Gérard LEBRUN</t>
         </is>
       </c>
-      <c r="E120" s="59" t="inlineStr">
+      <c r="E121" s="59" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/G%C3%A9rard_Lebrun"   title=" Wikipedia"&gt;Gérard LEBRUN&lt;/a&gt; était un philosophe franço-brésilien spécialiste de la philosophie allemande, notamment de Kant et de Hegel. Peu connu du grand public, il a pourtant profondément marqué la manière de lire les grands textes philosophiques au XXᵉ siècle. &lt;/p&gt; &lt;p&gt; Il renouvelle l’histoire de la philosophie en refusant d’en faire un simple “mémorial” de grands systèmes figés; il lit les œuvres comme des textes vivants, traversés de tensions et de dissonances. Il insiste sur la nécessité, pour l’historien de la philosophie, de suivre la mobilité du texte et de ne pas séparer théorie et pratique: chez Kant, par exemple, il met en lumière la façon dont la pratique vient “limiter” la prétention théorique de la raison. &lt;/p&gt; &lt;p&gt; Dans "La Patience du concept" et d’autres travaux, il montre un Hegel qui ne sacralise pas le “fait accompli”, mais pense une rationalité de l’histoire où du hasard peut surgir de la nécessité. Il met aussi en évidence la place de la peur dans la dialectique hégélienne: peur qui dresse les individus à la soumission à l’État, ce qui permet à Lebrun de croiser Hegel avec une lecture nietzschéenne de la domestication humaine. &lt;/p&gt; &lt;p&gt; Il a influencé durablement l’historiographie philosophique francophone et brésilienne, en montrant comment une lecture exigeante des textes peut corriger bien des contresens installés, notamment sur l’héritage hégélien de Marx ou la portée de la critique kantienne. &lt;/p&gt;</t>
         </is>
       </c>
-      <c r="F120" s="57" t="inlineStr">
+      <c r="F121" s="57" t="inlineStr">
         <is>
           <t>494w_Ceby5Q</t>
         </is>
       </c>
-      <c r="G120" s="59" t="inlineStr">
+      <c r="G121" s="59" t="inlineStr">
         <is>
           <t>"Gérard Lebrun: La patience du concept. Essai sur le discours hégélien." par Jtgrandtour</t>
         </is>
       </c>
-      <c r="H120" s="65" t="inlineStr">
+      <c r="H121" s="65" t="inlineStr">
         <is>
           <t>https://www.laphilo.fr/pho/lebrun-mini.webp</t>
         </is>
       </c>
-      <c r="J120" s="48" t="inlineStr">
+      <c r="J121" s="48" t="inlineStr">
         <is>
           <t>metaphysique ; epistemologie</t>
         </is>
       </c>
-      <c r="K120" s="48" t="inlineStr">
+      <c r="K121" s="48" t="inlineStr">
         <is>
           <t>Herméneutique</t>
         </is>
       </c>
-      <c r="L120" s="48" t="inlineStr">
+      <c r="L121" s="48" t="inlineStr">
         <is>
           <t>philosophe franco-brésilien spécialiste de la philosophie allemande.</t>
         </is>
       </c>
-      <c r="N120" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-    </row>
-    <row r="121" ht="180.75" customHeight="1" s="49">
-      <c r="A121" s="54" t="n">
+      <c r="N121" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+    </row>
+    <row r="122" ht="180.75" customHeight="1" s="49">
+      <c r="A122" s="54" t="n">
         <v>1930</v>
       </c>
-      <c r="B121" s="54" t="inlineStr">
+      <c r="B122" s="54" t="inlineStr">
         <is>
           <t>2019</t>
         </is>
       </c>
-      <c r="C121" s="54" t="inlineStr">
+      <c r="C122" s="54" t="inlineStr">
         <is>
           <t>1930 – 2019</t>
         </is>
       </c>
-      <c r="D121" s="55" t="inlineStr">
+      <c r="D122" s="55" t="inlineStr">
         <is>
           <t>Michel SERRES</t>
         </is>
       </c>
-      <c r="E121" s="56" t="inlineStr">
+      <c r="E122" s="56" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Michel_Serres"   title=" Wikipedia"&gt;Michel SERRES&lt;/a&gt; était un philosophe français célèbre par son œuvre abondante qui relie sciences, techniques, littérature et réflexion écologique. Sa personnalité publique, pédagogique et accessible en a fait une &lt;a href="https://institutmichelserres.ens-lyon.fr/spip.php?rubrique10" title="Institut Michel Serres"&gt;figure médiatique, &lt;/a&gt;  souvent invitée pour commenter les enjeux de société. &lt;/p&gt; &lt;p&gt; Sa pensée est marquée par le motif des passages : passages entre sciences et humanités, entre nature et culture, entre générations, symbolisés par la figure d’Hermès, dieu des messagers. Il refuse les cloisonnements disciplinaires et décrit le monde comme un réseau de relations, de flux et d’interférences plutôt que comme un ensemble d’objets isolés. Sa philosophie met l’accent sur le multiple, le changement, l’aléatoire, contre les visions trop fixistes ou unifiées de la réalité. &lt;/p&gt; &lt;p&gt; Sa thèse "Le Système de Leibniz et ses modèles mathématiques" paru en  1968  montre comment la pensée de Leibniz peut être éclairée par des outils mathématiques modernes. La série "Hermès" explore les échanges, les messages et les traductions entre domaines du savoir.  "Le Contrat naturel" paru en 1990 propose d’étendre le contrat social à la Terre elle‑même, en reconnaissant des droits à la nature et en repensant notre responsabilité écologique.  "Les Cinq Sens" paru en 1985 réhabilite le corps et la sensorialité comme voies de connaissance, contre une philosophie trop abstraite et désincarnée. &lt;/p&gt; &lt;p&gt; Philosophe des sciences : il s’inspire de la théorie du chaos, des catastrophes, des fractales, de la biologie et de l’informatique pour repenser notre rapport au réel. Il analyse tôt la crise écologique, la pollution et l’appropriation violente du monde par l’homme, notamment dans "Le Contrat naturel" et "Le Mal propre".
  &lt;/p&gt; &lt;p&gt; Son œuvre a profondément marqué la  &lt;a href="https://www.youtube.com/watch?v=1xqMSx2gOvY" title= "L’interview de Michel Serres par Stupefiant"&gt;philosophie française &lt;/a&gt; en montrant qu’on peut penser ensemble mathématiques, littérature, écologie, médias et éducation, dans une vision globale et ouverte du savoir. &lt;/p&gt;  &lt;audio controls title="pacifiste, troubadour par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/10351-07.01.2002-ITEMA_24343895-2001C3500E0212-ITE_00155773_RSCE-21-5606f1dfdfef9fd9095f32ba95faa842.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;  </t>
         </is>
       </c>
-      <c r="F121" s="54" t="inlineStr">
+      <c r="F122" s="54" t="inlineStr">
         <is>
           <t>n0z25Qebv94</t>
         </is>
       </c>
-      <c r="G121" s="56" t="inlineStr">
+      <c r="G122" s="56" t="inlineStr">
         <is>
           <t>"Mort de Michel Serres : rencontre avec le philosophe" par Le Monde</t>
         </is>
       </c>
-      <c r="H121" s="62" t="inlineStr">
+      <c r="H122" s="62" t="inlineStr">
         <is>
           <t>https://www.laphilo.fr/pho/serres-mini.webp</t>
         </is>
       </c>
-      <c r="J121" s="48" t="inlineStr">
+      <c r="J122" s="48" t="inlineStr">
         <is>
           <t>epistemologie</t>
         </is>
       </c>
-      <c r="K121" s="48" t="inlineStr">
+      <c r="K122" s="48" t="inlineStr">
         <is>
           <t>Constructivisme</t>
         </is>
       </c>
-      <c r="L121" s="48" t="inlineStr">
+      <c r="L122" s="48" t="inlineStr">
         <is>
           <t>philosophe français reliant sciences, techniques, littérature et réflexion écologique.</t>
         </is>
       </c>
-      <c r="N121" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-    </row>
-    <row r="122" ht="150.75" customHeight="1" s="49">
-      <c r="A122" s="57" t="n">
+      <c r="N122" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+    </row>
+    <row r="123" ht="150.75" customHeight="1" s="49">
+      <c r="A123" s="57" t="n">
         <v>1930</v>
       </c>
-      <c r="B122" s="57" t="inlineStr">
+      <c r="B123" s="57" t="inlineStr">
         <is>
           <t>2000</t>
         </is>
       </c>
-      <c r="C122" s="57" t="inlineStr">
+      <c r="C123" s="57" t="inlineStr">
         <is>
           <t>1930 – 2000</t>
         </is>
       </c>
-      <c r="D122" s="58" t="inlineStr">
+      <c r="D123" s="58" t="inlineStr">
         <is>
           <t>Gérard GRANEL</t>
         </is>
       </c>
-      <c r="E122" s="59" t="inlineStr">
+      <c r="E123" s="59" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/G%C3%A9rard_Granel"  title=" Wikipedia"&gt;Gérard GRANEL&lt;/a&gt; était un philosophe français, connu pour ses traductions et commentaires des œuvres de Husserl et Heidegger, et pour ses réflexions originales sur le capitalisme contemporain et l'enseignement philosophique. Agrégé de philosophie et professeur à l'Université de Toulouse-le Mirail, il fut l'une des &lt;a href="https://www.gerardgranel.com"  title=" gerard granel"&gt;figures les plus singulières &lt;/a&gt;  de la philosophie française de la seconde moitié du XXe siècle, associant une rigueur herméneutique exigeante à un engagement politique radical. &lt;/p&gt; &lt;p&gt; Ses traductions de textes fondamentaux de Husserl — notamment les &lt;em&gt;Leçons pour une phénoménologie de la conscience intime du temps&lt;/em&gt; (1964) — et de Heidegger — &lt;em&gt;Être et Temps&lt;/em&gt; (1986), traduction très discutée mais d'une grande rigueur herméneutique — constituent des apports décisifs à la diffusion de la phénoménologie en France. Dans son essai &lt;em&gt;L'Équivoque ontologique de la pensée kantienne&lt;/em&gt; (1970), il offre une interprétation originale de Kant à la lumière de la phénoménologie. &lt;/p&gt; &lt;p&gt; Dans &lt;a href="https://www.youtube.com/watch?v=DBGFMdmXgik"  title=" gerard granel apolis par Politproductions"&gt;ses essais tardifs, &lt;/a&gt; réunis notamment dans &lt;em&gt;De l'Université&lt;/em&gt; (1982) et &lt;em&gt;Traditionis traditio&lt;/em&gt; (1972), il développe une réflexion acérée sur la crise de l'université et de la transmission du savoir philosophique à l'ère capitaliste. Sa critique des formes contemporaines de la domination économique et culturelle, menée à partir des outils de la phénoménologie et du marxisme, est l'une des contributions les plus originales de sa pensée à la compréhension de la modernité. Penseur exigeant et inclassable, il garde aujourd'hui une audience fidèle parmi les philosophes français. &lt;/p&gt;</t>
         </is>
       </c>
-      <c r="F122" s="57" t="inlineStr">
+      <c r="F123" s="57" t="inlineStr">
         <is>
           <t xml:space="preserve">DBGFMdmXgik</t>
         </is>
       </c>
-      <c r="G122" s="59" t="inlineStr">
+      <c r="G123" s="59" t="inlineStr">
         <is>
           <t xml:space="preserve">"Présentation de  «  Apolis » de Gérard Granel" par Politproductions</t>
         </is>
       </c>
-      <c r="H122" s="65" t="inlineStr">
+      <c r="H123" s="65" t="inlineStr">
         <is>
           <t>https://www.laphilo.fr/pho/granel-mini.webp</t>
         </is>
       </c>
-      <c r="J122" s="48" t="inlineStr">
+      <c r="J123" s="48" t="inlineStr">
         <is>
           <t>metaphysique ; epistemologie</t>
         </is>
       </c>
-      <c r="K122" s="48" t="inlineStr">
+      <c r="K123" s="48" t="inlineStr">
         <is>
           <t>Phénoménologie</t>
         </is>
       </c>
-      <c r="L122" s="48" t="inlineStr">
+      <c r="L123" s="48" t="inlineStr">
         <is>
           <t>philosophe français traducteur avec commentaires des œuvres de Husserl et Heidegger.</t>
         </is>
       </c>
-      <c r="N122" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-    </row>
-    <row r="123" ht="164.25" customHeight="1" s="49">
-      <c r="A123" s="54" t="n">
+      <c r="N123" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+    </row>
+    <row r="124" ht="164.25" customHeight="1" s="49">
+      <c r="A124" s="54" t="n">
         <v>1934</v>
       </c>
-      <c r="B123" s="54" t="inlineStr">
+      <c r="B124" s="54" t="inlineStr">
         <is>
           <t>2013</t>
         </is>
       </c>
-      <c r="C123" s="54" t="inlineStr">
+      <c r="C124" s="54" t="inlineStr">
         <is>
           <t>1934 – 2013</t>
         </is>
       </c>
-      <c r="D123" s="55" t="inlineStr">
+      <c r="D124" s="55" t="inlineStr">
         <is>
           <t>Raymond BOUDON</t>
         </is>
       </c>
-      <c r="E123" s="62" t="inlineStr">
+      <c r="E124" s="62" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Raymond_Boudon"  title=" Wikipedia"&gt;Raymond BOUDON&lt;/a&gt; était un sociologue et philosophe social français, l'une des figures les plus importantes de la sociologie française de la seconde moitié du XXe siècle et un ardent défenseur du libéralisme intellectuel et de la rationalité. Son œuvre,  &lt;a href="https://www.quesaisje.com/raymond-boudon"  title=" Boudon raymond par que sais je ?"&gt;immense et plurielle, &lt;/a&gt; porte à la fois sur la méthodologie des sciences sociales, la théorie de l'action et la philosophie sociale. &lt;/p&gt; &lt;p&gt; Sa contribution la plus connue est l'élaboration d'une sociologie de l'individualisme méthodologique. Dans &lt;em&gt;L'Inégalité des chances&lt;/em&gt; (1973) et surtout dans &lt;em&gt;La Logique du social&lt;/em&gt; (1979) et &lt;em&gt;L'Art de se persuader des idées douteuses, fragiles ou fausses&lt;/em&gt; (1990), il défend l'idée que les faits sociaux s'expliquent par les actions et les croyances des individus, et que ces actions sont généralement rationnelles au sens large, c'est-à-dire fondées sur de « bonnes raisons » qui ne se réduisent pas  &lt;a href="https://www.youtube.com/watch?v=tMmKcRuoxp4"  title=" boudon l’inégalité des chances par La Sociothèque"&gt;aux seuls intérêts matériels.&lt;/a&gt;  Cette position s'oppose à la fois au structuralisme durkheimien et au réductionnisme économique. &lt;/p&gt; &lt;p&gt; Dans ses dernières œuvres — &lt;em&gt;Pourquoi les intellectuels n'aiment pas le libéralisme&lt;/em&gt; (2004), &lt;em&gt;La Rationalité&lt;/em&gt; (2009) — il s'engagea dans une défense résolue du libéralisme politique et intellectuel contre ce qu'il percevait comme les dérives relativistes et collectivistes de la pensée française contemporaine. Sociologue rigoureux et polémiste redoutable, il fut l'un des penseurs français les plus lus à l'étranger, notamment aux États-Unis et en Allemagne, où son travail sur la rationalité et les croyances sociales est largement reconnu. &lt;/p&gt;     &lt;audio controls title="Raymond Boudon par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/12003-15.01.2014-ITEMA_20575231-2014C18006S0015-21.mp3" type="audio/mpeg" align="center"&gt;&lt;/audio&gt;  </t>
         </is>
       </c>
-      <c r="F123" s="54" t="inlineStr">
+      <c r="F124" s="54" t="inlineStr">
         <is>
           <t>ZM2HKBS9S8M</t>
         </is>
       </c>
-      <c r="G123" s="56" t="inlineStr">
+      <c r="G124" s="56" t="inlineStr">
         <is>
           <t>"Avis de Raymond Boudon sur Bourdieu" par Horapollo</t>
         </is>
       </c>
-      <c r="H123" s="56" t="inlineStr">
+      <c r="H124" s="56" t="inlineStr">
         <is>
           <t>https://www.laphilo.fr/pho/rboudon-mini.webp</t>
         </is>
       </c>
-      <c r="J123" s="48" t="inlineStr">
+      <c r="J124" s="48" t="inlineStr">
         <is>
           <t>epistemologie ; politique</t>
         </is>
       </c>
-      <c r="K123" s="48" t="inlineStr">
+      <c r="K124" s="48" t="inlineStr">
         <is>
           <t>Constructivisme ; Individualisme méthodologique</t>
         </is>
       </c>
-      <c r="L123" s="48" t="inlineStr">
+      <c r="L124" s="48" t="inlineStr">
         <is>
           <t>philosophe social français, figure importante de la sociologie française.</t>
         </is>
       </c>
-      <c r="N123" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-    </row>
-    <row r="124" ht="255.75" customHeight="1" s="49">
-      <c r="A124" s="47">
+      <c r="N124" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+    </row>
+    <row r="125" ht="255.75" customHeight="1" s="49">
+      <c r="A125" s="47">
         <v>1934</v>
       </c>
-      <c r="B124" s="47">
+      <c r="B125" s="47">
         <v>1994</v>
       </c>
-      <c r="C124" s="47" t="inlineStr">
+      <c r="C125" s="47" t="inlineStr">
         <is>
           <t xml:space="preserve">1934 - 1994</t>
         </is>
       </c>
-      <c r="D124" s="47" t="inlineStr">
+      <c r="D125" s="47" t="inlineStr">
         <is>
           <t xml:space="preserve">Sarah KOFMAN</t>
         </is>
       </c>
-      <c r="E124" s="47" t="inlineStr">
+      <c r="E125" s="47" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Sarah_Kofman" title=" Wikipedia"&gt;Sarah KOFMAN&lt;/a&gt;&amp;nbsp;était une philosophe française, née à Paris dans une famille juive d'origine polonaise. En 1942, son père, rabbin, fut arrêté lors de la rafle du Vél' d'Hiv et assassiné à Auschwitz. Cachée pendant la guerre, elle raconta bien plus tard cette enfance dans &lt;em&gt;&lt;a href="https://www.youtube.com/watch?v=VIAbVde4ePM" title="Rue Ordener Rue Labat par exekow"&gt;Rue Ordener, rue Labat&lt;/a&gt;&lt;/em&gt; (1994), un récit bouleversant.&lt;/p&gt; &lt;p&gt;Professeure à la Sorbonne, proche de Jacques Derrida, elle consacra une grande partie de son œuvre à des lectures minutieuses de Nietzsche et de Freud, dont elle montre les ambiguïtés et les contradictions. Dans &lt;em&gt;L'Énigme de la femme&lt;/em&gt; (1980), elle analyse la manière dont Freud a pensé la féminité et ce que sa théorie révèle de ses propres préjugés. Elle écrivit aussi sur l'art, le rire et la littérature.&lt;/p&gt; &lt;p&gt;Sa méthode consiste à lire les grands textes au plus près, en repérant les métaphores, les exemples et les détails apparemment secondaires, pour y faire apparaître ce que l'auteur ne dit pas explicitement. Ses livres sur Nietzsche, comme &lt;em&gt;Nietzsche et la métaphore&lt;/em&gt; (1972), ont renouvelé la lecture de ce philosophe en France, en montrant l'importance du style et des images dans sa pensée.&lt;/p&gt; &lt;p&gt;Dans &lt;em&gt;Paroles suffoquées&lt;/em&gt; (1987), elle réfléchit, à partir de Maurice Blanchot et de Robert Antelme, à l'impossibilité et à la nécessité de parler d'Auschwitz. Elle mit &lt;a href="https://www.persee.fr/doc/grif_0770-6081_1997_hos_3_1_1922" title="Comment philosophe une femme par persée"&gt;fin à ses jours en 1994&lt;/a&gt;, le jour anniversaire de la naissance de Nietzsche. Son œuvre, d'une trentaine de livres, allie rigueur philosophique, écoute de la psychanalyse et mémoire de la Shoah.&lt;/p&gt;  &lt;audio controls title="Sarah Kofman, une enfance cachée entre la rue Ordener et la rue Labat par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/24541-12.10.2023-ITEMA_23517920-2010C3372E1858-21.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;</t>
         </is>
       </c>
-      <c r="F124" t="inlineStr">
+      <c r="F125" t="inlineStr">
         <is>
           <t xml:space="preserve">KdLreZP9TuI</t>
         </is>
       </c>
-      <c r="G124" s="47" t="inlineStr">
+      <c r="G125" s="47" t="inlineStr">
         <is>
           <t xml:space="preserve">"Sarah Kofman - Entretien (Agora)" par Artesquieu</t>
         </is>
       </c>
-      <c r="H124" s="47" t="inlineStr">
+      <c r="H125" s="47" t="inlineStr">
         <is>
           <t xml:space="preserve">https://www.laphilo.fr/pho/sarahkofman-mini.webp</t>
         </is>
       </c>
-      <c r="J124" s="47" t="inlineStr">
+      <c r="J125" s="47" t="inlineStr">
         <is>
           <t xml:space="preserve">esthetique ; ethique</t>
         </is>
       </c>
-      <c r="K124" s="47" t="inlineStr">
+      <c r="K125" s="47" t="inlineStr">
         <is>
           <t xml:space="preserve">Déconstructionnisme</t>
         </is>
       </c>
-      <c r="L124" s="47" t="inlineStr">
+      <c r="L125" s="47" t="inlineStr">
         <is>
           <t xml:space="preserve">philosophe française, lectrice de Nietzsche et de Freud, proche de Derrida, marquée par la Shoah.</t>
         </is>
       </c>
-      <c r="M124" t="inlineStr">
+      <c r="M125" t="inlineStr">
         <is>
           <t xml:space="preserve">femme ; juive</t>
         </is>
       </c>
-      <c r="N124" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-    </row>
-    <row r="125" ht="164.25" customHeight="1" s="49">
-      <c r="A125" s="57" t="n">
+      <c r="N125" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+    </row>
+    <row r="126" ht="164.25" customHeight="1" s="49">
+      <c r="A126" s="57" t="n">
         <v>1935</v>
       </c>
-      <c r="B125" s="57" t="inlineStr">
+      <c r="B126" s="57" t="inlineStr">
         <is>
           <t>2021</t>
         </is>
       </c>
-      <c r="C125" s="57" t="inlineStr">
+      <c r="C126" s="57" t="inlineStr">
         <is>
           <t>1935 – 2021</t>
         </is>
       </c>
-      <c r="D125" s="58" t="inlineStr">
+      <c r="D126" s="58" t="inlineStr">
         <is>
           <t>François FÉDIER</t>
         </is>
       </c>
-      <c r="E125" s="59" t="inlineStr">
+      <c r="E126" s="59" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Fran%C3%A7ois_F%C3%A9dier"  title=" Wikipedia"&gt;François FÉDIER&lt;/a&gt; était un philosophe français, principal traducteur de Martin Heidegger en français après Jean Beaufret dont il fut le disciple. Agrégé de philosophie et maître de conférences à la Sorbonne, il consacra l'essentiel de sa vie intellectuelle à la traduction, au commentaire et à la défense de l'œuvre de Heidegger, notamment face aux controverses suscitées par l'engagement politique du philosophe allemand.  &lt;a href="https://www.youtube.com/watch?v=ggAIziycK9c"  title=" françois fedier partage formel par philosopphies TV"&gt;Sa fidélité &lt;/a&gt; à Heidegger, absolue et parfois polémique, fit de lui une figure de référence mais aussi de controverse dans la philosophie française. &lt;/p&gt; &lt;p&gt; Ses traductions de textes heideggeriens — notamment &lt;em&gt;Acheminement vers la parole&lt;/em&gt; (1959), des textes sur Hölderlin, et de nombreux fragments et cours — sont caractérisées par une attention extrême à la lettre allemande et par le refus de faciliter l'accès au texte au détriment de sa pensée propre. Cette conception exigeante de la traduction philosophique, qui cherche à faire  &lt;a href="https://www.youtube.com/watch?v=i8Nb3W1stIo"  title=" françois fedier apport à la philosophie par Philosophie TV"&gt;résonner en français &lt;/a&gt; la langue même de la pensée heideggerienne, a été à la fois admirée pour sa rigueur et critiquée pour son obscurité. &lt;/p&gt; &lt;p&gt; Dans ses essais critiques — notamment &lt;em&gt;Heidegger : anatomie d'un scandale&lt;/em&gt; (1988), réponse aux attaques de Victor Farias —il  prit la défense de Heidegger face aux accusations de nazisme, défendant la thèse d'une erreur politique ponctuelle sans rapport avec le cœur de la pensée philosophique. Cette posture, vivement contestée, a nourri l'une des controverses les plus vives de la philosophie française de la fin du XXe siècle. Il reste une figure incontournable et clivante de la réception française de Heidegger. &lt;/p&gt;</t>
         </is>
       </c>
-      <c r="F125" s="57" t="inlineStr">
+      <c r="F126" s="57" t="inlineStr">
         <is>
           <t>i8Nb3W1stIo</t>
         </is>
       </c>
-      <c r="G125" s="59" t="inlineStr">
+      <c r="G126" s="59" t="inlineStr">
         <is>
           <t>"Francois Fédier Apports à la philosophie. De l'avenance" par Philosophie TV</t>
         </is>
       </c>
-      <c r="H125" s="65" t="inlineStr">
+      <c r="H126" s="65" t="inlineStr">
         <is>
           <t>https://www.laphilo.fr/pho/fedier-mini.webp</t>
         </is>
       </c>
-      <c r="J125" s="48" t="inlineStr">
+      <c r="J126" s="48" t="inlineStr">
         <is>
           <t>metaphysique</t>
         </is>
       </c>
-      <c r="K125" s="48" t="inlineStr">
+      <c r="K126" s="48" t="inlineStr">
         <is>
           <t>Phénoménologie</t>
         </is>
       </c>
-      <c r="L125" s="48" t="inlineStr">
+      <c r="L126" s="48" t="inlineStr">
         <is>
           <t>philosophe français, principal traducteur de Martin Heidegger en français.</t>
         </is>
       </c>
-      <c r="N125" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-    </row>
-    <row r="126" ht="164.25" customHeight="1" s="49">
-      <c r="A126" s="54" t="n">
+      <c r="N126" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+    </row>
+    <row r="127" ht="164.25" customHeight="1" s="49">
+      <c r="A127" s="54" t="n">
         <v>1935</v>
       </c>
-      <c r="B126" s="54" t="inlineStr">
+      <c r="B127" s="54" t="inlineStr">
         <is>
           <t>2003</t>
         </is>
       </c>
-      <c r="C126" s="54" t="inlineStr">
+      <c r="C127" s="54" t="inlineStr">
         <is>
           <t>1935 – 2003</t>
         </is>
       </c>
-      <c r="D126" s="55" t="inlineStr">
+      <c r="D127" s="55" t="inlineStr">
         <is>
           <t>Monique WITTIG</t>
         </is>
       </c>
-      <c r="E126" s="56" t="inlineStr">
+      <c r="E127" s="56" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Monique_Wittig"  title=" Wikipedia"&gt;Monique WITTIG&lt;/a&gt; était une écrivaine et philosophe française, figure fondatrice du féminisme matérialiste et de la théorie queer en France. Elle fut l'une des fondatrices du Mouvement de libération des femmes (MLF) en 1970. Auteure d'une œuvre littéraire et théorique  &lt;a href="https://laviedesidees.fr/Renversements-de-Monique-Wittig-6277"  title=" reversements de Monique WITTIG par laviedesidees"&gt;d'une grande originalité, &lt;/a&gt; elle s'installa aux États-Unis dans les années 1970 où elle enseigna dans plusieurs universités, contribuant à diffuser la pensée féministe française à l'échelle internationale. &lt;/p&gt; &lt;p&gt; Son premier roman, &lt;em&gt;L'Opoponax&lt;/em&gt; (1964, prix Médicis), est une œuvre expérimentale qui décrit l'enfance à travers un pronom impersonnel qui efface le genre, préfigurant ses réflexions théoriques ultérieures sur la langue et le genre. &lt;em&gt;Les Guérillères&lt;/em&gt; (1969) est un roman collectif qui figure une utopie féministe radicale. &lt;em&gt;Le Corps lesbien&lt;/em&gt; (1973) propose une réécriture poétique et politique du corps féminin et de la sexualité lesbienne. Ces œuvres litté raires mettent en pratique une déconstruction du langage comme vecteur de l'oppression patriarcale. &lt;/p&gt; &lt;p&gt; Dans ses essais théoriques, réunis dans &lt;em&gt;La Pensée straight&lt;/em&gt; (2001), Wittig développe une critique radicale de l'hétérosexualité obligatoire comme régime politique qui produit les catégories de « femme » et d'« homme » comme classes. Sa thèse centrale —  &lt;a href="https://www.youtube.com/watch?v=xTga507vuE8"  title=" c’est quoi être une femme du coup par Marinette"&gt;« les lesbiennes ne sont pas des femmes » &lt;/a&gt; — affirme que la catégorie « femme » est une construction politique de l'hétérosexualité dominante et que les lesbiennes, en refusant ce rapport, échappent à cette catégorie. Cette pensée a profondément influencé Judith Butler et les théories queer contemporaines. &lt;/p&gt;   &lt;audio controls title="La renaissance Wittig par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/25343-02.05.2025-ITEMA_24121665-2025C53458S0122-NET_MFC_69CE613B-224D-46F3-B177-81981898A856-21.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;  </t>
         </is>
       </c>
-      <c r="F126" s="54" t="inlineStr">
+      <c r="F127" s="54" t="inlineStr">
         <is>
           <t>cZH0FRIe0LM</t>
         </is>
       </c>
-      <c r="G126" s="56" t="inlineStr">
+      <c r="G127" s="56" t="inlineStr">
         <is>
           <t>"Monique Wittig, la révolutionnaire des sexes" par France Culture</t>
         </is>
       </c>
-      <c r="H126" s="62" t="inlineStr">
+      <c r="H127" s="62" t="inlineStr">
         <is>
           <t>https://www.laphilo.fr/pho/mwittig-mini.webp</t>
         </is>
       </c>
-      <c r="J126" s="48" t="inlineStr">
+      <c r="J127" s="48" t="inlineStr">
         <is>
           <t>politique ; ethique</t>
         </is>
       </c>
-      <c r="K126" s="48" t="inlineStr">
+      <c r="K127" s="48" t="inlineStr">
         <is>
           <t>Post-structuralisme ; Féminisme</t>
         </is>
       </c>
-      <c r="L126" s="48" t="inlineStr">
+      <c r="L127" s="48" t="inlineStr">
         <is>
           <t>philosophe française fondatrice du féminisme matérialiste &amp; de la théorie Queer.</t>
         </is>
       </c>
-      <c r="M126" t="inlineStr">
+      <c r="M127" t="inlineStr">
         <is>
           <t xml:space="preserve">femme</t>
         </is>
       </c>
-      <c r="N126" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-    </row>
-    <row r="127" ht="129" customHeight="1" s="49">
-      <c r="A127" s="47" t="n">
+      <c r="N127" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+    </row>
+    <row r="128" ht="129" customHeight="1" s="49">
+      <c r="A128" s="47" t="n">
         <v>1936</v>
       </c>
-      <c r="B127" s="47" t="n">
+      <c r="B128" s="47" t="n">
         <v>2026</v>
       </c>
-      <c r="C127" s="47" t="inlineStr">
+      <c r="C128" s="47" t="inlineStr">
         <is>
           <t>1936 – 2026</t>
         </is>
       </c>
-      <c r="D127" s="47" t="inlineStr">
+      <c r="D128" s="47" t="inlineStr">
         <is>
           <t>Michel HULIN</t>
         </is>
       </c>
-      <c r="E127" s="48" t="inlineStr">
+      <c r="E128" s="48" t="inlineStr">
         <is>
           <t xml:space="preserve"> &lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Michel_Hulin"  title=" Wikipedia"&gt;Michel HULIN&lt;/a&gt; était un philosophe français récemment décédé, grand spécialiste de la &lt;a href="https://www.youtube.com/watch?v=tJFic9y58Sc" title=" Aperçu de l’hindouisme avec Michel Hulin par Resonances "&gt;philosophie indienne &lt;/a&gt; et de la comparaison entre pensée européenne et pensée asiatique, notamment de l’Advaïta Vedānta, le courant « non‑dualiste » du vedānta. Longtemps professeur de philosophie indienne et comparée à l’université Paris‑Sorbonne, il a joué un rôle central dans la diffusion en France des grandes écoles de pensée de l’Inde. Sa carrière s’est accompagnée d’un important travail de traduction du sanskrit et de vulgarisation, accessible à un public non spécialiste. &lt;/p&gt; &lt;p&gt; Ses recherches portent d’une part sur  &lt;a href="https://www.youtube.com/watch?v=kaJP8yDwHeY" title=" For intérieur par Resonnances "&gt;la pensée indienne classique &lt;/a&gt;  (notion d’ahamkāra, textes vedāntins et shivaïtes d’inspiration tantrique), d’autre part sur les questions épistémologiques et métaphysiques que soulève la rencontre entre les traditions européennes et asiatiques. Dans sa thèse, Le Principe de l’ego dans la pensée indienne classique, il analyse la notion de « faux moi » et montre comment elle éclaire notre expérience ordinaire de la conscience. Il s’intéresse également à la question du temps, de l’éternité et des expériences dites mystiques, qu’il relie à des vécus très concrets. &lt;/p&gt; &lt;p&gt; Dans des ouvrages comme La Face cachée du temps, La Mystique sauvage, Hegel et l’Orient, Shankara et la non‑dualité ou encore l’anthologie L’Inde des sages, il  conjugue une érudition très précise et un style volontairement clair. Il montre comment des interrogations métaphysiques complexes – sur le moi, le temps, l’au‑delà ou l’expérience spirituelle – touchent directement la vie intérieure de chacun. Par son enseignement et ses livres, il a contribué à installer durablement en France une philosophie comparée attentive au dialogue entre Europe et Inde. &lt;audio controls title="  Philosophies indiennes (1/4) : Upanishads, les textes fondateurs ?  par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/10467-16.12.2013-ITEMA_20562153-2013C12410S0350-NET_FC_A092AF0E-5BC1-49EE-A72F-E62BB6A2A8B1-21.mp3" type="audio/mpeg" align="center"&gt;&lt;/audio&gt;  
 </t>
         </is>
       </c>
-      <c r="F127" s="47" t="inlineStr">
+      <c r="F128" s="47" t="inlineStr">
         <is>
           <t>cLbyvPtJW2c</t>
         </is>
       </c>
-      <c r="G127" s="90" t="inlineStr">
+      <c r="G128" s="90" t="inlineStr">
         <is>
           <t xml:space="preserve">le message des Upanishads par Baglis Tv</t>
         </is>
       </c>
-      <c r="H127" s="48" t="inlineStr">
+      <c r="H128" s="48" t="inlineStr">
         <is>
           <t>https://www.laphilo.fr/pho/mhulin-mini.webp</t>
         </is>
       </c>
-      <c r="J127" s="48" t="inlineStr">
+      <c r="J128" s="48" t="inlineStr">
         <is>
           <t>metaphysique ; spiritualite</t>
         </is>
       </c>
-      <c r="K127" s="48" t="inlineStr">
+      <c r="K128" s="48" t="inlineStr">
         <is>
           <t>Spiritualisme</t>
         </is>
       </c>
-      <c r="L127" s="48" t="inlineStr">
+      <c r="L128" s="48" t="inlineStr">
         <is>
           <t>philosophe français grand connaisseur de la philosophie indienne.</t>
         </is>
       </c>
-      <c r="N127" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-    </row>
-    <row r="128" ht="176.25" customHeight="1" s="49">
-      <c r="A128" s="47">
+      <c r="N128" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+    </row>
+    <row r="129" ht="176.25" customHeight="1" s="49">
+      <c r="A129" s="47">
         <v>1937</v>
       </c>
-      <c r="B128" s="47">
+      <c r="B129" s="47">
         <v>2026</v>
       </c>
-      <c r="C128" s="47" t="inlineStr">
+      <c r="C129" s="47" t="inlineStr">
         <is>
           <t xml:space="preserve">1937 – 2026</t>
         </is>
       </c>
-      <c r="D128" s="47" t="inlineStr">
+      <c r="D129" s="47" t="inlineStr">
         <is>
           <t xml:space="preserve">Éliane ESCOUBAS</t>
         </is>
       </c>
-      <c r="E128" s="85" t="inlineStr">
+      <c r="E129" s="85" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/%C3%89liane_Escoubas"  style="color:#6A142A"  title=" Wikipedia"&gt;Éliane ESCOUBAS&lt;/a&gt;  est une philosophe française, historienne de la philosophie et traductrice. Elle se rattache à l’école phénoménologique et travaille principalement sur la philosophie allemande, la phénoménologie de l’art et la psychiatrie phénoménologique, dite Daseinsanalyse. Après une formation marquée par les cours de Gérard Granel sur Husserl, Kant et Hegel à Toulouse, elle enseigne dans le secondaire puis devient maître de conférences, puis professeur de philosophie, tout en menant des recherches au CNRS et en participant à la création du Collège international de Philosophie. &lt;/p&gt; &lt;p&gt; Elle met au centre la phénoménologie de l’expérience sensible, en particulier la manière dont le monde et le sujet adviennent à travers le sentir, l’affect et la perception. Elle montre que la phénoménologie fournit un prisme particulièrement adapté pour penser l’esthétique, car l’œuvre d’art apparaît comme un mode privilégié pour saisir comment le sujet et le monde se co‑constituent dans une expérience sensible et existentielle. &lt;/p&gt; &lt;p&gt; Une grande partie de son œuvre est consacrée à une « esthétique du sentir » où l’art n’est pas seulement une illustration de la philosophie, mais un mode de connaissance autonome. Dans ses travaux comme Imago mundi. Topologie de l’art ou L’invention de l’art, elle montre que l’image et l’œuvre picturale ne se réduisent pas à « représentation » ou « signe », mais relèvent d’une apparition du monde lui‑même, d’une spatialité et d’une temporalité qui précèdent les catégories classiques de l’objet. &lt;/p&gt; &lt;p&gt; Sa philosophie s’ouvre aussi à la phénoménologie clinique et à la psychiatrie, notamment à travers la Daseinsanalyse et la place de l’affect et de l’affectivité dans la constitution du sujet. En explorant les affectivités dans la modernité et la phénoménologie, Escoubas prolonge ainsi une réflexion sur la manière dont le vécu, le corps et la subjectivité forment un champ de savoir propre, à la fois esthétique, analytique et existentiel. Elle meurt à Paris le 18 juillet 2026. &lt;/p&gt;  &lt;audio controls title="Eliane ESCOUBAS par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/10080-25.11.2011-ITEMA_20320112-2011C3403E0190-ITE_00047070_RSCE-21.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;</t>
         </is>
       </c>
-      <c r="H128" s="48" t="inlineStr">
+      <c r="H129" s="48" t="inlineStr">
         <is>
           <t xml:space="preserve">https://www.laphilo.fr/pho/eescoubas-mini.webp</t>
         </is>
       </c>
-      <c r="I128" t="inlineStr">
+      <c r="I129" t="inlineStr">
         <is>
           <t xml:space="preserve">https://laphilo.fr/photo/escoubas.webp</t>
         </is>
       </c>
-      <c r="J128" s="48" t="inlineStr">
+      <c r="J129" s="48" t="inlineStr">
         <is>
           <t xml:space="preserve">esthetique ; epistemologie</t>
         </is>
       </c>
-      <c r="K128" s="48" t="inlineStr">
+      <c r="K129" s="48" t="inlineStr">
         <is>
           <t xml:space="preserve">Phénoménologie</t>
         </is>
       </c>
-      <c r="L128" s="48" t="inlineStr">
+      <c r="L129" s="48" t="inlineStr">
         <is>
           <t xml:space="preserve">philosophe française, historienne de la philosophie et traductrice.</t>
         </is>
       </c>
-      <c r="M128" t="inlineStr">
+      <c r="M129" t="inlineStr">
         <is>
           <t xml:space="preserve">femme</t>
         </is>
       </c>
-      <c r="N128" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-    </row>
-    <row r="129" ht="185.25" customHeight="1" s="49">
-      <c r="A129" s="57" t="n">
+      <c r="N129" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+    </row>
+    <row r="130" ht="185.25" customHeight="1" s="49">
+      <c r="A130" s="57" t="n">
         <v>1938</v>
       </c>
-      <c r="B129" s="57" t="inlineStr">
+      <c r="B130" s="57" t="inlineStr">
         <is>
           <t>2017</t>
         </is>
       </c>
-      <c r="C129" s="57" t="inlineStr">
+      <c r="C130" s="57" t="inlineStr">
         <is>
           <t>1938 – 2017</t>
         </is>
       </c>
-      <c r="D129" s="58" t="inlineStr">
+      <c r="D130" s="58" t="inlineStr">
         <is>
           <t>Jean-François MARQUET</t>
         </is>
       </c>
-      <c r="E129" s="59" t="inlineStr">
+      <c r="E130" s="59" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Jean-Fran%C3%A7ois_Marquet"  title=" Wikipedia"&gt;Jean-François MARQUET&lt;/a&gt; était un philosophe français spécialiste de l'idéalisme allemand et de la mystique, connu pour ses travaux sur Schelling, Hegel, Böhme et &lt;a href="https://fr.wikipedia.org/wiki/N%C3%A9oplatonisme"  title=" neoplatonisme par Wikipedia"&gt;le néoplatonisme. &lt;/a&gt; Agrégé de philosophie et professeur à l'Université Paris-Sorbonne, il fut l'un des meilleurs connaisseurs français de Schelling et l'un des rares philosophes à s'être intéressé aux connexions entre la philosophie spéculative allemande et les traditions mystiques occidentales. &lt;/p&gt; &lt;p&gt; Sa thèse principale, &lt;em&gt;Liberté et Existence. Étude sur la formation de la philosophie de Schelling&lt;/em&gt; (1973), est une analyse rigoureuse et pénétrante du développement de la pensée de Schelling, depuis les premiers textes influencés par Fichte jusqu'à la philosophie tardive de la liberté et de la mythologie. Il y montre la cohérence profonde d'une pensée souvent jugée dispersée, en la centrant sur la problématique de la liberté comme indifférence originaire de l'être. &lt;/p&gt; &lt;p&gt; Dans &lt;em&gt;Miroirs de l'identité. La Littérature hantée par la philosophie&lt;/em&gt; (1996), il explore les relations entre philosophie et littérature à travers des auteurs comme Novalis, Kleist, Hoffmann et Nerval. Ses études sur Jakob Böhme et les thiosophes germaniques contribuèrent à ouvrir la philosophie française à des courants méconnus mais essentiels pour comprendre l'émergence de l'idéalisme allemand. Il représente un philosophe  &lt;a href="https://www.persee.fr/doc/abpo_0399-0826_1976_num_83_2_2819"  title=" les calendriers positivistes par persée"&gt;d'une rare érudition, &lt;/a&gt; capable de naviguer entre la rigueur conceptuelle et l'ouverture aux dimensions poétiques et spirituelles de la pensée. &lt;/p&gt;  &lt;audio controls title="Les strategies du secret par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/10194-14.02.2007-ITEMA_20058582-2007C3035S0033-MEM_000035816_RF-21.mp3" type="audio/mpeg" align="center"&gt;&lt;/audio&gt;  </t>
         </is>
       </c>
-      <c r="F129" s="57" t="inlineStr">
+      <c r="F130" s="57" t="inlineStr">
         <is>
           <t>W1PdYExCQRY</t>
         </is>
       </c>
-      <c r="G129" s="59" t="inlineStr">
+      <c r="G130" s="59" t="inlineStr">
         <is>
           <t>"JEAN FRANCOIS MARQUET" par Didier Doc Pilot</t>
         </is>
       </c>
-      <c r="H129" s="65" t="inlineStr">
+      <c r="H130" s="65" t="inlineStr">
         <is>
           <t>https://www.laphilo.fr/pho/jfmarquet-mini.webp</t>
         </is>
       </c>
-      <c r="J129" s="48" t="inlineStr">
+      <c r="J130" s="48" t="inlineStr">
         <is>
           <t>metaphysique</t>
         </is>
       </c>
-      <c r="K129" s="48" t="inlineStr">
+      <c r="K130" s="48" t="inlineStr">
         <is>
           <t>Phénoménologie</t>
         </is>
       </c>
-      <c r="L129" s="48" t="inlineStr">
+      <c r="L130" s="48" t="inlineStr">
         <is>
           <t>philosophe français spécialiste de l'idéalisme allemand et de la mystique.</t>
         </is>
       </c>
-      <c r="N129" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-    </row>
-    <row r="130" ht="216.75" customHeight="1" s="49">
-      <c r="A130" s="54" t="n">
+      <c r="N130" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+    </row>
+    <row r="131" ht="176.25" customHeight="1" s="49">
+      <c r="A131" s="47">
+        <v>1938</v>
+      </c>
+      <c r="B131" s="47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2021</t>
+        </is>
+      </c>
+      <c r="C131" s="47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1938 – 2021</t>
+        </is>
+      </c>
+      <c r="D131" s="47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pierre RABHI</t>
+        </is>
+      </c>
+      <c r="E131" s="85" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Pierre_Rabhi" title=" Wikipedia"&gt;Pierre RABHI&lt;/a&gt; est un agriculteur, essayiste et militant français, l’une des figures de l’&lt;a href="https://fr.wikipedia.org/wiki/%C3%89cologisme" title=" Wikipedia"&gt;écologie&lt;/a&gt; en France. Né Rabah Rabhi à Kenadsa, une oasis du sud de l’Algérie, il perd sa mère très jeune et est confié à un couple de Français d’Oran ; il se convertit au catholicisme et prend le prénom de Pierre. Venu à Paris, il travaille comme ouvrier, puis s’installe en 1961 avec sa femme Michèle dans les Cévennes ardéchoises, où il devient paysan et pratique une agriculture sans produits chimiques.&lt;/p&gt; &lt;p&gt;À partir de 1981, il forme des paysans au Burkina Faso, puis dans d’autres pays d’Afrique, à l’« &lt;a href="https://www.youtube.com/watch?v=3M0k-8hg-wc" title="L’agroécologie expliquée en 10 minutes ! Matthieu Calame par Metabolism of Cities"&gt;agroécologie &lt;/a&gt;», une agriculture qui respecte les sols et rend les communautés autonomes. Dans ses livres, comme &lt;em&gt;Vers la sobriété heureuse&lt;/em&gt; (2010), il critique la société de consommation et l’idéologie de la croissance : il faut apprendre à vivre avec moins pour être plus heureux. En 2007, il fonde le mouvement Colibris, d’après une légende amérindienne : pendant un incendie de forêt, le colibri apporte des gouttes d’eau dans son bec, car il « fait sa part ».&lt;/p&gt; &lt;p&gt;Très populaire, il est candidat à l’élection présidentielle de 2002, sans réunir les signatures nécessaires. &lt;a href="https://citations.ouest-france.fr/citations-pierre-rabhi-11954.html" title="Toutes les citations de Pierre Rabhi, ses pensées et sa biographie par citation du jour"&gt;Son discours spirituel&lt;/a&gt;, sa proximité avec l’anthroposophie et son peu d’intérêt pour les combats politiques lui valent aussi des critiques, notamment de journalistes et de scientifiques qui contestent certaines de ses affirmations sur l’agriculture. Il meurt à Lyon en 2021. Son appel à une « insurrection des consciences » a inspiré de nombreuses initiatives locales d’écologie.&lt;/p&gt;  &lt;audio controls title="La sobriété heureuse avec pierre Rabhi par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/11200-27.05.2012-ITEMA_20372105-2012C14958E0019-ITE_00051286_RSCE-21.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t xml:space="preserve">tSIQcpxtDCU</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"Pierre Rabhi : la cohérence d'une vie | #Documentaire" par Le Jour du Seigneur</t>
+        </is>
+      </c>
+      <c r="H131" s="48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/rabhi-mini.webp</t>
+        </is>
+      </c>
+      <c r="J131" s="48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ethique ; politique ; spiritualite</t>
+        </is>
+      </c>
+      <c r="K131" s="48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ecologisme</t>
+        </is>
+      </c>
+      <c r="L131" s="48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">agriculteur et essayiste français, pionnier de l’agroécologie et chantre de la « sobriété heureuse ».</t>
+        </is>
+      </c>
+      <c r="N131" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+      <c r="O131"/>
+    </row>
+    <row r="132" ht="216.75" customHeight="1" s="49">
+      <c r="A132" s="54" t="n">
         <v>1939</v>
       </c>
-      <c r="B130" s="54" t="inlineStr">
+      <c r="B132" s="54" t="inlineStr">
         <is>
           <t>2018</t>
         </is>
       </c>
-      <c r="C130" s="54" t="inlineStr">
+      <c r="C132" s="54" t="inlineStr">
         <is>
           <t>1939 – 2018</t>
         </is>
       </c>
-      <c r="D130" s="55" t="inlineStr">
+      <c r="D132" s="55" t="inlineStr">
         <is>
           <t>Clément ROSSET</t>
         </is>
       </c>
-      <c r="E130" s="62" t="inlineStr">
+      <c r="E132" s="62" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Cl%C3%A9ment_Rosset" title=" Wikipedia"&gt;Clément ROSSET&lt;/a&gt; était un philosophe français connu pour sa pensée radicale et son style d'écriture d'une grande clarté. Son œuvre est principalement centrée sur le concept du  &lt;a href="https://www.youtube.com/watch?v=I50Jbj6uQEU" title="Clément Rosset : la réalité ne convient pas ! par Kosmos"&gt;"réel"&lt;/a&gt;  et l'incapacité ou la difficulté de l'homme à l'accepter dans sa singularité et souvent sa cruauté. &lt;/p&gt; &lt;p&gt;&lt;a href="https://www.youtube.com/watch?v=8m_kXVBdtwg"  title=" Le réel et son double, Clément Rosset, 2.2 avant-propos par Thibault BELZACQ"&gt;Le Réel sans double&lt;/a&gt; : Son idée maîtresse est que le réel est unique, singulier et dépourvu de tout "double". Il n'y a pas d'arrière-monde, pas de sens caché, pas de consolation ou d'illusion qui puisse atténuer sa nature brute. Le réel est simplement ce qui est, dans son évidence la plus nue. &lt;/p&gt; &lt;p&gt;Le Refus du double et de l'illusion : Une grande partie de son travail consiste à traquer les différentes formes d'illusions et de doubles que l'humanité crée pour  &lt;a href="https://philitt.fr/2023/09/12/clement-rosset-tout-est-sans-raison/"  title="Clément Rosset : tout est sans raison par Phillitt"&gt;échapper à la confrontation&lt;/a&gt; directe avec le réel. Ces doubles peuvent être d'ordre métaphysique, moral, psychologique, ou même esthétique.&lt;/p&gt; &lt;p&gt;&lt;a href="https://www.youtube.com/watch?v=JDcudFE_uBQ"  title="Entretien avec Pierre Dumayet (1961) par Archives"&gt;Philosophie tragique&lt;/a&gt; et Joie : Bien que sa pensée puisse sembler sombre en insistant sur la cruauté et l'absurdité du réel, il développe une philosophie que l'on qualifie souvent de "tragique" au sens nietzschéen du terme. Il ne s'agit pas de désespoir, mais plutôt de l'affirmation de la vie et du réel tels qu'ils sont, y compris dans leurs aspects les plus difficiles. &lt;/p&gt; &lt;p&gt; Il est également remarquable par son style d'écriture. Loin du jargon philosophique abscons, il privilégie une langue simple, directe et percutante. Cette clarté formelle est au service de la clarté de sa pensée, cherchant à énoncer le réel avec le moins d'interférences possible. Son œuvre, bien que parfois restée en marge des courants universitaires dominants, a marqué par sa radicalité, sa lucidité et sa défense d'une confrontation sans fard avec le réel.  &lt;/p&gt; &lt;audio controls title="Clément Rosset par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/10080-20.12.2013-ITEMA_20564152-2013C3403E0215-21.mp3" type="audio/mpeg" align="center"&gt;&lt;/audio&gt;  </t>
         </is>
       </c>
-      <c r="F130" s="54" t="inlineStr">
+      <c r="F132" s="54" t="inlineStr">
         <is>
           <t>9m6CPt4pRlw</t>
         </is>
       </c>
-      <c r="G130" s="56" t="inlineStr">
+      <c r="G132" s="56" t="inlineStr">
         <is>
           <t>"Clément Rosset (1): Heureux, malgré tout" par Camille Tassel</t>
         </is>
       </c>
-      <c r="H130" s="62" t="inlineStr">
+      <c r="H132" s="62" t="inlineStr">
         <is>
           <t>https://www.laphilo.fr/pho/rosset-mini.webp</t>
         </is>
       </c>
-      <c r="J130" s="48" t="inlineStr">
+      <c r="J132" s="48" t="inlineStr">
         <is>
           <t>metaphysique ; ethique</t>
         </is>
       </c>
-      <c r="K130" s="48" t="inlineStr">
+      <c r="K132" s="48" t="inlineStr">
         <is>
           <t>Naturalisme</t>
         </is>
       </c>
-      <c r="L130" s="48" t="inlineStr">
+      <c r="L132" s="48" t="inlineStr">
         <is>
           <t>philosophe français du tragique et de la théorie du réel.</t>
         </is>
       </c>
-      <c r="N130" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-    </row>
-    <row r="131" ht="199.5" customHeight="1" s="49">
-      <c r="A131" s="57" t="n">
+      <c r="N132" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+    </row>
+    <row r="133" ht="199.5" customHeight="1" s="49">
+      <c r="A133" s="57" t="n">
         <v>1940</v>
       </c>
-      <c r="B131" s="57" t="inlineStr">
+      <c r="B133" s="57" t="inlineStr">
         <is>
           <t>2021</t>
         </is>
       </c>
-      <c r="C131" s="57" t="inlineStr">
+      <c r="C133" s="57" t="inlineStr">
         <is>
           <t>1940 – 2021</t>
         </is>
       </c>
-      <c r="D131" s="58" t="inlineStr">
+      <c r="D133" s="58" t="inlineStr">
         <is>
           <t>Jacques BOUVERESSE</t>
         </is>
       </c>
-      <c r="E131" s="65" t="inlineStr">
+      <c r="E133" s="65" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Jacques_Bouveresse"  title=" Wikipedia"&gt;Jacques BOUVERESSE&lt;/a&gt; était un philosophe français du courant analytique, connu pour son rationalisme exigeant, son &lt;a href="https://www.youtube.com/watch?v=mfGM00nmj20"  title=" Wittgenstein et l'intériorité 一 Jacques Bouveresse par Andrea Cirla "&gt;travail sur Wittgenstein &lt;/a&gt; et sa critique des dérives du milieu intellectuel français. Il a largement contribué à introduire et stabiliser en France une philosophie soucieuse de vérité, de clarté et d’argumentation rigoureuse. &lt;/p&gt; &lt;p&gt; Ses domaines privilégiés sont la philosophie de la connaissance, des sciences, des mathématiques, de la logique, du langage, ainsi qu’une philosophie de la culture attentive à la littérature et à la critique sociale.  Il se réclame du rationalisme des Lumières et s’inspire fortement de la philosophie analytique, du Cercle de Vienne, de Frege, de Gödel et de la tradition d’Europe centrale. Wittgenstein, qu’il contribue à faire connaître en France, est l’une de ses références centrales. &lt;/p&gt; &lt;p&gt; Il défend une position rationaliste dont le prolongement éthique est ce qu’il appelle la  &lt;a href="https://www.persee.fr/doc/lgge_0458-726x_1971_num_6_21_2079" title="Langage ordinaire et philosophie par Persée "&gt;"modestie intellectuelle" &lt;/a&gt; : ne pas exagérer ce que la philosophie peut faire, refuser le pathos et le prestige facile. Il combat le relativisme, l’historicisme radical et les remises en cause globales de la notion de vérité, notamment chez certains auteurs français, tout en reconnaissant par ailleurs leur importance. &lt;/p&gt; &lt;p&gt; Sa grande thèse, "Le Mythe de l’intériorité", porte sur Wittgenstein, le langage privé, l’expérience et la signification, et a joué un rôle clé dans la réception française de Wittgenstein. Il consacre de nombreux travaux à Robert Musil et Karl Kraus, qu’il lit comme des alliés dans un combat pour l’exactitude, la critique de la bêtise et des illusions de la culture moderne. &lt;/p&gt;  &lt;audio controls title="Jacques Bouveresse, à la recherche de la clarté par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/10351-11.05.2021-ITEMA_23961779-2000C3500E0287-21.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;</t>
         </is>
       </c>
-      <c r="F131" s="57" t="inlineStr">
+      <c r="F133" s="57" t="inlineStr">
         <is>
           <t>72_NdVNiFbg</t>
         </is>
       </c>
-      <c r="G131" s="59" t="inlineStr">
+      <c r="G133" s="59" t="inlineStr">
         <is>
           <t xml:space="preserve">"Jacques Bouveresse, Prodiges et vertiges de l'analogie" par Philosophie Analytique</t>
         </is>
       </c>
-      <c r="H131" s="65" t="inlineStr">
+      <c r="H133" s="65" t="inlineStr">
         <is>
           <t>https://www.laphilo.fr/pho/bouveresse-mini.webp</t>
         </is>
       </c>
-      <c r="J131" s="48" t="inlineStr">
+      <c r="J133" s="48" t="inlineStr">
         <is>
           <t>epistemologie ; logique</t>
         </is>
       </c>
-      <c r="K131" s="48" t="inlineStr">
+      <c r="K133" s="48" t="inlineStr">
         <is>
           <t>Analytique</t>
         </is>
       </c>
-      <c r="L131" s="48" t="inlineStr">
+      <c r="L133" s="48" t="inlineStr">
         <is>
           <t>philosophe français du courant analytique d'un rationalisme exigeant.</t>
         </is>
       </c>
-      <c r="N131" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-    </row>
-    <row r="132" ht="164.25" customHeight="1" s="49">
-      <c r="A132" s="54" t="n">
+      <c r="N133" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+    </row>
+    <row r="134" ht="164.25" customHeight="1" s="49">
+      <c r="A134" s="54" t="n">
         <v>1940</v>
       </c>
-      <c r="B132" s="54" t="inlineStr">
+      <c r="B134" s="54" t="inlineStr">
         <is>
           <t>2021</t>
         </is>
       </c>
-      <c r="C132" s="54" t="inlineStr">
+      <c r="C134" s="54" t="inlineStr">
         <is>
           <t>1940 – 2021</t>
         </is>
       </c>
-      <c r="D132" s="55" t="inlineStr">
+      <c r="D134" s="55" t="inlineStr">
         <is>
           <t>Jean-Luc NANCY</t>
         </is>
       </c>
-      <c r="E132" s="62" t="inlineStr">
+      <c r="E134" s="62" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Jean-Luc_Nancy"  title=" Wikipedia"&gt;Jean-Luc NANCY&lt;/a&gt; était un philosophe français, agrégé de philosophie, il fut professeur à l'Université de Strasbourg jusqu'à sa retraite. Sa pensée, en dialogue constant avec Heidegger, Derrida et Lacoue-Labarthe — avec lequel il collabora étroitement — porte sur le « sens du monde », la communauté, le corps et le toucher. &lt;/p&gt; &lt;p&gt; Son œuvre est marquée par le questionnement du « with » (avec), du « being-with » heideggerien. Dans &lt;em&gt;La Communauté désoeuvrée&lt;/em&gt; (1986), il développe une pensée de la communauté qui refuse toute forme d'immanentisme ou de fusion : la communauté véritable n'est pas une substance commune, mais  &lt;a href="https://www.youtube.com/watch?v=fZK6pEAPxEw"  title="jean luc Nancy par Institut Humanités "&gt;l'exposition partagée &lt;/a&gt; de la singularité de chacun. Cette réflexion, en dialogue critique avec Blanchot et Bataille, a eu un retentissement considérable dans les débats contemporains sur la politique, la communauté et l'identité. &lt;/p&gt; &lt;p&gt; Dans &lt;em&gt;Corpus&lt;/em&gt; (1992) et &lt;em&gt;Noli me tangere&lt;/em&gt; (2003), il explore  &lt;a href="https://www.youtube.com/watch?v=1kCExw6Wp9k"  title="jean luc Nancy par Lacan TV "&gt;la philosophie du corps &lt;/a&gt; et du toucher comme modes fondamentaux de l'être-au-monde. Son essai sur le sens — &lt;em&gt;Le Sens du monde&lt;/em&gt; (1993) — aborde la question de la possibilité du sens dans un monde déserté par les transcendances. &lt;em&gt;L'Intrus&lt;/em&gt; (2000), bref récit autobiographique sur sa transplantation cardiaque, mêle réflexion philosophique et expérience personnelle de la maladie et de l'altérité. Son œuvre, immense et diverse, témoigne d'une pensée vivante et rigoureuse toujours en dialogue avec la littérature, l'art et la politique. &lt;/p&gt;  &lt;audio controls title="Jean luc Nancy par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/11472-06.02.2011-ITEMA_20267545-2011C16153E0003-ITE_00040439_RSCE-21.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;</t>
         </is>
       </c>
-      <c r="F132" s="54" t="inlineStr">
+      <c r="F134" s="54" t="inlineStr">
         <is>
           <t>0ONnn-EL0BA</t>
         </is>
       </c>
-      <c r="G132" s="56" t="inlineStr">
+      <c r="G134" s="56" t="inlineStr">
         <is>
           <t>"Jean-Luc Nancy, philosophe à l'intelligence sensible" par France Culture</t>
         </is>
       </c>
-      <c r="H132" s="62" t="inlineStr">
+      <c r="H134" s="62" t="inlineStr">
         <is>
           <t>https://www.laphilo.fr/pho/jlnancy-mini.webp</t>
         </is>
       </c>
-      <c r="J132" s="48" t="inlineStr">
+      <c r="J134" s="48" t="inlineStr">
         <is>
           <t>metaphysique ; politique</t>
         </is>
       </c>
-      <c r="K132" s="48" t="inlineStr">
+      <c r="K134" s="48" t="inlineStr">
         <is>
           <t>Post-structuralisme</t>
         </is>
       </c>
-      <c r="L132" s="48" t="inlineStr">
+      <c r="L134" s="48" t="inlineStr">
         <is>
           <t>philosophe français qui porta le « sens du monde », la communauté, le corps et le toucher.</t>
         </is>
       </c>
-      <c r="N132" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-    </row>
-    <row r="133" ht="201" customHeight="1" s="49">
-      <c r="A133" s="54" t="n">
+      <c r="N134" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+    </row>
+    <row r="135" ht="201" customHeight="1" s="49">
+      <c r="A135" s="54" t="n">
         <v>1940</v>
       </c>
-      <c r="B133" s="54" t="n">
+      <c r="B135" s="54" t="n">
         <v>2007</v>
       </c>
-      <c r="C133" s="54" t="inlineStr">
+      <c r="C135" s="54" t="inlineStr">
         <is>
           <t>1940 – 2007</t>
         </is>
       </c>
-      <c r="D133" s="55" t="inlineStr">
+      <c r="D135" s="55" t="inlineStr">
         <is>
           <t>Philippe LACOUE-LABARTHE</t>
         </is>
       </c>
-      <c r="E133" s="62" t="inlineStr">
+      <c r="E135" s="62" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Philippe_Lacoue-Labarthe"  title=" Wikipedia"&gt;Philippe LACOUE-LABARTHE&lt;/a&gt; était un philosophe, critique littéraire, traducteur et théoricien français né à Tours et connu pour ses travaux sur la mimésis, le romantisme allemand, Hölderlin, Heidegger, Derrida et la relation entre esthétique et politique. Il a aussi beaucoup compté dans le milieu intellectuel de Strasbourg, où il a enseigné longtemps et travaillé avec Jean-Luc Nancy. &lt;/p&gt; &lt;p&gt; Son  &lt;a href="https://maitron.fr/lacoue-labarthe-philippe/"  title=" lacoue-labarthe par le maitron"&gt;œuvre interroge &lt;/a&gt; la façon dont l’art, la philosophie et la politique s’entrecroisent, notamment à travers la notion de mimésis et la critique de l’“esthétisation du politique”. Il a aussi travaillé sur le romantisme allemand et sur la réception de Hölderlin, qu’il considérait comme une figure majeure. &lt;/p&gt; &lt;p&gt; Parmi les livres souvent cités, on trouve Le Titre de la lettre avec Jean-Luc Nancy, L’Absolu littéraire, L’Imitation des modernes, La Fiction du politique et Heidegger, la politique du poème. Il a également traduit plusieurs auteurs allemands majeurs, dont Heidegger, Hölderlin, Nietzsche, Benjamin et Celan. &lt;/p&gt; &lt;p&gt; Sa pensée tourne autour de trois idées principales : La représentation n’est jamais transparente : ce que nous montrons, racontons ou jouons n’est jamais la réalité elle-même, mais une forme, un masque, une imitation. La littérature et le théâtre sont essentiels pour comprendre la philosophie, parce qu’ils révèlent ce que les concepts cachent ou simplifient.popups. Le lien entre esthétique et politique est dangereux : il a beaucoup réfléchi à la manière dont l’art, les mythes et les images peuvent servir le politique, y compris dans des formes fascisantes. &lt;/p&gt; 
  &lt;audio controls title="les versions de philippe lacoue labarthe par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/16409-16.03.2007-ITEMA_20062386-2007C6409S0011-MEM_000036772_RF-21.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;  </t>
         </is>
       </c>
-      <c r="F133" s="54" t="inlineStr">
+      <c r="F135" s="54" t="inlineStr">
         <is>
           <t>CI6zYPSwsoY</t>
         </is>
       </c>
-      <c r="G133" s="56" t="inlineStr">
+      <c r="G135" s="56" t="inlineStr">
         <is>
           <t>voyage a tubingen par capuseen</t>
         </is>
       </c>
-      <c r="H133" s="62" t="inlineStr">
+      <c r="H135" s="62" t="inlineStr">
         <is>
           <t>https://www.laphilo.fr/pho/pllabarthe-mini.webp</t>
         </is>
       </c>
-      <c r="J133" s="48" t="inlineStr">
+      <c r="J135" s="48" t="inlineStr">
         <is>
           <t>politique ; epistemologie</t>
         </is>
       </c>
-      <c r="K133" s="48" t="inlineStr">
+      <c r="K135" s="48" t="inlineStr">
         <is>
           <t>Déconstructionnisme</t>
         </is>
       </c>
-      <c r="L133" s="85" t="inlineStr">
+      <c r="L135" s="85" t="inlineStr">
         <is>
           <t xml:space="preserve"> philosophe et théoricien français connu pour ses travaux sur la mimésis et le romantisme allemand.</t>
         </is>
       </c>
-      <c r="N133" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-    </row>
-    <row r="134" ht="209.25" customHeight="1" s="49">
-      <c r="A134" s="57" t="n">
+      <c r="N135" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+    </row>
+    <row r="136" ht="209.25" customHeight="1" s="49">
+      <c r="A136" s="57" t="n">
         <v>1941</v>
       </c>
-      <c r="B134" s="57" t="inlineStr">
+      <c r="B136" s="57" t="inlineStr">
         <is>
           <t>2019</t>
         </is>
       </c>
-      <c r="C134" s="57" t="inlineStr">
+      <c r="C136" s="57" t="inlineStr">
         <is>
           <t>1941 – 2019</t>
         </is>
       </c>
-      <c r="D134" s="58" t="inlineStr">
+      <c r="D136" s="58" t="inlineStr">
         <is>
           <t>François DELAPORTE</t>
         </is>
       </c>
-      <c r="E134" s="59" t="inlineStr">
+      <c r="E136" s="59" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Fran%C3%A7ois_Delaporte"  title=" Wikipedia"&gt;François DELAPORTE&lt;/a&gt; était un philosophe français spécialiste d'histoire et de philosophie des sciences médicales et biologiques, connu notamment pour ses travaux sur l'histoire des maladies et la philosophie de Georges Canguilhem. Professeur à l'Université de Picardie, il fut l'un des continuateurs de la tradition canguilhémienne d'histoire et philosophie des sciences en France, appliquant cette approche à l'histoire de la médecine et de la biologie. &lt;/p&gt; &lt;p&gt; Son œuvre la plus importante, &lt;em&gt;   &lt;a href="https://www.persee.fr/doc/bec_0373-6237_1993_num_151_2_450700_t1_0415_0000_001"  title=" le savoir sur la maladie par persée"&gt;Le Savoir de la maladie. &lt;/a&gt; Essai sur le choléra de 1832 à Paris&lt;/em&gt; (1990), est une analyse philosophique de l'épidémie de choléra qui ravagea Paris en 1832. Suivant la méthode de Canguilhem et Foucault, il montre comment la compréhension d'une maladie est toujours insérée dans un réseau de savoirs, de pratiques et de pouvoirs qui configurent sa signification médicale et sociale. Cette étude est un modèle du genre pour l'articulation entre histoire des sciences et analyse philosophique. &lt;/p&gt; &lt;p&gt; Il contribua également à faire connaître la pensée de Canguilhem, notamment à travers des études sur &lt;em&gt;Le Normal et le Pathologique&lt;/em&gt; et sur la philosophie biologique canguilhémienne. Ses travaux sur l'histoire des figures du visage, réunis dans &lt;em&gt;Figures de la médecine&lt;/em&gt; (2009), constituent une autre contribution originale à l'intersection de l'histoire de l'art médical et de la philosophie du corps. Delaporte incarne une tradition française de philosophie de la médecine d'une grande rigueur et d'une réelle originalité. &lt;/p&gt;   &lt;audio controls title="François Laporte le vie monastique, pensée en mouvement  par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/11983-19.12.2013-ITEMA_20563752-2013C18137S0353-25.m4a" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;  </t>
         </is>
       </c>
-      <c r="F134" s="57" t="inlineStr">
+      <c r="F136" s="57" t="inlineStr">
         <is>
           <t>Y3FnglRhPxs</t>
         </is>
       </c>
-      <c r="G134" s="59" t="inlineStr">
+      <c r="G136" s="59" t="inlineStr">
         <is>
           <t>"François DELAPORTE 2014" par Colin Guillaume</t>
         </is>
       </c>
-      <c r="H134" s="65" t="inlineStr">
+      <c r="H136" s="65" t="inlineStr">
         <is>
           <t>https://www.laphilo.fr/pho/fdelaporte-mini.webp</t>
         </is>
       </c>
-      <c r="J134" s="48" t="inlineStr">
+      <c r="J136" s="48" t="inlineStr">
         <is>
           <t>epistemologie</t>
         </is>
       </c>
-      <c r="K134" s="48" t="inlineStr">
+      <c r="K136" s="48" t="inlineStr">
         <is>
           <t>Constructivisme</t>
         </is>
       </c>
-      <c r="L134" s="48" t="inlineStr">
+      <c r="L136" s="48" t="inlineStr">
         <is>
           <t>philosophe français spécialiste de philosophie des sciences médicales et biologiques.</t>
         </is>
       </c>
-      <c r="N134" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-    </row>
-    <row r="135" ht="218.25" customHeight="1" s="49">
-      <c r="A135" s="54" t="n">
+      <c r="N136" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+    </row>
+    <row r="137" ht="218.25" customHeight="1" s="49">
+      <c r="A137" s="54" t="n">
         <v>1944</v>
       </c>
-      <c r="B135" s="54" t="inlineStr">
+      <c r="B137" s="54" t="inlineStr">
         <is>
           <t>2022</t>
         </is>
       </c>
-      <c r="C135" s="54" t="inlineStr">
+      <c r="C137" s="54" t="inlineStr">
         <is>
           <t>1944 – 2022</t>
         </is>
       </c>
-      <c r="D135" s="55" t="inlineStr">
+      <c r="D137" s="55" t="inlineStr">
         <is>
           <t>Dominique LECOURT</t>
         </is>
       </c>
-      <c r="E135" s="63" t="inlineStr">
+      <c r="E137" s="63" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Dominique_Lecourt" title=" Wikipedia"&gt;Dominique LECOURT&lt;/a&gt; était un philosophe français connu pour ses travaux en philosophie des sciences et pour avoir prolongé, de manière originale, l’héritage de Gaston Bachelard et de Georges Canguilhem. Sa philosophie se déploie autour de la philosophie des sciences, des rapports entre savoir et pouvoir, et d’une réflexion éthique et politique sur la technoscience. &lt;/p&gt; &lt;p&gt; Disciple de Bachelard, il défend un "rationalisme appliqué" : la raison scientifique n’est pas une abstraction pure, mais une activité qui se confronte à des obstacles, des erreurs, des idéologies, et qui progresse en les surmontant. Dans cet esprit, il insiste sur le rôle des   &lt;a href="https://www.youtube.com/watch?v=YyntmVUC1wE"  title=" D Lecourt par booksmag"&gt;"obstacles épistémologiques" &lt;/a&gt;  qui déroutent la recherche et qu’il faut analyser pour comprendre les progrès de la science. Il montre aussi que l’imagination n’est pas l’ennemie de la science : elle est indispensable à l’invention scientifique autant qu’à la rigueur des démonstrations. &lt;/p&gt; &lt;p&gt; Il cherche à contrer à la fois  l’"arrogance du scientisme"  et la technophobie ou le catastrophisme qui voient dans la technique uniquement une menace. Pour lui, la philosophie des sciences doit donner les moyens de penser la puissance des technosciences sans la sacraliser ni la diaboliser. Cela implique un dialogue étroit avec les scientifiques, mais aussi avec les juristes, médecins, sociologues, responsables politiques, pour éclairer les choix collectifs. &lt;/p&gt; &lt;p&gt; Il développe une conception de la liberté qui refuse aussi bien l’individualisme égoïste que le "moralisme libertaire". La liberté, pour lui, se joue dans le rapport aux savoirs et aux techniques : il s’agit d’en faire des instruments d’émancipation plutôt que de domination.&lt;/p&gt; &lt;p&gt; Parmi ses nombreux livres (plus d’une trentaine), on peut citer : -"Lyssenko, histoire réelle d’une "science prolétarienne" : analyse de la manipulation politique de la biologie en URSS. "L’Amérique entre la Bible et Darwin" : sur les tensions entre science et religion aux États‑Unis. "Contre la peur" : proposition d’une éthique de la recherche qui affirme la valeur de l’esprit critique face aux discours alarmistes. &lt;a href="https://www.youtube.com/watch?v=3e2K5Ogywl4"  title=" De quoi le transhumanisme est-il le nom ? par Editions M-Editer"&gt;"Humain post‑humain" &lt;/a&gt;  : réflexion sur les promesses et les dangers du transhumanisme. &lt;/p&gt;   &lt;audio controls title="L'age de la peur par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/10075-03.03.2010-ITEMA_20218172-2010C6608S0062-NET_E99ABA70-9EA1-4399-B0F4-9460EA040C60-21.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;  </t>
         </is>
       </c>
-      <c r="F135" s="54" t="inlineStr">
+      <c r="F137" s="54" t="inlineStr">
         <is>
           <t>YyntmVUC1wE</t>
         </is>
       </c>
-      <c r="G135" s="56" t="inlineStr">
+      <c r="G137" s="56" t="inlineStr">
         <is>
           <t>"D Lecourt" par Booksmag</t>
         </is>
       </c>
-      <c r="H135" s="62" t="inlineStr">
+      <c r="H137" s="62" t="inlineStr">
         <is>
           <t>https://www.laphilo.fr/pho/lecourt-mini.webp</t>
         </is>
       </c>
-      <c r="J135" s="48" t="inlineStr">
+      <c r="J137" s="48" t="inlineStr">
         <is>
           <t>epistemologie</t>
         </is>
       </c>
-      <c r="K135" s="48" t="inlineStr">
+      <c r="K137" s="48" t="inlineStr">
         <is>
           <t>Marxisme ; Constructivisme</t>
         </is>
       </c>
-      <c r="L135" s="48" t="inlineStr">
+      <c r="L137" s="48" t="inlineStr">
         <is>
           <t>philosophe français connu pour ses travaux en philosophie des sciences.</t>
         </is>
       </c>
-      <c r="N135" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-    </row>
-    <row r="136" ht="157.5" customHeight="1" s="49">
-      <c r="A136" s="57" t="n">
+      <c r="N137" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+    </row>
+    <row r="138" ht="157.5" customHeight="1" s="49">
+      <c r="A138" s="57" t="n">
         <v>1945</v>
       </c>
-      <c r="B136" s="57" t="inlineStr">
+      <c r="B138" s="57" t="inlineStr">
         <is>
           <t>2006</t>
         </is>
       </c>
-      <c r="C136" s="57" t="inlineStr">
+      <c r="C138" s="57" t="inlineStr">
         <is>
           <t>1945 – 2006</t>
         </is>
       </c>
-      <c r="D136" s="58" t="inlineStr">
+      <c r="D138" s="58" t="inlineStr">
         <is>
           <t>Jean-Michel BERTHELOT</t>
         </is>
       </c>
-      <c r="E136" s="65" t="inlineStr">
+      <c r="E138" s="65" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Jean-Michel_Berthelot"  title=" Wikipedia"&gt;Jean-Michel BERTHELOT&lt;/a&gt; était un philosophe et sociologue français spécialiste d'épistémologie des sciences sociales. Professeur à l'Université de Paris IV-Sorbonne et à l'Université du Québec à Montréal, il contribua de manière décisive à la réflexion philosophique sur les fondements et les méthodes des sciences humaines et sociales. Son œuvre joint la rigueur épistémologique à une large culture philosophique et sociologique. &lt;/p&gt; &lt;p&gt; Son ouvrage principal, &lt;em&gt; &lt;a href="https://www.persee.fr/doc/sotra_0038-0296_1992_num_34_3_2605_t1_0388_0000_3"  title="l’intelligence du social par persée "&gt; L'Intelligence du social&lt;/a&gt; &lt;/em&gt; (1990), est une analyse approfondie des schèmes d'intelligibilité que les sciences sociales utilisent pour rendre compte de la réalité sociale : le schème causal, le schème fonctionnel, le schème structural, le schème herméneutique et d'autres modes d'explication. Berthelot montre que chaque paradigme sociologique privilégie un mode d'intelligibilité particulier, ce qui permet de comprendre à la fois leurs apports spécifiques et leurs limites. Ce livre constitue l'une des contributions les plus claires et les plus systématiques à la philosophie des sciences sociales en langue française. &lt;/p&gt; &lt;p&gt; Dans &lt;em&gt;Epistémologie des sciences sociales&lt;/em&gt; (2001, ouvrage collectif qu'il dirigea), il offrit un panorama complet des questions épistémologiques fondamentales que posent les sciences humaines et sociales : la causalité, la compréhension, la mesure, la modélisation, la réflexivité et les rapports entre science et valeurs. Ses travaux contribuèrent à établir l'épistémologie des sciences sociales comme une discipline à part entière dans le paysage universitaire français, en dialogue constant avec la philosophie des sciences anglophones et continentale. &lt;/p&gt;</t>
         </is>
       </c>
-      <c r="F136" s="57" t="inlineStr">
+      <c r="F138" s="57" t="inlineStr">
         <is>
           <t>032-iGqk37A</t>
         </is>
       </c>
-      <c r="G136" s="59" t="inlineStr">
+      <c r="G138" s="59" t="inlineStr">
         <is>
           <t>"JM BERTHELOT" par SFCR</t>
         </is>
       </c>
-      <c r="H136" s="65" t="inlineStr">
+      <c r="H138" s="65" t="inlineStr">
         <is>
           <t>https://www.laphilo.fr/pho/jmberthelot-mini.webp</t>
         </is>
       </c>
-      <c r="J136" s="48" t="inlineStr">
+      <c r="J138" s="48" t="inlineStr">
         <is>
           <t>epistemologie</t>
         </is>
       </c>
-      <c r="K136" s="48" t="inlineStr">
+      <c r="K138" s="48" t="inlineStr">
         <is>
           <t>Constructivisme</t>
         </is>
       </c>
-      <c r="L136" s="48" t="inlineStr">
+      <c r="L138" s="48" t="inlineStr">
         <is>
           <t>philosophe et sociologue français spécialiste d'épistémologie des sciences sociales.</t>
-        </is>
-      </c>
-      <c r="N136" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-    </row>
-    <row r="137" ht="166.5" customHeight="1" s="49">
-      <c r="A137" s="54" t="n">
-        <v>1946</v>
-      </c>
-      <c r="B137" s="54" t="inlineStr">
-        <is>
-          <t>2010</t>
-        </is>
-      </c>
-      <c r="C137" s="54" t="inlineStr">
-        <is>
-          <t>1946 – 2010</t>
-        </is>
-      </c>
-      <c r="D137" s="55" t="inlineStr">
-        <is>
-          <t>Daniel BENSAÏD</t>
-        </is>
-      </c>
-      <c r="E137" s="62" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Daniel_Bensa%C3%AFd"  title=" Wikipedia"&gt;Daniel BENSAÏD&lt;/a&gt; était un philosophe français marxiste, l'un des intellectuels les plus importants de la gauche radicale française de son époque. Né à Paris dans une famille juive d'origine algérienne, il fut l'un des leaders de la révolte étudiante de mai 1968 à Paris-Nanterre aux côtés de Daniel Cohn-Bendit. Professeur de philosophie à l'Université Paris VIII-Saint-Denis, il fut membre dirigeant de la Ligue communiste révolutionnaire (LCR) et de son successeur le Nouveau Parti Anticapitaliste (NPA). &lt;/p&gt; &lt;p&gt; Sa pensée philosophique chercha à renouveler le marxisme en le débarrassant des &lt;a href="https://www.youtube.com/watch?v=uxBvxfRI2CE"  title="la privatisation du monde par bibou11slalala "&gt; simplifications téléologiques &lt;/a&gt; et en l'ouvrant à des problématiques nouvelles. Dans &lt;em&gt;Marx l'intempestif&lt;/em&gt; (1995), il défend un Marx débarrassé du déterminisme historique et de la philosophie du progrès, un Marx « intempestif » qui pense la politique comme art du possible et de l'impossible, en dialogue avec Blaise Pascal et Walter Benjamin. Ce livre renouvela profondément la  &lt;a href="https://www.youtube.com/watch?v=is8Ya038-Q4"  title="l’héritage de Marx par socialtram "&gt; lecture de Marx &lt;/a&gt; dans la gauche française. &lt;/p&gt; &lt;p&gt; Dans &lt;em&gt;Le Pari mélancolique&lt;/em&gt; (1997) et &lt;em&gt;Résistances&lt;/em&gt; (2001), il développe une philosophie de l'engagement politique nourrie par la mélancolie des défaites mais portée par une fidélité irréductible à l'émancipation. Sa réflexion sur les rapports entre philosophie et politique, entre utopie et stratégie, constitue l'une des contributions les plus originales à la pensée marxiste contemporaine. Polémiste redoutable et pédagogue exigeant, il laissa une empreinte profonde sur plusieurs générations de militants et d'intellectuels de gauche. &lt;/p&gt;  &lt;audio controls title="Daniel Bensaid  par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/10075-11.12.2006-ITEMA_20049670-2006C6608S0221-MEM_000033324_RF-21.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt; </t>
-        </is>
-      </c>
-      <c r="F137" s="54" t="inlineStr">
-        <is>
-          <t>xFJLPfAwApo</t>
-        </is>
-      </c>
-      <c r="G137" s="56" t="inlineStr">
-        <is>
-          <t>"Daniel Bensaïd sur l'idée du communisme" par Videos Politiques</t>
-        </is>
-      </c>
-      <c r="H137" s="62" t="inlineStr">
-        <is>
-          <t>https://www.laphilo.fr/pho/bensaid-mini.webp</t>
-        </is>
-      </c>
-      <c r="J137" s="48" t="inlineStr">
-        <is>
-          <t>politique</t>
-        </is>
-      </c>
-      <c r="K137" s="48" t="inlineStr">
-        <is>
-          <t>Marxisme</t>
-        </is>
-      </c>
-      <c r="L137" s="48" t="inlineStr">
-        <is>
-          <t>philosophe français marxiste, intellectuel important de la gauche radicale française.</t>
-        </is>
-      </c>
-      <c r="M137" t="inlineStr">
-        <is>
-          <t xml:space="preserve">juive</t>
-        </is>
-      </c>
-      <c r="N137" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-    </row>
-    <row r="138" ht="210" customHeight="1" s="49">
-      <c r="A138" s="57" t="n">
-        <v>1947</v>
-      </c>
-      <c r="B138" s="57" t="inlineStr">
-        <is>
-          <t>2022</t>
-        </is>
-      </c>
-      <c r="C138" s="57" t="inlineStr">
-        <is>
-          <t>1947 - 2022</t>
-        </is>
-      </c>
-      <c r="D138" s="58" t="inlineStr">
-        <is>
-          <t>Bruno LATOUR</t>
-        </is>
-      </c>
-      <c r="E138" s="59" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Bruno_Latour"  title=" Wikipedia"&gt;Bruno LATOUR&lt;/a&gt;  est un sociologue, anthropologue et philosophe français connu pour ses travaux sur la sociologie des sciences, la philosophie des sciences et l'anthropologie des modernes.&lt;/p&gt; &lt;p&gt; L'un des concepts clés développés par Latour est celui de l'acteur-réseau, également connu sous le nom de &lt;a href="https://fr.wikipedia.org/wiki/Th%C3%A9orie_de_l%27acteur-r%C3%A9seau"  title="Théorie de l'acteur-réseau par Wikipedia "&gt; théorie de l'acteur-réseau (ANT)&lt;/a&gt;. Selon cette approche, les acteurs humains et non humains sont considérés comme des "actants" qui agissent en collaboration pour produire des réalités sociales complexes. L'ANT remet en question la distinction traditionnelle entre les sujets humains et les objets inanimés, soulignant plutôt les relations et les interactions entre eux. &lt;/p&gt; &lt;p&gt; Il s'est  intéressé aux enjeux environnementaux et a contribué au développement de l'écologie politique. Il a souligné l'importance de prendre en compte les dimensions politiques et sociales dans la compréhension des questions écologiques et climatiques. Son livre &lt;a href="http://www.bruno-latour.fr/sites/default/files/uploads/TELERAMA.pdf"  title="Nous n'avons jamais été moderne par Bruno-Latour "&gt; "Nous n'avons jamais été modernes" &lt;/a&gt; (1991) remet en question la distinction entre nature et culture, mettant en lumière les façons dont les sciences et les technologies façonnent notre compréhension du monde. &lt;/p&gt; &lt;p&gt; En plus de ses travaux académiques, Bruno Latour a également participé à des &lt;a href="https://profondeurdechamps.com/2012/10/19/entretien-avec-bruno-latour-12-lart-et-la-science/"  title="L'art et la science par Profondeurdechamps "&gt; projets artistiques &lt;/a&gt; et curatoriaux. Il a collaboré avec des artistes contemporains et a contribué à des expositions d'art qui explorent les thèmes de la science, de la technologie et de l'environnement.&lt;/p&gt; &lt;audio controls title="Introduction à la pensée de Bruno LATOUR par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/22676-06.05.2022-ITEMA_23017705-2022F45096S0126-22.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt; </t>
-        </is>
-      </c>
-      <c r="F138" s="57" t="inlineStr">
-        <is>
-          <t>BqM-sk_ZLeU</t>
-        </is>
-      </c>
-      <c r="G138" s="65" t="inlineStr">
-        <is>
-          <t>"Ce virus est là pour nous préparer au nouveau régime climatique" par France Culture</t>
-        </is>
-      </c>
-      <c r="H138" s="65" t="inlineStr">
-        <is>
-          <t>https://www.laphilo.fr/pho/latour-mini.webp</t>
-        </is>
-      </c>
-      <c r="J138" s="48" t="inlineStr">
-        <is>
-          <t>epistemologie ; politique</t>
-        </is>
-      </c>
-      <c r="K138" s="48" t="inlineStr">
-        <is>
-          <t>Constructivisme</t>
-        </is>
-      </c>
-      <c r="L138" s="48" t="inlineStr">
-        <is>
-          <t>philosophe français inscrit dans le mouvement du Nouveau Réalisme.</t>
         </is>
       </c>
       <c r="N138" t="inlineStr">
@@ -9214,461 +9213,482 @@
     </row>
     <row r="139" ht="166.5" customHeight="1" s="49">
       <c r="A139" s="54" t="n">
+        <v>1946</v>
+      </c>
+      <c r="B139" s="54" t="inlineStr">
+        <is>
+          <t>2010</t>
+        </is>
+      </c>
+      <c r="C139" s="54" t="inlineStr">
+        <is>
+          <t>1946 – 2010</t>
+        </is>
+      </c>
+      <c r="D139" s="55" t="inlineStr">
+        <is>
+          <t>Daniel BENSAÏD</t>
+        </is>
+      </c>
+      <c r="E139" s="62" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Daniel_Bensa%C3%AFd"  title=" Wikipedia"&gt;Daniel BENSAÏD&lt;/a&gt; était un philosophe français marxiste, l'un des intellectuels les plus importants de la gauche radicale française de son époque. Né à Paris dans une famille juive d'origine algérienne, il fut l'un des leaders de la révolte étudiante de mai 1968 à Paris-Nanterre aux côtés de Daniel Cohn-Bendit. Professeur de philosophie à l'Université Paris VIII-Saint-Denis, il fut membre dirigeant de la Ligue communiste révolutionnaire (LCR) et de son successeur le Nouveau Parti Anticapitaliste (NPA). &lt;/p&gt; &lt;p&gt; Sa pensée philosophique chercha à renouveler le marxisme en le débarrassant des &lt;a href="https://www.youtube.com/watch?v=uxBvxfRI2CE"  title="la privatisation du monde par bibou11slalala "&gt; simplifications téléologiques &lt;/a&gt; et en l'ouvrant à des problématiques nouvelles. Dans &lt;em&gt;Marx l'intempestif&lt;/em&gt; (1995), il défend un Marx débarrassé du déterminisme historique et de la philosophie du progrès, un Marx « intempestif » qui pense la politique comme art du possible et de l'impossible, en dialogue avec Blaise Pascal et Walter Benjamin. Ce livre renouvela profondément la  &lt;a href="https://www.youtube.com/watch?v=is8Ya038-Q4"  title="l’héritage de Marx par socialtram "&gt; lecture de Marx &lt;/a&gt; dans la gauche française. &lt;/p&gt; &lt;p&gt; Dans &lt;em&gt;Le Pari mélancolique&lt;/em&gt; (1997) et &lt;em&gt;Résistances&lt;/em&gt; (2001), il développe une philosophie de l'engagement politique nourrie par la mélancolie des défaites mais portée par une fidélité irréductible à l'émancipation. Sa réflexion sur les rapports entre philosophie et politique, entre utopie et stratégie, constitue l'une des contributions les plus originales à la pensée marxiste contemporaine. Polémiste redoutable et pédagogue exigeant, il laissa une empreinte profonde sur plusieurs générations de militants et d'intellectuels de gauche. &lt;/p&gt;  &lt;audio controls title="Daniel Bensaid  par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/10075-11.12.2006-ITEMA_20049670-2006C6608S0221-MEM_000033324_RF-21.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt; </t>
+        </is>
+      </c>
+      <c r="F139" s="54" t="inlineStr">
+        <is>
+          <t>xFJLPfAwApo</t>
+        </is>
+      </c>
+      <c r="G139" s="56" t="inlineStr">
+        <is>
+          <t>"Daniel Bensaïd sur l'idée du communisme" par Videos Politiques</t>
+        </is>
+      </c>
+      <c r="H139" s="62" t="inlineStr">
+        <is>
+          <t>https://www.laphilo.fr/pho/bensaid-mini.webp</t>
+        </is>
+      </c>
+      <c r="J139" s="48" t="inlineStr">
+        <is>
+          <t>politique</t>
+        </is>
+      </c>
+      <c r="K139" s="48" t="inlineStr">
+        <is>
+          <t>Marxisme</t>
+        </is>
+      </c>
+      <c r="L139" s="48" t="inlineStr">
+        <is>
+          <t>philosophe français marxiste, intellectuel important de la gauche radicale française.</t>
+        </is>
+      </c>
+      <c r="M139" t="inlineStr">
+        <is>
+          <t xml:space="preserve">juive</t>
+        </is>
+      </c>
+      <c r="N139" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+    </row>
+    <row r="140" ht="210" customHeight="1" s="49">
+      <c r="A140" s="57" t="n">
+        <v>1947</v>
+      </c>
+      <c r="B140" s="57" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="C140" s="57" t="inlineStr">
+        <is>
+          <t>1947 - 2022</t>
+        </is>
+      </c>
+      <c r="D140" s="58" t="inlineStr">
+        <is>
+          <t>Bruno LATOUR</t>
+        </is>
+      </c>
+      <c r="E140" s="59" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Bruno_Latour"  title=" Wikipedia"&gt;Bruno LATOUR&lt;/a&gt;  est un sociologue, anthropologue et philosophe français connu pour ses travaux sur la sociologie des sciences, la philosophie des sciences et l'anthropologie des modernes.&lt;/p&gt; &lt;p&gt; L'un des concepts clés développés par Latour est celui de l'acteur-réseau, également connu sous le nom de &lt;a href="https://fr.wikipedia.org/wiki/Th%C3%A9orie_de_l%27acteur-r%C3%A9seau"  title="Théorie de l'acteur-réseau par Wikipedia "&gt; théorie de l'acteur-réseau (ANT)&lt;/a&gt;. Selon cette approche, les acteurs humains et non humains sont considérés comme des "actants" qui agissent en collaboration pour produire des réalités sociales complexes. L'ANT remet en question la distinction traditionnelle entre les sujets humains et les objets inanimés, soulignant plutôt les relations et les interactions entre eux. &lt;/p&gt; &lt;p&gt; Il s'est  intéressé aux enjeux environnementaux et a contribué au développement de l'écologie politique. Il a souligné l'importance de prendre en compte les dimensions politiques et sociales dans la compréhension des questions écologiques et climatiques. Son livre &lt;a href="http://www.bruno-latour.fr/sites/default/files/uploads/TELERAMA.pdf"  title="Nous n'avons jamais été moderne par Bruno-Latour "&gt; "Nous n'avons jamais été modernes" &lt;/a&gt; (1991) remet en question la distinction entre nature et culture, mettant en lumière les façons dont les sciences et les technologies façonnent notre compréhension du monde. &lt;/p&gt; &lt;p&gt; En plus de ses travaux académiques, Bruno Latour a également participé à des &lt;a href="https://profondeurdechamps.com/2012/10/19/entretien-avec-bruno-latour-12-lart-et-la-science/"  title="L'art et la science par Profondeurdechamps "&gt; projets artistiques &lt;/a&gt; et curatoriaux. Il a collaboré avec des artistes contemporains et a contribué à des expositions d'art qui explorent les thèmes de la science, de la technologie et de l'environnement.&lt;/p&gt; &lt;audio controls title="Introduction à la pensée de Bruno LATOUR par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/22676-06.05.2022-ITEMA_23017705-2022F45096S0126-22.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt; </t>
+        </is>
+      </c>
+      <c r="F140" s="57" t="inlineStr">
+        <is>
+          <t>BqM-sk_ZLeU</t>
+        </is>
+      </c>
+      <c r="G140" s="65" t="inlineStr">
+        <is>
+          <t>"Ce virus est là pour nous préparer au nouveau régime climatique" par France Culture</t>
+        </is>
+      </c>
+      <c r="H140" s="65" t="inlineStr">
+        <is>
+          <t>https://www.laphilo.fr/pho/latour-mini.webp</t>
+        </is>
+      </c>
+      <c r="J140" s="48" t="inlineStr">
+        <is>
+          <t>epistemologie ; politique</t>
+        </is>
+      </c>
+      <c r="K140" s="48" t="inlineStr">
+        <is>
+          <t>Constructivisme</t>
+        </is>
+      </c>
+      <c r="L140" s="48" t="inlineStr">
+        <is>
+          <t>philosophe français inscrit dans le mouvement du Nouveau Réalisme.</t>
+        </is>
+      </c>
+      <c r="N140" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+    </row>
+    <row r="141" ht="166.5" customHeight="1" s="49">
+      <c r="A141" s="54" t="n">
         <v>1949</v>
       </c>
-      <c r="B139" s="54" t="inlineStr">
+      <c r="B141" s="54" t="inlineStr">
         <is>
           <t>2017</t>
         </is>
       </c>
-      <c r="C139" s="54" t="inlineStr">
+      <c r="C141" s="54" t="inlineStr">
         <is>
           <t>1949 – 2017</t>
         </is>
       </c>
-      <c r="D139" s="55" t="inlineStr">
+      <c r="D141" s="55" t="inlineStr">
         <is>
           <t>Robert DAMIEN</t>
         </is>
       </c>
-      <c r="E139" s="56" t="inlineStr">
+      <c r="E141" s="56" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Robert_Damien"  title=" Wikipedia"&gt;Robert DAMIEN&lt;/a&gt;   était un philosophe français  spécialiste de l'autorité politique et des tensions démocratiques, connu pour sa réhabilitation éthique de l'autorité comme principe d'élévation collective. Il incarna un rationalisme républicain franc et dialogique. &lt;/p&gt; &lt;p&gt; Il réfléchit aux tensions indépassables de la démocratie : décision vs connaissance, immanence vs autorité, pluralisme vs unité. L'autorité n'est pas abus ou force, mais "augmentation" (étymologiquement) : réciproque, fraternelle, légitime si elle élève sans domination, en rendant des comptes publics. Il prône un "pluralisme cohérent" (inspiré de Bachelard), un cogito relationnel et un État stratège sous souverainetés plurielles, face au déclin des absolus. &lt;/p&gt; &lt;p&gt; Joueur et &lt;a href="https://www.dailymotion.com/video/x18br7c" title="Robert Damien : de la figure de l'entraîneur à celle de Mandela par mediapart"&gt;entraîneur de rugby &lt;/a&gt; au CS Lons-le-Saunier, il intégrait le sport comme modèle philosophique du collectif et de l'autorité républicaine. Le rugby incarne pour lui une coopération interdépendante où la diversité des talents (puissants et habiles) fusionne en "Nous" : circulation du ballon prime sur l'individualisme, reliant partenaires contre adversaire. Pas de "joueurs isolés", mais des équipes où le "jeu sans ballon" (replacements, soutiens obscurs) assure continuité, révélant un "Moi nouveau" via le collectif. Dans "Activité physique et exercices spirituels" paru en 2005, le sport n'est pas idéologique mais matrice de fraternité : effort charnel révèle puissances collectives, appliquées à politique et bibliothèques (pluralité ordonnée). &lt;/p&gt;</t>
         </is>
       </c>
-      <c r="F139" s="54" t="inlineStr">
+      <c r="F141" s="54" t="inlineStr">
         <is>
           <t>iBriZ4Lhzfg</t>
         </is>
       </c>
-      <c r="G139" s="56" t="inlineStr">
+      <c r="G141" s="56" t="inlineStr">
         <is>
           <t>"robert damien les trois qualites de l autorite" par Sylvie Formero</t>
         </is>
       </c>
-      <c r="H139" s="62" t="inlineStr">
+      <c r="H141" s="62" t="inlineStr">
         <is>
           <t>https://www.laphilo.fr/pho/rdamien-mini.webp</t>
         </is>
       </c>
-      <c r="J139" s="48" t="inlineStr">
+      <c r="J141" s="48" t="inlineStr">
         <is>
           <t>politique ; epistemologie</t>
         </is>
       </c>
-      <c r="K139" s="48" t="inlineStr">
+      <c r="K141" s="48" t="inlineStr">
         <is>
           <t>Herméneutique</t>
         </is>
       </c>
-      <c r="L139" s="48" t="inlineStr">
+      <c r="L141" s="48" t="inlineStr">
         <is>
           <t>religieux français spécialiste de l'autorité politique &amp; des tensions démocratiques.</t>
         </is>
       </c>
-      <c r="N139" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-    </row>
-    <row r="140" ht="210.75" customHeight="1" s="49">
-      <c r="A140" s="57" t="n">
+      <c r="N141" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+    </row>
+    <row r="142" ht="210.75" customHeight="1" s="49">
+      <c r="A142" s="57" t="n">
         <v>1950</v>
       </c>
-      <c r="B140" s="57" t="inlineStr">
+      <c r="B142" s="57" t="inlineStr">
         <is>
           <t>2022</t>
         </is>
       </c>
-      <c r="C140" s="57" t="inlineStr">
+      <c r="C142" s="57" t="inlineStr">
         <is>
           <t>1950 – 2022</t>
         </is>
       </c>
-      <c r="D140" s="58" t="inlineStr">
+      <c r="D142" s="58" t="inlineStr">
         <is>
           <t>Catherine COLLIOT-THELENE</t>
         </is>
       </c>
-      <c r="E140" s="65" t="inlineStr">
+      <c r="E142" s="65" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Catherine_Colliot-Th%C3%A9l%C3%A8ne" title=" Wikipedia"&gt;Catherine COLLIOT-THELENE&lt;/a&gt; était une philosophe française  majeure de la philosophie politique contemporaine, spécialiste de Max Weber et penseuse des droits, de la démocratie et de la propriété dans un cadre cosmopolitique. Membre de l’Institut universitaire de France, elle est reconnue comme une référence internationale des études wébériennes. &lt;/p&gt; &lt;p&gt; Son travail se situe au croisement de la philosophie politique et des sciences sociales, avec trois pôles principaux :  &lt;a href="https://www.youtube.com/watch?v=krUYFtq9Jww" title="Max Weber et la violence légitime de l’état par France Culture"&gt;Max Weber, la démocratie et les droits, &lt;/a&gt;  la propriété et le cosmopolitisme.  Elle traduit et commente plusieurs textes de Weber, notamment Le Savant et le politique et Les Communautés, en montrant en détail ses concepts de rationalisation, de désenchantement et de domination. &lt;/p&gt; &lt;p&gt; À partir des années 2000, elle se concentre sur les droits subjectifs, leur articulation avec l’individualisme contemporain et la transformation des rapports entre pouvoirs politiques et économiques. Elle insiste sur la nécessité de penser la normativité (ce qui doit être) à partir d’une analyse précise des structures sociales réelles, d’où son dialogue constant avec le droit, l’histoire et la sociologie. &lt;/p&gt; &lt;p&gt; Dans "La Démocratie sans “demos”  paru en 2011, elle remet en question l’identification classique entre "peuple" et "démocratie". Elle critique la superposition entre souveraineté du peuple et souveraineté territoriale de l’État, qui conduit selon elle à des versions exclusives de la démocratie. &lt;a href="https://www.youtube.com/watch?v=ps2ixtEpgYI" title="la democratie c’est le droit de resistance par Journal l’Humanitét"&gt;Sa philosophie cherche &lt;/a&gt;  une démocratie fondée sur des droits universalisables et sur la participation de tous les sujets, plutôt que sur l’appartenance à une communauté nationale préconstituée. &lt;/p&gt; &lt;p&gt; Elle refuse la séparation entre théorie pure et monde social : pour elle, la philosophie politique doit dialoguer avec les sciences sociales pour produire une critique efficace des institutions et des inégalités. Elle a accompagné, sans posture militante classique mais avec une forte implication intellectuelle, les luttes pour les droits des femmes, des exclus et des étrangers, en cherchant à fournir des outils conceptuels pour penser l’égalité aujourd’hui. &lt;/p&gt; 
  &lt;audio controls title="Les défis juridiques de la migration : existe-t-il un droit à la libre circulation ? par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/21447-09.02.2022-ITEMA_22927630-2022C27677S0040-21.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;</t>
         </is>
       </c>
-      <c r="F140" s="57" t="inlineStr">
+      <c r="F142" s="57" t="inlineStr">
         <is>
           <t>g_YhgkqNE98</t>
         </is>
       </c>
-      <c r="G140" s="59" t="inlineStr">
+      <c r="G142" s="59" t="inlineStr">
         <is>
           <t>"La démocratie des droits : de Weber à Kant", entretien avec Catherine Colliot-Thélène" par Politika</t>
         </is>
       </c>
-      <c r="H140" s="65" t="inlineStr">
+      <c r="H142" s="65" t="inlineStr">
         <is>
           <t>https://www.laphilo.fr/pho/thelene-mini.webp</t>
         </is>
       </c>
-      <c r="J140" s="48" t="inlineStr">
+      <c r="J142" s="48" t="inlineStr">
         <is>
           <t>politique</t>
         </is>
       </c>
-      <c r="K140" s="48" t="inlineStr">
+      <c r="K142" s="48" t="inlineStr">
         <is>
           <t>Libéralisme</t>
         </is>
       </c>
-      <c r="L140" s="48" t="inlineStr">
+      <c r="L142" s="48" t="inlineStr">
         <is>
           <t>philosophe française majeure de la philosophie politique contemporaine.</t>
         </is>
       </c>
-      <c r="M140" t="inlineStr">
+      <c r="M142" t="inlineStr">
         <is>
           <t xml:space="preserve">femme</t>
         </is>
       </c>
-      <c r="N140" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-    </row>
-    <row r="141" ht="171.75" customHeight="1" s="49">
-      <c r="A141" s="54" t="n">
+      <c r="N142" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+    </row>
+    <row r="143" ht="171.75" customHeight="1" s="49">
+      <c r="A143" s="54" t="n">
         <v>1952</v>
       </c>
-      <c r="B141" s="54" t="inlineStr">
+      <c r="B143" s="54" t="inlineStr">
         <is>
           <t>2020</t>
         </is>
       </c>
-      <c r="C141" s="54" t="inlineStr">
+      <c r="C143" s="54" t="inlineStr">
         <is>
           <t>1952 – 2020</t>
         </is>
       </c>
-      <c r="D141" s="55" t="inlineStr">
+      <c r="D143" s="55" t="inlineStr">
         <is>
           <t xml:space="preserve">Bernard STIEGLER</t>
         </is>
       </c>
-      <c r="E141" s="56" t="inlineStr">
+      <c r="E143" s="56" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Bernard_Stiegler"  title=" Wikipedia"&gt;Bernard STIEGLER&lt;/a&gt; était un philosophe français, l'une des figures les plus originales et les plus influentes de la philosophie française. Né à Villebon-sur-Yvette, son parcours intellectuel fut marqué par une expérience singulière : il prépara sa thèse en philosophie pendant les cinq années qu'il passa en prison (1978-1983), condamné pour braquages. Docteur en philosophie sous la direction de Jacques Derrida, il fut directeur du département du développement culturel du Centre Pompidou puis directeur de l'Institut de Recherche et d'Innovation (IRI). &lt;/p&gt; &lt;p&gt; Son œuvre maîtresse, la trilogie &lt;em&gt;&lt;a href="https://www.youtube.com/watch?v=nwmOFXzCJUg" title="Bernard Stiegler a propos de la technique par Adrien Payet"&gt;La Technique et le Temps&lt;/a&gt; &lt;/em&gt; (1994-2001), constitue l'une des analyses philosophiques les plus ambitieuses de la technique et de ses effets sur la temporalité humaine. S'appuyant sur Simondon, Derrida et Heidegger, il y défend la thèse que l'être humain est fondamentalement un être technique : c'est par la technique — les « rétentions tertiaires », les objets qui externalisent la mémoire — que l'humain se constitue comme tel. La technique n'est pas un simple outil mais la condition même de la temporalité humaine et de la transmission culturelle. &lt;/p&gt; &lt;p&gt; Dans ses ouvrages ultérieurs — &lt;em&gt;De la misère symbolique&lt;/em&gt; (2004), &lt;em&gt;Prendre soin&lt;/em&gt; (2008), &lt;em&gt;États de choc&lt;/em&gt; (2012) — il  &lt;a href="https://www.youtube.com/watch?v=IOei5Kb1cQI" title="Bernard Stiegler par France 24"&gt;développa une critique &lt;/a&gt;  de l'économie de l'attention et du capitalisme des plateformes numériques, montrant comment ceux-ci détruisent les « savoirs faire » et « savoirs vivre » qui constituent le tissu de l'existence humaine. Sa pensée, nourrie d'une profonde inquiétude sur les effets destructeurs des industries culturelles et numériques, propose une pharmacologie de la technique : la technique est un pharmakon, à la fois poison et remède. &lt;/p&gt;  &lt;audio controls title="Bernard Stiegler : je reflechis au rapport entre technique et le mal  par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/13915-05.11.2017-ITEMA_21460251-5.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;</t>
         </is>
       </c>
-      <c r="F141" s="54" t="inlineStr">
+      <c r="F143" s="54" t="inlineStr">
         <is>
           <t>Q10Ski-xusk</t>
         </is>
       </c>
-      <c r="G141" s="56" t="inlineStr">
+      <c r="G143" s="56" t="inlineStr">
         <is>
           <t>"Mémoire et personnalité - Bernard Stiegler" par Obserbatoire B2V des Mémoires</t>
         </is>
       </c>
-      <c r="H141" s="62" t="inlineStr">
+      <c r="H143" s="62" t="inlineStr">
         <is>
           <t>https://www.laphilo.fr/pho/bstiegler-mini.webp</t>
         </is>
       </c>
-      <c r="J141" s="48" t="inlineStr">
+      <c r="J143" s="48" t="inlineStr">
         <is>
           <t>politique ; epistemologie</t>
         </is>
       </c>
-      <c r="K141" s="48" t="inlineStr">
+      <c r="K143" s="48" t="inlineStr">
         <is>
           <t>Post-structuralisme</t>
         </is>
       </c>
-      <c r="L141" s="48" t="inlineStr">
+      <c r="L143" s="48" t="inlineStr">
         <is>
           <t>philosophe français qui fit une analyse ambitieuse de la technique et de ses effets.</t>
         </is>
       </c>
-      <c r="N141" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-    </row>
-    <row r="142" ht="135.75" customHeight="1" s="49">
-      <c r="A142" s="57" t="n">
+      <c r="N143" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+    </row>
+    <row r="144" ht="135.75" customHeight="1" s="49">
+      <c r="A144" s="57" t="n">
         <v>1959</v>
       </c>
-      <c r="B142" s="57" t="inlineStr">
+      <c r="B144" s="57" t="inlineStr">
         <is>
           <t>2014</t>
         </is>
       </c>
-      <c r="C142" s="57" t="inlineStr">
+      <c r="C144" s="57" t="inlineStr">
         <is>
           <t>1959 – 2014</t>
         </is>
       </c>
-      <c r="D142" s="58" t="inlineStr">
+      <c r="D144" s="58" t="inlineStr">
         <is>
           <t>Bernard MABILLE</t>
         </is>
       </c>
-      <c r="E142" s="65" t="inlineStr">
+      <c r="E144" s="65" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Bernard_Mabille_(philosophe)"  style="color:#6A142A"  title=" Wikipedia"&gt;Bernard MABILLE&lt;/a&gt; était un philosophe français spécialiste de dialectique et de philosophie hégélienne, ainsi que de métaphysique contemporaine. Agrégé de philosophie et professeur à l'Université Paris IV-Sorbonne, il fut l'un des meilleurs connaisseurs français de Hegel et contribua de manière significative au renouvellement des études hégéliennes en France dans les dernières décennies du XXe siècle. &lt;/p&gt; &lt;p&gt; Sa thèse principale, &lt;em&gt;Hegel : l'épreuve de la contingence&lt;/em&gt; (1999), est une lecture originale de la philosophie hégélienne à la lumière de la problématique de la contingence. Contre les lectures qui réduisent Hegel à un penseur du nécessaire et du rationnel, Mabille montre que la contingence est au cœur même du système hégélien et que la dialectique est précisément la méthode qui permet de penser le passage du contingent au nécessaire sans l'éliminer. Cette relecture contribua à ouvrir la philosophie hégélienne à des problématiques contemporaines. &lt;/p&gt; &lt;p&gt; Dans ses travaux sur la métaphysique et la dialectique, Mabille s'intéressa également aux rapports entre la philosophie hégélienne et la phénoménologie française, notamment Merleau-Ponty et Henry. Son enseignement à la Sorbonne forma plusieurs générations d'étudiants à la rigueur de la pensée dialectique. Sa disparition prématurée priva la philosophie française d'un penseur rigoureux dont l'œuvre, bien que de volume limité, témoigne d'une lecture profonde et originale de l'idéalisme allemand et de ses prolongements contemporains. &lt;/p&gt;</t>
         </is>
       </c>
-      <c r="F142" s="57" t="inlineStr">
+      <c r="F144" s="57" t="inlineStr">
         <is>
           <t>2ZxXXD2lk_Q</t>
         </is>
       </c>
-      <c r="G142" s="59" t="inlineStr">
+      <c r="G144" s="59" t="inlineStr">
         <is>
           <t>Bernard MABILLE par La Compagnie des indes TV</t>
         </is>
       </c>
-      <c r="H142" s="65" t="inlineStr">
+      <c r="H144" s="65" t="inlineStr">
         <is>
           <t>https://www.laphilo.fr/pho/bnabille-mini.webp</t>
         </is>
       </c>
-      <c r="J142" s="48" t="inlineStr">
+      <c r="J144" s="48" t="inlineStr">
         <is>
           <t>metaphysique</t>
         </is>
       </c>
-      <c r="K142" s="48" t="inlineStr">
+      <c r="K144" s="48" t="inlineStr">
         <is>
           <t>Idéalisme allemand</t>
         </is>
       </c>
-      <c r="L142" s="48" t="inlineStr">
+      <c r="L144" s="48" t="inlineStr">
         <is>
           <t>philosophe français spécialiste de dialectique et de philosophie hégélienne.</t>
         </is>
       </c>
-      <c r="N142" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-    </row>
-    <row r="143" ht="176.25" customHeight="1" s="49">
-      <c r="A143" s="47" t="n">
+      <c r="N144" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+    </row>
+    <row r="145" ht="176.25" customHeight="1" s="49">
+      <c r="A145" s="47" t="n">
         <v>1964</v>
       </c>
-      <c r="B143" s="47" t="n">
+      <c r="B145" s="47" t="n">
         <v>2017</v>
       </c>
-      <c r="C143" s="47" t="inlineStr">
+      <c r="C145" s="47" t="inlineStr">
         <is>
           <t>1964 – 2017</t>
         </is>
       </c>
-      <c r="D143" s="47" t="inlineStr">
+      <c r="D145" s="47" t="inlineStr">
         <is>
           <t>Anne DUFOURMANTELLE</t>
         </is>
       </c>
-      <c r="E143" s="85" t="inlineStr">
+      <c r="E145" s="85" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Anne_Dufourmantelle"  title=" Wikipedia"&gt;Anne DUFOURMANTELLE&lt;/a&gt; était une philosophe et psychanalyste française dont l’œuvre, marquée par une grande finesse d’analyse, explore la vulnérabilité humaine, le risque, le secret et l’hospitalité. Bien qu’elle ne soit pas une théoricienne du &lt;a href="https://fr.wikipedia.org/wiki/Constructivisme_(%C3%A9pist%C3%A9mologie)"  title="Constructivisme par Wikipedia"&gt;« constructivisme »&lt;/a&gt;  au sens politique ou académique strict, sa pensée entre en résonance avec une réflexion sur la manière dont nous bâtissons notre rapport au monde et à l’autre. &lt;/p&gt; &lt;p&gt; Son concept d'&lt;a href="https://www.umc.org/fr/content/what-is-radical-hospitality"  title="Qu’est ce que l’hospitalité radicale par umc"&gt;« hospitalité radicale », &lt;/a&gt; nourri de ses travaux avec Jacques Derrida, propose d'accueillir l'inconnu sans conditions, voyant dans cette ouverture une forme de résistance à la fermeture du monde. Elle invite à une éthique de la rencontre où la vulnérabilité n'est pas un défaut, mais un espace de croissance mutuelle qui défie les normes sociales établies. &lt;/p&gt; &lt;p&gt; '&lt;a href="https://www.youtube.com/watch?v=QAlsJD3IAs0"  title="L’envers du feu par Librairie mollat"&gt;Dans des ouvrages &lt;/a&gt; comme Éloge du risque, elle explore la tension entre la sécurité et l'aventure de vivre, encourageant une liberté de penser et d'aimer qui dépasse les discours ambiants. Elle percevait la psychanalyse et la philosophie comme des outils pour « traquer » les mutations invisibles de notre époque et redonner du sens à nos vies intérieures. &lt;/p&gt; &lt;p&gt; Sa disparition brutale en 2017, alors qu'elle portait secours à des enfants en mer, a été perçue comme l'incarnation ultime de son engagement philosophique : une éthique en actes où le souci de l'autre devient une responsabilité immédiate. Son héritage intellectuel reste une source d'inspiration pour ceux qui cherchent à penser la douceur, l'enfance et la résistance dans un monde en mutation. &lt;/p&gt; 
 &lt;audio controls title="Anne Dufourmantelle par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/11189-07.11.2011-ITEMA_20320628-2011C15000E0211-ITE_00045291_RSCE-21.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;
 </t>
         </is>
       </c>
-      <c r="F143" s="47" t="inlineStr">
+      <c r="F145" s="47" t="inlineStr">
         <is>
           <t>PCCcMUiurLo</t>
         </is>
       </c>
-      <c r="G143" s="48" t="inlineStr">
+      <c r="G145" s="48" t="inlineStr">
         <is>
           <t>Hommage à Anne DUFOURMANTELLE par PhiloCloud</t>
         </is>
       </c>
-      <c r="H143" s="48" t="inlineStr">
+      <c r="H145" s="48" t="inlineStr">
         <is>
           <t>https://www.laphilo.fr/pho/adufourmantelle-mini.webp</t>
         </is>
       </c>
-      <c r="J143" s="48" t="inlineStr">
+      <c r="J145" s="48" t="inlineStr">
         <is>
           <t>ethique ; esthetique</t>
         </is>
       </c>
-      <c r="K143" s="48" t="inlineStr">
+      <c r="K145" s="48" t="inlineStr">
         <is>
           <t>Phénoménologie</t>
         </is>
       </c>
-      <c r="L143" s="48" t="inlineStr">
+      <c r="L145" s="48" t="inlineStr">
         <is>
           <t>philosophe et psychanalyste française fine analyste, qui explore la vulnérabilité humaine.</t>
         </is>
       </c>
-      <c r="M143" t="inlineStr">
+      <c r="M145" t="inlineStr">
         <is>
           <t xml:space="preserve">femme</t>
         </is>
       </c>
-      <c r="N143" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-    </row>
-    <row r="144" ht="176.25" customHeight="1" s="49">
-      <c r="A144" s="47">
-        <v>1881</v>
-      </c>
-      <c r="B144" s="47" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1955</t>
-        </is>
-      </c>
-      <c r="C144" s="47" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1881 – 1955</t>
-        </is>
-      </c>
-      <c r="D144" s="47" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Pierre TEILHARD DE CHARDIN</t>
-        </is>
-      </c>
-      <c r="E144" s="85" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Pierre_Teilhard_de_Chardin" title=" Wikipedia"&gt;Pierre TEILHARD DE CHARDIN&lt;/a&gt; est un prêtre jésuite, paléontologue et philosophe français, qui a voulu réconcilier la foi chrétienne et la théorie de l’évolution. Né en Auvergne, il entre chez les jésuites et devient un spécialiste reconnu de la &lt;a href="https://fr.wikipedia.org/wiki/Pal%C3%A9ontologie" title=" Wikipedia"&gt;paléontologie&lt;/a&gt;. Brancardier pendant la Première Guerre mondiale, il passe ensuite plus de vingt ans en Chine, où il participe aux recherches sur l’&lt;a href="https://fr.wikipedia.org/wiki/Homme_de_P%C3%A9kin" title=" Wikipedia"&gt;Homme de Pékin&lt;/a&gt;, l’un des plus anciens fossiles humains connus, et prend part en 1931-1932 à la &lt;a href="https://fr.wikipedia.org/wiki/Croisi%C3%A8re_jaune" title=" Wikipedia"&gt;Croisière jaune&lt;/a&gt;, grande expédition à travers l’Asie centrale.&lt;/p&gt; &lt;p&gt;Dans &lt;em&gt;Le Phénomène humain&lt;/em&gt;, écrit dans les années 1930 et publié après sa mort, il décrit l’univers comme un grand mouvement d’évolution, de la matière à la vie, puis de la vie à la pensée. À mesure que la matière se complexifie, la conscience grandit : c’est la « loi de complexité-conscience ». Avec l’homme apparaît une nouvelle couche de la Terre, la &lt;a href="https://fr.wikipedia.org/wiki/Noosph%C3%A8re" title=" Wikipedia"&gt;noosphère&lt;/a&gt;, la sphère de la pensée, qui relie peu à peu tous les esprits.&lt;/p&gt; &lt;p&gt;Cette évolution est selon lui orientée vers un point de convergence final, le &lt;a href="https://fr.wikipedia.org/wiki/Point_Om%C3%A9ga" title=" Wikipedia"&gt;point Oméga&lt;/a&gt;, qu’il identifie au Christ cosmique, où l’humanité s’unira sans perdre la personnalité de chacun. Son autre grand texte, &lt;em&gt;Le Milieu divin&lt;/em&gt;, médite sur la présence de Dieu dans toutes les activités humaines. Ses idées inquiètent Rome, qui lui interdit de publier ses écrits philosophiques et l’éloigne de France. Il meurt à New York en 1955. Publiée après sa mort, son œuvre connaît un succès mondial, et l’on voit parfois dans la noosphère une anticipation d’Internet.&lt;/p&gt;</t>
-        </is>
-      </c>
-      <c r="H144" s="48" t="inlineStr">
-        <is>
-          <t xml:space="preserve">https://www.laphilo.fr/pho/teilhard-mini.webp</t>
-        </is>
-      </c>
-      <c r="J144" s="48" t="inlineStr">
-        <is>
-          <t xml:space="preserve">metaphysique ; spiritualite</t>
-        </is>
-      </c>
-      <c r="K144" s="48" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Spiritualisme ; Panenthéisme</t>
-        </is>
-      </c>
-      <c r="L144" s="48" t="inlineStr">
-        <is>
-          <t xml:space="preserve">jésuite et paléontologue français, penseur d’une évolution cosmique orientée vers la conscience et l’esprit.</t>
-        </is>
-      </c>
-      <c r="N144" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-      <c r="O144">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="145" ht="176.25" customHeight="1" s="49">
-      <c r="A145" s="47">
-        <v>1868</v>
-      </c>
-      <c r="B145" s="47" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1952</t>
-        </is>
-      </c>
-      <c r="C145" s="47" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1868 – 1952</t>
-        </is>
-      </c>
-      <c r="D145" s="47" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Charles MAURRAS</t>
-        </is>
-      </c>
-      <c r="E145" s="85" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Charles_Maurras" title=" Wikipedia"&gt;Charles MAURRAS&lt;/a&gt; est un écrivain, journaliste et théoricien politique français, le maître à penser de l’&lt;a href="https://fr.wikipedia.org/wiki/Action_fran%C3%A7aise" title=" Wikipedia"&gt;Action française&lt;/a&gt;. Né en 1868 à Martigues, en Provence, il devient sourd vers quatorze ans, perd la foi, et monte à Paris, où il se fait connaître comme critique littéraire et poète, défenseur d’un classicisme inspiré de la Grèce contre le romantisme, qu’il juge source de désordre. L’affaire Dreyfus le jette dans la politique : en 1898, il justifie le faux du colonel Henry au nom de l’intérêt de l’armée et de l’État.&lt;/p&gt; &lt;p&gt;Avec son &lt;em&gt;Enquête sur la monarchie&lt;/em&gt; (1900), il convertit l’Action française à la royauté. Sa doctrine, le « nationalisme intégral », place la nation au-dessus de tout : seule une monarchie héréditaire, antiparlementaire et décentralisée pourrait garantir l’ordre et la durée que la République, gouvernement des partis et de l’opinion, détruirait. Agnostique, il défend pourtant l’Église catholique comme une force d’ordre. Il appelle sa méthode l’« empirisme organisateur » : tirer de l’histoire les lois du bon gouvernement. Il dénonce les « quatre États confédérés » qui, selon lui, rongent la France : les juifs, les protestants, les francs-maçons et les « métèques ». Cet antisémitisme d’État est au cœur de sa pensée.&lt;/p&gt; &lt;p&gt;Son quotidien, &lt;em&gt;L’Action française&lt;/em&gt;, exerce une influence considérable sur la droite et sur une partie de la jeunesse intellectuelle, malgré la condamnation du mouvement par le pape Pie XI en 1926. Maurras entre à l’Académie française en 1938. Hostile à l’Allemagne, il soutient pourtant en 1940 le maréchal Pétain, dont l’arrivée au pouvoir est pour lui une « divine surprise ». Condamné en 1945 à la réclusion à perpétuité et à la dégradation nationale pour intelligence avec l’ennemi, il s’écrie : « C’est la revanche de Dreyfus ! » Gracié pour raison de santé, il meurt en 1952. Sa pensée a durablement marqué l’extrême droite française.&lt;/p&gt;</t>
-        </is>
-      </c>
-      <c r="H145" s="48" t="inlineStr">
-        <is>
-          <t xml:space="preserve">https://www.laphilo.fr/pho/maurras-mini.webp</t>
-        </is>
-      </c>
-      <c r="J145" s="48" t="inlineStr">
-        <is>
-          <t xml:space="preserve">politique</t>
-        </is>
-      </c>
-      <c r="K145" s="48" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Maurrassisme ; Conservatisme</t>
-        </is>
-      </c>
-      <c r="L145" s="48" t="inlineStr">
-        <is>
-          <t xml:space="preserve">écrivain et théoricien politique français, chef de l’Action française et du « nationalisme intégral ».</t>
-        </is>
-      </c>
       <c r="N145" t="inlineStr">
         <is>
           <t xml:space="preserve">occident</t>
         </is>
       </c>
-      <c r="O145"/>
     </row>
     <row r="146" ht="176.25" customHeight="1" s="49">
       <c r="A146" s="47">
-        <v>1827</v>
+        <v>1868</v>
       </c>
       <c r="B146" s="47" t="inlineStr">
         <is>
-          <t xml:space="preserve">1907</t>
+          <t xml:space="preserve">1952</t>
         </is>
       </c>
       <c r="C146" s="47" t="inlineStr">
         <is>
-          <t xml:space="preserve">1827 – 1907</t>
+          <t xml:space="preserve">1868 – 1952</t>
         </is>
       </c>
       <c r="D146" s="47" t="inlineStr">
         <is>
-          <t xml:space="preserve">Marcellin BERTHELOT</t>
+          <t xml:space="preserve">Charles MAURRAS</t>
         </is>
       </c>
       <c r="E146" s="85" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Marcellin_Berthelot" title=" Wikipedia"&gt;Marcellin BERTHELOT&lt;/a&gt; est un chimiste, historien des sciences et homme politique français, l’une des figures les plus représentatives du &lt;a href="https://fr.wikipedia.org/wiki/Scientisme" title=" Wikipedia"&gt;scientisme&lt;/a&gt;. Né à Paris en 1827, fils d’un médecin, il devient l’un des fondateurs de la chimie organique de synthèse : il montre qu’on peut fabriquer en laboratoire, à partir des éléments, des corps jusque-là produits seulement par les êtres vivants, comme l’acétylène, le méthane ou l’alcool. Il en tire une leçon philosophique : il n’existe pas de « force vitale » mystérieuse, la vie obéit aux mêmes lois que la matière.&lt;/p&gt; &lt;p&gt;Pour Berthelot, la science expérimentale est la seule voie vers la vérité, et elle doit aussi fonder la morale et la politique. « Le monde est aujourd’hui sans mystère », écrit-il en 1885 : ce que la science ne sait pas encore, elle le saura demain. Ami de &lt;a href="https://fr.wikipedia.org/wiki/Ernest_Renan" title=" Wikipedia"&gt;Ernest Renan&lt;/a&gt;, avec qui il partage la foi dans l’avenir de la science, il expose ses idées dans &lt;em&gt;Science et morale&lt;/em&gt; (1897). En 1895, quand le critique Ferdinand Brunetière proclame la « faillite de la science », qui n’aurait pas tenu ses promesses morales, Berthelot devient le porte-parole de la réplique républicaine et laïque.&lt;/p&gt; &lt;p&gt;Sénateur inamovible, il est ministre de l’Instruction publique (1886-1887) puis des Affaires étrangères (1895-1896), et défend une école laïque fondée sur les sciences. Professeur au Collège de France, secrétaire perpétuel de l’Académie des sciences, il s’oppose aussi à la théorie atomique, qu’il juge trop hypothétique. Il meurt en 1907 le même jour que sa femme, et tous deux sont inhumés au Panthéon.&lt;/p&gt;</t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Charles_Maurras" title=" Wikipedia"&gt;Charles MAURRAS&lt;/a&gt; est un écrivain, journaliste et théoricien politique français, le maître à penser de l’&lt;a href="https://fr.wikipedia.org/wiki/Action_fran%C3%A7aise" title=" Wikipedia"&gt;Action française&lt;/a&gt;. Né en 1868 à Martigues, en Provence, il devient sourd vers quatorze ans, perd la foi, et monte à Paris, où il se fait connaître comme critique littéraire et poète, défenseur d’un classicisme inspiré de la Grèce contre le romantisme, qu’il juge source de désordre. L’affaire Dreyfus le jette dans la politique : en 1898, il justifie le faux du colonel Henry au nom de l’intérêt de l’armée et de l’État.&lt;/p&gt; &lt;p&gt;Avec son &lt;em&gt;Enquête sur la monarchie&lt;/em&gt; (1900), il convertit l’Action française à la royauté. Sa doctrine, le « nationalisme intégral », place la nation au-dessus de tout : seule une monarchie héréditaire, antiparlementaire et décentralisée pourrait garantir l’ordre et la durée que la République, gouvernement des partis et de l’opinion, détruirait. Agnostique, il défend pourtant l’Église catholique comme une force d’ordre. Il appelle sa méthode l’« empirisme organisateur » : tirer de l’histoire les lois du bon gouvernement. Il dénonce les « quatre États confédérés » qui, selon lui, rongent la France : les juifs, les protestants, les francs-maçons et les « métèques ». Cet antisémitisme d’État est au cœur de sa pensée.&lt;/p&gt; &lt;p&gt;Son quotidien, &lt;em&gt;L’Action française&lt;/em&gt;, exerce une influence considérable sur la droite et sur une partie de la jeunesse intellectuelle, malgré la condamnation du mouvement par le pape Pie XI en 1926. Maurras entre à l’Académie française en 1938. Hostile à l’Allemagne, il soutient pourtant en 1940 le maréchal Pétain, dont l’arrivée au pouvoir est pour lui une « divine surprise ». Condamné en 1945 à la réclusion à perpétuité et à la dégradation nationale pour intelligence avec l’ennemi, il s’écrie : « C’est la revanche de Dreyfus ! » Gracié pour raison de santé, il meurt en 1952. Sa pensée a durablement marqué l’extrême droite française.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H146" s="48" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.laphilo.fr/pho/berthelot-mini.webp</t>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/maurras-mini.webp</t>
         </is>
       </c>
       <c r="J146" s="48" t="inlineStr">
         <is>
-          <t xml:space="preserve">epistemologie ; politique</t>
+          <t xml:space="preserve">politique</t>
         </is>
       </c>
       <c r="K146" s="48" t="inlineStr">
         <is>
-          <t xml:space="preserve">Scientisme ; Positivisme</t>
+          <t xml:space="preserve">Maurrassisme ; Conservatisme</t>
         </is>
       </c>
       <c r="L146" s="48" t="inlineStr">
         <is>
-          <t xml:space="preserve">chimiste et homme politique français, figure emblématique du scientisme.</t>
+          <t xml:space="preserve">écrivain et théoricien politique français, chef de l’Action française et du « nationalisme intégral ».</t>
         </is>
       </c>
       <c r="N146" t="inlineStr">
@@ -9680,46 +9700,46 @@
     </row>
     <row r="147" ht="176.25" customHeight="1" s="49">
       <c r="A147" s="47">
-        <v>1861</v>
+        <v>1827</v>
       </c>
       <c r="B147" s="47" t="inlineStr">
         <is>
-          <t xml:space="preserve">1916</t>
+          <t xml:space="preserve">1907</t>
         </is>
       </c>
       <c r="C147" s="47" t="inlineStr">
         <is>
-          <t xml:space="preserve">1861 – 1916</t>
+          <t xml:space="preserve">1827 – 1907</t>
         </is>
       </c>
       <c r="D147" s="47" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pierre DUHEM</t>
+          <t xml:space="preserve">Marcellin BERTHELOT</t>
         </is>
       </c>
       <c r="E147" s="85" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Pierre_Duhem" title=" Wikipedia"&gt;Pierre DUHEM&lt;/a&gt; est un physicien, philosophe et historien des sciences français. Né à Paris en 1861, brillant élève de l’École normale supérieure, il consacre ses travaux de physique à la thermodynamique. Une thèse où il critique les idées du chimiste Marcellin Berthelot est refusée ; Berthelot, très puissant, l’empêche ensuite d’obtenir un poste à Paris, et Duhem, catholique convaincu, fait sa carrière en province, à Lille, à Rennes, puis à Bordeaux.&lt;/p&gt; &lt;p&gt;Dans &lt;em&gt;La Théorie physique, son objet, sa structure&lt;/em&gt; (1906), il soutient qu’une théorie physique n’explique pas la réalité cachée des choses, ce qui relève de la métaphysique : elle est un système de propositions mathématiques qui représente et classe le plus simplement possible les lois expérimentales. Il faut, comme disaient les astronomes grecs, « sauver les phénomènes ». Surtout, une expérience ne peut jamais réfuter une hypothèse isolée : elle met en jeu tout un ensemble de théories et d’instruments, et si la prédiction échoue, on ne sait pas laquelle des hypothèses est fausse. Il n’y a donc pas d’« expérience cruciale ». Cette idée, reprise par Quine, est connue comme la &lt;a href="https://fr.wikipedia.org/wiki/Th%C3%A8se_de_Duhem-Quine" title=" Wikipedia"&gt;thèse de Duhem-Quine&lt;/a&gt;.&lt;/p&gt; &lt;p&gt;Duhem est aussi un grand historien des sciences. Dans les dix volumes du &lt;em&gt;Système du monde&lt;/em&gt;, il redécouvre la physique du Moyen Âge, celle de Jean Buridan et de Nicole Oresme, et montre que la science moderne ne naît pas d’une rupture brutale avec les siècles « obscurs », mais les prolonge. Il meurt en 1916. Son instrumentalisme et son holisme ont profondément marqué la philosophie des sciences du XXe siècle.&lt;/p&gt;</t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Marcellin_Berthelot" title=" Wikipedia"&gt;Marcellin BERTHELOT&lt;/a&gt; est un chimiste, historien des sciences et homme politique français, l’une des figures les plus représentatives du &lt;a href="https://fr.wikipedia.org/wiki/Scientisme" title=" Wikipedia"&gt;scientisme&lt;/a&gt;. Né à Paris en 1827, fils d’un médecin, il devient l’un des fondateurs de la chimie organique de synthèse : il montre qu’on peut fabriquer en laboratoire, à partir des éléments, des corps jusque-là produits seulement par les êtres vivants, comme l’acétylène, le méthane ou l’alcool. Il en tire une leçon philosophique : il n’existe pas de « force vitale » mystérieuse, la vie obéit aux mêmes lois que la matière.&lt;/p&gt; &lt;p&gt;Pour Berthelot, la science expérimentale est la seule voie vers la vérité, et elle doit aussi fonder la morale et la politique. « Le monde est aujourd’hui sans mystère », écrit-il en 1885 : ce que la science ne sait pas encore, elle le saura demain. Ami de &lt;a href="https://fr.wikipedia.org/wiki/Ernest_Renan" title=" Wikipedia"&gt;Ernest Renan&lt;/a&gt;, avec qui il partage la foi dans l’avenir de la science, il expose ses idées dans &lt;em&gt;Science et morale&lt;/em&gt; (1897). En 1895, quand le critique Ferdinand Brunetière proclame la « faillite de la science », qui n’aurait pas tenu ses promesses morales, Berthelot devient le porte-parole de la réplique républicaine et laïque.&lt;/p&gt; &lt;p&gt;Sénateur inamovible, il est ministre de l’Instruction publique (1886-1887) puis des Affaires étrangères (1895-1896), et défend une école laïque fondée sur les sciences. Professeur au Collège de France, secrétaire perpétuel de l’Académie des sciences, il s’oppose aussi à la théorie atomique, qu’il juge trop hypothétique. Il meurt en 1907 le même jour que sa femme, et tous deux sont inhumés au Panthéon.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H147" s="48" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.laphilo.fr/pho/duhem-mini.webp</t>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/berthelot-mini.webp</t>
         </is>
       </c>
       <c r="J147" s="48" t="inlineStr">
         <is>
-          <t xml:space="preserve">epistemologie</t>
+          <t xml:space="preserve">epistemologie ; politique</t>
         </is>
       </c>
       <c r="K147" s="48" t="inlineStr">
         <is>
-          <t xml:space="preserve">Instrumentalisme ; Holisme</t>
+          <t xml:space="preserve">Scientisme ; Positivisme</t>
         </is>
       </c>
       <c r="L147" s="48" t="inlineStr">
         <is>
-          <t xml:space="preserve">physicien et philosophe des sciences français, pour qui une hypothèse n’est jamais testée seule.</t>
+          <t xml:space="preserve">chimiste et homme politique français, figure emblématique du scientisme.</t>
         </is>
       </c>
       <c r="N147" t="inlineStr">
@@ -9731,46 +9751,46 @@
     </row>
     <row r="148" ht="176.25" customHeight="1" s="49">
       <c r="A148" s="47">
-        <v>1854</v>
+        <v>1861</v>
       </c>
       <c r="B148" s="47" t="inlineStr">
         <is>
-          <t xml:space="preserve">1912</t>
+          <t xml:space="preserve">1916</t>
         </is>
       </c>
       <c r="C148" s="47" t="inlineStr">
         <is>
-          <t xml:space="preserve">1854 – 1912</t>
+          <t xml:space="preserve">1861 – 1916</t>
         </is>
       </c>
       <c r="D148" s="47" t="inlineStr">
         <is>
-          <t xml:space="preserve">Henri POINCARÉ</t>
+          <t xml:space="preserve">Pierre DUHEM</t>
         </is>
       </c>
       <c r="E148" s="85" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Henri_Poincar%C3%A9" title=" Wikipedia"&gt;Henri POINCARÉ&lt;/a&gt; est un mathématicien, physicien et philosophe des sciences français, l’un des derniers savants universels. Né à Nancy en 1854, polytechnicien et ingénieur des mines, il enseigne à la Sorbonne à partir de 1881. Il renouvelle presque toutes les branches des mathématiques : il fonde la topologie, découvre en étudiant le mouvement de trois corps célestes les comportements imprévisibles qu’on appellera « chaos », et pose en 1905, en même temps qu’Einstein, les bases mathématiques de la relativité restreinte.&lt;/p&gt; &lt;p&gt;Dans &lt;em&gt;La Science et l’Hypothèse&lt;/em&gt; (1902), il défend le &lt;a href="https://fr.wikipedia.org/wiki/Conventionnalisme" title=" Wikipedia"&gt;conventionnalisme&lt;/a&gt; : certains principes de la science ne sont ni des vérités a priori ni des faits d’expérience, mais des conventions. Ainsi, aucune expérience ne peut dire si l’espace est euclidien ou non : nous choisissons la géométrie d’Euclide parce qu’elle est la plus commode. Ces conventions ne sont pas arbitraires, car l’expérience nous guide, mais elles ne peuvent être ni vraies ni fausses. La science ne connaît pas les choses elles-mêmes, mais les rapports entre les choses.&lt;/p&gt; &lt;p&gt;Dans &lt;em&gt;La Valeur de la science&lt;/em&gt; (1905) et &lt;em&gt;Science et méthode&lt;/em&gt; (1908), il s’oppose aussi aux logiciens, comme Russell, qui veulent réduire les mathématiques à la logique : pour lui, le raisonnement mathématique repose sur une intuition. Il décrit le rôle de l’inconscient dans la découverte, à partir de ses propres illuminations soudaines, comme celle qui lui vint en montant dans un omnibus. Élu à l’Académie française en 1908, il meurt à Paris en 1912.&lt;/p&gt;</t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Pierre_Duhem" title=" Wikipedia"&gt;Pierre DUHEM&lt;/a&gt; est un physicien, philosophe et historien des sciences français. Né à Paris en 1861, brillant élève de l’École normale supérieure, il consacre ses travaux de physique à la thermodynamique. Une thèse où il critique les idées du chimiste Marcellin Berthelot est refusée ; Berthelot, très puissant, l’empêche ensuite d’obtenir un poste à Paris, et Duhem, catholique convaincu, fait sa carrière en province, à Lille, à Rennes, puis à Bordeaux.&lt;/p&gt; &lt;p&gt;Dans &lt;em&gt;La Théorie physique, son objet, sa structure&lt;/em&gt; (1906), il soutient qu’une théorie physique n’explique pas la réalité cachée des choses, ce qui relève de la métaphysique : elle est un système de propositions mathématiques qui représente et classe le plus simplement possible les lois expérimentales. Il faut, comme disaient les astronomes grecs, « sauver les phénomènes ». Surtout, une expérience ne peut jamais réfuter une hypothèse isolée : elle met en jeu tout un ensemble de théories et d’instruments, et si la prédiction échoue, on ne sait pas laquelle des hypothèses est fausse. Il n’y a donc pas d’« expérience cruciale ». Cette idée, reprise par Quine, est connue comme la &lt;a href="https://fr.wikipedia.org/wiki/Th%C3%A8se_de_Duhem-Quine" title=" Wikipedia"&gt;thèse de Duhem-Quine&lt;/a&gt;.&lt;/p&gt; &lt;p&gt;Duhem est aussi un grand historien des sciences. Dans les dix volumes du &lt;em&gt;Système du monde&lt;/em&gt;, il redécouvre la physique du Moyen Âge, celle de Jean Buridan et de Nicole Oresme, et montre que la science moderne ne naît pas d’une rupture brutale avec les siècles « obscurs », mais les prolonge. Il meurt en 1916. Son instrumentalisme et son holisme ont profondément marqué la philosophie des sciences du XXe siècle.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H148" s="48" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.laphilo.fr/pho/poincare-mini.webp</t>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/duhem-mini.webp</t>
         </is>
       </c>
       <c r="J148" s="48" t="inlineStr">
         <is>
-          <t xml:space="preserve">epistemologie ; logique</t>
+          <t xml:space="preserve">epistemologie</t>
         </is>
       </c>
       <c r="K148" s="48" t="inlineStr">
         <is>
-          <t xml:space="preserve">Conventionnalisme</t>
+          <t xml:space="preserve">Instrumentalisme ; Holisme</t>
         </is>
       </c>
       <c r="L148" s="48" t="inlineStr">
         <is>
-          <t xml:space="preserve">mathématicien et physicien français, philosophe des sciences et fondateur du conventionnalisme.</t>
+          <t xml:space="preserve">physicien et philosophe des sciences français, pour qui une hypothèse n’est jamais testée seule.</t>
         </is>
       </c>
       <c r="N148" t="inlineStr">
@@ -9778,52 +9798,50 @@
           <t xml:space="preserve">occident</t>
         </is>
       </c>
-      <c r="O148">
-        <v>2</v>
-      </c>
+      <c r="O148"/>
     </row>
     <row r="149" ht="176.25" customHeight="1" s="49">
       <c r="A149" s="47">
-        <v>1866</v>
+        <v>1854</v>
       </c>
       <c r="B149" s="47" t="inlineStr">
         <is>
-          <t xml:space="preserve">1947</t>
+          <t xml:space="preserve">1912</t>
         </is>
       </c>
       <c r="C149" s="47" t="inlineStr">
         <is>
-          <t xml:space="preserve">1866 – 1947</t>
+          <t xml:space="preserve">1854 – 1912</t>
         </is>
       </c>
       <c r="D149" s="47" t="inlineStr">
         <is>
-          <t xml:space="preserve">Léon ROBIN</t>
+          <t xml:space="preserve">Henri POINCARÉ</t>
         </is>
       </c>
       <c r="E149" s="85" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/L%C3%A9on_Robin" title=" Wikipedia"&gt;Léon ROBIN&lt;/a&gt; est un philosophe et historien français de la philosophie, l’un des grands spécialistes de la pensée grecque. Né à Nantes en 1866, fils de marchand, il est reçu à l’agrégation de philosophie en 1891 et enseigne longtemps dans les lycées, à Compiègne, Vendôme et Angers. Élève et disciple d’Octave Hamelin, il publie après la mort de celui-ci son cours sur &lt;em&gt;Le Système d’Aristote&lt;/em&gt;. Il enseigne ensuite à Caen, puis à la Sorbonne de 1913 à 1937, où il occupe à partir de 1924 la chaire d’histoire de la philosophie antique.&lt;/p&gt; &lt;p&gt;Sa thèse, &lt;em&gt;La Théorie platonicienne des Idées et des nombres d’après Aristote&lt;/em&gt; (1908), s’appuie sur les témoignages d’Aristote pour reconstituer l’enseignement oral de &lt;a href="https://fr.wikipedia.org/wiki/Platon" title=" Wikipedia"&gt;Platon&lt;/a&gt; à l’Académie, où les Idées sont rattachées à des principes mathématiques, l’Un et la Dyade. Dans &lt;em&gt;La Pensée grecque et les origines de l’esprit scientifique&lt;/em&gt; (1923), il retrace la naissance de la raison grecque, des premiers physiciens d’Ionie jusqu’aux écoles hellénistiques. Il consacre aussi des livres à la morale antique, à Platon et au scepticisme de Pyrrhon, toujours appuyés sur une lecture rigoureuse des textes grecs.&lt;/p&gt; &lt;p&gt;Son œuvre la plus durable est la traduction des œuvres complètes de Platon pour la Bibliothèque de la Pléiade, qu’il dirige et dont il traduit lui-même la plus grande partie : précise et élégante, elle a fait lire Platon à des générations de lecteurs français. Il dirige aussi l’Institut international de philosophie. Il meurt à Paris en 1947. Pierre-Maxime Schuhl lui a succédé à la Sorbonne.&lt;/p&gt;</t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Henri_Poincar%C3%A9" title=" Wikipedia"&gt;Henri POINCARÉ&lt;/a&gt; est un mathématicien, physicien et philosophe des sciences français, l’un des derniers savants universels. Né à Nancy en 1854, polytechnicien et ingénieur des mines, il enseigne à la Sorbonne à partir de 1881. Il renouvelle presque toutes les branches des mathématiques : il fonde la topologie, découvre en étudiant le mouvement de trois corps célestes les comportements imprévisibles qu’on appellera « chaos », et pose en 1905, en même temps qu’Einstein, les bases mathématiques de la relativité restreinte.&lt;/p&gt; &lt;p&gt;Dans &lt;em&gt;La Science et l’Hypothèse&lt;/em&gt; (1902), il défend le &lt;a href="https://fr.wikipedia.org/wiki/Conventionnalisme" title=" Wikipedia"&gt;conventionnalisme&lt;/a&gt; : certains principes de la science ne sont ni des vérités a priori ni des faits d’expérience, mais des conventions. Ainsi, aucune expérience ne peut dire si l’espace est euclidien ou non : nous choisissons la géométrie d’Euclide parce qu’elle est la plus commode. Ces conventions ne sont pas arbitraires, car l’expérience nous guide, mais elles ne peuvent être ni vraies ni fausses. La science ne connaît pas les choses elles-mêmes, mais les rapports entre les choses.&lt;/p&gt; &lt;p&gt;Dans &lt;em&gt;La Valeur de la science&lt;/em&gt; (1905) et &lt;em&gt;Science et méthode&lt;/em&gt; (1908), il s’oppose aussi aux logiciens, comme Russell, qui veulent réduire les mathématiques à la logique : pour lui, le raisonnement mathématique repose sur une intuition. Il décrit le rôle de l’inconscient dans la découverte, à partir de ses propres illuminations soudaines, comme celle qui lui vint en montant dans un omnibus. Élu à l’Académie française en 1908, il meurt à Paris en 1912.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H149" s="48" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.laphilo.fr/pho/leonrobin-mini.webp</t>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/poincare-mini.webp</t>
         </is>
       </c>
       <c r="J149" s="48" t="inlineStr">
         <is>
-          <t xml:space="preserve">metaphysique ; epistemologie</t>
+          <t xml:space="preserve">epistemologie ; logique</t>
         </is>
       </c>
       <c r="K149" s="48" t="inlineStr">
         <is>
-          <t xml:space="preserve">Platonisme</t>
+          <t xml:space="preserve">Conventionnalisme</t>
         </is>
       </c>
       <c r="L149" s="48" t="inlineStr">
         <is>
-          <t xml:space="preserve">historien français de la philosophie grecque, grand interprète et traducteur de Platon.</t>
+          <t xml:space="preserve">mathématicien et physicien français, philosophe des sciences et fondateur du conventionnalisme.</t>
         </is>
       </c>
       <c r="N149" t="inlineStr">
@@ -9831,50 +9849,52 @@
           <t xml:space="preserve">occident</t>
         </is>
       </c>
-      <c r="O149"/>
+      <c r="O149">
+        <v>2</v>
+      </c>
     </row>
     <row r="150" ht="176.25" customHeight="1" s="49">
       <c r="A150" s="47">
-        <v>1898</v>
+        <v>1866</v>
       </c>
       <c r="B150" s="47" t="inlineStr">
         <is>
-          <t xml:space="preserve">1994</t>
+          <t xml:space="preserve">1947</t>
         </is>
       </c>
       <c r="C150" s="47" t="inlineStr">
         <is>
-          <t xml:space="preserve">1898 – 1994</t>
+          <t xml:space="preserve">1866 – 1947</t>
         </is>
       </c>
       <c r="D150" s="47" t="inlineStr">
         <is>
-          <t xml:space="preserve">Henri GOUHIER</t>
+          <t xml:space="preserve">Léon ROBIN</t>
         </is>
       </c>
       <c r="E150" s="85" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Henri_Gouhier" title=" Wikipedia"&gt;Henri GOUHIER&lt;/a&gt; est un philosophe, historien de la philosophie et critique de théâtre français. Né à Auxerre en 1898, fils d’un clerc de notaire et d’une modiste, il entre à l’École normale supérieure en 1919 et est reçu premier à l’agrégation de philosophie en 1921. Élève d’&lt;a href="https://fr.wikipedia.org/wiki/%C3%89tienne_Gilson" title=" Wikipedia"&gt;Étienne Gilson&lt;/a&gt;, qui lui demande de faire pour la pensée française moderne ce qu’il fait lui-même pour le Moyen Âge, il enseigne à Lille, à Bordeaux, puis à la Sorbonne de 1941 à 1968, dans la chaire d’histoire de la pensée religieuse en France.&lt;/p&gt; &lt;p&gt;Il consacre sa vie à la philosophie française de Descartes à Bergson, qu’il lit en historien attentif aux convictions religieuses des auteurs. Il étudie la pensée religieuse de Descartes, Malebranche, Pascal, et surtout, dans trois volumes, la jeunesse d’Auguste Comte et la naissance du positivisme. Il montre comment le fondateur de la religion de l’Humanité a remplacé Dieu par l’humanité. Ces travaux inspirent le théologien Henri de Lubac pour &lt;em&gt;Le Drame de l’humanisme athée&lt;/em&gt; (1944). Il écrit aussi sur les conversions de Maine de Biran, sur Rousseau et sur Bergson, et défend l’idée d’une philosophie chrétienne.&lt;/p&gt; &lt;p&gt;Passionné de théâtre, il est pendant des décennies critique dramatique et publie &lt;em&gt;L’Essence du théâtre&lt;/em&gt; (1943), où il voit dans la représentation une présence réelle, une action vivante et non un simple texte. Membre de l’Académie des sciences morales et politiques, il est élu en 1979 à l’Académie française, au fauteuil de son maître Gilson. Il meurt à Paris en 1994.&lt;/p&gt;</t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/L%C3%A9on_Robin" title=" Wikipedia"&gt;Léon ROBIN&lt;/a&gt; est un philosophe et historien français de la philosophie, l’un des grands spécialistes de la pensée grecque. Né à Nantes en 1866, fils de marchand, il est reçu à l’agrégation de philosophie en 1891 et enseigne longtemps dans les lycées, à Compiègne, Vendôme et Angers. Élève et disciple d’Octave Hamelin, il publie après la mort de celui-ci son cours sur &lt;em&gt;Le Système d’Aristote&lt;/em&gt;. Il enseigne ensuite à Caen, puis à la Sorbonne de 1913 à 1937, où il occupe à partir de 1924 la chaire d’histoire de la philosophie antique.&lt;/p&gt; &lt;p&gt;Sa thèse, &lt;em&gt;La Théorie platonicienne des Idées et des nombres d’après Aristote&lt;/em&gt; (1908), s’appuie sur les témoignages d’Aristote pour reconstituer l’enseignement oral de &lt;a href="https://fr.wikipedia.org/wiki/Platon" title=" Wikipedia"&gt;Platon&lt;/a&gt; à l’Académie, où les Idées sont rattachées à des principes mathématiques, l’Un et la Dyade. Dans &lt;em&gt;La Pensée grecque et les origines de l’esprit scientifique&lt;/em&gt; (1923), il retrace la naissance de la raison grecque, des premiers physiciens d’Ionie jusqu’aux écoles hellénistiques. Il consacre aussi des livres à la morale antique, à Platon et au scepticisme de Pyrrhon, toujours appuyés sur une lecture rigoureuse des textes grecs.&lt;/p&gt; &lt;p&gt;Son œuvre la plus durable est la traduction des œuvres complètes de Platon pour la Bibliothèque de la Pléiade, qu’il dirige et dont il traduit lui-même la plus grande partie : précise et élégante, elle a fait lire Platon à des générations de lecteurs français. Il dirige aussi l’Institut international de philosophie. Il meurt à Paris en 1947. Pierre-Maxime Schuhl lui a succédé à la Sorbonne.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H150" s="48" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.laphilo.fr/pho/gouhier-mini.webp</t>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/leonrobin-mini.webp</t>
         </is>
       </c>
       <c r="J150" s="48" t="inlineStr">
         <is>
-          <t xml:space="preserve">metaphysique ; spiritualite ; esthetique</t>
+          <t xml:space="preserve">metaphysique ; epistemologie</t>
         </is>
       </c>
       <c r="K150" s="48" t="inlineStr">
         <is>
-          <t xml:space="preserve">Spiritualisme ; Cartésianisme</t>
+          <t xml:space="preserve">Platonisme</t>
         </is>
       </c>
       <c r="L150" s="48" t="inlineStr">
         <is>
-          <t xml:space="preserve">historien français de la philosophie, de Descartes à Bergson, et critique dramatique.</t>
+          <t xml:space="preserve">historien français de la philosophie grecque, grand interprète et traducteur de Platon.</t>
         </is>
       </c>
       <c r="N150" t="inlineStr">
@@ -9886,46 +9906,46 @@
     </row>
     <row r="151" ht="176.25" customHeight="1" s="49">
       <c r="A151" s="47">
-        <v>1918</v>
+        <v>1898</v>
       </c>
       <c r="B151" s="47" t="inlineStr">
         <is>
-          <t xml:space="preserve">1990</t>
+          <t xml:space="preserve">1994</t>
         </is>
       </c>
       <c r="C151" s="47" t="inlineStr">
         <is>
-          <t xml:space="preserve">1918 – 1990</t>
+          <t xml:space="preserve">1898 – 1994</t>
         </is>
       </c>
       <c r="D151" s="47" t="inlineStr">
         <is>
-          <t xml:space="preserve">Henri BIRAULT</t>
+          <t xml:space="preserve">Henri GOUHIER</t>
         </is>
       </c>
       <c r="E151" s="85" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Henri_Birault" title=" Wikipedia"&gt;Henri BIRAULT&lt;/a&gt; est un philosophe français. Né à Paris en 1918, il entre à l’École normale supérieure en 1939, dans la même promotion que Louis Althusser et Jules Vuillemin, et est reçu deuxième à l’agrégation de philosophie en 1945. Élève de Louis Lavelle et de Jean Nabert, il découvre ensuite l’œuvre de &lt;a href="https://fr.wikipedia.org/wiki/Martin_Heidegger" title=" Wikipedia"&gt;Martin Heidegger&lt;/a&gt;, dont il devient, avec Jean Beaufret, l’un des grands commentateurs français. Il enseigne en khâgne au lycée Henri-IV, puis à la Sorbonne.&lt;/p&gt; &lt;p&gt;Professeur admiré, il marque plusieurs générations d’étudiants par ses lectures lentes et minutieuses des textes, qu’il lit dans leur langue d’origine, en grec, en latin, en allemand. Sa réflexion, nourrie de Pascal, de Kant, de Nietzsche et de Heidegger, porte sur la question de l’être et sur la finitude humaine. Avec Heidegger, il cherche à comprendre ce que veut dire penser, au-delà de la métaphysique qui a réduit l’être à un objet disponible pour la science et la technique. Il en tire &lt;em&gt;Heidegger et l’expérience de la pensée&lt;/em&gt; (1978), qui reste l’une des grandes introductions françaises à cette œuvre difficile.&lt;/p&gt; &lt;p&gt;Sa contribution la plus célèbre, « De la béatitude chez Nietzsche », présentée en 1964 au colloque de Royaumont, montre que Nietzsche n’est pas seulement le penseur de la volonté de puissance et de la mort de Dieu, mais aussi celui d’une joie, d’une approbation sans réserve de la vie, de l’« amour du destin ». Respecté par Deleuze et ses contemporains, il publie peu et réécrit sans cesse. Il meurt en 1990. &lt;em&gt;De l’Être, du divin et des dieux&lt;/em&gt; paraît en 2005.&lt;/p&gt;</t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Henri_Gouhier" title=" Wikipedia"&gt;Henri GOUHIER&lt;/a&gt; est un philosophe, historien de la philosophie et critique de théâtre français. Né à Auxerre en 1898, fils d’un clerc de notaire et d’une modiste, il entre à l’École normale supérieure en 1919 et est reçu premier à l’agrégation de philosophie en 1921. Élève d’&lt;a href="https://fr.wikipedia.org/wiki/%C3%89tienne_Gilson" title=" Wikipedia"&gt;Étienne Gilson&lt;/a&gt;, qui lui demande de faire pour la pensée française moderne ce qu’il fait lui-même pour le Moyen Âge, il enseigne à Lille, à Bordeaux, puis à la Sorbonne de 1941 à 1968, dans la chaire d’histoire de la pensée religieuse en France.&lt;/p&gt; &lt;p&gt;Il consacre sa vie à la philosophie française de Descartes à Bergson, qu’il lit en historien attentif aux convictions religieuses des auteurs. Il étudie la pensée religieuse de Descartes, Malebranche, Pascal, et surtout, dans trois volumes, la jeunesse d’Auguste Comte et la naissance du positivisme. Il montre comment le fondateur de la religion de l’Humanité a remplacé Dieu par l’humanité. Ces travaux inspirent le théologien Henri de Lubac pour &lt;em&gt;Le Drame de l’humanisme athée&lt;/em&gt; (1944). Il écrit aussi sur les conversions de Maine de Biran, sur Rousseau et sur Bergson, et défend l’idée d’une philosophie chrétienne.&lt;/p&gt; &lt;p&gt;Passionné de théâtre, il est pendant des décennies critique dramatique et publie &lt;em&gt;L’Essence du théâtre&lt;/em&gt; (1943), où il voit dans la représentation une présence réelle, une action vivante et non un simple texte. Membre de l’Académie des sciences morales et politiques, il est élu en 1979 à l’Académie française, au fauteuil de son maître Gilson. Il meurt à Paris en 1994.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H151" s="48" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.laphilo.fr/pho/birault-mini.webp</t>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/gouhier-mini.webp</t>
         </is>
       </c>
       <c r="J151" s="48" t="inlineStr">
         <is>
-          <t xml:space="preserve">metaphysique ; spiritualite</t>
+          <t xml:space="preserve">metaphysique ; spiritualite ; esthetique</t>
         </is>
       </c>
       <c r="K151" s="48" t="inlineStr">
         <is>
-          <t xml:space="preserve">Phénoménologie</t>
+          <t xml:space="preserve">Spiritualisme ; Cartésianisme</t>
         </is>
       </c>
       <c r="L151" s="48" t="inlineStr">
         <is>
-          <t xml:space="preserve">philosophe français, grand lecteur de Heidegger, de Nietzsche et de Pascal.</t>
+          <t xml:space="preserve">historien français de la philosophie, de Descartes à Bergson, et critique dramatique.</t>
         </is>
       </c>
       <c r="N151" t="inlineStr">
@@ -9937,51 +9957,46 @@
     </row>
     <row r="152" ht="176.25" customHeight="1" s="49">
       <c r="A152" s="47">
-        <v>1923</v>
+        <v>1918</v>
       </c>
       <c r="B152" s="47" t="inlineStr">
         <is>
-          <t xml:space="preserve">2007</t>
+          <t xml:space="preserve">1990</t>
         </is>
       </c>
       <c r="C152" s="47" t="inlineStr">
         <is>
-          <t xml:space="preserve">1923 – 2007</t>
+          <t xml:space="preserve">1918 – 1990</t>
         </is>
       </c>
       <c r="D152" s="47" t="inlineStr">
         <is>
-          <t xml:space="preserve">André GORZ</t>
+          <t xml:space="preserve">Henri BIRAULT</t>
         </is>
       </c>
       <c r="E152" s="85" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Andr%C3%A9_Gorz" title=" Wikipedia"&gt;André GORZ&lt;/a&gt; est un philosophe et journaliste français d’origine autrichienne, l’un des fondateurs de l’écologie politique. Né Gerhart Hirsch à Vienne en 1923, d’un père juif et d’une mère catholique, il est envoyé en Suisse en 1939 pour échapper à la guerre et y devient ingénieur chimiste. En 1946, il rencontre &lt;a href="https://fr.wikipedia.org/wiki/Jean-Paul_Sartre" title=" Wikipedia"&gt;Jean-Paul Sartre&lt;/a&gt;, qui le marque profondément. Installé à Paris en 1949, il écrit sous le nom de Michel Bosquet pour &lt;em&gt;L’Express&lt;/em&gt;, puis participe en 1964 à la fondation du &lt;em&gt;Nouvel Observateur&lt;/em&gt;.&lt;/p&gt; &lt;p&gt;Dans &lt;em&gt;Le Traître&lt;/em&gt; (1958), préfacé par Sartre, il analyse sa propre vie en existentialiste. Penseur du marxisme critique, il s’intéresse ensuite au travail : dans &lt;em&gt;Adieux au prolétariat&lt;/em&gt; (1980), il affirme que la classe ouvrière n’est plus le sujet de l’émancipation, et que la libération passe par la réduction du temps de travail. L’automatisation permettrait de travailler beaucoup moins, et de développer les activités libres, choisies pour elles-mêmes, plutôt que de produire et consommer toujours plus.&lt;/p&gt; &lt;p&gt;Dès &lt;em&gt;Écologie et politique&lt;/em&gt; (1975), il relie la crise écologique au capitalisme : la croissance infinie détruit la nature et les liens humains. L’écologie doit être une politique de l’autonomie, qui permette de « produire moins, vivre mieux ». Il défendra plus tard un revenu d’existence versé à tous, indépendamment de l’emploi. Dans &lt;em&gt;Lettre à D.&lt;/em&gt; (2006), il écrit un émouvant livre d’amour à sa femme Dorine, gravement malade. Ils se donnent la mort ensemble en 2007, dans leur maison de Vosnon, dans l’Aube.&lt;/p&gt;</t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Henri_Birault" title=" Wikipedia"&gt;Henri BIRAULT&lt;/a&gt; est un philosophe français. Né à Paris en 1918, il entre à l’École normale supérieure en 1939, dans la même promotion que Louis Althusser et Jules Vuillemin, et est reçu deuxième à l’agrégation de philosophie en 1945. Élève de Louis Lavelle et de Jean Nabert, il découvre ensuite l’œuvre de &lt;a href="https://fr.wikipedia.org/wiki/Martin_Heidegger" title=" Wikipedia"&gt;Martin Heidegger&lt;/a&gt;, dont il devient, avec Jean Beaufret, l’un des grands commentateurs français. Il enseigne en khâgne au lycée Henri-IV, puis à la Sorbonne.&lt;/p&gt; &lt;p&gt;Professeur admiré, il marque plusieurs générations d’étudiants par ses lectures lentes et minutieuses des textes, qu’il lit dans leur langue d’origine, en grec, en latin, en allemand. Sa réflexion, nourrie de Pascal, de Kant, de Nietzsche et de Heidegger, porte sur la question de l’être et sur la finitude humaine. Avec Heidegger, il cherche à comprendre ce que veut dire penser, au-delà de la métaphysique qui a réduit l’être à un objet disponible pour la science et la technique. Il en tire &lt;em&gt;Heidegger et l’expérience de la pensée&lt;/em&gt; (1978), qui reste l’une des grandes introductions françaises à cette œuvre difficile.&lt;/p&gt; &lt;p&gt;Sa contribution la plus célèbre, « De la béatitude chez Nietzsche », présentée en 1964 au colloque de Royaumont, montre que Nietzsche n’est pas seulement le penseur de la volonté de puissance et de la mort de Dieu, mais aussi celui d’une joie, d’une approbation sans réserve de la vie, de l’« amour du destin ». Respecté par Deleuze et ses contemporains, il publie peu et réécrit sans cesse. Il meurt en 1990. &lt;em&gt;De l’Être, du divin et des dieux&lt;/em&gt; paraît en 2005.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H152" s="48" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.laphilo.fr/pho/gorz-mini.webp</t>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/birault-mini.webp</t>
         </is>
       </c>
       <c r="J152" s="48" t="inlineStr">
         <is>
-          <t xml:space="preserve">politique ; ethique</t>
+          <t xml:space="preserve">metaphysique ; spiritualite</t>
         </is>
       </c>
       <c r="K152" s="48" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ecologisme ; Marxisme</t>
+          <t xml:space="preserve">Phénoménologie</t>
         </is>
       </c>
       <c r="L152" s="48" t="inlineStr">
         <is>
-          <t xml:space="preserve">philosophe et journaliste français, l’un des fondateurs de l’écologie politique.</t>
-        </is>
-      </c>
-      <c r="M152" t="inlineStr">
-        <is>
-          <t xml:space="preserve">juive</t>
+          <t xml:space="preserve">philosophe français, grand lecteur de Heidegger, de Nietzsche et de Pascal.</t>
         </is>
       </c>
       <c r="N152" t="inlineStr">
@@ -9989,52 +10004,55 @@
           <t xml:space="preserve">occident</t>
         </is>
       </c>
-      <c r="O152">
-        <v>2</v>
-      </c>
+      <c r="O152"/>
     </row>
     <row r="153" ht="176.25" customHeight="1" s="49">
       <c r="A153" s="47">
-        <v>1936</v>
+        <v>1923</v>
       </c>
       <c r="B153" s="47" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025</t>
+          <t xml:space="preserve">2007</t>
         </is>
       </c>
       <c r="C153" s="47" t="inlineStr">
         <is>
-          <t xml:space="preserve">1936 – 2025</t>
+          <t xml:space="preserve">1923 – 2007</t>
         </is>
       </c>
       <c r="D153" s="47" t="inlineStr">
         <is>
-          <t xml:space="preserve">Alain ROGER</t>
+          <t xml:space="preserve">André GORZ</t>
         </is>
       </c>
       <c r="E153" s="85" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Alain_Roger" title=" Wikipedia"&gt;Alain ROGER&lt;/a&gt; est un philosophe et écrivain français. Né à Mirecourt, dans les Vosges, en 1936, ancien élève de l’École normale supérieure, agrégé de philosophie et élève de &lt;a href="https://fr.wikipedia.org/wiki/Gilles_Deleuze" title=" Wikipedia"&gt;Gilles Deleuze&lt;/a&gt;, il enseigne l’esthétique à l’université de Clermont-Ferrand. Romancier, il publie notamment &lt;em&gt;La Travestie&lt;/em&gt; (1987), adaptée au cinéma par Yves Boisset. Mais il est surtout connu comme le grand théoricien français du &lt;a href="https://fr.wikipedia.org/wiki/Paysage" title=" Wikipedia"&gt;paysage&lt;/a&gt;, auquel il consacre l’essentiel de son œuvre de philosophe.&lt;/p&gt; &lt;p&gt;Dans &lt;em&gt;Nus et paysages&lt;/em&gt; (1978) puis dans le &lt;em&gt;Court traité du paysage&lt;/em&gt; (1997), il soutient que la beauté de la nature n’est pas naturelle : nous voyons le monde à travers les œuvres d’art. Il reprend à Montaigne le mot « artialisation » pour désigner cette transformation de la nature par l’art. Elle peut être directe, « in situ », quand on façonne un jardin ou un corps, ou indirecte, « in visu », quand la peinture, la poésie ou la photographie éduquent notre regard. Le paysage naît ainsi au XVe siècle dans la peinture flamande, par la « fenêtre » ouverte au fond des tableaux.&lt;/p&gt; &lt;p&gt;Il montre que des lieux longtemps jugés affreux, comme la montagne ou le bord de mer, ne sont devenus beaux qu’au XVIIIe siècle, grâce aux écrivains et aux peintres. Ses travaux inspirent paysagistes et aménageurs, et il enseigne à l’école d’architecture de Paris-La Villette. Il est aussi l’auteur d’un &lt;em&gt;Bréviaire de la bêtise&lt;/em&gt; (2008), recueil d’aphorismes sur la sottise et ses formes les plus savantes. Il meurt à Belley, dans l’Ain, le 7 octobre 2025.&lt;/p&gt;</t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Andr%C3%A9_Gorz" title=" Wikipedia"&gt;André GORZ&lt;/a&gt; est un philosophe et journaliste français d’origine autrichienne, l’un des fondateurs de l’écologie politique. Né Gerhart Hirsch à Vienne en 1923, d’un père juif et d’une mère catholique, il est envoyé en Suisse en 1939 pour échapper à la guerre et y devient ingénieur chimiste. En 1946, il rencontre &lt;a href="https://fr.wikipedia.org/wiki/Jean-Paul_Sartre" title=" Wikipedia"&gt;Jean-Paul Sartre&lt;/a&gt;, qui le marque profondément. Installé à Paris en 1949, il écrit sous le nom de Michel Bosquet pour &lt;em&gt;L’Express&lt;/em&gt;, puis participe en 1964 à la fondation du &lt;em&gt;Nouvel Observateur&lt;/em&gt;.&lt;/p&gt; &lt;p&gt;Dans &lt;em&gt;Le Traître&lt;/em&gt; (1958), préfacé par Sartre, il analyse sa propre vie en existentialiste. Penseur du marxisme critique, il s’intéresse ensuite au travail : dans &lt;em&gt;Adieux au prolétariat&lt;/em&gt; (1980), il affirme que la classe ouvrière n’est plus le sujet de l’émancipation, et que la libération passe par la réduction du temps de travail. L’automatisation permettrait de travailler beaucoup moins, et de développer les activités libres, choisies pour elles-mêmes, plutôt que de produire et consommer toujours plus.&lt;/p&gt; &lt;p&gt;Dès &lt;em&gt;Écologie et politique&lt;/em&gt; (1975), il relie la crise écologique au capitalisme : la croissance infinie détruit la nature et les liens humains. L’écologie doit être une politique de l’autonomie, qui permette de « produire moins, vivre mieux ». Il défendra plus tard un revenu d’existence versé à tous, indépendamment de l’emploi. Dans &lt;em&gt;Lettre à D.&lt;/em&gt; (2006), il écrit un émouvant livre d’amour à sa femme Dorine, gravement malade. Ils se donnent la mort ensemble en 2007, dans leur maison de Vosnon, dans l’Aube.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H153" s="48" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.laphilo.fr/pho/alainroger-mini.webp</t>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/gorz-mini.webp</t>
         </is>
       </c>
       <c r="J153" s="48" t="inlineStr">
         <is>
-          <t xml:space="preserve">esthetique</t>
+          <t xml:space="preserve">politique ; ethique</t>
         </is>
       </c>
       <c r="K153" s="48" t="inlineStr">
         <is>
-          <t xml:space="preserve">Constructivisme</t>
+          <t xml:space="preserve">Ecologisme ; Marxisme</t>
         </is>
       </c>
       <c r="L153" s="48" t="inlineStr">
         <is>
-          <t xml:space="preserve">philosophe et romancier français, théoricien de l’« artialisation » et de l’invention du paysage.</t>
+          <t xml:space="preserve">philosophe et journaliste français, l’un des fondateurs de l’écologie politique.</t>
+        </is>
+      </c>
+      <c r="M153" t="inlineStr">
+        <is>
+          <t xml:space="preserve">juive</t>
         </is>
       </c>
       <c r="N153" t="inlineStr">
@@ -10042,50 +10060,52 @@
           <t xml:space="preserve">occident</t>
         </is>
       </c>
-      <c r="O153"/>
+      <c r="O153">
+        <v>2</v>
+      </c>
     </row>
     <row r="154" ht="176.25" customHeight="1" s="49">
       <c r="A154" s="47">
-        <v>1938</v>
+        <v>1936</v>
       </c>
       <c r="B154" s="47" t="inlineStr">
         <is>
-          <t xml:space="preserve">2021</t>
+          <t xml:space="preserve">2025</t>
         </is>
       </c>
       <c r="C154" s="47" t="inlineStr">
         <is>
-          <t xml:space="preserve">1938 – 2021</t>
+          <t xml:space="preserve">1936 – 2025</t>
         </is>
       </c>
       <c r="D154" s="47" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pierre RABHI</t>
+          <t xml:space="preserve">Alain ROGER</t>
         </is>
       </c>
       <c r="E154" s="85" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Pierre_Rabhi" title=" Wikipedia"&gt;Pierre RABHI&lt;/a&gt; est un agriculteur, essayiste et militant français, l’une des figures de l’&lt;a href="https://fr.wikipedia.org/wiki/%C3%89cologisme" title=" Wikipedia"&gt;écologie&lt;/a&gt; en France. Né Rabah Rabhi en 1938 à Kenadsa, une oasis du sud de l’Algérie, il perd sa mère très jeune et est confié à un couple de Français d’Oran ; il se convertit au catholicisme et prend le prénom de Pierre. Venu à Paris, il travaille comme ouvrier, puis s’installe en 1961 avec sa femme Michèle dans les Cévennes ardéchoises, où il devient paysan et pratique une agriculture sans produits chimiques.&lt;/p&gt; &lt;p&gt;À partir de 1981, il forme des paysans au Burkina Faso, puis dans d’autres pays d’Afrique, à l’« agroécologie », une agriculture qui respecte les sols et rend les communautés autonomes. Dans ses livres, comme &lt;em&gt;Vers la sobriété heureuse&lt;/em&gt; (2010), il critique la société de consommation et l’idéologie de la croissance : il faut apprendre à vivre avec moins pour être plus heureux. En 2007, il fonde le mouvement Colibris, d’après une légende amérindienne : pendant un incendie de forêt, le colibri apporte des gouttes d’eau dans son bec, car il « fait sa part ».&lt;/p&gt; &lt;p&gt;Très populaire, il est candidat à l’élection présidentielle de 2002, sans réunir les signatures nécessaires. Son discours spirituel, sa proximité avec l’anthroposophie et son peu d’intérêt pour les combats politiques lui valent aussi des critiques, notamment de journalistes et de scientifiques qui contestent certaines de ses affirmations sur l’agriculture. Il meurt à Lyon en 2021. Son appel à une « insurrection des consciences » a inspiré de nombreuses initiatives locales d’écologie.&lt;/p&gt;</t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Alain_Roger" title=" Wikipedia"&gt;Alain ROGER&lt;/a&gt; est un philosophe et écrivain français. Né à Mirecourt, dans les Vosges, en 1936, ancien élève de l’École normale supérieure, agrégé de philosophie et élève de &lt;a href="https://fr.wikipedia.org/wiki/Gilles_Deleuze" title=" Wikipedia"&gt;Gilles Deleuze&lt;/a&gt;, il enseigne l’esthétique à l’université de Clermont-Ferrand. Romancier, il publie notamment &lt;em&gt;La Travestie&lt;/em&gt; (1987), adaptée au cinéma par Yves Boisset. Mais il est surtout connu comme le grand théoricien français du &lt;a href="https://fr.wikipedia.org/wiki/Paysage" title=" Wikipedia"&gt;paysage&lt;/a&gt;, auquel il consacre l’essentiel de son œuvre de philosophe.&lt;/p&gt; &lt;p&gt;Dans &lt;em&gt;Nus et paysages&lt;/em&gt; (1978) puis dans le &lt;em&gt;Court traité du paysage&lt;/em&gt; (1997), il soutient que la beauté de la nature n’est pas naturelle : nous voyons le monde à travers les œuvres d’art. Il reprend à Montaigne le mot « artialisation » pour désigner cette transformation de la nature par l’art. Elle peut être directe, « in situ », quand on façonne un jardin ou un corps, ou indirecte, « in visu », quand la peinture, la poésie ou la photographie éduquent notre regard. Le paysage naît ainsi au XVe siècle dans la peinture flamande, par la « fenêtre » ouverte au fond des tableaux.&lt;/p&gt; &lt;p&gt;Il montre que des lieux longtemps jugés affreux, comme la montagne ou le bord de mer, ne sont devenus beaux qu’au XVIIIe siècle, grâce aux écrivains et aux peintres. Ses travaux inspirent paysagistes et aménageurs, et il enseigne à l’école d’architecture de Paris-La Villette. Il est aussi l’auteur d’un &lt;em&gt;Bréviaire de la bêtise&lt;/em&gt; (2008), recueil d’aphorismes sur la sottise et ses formes les plus savantes. Il meurt à Belley, dans l’Ain, le 7 octobre 2025.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H154" s="48" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.laphilo.fr/pho/rabhi-mini.webp</t>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/alainroger-mini.webp</t>
         </is>
       </c>
       <c r="J154" s="48" t="inlineStr">
         <is>
-          <t xml:space="preserve">ethique ; politique ; spiritualite</t>
+          <t xml:space="preserve">esthetique</t>
         </is>
       </c>
       <c r="K154" s="48" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ecologisme</t>
+          <t xml:space="preserve">Constructivisme</t>
         </is>
       </c>
       <c r="L154" s="48" t="inlineStr">
         <is>
-          <t xml:space="preserve">agriculteur et essayiste français, pionnier de l’agroécologie et chantre de la « sobriété heureuse ».</t>
+          <t xml:space="preserve">philosophe et romancier français, théoricien de l’« artialisation » et de l’invention du paysage.</t>
         </is>
       </c>
       <c r="N154" t="inlineStr">
@@ -10138,86 +10158,86 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E46" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Marcel_Mauss&quot; title=&quot; Wikipedia&quot;&gt;Marcel MAUSS&lt;/a&gt; était un penseur des sciences sociales françaises, à la fois sociologue, anthropologue et penseur des religions, connu aussi comme le neveu et collaborateur d’Émile Durkheim, et comme l’un des fondateurs de l’anthropologie française.&lt;/p&gt; &lt;p&gt; Son œuvre la plus célèbre est &lt;a href=&quot;https://www.youtube.com/watch?v=3mwEKA0vPqY&quot;  title=&quot;le fait social total par culture philo&quot;&gt;Essai sur le don. &lt;/a&gt; &lt;/p&gt; Dans ce texte, il montre que le don n’est jamais un geste purement gratuit : il crée des liens, des obligations de donner, recevoir et rendre. Il montre que l’échange humain n’est pas seulement matériel, mais aussi moral, symbolique et politique, parce qu’il crée des obligations réciproques. C’est une idée profondément philosophique, car elle interroge ce qui fonde le lien entre les personnes et les sociétés et qu’elle révèle que les échanges humains ne sont pas seulement économiques, mais aussi sociaux, moraux et symboliques. &lt;/p&gt; &lt;p&gt; Il a aussi travaillé sur le sacré, le sacrifice, la magie, les rites, les classifications et  &lt;a href=&quot;https://www.nonfiction.fr/article-614-marcel-mauss-un-anthropologue-au-service-de-la-democratie.htm&quot;  title=&quot;Marcel Mauss anthropologue au service de la démocratie par Société&quot;&gt;les techniques du corps. &lt;/a&gt; Son approche consiste à comparer les sociétés pour comprendre ce qui structure la vie collective, au lieu de réduire les comportements humains à des choix individuels isolés. Il a ainsi contribué à faire de l’anthropologie une science des formes de vie sociale dans leur ensemble. &lt;/p&gt; &lt;p&gt; Il est proche de la tradition de la sociologie française classique mais il dépasse aussi cette école par son attention au symbolique, à la réciprocité et à la complexité des faits sociaux, ce qui explique pourquoi on le lit encore beaucoup aujourd’hui. Il propose  une manière différente de comprendre le monde en reprenant  &lt;a href=&quot;https://www.youtube.com/watch?v=DlJ7I3j84Ls&quot;  title=&quot;Marcel Mauss technique et civilisation par Cultures et Savoirs&quot;&gt;Habitus de Aristote &lt;/a&gt; car il n’est pas un philosophe de système, mais un penseur de la relation, de l’obligation et de la réciprocité, ce qui fait de lui une figure très importante pour comprendre l’humain. &lt;/p&gt;   &lt;audio controls title=&quot;Marcel MAUSS la pression du cadeau  par France Culture&quot;&gt; &lt;source src=&quot;https://media.radiofrance-podcast.net/podcast09/10467-20.10.2025-ITEMA_24284482-2025C48904S0293-NET_MFC_6DED14CA-5D8D-433D-ABFB-4B166937A5CF-21-ba959af78fc1deaf5b1fdfac4d98255c.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt;&lt;/audio&gt;&#10;" r:id="rId23"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H46" display="https://www.laphilo.fr/pho/mmauss-mini.webp" r:id="rId24"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E47" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Abel_Rey&quot; title=&quot; Wikipedia&quot;&gt;Abel REY&lt;/a&gt; était un philosophe français spécialiste d'histoire et de philosophie des sciences, qui contribua de manière décisive à l'institutionnalisation de cette discipline en France dans la première moitié du XXe siècle. Agrégé de philosophie et docteur ès lettres, il fut professeur à la Sorbonne et fonda avec Lucien Lévy-Bruhl et Henri Berr l'Institut d'histoire des sciences et des techniques en 1932. Son œuvre étendue embrasse l'histoire de la physique antique et moderne, la théorie de la connaissance et l'épistémologie générale. &lt;/p&gt; &lt;p&gt; Sa thèse principale, &lt;em&gt;La Théorie de la physique chez les physiciens contemporains&lt;/em&gt; (1907), est une analyse comparative des différentes interprétations philosophiques de la physique moderne au tournant du XXe siècle, examinant les positions de Mach, Duhem, Ostwald et Poincaré. Rey y défend un réalisme critique nuancé, qui reconnaît la valeur objective des théories physiques sans pour autant verser dans un réalisme naïf. Cette position lui vaut l'attention de Lénine qui le cite — de manière critique — dans &lt;em&gt;Matérialisme et empiriocriticisme&lt;/em&gt;. &lt;/p&gt; &lt;p&gt; Dans sa grande synthèse en plusieurs volumes sur &lt;em&gt;La Science orientale avant les Grecs&lt;/em&gt; et &lt;em&gt;La Jeunesse de la science grecque&lt;/em&gt;, Rey tenta une reconstruction rigoureuse des origines de la pensée scientifique en Mésopotamie, en Égypte et dans la Grèce archaïque, travail pionnier dans le domaine de l'histoire des sciences anciennes. Son œuvre illustre parfaitement le projet intellectuel du Centre International de Synthèse de Henri Berr : relier philosophie, sciences et histoire dans une perspective d'ensemble sur le progrès de la connaissance humaine. &lt;/p&gt;" r:id="rId25"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H50" display="https://www.laphilo.fr/pho/jchevalier-mini.webp" r:id="rId26"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E52" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Ren%C3%A9_Le_Senne&quot; title=&quot; Wikipedia&quot;&gt;René le SENNE&lt;/a&gt; était un philosophe français, cofondateur avec Louis Lavelle du mouvement dit de « La Philosophie de l'Esprit » ou « philosophie de la valeur », l'une des réponses spécifiquement françaises aux courants existentialistes et phénoménologiques qui se développaient en Europe dans la première moitié du XXe siècle. &lt;/p&gt; &lt;p&gt; Sa pensée s'organise autour du concept de valeur et d'obstacle. Dans son œuvre principale, &lt;em&gt;Obstacle et Valeur&lt;/em&gt; (1934), il développe &lt;a href=&quot;https://www.persee.fr/doc/phlou_0035-3841_1955_num_53_37_4532&quot;  title=&quot; René de Senne par persée&quot;&gt;une philosophie de l'épreuve &lt;/a&gt; : c'est dans la rencontre avec l'obstacle, dans la résistance que le réel oppose à nos désirs et à nos projets, que l'esprit se découvre lui-même et prend conscience de sa vocation à réaliser des valeurs. La valeur n'est pas donnée mais conquise à travers la lutte, et c'est dans cette tension permanente entre l'Etre et la conscience que réside la vie spirituelle. &lt;/p&gt; &lt;p&gt; Il est aussi l'auteur d'un &lt;em&gt;Traité de caractérologie&lt;/em&gt; (1945), ouvrage qui connut un large succès et qui cherche à établir une science rigoureuse des types de caractère humain. Distinguant plusieurs dimensions du caractère (émotivité, activité, résonance), il proposa une taxinomie des tempéraments qui eut une influence durable dans la psychologie et la pédagogie françaises. Cette double orientation, métaphysique et psychologique, fait de Le Senne un penseur original qui tenta de réconcilier la rigueur de l'analyse avec la profondeur de la réflexion sur l'existence humaine. &lt;/p&gt;" r:id="rId27"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E53" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Ra%C3%AFssa_Maritain&quot;  title=&quot; Wikipedia&quot;&gt;Raïssa MARITAIN&lt;/a&gt; était une philosophe, poétesse et mystique franco-russe. Née dans une famille juive, elle émigra en France avec sa famille dans l'enfance, étudia à la Sorbonne où elle rencontra Jacques Maritain, et se convertit avec lui au catholicisme en 1906 sous l'influence de Léon Bloy. Ensemble, ils formèrent l'un des &lt;a href=&quot;https://www.lavie.fr/idees/histoire/jacques-et-raissa-maritain-est-deux-88033.php&quot; title=&quot;jacques e traîssa par lavie,fr&quot;&gt;couples intellectuels &lt;/a&gt; les plus féconds de cette époque. &lt;/p&gt; &lt;p&gt; Elle apporta une contribution originale et irremplaçable à l'œuvre commune du couple. Poétesse d'une grande sensibilité, elle exprima dans des recueils comme &lt;em&gt;La Vie donnée&lt;/em&gt; (1935) une expérience mystique intense nourrie par la tradition juive et la spiritualité chrétienne. Ses &lt;em&gt;&lt;a href=&quot;https://www.youtube.com/watch?v=aKqCOZIq198&quot; title=&quot;la vérité par l’amitié par le verbe medias&quot;&gt;Grandes Amitiés &lt;/a&gt; &lt;/em&gt; (1941-1944), mémoires en deux volumes, constituent un témoignage exceptionnel sur la vie intellectuelle et spirituelle de l'entre-deux-guerres, évoquant ses rencontres avec Léon Bloy, Henri Bergson, Ernest Psichari, Jean Cocteau et de nombreux &lt;a href=&quot;http://palimpsestes.fr/metaphysique/textes/rmaritain_angoisse.html&quot; title=&quot;raissa maritain les grandes amitiés par palimpsestes.fr&quot;&gt;autres artistes et penseurs. &lt;/a&gt; &lt;/p&gt; &lt;p&gt; Elle contribua également aux travaux philosophiques de son mari, notamment aux réflexions sur la poésie et la connaissance poétique exposées dans &lt;em&gt;Situation de la poésie&lt;/em&gt; (1938), ouvrage qu'ils rédigèrent ensemble. Sa pensée sur le rapport entre expérience mystique, création artistique et connaissance philosophique constitue un apport original à la philosophie catholique française. Figure de la conversion et de l'engagement intellectuel au service de la foi, elle incarne une manière particulièrement intensément vécue de la vie de l'esprit. &lt;/p&gt;" r:id="rId28"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E55" display="https://louismassignon.fr/" r:id="rId29"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H55" display="https://www.laphilo.fr/pho/lmassignon-mini.webp" r:id="rId30"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H60" display="https://www.laphilo.fr/pho/gmarcel-mini.webp" r:id="rId31"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E62" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Alexandre_Koyr%C3%A9&quot;  title=&quot; Wikipedia&quot;&gt;Alexandre KOYRÉ&lt;/a&gt; était un philosophe et historien des sciences français d'origine russe, l'un des fondateurs de l'histoire des sciences modernes et un penseur dont l'influence sur l'historiographie scientifique mondiale fut décisive. Né à Taganrog en Russie, il étudia à Göttingen auprès de Husserl et de Hilbert avant de s'établir à Paris où il devint directeur d'études à l'École pratique des hautes études. Après la guerre, il partagea sa carrière entre Paris et Princeton. &lt;/p&gt; &lt;p&gt; Son œuvre maîtresse, &lt;em&gt;Études galiléennes&lt;/em&gt; (1939), est une révolution dans l'histoire des sciences. Contre la vision positiviste d'une science qui progresse par accumulation de faits expérimentaux, Koyré montre que la révolution scientifique du XVIIe siècle constitua une transformation radicale de la structure conceptuelle par laquelle les hommes pensaient la nature : le passage du cosmos aristotélicien, fini et ordonné, à l'univers infini et homogène de la physique classique. Cette thèse centrale, que l'histoire des sciences est d'abord une histoire des structures intellectuelles et non une simple accumulation de données, renouvela entièrement la discipline. &lt;/p&gt; &lt;p&gt; Dans &lt;em&gt;Du Monde clos à l'univers infini&lt;/em&gt; (1957), il approfondit cette thèse en retraçant la mutation cosmologique du XVIe au XVIIe siècle de Copernic à Newton. Ses travaux sur Descartes, Boyle et Newton sont également des contributions majeures. Son influence sur Thomas Kuhn — qui lui rendit hommage dans &lt;em&gt;La Structure des révolutions scientifiques&lt;/em&gt; — témoigne de la portée internationale de son travail. Koyré représente le modèle du philosophe-historien dont la rigueur intellectuelle a transformé durablement la compréhension du développement de la pensée scientifique. &lt;/p&gt;" r:id="rId32"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E63" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Gabriel_Madinier&quot;  title=&quot; Wikipedia&quot;&gt;Gabriel MADINIER&lt;/a&gt; était un philosophe français de tradition spiritualiste et réflexive, professeur à l’Université de Lyon, connu surtout pour sa « trilogie » sur la conscience (Conscience et mouvement, Conscience et amour, Conscience et signification) et pour son analyse de la conscience morale. Sa pensée s’inscrit dans le sillage de la philosophie de l’esprit française et vise à fonder une métaphysique et une éthique à partir de l’acte même par lequel la conscience se pose. &lt;/p&gt; &lt;p&gt; Fidèle à la méthode réflexive héritée de Lagneau et de Maine de Biran, il cherche à saisir le moi non comme un objet, mais dans l’acte même par lequel il se pose. Dans &lt;a href=&quot;https://www.persee.fr/doc/phlou_0776-555x_1940_num_43_67_4030_t1_0292_0000_2&quot;  title=&quot;gabriel madinier , conscience et mouvement par persée&quot;&gt;Conscience et mouvement &lt;/a&gt;  (1938), il montre que la conscience n’est pas séparable de la motricité : le geste, l’effort, le mouvement sont des manifestations concrètes à travers lesquelles la conscience s’éprouve et se constitue. Cette « conscience motrice » lui permet de dépasser les impasses du parallélisme et de l’objectivisme en ancrant la vie spirituelle dans l’expérience vécue du sujet agissant. &lt;/p&gt; &lt;p&gt; Dans Conscience et amour (1938), il prolonge cette enquête en explorant les conditions « surdéterminantes » de l’acte du moi, c’est-à-dire ce qui l’oriente vers autrui et vers la valeur. Le « Nous » n’est pas une simple donnée sociologique, mais une structure de la conscience où l’amour apparaît comme catégorie suprême de la raison, capable à la fois de distinguer et d’unir. Il y dessine une métaphysique du lien : au-delà du plan empirique des relations, l’amour se développe par la médiation de la justice et ouvre sur une dimension religieuse (rapport à Dieu) sans quitter le terrain de la psychologie réflexive. &lt;/p&gt; &lt;p&gt; Avec Conscience et signification (1953), il achève sa trilogie en proposant une véritable « métaphysique du signe » : la conscience est essentiellement productrice de sens, et c’est dans le Cogito que la conscience morale prend son origine. Il en tire, dans La conscience morale (1954), les conséquences éthiques : un rationalisme à la fois métaphysique et moral, d’inspiration très française, qui voit dans la raison la source des plus hautes exigences et dans l’amour (dont le christianisme révèle la signification universelle) l’explication ultime du réel. Pour lui, « ou le monde est absurde, ou l’amour explique tout », formule qui résume son option pour un spiritualisme rationnel ouvert à la transcendance. &lt;/p&gt; &lt;p&gt; Longtemps moins célèbre que d’autres représentants du spiritualisme français, il est reconnu par ses pairs comme un métaphysicien du signe et un penseur exigeant de la conscience et de l’amour. Ses ouvrages, réédités et parfois préfacés (notamment par Henri Gouhier et Aimé Forest), continuent d’intéresser ceux qui cherchent une philosophie réflexive, ancrée dans l’expérience concrète, mais capable de déboucher sur une éthique et une métaphysique intégrales. En ce sens, il prolonge et approfondit la tradition biranienne en lui donnant une tournure à la fois psychologique, morale et religieuse. &lt;/p&gt; &#10;&#10;" r:id="rId33"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H63" display="https://www.laphilo.fr/pho/gmadinier-mini.webp" r:id="rId34"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I63" display="https://www.laphilo.fr/photo/gmadinier.webp" r:id="rId35"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E64" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Gaston_Berger&quot;  title=&quot; Wikipedia&quot;&gt;Gaston BERGER&lt;/a&gt; était un philosophe, chef d’entreprise et haut fonctionnaire français connu pour avoir développé la notion de prospective et pour ses travaux sur la phénoménologie de Husserl. Il a cherché toute sa vie à articuler réflexion philosophique et action concrète, aussi bien dans l’industrie que dans l’administration de l’enseignement supérieur. Il fonde en 1925 la Société &lt;a href=&quot;https://www.youtube.com/watch?v=gChPu0ENNxI&quot; title=&quot; Centre Gaston Berger par Insa toulouse&quot;&gt;d’études philosophiques &lt;/a&gt; et la revue Études philosophiques, qui deviendront des lieux importants de la réflexion française.&#10; &lt;/p&gt; &lt;p&gt; Fondateur du mouvement de “prospective”, qu’il définit comme une science de l’“homme à venir”, vise à comprendre l’avenir possible pour mieux participer à sa réalisation, en réfléchissant aux besoins futurs tant culturels et moraux que techniques et matériels. Il crée le Centre international de prospective afin de favoriser des réflexions interdisciplinaires sur les futurs souhaitables et les responsabilités collectives.  &lt;/p&gt; &lt;p&gt;Il est l’un des principaux introducteurs de la phénoménologie d’Edmund Husserl en France, à laquelle il consacre sa thèse. Il propose la “théorétique”, conçue comme une science de la compréhension, qui vise à donner des outils conceptuels pour mieux saisir le réel et guider l’action.&#10; &lt;/p&gt; &lt;p&gt;Sa recherche se centre sur la conscience: valeur de la connaissance, présence de l’être, situation du moi, engagement, dialogue, amour, temps, courage. Il esquisse une phénoménologie de la mémoire où le devenir est une donnée concrète et le temps une construction ou un “mythe collectif” permettant aux hommes d’espérer et d’agir ensemble &lt;/p&gt; &lt;p&gt;  Il  incarne une figure de “philosophe‑administrateur”: il voit dans l’organisation et l’administration d’abord des problèmes humains avant d’être techniques. Son œuvre défend l’idée que la connaissance gratuite est à la fois facteur d’épanouissement personnel et condition d’une démocratie vivante. &lt;/p&gt;" r:id="rId36"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E65" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Georges_Bataille&quot; title=&quot; Wikipedia&quot;&gt;George BATAILLE&lt;/a&gt;  est un écrivain, philosophe, anthropologue et sociologue français, souvent qualifié de metaphysicien du mal pour son intérêt pour le sexe, la mort, la dégradation et le pouvoir de l'obscène. Il fut bibliothécaire, fondateur du Collège de Sociologie en 1937, et membre du journal Acéphale. Largement ignoré durant sa vie, il est aujourd'hui une figure centrale  &lt;a href=&quot;https://www.youtube.com/watch?v=ub2Ucoxs5fk&quot;  title=&quot;une vie, une œuvre par rien ne veut rien dire&quot;&gt;de l'intelligence française &lt;/a&gt; et a influencé des penseurs comme Foucault, Derrida ou Deleuze. &lt;/p&gt; &lt;p&gt; Sa philosophie se centre sur l'expérience intérieure, décrite comme un « voyage au bout du possible de l'homme », une extase ou ravissement qui nous porte au-delà des limites. Cette expérience s'atteint dans l'ivresse, l'érotisme, le rire, l'effusion poétique —  &lt;a href=&quot;https://blogs.mediapart.fr/amadouba19gmailcom/blog/150125/georges-bataille-1897-1962-mystique-transgressif-amadou-bal-ba&quot;  title=&quot;Georges Bataille mystique transgressif par blogs mediapart&quot;&gt;sans révélation divine, &lt;/a&gt;  dans un athéisme féroce. L'expérience intérieure est une plongée dans l'abîme où les repères s'effondrent, le savoir est aboli, la pensée défaite : « je saisis en sombrant que la seule vérité de l'homme, enfin entrevue, est d'être une supplication sans réponse ». &lt;/p&gt; &lt;p&gt; Il  est le penseur du mal, de l'excès, du négatif et de l'érotisme, considérés comme autant d'expériences intérieures. Il fut attiré par la violence et la disruption qu'elle pourrait causer au capitalisme et aux valeurs bourgeoises. Il explore les &lt;a href=&quot;https://www.persee.fr/doc/litt_0047-4800_1985_num_58_2_1389&quot;  title=&quot;Georges Bataille et la mort par persee&quot;&gt;« expériences limites » &lt;/a&gt; corporelles : cruauté, érotisme, transgression, subversion, sacrifice et excès, qui transcendent la pensée rationnelle. Ces expériences sont des voies pour acquérir une souveraineté personnelle, où la rationalité est suspendue lorsqu'on s'abandonne aux objets de ses désirs. &lt;/p&gt; &lt;p&gt; Parmi ses concepts clés, on trouve la sovereaneté (la liberté comme « seul miracle profane : impossible et pourtant là »), le sperpero ou dépense (déploiement inutile), et la partie maudite. La partie maudite exprime notre rapport à la mort, la violence et l'érotisme — la part sauvagement excessive de l'énergie qui ne peut être intégrée au système. Le sacré et l'abjection s'épousent chez lui sous une forme de dépassement des antinomies : le sacré est « à la fois saint et maudit, pur et impur, blanc et noir ». &lt;/p&gt; &lt;p&gt; Son œuvre Sur Nietzsche offre une nouvelle vision révolutionnaire du philosophe allemand, qui influença significativement Foucault, Derrida, Barthes et autres. Ses conceptions de la souveraineté, du sperpero et du sacrifice auront une grande influence sur les philosophes du XXe siècle, et ses idées sont reprises par Derrida, Kristeva et Sollers. &lt;/p&gt; &#10; &lt;audio controls title=&quot;Georges Bataille par France Culture&quot;&gt; &lt;source src=&quot;https://media.radiofrance-podcast.net/podcast09/13915-21.02.2024-ITEMA_23655177-2023C3372E0061-NET_MFC_CC62CF01-3F56-460F-B780-97916C17B0D7-21-7d903e2b8ecc4f9a64f0bed40bc4f642.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt; &#10;&#10;" r:id="rId37"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H65" display="https://www.laphilo.fr/pho/gbataille-mini.webp" r:id="rId38"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E66" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Aim%C3%A9_Forest&quot; title=&quot; Wikipedia&quot;&gt;Aimé FOREST&lt;/a&gt; était t un philosophe français spiritualiste, à la fois historien de la philosophie médiévale et métaphysicien d’inspiration thomiste et augustinienne. Sa pensée, souvent qualifiée de « philosophie du consentement », vise à articuler réalisme métaphysique, intériorité et sagesse chrétienne dans une démarche à la fois contemplative et concrète. &lt;/p&gt; &lt;p&gt; Né à Rancon (Haute-Vienne), agrégé de philosophie en 1921, il enseigne d’abord dans le secondaire avant de soutenir, en 1931, une thèse majeure sur La structure métaphysique du concret selon saint Thomas d’Aquin. Il occupe ensuite des chaires universitaires à Grenoble puis à Montpellier (1943–1968), où il forme plusieurs générations d’étudiants tout en publiant une œuvre abondante, jalonnée par des ouvrages comme Du consentement à l’être (1935), Consentement et création (1943), L’Avènement de l’âme (1973) ou Nos promesses encloses (1985). &lt;/p&gt; &lt;p&gt; Le titre même de son ouvrage phare indique l’axe central de sa philosophie : l’être ne se conquiert pas par la seule maîtrise conceptuelle, mais se reçoit dans un acte de consentement. Contre un idéalisme abstrait, Forest insiste sur la réalité concrète de l’existence et sur la nécessité, pour la pensée, de s’ouvrir à ce qui la précède et la soutient. Ce consentement n’est pas passivité, mais disposition active de l’intelligence à accueillir la vérité de l’être, vérité qui se dévoile davantage dans l’expérience intérieure que dans la construction systématique. &lt;/p&gt; &lt;p&gt; Influencé par Pascal, Maine de Biran, Louis Lavelle et Blondel, il développe une philosophie de l’intériorité où l’esprit découvre sa vocation sapientielle. L’âme n’est pas un objet parmi d’autres, mais le lieu où se noue le rapport à l’être et où se manifeste un « lien spirituel » qui unit les personnes entre elles et à la transcendance. Des titres comme L’Avènement de l’âme ou Essai sur les formes du lien spirituel montrent que sa métaphysique débouche sur une anthropologie spirituelle attentive à l’amour, à la promesse et à la communauté des esprits. &lt;/p&gt; &lt;p&gt;  Il assume explicitement la figure du « philosophe chrétien » : pour lui, la raison trouve son élan naturel dans le consentement au soutien de la foi, qui ne la supprime pas mais l’élève et l’assure. Sa démarche intègre thomisme et augustinisme dans une « sagesse plus haute que le thomisme », où métaphysique, mystique et amour convergent vers une sagesse intégrale. Cette orientation le place en marge des grands courants dominants du XXᵉ siècle (phénoménologie, existentialisme, pensée allemande), au profit d’une voie spirituelle, réaliste et universelle. &lt;/p&gt; &lt;p&gt; Longtemps peu connu hors des cercles spécialisés, il fait l’objet d’un regain d’attention grâce à des études (Michel Mahé, Philippe-Marie Margelidon, etc.) qui mettent en lumière la cohérence de son itinéraire. Son œuvre intéresse aujourd’hui ceux qui cherchent une métaphysique non dogmatique, ancrée dans l’expérience concrète et l’intériorité, tout en restant ouverte à la dimension religieuse. En ce sens, il propose moins un système clos qu’un chemin de sagesse : apprendre à consentir à l’être, à habiter son intériorité et à reconnaître, dans l’amour et la promesse, les formes vivantes du lien spirituel.&lt;/p&gt; &#10;&#10;&#10;&#10;" r:id="rId39"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H66" display="https://www.laphilo.fr/pho/aforest-mini.webp" r:id="rId40"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I66" display="https://www.laphilo.fr/photo/aforest.webp" r:id="rId41"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E70" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Vladimir_Jank%C3%A9l%C3%A9vitch&quot;   title=&quot; Wikipedia&quot;&gt;Vladimir JANKÉLÉVITCH&lt;/a&gt; était un philosophe français d'origine russe, influencé par Bergson, connu pour sa pensée originale &lt;a href=&quot;https://www.youtube.com/watch?v=498pItDm0vA&quot; title=&quot; Vladimir Jankélévitch : penser la morale, aimer le monde par Ina Culture&quot;&gt;mêlant morale, &lt;/a&gt; temps, musique, souvent en marge des courants dominants. Il  cultive un style littéraire élégant, improvisé, centré sur l'expérience vécue, le cœur et l'ineffable, refusant les systèmes rigides. &lt;/p&gt; &lt;p&gt;  Pour lui, la morale prime sur tout : elle est hyperbolique, urgente, guidée par le cœur et l'instant de la décision, au-delà des devoirs rationnels ; elle rejoint la métaphysique.  Il conçoit &lt;a href=&quot;https://www.youtube.com/watch?v=G6hbXImCmJA&quot; title=&quot;Vladimir Jankélévitch, penser la vie par LCP&quot;&gt;la liberté &lt;/a&gt; comme dynamique, non statique  amenant à une prise de conscience en mouvement, vers un &quot;au-delà de soi&quot; ; l'homme libre agit authentiquement, sans dogmes. &lt;/p&gt; &lt;p&gt; &lt;a href=&quot;https://maitron.fr/jankelevitch-vladimir/&quot; title=&quot; Vladimir Jankélévitch par maitron.fr&quot;&gt; Pour lui, &lt;/a&gt; la musique transcende l'esthétique pour devenir une expérience philosophique et métaphysique. Elle incarne l'irréversibilité du temps et l'instant fugace, reliant le sensible à l'intelligible sans jamais se réduire à une structure figée ou un algorithme. Elle exprime l'inexprimable : émotions, mystère de l'être, profondeur existentielle que le discours rationnel esquive. Le silence y joue un rôle clé, non comme absence, mais comme plénitude qui invite à l'introspection et à la transcendance. Il a consacré une douzaine d'ouvrages à la musique, comme Fauré et le Ineffable, Debussy et le Mystère ou Ravel, où philosophie et analyse musicale fusionnent en une prose poétique et improvisée.&lt;/p&gt; &lt;p&gt; Ses Œuvres majeures : -&quot;Philosophie première&quot; paru en 1954 : métaphysique vitaliste.  - Le &lt;a href=&quot;https://www.youtube.com/watch?v=KUUGJfgMoj0&quot; title=&quot;Vladimir Jankélévitch en 1980, philosophe du Je-ne-sais-quoi et du Presque-rien? par Radio-Canada Archives&quot;&gt;&quot;Je-ne-sais-quoi et le Presque-rien&quot; &lt;/a&gt; paru en 1957. - &quot;La Mort&quot; paru en 1967 et  -&quot;L'Irréversible et la Nostalgie&quot; en 1974. &lt;/p&gt; &#10;&lt;p&gt; &lt;/p&gt;   &lt;audio controls title=&quot;Avoir raison avec... Vladimir Jankélévitch par France Culture&quot;&gt; &lt;source src=&quot;https://media.radiofrance-podcast.net/podcast09/17362-07.08.2017-ITEMA_21402275-2017C35448E0026-NET_FC_4ECDB095-2595-41D4-AA28-F4A95CC22729-21.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt;  " r:id="rId42"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E75" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Emmanuel_Mounier&quot;  title=&quot; Wikipedia&quot;&gt;Emmanuel MOUNIER&lt;/a&gt; était un philosophe français connu comme le fondateur du personnalisme, un courant qui veut remettre la personne humaine au centre de la pensée et de la vie sociale. &lt;/p&gt; &lt;p&gt; Sa philosophie naît dans un contexte de crise : montée du capitalisme, du fascisme, du marxisme et sentiment que l’homme est écrasé par des systèmes trop abstraits. Il refuse à la fois l’individualisme, qui isole l’être humain, et le collectivisme, qui le dissout dans le groupe. &lt;/p&gt; &lt;p&gt; Pour lui, la personne n’est pas seulement un individu biologique ou social.  &lt;a href=&quot;https://www.youtube.com/watch?v=T8tZ7E0D49k&quot;  title=&quot;emmanuel mounier par kto tv&quot;&gt;&quot;C’est un être libre, &lt;/a&gt; responsable, ouvert aux autres et appelé à se construire dans l’engagement, la relation et la vie communautaire. Cette idée donne à sa pensée une dimension à la fois morale, politique et spirituelle. &lt;/p&gt; &lt;p&gt; Il est aussi profondément chrétien, mais un chrétien engagé dans le monde. Avec  &lt;a href=&quot;https://maitron.fr/mounier-emmanuel-hippolyte-henri/&quot;  title=&quot;emmanuel mounier par maitron&quot;&gt;la revue Esprit, &lt;/a&gt; qu’il fonde en 1932, il cherche à faire dialoguer la foi, la réflexion philosophique et les grands problèmes de son époque, comme la guerre, la démocratie ou la justice sociale. Il défend une forme de « révolution spirituelle », c’est-à-dire une transformation intérieure et sociale de l’homme et des institutions. &lt;/p&gt; &lt;p&gt; la philosophie de Mounier propose une vision exigeante de l’humain : la personne doit être respectée dans sa dignité, sa liberté et sa vocation relationnelle. Son influence a été importante sur la pensée chrétienne, la philosophie sociale et les débats sur la démocratie au XXe siècle. &lt;/p&gt; &lt;audio controls title=&quot;Les murs blancs revue esprit par France Culture&quot;&gt; &lt;source src=&quot;https://media.radiofrance-podcast.net/podcast09/17473-14.03.2021-ITEMA_22602800-2021B20595S0073.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt; &#10;" r:id="rId43"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H75" display="https://www.laphilo.fr/pho/emounier-mini.webp" r:id="rId44"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I81" display="https://www.laphilo.fr/photo/jbeaufret.webp" r:id="rId45"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E82" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Maurice_Merleau-Ponty&quot; title=&quot; Wikipedia&quot;&gt;Maurice MERLEAU-PONTY&lt;/a&gt; était un philosophe français connu pour ses contributions à la phénoménologie, à la philosophie de la perception et à l’existentialisme. Il  s’inspire de plusieurs courants et penseurs et  reprend l’idée d’une description des expériences vécues, mais critique l’idéalisme husserlien. Dans son oeurvre majeure &lt;a href=&quot;https://www.youtube.com/watch?v=RrD5SEiXr_A&quot;  title=&quot; La phénoménologie de Maurice Merleau-Ponty par Tes grands auteurs en petits morceaux&quot;&gt;&quot;Phénoménalogie de la perception&quot;&lt;/a&gt; il  y développe une critique radicale des approches traditionnelles de la perception pour proposer une vision incarnée et existentielle de l’expérience humaine. Il rejette la séparation cartésienne entre le corps et l’esprit &lt;a href=&quot;https://classiques.uqam.ca/classiques/merleau_ponty_maurice/sens_et_non_sens/sens_et_non_sens.html&quot;  title=&quot;  Maurice Merleau-Ponty sens et non sens  par UQAM&quot;&gt;(sens et non sens)&lt;/a&gt;. Pour lui, le corps n’est pas un objet, mais un sujet percevant :  &lt;/p&gt; &lt;p&gt;&#10;-  Le corps propre : C’est par lui que nous faisons l’expérience du monde. Il est à la fois sujet et objet, toujours déjà engagé dans un environnement. &lt;/p&gt; &lt;p&gt; - La perception comme ouverture au monde : &lt;a href=&quot;https://www.youtube.com/watch?v=yiHMPFMCUvo&quot; title=&quot;MERLEAU-PONTY - L'OEIL ET L'ESPRIT par Kosmos&quot;&gt;Percevoir&lt;/a&gt; , c’est être en dialogue avec le monde, pas simplement recevoir des données sensorielles. &lt;/p&gt;  &lt;p&gt;   Il  s’intéresse au langage comme geste corporel. Pour lui, la parole n’est pas un simple véhicule de la pensée, mais une incarnation du sens et l’art montre comment l’expression émerge de la perception. &lt;/p&gt; &lt;p&gt; Dans &quot;Le Visible et l’invisible&quot;, il développe une  &lt;a href=&quot;https://www.youtube.com/watch?v=wZNUUGSZHMs&quot;  title=&quot; Maurice Merleau-Ponty - Entretien : Heure de culture française par Artesquieu &quot;&gt;ontologie originale&lt;/a&gt; où le &quot;chair&quot; est ni matière ni esprit, c’est une substance sensible qui unit le corps et le monde.  Chiasme : Concept décrivant l’entrelacs du voyant et du visible, du touchant et du touché (ex. : quand je me touche la main, je suis à la fois sujet et objet).  L’invisible : Non pas l’absence de visible, mais ce qui le structure. &lt;/p&gt;   &lt;audio controls title=&quot;Maurice Merleau-Ponty : Partie 8/12- La crise de la pensée religieuse par France Culture&quot;&gt; &lt;source src=&quot;https://media.radiofrance-podcast.net/podcast09/13915-20.11.2014-ITEMA_20690515-2013C3372E0710-21.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt;  " r:id="rId46"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E84" display="&lt;p&gt; &lt;a href=&quot;https://fr.wikipedia.org/wiki/Claude_L%C3%A9vi-Strauss&quot;  title=&quot; Wikipedia&quot;&gt;Claude LEVI-STRAUSS&lt;/a&gt; était un anthropologue et ethnologue français, considéré comme l’une des grandes figures intellectuelles du XXᵉ siècle. Après des études de droit puis de philosophie, il se tourne vers l’ethnologie et commence ses premières missions de terrain au Brésil dans les années 1930, auprès de peuples amérindiens du Mato Grosso et de l’Amazonie. De ces expériences, il tirera notamment le livre Tristes tropiques, qui le rend célèbre auprès d’un public plus large en mêlant récit de voyage, &lt;a href=&quot;https://www.youtube.com/watch?v=Fk7du0Avh7U&quot; title=&quot;peuples amerindiens levi-strauss par ina culture&quot;&gt; réflexion sur les sociétés &lt;/a&gt; dites « primitives » et critique de l’ethnocentrisme occidental. &lt;/p&gt; &lt;p&gt; Il est connu pour avoir fondé l’anthropologie structurale, une manière d’étudier les cultures qui cherche les structures profondes, souvent inconscientes, qui organisent les systèmes de parenté, les mythes, les rites et plus largement les formes de vie sociales. Inspiré par la linguistique structurale, il considère que les faits culturels sont comme des langages : ce qui compte, ce sont les relations entre les éléments, plutôt que les éléments pris isolément. Sa méthode vise à réduire la diversité apparente des cultures à des ensembles de relations et d’oppositions formelles, par exemple des oppositions binaires (nature/culture, cru/cuit, vie/mort) qui structurent l’imaginaire. &lt;/p&gt; &lt;p&gt; Une partie centrale de son œuvre concerne les systèmes de parenté et l’alliance matrimoniale, qu’il étudie en détail dans Les structures élémentaires de la parenté, publié en 1949. Il y développe la théorie de l’alliance, selon laquelle les liens de parenté ne sont pas seulement des liens de sang, mais aussi des échanges de femmes entre groupes qui créent des solidarités et des obligations réciproques. Le mariage devient ainsi un mécanisme de communication sociale, une manière d’établir des réseaux d’alliance qui rendent possible la cohésion de la société. &lt;/p&gt; &lt;p&gt; Un autre volet majeur de sa pensée est son travail sur les mythes, en particulier dans les quatre volumes des Mythologiques, où il cherche à montrer que les mythes des différentes cultures, malgré leur grande diversité, obéissent à des schémas de transformation et à des structures communes. Pour lui, le mythe n’est pas une simple histoire, mais un système logique qui met en scène des oppositions et des médiations  pour résoudre symboliquement des tensions fondamentales. En analysant les mythes comme des ensembles de relations, il soutient que  &lt;a href=&quot;https://www.youtube.com/watch?v=fC0HUuXknHk&quot; title=&quot;etre pessimiste pour l’avenir par ina culture&quot;&gt;l’esprit humain fonctionne &lt;/a&gt;  partout selon des structures universelles, même si le contenu des récits varie. &lt;/p&gt; &lt;p&gt; Il développa une réflexion plus générale sur la diversité culturelle et les effets du colonialisme et de la modernité, notamment dans Tristes tropiques où il critique la tendance du monde moderne à homogénéiser et à détruire les différences culturelles. Il affirme l’idée que toutes les cultures sont égales en dignité et que la diversité des formes de vie humaines représente une richesse qu’il faut préserver, plutôt qu’un obstacle à dépasser. Son œuvre, reconnue par de nombreuses distinctions (médaille d’or du CNRS, élection à l’Académie française, prix Érasme, etc.), a contribué à transformer notre manière de penser le rapport entre l’Occident et les autres sociétés, ainsi que les fondements mêmes des sciences sociales. &lt;/p&gt;    &lt;audio controls title=&quot;sur les pas de claude levi-dtrausspar France Culture&quot;&gt; &lt;source src=&quot;https://media.radiofrance-podcast.net/podcast09/13019-03.08.2022-ITEMA_23099095-2022F20970S0215-22.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt;  " r:id="rId47"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H84" display="https://www.laphilo.fr/pho/clstrauss-mini.webp" r:id="rId48"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I88" display="https://www.laphilo.fr/photo/morotsir.webp" r:id="rId49"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E90" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Henri_Maldiney&quot;  title=&quot; Wikipedia&quot;&gt;Henri MALDINEY&lt;/a&gt; était un philosophe français, l'une des figures les plus importantes de la phénoménologie française, connu pour sa réflexion originale sur l'art, la psychiatrie et l'existence. Né à Lyon, agrégé de philosophie, il enseigna à l'Université de Lyon pendant toute sa carrière. Sa pensée, &lt;a href=&quot;https://www.henri-maldiney.org/&quot;  title=&quot;henri MALDINEY&quot;&gt; d'une grande densité &lt;/a&gt; et d'un style exigeant, se développe à l'intersection de la phénoménologie husserlienne et heideggerienne, de la psychiatrie phénoménologique (notamment Binswanger) et d'une réflexion approfondie sur les arts plastiques et la musique. &lt;/p&gt; &lt;p&gt; Son œuvre maîtresse, &lt;em&gt;Regard, Parole, Espace&lt;/em&gt; (1973), est une méditation profonde sur la perception, le langage et l'espace à partir de l'analyse d'œuvres plastiques et poétiques.  &lt;a href=&quot;https://www.persee.fr/doc/chime_0986-6035_2001_num_44_1_2388/&quot;  title=&quot;henri MALDINEY par persée &quot;&gt; Il y développe &lt;/a&gt; une phénoménologie du pathique — du mode d'être fondamental par lequel nous sommes d'abord « touchés » par ce qui nous vient — par opposition au gnostique, qui serait le rapport détaché et objectivant à la réalité. Cette distinction lui permet d'analyser de manière originale la perception esthétique, l'expérience psychopathologique et la rencontre avec l'autre. &lt;/p&gt; &lt;p&gt; Dans &lt;em&gt;&lt;a href=&quot;https://fr.wikiversity.org/wiki/Penser_l%27homme_et_la_folie&quot;  title=&quot;pensée l’homme et la folie  par wikipedia &quot;&gt;Penser l'homme et la folie &lt;/a&gt; &lt;/em&gt; (1991) et &lt;em&gt;L'Art, l'éclair de l'être&lt;/em&gt; (1993), il approfondit sa réflexion sur les relations entre existence, folie et création artistique. Pour lui, l'art n'est pas un objet parmi d'autres mais une modalité d'existence, un surgissement de sens qui déborde toute représentation. Sa pensée, qui articule phénoménologie, psychiatrie et esthétique, a exercé une influence durable sur la psychiatrie phénoménologique française et sur les études d'esthétique philosophique. &lt;/p&gt;  &lt;audio controls title=&quot;hommage à Henri Maldiney par France Culture&quot;&gt; &lt;source src=&quot;https://media.radiofrance-podcast.net/podcast09/10080-14.12.2013-ITEMA_20561627-2013C3403E0239-21.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt; " r:id="rId50"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E91" display="&lt;p&gt; &lt;a href=&quot;https://fr.wikipedia.org/wiki/Albert_Camus&quot;  title=&quot; Wikipedia&quot;&gt;Albert CAMUS&lt;/a&gt; était un philosophe et écrivain français dont le courant de pensée est l'Existentialisme. Il a abordé de nombreux sujets philosophiques, notamment &lt;a href=&quot;https://www.youtube.com/watch?v=kAm_I8nwjnc&amp;t=498s&amp;ab_channel=LePr%C3%A9cepteur&quot;   title=&quot;L'absure par le Précepteur&quot;&gt;l'absurdité de la vie&lt;/a&gt;, la liberté individuelle, la révolte, l'amour.&lt;/p&gt; &lt;p&gt;Il a écrit plusieurs ouvrage comme  &lt;a href=&quot;https://www.youtube.com/watch?v=vpzwD2cqqII&amp;ab_channel=LePr%C3%A9cepteur&quot;  title=&quot;L'étranger par le Précepteur&quot;&gt;&quot;l'Étranger&quot;&lt;/a&gt;  ou &quot;Le Mythe de Sisyphe&quot; où il  a développé l'idée que la vie est fondamentalement absurde, car elle ne contient pas de sens intrinsèque ou de finalité. Il a expliqué que l'homme est confronté à un monde qui ne lui donne pas de réponses claires ou satisfaisantes à ses questions sur l'existence et que, par conséquent, il doit créer son propre sens de la vie. &lt;/p&gt; &lt;p&gt;Camus a également écrit sur la liberté individuelle et la révolte contre l'oppression avec son livre &lt;a href=&quot;https://www.youtube.com/watch?v=XLbXH2kVOJ8&quot;  title=&quot;La Peste par le France Culture&quot;&gt;&quot; la Peste&quot;&lt;/a&gt; sortie en 1947 où Il défend la position selon laquelle l'individu doit être libre de poursuivre ses propres intérêts et passions, et que la tyrannie et l'oppression sont des forces qui doivent être combattues. Après le cycle de l'absurde, il entame le cycle de la &lt;a href=&quot;https://www.youtube.com/watch?v=pkRWhuO0wX0&amp;ab_channel=AlainBajom%C3%A9er&quot; title=&quot;La Révolte par Alain Bajomée&quot;&gt;révolte.&lt;/a&gt; &lt;/p&gt; &lt;p&gt;Enfin, il a écrit sur l'amour et l'amitié, explorant la façon dont ces sentiments peuvent apporter de la signification et de la valeur à la vie et a réfléchi sur la solitude et l'isolement, soulignant que ces expériences peuvent être à la fois douloureuses et enrichissantes. &lt;/p&gt;   &lt;audio controls title=&quot;Albert Camus par France Culture&quot;&gt; &lt;source src=&quot;https://cdn.radiofrance.fr/s3/cruiser-production/static/inter/sons/2011/07/s27/NET_2f8a9ed7-086a-40ee-9d75-b184f9e5f99a.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt; &#10;" r:id="rId51"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E92" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Paul_Ric%C5%93ur&quot;   title=&quot; Wikipedia&quot;&gt;Paul RICOEUR&lt;/a&gt; était un  philosophe français considéré comme le dernier &lt;a href=&quot;https://www.lemonde.fr/a-la-une/article/2005/05/21/paul-ricoeur-philosophe-de-tous-les-dialogues_652552_3208.html&quot;  title=&quot;Paul Ricoeur, philosophe de tous les dialogues par Le Monde&quot;&gt;&quot;grands penseurs&quot; &lt;/a&gt; à la croisée de la phénoménologie, de l’herméneutique, de la philosophie du langage et de l’éthique. &lt;/p&gt; &lt;p&gt; Dans “Le volontaire et l’involontaire” et “Finitude et culpabilité”, il analyse la volonté humaine comme toujours prise entre liberté et contraintes, capacité d’agir et fragilité, ce qui nourrit sa réflexion sur la faute et la responsabilité.  Ses travaux sur le symbole et l’interprétation montrent que l’être humain se comprend à travers  &lt;a href=&quot;https://www.youtube.com/watch?v=QLOwycKenCI&quot; title=&quot;En 1965, le philosophe Paul Ricoeur commente la contre-culture beatnik par Radio-Canada&quot;&gt; des symboles &lt;/a&gt;, des récits et des textes, dont le sens n’est jamais donné immédiatement mais demande un travail d’interprétation. Son projet est de tenir ensemble la compréhension “interprétative” et les approches critiques (psychanalyse, structuralisme), en assumant les “conflits d’interprétations” plutôt que de chercher une seule lecture définitive. &lt;/p&gt; &lt;p&gt; Il conçoit  &lt;a href=&quot;https://www.youtube.com/watch?v=uX76UVhBIqs&quot;  title=&quot;Paul Ricoeur, l’herméneutique du soupçon par Baglis Tv&quot;&gt; l’herméneutique&lt;/a&gt; comme une philosophie de l’interprétation qui assume la distance entre nous et les textes, les événements, les autres, et qui cherche une vérité située dans ce travail d’interprétation plutôt que dans une évidence immédiate.​ Il insiste sur le fait qu’il n’existe pas de philosophie “sans présuppositions” : toute compréhension passe par des pré-compréhensions, que la critique vient transformer, ce qui l’amène à articuler la lecture soupçonneuse (Marx, Nietzsche, Freud) et la lecture de confiance. &lt;/p&gt; &lt;p&gt; Il développe une éthique de la “vie bonne, avec et pour les autres, dans des institutions justes” (formule célèbre de “Soi-même comme un autre”), où l’éthique (visée de la vie bonne) précède la morale (règles, normes).​ &#10;Il met au centre le “sujet capable” (capable de parler, agir, se raconter, se tenir pour responsable) mais toujours fragile, et pense la justice comme articulation entre la reconnaissance de la vulnérabilité des personnes et la nécessité d’institutions justes.​ &lt;/p&gt; &lt;p&gt; Ses analyses de la mémoire, de l’histoire et du pardon nourrissent aussi les débats contemporains sur le “devoir de mémoire”, les violences politiques et les possibilités de réconciliation. &lt;/p&gt;   &lt;audio controls title=&quot;La pensée de Paul Ricoeur par France Culture&quot;&gt; &lt;source src=&quot;https://media.radiofrance-podcast.net/podcast09/10467-18.11.2013-ITEMA_20550371-2013C12410S0322-NET_FC_66E918EC-2266-4DF5-B6E4-489E465FA68D-21.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt;" r:id="rId52"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H93" display="https://www.laphilo.fr/pho/lgoldmann-mini.webp" r:id="rId53"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E94" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Marguerite_Duras&quot;  title=&quot; Wikipedia&quot;&gt;Marguerite DURAS&lt;/a&gt; n’était pas une philosophe au sens académique, mais son œuvre littéraire, cinématographique et théâtrale déploie  &lt;a href=&quot;https://www.marguerite-duras.com/Biographie.php&quot;  title=&quot;marguerite duras -biographie&quot;&gt;une pensée originale, &lt;/a&gt; centrée sur l’écriture, le désir, la mémoire et la condition humaine. &lt;/p&gt; &lt;p&gt; Elle récuse le dualisme corps/esprit hérité de la tradition philosophique et religieuse occidentale, et propose plutôt un monisme matérialiste : l’être est fait d’une seule substance, la matière, et le corps y est réhabilité contre les représentations littéraires marquées par le péché originel. Cette vision s’enracine aussi dans son athéisme et dans l’influence de la philosophie orientale, vécue durant ses dix-huit premières années en Indochine. &lt;/p&gt; &lt;p&gt; Pour elle, écrire, c’est « donner corps au paradoxe » et signifier le désir : l’écriture est le lieu même de la « vérité du désir », souvent orientée vers un objet absent, inaccessible. Elle décrit l’écriture comme un acte de silence et de cri : « Écrire c’est ne pas parler. C’est se taire. C’est hurler sans bruit. », libérant un  &lt;a href=&quot;https://www.youtube.com/watch?v=KBum9zj-9p8&quot;  title=&quot;marguerite duras -détruire pour mieux reconstruire par france culture&quot;&gt;désir refoulé &lt;/a&gt; par la société. La mémoire est inséparable du désir et de l’écriture : elle n’est pas fiable, et c’est par l’affabulation et la réinscription dans le texte que les souvenirs acquièrent une existence réelle. L’écriture devient alors travail de mémoire et de deuil, une manière de faire durer la vie face à la mort, en traitant « la mémoire de l’oubli ». &lt;/p&gt; &lt;p&gt; Elle met en scène un sujet humain inconsistant, « fantomatique », essentiellement seul et dépourvu d’identité stable, s’opposant au « fantasme d’identité » de la philosophie occidentale. Tout en restant distante du militantisme féministe, son œuvre défend la cause des femmes et explore la liberté, la passivité et la dynamique masculin/féminin, notamment dans sa dernière période créatrice. &lt;/p&gt; &lt;p&gt; Bien qu’elle affirme ne pas écrire ex nihilo et reconnaisse des inspirations (Pascal, Diderot, Rousseau, Kierkegaard), elle s’en détache en déclarant avoir oublié ses lectures, marquant une relation paradoxale à la philosophie. Son rapport à la pensée se manifeste par des interrogations sur le temps, la matière et la souffrance, faisant de l’écriture le seul moyen d’exprimer des émotions fondamentales que le langage ordinaire ne peut porter. &lt;/p&gt; &#10;&lt;audio controls title=&quot;Marguerite DURAS , je mets la musique au-dessus de tout par France Culture&quot;&gt; &lt;source src=&quot;https://media.radiofrance-podcast.net/podcast09/20333-02.01.2023-ITEMA_23242749-2022M36310E0193-25.m4a&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt;  " r:id="rId54"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H94" display="https://www.laphilo.fr/pho/mduras-mini.webp" r:id="rId55"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E95" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Louis_Althusser&quot;  title=&quot; Wikipedia&quot;&gt;Louis ALTHUSSER&lt;/a&gt; était un philosophe connu pour ses efforts de renouvellement de la pensée marxiste et ses concepts novateurs.  Parmi ses concepts clés, on peut citer : &lt;/p&gt;  &lt;p&gt; - La coupure épistémologique : Il soutient qu'il existe une rupture radicale entre les œuvres de jeunesse de Marx  et ses œuvres de la maturité (notamment Le Capital). Cette coupure marquerait le passage d'une idéologie humaniste à une science de l'histoire, le matérialisme historique. &lt;/p&gt; &lt;p&gt; - L'idéologie et les Appareils Idéologiques d'État &lt;a href=&quot;https://www.youtube.com/watch?v=ZtJjAs7kLpo&quot;  title=&quot; Louis Althusser AIE par Cinema culture&quot;&gt;(AIE) &lt;/a&gt;: Il développe une théorie influente de l'idéologie avec un ensemble d'idées fausses, mais une &quot;représentation du rapport imaginaire des individus à leurs conditions réelles d'existence&quot;. Elle fonctionne en &quot;interpellant&quot; les individus en sujets. Les AIE (comme l'école, l'Église, la famille, les médias) jouent un rôle crucial dans la reproduction des rapports de production capitalistes en diffusant l'idéologie dominante. &lt;/p&gt; &lt;p&gt; - La surdétermination : Emprunté à la psychanalyse, ce concept lui permet de penser la complexité des contradictions dans une société. Une contradiction principale entre les forces productives et les rapports de production est toujours surdéterminée par d'autres contradictions secondaires. &lt;/p&gt; &lt;p&gt; - Le procès sans sujet : Il critique l'idée que l'histoire serait le produit de l'action consciente d'un sujet et insiste sur le fait que l'histoire est un &lt;a href=&quot;https://www.youtube.com/watch?v=Syi7hOQcNUs&quot;  title=&quot; Louis Althusser sur la civilisation par Artesquieu&quot;&gt;processus déterminé&lt;/a&gt; par des structures. &lt;/p&gt; &lt;p&gt;  - La philosophie comme &quot;lutte de classes dans la théorie&quot; : Il conçoit la philosophie non pas comme une quête de vérité absolue, mais comme une intervention politique dans le champ théorique, reflétant les luttes de classes. Il parle aussi de la &quot;philosophie spontanée des savants&quot; pour désigner les présupposés idéologiques inconscients qui peuvent influencer le travail scientifique. &lt;/p&gt; &lt;p&gt; Parmi ses publications les plus importantes, on peut mentionner : &lt;/p&gt; &lt;p&gt;- Montesquieu, la politique et l'histoire : Une analyse de la pensée politique de Montesquieu.  - Lénine et la philosophie : Développe sa conception de la philosophie comme pratique politique.  - L'avenir dure longtemps (suivi de Les Faits) (1992, posthume) : Une autobiographie où il revient sur sa vie, ses troubles psychiques et le meurtre de sa femme, Hélène Rytmann, en 1980. Cet événement tragique a conduit à son internement psychiatrique et a mis fin à sa carrière publique. &lt;/p&gt;  &lt;audio controls title=&quot; Louis Althusser par France Culture&quot;&gt; &lt;source src=&quot;https://media.radiofrance-podcast.net/podcast09/11189-11.07.2011-ITEMA_20296434-2011C15000E0126-ITE_00044081_RSCE-21.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt;&lt;/audio&gt; " r:id="rId56"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E97" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Suzanne_Bachelard&quot; title=&quot; Wikipedia&quot;&gt;Suzanne BACHELARD&lt;/a&gt; était une philosophe française spécialiste de phénoménologie et de logique, fille du célèbre Gaston Bachelard. Agrégée de philosophie et docteur ès lettres, elle fut professeur à la Sorbonne et contribua de manière significative à la diffusion et à l'approfondissement de la &lt;a href=&quot;https://www.persee.fr/doc/phlou_0035-3841_1954_num_52_34_4491&quot;  title=&quot;phénoménologie husserlienne et hegelienne par persée&quot;&gt;phénoménologie husserlienne &lt;/a&gt;  en France. Son travail intellectuel, longtemps éclipsé par la stature de son père, mérite d'être apprécié pour lui-même. &lt;/p&gt; &lt;p&gt; Sa thèse principale, &lt;em&gt;&lt;a href=&quot;https://www.persee.fr/doc/phlou_0035-3841_1984_num_82_56_6315&quot;  title=&quot;le problème de la logique pure par persée&quot;&gt;La Logique de Husserl : &lt;/a&gt;  étude sur Logique formelle et Logique transcendantale&lt;/em&gt; (1957), est une analyse rigoureuse et pénétrante de la philosophie logique de Husserl, en particulier de la distinction entre logique formelle et logique transcendantale. Cette œuvre constitue une contribution importante à la réception française de la phénoménologie husserlienne et à la compréhension des rapports entre logique formelle et constitution transcendantale du sens. &lt;/p&gt; &lt;p&gt; Elle publia également des travaux sur la temporalité, notamment &lt;em&gt;Une étude sur la phénoménologie du temps de Husserl&lt;/em&gt; et contribua à faire connaître en France des aspects moins explorés de la phénoménologie, en particulier la théorie husserlienne de la conscience intime du temps. Professeur engagée et pédagogue de talent, elle forma plusieurs générations d'étudiants à la rigueur phénoménologique. Son œuvre illustre la richesse et la profondeur de la réception française de la phénoménologie husserlienne dans la seconde moitié du XXe siècle. &lt;/p&gt;" r:id="rId57"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I97" display="https://www.laphilo.fr/photo/sbachelard.webp" r:id="rId58"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E98" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Jules_Vuillemin&quot;  title=&quot; Wikipedia&quot;&gt;Jules VUILLEMIN&lt;/a&gt;  était un philosophe français qui  s'est distingué par son travail en  &lt;a href=&quot;https://hal.science/hal-04409311v1/document&quot; title=&quot;Jules Vuillemin, philosdophie analytique contrarié par hal&quot;&gt;philosophie analytique &lt;/a&gt;, en épistémologie et en histoire de la philosophie.  Il diffuse en France les idées de Bertrand Russell, Rudolf Carnap et Willard Van Orman Quine, influençant des penseurs comme Jacques Bouveresse. Ses débuts touchent à  &lt;a href=&quot;https://lafrancebyzantine.blogspot.com/2016/09/jules-vuillemin-t-il-ete-existentialiste.html&quot;  title=&quot;Jules Vuillemin at'il été existantialiste? par lafrancebyzantine&quot;&gt;l'existentialisme &lt;/a&gt; et au marxisme, mais il évolue vers un rationalisme rigoureux, rejetant les excès de Sartre ou Heidegger. &lt;/p&gt; &lt;p&gt; Ses œuvres majeures : - &quot;Nécessité ou contingence&quot; paru en 1984, qui analyse les systèmes philosophiques par une approche logique et historique, et &quot;La philosophie de l'algèbre&quot; paru en 1962 ou il explore la nécessité, la contingence, la logique et les sciences, insistant sur la cohérence interne des systèmes selon l'héritage de Martial Gueroult. Épistémologue de premier plan avec Gilles Gaston Granger et René Thom, il défend une philosophie attentive aux mathématiques et à la physique. &lt;/p&gt; &lt;p&gt; Il s'intéresse à Kant, Descartes, la liberté et la métaphysique de la nature, tout en critiquant les réductions existentialistes au profit d'une raison objective. Ses archives sont conservées au Laboratoire de Philosophie et d'Histoire des Sciences à Nancy. Auteur de plus de vingt livres, il reste une figure de la rigueur philosophique française. &lt;/p&gt;" r:id="rId59"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H101" display="https://www.laphilo.fr/pho/emorin-mini.webp" r:id="rId60"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E104" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Ren%C3%A9_Girard&quot; title=&quot; Wikipedia&quot;&gt;René GIRARD&lt;/a&gt; était un philosophe, anthropologue et critique littéraire français dont la pensée, souvent qualifiée de &quot;théorie mimétique&quot;, repose sur des concepts clés interdépendants qui expliquent la nature du désir humain, de la violence et du sacré. &lt;/p&gt; &lt;p&gt;Nous ne désirons pas intrinsèquement des objets ou des personnes, mais nous désirons ce que les autres désirent. Notre  &lt;a href=&quot;https://www.youtube.com/watch?v=9tn7RVVD_bA&quot; title=&quot;Le désir mimétique par le Precepteur&quot;&gt;désir est &quot;triangulaire&quot; &lt;/a&gt; : il y a un sujet (celui qui désire), un objet, et un modèle (celui dont le désir influence le sujet). Voici les 3 points clés : &lt;/p&gt; &lt;p&gt;- Le modèle comme médiateur : Le modèle n'est pas simplement une personne qui possède l'objet désiré, mais celui qui nous le révèle comme désirable. &lt;/p&gt; &lt;p&gt; - &lt;a href=&quot;https://www.youtube.com/watch?v=7scJjspwo9M&quot; title=&quot;La rivalité mimétique par le Precepteur&quot;&gt;La rivalité mimétique &lt;/a&gt; : Lorsque plusieurs personnes désirent le même objet, une rivalité mimétique émerge et elle peut devenir intense et se substituer à l'objet initial. &lt;/p&gt; &lt;p&gt; - Le désir métaphysique : Il distingue le désir des objets matériels du désir d'être, plus profond car il porte sur quelque chose d'insaisissable. &lt;/p&gt; &lt;p&gt; Dans son ouvrages &quot;Mensonge romantique et vérité romanesque&quot;, il montre comment les grands romanciers ont intuitivement compris la nature mimétique du désir et les illusions &quot;romantiques&quot; qui le masquent. &lt;/p&gt; &lt;p&gt; Selon lui, les sociétés humaines ont développé un mécanisme archaïque pour résoudre ces crises mimétiques : le mécanisme du &lt;a href=&quot;https://www.youtube.com/watch?v=QYTKoHPrKxI&quot; title=&quot; La fabrique du bouc émissaire par le Parole de Philosophe&quot;&gt;bouc émissaire&lt;/a&gt; dont voici les points clés : &lt;/p&gt; &lt;p&gt; - La désignation d'une victime : Au point culminant de la crise, l'attention de la communauté se focalise sur un individu ou un groupe particulier, accusé d'être la cause du désordre. &lt;/p&gt; &lt;p&gt; - L'unanimité contre la victime :  &lt;a href=&quot;https://www.dailymotion.com/video/xv8mim&quot;  title=&quot; René Girard, la violence et le sacré par le Parole de mySkreen&quot;&gt;La violence mimétique&lt;/a&gt;, initialement diffuse, se canalise et se concentre sur ce bouc émissaire. L'expulsion ou la mort de la victime rétablit temporairement la paix. &lt;/p&gt; &lt;p&gt; - La sacralisation de la victime : après avoir été la source du mal, elle est souvent sacralisée. On lui attribue un pouvoir extraordinaire, capable à la fois de provoquer la crise et de la résoudre. &lt;/p&gt; &lt;p&gt; - Le rite et le mythe : Les rites sacrificiels et les mythes sont des tentatives de reproduire et de commémorer le meurtre fondateur du bouc émissaire. &lt;/p&gt; &lt;p&gt;Il reste une figure intellectuelle majeure, dont les idées continuent d'inspirer et de provoquer la réflexion sur la nature humaine, la culture et la religion. &lt;/p&gt; &lt;audio controls title=&quot;René Girard, des choses cachées depuis la fondation du monde&quot; par France Culture&quot;&gt; &lt;source src=&quot;https://media.radiofrance-podcast.net/podcast09/13915-24.12.2023-ITEMA_23566825-2023C3372E0859-21.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt;&lt;/audio&gt;  " r:id="rId61"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E105" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Jean-Claude_Margolin&quot;  title=&quot; Wikipedia&quot;&gt;Jean-Claude MARGOLIN&lt;/a&gt; était un philosophe et humaniste français, spécialiste reconnu de la pensée de la Renaissance et notamment d'Érasme de Rotterdam. Agrégé de philosophie et docteur ès lettres, il fut directeur de recherches au CNRS et l'un des fondateurs du Centre d'études supérieures de la Renaissance à Tours. Son œuvre immense, qui combine érudition philologique et analyse philosophique, constitue une contribution majeure à la connaissance de l'humanisme de la Renaissance. &lt;/p&gt; &lt;p&gt; Ses travaux sur Érasme — dont une biographie de référence, &lt;em&gt;&lt;a href=&quot;https://www.persee.fr/doc/rhren_0181-6799_1995_num_40_1_2825&quot; title=&quot;jean claude Margolin Erasme precepteur par Persée &quot;&gt;Érasme par lui-même&lt;/a&gt; &lt;/em&gt; (1965, réédité plusieurs fois), et de nombreuses éditions critiques et traductions d'œuvres érasmiennes — font de lui l'un des plus grands érasmistes du XXe siècle. Il contribua à montrer la cohérence et la profondeur de la pensée d'Érasme, souvent réduite à un simple « humanisme » de bon sens, en soulignant la rigueur de sa théologie chrétienne, la finesse de son anthropologie et la complexité de son rapport à la Réforme. &lt;/p&gt; &lt;p&gt; Il s'intéressa à l'ensemble de la culture philosophique et littéraire de la Renaissance : Rabelais, Montaigne, Vives, Thomas More, et aux grandes questions de cette époque comme la définition de l'humanisme, les rapports entre foi et raison, l'éducation et la rhétorique. Sa direction de la revue &lt;em&gt;&lt;a href=&quot;https://www.persee.fr/doc/rhren_1771-1347_2013_num_76_1_3288&quot; title=&quot;jean claude Margolin humaniste par Persée &quot;&gt;Bibliothèque d'Humanisme &lt;/a&gt; et Renaissance&lt;/em&gt; et ses nombreuses contributions collectives firent de lui un animateur central de la recherche internationale sur la Renaissance. Son œuvre témoigne d'une conception exigeante de l'histoire de la philosophie comme restitution vivante d'une pensée dans toute sa richesse. &lt;/p&gt;  &lt;audio controls title=La folie Erasme par France Culture&quot;&gt; &lt;source src=&quot;https://media.radiofrance-podcast.net/podcast09/10467-15.01.2010-ITEMA_20211948-2010C12410E0018-NET_6E4A59B9-E10B-4E2F-A507-FFDDA95137E9_FC-21.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt;&lt;/audio&gt; " r:id="rId62"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E108" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Gilles_Deleuze&quot; title=&quot; Wikipedia&quot;&gt;Gilles DELEUZE&lt;/a&gt; était un philosophe français qui a profondément marqué la pensée contemporaine dans une  &lt;a href=&quot;http://sos.philosophie.free.fr/deleuze.php&quot; style=&quot;color:#88A1E9&quot; title=&quot; Gilles Deleuze  par SOS philo&quot;&gt;critique radicale&lt;/a&gt;oeuvre foisonnante et complexe.  Au cœur de sa philosophie se trouve une  &lt;a href=&quot;https://www.youtube.com/watch?v=4ybvyj_Pk7M&quot; title=&quot; Gilles Deleuze : l'art et les sociétés de contrôle par lINTELLECT FOCUS&quot;&gt;critique radicale&lt;/a&gt; de la pensée traditionnelle occidentale, qu'il accuse d'être dominée par une logique de la représentation, de l'identité et de la négation. &lt;/p&gt; &lt;p&gt; Il cherche à penser la différence en elle-même qui n'est pas secondaire ou dérivée, mais originaire.  Le monde n'est pas constitué d'entités fixes et identiques qui entreraient ensuite en relation, mais d'un flux incessant de différences, de variations et de devenirs. Il conçoit plutôt la pensée comme une force créatrice qui produit des concepts pour appréhender et transformer le réel qui n'est pas statique, mais un processus continu de transformation, d'hybridation et de métamorphose. Ses oeuvres principales sont : &lt;/p&gt; &lt;p&gt; - &lt;a href=&quot;https://www.youtube.com/watch?v=ia0FpHbHa_U&quot;  title=&quot; Différence et répétition de Gilles Deleuze (French Audiobook/Livre audio) 1 Avant propos par Chad A Haag Philosophy Channel&quot;&gt;&quot;Différence et Répétition&quot;&lt;/a&gt; : Oeuvre métaphysique majeure, où il développe sa pensée de la différence et critique la conception traditionnelle de la répétition comme reproduction de l'identique. &lt;/p&gt; &#10;&lt;p&gt; - &quot;Logique du sens&quot; : Une exploration des paradoxes du langage et du sens à travers une lecture originale de Lewis Carroll et des stoïciens. &lt;/p&gt; &#10;&lt;p&gt; - &quot;Qu'est-ce que la philosophie ?&quot; (avec Félix Guattari) : Une réflexion sur la nature de la philosophie comme création de concepts, distincte de la science et de l'art. &lt;/p&gt; &lt;p&gt;  Sa rencontre avec Felix Guattari donne naissance à 2 ouvrages majeurs :&lt;a href=&quot;https://www.youtube.com/watch?v=JQE4_2ti_10&amp;t=78s&quot; title=&quot; La pensée politique de Deleuze et Guattari - Partie 1 / L'anti-Oedipe par Politikon&quot;&gt;&quot; L'Anti-Œdipe &quot;&lt;/a&gt;  : Critique radicale de la psychanalyse et une exploration du désir comme force révolutionnaire et &lt;a href=&quot;https://www.youtube.com/watch?v=E01RyGu3Zac&quot; title=&quot;La pensée politique de Deleuze et Guattari - Partie 2 / Mille Plateaux par Politikon&quot;&gt;&quot; Mille Plateaux &quot;&lt;/a&gt;   : Une œuvre foisonnante qui explore une multitude de thèmes (le territoire, le devenir ) à travers le  &lt;a href=&quot;https://www.youtube.com/watch?v=RQ2rJWwXilw&quot; title=&quot;The Rhizome - A Thousand Plateaus, Deleuze and Guattari par Then &amp; Now&quot;&gt;concept de Rhizome&lt;/a&gt;. &lt;/p&gt; &lt;p&gt; Il  est un philosophe majeur qui a profondément transformé notre manière de  &lt;a href=&quot;https://diacritik.com/category/deleuze/&quot; title=&quot; Deleuze par Diacritik&quot;&gt;penser la différence&lt;/a&gt;, la multiplicité, le devenir et la créativité. &lt;/p&gt; &lt;audio controls title=&quot;Gilles Deleuze, notre contemporain&quot; par France Culture&quot;&gt; &lt;source src=&quot;https://media.radiofrance-podcast.net/podcast09/11189-19.11.2012-ITEMA_20421487-2012C15000E0183-ITE_00054426_RSCE-21.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt;&lt;/audio&gt; " r:id="rId63"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E110" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Fran%C3%A7ois_Wahl&quot;  title=&quot; Wikipedia&quot;&gt;François WAHL&lt;/a&gt; était un philosophe et éditeur français, figure centrale de la vie intellectuelle française de la fin des années 1950 au début des années 1990, surtout connu pour avoir promu le structuralisme et la psychanalyse aux Éditions du Seuil. l a régné pendant trente ans sur le domaine des sciences humaines et la littérature italienne au Seuil, publiant Jacques Lacan, Françoise Dolto, Paul Ricœur, Roland Barthes, Philippe Sollers, Alain Badiou, Jean-Cla Milner, ainsi que des auteurs italiens comme Carlo Emilio Gadda et Italo Calvino. Il est décrit comme un « structuraliste dans l’âme », construisant son activité éditoriale comme une structure où chaque choix (acceptations, refus, retraductions) faisait système, appliquant la doctrine structuraliste à son métier d’éditeur. &lt;/p&gt; &lt;p&gt; Il est l’auteur de trois ouvrages majeurs :  &lt;a href=&quot;https://philosophie.ac-normandie.fr/spip.php?article148&quot; title=&quot;qu’est ce que la philosophie par françois Wahl &quot;&gt;Qu’est-ce que le structuralisme ? &lt;/a&gt; , Philosophie (1973), Introduction au discours du tableau (1996) et Le Perçu (2007). Dans Introduction au discours du tableau, il étudie les œuvres de Poussin, Memling ou Bellini pour montrer que le « visible » apparaît sous deux espèces : le paysage et le tableau, articulant ainsi esthétique et théorie du signe. Le Perçu propose une exploration critique des phénoménologies du XXᵉ siècle, en mobilisant les concepts de discours, sujet, désir et énoncé pour formaliser une analyse du « fait esthétique » . &lt;/p&gt; &lt;p&gt; La ligne directrice de sa pensée peut se résumer à un repérage du concept de sujet dans la philosophie contemporaine et son introduction dans le champ de l’esthétique. Il a écrit de nombreux articles discutant les œuvres d’auteurs comme Badiou, Bataille, Barthes, Foucault ou Lacan, et son dernier grand livre, La dissidence du sujet, rassemble ces réflexions sur le sujet, le désir et le discours dans la philosophie et l’art. &lt;/p&gt; &lt;audio controls title=&quot;les fluides d’Aristote /hommage à f Wahl par France Culture&quot;&gt; &lt;source src=&quot;https://media.radiofrance-podcast.net/podcast09/12003-17.09.2014-ITEMA_20670365-2014C18006S0260-21.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt;&lt;/audio&gt;  " r:id="rId64"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H110" display="https://www.laphilo.fr/pho/fwahl-mini.webp" r:id="rId65"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I110" display="https://www.laphilo.fr/photo/fwahl.webp" r:id="rId66"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H112" display="https://www.laphilo.fr/pho/jmeyendorff-mini.webp" r:id="rId67"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H114" display="https://www.laphilo.fr/pho/hdamisch-mini.webp" r:id="rId68"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E115" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Bernard_Bourgeois&quot;  title=&quot; Wikipedia&quot;&gt;Bernard BOURGEOIS&lt;/a&gt; était un philosophes français connu comme le grand traducteur et interprète de Hegel en langue française. Ancien élève de l’École normale supérieure, agrégé de philosophie, il a enseigné à Lyon puis à Paris I–Sorbonne, avant d’être élu à l’Académie des sciences morales et politiques, qu’il a présidée en 2014. &lt;/p&gt; &lt;p&gt; Sa philosophie se définit d’abord par un  &lt;a href=&quot;https://academiesciencesmoralesetpolitiques.fr/membres-titulaires/section-i-philosophie-2/bernard-bourgeois/&quot; title=&quot;bernard bourgeois carrière et travaux académique par académie des sciences&quot;&gt;travail historique et philologique &lt;/a&gt;  monumental sur l’idéalisme allemand, de Kant à Marx, avec un centre de gravité hégélien. Il a traduit et annoté des milliers de pages de Hegel (Phénoménologie de l’esprit, Encyclopédie des sciences philosophiques, Science de la logique, écrits de droit naturel, textes pédagogiques), en s’efforçant de restituer la rigueur conceptuelle et la cohérence systématique de la pensée hégélienne. &lt;/p&gt; &lt;p&gt; Au-delà de la traduction, il défend une lecture de Hegel comme philosophe de la liberté et de la raison dans l’histoire. Pour lui, Hegel ne célèbre pas un destin aveugle ni une fin dogmatique de l’histoire, mais pense l’historicité de l’Esprit comme déploiement de formes de rationalité et d’institutions où la liberté devient concrète (droit, État, vie éthique). Cette orientation se retrouve dans ses communications à l’Académie, par exemple sur &lt;a href=&quot;https://www.youtube.com/watch?v=YRErwGZWBqc/&quot; title=&quot;bernard bourgeois , hegel et le droit par pkpdlm&quot;&gt;« Hegel et le droit » &lt;/a&gt;  ou « La fin de l’histoire selon Hegel », où il montre comment la philosophie hégélienne éclaire les problèmes politiques et juridiques modernes. &lt;/p&gt; &lt;p&gt; Sa propre philosophie n’est pas un système indépendant de type hégélien, mais une méditation exigeante sur les conditions de la rationalité spéculative et sur la manière dont la philosophie peut habiter son époque. Il insiste sur la nécessité de « relire constamment » Hegel plutôt que de le lire une fois pour toutes, parce que la pensée spéculative demande un travail continu de reprise et d’approfondissement. En ce sens, sa philosophie est une pratique de la raison qui se forme au contact des textes, des concepts et des problèmes que Hegel a portés à leur plus haute expression. &lt;/p&gt; &#10;&#10;" r:id="rId69"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H115" display="https://www.laphilo.fr/pho/bbourgeois-mini.webp" r:id="rId70"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H116" display="https://www.laphilo.fr/pho/baudrillard-mini.webp" r:id="rId71"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E119" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/F%C3%A9lix_Guattari&quot;  title=&quot; Wikipedia&quot;&gt;Félix GUATTARI&lt;/a&gt; était un philosophe, psychanalyste et  &lt;a href=&quot;https://maitron.fr/guattari-felix/&quot; title=&quot; BOURDIEU - L'habitus par Cyrus North&quot;&gt;militant intellectuel &lt;/a&gt; français connu pour sa collaboration avec Gilles Deleuze, mais il a aussi développé une pensée personnelle très originale. Sa philosophie se situe surtout dans le courant du post-structuralisme et de la pensée critique contemporaine. Elle s’oppose aux idées trop fixes de sujet, d’identité ou de structure, et insiste au contraire sur les processus, les relations et les transformations. &lt;/p&gt; &lt;p&gt; Un de ses apports centraux est la notion de subjectivité comme quelque chose de produit par des agencements multiples. Pour lui, la subjectivité n’est pas seulement intérieure ou individuelle : elle se fabrique aussi dans les institutions, les médias, la politique, la famille et les environnements techniques. &lt;/p&gt; &lt;p&gt; Il a aussi travaillé sur la psychanalyse, en critiquant ce qu’il voyait comme ses formes trop normatives, notamment autour du complexe d’Œdipe. Dans &lt;a href=&quot;https://enseignants.lumni.fr/fiche-media/00000001135/l-anti-oedipe-de-gilles-deleuze-et-felix-guattari.html&quot; title=&quot; anti-oedipe  deleuze et guattari par enseignants lumni&quot;&gt;L’Anti-Œdipe &lt;/a&gt; et Mille Plateaux, il défend avec Deleuze une pensée des flux, des désirs, des « rhizomes » et des lignes de fuite, contre les modèles hiérarchiques et fermés. &lt;/p&gt; &lt;p&gt; On peut donc le placer à la croisée de plusieurs branches : philosophie politique, philosophie de la subjectivité, psychanalyse critique et théorie sociale. Sa pensée est souvent associée à des idées comme l’écologie mentale, la créativité collective et la transformation des formes de vie. &lt;/p&gt;  &#10; &lt;audio controls title=&quot;la fin du politique par France Culture&quot;&gt; &lt;source src=&quot;https://media.radiofrance-podcast.net/podcast09/13915-16.03.2022-ITEMA_22964487-2022C3372E0135-NET_MFC_B9CCC943-E790-4029-A9C3-4076BC2B331E-21-443183d5ed7da523138c0280fb088809.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt;&lt;/audio&gt;  " r:id="rId72"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H119" display="https://www.laphilo.fr/pho/fguattari-mini.webp" r:id="rId73"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H120" display="https://www.laphilo.fr/pho/lebrun-mini.webp" r:id="rId74"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H121" display="https://www.laphilo.fr/pho/serres-mini.webp" r:id="rId75"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H122" display="https://www.laphilo.fr/pho/granel-mini.webp" r:id="rId76"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E123" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Raymond_Boudon&quot;  title=&quot; Wikipedia&quot;&gt;Raymond BOUDON&lt;/a&gt; était un sociologue et philosophe social français, l'une des figures les plus importantes de la sociologie française de la seconde moitié du XXe siècle et un ardent défenseur du libéralisme intellectuel et de la rationalité. Son œuvre,  &lt;a href=&quot;https://www.quesaisje.com/raymond-boudon&quot;  title=&quot; Boudon raymond par que sais je ?&quot;&gt;immense et plurielle, &lt;/a&gt; porte à la fois sur la méthodologie des sciences sociales, la théorie de l'action et la philosophie sociale. &lt;/p&gt; &lt;p&gt; Sa contribution la plus connue est l'élaboration d'une sociologie de l'individualisme méthodologique. Dans &lt;em&gt;L'Inégalité des chances&lt;/em&gt; (1973) et surtout dans &lt;em&gt;La Logique du social&lt;/em&gt; (1979) et &lt;em&gt;L'Art de se persuader des idées douteuses, fragiles ou fausses&lt;/em&gt; (1990), il défend l'idée que les faits sociaux s'expliquent par les actions et les croyances des individus, et que ces actions sont généralement rationnelles au sens large, c'est-à-dire fondées sur de « bonnes raisons » qui ne se réduisent pas  &lt;a href=&quot;https://www.youtube.com/watch?v=tMmKcRuoxp4&quot;  title=&quot; boudon l’inégalité des chances par La Sociothèque&quot;&gt;aux seuls intérêts matériels.&lt;/a&gt;  Cette position s'oppose à la fois au structuralisme durkheimien et au réductionnisme économique. &lt;/p&gt; &lt;p&gt; Dans ses dernières œuvres — &lt;em&gt;Pourquoi les intellectuels n'aiment pas le libéralisme&lt;/em&gt; (2004), &lt;em&gt;La Rationalité&lt;/em&gt; (2009) — il s'engagea dans une défense résolue du libéralisme politique et intellectuel contre ce qu'il percevait comme les dérives relativistes et collectivistes de la pensée française contemporaine. Sociologue rigoureux et polémiste redoutable, il fut l'un des penseurs français les plus lus à l'étranger, notamment aux États-Unis et en Allemagne, où son travail sur la rationalité et les croyances sociales est largement reconnu. &lt;/p&gt;     &lt;audio controls title=&quot;Raymond Boudon par France Culture&quot;&gt; &lt;source src=&quot;https://media.radiofrance-podcast.net/podcast09/12003-15.01.2014-ITEMA_20575231-2014C18006S0015-21.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt;&lt;/audio&gt;  " r:id="rId77"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H125" display="https://www.laphilo.fr/pho/fedier-mini.webp" r:id="rId78"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H126" display="https://www.laphilo.fr/pho/mwittig-mini.webp" r:id="rId79"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E127" display=" &lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Michel_Hulin&quot;  title=&quot; Wikipedia&quot;&gt;Michel HULIN&lt;/a&gt; était un philosophe français récemment décédé, grand spécialiste de la &lt;a href=&quot;https://www.youtube.com/watch?v=tJFic9y58Sc&quot; title=&quot; Aperçu de l’hindouisme avec Michel Hulin par Resonances &quot;&gt;philosophie indienne &lt;/a&gt; et de la comparaison entre pensée européenne et pensée asiatique, notamment de l’Advaïta Vedānta, le courant « non‑dualiste » du vedānta. Longtemps professeur de philosophie indienne et comparée à l’université Paris‑Sorbonne, il a joué un rôle central dans la diffusion en France des grandes écoles de pensée de l’Inde. Sa carrière s’est accompagnée d’un important travail de traduction du sanskrit et de vulgarisation, accessible à un public non spécialiste. &lt;/p&gt; &lt;p&gt; Ses recherches portent d’une part sur  &lt;a href=&quot;https://www.youtube.com/watch?v=kaJP8yDwHeY&quot; title=&quot; For intérieur par Resonnances &quot;&gt;la pensée indienne classique &lt;/a&gt;  (notion d’ahamkāra, textes vedāntins et shivaïtes d’inspiration tantrique), d’autre part sur les questions épistémologiques et métaphysiques que soulève la rencontre entre les traditions européennes et asiatiques. Dans sa thèse, Le Principe de l’ego dans la pensée indienne classique, il analyse la notion de « faux moi » et montre comment elle éclaire notre expérience ordinaire de la conscience. Il s’intéresse également à la question du temps, de l’éternité et des expériences dites mystiques, qu’il relie à des vécus très concrets. &lt;/p&gt; &lt;p&gt; Dans des ouvrages comme La Face cachée du temps, La Mystique sauvage, Hegel et l’Orient, Shankara et la non‑dualité ou encore l’anthologie L’Inde des sages, il  conjugue une érudition très précise et un style volontairement clair. Il montre comment des interrogations métaphysiques complexes – sur le moi, le temps, l’au‑delà ou l’expérience spirituelle – touchent directement la vie intérieure de chacun. Par son enseignement et ses livres, il a contribué à installer durablement en France une philosophie comparée attentive au dialogue entre Europe et Inde. &lt;p&gt; &lt;/p&gt;&lt;audio controls title=&quot;  Philosophies indiennes (1/4) : Upanishads, les textes fondateurs ?  par France Culture&quot;&gt; &lt;source src=&quot;https://media.radiofrance-podcast.net/podcast09/10467-16.12.2013-ITEMA_20562153-2013C12410S0350-NET_FC_A092AF0E-5BC1-49EE-A72F-E62BB6A2A8B1-21.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt;&lt;/audio&gt;  &lt;p&gt;  &lt;/p&gt;&#10;" r:id="rId80"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H127" display="https://www.laphilo.fr/pho/mhulin-mini.webp" r:id="rId81"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H129" display="https://www.laphilo.fr/pho/jfmarquet-mini.webp" r:id="rId82"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E130" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Cl%C3%A9ment_Rosset&quot; title=&quot; Wikipedia&quot;&gt;Clément ROSSET&lt;/a&gt; était un philosophe français connu pour sa pensée radicale et son style d'écriture d'une grande clarté. Son œuvre est principalement centrée sur le concept du  &lt;a href=&quot;https://www.youtube.com/watch?v=I50Jbj6uQEU&quot; title=&quot;Clément Rosset : la réalité ne convient pas ! par Kosmos&quot;&gt;&quot;réel&quot;&lt;/a&gt;  et l'incapacité ou la difficulté de l'homme à l'accepter dans sa singularité et souvent sa cruauté. Voici les points essentiels concernant sa philosophie : &lt;/p&gt; &lt;p&gt; - &lt;a href=&quot;https://www.youtube.com/watch?v=8m_kXVBdtwg&quot;  title=&quot; Le réel et son double, Clément Rosset, 2.2 avant-propos par Thibault BELZACQ&quot;&gt;Le Réel sans double&lt;/a&gt; : Son idée maîtresse est que le réel est unique, singulier et dépourvu de tout &quot;double&quot;. Il n'y a pas d'arrière-monde, pas de sens caché, pas de consolation ou d'illusion qui puisse atténuer sa nature brute. Le réel est simplement ce qui est, dans son évidence la plus nue. &lt;/p&gt; &lt;p&gt; - Le Refus du double et de l'illusion : Une grande partie de son travail consiste à traquer les différentes formes d'illusions et de doubles que l'humanité crée pour  &lt;a href=&quot;https://philitt.fr/2023/09/12/clement-rosset-tout-est-sans-raison/&quot;  title=&quot;Clément Rosset : tout est sans raison par Phillitt&quot;&gt;échapper à la confrontation&lt;/a&gt; directe avec le réel. Ces doubles peuvent être d'ordre métaphysique, moral, psychologique, ou même esthétique.&lt;/p&gt; &lt;p&gt; - &lt;a href=&quot;https://www.youtube.com/watch?v=JDcudFE_uBQ&quot;  title=&quot;Entretien avec Pierre Dumayet (1961) par Archives&quot;&gt;Philosophie tragique&lt;/a&gt; et Joie : Bien que sa pensée puisse sembler sombre en insistant sur la cruauté et l'absurdité du réel, il développe une philosophie que l'on qualifie souvent de &quot;tragique&quot; au sens nietzschéen du terme. Il ne s'agit pas de désespoir, mais plutôt de l'affirmation de la vie et du réel tels qu'ils sont, y compris dans leurs aspects les plus difficiles. &lt;/p&gt; &lt;p&gt; Il est également remarquable par son style d'écriture. Loin du jargon philosophique abscons, il privilégie une langue simple, directe et percutante. Cette clarté formelle est au service de la clarté de sa pensée, cherchant à énoncer le réel avec le moins d'interférences possible. Son œuvre, bien que parfois restée en marge des courants universitaires dominants, a marqué par sa radicalité, sa lucidité et sa défense d'une confrontation sans fard avec le réel.  &lt;/p&gt; &lt;audio controls title=&quot;Clément Rosset par France Culture&quot;&gt; &lt;source src=&quot;https://media.radiofrance-podcast.net/podcast09/10080-20.12.2013-ITEMA_20564152-2013C3403E0215-21.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt;&lt;/audio&gt;  " r:id="rId83"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H130" display="https://www.laphilo.fr/pho/rosset-mini.webp" r:id="rId84"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E131" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Jacques_Bouveresse&quot;  title=&quot; Wikipedia&quot;&gt;Jacques BOUVERESSE&lt;/a&gt; était un philosophe français du courant analytique, connu pour son rationalisme exigeant, son &lt;a href=&quot;https://www.youtube.com/watch?v=mfGM00nmj20&quot;  title=&quot; Wittgenstein et l'intériorité 一 Jacques Bouveresse par Andrea Cirla &quot;&gt;travail sur Wittgenstein &lt;/a&gt; et sa critique des dérives du milieu intellectuel français. Il a largement contribué à introduire et stabiliser en France une philosophie soucieuse de vérité, de clarté et d’argumentation rigoureuse. &lt;/p&gt; &lt;p&gt; Ses domaines privilégiés sont la philosophie de la connaissance, des sciences, des mathématiques, de la logique, du langage, ainsi qu’une philosophie de la culture attentive à la littérature et à la critique sociale.  Il se réclame du rationalisme des Lumières et s’inspire fortement de la philosophie analytique, du Cercle de Vienne, de Frege, de Gödel et de la tradition d’Europe centrale. Wittgenstein, qu’il contribue à faire connaître en France, est l’une de ses références centrales. &lt;/p&gt; &lt;p&gt; Il défend une position rationaliste dont le prolongement éthique est ce qu’il appelle la  &lt;a href=&quot;https://www.persee.fr/doc/lgge_0458-726x_1971_num_6_21_2079&quot; title=&quot;Langage ordinaire et philosophie par Persée &quot;&gt;&quot;modestie intellectuelle&quot; &lt;/a&gt; : ne pas exagérer ce que la philosophie peut faire, refuser le pathos et le prestige facile. Il combat le relativisme, l’historicisme radical et les remises en cause globales de la notion de vérité, notamment chez certains auteurs français, tout en reconnaissant par ailleurs leur importance. &lt;/p&gt; &lt;p&gt; Sa grande thèse, &quot;Le Mythe de l’intériorité&quot;, porte sur Wittgenstein, le langage privé, l’expérience et la signification, et a joué un rôle clé dans la réception française de Wittgenstein. Il consacre de nombreux travaux à Robert Musil et Karl Kraus, qu’il lit comme des alliés dans un combat pour l’exactitude, la critique de la bêtise et des illusions de la culture moderne. &lt;/p&gt;  &lt;audio controls title=&quot;Jacques Bouveresse, à la recherche de la clarté par France Culture&quot;&gt; &lt;source src=&quot;https://media.radiofrance-podcast.net/podcast09/10351-11.05.2021-ITEMA_23961779-2000C3500E0287-21.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt;" r:id="rId85"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H131" display="https://www.laphilo.fr/pho/bouveresse-mini.webp" r:id="rId86"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E132" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Jean-Luc_Nancy&quot;  title=&quot; Wikipedia&quot;&gt;Jean-Luc NANCY&lt;/a&gt; était un philosophe français, agrégé de philosophie, il fut professeur à l'Université de Strasbourg jusqu'à sa retraite. Sa pensée, en dialogue constant avec Heidegger, Derrida et Lacoue-Labarthe — avec lequel il collabora étroitement — porte sur le « sens du monde », la communauté, le corps et le toucher. &lt;/p&gt; &lt;p&gt; Son œuvre est marquée par le questionnement du « with » (avec), du « being-with » heideggerien. Dans &lt;em&gt;La Communauté désoeuvrée&lt;/em&gt; (1986), il développe une pensée de la communauté qui refuse toute forme d'immanentisme ou de fusion : la communauté véritable n'est pas une substance commune, mais  &lt;a href=&quot;https://www.youtube.com/watch?v=fZK6pEAPxEw&quot;  title=&quot;jean luc Nancy par Institut Humanités &quot;&gt;l'exposition partagée &lt;/a&gt; de la singularité de chacun. Cette réflexion, en dialogue critique avec Blanchot et Bataille, a eu un retentissement considérable dans les débats contemporains sur la politique, la communauté et l'identité. &lt;/p&gt; &lt;p&gt; Dans &lt;em&gt;Corpus&lt;/em&gt; (1992) et &lt;em&gt;Noli me tangere&lt;/em&gt; (2003), il explore  &lt;a href=&quot;https://www.youtube.com/watch?v=1kCExw6Wp9k&quot;  title=&quot;jean luc Nancy par Lacan TV &quot;&gt;la philosophie du corps &lt;/a&gt; et du toucher comme modes fondamentaux de l'être-au-monde. Son essai sur le sens — &lt;em&gt;Le Sens du monde&lt;/em&gt; (1993) — aborde la question de la possibilité du sens dans un monde déserté par les transcendances. &lt;em&gt;L'Intrus&lt;/em&gt; (2000), bref récit autobiographique sur sa transplantation cardiaque, mêle réflexion philosophique et expérience personnelle de la maladie et de l'altérité. Son œuvre, immense et diverse, témoigne d'une pensée vivante et rigoureuse toujours en dialogue avec la littérature, l'art et la politique. &lt;/p&gt;  &lt;audio controls title=&quot;Jean luc Nancy par France Culture&quot;&gt; &lt;source src=&quot;https://media.radiofrance-podcast.net/podcast09/11472-06.02.2011-ITEMA_20267545-2011C16153E0003-ITE_00040439_RSCE-21.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt;" r:id="rId87"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H132" display="https://www.laphilo.fr/pho/jlnancy-mini.webp" r:id="rId88"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E133" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Philippe_Lacoue-Labarthe&quot;  title=&quot; Wikipedia&quot;&gt;Philippe LACOUE-LABARTHE&lt;/a&gt; était un philosophe, critique littéraire, traducteur et théoricien français né à Tours et connu pour ses travaux sur la mimésis, le romantisme allemand, Hölderlin, Heidegger, Derrida et la relation entre esthétique et politique. Il a aussi beaucoup compté dans le milieu intellectuel de Strasbourg, où il a enseigné longtemps et travaillé avec Jean-Luc Nancy. &lt;/p&gt; &lt;p&gt; Son  &lt;a href=&quot;https://maitron.fr/lacoue-labarthe-philippe/&quot;  title=&quot; lacoue-labarthe par le maitron&quot;&gt;œuvre interroge &lt;/a&gt; la façon dont l’art, la philosophie et la politique s’entrecroisent, notamment à travers la notion de mimésis et la critique de l’“esthétisation du politique”. Il a aussi travaillé sur le romantisme allemand et sur la réception de Hölderlin, qu’il considérait comme une figure majeure. &lt;/p&gt; &lt;p&gt; Parmi les livres souvent cités, on trouve Le Titre de la lettre avec Jean-Luc Nancy, L’Absolu littéraire, L’Imitation des modernes, La Fiction du politique et Heidegger, la politique du poème. Il a également traduit plusieurs auteurs allemands majeurs, dont Heidegger, Hölderlin, Nietzsche, Benjamin et Celan. &lt;/p&gt; &lt;p&gt; Sa pensée tourne autour de trois idées principales : - La représentation n’est jamais transparente : ce que nous montrons, racontons ou jouons n’est jamais la réalité elle-même, mais une forme, un masque, une imitation. - La littérature et le théâtre sont essentiels pour comprendre la philosophie, parce qu’ils révèlent ce que les concepts cachent ou simplifient.popups. - Le lien entre esthétique et politique est dangereux : il a beaucoup réfléchi à la manière dont l’art, les mythes et les images peuvent servir le politique, y compris dans des formes fascisantes. &lt;/p&gt; &#10; &lt;audio controls title=&quot;les versions de philippe lacoue labarthe par France Culture&quot;&gt; &lt;source src=&quot;https://media.radiofrance-podcast.net/podcast09/16409-16.03.2007-ITEMA_20062386-2007C6409S0011-MEM_000036772_RF-21.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt;  " r:id="rId89"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H133" display="https://www.laphilo.fr/pho/pllabarthe-mini.webp" r:id="rId90"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H134" display="https://www.laphilo.fr/pho/fdelaporte-mini.webp" r:id="rId91"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H135" display="https://www.laphilo.fr/pho/lecourt-mini.webp" r:id="rId92"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E136" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Jean-Michel_Berthelot&quot;  title=&quot; Wikipedia&quot;&gt;Jean-Michel BERTHELOT&lt;/a&gt; était un philosophe et sociologue français spécialiste d'épistémologie des sciences sociales. Professeur à l'Université de Paris IV-Sorbonne et à l'Université du Québec à Montréal, il contribua de manière décisive à la réflexion philosophique sur les fondements et les méthodes des sciences humaines et sociales. Son œuvre joint la rigueur épistémologique à une large culture philosophique et sociologique. &lt;/p&gt; &lt;p&gt; Son ouvrage principal, &lt;em&gt; &lt;a href=&quot;https://www.persee.fr/doc/sotra_0038-0296_1992_num_34_3_2605_t1_0388_0000_3&quot;  title=&quot;l’intelligence du social par persée &quot;&gt; L'Intelligence du social&lt;/a&gt; &lt;/em&gt; (1990), est une analyse approfondie des schèmes d'intelligibilité que les sciences sociales utilisent pour rendre compte de la réalité sociale : le schème causal, le schème fonctionnel, le schème structural, le schème herméneutique et d'autres modes d'explication. Berthelot montre que chaque paradigme sociologique privilégie un mode d'intelligibilité particulier, ce qui permet de comprendre à la fois leurs apports spécifiques et leurs limites. Ce livre constitue l'une des contributions les plus claires et les plus systématiques à la philosophie des sciences sociales en langue française. &lt;/p&gt; &lt;p&gt; Dans &lt;em&gt;Epistémologie des sciences sociales&lt;/em&gt; (2001, ouvrage collectif qu'il dirigea), il offrit un panorama complet des questions épistémologiques fondamentales que posent les sciences humaines et sociales : la causalité, la compréhension, la mesure, la modélisation, la réflexivité et les rapports entre science et valeurs. Ses travaux contribuèrent à établir l'épistémologie des sciences sociales comme une discipline à part entière dans le paysage universitaire français, en dialogue constant avec la philosophie des sciences anglophones et continentale. &lt;/p&gt;" r:id="rId93"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H136" display="https://www.laphilo.fr/pho/jmberthelot-mini.webp" r:id="rId94"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E137" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Daniel_Bensa%C3%AFd&quot;  title=&quot; Wikipedia&quot;&gt;Daniel BENSAÏD&lt;/a&gt; était un philosophe français marxiste, l'un des intellectuels les plus importants de la gauche radicale française de son époque. Né à Paris dans une famille juive d'origine algérienne, il fut l'un des leaders de la révolte étudiante de mai 1968 à Paris-Nanterre aux côtés de Daniel Cohn-Bendit. Professeur de philosophie à l'Université Paris VIII-Saint-Denis, il fut membre dirigeant de la Ligue communiste révolutionnaire (LCR) et de son successeur le Nouveau Parti Anticapitaliste (NPA). &lt;/p&gt; &lt;p&gt; Sa pensée philosophique chercha à renouveler le marxisme en le débarrassant des &lt;a href=&quot;https://www.youtube.com/watch?v=uxBvxfRI2CE&quot;  title=&quot;la privatisation du monde par bibou11slalala &quot;&gt; simplifications téléologiques &lt;/a&gt; et en l'ouvrant à des problématiques nouvelles. Dans &lt;em&gt;Marx l'intempestif&lt;/em&gt; (1995), il défend un Marx débarrassé du déterminisme historique et de la philosophie du progrès, un Marx « intempestif » qui pense la politique comme art du possible et de l'impossible, en dialogue avec Blaise Pascal et Walter Benjamin. Ce livre renouvela profondément la  &lt;a href=&quot;https://www.youtube.com/watch?v=is8Ya038-Q4&quot;  title=&quot;l’héritage de Marx par socialtram &quot;&gt; lecture de Marx &lt;/a&gt; dans la gauche française. &lt;/p&gt; &lt;p&gt; Dans &lt;em&gt;Le Pari mélancolique&lt;/em&gt; (1997) et &lt;em&gt;Résistances&lt;/em&gt; (2001), il développe une philosophie de l'engagement politique nourrie par la mélancolie des défaites mais portée par une fidélité irréductible à l'émancipation. Sa réflexion sur les rapports entre philosophie et politique, entre utopie et stratégie, constitue l'une des contributions les plus originales à la pensée marxiste contemporaine. Polémiste redoutable et pédagogue exigeant, il laissa une empreinte profonde sur plusieurs générations de militants et d'intellectuels de gauche. &lt;/p&gt;  &lt;audio controls title=&quot;Daniel Bensaid  par France Culture&quot;&gt; &lt;source src=&quot;https://media.radiofrance-podcast.net/podcast09/10075-11.12.2006-ITEMA_20049670-2006C6608S0221-MEM_000033324_RF-21.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt; " r:id="rId95"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H137" display="https://www.laphilo.fr/pho/bensaid-mini.webp" r:id="rId96"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G138" display="&quot;Ce virus est là pour nous préparer au nouveau régime climatique&quot; par France Culture" r:id="rId97"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H138" display="https://www.laphilo.fr/pho/latour-mini.webp" r:id="rId98"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H139" display="https://www.laphilo.fr/pho/rdamien-mini.webp" r:id="rId99"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E140" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Catherine_Colliot-Th%C3%A9l%C3%A8ne&quot; title=&quot; Wikipedia&quot;&gt;Catherine COLLIOT-THELENE&lt;/a&gt; était une philosophe française  majeure de la philosophie politique contemporaine, spécialiste de Max Weber et penseuse des droits, de la démocratie et de la propriété dans un cadre cosmopolitique. Membre de l’Institut universitaire de France, elle est reconnue comme une référence internationale des études wébériennes. &lt;/p&gt; &lt;p&gt; Son travail se situe au croisement de la philosophie politique et des sciences sociales, avec trois pôles principaux :  &lt;a href=&quot;https://www.youtube.com/watch?v=krUYFtq9Jww&quot; title=&quot;Max Weber et la violence légitime de l’état par France Culture&quot;&gt;Max Weber, la démocratie et les droits, &lt;/a&gt;  la propriété et le cosmopolitisme.  Elle traduit et commente plusieurs textes de Weber, notamment Le Savant et le politique et Les Communautés, en montrant en détail ses concepts de rationalisation, de désenchantement et de domination. &lt;/p&gt; &lt;p&gt; À partir des années 2000, elle se concentre sur les droits subjectifs, leur articulation avec l’individualisme contemporain et la transformation des rapports entre pouvoirs politiques et économiques. Elle insiste sur la nécessité de penser la normativité (ce qui doit être) à partir d’une analyse précise des structures sociales réelles, d’où son dialogue constant avec le droit, l’histoire et la sociologie. &lt;/p&gt; &lt;p&gt; Dans &quot;La Démocratie sans “demos”  paru en 2011, elle remet en question l’identification classique entre &quot;peuple&quot; et &quot;démocratie&quot;. Elle critique la superposition entre souveraineté du peuple et souveraineté territoriale de l’État, qui conduit selon elle à des versions exclusives de la démocratie. &lt;a href=&quot;https://www.youtube.com/watch?v=ps2ixtEpgYI&quot; title=&quot;la democratie c’est le droit de resistance par Journal l’Humanitét&quot;&gt;Sa philosophie cherche &lt;/a&gt;  une démocratie fondée sur des droits universalisables et sur la participation de tous les sujets, plutôt que sur l’appartenance à une communauté nationale préconstituée. &lt;/p&gt; &lt;p&gt; Elle refuse la séparation entre théorie pure et monde social : pour elle, la philosophie politique doit dialoguer avec les sciences sociales pour produire une critique efficace des institutions et des inégalités. Elle a accompagné, sans posture militante classique mais avec une forte implication intellectuelle, les luttes pour les droits des femmes, des exclus et des étrangers, en cherchant à fournir des outils conceptuels pour penser l’égalité aujourd’hui. &lt;/p&gt; &#10; &lt;audio controls title=&quot;Les défis juridiques de la migration : existe-t-il un droit à la libre circulation ? par France Culture&quot;&gt; &lt;source src=&quot;https://media.radiofrance-podcast.net/podcast09/21447-09.02.2022-ITEMA_22927630-2022C27677S0040-21.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt;" r:id="rId100"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H140" display="https://www.laphilo.fr/pho/thelene-mini.webp" r:id="rId101"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H141" display="https://www.laphilo.fr/pho/bstiegler-mini.webp" r:id="rId102"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E142" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Bernard_Mabille_(philosophe)&quot;  style=&quot;color:#6A142A&quot;  title=&quot; Wikipedia&quot;&gt;Bernard MABILLE&lt;/a&gt; était un philosophe français spécialiste de dialectique et de philosophie hégélienne, ainsi que de métaphysique contemporaine. Agrégé de philosophie et professeur à l'Université Paris IV-Sorbonne, il fut l'un des meilleurs connaisseurs français de Hegel et contribua de manière significative au renouvellement des études hégéliennes en France dans les dernières décennies du XXe siècle. &lt;/p&gt; &lt;p&gt; Sa thèse principale, &lt;em&gt;Hegel : l'épreuve de la contingence&lt;/em&gt; (1999), est une lecture originale de la philosophie hégélienne à la lumière de la problématique de la contingence. Contre les lectures qui réduisent Hegel à un penseur du nécessaire et du rationnel, Mabille montre que la contingence est au cœur même du système hégélien et que la dialectique est précisément la méthode qui permet de penser le passage du contingent au nécessaire sans l'éliminer. Cette relecture contribua à ouvrir la philosophie hégélienne à des problématiques contemporaines. &lt;/p&gt; &lt;p&gt; Dans ses travaux sur la métaphysique et la dialectique, Mabille s'intéressa également aux rapports entre la philosophie hégélienne et la phénoménologie française, notamment Merleau-Ponty et Henry. Son enseignement à la Sorbonne forma plusieurs générations d'étudiants à la rigueur de la pensée dialectique. Sa disparition prématurée priva la philosophie française d'un penseur rigoureux dont l'œuvre, bien que de volume limité, témoigne d'une lecture profonde et originale de l'idéalisme allemand et de ses prolongements contemporains. &lt;/p&gt;" r:id="rId103"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H142" display="https://www.laphilo.fr/pho/bnabille-mini.webp" r:id="rId104"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H143" display="https://www.laphilo.fr/pho/adufourmantelle-mini.webp" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H51" display="https://www.laphilo.fr/pho/jchevalier-mini.webp" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E53" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Ren%C3%A9_Le_Senne&quot; title=&quot; Wikipedia&quot;&gt;René le SENNE&lt;/a&gt; était un philosophe français, cofondateur avec Louis Lavelle du mouvement dit de « La Philosophie de l'Esprit » ou « philosophie de la valeur », l'une des réponses spécifiquement françaises aux courants existentialistes et phénoménologiques qui se développaient en Europe dans la première moitié du XXe siècle. &lt;/p&gt; &lt;p&gt; Sa pensée s'organise autour du concept de valeur et d'obstacle. Dans son œuvre principale, &lt;em&gt;Obstacle et Valeur&lt;/em&gt; (1934), il développe &lt;a href=&quot;https://www.persee.fr/doc/phlou_0035-3841_1955_num_53_37_4532&quot;  title=&quot; René de Senne par persée&quot;&gt;une philosophie de l'épreuve &lt;/a&gt; : c'est dans la rencontre avec l'obstacle, dans la résistance que le réel oppose à nos désirs et à nos projets, que l'esprit se découvre lui-même et prend conscience de sa vocation à réaliser des valeurs. La valeur n'est pas donnée mais conquise à travers la lutte, et c'est dans cette tension permanente entre l'Etre et la conscience que réside la vie spirituelle. &lt;/p&gt; &lt;p&gt; Il est aussi l'auteur d'un &lt;em&gt;Traité de caractérologie&lt;/em&gt; (1945), ouvrage qui connut un large succès et qui cherche à établir une science rigoureuse des types de caractère humain. Distinguant plusieurs dimensions du caractère (émotivité, activité, résonance), il proposa une taxinomie des tempéraments qui eut une influence durable dans la psychologie et la pédagogie françaises. Cette double orientation, métaphysique et psychologique, fait de Le Senne un penseur original qui tenta de réconcilier la rigueur de l'analyse avec la profondeur de la réflexion sur l'existence humaine. &lt;/p&gt;" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E54" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Ra%C3%AFssa_Maritain&quot;  title=&quot; Wikipedia&quot;&gt;Raïssa MARITAIN&lt;/a&gt; était une philosophe, poétesse et mystique franco-russe. Née dans une famille juive, elle émigra en France avec sa famille dans l'enfance, étudia à la Sorbonne où elle rencontra Jacques Maritain, et se convertit avec lui au catholicisme en 1906 sous l'influence de Léon Bloy. Ensemble, ils formèrent l'un des &lt;a href=&quot;https://www.lavie.fr/idees/histoire/jacques-et-raissa-maritain-est-deux-88033.php&quot; title=&quot;jacques e traîssa par lavie,fr&quot;&gt;couples intellectuels &lt;/a&gt; les plus féconds de cette époque. &lt;/p&gt; &lt;p&gt; Elle apporta une contribution originale et irremplaçable à l'œuvre commune du couple. Poétesse d'une grande sensibilité, elle exprima dans des recueils comme &lt;em&gt;La Vie donnée&lt;/em&gt; (1935) une expérience mystique intense nourrie par la tradition juive et la spiritualité chrétienne. Ses &lt;em&gt;&lt;a href=&quot;https://www.youtube.com/watch?v=aKqCOZIq198&quot; title=&quot;la vérité par l’amitié par le verbe medias&quot;&gt;Grandes Amitiés &lt;/a&gt; &lt;/em&gt; (1941-1944), mémoires en deux volumes, constituent un témoignage exceptionnel sur la vie intellectuelle et spirituelle de l'entre-deux-guerres, évoquant ses rencontres avec Léon Bloy, Henri Bergson, Ernest Psichari, Jean Cocteau et de nombreux &lt;a href=&quot;http://palimpsestes.fr/metaphysique/textes/rmaritain_angoisse.html&quot; title=&quot;raissa maritain les grandes amitiés par palimpsestes.fr&quot;&gt;autres artistes et penseurs. &lt;/a&gt; &lt;/p&gt; &lt;p&gt; Elle contribua également aux travaux philosophiques de son mari, notamment aux réflexions sur la poésie et la connaissance poétique exposées dans &lt;em&gt;Situation de la poésie&lt;/em&gt; (1938), ouvrage qu'ils rédigèrent ensemble. Sa pensée sur le rapport entre expérience mystique, création artistique et connaissance philosophique constitue un apport original à la philosophie catholique française. Figure de la conversion et de l'engagement intellectuel au service de la foi, elle incarne une manière particulièrement intensément vécue de la vie de l'esprit. &lt;/p&gt;" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E56" display="https://louismassignon.fr/" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H56" display="https://www.laphilo.fr/pho/lmassignon-mini.webp" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H61" display="https://www.laphilo.fr/pho/gmarcel-mini.webp" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E63" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Alexandre_Koyr%C3%A9&quot;  title=&quot; Wikipedia&quot;&gt;Alexandre KOYRÉ&lt;/a&gt; était un philosophe et historien des sciences français d'origine russe, l'un des fondateurs de l'histoire des sciences modernes et un penseur dont l'influence sur l'historiographie scientifique mondiale fut décisive. Né à Taganrog en Russie, il étudia à Göttingen auprès de Husserl et de Hilbert avant de s'établir à Paris où il devint directeur d'études à l'École pratique des hautes études. Après la guerre, il partagea sa carrière entre Paris et Princeton. &lt;/p&gt; &lt;p&gt; Son œuvre maîtresse, &lt;em&gt;Études galiléennes&lt;/em&gt; (1939), est une révolution dans l'histoire des sciences. Contre la vision positiviste d'une science qui progresse par accumulation de faits expérimentaux, Koyré montre que la révolution scientifique du XVIIe siècle constitua une transformation radicale de la structure conceptuelle par laquelle les hommes pensaient la nature : le passage du cosmos aristotélicien, fini et ordonné, à l'univers infini et homogène de la physique classique. Cette thèse centrale, que l'histoire des sciences est d'abord une histoire des structures intellectuelles et non une simple accumulation de données, renouvela entièrement la discipline. &lt;/p&gt; &lt;p&gt; Dans &lt;em&gt;Du Monde clos à l'univers infini&lt;/em&gt; (1957), il approfondit cette thèse en retraçant la mutation cosmologique du XVIe au XVIIe siècle de Copernic à Newton. Ses travaux sur Descartes, Boyle et Newton sont également des contributions majeures. Son influence sur Thomas Kuhn — qui lui rendit hommage dans &lt;em&gt;La Structure des révolutions scientifiques&lt;/em&gt; — témoigne de la portée internationale de son travail. Koyré représente le modèle du philosophe-historien dont la rigueur intellectuelle a transformé durablement la compréhension du développement de la pensée scientifique. &lt;/p&gt;" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E64" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Gabriel_Madinier&quot;  title=&quot; Wikipedia&quot;&gt;Gabriel MADINIER&lt;/a&gt; était un philosophe français de tradition spiritualiste et réflexive, professeur à l’Université de Lyon, connu surtout pour sa « trilogie » sur la conscience (Conscience et mouvement, Conscience et amour, Conscience et signification) et pour son analyse de la conscience morale. Sa pensée s’inscrit dans le sillage de la philosophie de l’esprit française et vise à fonder une métaphysique et une éthique à partir de l’acte même par lequel la conscience se pose. &lt;/p&gt; &lt;p&gt; Fidèle à la méthode réflexive héritée de Lagneau et de Maine de Biran, il cherche à saisir le moi non comme un objet, mais dans l’acte même par lequel il se pose. Dans &lt;a href=&quot;https://www.persee.fr/doc/phlou_0776-555x_1940_num_43_67_4030_t1_0292_0000_2&quot;  title=&quot;gabriel madinier , conscience et mouvement par persée&quot;&gt;Conscience et mouvement &lt;/a&gt;  (1938), il montre que la conscience n’est pas séparable de la motricité : le geste, l’effort, le mouvement sont des manifestations concrètes à travers lesquelles la conscience s’éprouve et se constitue. Cette « conscience motrice » lui permet de dépasser les impasses du parallélisme et de l’objectivisme en ancrant la vie spirituelle dans l’expérience vécue du sujet agissant. &lt;/p&gt; &lt;p&gt; Dans Conscience et amour (1938), il prolonge cette enquête en explorant les conditions « surdéterminantes » de l’acte du moi, c’est-à-dire ce qui l’oriente vers autrui et vers la valeur. Le « Nous » n’est pas une simple donnée sociologique, mais une structure de la conscience où l’amour apparaît comme catégorie suprême de la raison, capable à la fois de distinguer et d’unir. Il y dessine une métaphysique du lien : au-delà du plan empirique des relations, l’amour se développe par la médiation de la justice et ouvre sur une dimension religieuse (rapport à Dieu) sans quitter le terrain de la psychologie réflexive. &lt;/p&gt; &lt;p&gt; Avec Conscience et signification (1953), il achève sa trilogie en proposant une véritable « métaphysique du signe » : la conscience est essentiellement productrice de sens, et c’est dans le Cogito que la conscience morale prend son origine. Il en tire, dans La conscience morale (1954), les conséquences éthiques : un rationalisme à la fois métaphysique et moral, d’inspiration très française, qui voit dans la raison la source des plus hautes exigences et dans l’amour (dont le christianisme révèle la signification universelle) l’explication ultime du réel. Pour lui, « ou le monde est absurde, ou l’amour explique tout », formule qui résume son option pour un spiritualisme rationnel ouvert à la transcendance. &lt;/p&gt; &lt;p&gt; Longtemps moins célèbre que d’autres représentants du spiritualisme français, il est reconnu par ses pairs comme un métaphysicien du signe et un penseur exigeant de la conscience et de l’amour. Ses ouvrages, réédités et parfois préfacés (notamment par Henri Gouhier et Aimé Forest), continuent d’intéresser ceux qui cherchent une philosophie réflexive, ancrée dans l’expérience concrète, mais capable de déboucher sur une éthique et une métaphysique intégrales. En ce sens, il prolonge et approfondit la tradition biranienne en lui donnant une tournure à la fois psychologique, morale et religieuse. &lt;/p&gt; &#10;&#10;" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H64" display="https://www.laphilo.fr/pho/gmadinier-mini.webp" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I64" display="https://www.laphilo.fr/photo/gmadinier.webp" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E65" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Gaston_Berger&quot;  title=&quot; Wikipedia&quot;&gt;Gaston BERGER&lt;/a&gt; était un philosophe, chef d’entreprise et haut fonctionnaire français connu pour avoir développé la notion de prospective et pour ses travaux sur la phénoménologie de Husserl. Il a cherché toute sa vie à articuler réflexion philosophique et action concrète, aussi bien dans l’industrie que dans l’administration de l’enseignement supérieur. Il fonde en 1925 la Société &lt;a href=&quot;https://www.youtube.com/watch?v=gChPu0ENNxI&quot; title=&quot; Centre Gaston Berger par Insa toulouse&quot;&gt;d’études philosophiques &lt;/a&gt; et la revue Études philosophiques, qui deviendront des lieux importants de la réflexion française.&#10; &lt;/p&gt; &lt;p&gt; Fondateur du mouvement de “prospective”, qu’il définit comme une science de l’“homme à venir”, vise à comprendre l’avenir possible pour mieux participer à sa réalisation, en réfléchissant aux besoins futurs tant culturels et moraux que techniques et matériels. Il crée le Centre international de prospective afin de favoriser des réflexions interdisciplinaires sur les futurs souhaitables et les responsabilités collectives.  &lt;/p&gt; &lt;p&gt;Il est l’un des principaux introducteurs de la phénoménologie d’Edmund Husserl en France, à laquelle il consacre sa thèse. Il propose la “théorétique”, conçue comme une science de la compréhension, qui vise à donner des outils conceptuels pour mieux saisir le réel et guider l’action.&#10; &lt;/p&gt; &lt;p&gt;Sa recherche se centre sur la conscience: valeur de la connaissance, présence de l’être, situation du moi, engagement, dialogue, amour, temps, courage. Il esquisse une phénoménologie de la mémoire où le devenir est une donnée concrète et le temps une construction ou un “mythe collectif” permettant aux hommes d’espérer et d’agir ensemble &lt;/p&gt; &lt;p&gt;  Il  incarne une figure de “philosophe‑administrateur”: il voit dans l’organisation et l’administration d’abord des problèmes humains avant d’être techniques. Son œuvre défend l’idée que la connaissance gratuite est à la fois facteur d’épanouissement personnel et condition d’une démocratie vivante. &lt;/p&gt;" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E66" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Georges_Bataille&quot; title=&quot; Wikipedia&quot;&gt;George BATAILLE&lt;/a&gt;  est un écrivain, philosophe, anthropologue et sociologue français, souvent qualifié de metaphysicien du mal pour son intérêt pour le sexe, la mort, la dégradation et le pouvoir de l'obscène. Il fut bibliothécaire, fondateur du Collège de Sociologie en 1937, et membre du journal Acéphale. Largement ignoré durant sa vie, il est aujourd'hui une figure centrale  &lt;a href=&quot;https://www.youtube.com/watch?v=ub2Ucoxs5fk&quot;  title=&quot;une vie, une œuvre par rien ne veut rien dire&quot;&gt;de l'intelligence française &lt;/a&gt; et a influencé des penseurs comme Foucault, Derrida ou Deleuze. &lt;/p&gt; &lt;p&gt; Sa philosophie se centre sur l'expérience intérieure, décrite comme un « voyage au bout du possible de l'homme », une extase ou ravissement qui nous porte au-delà des limites. Cette expérience s'atteint dans l'ivresse, l'érotisme, le rire, l'effusion poétique —  &lt;a href=&quot;https://blogs.mediapart.fr/amadouba19gmailcom/blog/150125/georges-bataille-1897-1962-mystique-transgressif-amadou-bal-ba&quot;  title=&quot;Georges Bataille mystique transgressif par blogs mediapart&quot;&gt;sans révélation divine, &lt;/a&gt;  dans un athéisme féroce. L'expérience intérieure est une plongée dans l'abîme où les repères s'effondrent, le savoir est aboli, la pensée défaite : « je saisis en sombrant que la seule vérité de l'homme, enfin entrevue, est d'être une supplication sans réponse ». &lt;/p&gt; &lt;p&gt; Il  est le penseur du mal, de l'excès, du négatif et de l'érotisme, considérés comme autant d'expériences intérieures. Il fut attiré par la violence et la disruption qu'elle pourrait causer au capitalisme et aux valeurs bourgeoises. Il explore les &lt;a href=&quot;https://www.persee.fr/doc/litt_0047-4800_1985_num_58_2_1389&quot;  title=&quot;Georges Bataille et la mort par persee&quot;&gt;« expériences limites » &lt;/a&gt; corporelles : cruauté, érotisme, transgression, subversion, sacrifice et excès, qui transcendent la pensée rationnelle. Ces expériences sont des voies pour acquérir une souveraineté personnelle, où la rationalité est suspendue lorsqu'on s'abandonne aux objets de ses désirs. &lt;/p&gt; &lt;p&gt; Parmi ses concepts clés, on trouve la sovereaneté (la liberté comme « seul miracle profane : impossible et pourtant là »), le sperpero ou dépense (déploiement inutile), et la partie maudite. La partie maudite exprime notre rapport à la mort, la violence et l'érotisme — la part sauvagement excessive de l'énergie qui ne peut être intégrée au système. Le sacré et l'abjection s'épousent chez lui sous une forme de dépassement des antinomies : le sacré est « à la fois saint et maudit, pur et impur, blanc et noir ». &lt;/p&gt; &lt;p&gt; Son œuvre Sur Nietzsche offre une nouvelle vision révolutionnaire du philosophe allemand, qui influença significativement Foucault, Derrida, Barthes et autres. Ses conceptions de la souveraineté, du sperpero et du sacrifice auront une grande influence sur les philosophes du XXe siècle, et ses idées sont reprises par Derrida, Kristeva et Sollers. &lt;/p&gt; &#10; &lt;audio controls title=&quot;Georges Bataille par France Culture&quot;&gt; &lt;source src=&quot;https://media.radiofrance-podcast.net/podcast09/13915-21.02.2024-ITEMA_23655177-2023C3372E0061-NET_MFC_CC62CF01-3F56-460F-B780-97916C17B0D7-21-7d903e2b8ecc4f9a64f0bed40bc4f642.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt; &#10;&#10;" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H66" display="https://www.laphilo.fr/pho/gbataille-mini.webp" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E67" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Aim%C3%A9_Forest&quot; title=&quot; Wikipedia&quot;&gt;Aimé FOREST&lt;/a&gt; était t un philosophe français spiritualiste, à la fois historien de la philosophie médiévale et métaphysicien d’inspiration thomiste et augustinienne. Sa pensée, souvent qualifiée de « philosophie du consentement », vise à articuler réalisme métaphysique, intériorité et sagesse chrétienne dans une démarche à la fois contemplative et concrète. &lt;/p&gt; &lt;p&gt; Né à Rancon (Haute-Vienne), agrégé de philosophie en 1921, il enseigne d’abord dans le secondaire avant de soutenir, en 1931, une thèse majeure sur La structure métaphysique du concret selon saint Thomas d’Aquin. Il occupe ensuite des chaires universitaires à Grenoble puis à Montpellier (1943–1968), où il forme plusieurs générations d’étudiants tout en publiant une œuvre abondante, jalonnée par des ouvrages comme Du consentement à l’être (1935), Consentement et création (1943), L’Avènement de l’âme (1973) ou Nos promesses encloses (1985). &lt;/p&gt; &lt;p&gt; Le titre même de son ouvrage phare indique l’axe central de sa philosophie : l’être ne se conquiert pas par la seule maîtrise conceptuelle, mais se reçoit dans un acte de consentement. Contre un idéalisme abstrait, Forest insiste sur la réalité concrète de l’existence et sur la nécessité, pour la pensée, de s’ouvrir à ce qui la précède et la soutient. Ce consentement n’est pas passivité, mais disposition active de l’intelligence à accueillir la vérité de l’être, vérité qui se dévoile davantage dans l’expérience intérieure que dans la construction systématique. &lt;/p&gt; &lt;p&gt; Influencé par Pascal, Maine de Biran, Louis Lavelle et Blondel, il développe une philosophie de l’intériorité où l’esprit découvre sa vocation sapientielle. L’âme n’est pas un objet parmi d’autres, mais le lieu où se noue le rapport à l’être et où se manifeste un « lien spirituel » qui unit les personnes entre elles et à la transcendance. Des titres comme L’Avènement de l’âme ou Essai sur les formes du lien spirituel montrent que sa métaphysique débouche sur une anthropologie spirituelle attentive à l’amour, à la promesse et à la communauté des esprits. &lt;/p&gt; &lt;p&gt;  Il assume explicitement la figure du « philosophe chrétien » : pour lui, la raison trouve son élan naturel dans le consentement au soutien de la foi, qui ne la supprime pas mais l’élève et l’assure. Sa démarche intègre thomisme et augustinisme dans une « sagesse plus haute que le thomisme », où métaphysique, mystique et amour convergent vers une sagesse intégrale. Cette orientation le place en marge des grands courants dominants du XXᵉ siècle (phénoménologie, existentialisme, pensée allemande), au profit d’une voie spirituelle, réaliste et universelle. &lt;/p&gt; &lt;p&gt; Longtemps peu connu hors des cercles spécialisés, il fait l’objet d’un regain d’attention grâce à des études (Michel Mahé, Philippe-Marie Margelidon, etc.) qui mettent en lumière la cohérence de son itinéraire. Son œuvre intéresse aujourd’hui ceux qui cherchent une métaphysique non dogmatique, ancrée dans l’expérience concrète et l’intériorité, tout en restant ouverte à la dimension religieuse. En ce sens, il propose moins un système clos qu’un chemin de sagesse : apprendre à consentir à l’être, à habiter son intériorité et à reconnaître, dans l’amour et la promesse, les formes vivantes du lien spirituel.&lt;/p&gt; &#10;&#10;&#10;&#10;" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H67" display="https://www.laphilo.fr/pho/aforest-mini.webp" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I67" display="https://www.laphilo.fr/photo/aforest.webp" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E71" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Vladimir_Jank%C3%A9l%C3%A9vitch&quot;   title=&quot; Wikipedia&quot;&gt;Vladimir JANKÉLÉVITCH&lt;/a&gt; était un philosophe français d'origine russe, influencé par Bergson, connu pour sa pensée originale &lt;a href=&quot;https://www.youtube.com/watch?v=498pItDm0vA&quot; title=&quot; Vladimir Jankélévitch : penser la morale, aimer le monde par Ina Culture&quot;&gt;mêlant morale, &lt;/a&gt; temps, musique, souvent en marge des courants dominants. Il  cultive un style littéraire élégant, improvisé, centré sur l'expérience vécue, le cœur et l'ineffable, refusant les systèmes rigides. &lt;/p&gt; &lt;p&gt;  Pour lui, la morale prime sur tout : elle est hyperbolique, urgente, guidée par le cœur et l'instant de la décision, au-delà des devoirs rationnels ; elle rejoint la métaphysique.  Il conçoit &lt;a href=&quot;https://www.youtube.com/watch?v=G6hbXImCmJA&quot; title=&quot;Vladimir Jankélévitch, penser la vie par LCP&quot;&gt;la liberté &lt;/a&gt; comme dynamique, non statique  amenant à une prise de conscience en mouvement, vers un &quot;au-delà de soi&quot; ; l'homme libre agit authentiquement, sans dogmes. &lt;/p&gt; &lt;p&gt; &lt;a href=&quot;https://maitron.fr/jankelevitch-vladimir/&quot; title=&quot; Vladimir Jankélévitch par maitron.fr&quot;&gt; Pour lui, &lt;/a&gt; la musique transcende l'esthétique pour devenir une expérience philosophique et métaphysique. Elle incarne l'irréversibilité du temps et l'instant fugace, reliant le sensible à l'intelligible sans jamais se réduire à une structure figée ou un algorithme. Elle exprime l'inexprimable : émotions, mystère de l'être, profondeur existentielle que le discours rationnel esquive. Le silence y joue un rôle clé, non comme absence, mais comme plénitude qui invite à l'introspection et à la transcendance. Il a consacré une douzaine d'ouvrages à la musique, comme Fauré et le Ineffable, Debussy et le Mystère ou Ravel, où philosophie et analyse musicale fusionnent en une prose poétique et improvisée.&lt;/p&gt; &lt;p&gt; Ses Œuvres majeures : -&quot;Philosophie première&quot; paru en 1954 : métaphysique vitaliste.  - Le &lt;a href=&quot;https://www.youtube.com/watch?v=KUUGJfgMoj0&quot; title=&quot;Vladimir Jankélévitch en 1980, philosophe du Je-ne-sais-quoi et du Presque-rien? par Radio-Canada Archives&quot;&gt;&quot;Je-ne-sais-quoi et le Presque-rien&quot; &lt;/a&gt; paru en 1957. - &quot;La Mort&quot; paru en 1967 et  -&quot;L'Irréversible et la Nostalgie&quot; en 1974. &lt;/p&gt; &#10;&lt;p&gt; &lt;/p&gt;   &lt;audio controls title=&quot;Avoir raison avec... Vladimir Jankélévitch par France Culture&quot;&gt; &lt;source src=&quot;https://media.radiofrance-podcast.net/podcast09/17362-07.08.2017-ITEMA_21402275-2017C35448E0026-NET_FC_4ECDB095-2595-41D4-AA28-F4A95CC22729-21.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt;  " r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E76" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Emmanuel_Mounier&quot;  title=&quot; Wikipedia&quot;&gt;Emmanuel MOUNIER&lt;/a&gt; était un philosophe français connu comme le fondateur du personnalisme, un courant qui veut remettre la personne humaine au centre de la pensée et de la vie sociale. &lt;/p&gt; &lt;p&gt; Sa philosophie naît dans un contexte de crise : montée du capitalisme, du fascisme, du marxisme et sentiment que l’homme est écrasé par des systèmes trop abstraits. Il refuse à la fois l’individualisme, qui isole l’être humain, et le collectivisme, qui le dissout dans le groupe. &lt;/p&gt; &lt;p&gt; Pour lui, la personne n’est pas seulement un individu biologique ou social.  &lt;a href=&quot;https://www.youtube.com/watch?v=T8tZ7E0D49k&quot;  title=&quot;emmanuel mounier par kto tv&quot;&gt;&quot;C’est un être libre, &lt;/a&gt; responsable, ouvert aux autres et appelé à se construire dans l’engagement, la relation et la vie communautaire. Cette idée donne à sa pensée une dimension à la fois morale, politique et spirituelle. &lt;/p&gt; &lt;p&gt; Il est aussi profondément chrétien, mais un chrétien engagé dans le monde. Avec  &lt;a href=&quot;https://maitron.fr/mounier-emmanuel-hippolyte-henri/&quot;  title=&quot;emmanuel mounier par maitron&quot;&gt;la revue Esprit, &lt;/a&gt; qu’il fonde en 1932, il cherche à faire dialoguer la foi, la réflexion philosophique et les grands problèmes de son époque, comme la guerre, la démocratie ou la justice sociale. Il défend une forme de « révolution spirituelle », c’est-à-dire une transformation intérieure et sociale de l’homme et des institutions. &lt;/p&gt; &lt;p&gt; la philosophie de Mounier propose une vision exigeante de l’humain : la personne doit être respectée dans sa dignité, sa liberté et sa vocation relationnelle. Son influence a été importante sur la pensée chrétienne, la philosophie sociale et les débats sur la démocratie au XXe siècle. &lt;/p&gt; &lt;audio controls title=&quot;Les murs blancs revue esprit par France Culture&quot;&gt; &lt;source src=&quot;https://media.radiofrance-podcast.net/podcast09/17473-14.03.2021-ITEMA_22602800-2021B20595S0073.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt; &#10;" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H76" display="https://www.laphilo.fr/pho/emounier-mini.webp" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I82" display="https://www.laphilo.fr/photo/jbeaufret.webp" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E83" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Maurice_Merleau-Ponty&quot; title=&quot; Wikipedia&quot;&gt;Maurice MERLEAU-PONTY&lt;/a&gt; était un philosophe français connu pour ses contributions à la phénoménologie, à la philosophie de la perception et à l’existentialisme. Il  s’inspire de plusieurs courants et penseurs et  reprend l’idée d’une description des expériences vécues, mais critique l’idéalisme husserlien. Dans son oeurvre majeure &lt;a href=&quot;https://www.youtube.com/watch?v=RrD5SEiXr_A&quot;  title=&quot; La phénoménologie de Maurice Merleau-Ponty par Tes grands auteurs en petits morceaux&quot;&gt;&quot;Phénoménalogie de la perception&quot;&lt;/a&gt; il  y développe une critique radicale des approches traditionnelles de la perception pour proposer une vision incarnée et existentielle de l’expérience humaine. Il rejette la séparation cartésienne entre le corps et l’esprit &lt;a href=&quot;https://classiques.uqam.ca/classiques/merleau_ponty_maurice/sens_et_non_sens/sens_et_non_sens.html&quot;  title=&quot;  Maurice Merleau-Ponty sens et non sens  par UQAM&quot;&gt;(sens et non sens)&lt;/a&gt;. Pour lui, le corps n’est pas un objet, mais un sujet percevant :  &lt;/p&gt; &lt;p&gt;&#10;-  Le corps propre : C’est par lui que nous faisons l’expérience du monde. Il est à la fois sujet et objet, toujours déjà engagé dans un environnement. &lt;/p&gt; &lt;p&gt; - La perception comme ouverture au monde : &lt;a href=&quot;https://www.youtube.com/watch?v=yiHMPFMCUvo&quot; title=&quot;MERLEAU-PONTY - L'OEIL ET L'ESPRIT par Kosmos&quot;&gt;Percevoir&lt;/a&gt; , c’est être en dialogue avec le monde, pas simplement recevoir des données sensorielles. &lt;/p&gt;  &lt;p&gt;   Il  s’intéresse au langage comme geste corporel. Pour lui, la parole n’est pas un simple véhicule de la pensée, mais une incarnation du sens et l’art montre comment l’expression émerge de la perception. &lt;/p&gt; &lt;p&gt; Dans &quot;Le Visible et l’invisible&quot;, il développe une  &lt;a href=&quot;https://www.youtube.com/watch?v=wZNUUGSZHMs&quot;  title=&quot; Maurice Merleau-Ponty - Entretien : Heure de culture française par Artesquieu &quot;&gt;ontologie originale&lt;/a&gt; où le &quot;chair&quot; est ni matière ni esprit, c’est une substance sensible qui unit le corps et le monde.  Chiasme : Concept décrivant l’entrelacs du voyant et du visible, du touchant et du touché (ex. : quand je me touche la main, je suis à la fois sujet et objet).  L’invisible : Non pas l’absence de visible, mais ce qui le structure. &lt;/p&gt;   &lt;audio controls title=&quot;Maurice Merleau-Ponty : Partie 8/12- La crise de la pensée religieuse par France Culture&quot;&gt; &lt;source src=&quot;https://media.radiofrance-podcast.net/podcast09/13915-20.11.2014-ITEMA_20690515-2013C3372E0710-21.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt;  " r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E85" display="&lt;p&gt; &lt;a href=&quot;https://fr.wikipedia.org/wiki/Claude_L%C3%A9vi-Strauss&quot;  title=&quot; Wikipedia&quot;&gt;Claude LEVI-STRAUSS&lt;/a&gt; était un anthropologue et ethnologue français, considéré comme l’une des grandes figures intellectuelles du XXᵉ siècle. Après des études de droit puis de philosophie, il se tourne vers l’ethnologie et commence ses premières missions de terrain au Brésil dans les années 1930, auprès de peuples amérindiens du Mato Grosso et de l’Amazonie. De ces expériences, il tirera notamment le livre Tristes tropiques, qui le rend célèbre auprès d’un public plus large en mêlant récit de voyage, &lt;a href=&quot;https://www.youtube.com/watch?v=Fk7du0Avh7U&quot; title=&quot;peuples amerindiens levi-strauss par ina culture&quot;&gt; réflexion sur les sociétés &lt;/a&gt; dites « primitives » et critique de l’ethnocentrisme occidental. &lt;/p&gt; &lt;p&gt; Il est connu pour avoir fondé l’anthropologie structurale, une manière d’étudier les cultures qui cherche les structures profondes, souvent inconscientes, qui organisent les systèmes de parenté, les mythes, les rites et plus largement les formes de vie sociales. Inspiré par la linguistique structurale, il considère que les faits culturels sont comme des langages : ce qui compte, ce sont les relations entre les éléments, plutôt que les éléments pris isolément. Sa méthode vise à réduire la diversité apparente des cultures à des ensembles de relations et d’oppositions formelles, par exemple des oppositions binaires (nature/culture, cru/cuit, vie/mort) qui structurent l’imaginaire. &lt;/p&gt; &lt;p&gt; Une partie centrale de son œuvre concerne les systèmes de parenté et l’alliance matrimoniale, qu’il étudie en détail dans Les structures élémentaires de la parenté, publié en 1949. Il y développe la théorie de l’alliance, selon laquelle les liens de parenté ne sont pas seulement des liens de sang, mais aussi des échanges de femmes entre groupes qui créent des solidarités et des obligations réciproques. Le mariage devient ainsi un mécanisme de communication sociale, une manière d’établir des réseaux d’alliance qui rendent possible la cohésion de la société. &lt;/p&gt; &lt;p&gt; Un autre volet majeur de sa pensée est son travail sur les mythes, en particulier dans les quatre volumes des Mythologiques, où il cherche à montrer que les mythes des différentes cultures, malgré leur grande diversité, obéissent à des schémas de transformation et à des structures communes. Pour lui, le mythe n’est pas une simple histoire, mais un système logique qui met en scène des oppositions et des médiations  pour résoudre symboliquement des tensions fondamentales. En analysant les mythes comme des ensembles de relations, il soutient que  &lt;a href=&quot;https://www.youtube.com/watch?v=fC0HUuXknHk&quot; title=&quot;etre pessimiste pour l’avenir par ina culture&quot;&gt;l’esprit humain fonctionne &lt;/a&gt;  partout selon des structures universelles, même si le contenu des récits varie. &lt;/p&gt; &lt;p&gt; Il développa une réflexion plus générale sur la diversité culturelle et les effets du colonialisme et de la modernité, notamment dans Tristes tropiques où il critique la tendance du monde moderne à homogénéiser et à détruire les différences culturelles. Il affirme l’idée que toutes les cultures sont égales en dignité et que la diversité des formes de vie humaines représente une richesse qu’il faut préserver, plutôt qu’un obstacle à dépasser. Son œuvre, reconnue par de nombreuses distinctions (médaille d’or du CNRS, élection à l’Académie française, prix Érasme, etc.), a contribué à transformer notre manière de penser le rapport entre l’Occident et les autres sociétés, ainsi que les fondements mêmes des sciences sociales. &lt;/p&gt;    &lt;audio controls title=&quot;sur les pas de claude levi-dtrausspar France Culture&quot;&gt; &lt;source src=&quot;https://media.radiofrance-podcast.net/podcast09/13019-03.08.2022-ITEMA_23099095-2022F20970S0215-22.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt;  " r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H85" display="https://www.laphilo.fr/pho/clstrauss-mini.webp" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I89" display="https://www.laphilo.fr/photo/morotsir.webp" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E91" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Henri_Maldiney&quot;  title=&quot; Wikipedia&quot;&gt;Henri MALDINEY&lt;/a&gt; était un philosophe français, l'une des figures les plus importantes de la phénoménologie française, connu pour sa réflexion originale sur l'art, la psychiatrie et l'existence. Né à Lyon, agrégé de philosophie, il enseigna à l'Université de Lyon pendant toute sa carrière. Sa pensée, &lt;a href=&quot;https://www.henri-maldiney.org/&quot;  title=&quot;henri MALDINEY&quot;&gt; d'une grande densité &lt;/a&gt; et d'un style exigeant, se développe à l'intersection de la phénoménologie husserlienne et heideggerienne, de la psychiatrie phénoménologique (notamment Binswanger) et d'une réflexion approfondie sur les arts plastiques et la musique. &lt;/p&gt; &lt;p&gt; Son œuvre maîtresse, &lt;em&gt;Regard, Parole, Espace&lt;/em&gt; (1973), est une méditation profonde sur la perception, le langage et l'espace à partir de l'analyse d'œuvres plastiques et poétiques.  &lt;a href=&quot;https://www.persee.fr/doc/chime_0986-6035_2001_num_44_1_2388/&quot;  title=&quot;henri MALDINEY par persée &quot;&gt; Il y développe &lt;/a&gt; une phénoménologie du pathique — du mode d'être fondamental par lequel nous sommes d'abord « touchés » par ce qui nous vient — par opposition au gnostique, qui serait le rapport détaché et objectivant à la réalité. Cette distinction lui permet d'analyser de manière originale la perception esthétique, l'expérience psychopathologique et la rencontre avec l'autre. &lt;/p&gt; &lt;p&gt; Dans &lt;em&gt;&lt;a href=&quot;https://fr.wikiversity.org/wiki/Penser_l%27homme_et_la_folie&quot;  title=&quot;pensée l’homme et la folie  par wikipedia &quot;&gt;Penser l'homme et la folie &lt;/a&gt; &lt;/em&gt; (1991) et &lt;em&gt;L'Art, l'éclair de l'être&lt;/em&gt; (1993), il approfondit sa réflexion sur les relations entre existence, folie et création artistique. Pour lui, l'art n'est pas un objet parmi d'autres mais une modalité d'existence, un surgissement de sens qui déborde toute représentation. Sa pensée, qui articule phénoménologie, psychiatrie et esthétique, a exercé une influence durable sur la psychiatrie phénoménologique française et sur les études d'esthétique philosophique. &lt;/p&gt;  &lt;audio controls title=&quot;hommage à Henri Maldiney par France Culture&quot;&gt; &lt;source src=&quot;https://media.radiofrance-podcast.net/podcast09/10080-14.12.2013-ITEMA_20561627-2013C3403E0239-21.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt; " r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E92" display="&lt;p&gt; &lt;a href=&quot;https://fr.wikipedia.org/wiki/Albert_Camus&quot;  title=&quot; Wikipedia&quot;&gt;Albert CAMUS&lt;/a&gt; était un philosophe et écrivain français dont le courant de pensée est l'Existentialisme. Il a abordé de nombreux sujets philosophiques, notamment &lt;a href=&quot;https://www.youtube.com/watch?v=kAm_I8nwjnc&amp;t=498s&amp;ab_channel=LePr%C3%A9cepteur&quot;   title=&quot;L'absure par le Précepteur&quot;&gt;l'absurdité de la vie&lt;/a&gt;, la liberté individuelle, la révolte, l'amour.&lt;/p&gt; &lt;p&gt;Il a écrit plusieurs ouvrage comme  &lt;a href=&quot;https://www.youtube.com/watch?v=vpzwD2cqqII&amp;ab_channel=LePr%C3%A9cepteur&quot;  title=&quot;L'étranger par le Précepteur&quot;&gt;&quot;l'Étranger&quot;&lt;/a&gt;  ou &quot;Le Mythe de Sisyphe&quot; où il  a développé l'idée que la vie est fondamentalement absurde, car elle ne contient pas de sens intrinsèque ou de finalité. Il a expliqué que l'homme est confronté à un monde qui ne lui donne pas de réponses claires ou satisfaisantes à ses questions sur l'existence et que, par conséquent, il doit créer son propre sens de la vie. &lt;/p&gt; &lt;p&gt;Camus a également écrit sur la liberté individuelle et la révolte contre l'oppression avec son livre &lt;a href=&quot;https://www.youtube.com/watch?v=XLbXH2kVOJ8&quot;  title=&quot;La Peste par le France Culture&quot;&gt;&quot; la Peste&quot;&lt;/a&gt; sortie en 1947 où Il défend la position selon laquelle l'individu doit être libre de poursuivre ses propres intérêts et passions, et que la tyrannie et l'oppression sont des forces qui doivent être combattues. Après le cycle de l'absurde, il entame le cycle de la &lt;a href=&quot;https://www.youtube.com/watch?v=pkRWhuO0wX0&amp;ab_channel=AlainBajom%C3%A9er&quot; title=&quot;La Révolte par Alain Bajomée&quot;&gt;révolte.&lt;/a&gt; &lt;/p&gt; &lt;p&gt;Enfin, il a écrit sur l'amour et l'amitié, explorant la façon dont ces sentiments peuvent apporter de la signification et de la valeur à la vie et a réfléchi sur la solitude et l'isolement, soulignant que ces expériences peuvent être à la fois douloureuses et enrichissantes. &lt;/p&gt;   &lt;audio controls title=&quot;Albert Camus par France Culture&quot;&gt; &lt;source src=&quot;https://cdn.radiofrance.fr/s3/cruiser-production/static/inter/sons/2011/07/s27/NET_2f8a9ed7-086a-40ee-9d75-b184f9e5f99a.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt; &#10;" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E93" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Paul_Ric%C5%93ur&quot;   title=&quot; Wikipedia&quot;&gt;Paul RICOEUR&lt;/a&gt; était un  philosophe français considéré comme le dernier &lt;a href=&quot;https://www.lemonde.fr/a-la-une/article/2005/05/21/paul-ricoeur-philosophe-de-tous-les-dialogues_652552_3208.html&quot;  title=&quot;Paul Ricoeur, philosophe de tous les dialogues par Le Monde&quot;&gt;&quot;grands penseurs&quot; &lt;/a&gt; à la croisée de la phénoménologie, de l’herméneutique, de la philosophie du langage et de l’éthique. &lt;/p&gt; &lt;p&gt; Dans “Le volontaire et l’involontaire” et “Finitude et culpabilité”, il analyse la volonté humaine comme toujours prise entre liberté et contraintes, capacité d’agir et fragilité, ce qui nourrit sa réflexion sur la faute et la responsabilité.  Ses travaux sur le symbole et l’interprétation montrent que l’être humain se comprend à travers  &lt;a href=&quot;https://www.youtube.com/watch?v=QLOwycKenCI&quot; title=&quot;En 1965, le philosophe Paul Ricoeur commente la contre-culture beatnik par Radio-Canada&quot;&gt; des symboles &lt;/a&gt;, des récits et des textes, dont le sens n’est jamais donné immédiatement mais demande un travail d’interprétation. Son projet est de tenir ensemble la compréhension “interprétative” et les approches critiques (psychanalyse, structuralisme), en assumant les “conflits d’interprétations” plutôt que de chercher une seule lecture définitive. &lt;/p&gt; &lt;p&gt; Il conçoit  &lt;a href=&quot;https://www.youtube.com/watch?v=uX76UVhBIqs&quot;  title=&quot;Paul Ricoeur, l’herméneutique du soupçon par Baglis Tv&quot;&gt; l’herméneutique&lt;/a&gt; comme une philosophie de l’interprétation qui assume la distance entre nous et les textes, les événements, les autres, et qui cherche une vérité située dans ce travail d’interprétation plutôt que dans une évidence immédiate.​ Il insiste sur le fait qu’il n’existe pas de philosophie “sans présuppositions” : toute compréhension passe par des pré-compréhensions, que la critique vient transformer, ce qui l’amène à articuler la lecture soupçonneuse (Marx, Nietzsche, Freud) et la lecture de confiance. &lt;/p&gt; &lt;p&gt; Il développe une éthique de la “vie bonne, avec et pour les autres, dans des institutions justes” (formule célèbre de “Soi-même comme un autre”), où l’éthique (visée de la vie bonne) précède la morale (règles, normes).​ &#10;Il met au centre le “sujet capable” (capable de parler, agir, se raconter, se tenir pour responsable) mais toujours fragile, et pense la justice comme articulation entre la reconnaissance de la vulnérabilité des personnes et la nécessité d’institutions justes.​ &lt;/p&gt; &lt;p&gt; Ses analyses de la mémoire, de l’histoire et du pardon nourrissent aussi les débats contemporains sur le “devoir de mémoire”, les violences politiques et les possibilités de réconciliation. &lt;/p&gt;   &lt;audio controls title=&quot;La pensée de Paul Ricoeur par France Culture&quot;&gt; &lt;source src=&quot;https://media.radiofrance-podcast.net/podcast09/10467-18.11.2013-ITEMA_20550371-2013C12410S0322-NET_FC_66E918EC-2266-4DF5-B6E4-489E465FA68D-21.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt;" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H94" display="https://www.laphilo.fr/pho/lgoldmann-mini.webp" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E95" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Marguerite_Duras&quot;  title=&quot; Wikipedia&quot;&gt;Marguerite DURAS&lt;/a&gt; n’était pas une philosophe au sens académique, mais son œuvre littéraire, cinématographique et théâtrale déploie  &lt;a href=&quot;https://www.marguerite-duras.com/Biographie.php&quot;  title=&quot;marguerite duras -biographie&quot;&gt;une pensée originale, &lt;/a&gt; centrée sur l’écriture, le désir, la mémoire et la condition humaine. &lt;/p&gt; &lt;p&gt; Elle récuse le dualisme corps/esprit hérité de la tradition philosophique et religieuse occidentale, et propose plutôt un monisme matérialiste : l’être est fait d’une seule substance, la matière, et le corps y est réhabilité contre les représentations littéraires marquées par le péché originel. Cette vision s’enracine aussi dans son athéisme et dans l’influence de la philosophie orientale, vécue durant ses dix-huit premières années en Indochine. &lt;/p&gt; &lt;p&gt; Pour elle, écrire, c’est « donner corps au paradoxe » et signifier le désir : l’écriture est le lieu même de la « vérité du désir », souvent orientée vers un objet absent, inaccessible. Elle décrit l’écriture comme un acte de silence et de cri : « Écrire c’est ne pas parler. C’est se taire. C’est hurler sans bruit. », libérant un  &lt;a href=&quot;https://www.youtube.com/watch?v=KBum9zj-9p8&quot;  title=&quot;marguerite duras -détruire pour mieux reconstruire par france culture&quot;&gt;désir refoulé &lt;/a&gt; par la société. La mémoire est inséparable du désir et de l’écriture : elle n’est pas fiable, et c’est par l’affabulation et la réinscription dans le texte que les souvenirs acquièrent une existence réelle. L’écriture devient alors travail de mémoire et de deuil, une manière de faire durer la vie face à la mort, en traitant « la mémoire de l’oubli ». &lt;/p&gt; &lt;p&gt; Elle met en scène un sujet humain inconsistant, « fantomatique », essentiellement seul et dépourvu d’identité stable, s’opposant au « fantasme d’identité » de la philosophie occidentale. Tout en restant distante du militantisme féministe, son œuvre défend la cause des femmes et explore la liberté, la passivité et la dynamique masculin/féminin, notamment dans sa dernière période créatrice. &lt;/p&gt; &lt;p&gt; Bien qu’elle affirme ne pas écrire ex nihilo et reconnaisse des inspirations (Pascal, Diderot, Rousseau, Kierkegaard), elle s’en détache en déclarant avoir oublié ses lectures, marquant une relation paradoxale à la philosophie. Son rapport à la pensée se manifeste par des interrogations sur le temps, la matière et la souffrance, faisant de l’écriture le seul moyen d’exprimer des émotions fondamentales que le langage ordinaire ne peut porter. &lt;/p&gt; &#10;&lt;audio controls title=&quot;Marguerite DURAS , je mets la musique au-dessus de tout par France Culture&quot;&gt; &lt;source src=&quot;https://media.radiofrance-podcast.net/podcast09/20333-02.01.2023-ITEMA_23242749-2022M36310E0193-25.m4a&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt;  " r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H95" display="https://www.laphilo.fr/pho/mduras-mini.webp" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E96" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Louis_Althusser&quot;  title=&quot; Wikipedia&quot;&gt;Louis ALTHUSSER&lt;/a&gt; était un philosophe connu pour ses efforts de renouvellement de la pensée marxiste et ses concepts novateurs.  Parmi ses concepts clés, on peut citer : &lt;/p&gt;  &lt;p&gt; - La coupure épistémologique : Il soutient qu'il existe une rupture radicale entre les œuvres de jeunesse de Marx  et ses œuvres de la maturité (notamment Le Capital). Cette coupure marquerait le passage d'une idéologie humaniste à une science de l'histoire, le matérialisme historique. &lt;/p&gt; &lt;p&gt; - L'idéologie et les Appareils Idéologiques d'État &lt;a href=&quot;https://www.youtube.com/watch?v=ZtJjAs7kLpo&quot;  title=&quot; Louis Althusser AIE par Cinema culture&quot;&gt;(AIE) &lt;/a&gt;: Il développe une théorie influente de l'idéologie avec un ensemble d'idées fausses, mais une &quot;représentation du rapport imaginaire des individus à leurs conditions réelles d'existence&quot;. Elle fonctionne en &quot;interpellant&quot; les individus en sujets. Les AIE (comme l'école, l'Église, la famille, les médias) jouent un rôle crucial dans la reproduction des rapports de production capitalistes en diffusant l'idéologie dominante. &lt;/p&gt; &lt;p&gt; - La surdétermination : Emprunté à la psychanalyse, ce concept lui permet de penser la complexité des contradictions dans une société. Une contradiction principale entre les forces productives et les rapports de production est toujours surdéterminée par d'autres contradictions secondaires. &lt;/p&gt; &lt;p&gt; - Le procès sans sujet : Il critique l'idée que l'histoire serait le produit de l'action consciente d'un sujet et insiste sur le fait que l'histoire est un &lt;a href=&quot;https://www.youtube.com/watch?v=Syi7hOQcNUs&quot;  title=&quot; Louis Althusser sur la civilisation par Artesquieu&quot;&gt;processus déterminé&lt;/a&gt; par des structures. &lt;/p&gt; &lt;p&gt;  - La philosophie comme &quot;lutte de classes dans la théorie&quot; : Il conçoit la philosophie non pas comme une quête de vérité absolue, mais comme une intervention politique dans le champ théorique, reflétant les luttes de classes. Il parle aussi de la &quot;philosophie spontanée des savants&quot; pour désigner les présupposés idéologiques inconscients qui peuvent influencer le travail scientifique. &lt;/p&gt; &lt;p&gt; Parmi ses publications les plus importantes, on peut mentionner : &lt;/p&gt; &lt;p&gt;- Montesquieu, la politique et l'histoire : Une analyse de la pensée politique de Montesquieu.  - Lénine et la philosophie : Développe sa conception de la philosophie comme pratique politique.  - L'avenir dure longtemps (suivi de Les Faits) (1992, posthume) : Une autobiographie où il revient sur sa vie, ses troubles psychiques et le meurtre de sa femme, Hélène Rytmann, en 1980. Cet événement tragique a conduit à son internement psychiatrique et a mis fin à sa carrière publique. &lt;/p&gt;  &lt;audio controls title=&quot; Louis Althusser par France Culture&quot;&gt; &lt;source src=&quot;https://media.radiofrance-podcast.net/podcast09/11189-11.07.2011-ITEMA_20296434-2011C15000E0126-ITE_00044081_RSCE-21.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt;&lt;/audio&gt; " r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E98" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Suzanne_Bachelard&quot; title=&quot; Wikipedia&quot;&gt;Suzanne BACHELARD&lt;/a&gt; était une philosophe française spécialiste de phénoménologie et de logique, fille du célèbre Gaston Bachelard. Agrégée de philosophie et docteur ès lettres, elle fut professeur à la Sorbonne et contribua de manière significative à la diffusion et à l'approfondissement de la &lt;a href=&quot;https://www.persee.fr/doc/phlou_0035-3841_1954_num_52_34_4491&quot;  title=&quot;phénoménologie husserlienne et hegelienne par persée&quot;&gt;phénoménologie husserlienne &lt;/a&gt;  en France. Son travail intellectuel, longtemps éclipsé par la stature de son père, mérite d'être apprécié pour lui-même. &lt;/p&gt; &lt;p&gt; Sa thèse principale, &lt;em&gt;&lt;a href=&quot;https://www.persee.fr/doc/phlou_0035-3841_1984_num_82_56_6315&quot;  title=&quot;le problème de la logique pure par persée&quot;&gt;La Logique de Husserl : &lt;/a&gt;  étude sur Logique formelle et Logique transcendantale&lt;/em&gt; (1957), est une analyse rigoureuse et pénétrante de la philosophie logique de Husserl, en particulier de la distinction entre logique formelle et logique transcendantale. Cette œuvre constitue une contribution importante à la réception française de la phénoménologie husserlienne et à la compréhension des rapports entre logique formelle et constitution transcendantale du sens. &lt;/p&gt; &lt;p&gt; Elle publia également des travaux sur la temporalité, notamment &lt;em&gt;Une étude sur la phénoménologie du temps de Husserl&lt;/em&gt; et contribua à faire connaître en France des aspects moins explorés de la phénoménologie, en particulier la théorie husserlienne de la conscience intime du temps. Professeur engagée et pédagogue de talent, elle forma plusieurs générations d'étudiants à la rigueur phénoménologique. Son œuvre illustre la richesse et la profondeur de la réception française de la phénoménologie husserlienne dans la seconde moitié du XXe siècle. &lt;/p&gt;" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I98" display="https://www.laphilo.fr/photo/sbachelard.webp" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E99" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Jules_Vuillemin&quot;  title=&quot; Wikipedia&quot;&gt;Jules VUILLEMIN&lt;/a&gt;  était un philosophe français qui  s'est distingué par son travail en  &lt;a href=&quot;https://hal.science/hal-04409311v1/document&quot; title=&quot;Jules Vuillemin, philosdophie analytique contrarié par hal&quot;&gt;philosophie analytique &lt;/a&gt;, en épistémologie et en histoire de la philosophie.  Il diffuse en France les idées de Bertrand Russell, Rudolf Carnap et Willard Van Orman Quine, influençant des penseurs comme Jacques Bouveresse. Ses débuts touchent à  &lt;a href=&quot;https://lafrancebyzantine.blogspot.com/2016/09/jules-vuillemin-t-il-ete-existentialiste.html&quot;  title=&quot;Jules Vuillemin at'il été existantialiste? par lafrancebyzantine&quot;&gt;l'existentialisme &lt;/a&gt; et au marxisme, mais il évolue vers un rationalisme rigoureux, rejetant les excès de Sartre ou Heidegger. &lt;/p&gt; &lt;p&gt; Ses œuvres majeures : - &quot;Nécessité ou contingence&quot; paru en 1984, qui analyse les systèmes philosophiques par une approche logique et historique, et &quot;La philosophie de l'algèbre&quot; paru en 1962 ou il explore la nécessité, la contingence, la logique et les sciences, insistant sur la cohérence interne des systèmes selon l'héritage de Martial Gueroult. Épistémologue de premier plan avec Gilles Gaston Granger et René Thom, il défend une philosophie attentive aux mathématiques et à la physique. &lt;/p&gt; &lt;p&gt; Il s'intéresse à Kant, Descartes, la liberté et la métaphysique de la nature, tout en critiquant les réductions existentialistes au profit d'une raison objective. Ses archives sont conservées au Laboratoire de Philosophie et d'Histoire des Sciences à Nancy. Auteur de plus de vingt livres, il reste une figure de la rigueur philosophique française. &lt;/p&gt;" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H102" display="https://www.laphilo.fr/pho/emorin-mini.webp" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E105" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Ren%C3%A9_Girard&quot; title=&quot; Wikipedia&quot;&gt;René GIRARD&lt;/a&gt; était un philosophe, anthropologue et critique littéraire français dont la pensée, souvent qualifiée de &quot;théorie mimétique&quot;, repose sur des concepts clés interdépendants qui expliquent la nature du désir humain, de la violence et du sacré. &lt;/p&gt; &lt;p&gt;Nous ne désirons pas intrinsèquement des objets ou des personnes, mais nous désirons ce que les autres désirent. Notre  &lt;a href=&quot;https://www.youtube.com/watch?v=9tn7RVVD_bA&quot; title=&quot;Le désir mimétique par le Precepteur&quot;&gt;désir est &quot;triangulaire&quot; &lt;/a&gt; : il y a un sujet (celui qui désire), un objet, et un modèle (celui dont le désir influence le sujet). Voici les 3 points clés : &lt;/p&gt; &lt;p&gt;- Le modèle comme médiateur : Le modèle n'est pas simplement une personne qui possède l'objet désiré, mais celui qui nous le révèle comme désirable. &lt;/p&gt; &lt;p&gt; - &lt;a href=&quot;https://www.youtube.com/watch?v=7scJjspwo9M&quot; title=&quot;La rivalité mimétique par le Precepteur&quot;&gt;La rivalité mimétique &lt;/a&gt; : Lorsque plusieurs personnes désirent le même objet, une rivalité mimétique émerge et elle peut devenir intense et se substituer à l'objet initial. &lt;/p&gt; &lt;p&gt; - Le désir métaphysique : Il distingue le désir des objets matériels du désir d'être, plus profond car il porte sur quelque chose d'insaisissable. &lt;/p&gt; &lt;p&gt; Dans son ouvrages &quot;Mensonge romantique et vérité romanesque&quot;, il montre comment les grands romanciers ont intuitivement compris la nature mimétique du désir et les illusions &quot;romantiques&quot; qui le masquent. &lt;/p&gt; &lt;p&gt; Selon lui, les sociétés humaines ont développé un mécanisme archaïque pour résoudre ces crises mimétiques : le mécanisme du &lt;a href=&quot;https://www.youtube.com/watch?v=QYTKoHPrKxI&quot; title=&quot; La fabrique du bouc émissaire par le Parole de Philosophe&quot;&gt;bouc émissaire&lt;/a&gt; dont voici les points clés : &lt;/p&gt; &lt;p&gt; - La désignation d'une victime : Au point culminant de la crise, l'attention de la communauté se focalise sur un individu ou un groupe particulier, accusé d'être la cause du désordre. &lt;/p&gt; &lt;p&gt; - L'unanimité contre la victime :  &lt;a href=&quot;https://www.dailymotion.com/video/xv8mim&quot;  title=&quot; René Girard, la violence et le sacré par le Parole de mySkreen&quot;&gt;La violence mimétique&lt;/a&gt;, initialement diffuse, se canalise et se concentre sur ce bouc émissaire. L'expulsion ou la mort de la victime rétablit temporairement la paix. &lt;/p&gt; &lt;p&gt; - La sacralisation de la victime : après avoir été la source du mal, elle est souvent sacralisée. On lui attribue un pouvoir extraordinaire, capable à la fois de provoquer la crise et de la résoudre. &lt;/p&gt; &lt;p&gt; - Le rite et le mythe : Les rites sacrificiels et les mythes sont des tentatives de reproduire et de commémorer le meurtre fondateur du bouc émissaire. &lt;/p&gt; &lt;p&gt;Il reste une figure intellectuelle majeure, dont les idées continuent d'inspirer et de provoquer la réflexion sur la nature humaine, la culture et la religion. &lt;/p&gt; &lt;audio controls title=&quot;René Girard, des choses cachées depuis la fondation du monde&quot; par France Culture&quot;&gt; &lt;source src=&quot;https://media.radiofrance-podcast.net/podcast09/13915-24.12.2023-ITEMA_23566825-2023C3372E0859-21.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt;&lt;/audio&gt;  " r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E106" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Jean-Claude_Margolin&quot;  title=&quot; Wikipedia&quot;&gt;Jean-Claude MARGOLIN&lt;/a&gt; était un philosophe et humaniste français, spécialiste reconnu de la pensée de la Renaissance et notamment d'Érasme de Rotterdam. Agrégé de philosophie et docteur ès lettres, il fut directeur de recherches au CNRS et l'un des fondateurs du Centre d'études supérieures de la Renaissance à Tours. Son œuvre immense, qui combine érudition philologique et analyse philosophique, constitue une contribution majeure à la connaissance de l'humanisme de la Renaissance. &lt;/p&gt; &lt;p&gt; Ses travaux sur Érasme — dont une biographie de référence, &lt;em&gt;&lt;a href=&quot;https://www.persee.fr/doc/rhren_0181-6799_1995_num_40_1_2825&quot; title=&quot;jean claude Margolin Erasme precepteur par Persée &quot;&gt;Érasme par lui-même&lt;/a&gt; &lt;/em&gt; (1965, réédité plusieurs fois), et de nombreuses éditions critiques et traductions d'œuvres érasmiennes — font de lui l'un des plus grands érasmistes du XXe siècle. Il contribua à montrer la cohérence et la profondeur de la pensée d'Érasme, souvent réduite à un simple « humanisme » de bon sens, en soulignant la rigueur de sa théologie chrétienne, la finesse de son anthropologie et la complexité de son rapport à la Réforme. &lt;/p&gt; &lt;p&gt; Il s'intéressa à l'ensemble de la culture philosophique et littéraire de la Renaissance : Rabelais, Montaigne, Vives, Thomas More, et aux grandes questions de cette époque comme la définition de l'humanisme, les rapports entre foi et raison, l'éducation et la rhétorique. Sa direction de la revue &lt;em&gt;&lt;a href=&quot;https://www.persee.fr/doc/rhren_1771-1347_2013_num_76_1_3288&quot; title=&quot;jean claude Margolin humaniste par Persée &quot;&gt;Bibliothèque d'Humanisme &lt;/a&gt; et Renaissance&lt;/em&gt; et ses nombreuses contributions collectives firent de lui un animateur central de la recherche internationale sur la Renaissance. Son œuvre témoigne d'une conception exigeante de l'histoire de la philosophie comme restitution vivante d'une pensée dans toute sa richesse. &lt;/p&gt;  &lt;audio controls title=La folie Erasme par France Culture&quot;&gt; &lt;source src=&quot;https://media.radiofrance-podcast.net/podcast09/10467-15.01.2010-ITEMA_20211948-2010C12410E0018-NET_6E4A59B9-E10B-4E2F-A507-FFDDA95137E9_FC-21.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt;&lt;/audio&gt; " r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E109" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Gilles_Deleuze&quot; title=&quot; Wikipedia&quot;&gt;Gilles DELEUZE&lt;/a&gt; était un philosophe français qui a profondément marqué la pensée contemporaine dans une  &lt;a href=&quot;http://sos.philosophie.free.fr/deleuze.php&quot; style=&quot;color:#88A1E9&quot; title=&quot; Gilles Deleuze  par SOS philo&quot;&gt;critique radicale&lt;/a&gt;oeuvre foisonnante et complexe.  Au cœur de sa philosophie se trouve une  &lt;a href=&quot;https://www.youtube.com/watch?v=4ybvyj_Pk7M&quot; title=&quot; Gilles Deleuze : l'art et les sociétés de contrôle par lINTELLECT FOCUS&quot;&gt;critique radicale&lt;/a&gt; de la pensée traditionnelle occidentale, qu'il accuse d'être dominée par une logique de la représentation, de l'identité et de la négation. &lt;/p&gt; &lt;p&gt; Il cherche à penser la différence en elle-même qui n'est pas secondaire ou dérivée, mais originaire.  Le monde n'est pas constitué d'entités fixes et identiques qui entreraient ensuite en relation, mais d'un flux incessant de différences, de variations et de devenirs. Il conçoit plutôt la pensée comme une force créatrice qui produit des concepts pour appréhender et transformer le réel qui n'est pas statique, mais un processus continu de transformation, d'hybridation et de métamorphose. Ses oeuvres principales sont : &lt;/p&gt; &lt;p&gt; - &lt;a href=&quot;https://www.youtube.com/watch?v=ia0FpHbHa_U&quot;  title=&quot; Différence et répétition de Gilles Deleuze (French Audiobook/Livre audio) 1 Avant propos par Chad A Haag Philosophy Channel&quot;&gt;&quot;Différence et Répétition&quot;&lt;/a&gt; : Oeuvre métaphysique majeure, où il développe sa pensée de la différence et critique la conception traditionnelle de la répétition comme reproduction de l'identique. &lt;/p&gt; &#10;&lt;p&gt; - &quot;Logique du sens&quot; : Une exploration des paradoxes du langage et du sens à travers une lecture originale de Lewis Carroll et des stoïciens. &lt;/p&gt; &#10;&lt;p&gt; - &quot;Qu'est-ce que la philosophie ?&quot; (avec Félix Guattari) : Une réflexion sur la nature de la philosophie comme création de concepts, distincte de la science et de l'art. &lt;/p&gt; &lt;p&gt;  Sa rencontre avec Felix Guattari donne naissance à 2 ouvrages majeurs :&lt;a href=&quot;https://www.youtube.com/watch?v=JQE4_2ti_10&amp;t=78s&quot; title=&quot; La pensée politique de Deleuze et Guattari - Partie 1 / L'anti-Oedipe par Politikon&quot;&gt;&quot; L'Anti-Œdipe &quot;&lt;/a&gt;  : Critique radicale de la psychanalyse et une exploration du désir comme force révolutionnaire et &lt;a href=&quot;https://www.youtube.com/watch?v=E01RyGu3Zac&quot; title=&quot;La pensée politique de Deleuze et Guattari - Partie 2 / Mille Plateaux par Politikon&quot;&gt;&quot; Mille Plateaux &quot;&lt;/a&gt;   : Une œuvre foisonnante qui explore une multitude de thèmes (le territoire, le devenir ) à travers le  &lt;a href=&quot;https://www.youtube.com/watch?v=RQ2rJWwXilw&quot; title=&quot;The Rhizome - A Thousand Plateaus, Deleuze and Guattari par Then &amp; Now&quot;&gt;concept de Rhizome&lt;/a&gt;. &lt;/p&gt; &lt;p&gt; Il  est un philosophe majeur qui a profondément transformé notre manière de  &lt;a href=&quot;https://diacritik.com/category/deleuze/&quot; title=&quot; Deleuze par Diacritik&quot;&gt;penser la différence&lt;/a&gt;, la multiplicité, le devenir et la créativité. &lt;/p&gt; &lt;audio controls title=&quot;Gilles Deleuze, notre contemporain&quot; par France Culture&quot;&gt; &lt;source src=&quot;https://media.radiofrance-podcast.net/podcast09/11189-19.11.2012-ITEMA_20421487-2012C15000E0183-ITE_00054426_RSCE-21.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt;&lt;/audio&gt; " r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E111" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Fran%C3%A7ois_Wahl&quot;  title=&quot; Wikipedia&quot;&gt;François WAHL&lt;/a&gt; était un philosophe et éditeur français, figure centrale de la vie intellectuelle française de la fin des années 1950 au début des années 1990, surtout connu pour avoir promu le structuralisme et la psychanalyse aux Éditions du Seuil. l a régné pendant trente ans sur le domaine des sciences humaines et la littérature italienne au Seuil, publiant Jacques Lacan, Françoise Dolto, Paul Ricœur, Roland Barthes, Philippe Sollers, Alain Badiou, Jean-Cla Milner, ainsi que des auteurs italiens comme Carlo Emilio Gadda et Italo Calvino. Il est décrit comme un « structuraliste dans l’âme », construisant son activité éditoriale comme une structure où chaque choix (acceptations, refus, retraductions) faisait système, appliquant la doctrine structuraliste à son métier d’éditeur. &lt;/p&gt; &lt;p&gt; Il est l’auteur de trois ouvrages majeurs :  &lt;a href=&quot;https://philosophie.ac-normandie.fr/spip.php?article148&quot; title=&quot;qu’est ce que la philosophie par françois Wahl &quot;&gt;Qu’est-ce que le structuralisme ? &lt;/a&gt; , Philosophie (1973), Introduction au discours du tableau (1996) et Le Perçu (2007). Dans Introduction au discours du tableau, il étudie les œuvres de Poussin, Memling ou Bellini pour montrer que le « visible » apparaît sous deux espèces : le paysage et le tableau, articulant ainsi esthétique et théorie du signe. Le Perçu propose une exploration critique des phénoménologies du XXᵉ siècle, en mobilisant les concepts de discours, sujet, désir et énoncé pour formaliser une analyse du « fait esthétique » . &lt;/p&gt; &lt;p&gt; La ligne directrice de sa pensée peut se résumer à un repérage du concept de sujet dans la philosophie contemporaine et son introduction dans le champ de l’esthétique. Il a écrit de nombreux articles discutant les œuvres d’auteurs comme Badiou, Bataille, Barthes, Foucault ou Lacan, et son dernier grand livre, La dissidence du sujet, rassemble ces réflexions sur le sujet, le désir et le discours dans la philosophie et l’art. &lt;/p&gt; &lt;audio controls title=&quot;les fluides d’Aristote /hommage à f Wahl par France Culture&quot;&gt; &lt;source src=&quot;https://media.radiofrance-podcast.net/podcast09/12003-17.09.2014-ITEMA_20670365-2014C18006S0260-21.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt;&lt;/audio&gt;  " r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H111" display="https://www.laphilo.fr/pho/fwahl-mini.webp" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I111" display="https://www.laphilo.fr/photo/fwahl.webp" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H113" display="https://www.laphilo.fr/pho/jmeyendorff-mini.webp" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H115" display="https://www.laphilo.fr/pho/hdamisch-mini.webp" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E116" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Bernard_Bourgeois&quot;  title=&quot; Wikipedia&quot;&gt;Bernard BOURGEOIS&lt;/a&gt; était un philosophes français connu comme le grand traducteur et interprète de Hegel en langue française. Ancien élève de l’École normale supérieure, agrégé de philosophie, il a enseigné à Lyon puis à Paris I–Sorbonne, avant d’être élu à l’Académie des sciences morales et politiques, qu’il a présidée en 2014. &lt;/p&gt; &lt;p&gt; Sa philosophie se définit d’abord par un  &lt;a href=&quot;https://academiesciencesmoralesetpolitiques.fr/membres-titulaires/section-i-philosophie-2/bernard-bourgeois/&quot; title=&quot;bernard bourgeois carrière et travaux académique par académie des sciences&quot;&gt;travail historique et philologique &lt;/a&gt;  monumental sur l’idéalisme allemand, de Kant à Marx, avec un centre de gravité hégélien. Il a traduit et annoté des milliers de pages de Hegel (Phénoménologie de l’esprit, Encyclopédie des sciences philosophiques, Science de la logique, écrits de droit naturel, textes pédagogiques), en s’efforçant de restituer la rigueur conceptuelle et la cohérence systématique de la pensée hégélienne. &lt;/p&gt; &lt;p&gt; Au-delà de la traduction, il défend une lecture de Hegel comme philosophe de la liberté et de la raison dans l’histoire. Pour lui, Hegel ne célèbre pas un destin aveugle ni une fin dogmatique de l’histoire, mais pense l’historicité de l’Esprit comme déploiement de formes de rationalité et d’institutions où la liberté devient concrète (droit, État, vie éthique). Cette orientation se retrouve dans ses communications à l’Académie, par exemple sur &lt;a href=&quot;https://www.youtube.com/watch?v=YRErwGZWBqc/&quot; title=&quot;bernard bourgeois , hegel et le droit par pkpdlm&quot;&gt;« Hegel et le droit » &lt;/a&gt;  ou « La fin de l’histoire selon Hegel », où il montre comment la philosophie hégélienne éclaire les problèmes politiques et juridiques modernes. &lt;/p&gt; &lt;p&gt; Sa propre philosophie n’est pas un système indépendant de type hégélien, mais une méditation exigeante sur les conditions de la rationalité spéculative et sur la manière dont la philosophie peut habiter son époque. Il insiste sur la nécessité de « relire constamment » Hegel plutôt que de le lire une fois pour toutes, parce que la pensée spéculative demande un travail continu de reprise et d’approfondissement. En ce sens, sa philosophie est une pratique de la raison qui se forme au contact des textes, des concepts et des problèmes que Hegel a portés à leur plus haute expression. &lt;/p&gt; &#10;&#10;" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H116" display="https://www.laphilo.fr/pho/bbourgeois-mini.webp" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H117" display="https://www.laphilo.fr/pho/baudrillard-mini.webp" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E120" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/F%C3%A9lix_Guattari&quot;  title=&quot; Wikipedia&quot;&gt;Félix GUATTARI&lt;/a&gt; était un philosophe, psychanalyste et  &lt;a href=&quot;https://maitron.fr/guattari-felix/&quot; title=&quot; BOURDIEU - L'habitus par Cyrus North&quot;&gt;militant intellectuel &lt;/a&gt; français connu pour sa collaboration avec Gilles Deleuze, mais il a aussi développé une pensée personnelle très originale. Sa philosophie se situe surtout dans le courant du post-structuralisme et de la pensée critique contemporaine. Elle s’oppose aux idées trop fixes de sujet, d’identité ou de structure, et insiste au contraire sur les processus, les relations et les transformations. &lt;/p&gt; &lt;p&gt; Un de ses apports centraux est la notion de subjectivité comme quelque chose de produit par des agencements multiples. Pour lui, la subjectivité n’est pas seulement intérieure ou individuelle : elle se fabrique aussi dans les institutions, les médias, la politique, la famille et les environnements techniques. &lt;/p&gt; &lt;p&gt; Il a aussi travaillé sur la psychanalyse, en critiquant ce qu’il voyait comme ses formes trop normatives, notamment autour du complexe d’Œdipe. Dans &lt;a href=&quot;https://enseignants.lumni.fr/fiche-media/00000001135/l-anti-oedipe-de-gilles-deleuze-et-felix-guattari.html&quot; title=&quot; anti-oedipe  deleuze et guattari par enseignants lumni&quot;&gt;L’Anti-Œdipe &lt;/a&gt; et Mille Plateaux, il défend avec Deleuze une pensée des flux, des désirs, des « rhizomes » et des lignes de fuite, contre les modèles hiérarchiques et fermés. &lt;/p&gt; &lt;p&gt; On peut donc le placer à la croisée de plusieurs branches : philosophie politique, philosophie de la subjectivité, psychanalyse critique et théorie sociale. Sa pensée est souvent associée à des idées comme l’écologie mentale, la créativité collective et la transformation des formes de vie. &lt;/p&gt;  &#10; &lt;audio controls title=&quot;la fin du politique par France Culture&quot;&gt; &lt;source src=&quot;https://media.radiofrance-podcast.net/podcast09/13915-16.03.2022-ITEMA_22964487-2022C3372E0135-NET_MFC_B9CCC943-E790-4029-A9C3-4076BC2B331E-21-443183d5ed7da523138c0280fb088809.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt;&lt;/audio&gt;  " r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H120" display="https://www.laphilo.fr/pho/fguattari-mini.webp" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H121" display="https://www.laphilo.fr/pho/lebrun-mini.webp" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H122" display="https://www.laphilo.fr/pho/serres-mini.webp" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H123" display="https://www.laphilo.fr/pho/granel-mini.webp" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E124" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Raymond_Boudon&quot;  title=&quot; Wikipedia&quot;&gt;Raymond BOUDON&lt;/a&gt; était un sociologue et philosophe social français, l'une des figures les plus importantes de la sociologie française de la seconde moitié du XXe siècle et un ardent défenseur du libéralisme intellectuel et de la rationalité. Son œuvre,  &lt;a href=&quot;https://www.quesaisje.com/raymond-boudon&quot;  title=&quot; Boudon raymond par que sais je ?&quot;&gt;immense et plurielle, &lt;/a&gt; porte à la fois sur la méthodologie des sciences sociales, la théorie de l'action et la philosophie sociale. &lt;/p&gt; &lt;p&gt; Sa contribution la plus connue est l'élaboration d'une sociologie de l'individualisme méthodologique. Dans &lt;em&gt;L'Inégalité des chances&lt;/em&gt; (1973) et surtout dans &lt;em&gt;La Logique du social&lt;/em&gt; (1979) et &lt;em&gt;L'Art de se persuader des idées douteuses, fragiles ou fausses&lt;/em&gt; (1990), il défend l'idée que les faits sociaux s'expliquent par les actions et les croyances des individus, et que ces actions sont généralement rationnelles au sens large, c'est-à-dire fondées sur de « bonnes raisons » qui ne se réduisent pas  &lt;a href=&quot;https://www.youtube.com/watch?v=tMmKcRuoxp4&quot;  title=&quot; boudon l’inégalité des chances par La Sociothèque&quot;&gt;aux seuls intérêts matériels.&lt;/a&gt;  Cette position s'oppose à la fois au structuralisme durkheimien et au réductionnisme économique. &lt;/p&gt; &lt;p&gt; Dans ses dernières œuvres — &lt;em&gt;Pourquoi les intellectuels n'aiment pas le libéralisme&lt;/em&gt; (2004), &lt;em&gt;La Rationalité&lt;/em&gt; (2009) — il s'engagea dans une défense résolue du libéralisme politique et intellectuel contre ce qu'il percevait comme les dérives relativistes et collectivistes de la pensée française contemporaine. Sociologue rigoureux et polémiste redoutable, il fut l'un des penseurs français les plus lus à l'étranger, notamment aux États-Unis et en Allemagne, où son travail sur la rationalité et les croyances sociales est largement reconnu. &lt;/p&gt;     &lt;audio controls title=&quot;Raymond Boudon par France Culture&quot;&gt; &lt;source src=&quot;https://media.radiofrance-podcast.net/podcast09/12003-15.01.2014-ITEMA_20575231-2014C18006S0015-21.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt;&lt;/audio&gt;  " r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H126" display="https://www.laphilo.fr/pho/fedier-mini.webp" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H127" display="https://www.laphilo.fr/pho/mwittig-mini.webp" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E128" display=" &lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Michel_Hulin&quot;  title=&quot; Wikipedia&quot;&gt;Michel HULIN&lt;/a&gt; était un philosophe français récemment décédé, grand spécialiste de la &lt;a href=&quot;https://www.youtube.com/watch?v=tJFic9y58Sc&quot; title=&quot; Aperçu de l’hindouisme avec Michel Hulin par Resonances &quot;&gt;philosophie indienne &lt;/a&gt; et de la comparaison entre pensée européenne et pensée asiatique, notamment de l’Advaïta Vedānta, le courant « non‑dualiste » du vedānta. Longtemps professeur de philosophie indienne et comparée à l’université Paris‑Sorbonne, il a joué un rôle central dans la diffusion en France des grandes écoles de pensée de l’Inde. Sa carrière s’est accompagnée d’un important travail de traduction du sanskrit et de vulgarisation, accessible à un public non spécialiste. &lt;/p&gt; &lt;p&gt; Ses recherches portent d’une part sur  &lt;a href=&quot;https://www.youtube.com/watch?v=kaJP8yDwHeY&quot; title=&quot; For intérieur par Resonnances &quot;&gt;la pensée indienne classique &lt;/a&gt;  (notion d’ahamkāra, textes vedāntins et shivaïtes d’inspiration tantrique), d’autre part sur les questions épistémologiques et métaphysiques que soulève la rencontre entre les traditions européennes et asiatiques. Dans sa thèse, Le Principe de l’ego dans la pensée indienne classique, il analyse la notion de « faux moi » et montre comment elle éclaire notre expérience ordinaire de la conscience. Il s’intéresse également à la question du temps, de l’éternité et des expériences dites mystiques, qu’il relie à des vécus très concrets. &lt;/p&gt; &lt;p&gt; Dans des ouvrages comme La Face cachée du temps, La Mystique sauvage, Hegel et l’Orient, Shankara et la non‑dualité ou encore l’anthologie L’Inde des sages, il  conjugue une érudition très précise et un style volontairement clair. Il montre comment des interrogations métaphysiques complexes – sur le moi, le temps, l’au‑delà ou l’expérience spirituelle – touchent directement la vie intérieure de chacun. Par son enseignement et ses livres, il a contribué à installer durablement en France une philosophie comparée attentive au dialogue entre Europe et Inde. &lt;p&gt; &lt;/p&gt;&lt;audio controls title=&quot;  Philosophies indiennes (1/4) : Upanishads, les textes fondateurs ?  par France Culture&quot;&gt; &lt;source src=&quot;https://media.radiofrance-podcast.net/podcast09/10467-16.12.2013-ITEMA_20562153-2013C12410S0350-NET_FC_A092AF0E-5BC1-49EE-A72F-E62BB6A2A8B1-21.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt;&lt;/audio&gt;  &lt;p&gt;  &lt;/p&gt;&#10;" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H128" display="https://www.laphilo.fr/pho/mhulin-mini.webp" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H130" display="https://www.laphilo.fr/pho/jfmarquet-mini.webp" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E132" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Cl%C3%A9ment_Rosset&quot; title=&quot; Wikipedia&quot;&gt;Clément ROSSET&lt;/a&gt; était un philosophe français connu pour sa pensée radicale et son style d'écriture d'une grande clarté. Son œuvre est principalement centrée sur le concept du  &lt;a href=&quot;https://www.youtube.com/watch?v=I50Jbj6uQEU&quot; title=&quot;Clément Rosset : la réalité ne convient pas ! par Kosmos&quot;&gt;&quot;réel&quot;&lt;/a&gt;  et l'incapacité ou la difficulté de l'homme à l'accepter dans sa singularité et souvent sa cruauté. Voici les points essentiels concernant sa philosophie : &lt;/p&gt; &lt;p&gt; - &lt;a href=&quot;https://www.youtube.com/watch?v=8m_kXVBdtwg&quot;  title=&quot; Le réel et son double, Clément Rosset, 2.2 avant-propos par Thibault BELZACQ&quot;&gt;Le Réel sans double&lt;/a&gt; : Son idée maîtresse est que le réel est unique, singulier et dépourvu de tout &quot;double&quot;. Il n'y a pas d'arrière-monde, pas de sens caché, pas de consolation ou d'illusion qui puisse atténuer sa nature brute. Le réel est simplement ce qui est, dans son évidence la plus nue. &lt;/p&gt; &lt;p&gt; - Le Refus du double et de l'illusion : Une grande partie de son travail consiste à traquer les différentes formes d'illusions et de doubles que l'humanité crée pour  &lt;a href=&quot;https://philitt.fr/2023/09/12/clement-rosset-tout-est-sans-raison/&quot;  title=&quot;Clément Rosset : tout est sans raison par Phillitt&quot;&gt;échapper à la confrontation&lt;/a&gt; directe avec le réel. Ces doubles peuvent être d'ordre métaphysique, moral, psychologique, ou même esthétique.&lt;/p&gt; &lt;p&gt; - &lt;a href=&quot;https://www.youtube.com/watch?v=JDcudFE_uBQ&quot;  title=&quot;Entretien avec Pierre Dumayet (1961) par Archives&quot;&gt;Philosophie tragique&lt;/a&gt; et Joie : Bien que sa pensée puisse sembler sombre en insistant sur la cruauté et l'absurdité du réel, il développe une philosophie que l'on qualifie souvent de &quot;tragique&quot; au sens nietzschéen du terme. Il ne s'agit pas de désespoir, mais plutôt de l'affirmation de la vie et du réel tels qu'ils sont, y compris dans leurs aspects les plus difficiles. &lt;/p&gt; &lt;p&gt; Il est également remarquable par son style d'écriture. Loin du jargon philosophique abscons, il privilégie une langue simple, directe et percutante. Cette clarté formelle est au service de la clarté de sa pensée, cherchant à énoncer le réel avec le moins d'interférences possible. Son œuvre, bien que parfois restée en marge des courants universitaires dominants, a marqué par sa radicalité, sa lucidité et sa défense d'une confrontation sans fard avec le réel.  &lt;/p&gt; &lt;audio controls title=&quot;Clément Rosset par France Culture&quot;&gt; &lt;source src=&quot;https://media.radiofrance-podcast.net/podcast09/10080-20.12.2013-ITEMA_20564152-2013C3403E0215-21.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt;&lt;/audio&gt;  " r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H132" display="https://www.laphilo.fr/pho/rosset-mini.webp" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E133" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Jacques_Bouveresse&quot;  title=&quot; Wikipedia&quot;&gt;Jacques BOUVERESSE&lt;/a&gt; était un philosophe français du courant analytique, connu pour son rationalisme exigeant, son &lt;a href=&quot;https://www.youtube.com/watch?v=mfGM00nmj20&quot;  title=&quot; Wittgenstein et l'intériorité 一 Jacques Bouveresse par Andrea Cirla &quot;&gt;travail sur Wittgenstein &lt;/a&gt; et sa critique des dérives du milieu intellectuel français. Il a largement contribué à introduire et stabiliser en France une philosophie soucieuse de vérité, de clarté et d’argumentation rigoureuse. &lt;/p&gt; &lt;p&gt; Ses domaines privilégiés sont la philosophie de la connaissance, des sciences, des mathématiques, de la logique, du langage, ainsi qu’une philosophie de la culture attentive à la littérature et à la critique sociale.  Il se réclame du rationalisme des Lumières et s’inspire fortement de la philosophie analytique, du Cercle de Vienne, de Frege, de Gödel et de la tradition d’Europe centrale. Wittgenstein, qu’il contribue à faire connaître en France, est l’une de ses références centrales. &lt;/p&gt; &lt;p&gt; Il défend une position rationaliste dont le prolongement éthique est ce qu’il appelle la  &lt;a href=&quot;https://www.persee.fr/doc/lgge_0458-726x_1971_num_6_21_2079&quot; title=&quot;Langage ordinaire et philosophie par Persée &quot;&gt;&quot;modestie intellectuelle&quot; &lt;/a&gt; : ne pas exagérer ce que la philosophie peut faire, refuser le pathos et le prestige facile. Il combat le relativisme, l’historicisme radical et les remises en cause globales de la notion de vérité, notamment chez certains auteurs français, tout en reconnaissant par ailleurs leur importance. &lt;/p&gt; &lt;p&gt; Sa grande thèse, &quot;Le Mythe de l’intériorité&quot;, porte sur Wittgenstein, le langage privé, l’expérience et la signification, et a joué un rôle clé dans la réception française de Wittgenstein. Il consacre de nombreux travaux à Robert Musil et Karl Kraus, qu’il lit comme des alliés dans un combat pour l’exactitude, la critique de la bêtise et des illusions de la culture moderne. &lt;/p&gt;  &lt;audio controls title=&quot;Jacques Bouveresse, à la recherche de la clarté par France Culture&quot;&gt; &lt;source src=&quot;https://media.radiofrance-podcast.net/podcast09/10351-11.05.2021-ITEMA_23961779-2000C3500E0287-21.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt;" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H133" display="https://www.laphilo.fr/pho/bouveresse-mini.webp" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E134" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Jean-Luc_Nancy&quot;  title=&quot; Wikipedia&quot;&gt;Jean-Luc NANCY&lt;/a&gt; était un philosophe français, agrégé de philosophie, il fut professeur à l'Université de Strasbourg jusqu'à sa retraite. Sa pensée, en dialogue constant avec Heidegger, Derrida et Lacoue-Labarthe — avec lequel il collabora étroitement — porte sur le « sens du monde », la communauté, le corps et le toucher. &lt;/p&gt; &lt;p&gt; Son œuvre est marquée par le questionnement du « with » (avec), du « being-with » heideggerien. Dans &lt;em&gt;La Communauté désoeuvrée&lt;/em&gt; (1986), il développe une pensée de la communauté qui refuse toute forme d'immanentisme ou de fusion : la communauté véritable n'est pas une substance commune, mais  &lt;a href=&quot;https://www.youtube.com/watch?v=fZK6pEAPxEw&quot;  title=&quot;jean luc Nancy par Institut Humanités &quot;&gt;l'exposition partagée &lt;/a&gt; de la singularité de chacun. Cette réflexion, en dialogue critique avec Blanchot et Bataille, a eu un retentissement considérable dans les débats contemporains sur la politique, la communauté et l'identité. &lt;/p&gt; &lt;p&gt; Dans &lt;em&gt;Corpus&lt;/em&gt; (1992) et &lt;em&gt;Noli me tangere&lt;/em&gt; (2003), il explore  &lt;a href=&quot;https://www.youtube.com/watch?v=1kCExw6Wp9k&quot;  title=&quot;jean luc Nancy par Lacan TV &quot;&gt;la philosophie du corps &lt;/a&gt; et du toucher comme modes fondamentaux de l'être-au-monde. Son essai sur le sens — &lt;em&gt;Le Sens du monde&lt;/em&gt; (1993) — aborde la question de la possibilité du sens dans un monde déserté par les transcendances. &lt;em&gt;L'Intrus&lt;/em&gt; (2000), bref récit autobiographique sur sa transplantation cardiaque, mêle réflexion philosophique et expérience personnelle de la maladie et de l'altérité. Son œuvre, immense et diverse, témoigne d'une pensée vivante et rigoureuse toujours en dialogue avec la littérature, l'art et la politique. &lt;/p&gt;  &lt;audio controls title=&quot;Jean luc Nancy par France Culture&quot;&gt; &lt;source src=&quot;https://media.radiofrance-podcast.net/podcast09/11472-06.02.2011-ITEMA_20267545-2011C16153E0003-ITE_00040439_RSCE-21.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt;" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H134" display="https://www.laphilo.fr/pho/jlnancy-mini.webp" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E135" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Philippe_Lacoue-Labarthe&quot;  title=&quot; Wikipedia&quot;&gt;Philippe LACOUE-LABARTHE&lt;/a&gt; était un philosophe, critique littéraire, traducteur et théoricien français né à Tours et connu pour ses travaux sur la mimésis, le romantisme allemand, Hölderlin, Heidegger, Derrida et la relation entre esthétique et politique. Il a aussi beaucoup compté dans le milieu intellectuel de Strasbourg, où il a enseigné longtemps et travaillé avec Jean-Luc Nancy. &lt;/p&gt; &lt;p&gt; Son  &lt;a href=&quot;https://maitron.fr/lacoue-labarthe-philippe/&quot;  title=&quot; lacoue-labarthe par le maitron&quot;&gt;œuvre interroge &lt;/a&gt; la façon dont l’art, la philosophie et la politique s’entrecroisent, notamment à travers la notion de mimésis et la critique de l’“esthétisation du politique”. Il a aussi travaillé sur le romantisme allemand et sur la réception de Hölderlin, qu’il considérait comme une figure majeure. &lt;/p&gt; &lt;p&gt; Parmi les livres souvent cités, on trouve Le Titre de la lettre avec Jean-Luc Nancy, L’Absolu littéraire, L’Imitation des modernes, La Fiction du politique et Heidegger, la politique du poème. Il a également traduit plusieurs auteurs allemands majeurs, dont Heidegger, Hölderlin, Nietzsche, Benjamin et Celan. &lt;/p&gt; &lt;p&gt; Sa pensée tourne autour de trois idées principales : - La représentation n’est jamais transparente : ce que nous montrons, racontons ou jouons n’est jamais la réalité elle-même, mais une forme, un masque, une imitation. - La littérature et le théâtre sont essentiels pour comprendre la philosophie, parce qu’ils révèlent ce que les concepts cachent ou simplifient.popups. - Le lien entre esthétique et politique est dangereux : il a beaucoup réfléchi à la manière dont l’art, les mythes et les images peuvent servir le politique, y compris dans des formes fascisantes. &lt;/p&gt; &#10; &lt;audio controls title=&quot;les versions de philippe lacoue labarthe par France Culture&quot;&gt; &lt;source src=&quot;https://media.radiofrance-podcast.net/podcast09/16409-16.03.2007-ITEMA_20062386-2007C6409S0011-MEM_000036772_RF-21.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt;  " r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H135" display="https://www.laphilo.fr/pho/pllabarthe-mini.webp" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H136" display="https://www.laphilo.fr/pho/fdelaporte-mini.webp" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H137" display="https://www.laphilo.fr/pho/lecourt-mini.webp" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E138" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Jean-Michel_Berthelot&quot;  title=&quot; Wikipedia&quot;&gt;Jean-Michel BERTHELOT&lt;/a&gt; était un philosophe et sociologue français spécialiste d'épistémologie des sciences sociales. Professeur à l'Université de Paris IV-Sorbonne et à l'Université du Québec à Montréal, il contribua de manière décisive à la réflexion philosophique sur les fondements et les méthodes des sciences humaines et sociales. Son œuvre joint la rigueur épistémologique à une large culture philosophique et sociologique. &lt;/p&gt; &lt;p&gt; Son ouvrage principal, &lt;em&gt; &lt;a href=&quot;https://www.persee.fr/doc/sotra_0038-0296_1992_num_34_3_2605_t1_0388_0000_3&quot;  title=&quot;l’intelligence du social par persée &quot;&gt; L'Intelligence du social&lt;/a&gt; &lt;/em&gt; (1990), est une analyse approfondie des schèmes d'intelligibilité que les sciences sociales utilisent pour rendre compte de la réalité sociale : le schème causal, le schème fonctionnel, le schème structural, le schème herméneutique et d'autres modes d'explication. Berthelot montre que chaque paradigme sociologique privilégie un mode d'intelligibilité particulier, ce qui permet de comprendre à la fois leurs apports spécifiques et leurs limites. Ce livre constitue l'une des contributions les plus claires et les plus systématiques à la philosophie des sciences sociales en langue française. &lt;/p&gt; &lt;p&gt; Dans &lt;em&gt;Epistémologie des sciences sociales&lt;/em&gt; (2001, ouvrage collectif qu'il dirigea), il offrit un panorama complet des questions épistémologiques fondamentales que posent les sciences humaines et sociales : la causalité, la compréhension, la mesure, la modélisation, la réflexivité et les rapports entre science et valeurs. Ses travaux contribuèrent à établir l'épistémologie des sciences sociales comme une discipline à part entière dans le paysage universitaire français, en dialogue constant avec la philosophie des sciences anglophones et continentale. &lt;/p&gt;" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H138" display="https://www.laphilo.fr/pho/jmberthelot-mini.webp" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E139" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Daniel_Bensa%C3%AFd&quot;  title=&quot; Wikipedia&quot;&gt;Daniel BENSAÏD&lt;/a&gt; était un philosophe français marxiste, l'un des intellectuels les plus importants de la gauche radicale française de son époque. Né à Paris dans une famille juive d'origine algérienne, il fut l'un des leaders de la révolte étudiante de mai 1968 à Paris-Nanterre aux côtés de Daniel Cohn-Bendit. Professeur de philosophie à l'Université Paris VIII-Saint-Denis, il fut membre dirigeant de la Ligue communiste révolutionnaire (LCR) et de son successeur le Nouveau Parti Anticapitaliste (NPA). &lt;/p&gt; &lt;p&gt; Sa pensée philosophique chercha à renouveler le marxisme en le débarrassant des &lt;a href=&quot;https://www.youtube.com/watch?v=uxBvxfRI2CE&quot;  title=&quot;la privatisation du monde par bibou11slalala &quot;&gt; simplifications téléologiques &lt;/a&gt; et en l'ouvrant à des problématiques nouvelles. Dans &lt;em&gt;Marx l'intempestif&lt;/em&gt; (1995), il défend un Marx débarrassé du déterminisme historique et de la philosophie du progrès, un Marx « intempestif » qui pense la politique comme art du possible et de l'impossible, en dialogue avec Blaise Pascal et Walter Benjamin. Ce livre renouvela profondément la  &lt;a href=&quot;https://www.youtube.com/watch?v=is8Ya038-Q4&quot;  title=&quot;l’héritage de Marx par socialtram &quot;&gt; lecture de Marx &lt;/a&gt; dans la gauche française. &lt;/p&gt; &lt;p&gt; Dans &lt;em&gt;Le Pari mélancolique&lt;/em&gt; (1997) et &lt;em&gt;Résistances&lt;/em&gt; (2001), il développe une philosophie de l'engagement politique nourrie par la mélancolie des défaites mais portée par une fidélité irréductible à l'émancipation. Sa réflexion sur les rapports entre philosophie et politique, entre utopie et stratégie, constitue l'une des contributions les plus originales à la pensée marxiste contemporaine. Polémiste redoutable et pédagogue exigeant, il laissa une empreinte profonde sur plusieurs générations de militants et d'intellectuels de gauche. &lt;/p&gt;  &lt;audio controls title=&quot;Daniel Bensaid  par France Culture&quot;&gt; &lt;source src=&quot;https://media.radiofrance-podcast.net/podcast09/10075-11.12.2006-ITEMA_20049670-2006C6608S0221-MEM_000033324_RF-21.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt; " r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H139" display="https://www.laphilo.fr/pho/bensaid-mini.webp" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G140" display="&quot;Ce virus est là pour nous préparer au nouveau régime climatique&quot; par France Culture" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H140" display="https://www.laphilo.fr/pho/latour-mini.webp" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H141" display="https://www.laphilo.fr/pho/rdamien-mini.webp" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E142" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Catherine_Colliot-Th%C3%A9l%C3%A8ne&quot; title=&quot; Wikipedia&quot;&gt;Catherine COLLIOT-THELENE&lt;/a&gt; était une philosophe française  majeure de la philosophie politique contemporaine, spécialiste de Max Weber et penseuse des droits, de la démocratie et de la propriété dans un cadre cosmopolitique. Membre de l’Institut universitaire de France, elle est reconnue comme une référence internationale des études wébériennes. &lt;/p&gt; &lt;p&gt; Son travail se situe au croisement de la philosophie politique et des sciences sociales, avec trois pôles principaux :  &lt;a href=&quot;https://www.youtube.com/watch?v=krUYFtq9Jww&quot; title=&quot;Max Weber et la violence légitime de l’état par France Culture&quot;&gt;Max Weber, la démocratie et les droits, &lt;/a&gt;  la propriété et le cosmopolitisme.  Elle traduit et commente plusieurs textes de Weber, notamment Le Savant et le politique et Les Communautés, en montrant en détail ses concepts de rationalisation, de désenchantement et de domination. &lt;/p&gt; &lt;p&gt; À partir des années 2000, elle se concentre sur les droits subjectifs, leur articulation avec l’individualisme contemporain et la transformation des rapports entre pouvoirs politiques et économiques. Elle insiste sur la nécessité de penser la normativité (ce qui doit être) à partir d’une analyse précise des structures sociales réelles, d’où son dialogue constant avec le droit, l’histoire et la sociologie. &lt;/p&gt; &lt;p&gt; Dans &quot;La Démocratie sans “demos”  paru en 2011, elle remet en question l’identification classique entre &quot;peuple&quot; et &quot;démocratie&quot;. Elle critique la superposition entre souveraineté du peuple et souveraineté territoriale de l’État, qui conduit selon elle à des versions exclusives de la démocratie. &lt;a href=&quot;https://www.youtube.com/watch?v=ps2ixtEpgYI&quot; title=&quot;la democratie c’est le droit de resistance par Journal l’Humanitét&quot;&gt;Sa philosophie cherche &lt;/a&gt;  une démocratie fondée sur des droits universalisables et sur la participation de tous les sujets, plutôt que sur l’appartenance à une communauté nationale préconstituée. &lt;/p&gt; &lt;p&gt; Elle refuse la séparation entre théorie pure et monde social : pour elle, la philosophie politique doit dialoguer avec les sciences sociales pour produire une critique efficace des institutions et des inégalités. Elle a accompagné, sans posture militante classique mais avec une forte implication intellectuelle, les luttes pour les droits des femmes, des exclus et des étrangers, en cherchant à fournir des outils conceptuels pour penser l’égalité aujourd’hui. &lt;/p&gt; &#10; &lt;audio controls title=&quot;Les défis juridiques de la migration : existe-t-il un droit à la libre circulation ? par France Culture&quot;&gt; &lt;source src=&quot;https://media.radiofrance-podcast.net/podcast09/21447-09.02.2022-ITEMA_22927630-2022C27677S0040-21.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt;" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H142" display="https://www.laphilo.fr/pho/thelene-mini.webp" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H143" display="https://www.laphilo.fr/pho/bstiegler-mini.webp" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E144" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Bernard_Mabille_(philosophe)&quot;  style=&quot;color:#6A142A&quot;  title=&quot; Wikipedia&quot;&gt;Bernard MABILLE&lt;/a&gt; était un philosophe français spécialiste de dialectique et de philosophie hégélienne, ainsi que de métaphysique contemporaine. Agrégé de philosophie et professeur à l'Université Paris IV-Sorbonne, il fut l'un des meilleurs connaisseurs français de Hegel et contribua de manière significative au renouvellement des études hégéliennes en France dans les dernières décennies du XXe siècle. &lt;/p&gt; &lt;p&gt; Sa thèse principale, &lt;em&gt;Hegel : l'épreuve de la contingence&lt;/em&gt; (1999), est une lecture originale de la philosophie hégélienne à la lumière de la problématique de la contingence. Contre les lectures qui réduisent Hegel à un penseur du nécessaire et du rationnel, Mabille montre que la contingence est au cœur même du système hégélien et que la dialectique est précisément la méthode qui permet de penser le passage du contingent au nécessaire sans l'éliminer. Cette relecture contribua à ouvrir la philosophie hégélienne à des problématiques contemporaines. &lt;/p&gt; &lt;p&gt; Dans ses travaux sur la métaphysique et la dialectique, Mabille s'intéressa également aux rapports entre la philosophie hégélienne et la phénoménologie française, notamment Merleau-Ponty et Henry. Son enseignement à la Sorbonne forma plusieurs générations d'étudiants à la rigueur de la pensée dialectique. Sa disparition prématurée priva la philosophie française d'un penseur rigoureux dont l'œuvre, bien que de volume limité, témoigne d'une lecture profonde et originale de l'idéalisme allemand et de ses prolongements contemporains. &lt;/p&gt;" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H144" display="https://www.laphilo.fr/pho/bnabille-mini.webp" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H145" display="https://www.laphilo.fr/pho/adufourmantelle-mini.webp" r:id="rId105"/>
   </hyperlinks>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>

--- a/data/frise-philosophes-france.xlsx
+++ b/data/frise-philosophes-france.xlsx
@@ -938,7 +938,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:O154"/>
+  <dimension ref="A1:O157"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="4.59" customWidth="1" style="47" min="1" max="1"/>
@@ -10114,6 +10114,161 @@
         </is>
       </c>
       <c r="O154"/>
+    </row>
+    <row r="155" ht="176.25" customHeight="1" s="49">
+      <c r="A155" s="47">
+        <v>1875</v>
+      </c>
+      <c r="B155" s="47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1965</t>
+        </is>
+      </c>
+      <c r="C155" s="47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1875 – 1965</t>
+        </is>
+      </c>
+      <c r="D155" s="47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Albert SCHWEITZER</t>
+        </is>
+      </c>
+      <c r="E155" s="85" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Albert_Schweitzer" title=" Wikipedia"&gt;Albert SCHWEITZER&lt;/a&gt; est un théologien, philosophe, musicien et médecin alsacien. Né en 1875 à Kaysersberg, alors allemand, fils de pasteur, il étudie à Strasbourg la théologie et la philosophie, avec une thèse sur la philosophie de la religion de Kant. Organiste réputé, il publie un grand livre sur Bach. Dans son &lt;em&gt;Histoire des recherches sur la vie de Jésus&lt;/em&gt; (1906), il montre que le Jésus historique était un prophète qui annonçait la fin imminente du monde, bien loin de l’image qu’en donnait la théologie libérale.&lt;/p&gt; &lt;p&gt;À trente ans, il décide de servir l’humanité souffrante : il étudie la médecine et part en 1913 avec sa femme Hélène à Lambaréné, au Gabon, où il fonde un hôpital au bord de l’Ogooué. En 1915, sur ce fleuve, au milieu d’un troupeau d’hippopotames, lui vient la formule qu’il cherchait : « respect de la vie ». « Je suis vie qui veut vivre, au milieu de vie qui veut vivre. » Le bien consiste à conserver et à favoriser la vie, le mal à la détruire ou à l’entraver. Cette éthique, qui s’étend à tous les êtres vivants, est au cœur de sa &lt;em&gt;Philosophie de la civilisation&lt;/em&gt; (1923).&lt;/p&gt; &lt;p&gt;Citoyen allemand, il est interné en France en 1917 avec sa femme, puis devient français après 1918. Ses tournées de concerts et de conférences en Europe financent l’hôpital, qu’il ne cesse d’agrandir. Il reçoit en 1953 le prix Nobel de la paix et, à la fin de sa vie, s’engage contre les essais nucléaires. On lui a aussi reproché un certain paternalisme envers les Africains. Il meurt à Lambaréné en 1965.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="H155" s="48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/schweitzer-mini.webp</t>
+        </is>
+      </c>
+      <c r="J155" s="48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ethique ; spiritualite</t>
+        </is>
+      </c>
+      <c r="K155" s="48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Humanisme</t>
+        </is>
+      </c>
+      <c r="L155" s="48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">théologien, philosophe, organiste et médecin alsacien, penseur du « respect de la vie », prix Nobel de la paix.</t>
+        </is>
+      </c>
+      <c r="N155" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+      <c r="O155"/>
+    </row>
+    <row r="156" ht="176.25" customHeight="1" s="49">
+      <c r="A156" s="47">
+        <v>1828</v>
+      </c>
+      <c r="B156" s="47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1893</t>
+        </is>
+      </c>
+      <c r="C156" s="47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1828 – 1893</t>
+        </is>
+      </c>
+      <c r="D156" s="47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hippolyte TAINE</t>
+        </is>
+      </c>
+      <c r="E156" s="85" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Hippolyte_Taine" title=" Wikipedia"&gt;Hippolyte TAINE&lt;/a&gt; est un philosophe, historien et critique français. Né à Vouziers, dans les Ardennes, en 1828, il entre premier à l’École normale supérieure en 1848, mais échoue à l’agrégation de philosophie, son jury jugeant ses idées trop audacieuses. Dans &lt;em&gt;Les Philosophes classiques du XIXe siècle en France&lt;/em&gt; (1857), il attaque la philosophie officielle de Victor Cousin. Professeur d’esthétique à l’École des beaux-arts, il entre à l’Académie française en 1878. Il meurt à Paris en 1893.&lt;/p&gt; &lt;p&gt;Il veut appliquer aux œuvres humaines la méthode des sciences de la nature. Dans l’&lt;em&gt;Histoire de la littérature anglaise&lt;/em&gt; (1863), il explique chaque œuvre par trois causes : la « race », les dispositions héréditaires d’un peuple, le « milieu », c’est-à-dire le climat et la société, et le « moment », l’époque. Il écrit : « Le vice et la vertu sont des produits comme le vitriol et le sucre. » Dans &lt;em&gt;De l’intelligence&lt;/em&gt; (1870), il fonde une psychologie scientifique, pour qui la perception est une « hallucination vraie ». Il incarne ainsi le &lt;a href="https://fr.wikipedia.org/wiki/Positivisme" title=" Wikipedia"&gt;positivisme&lt;/a&gt; et le déterminisme de son temps.&lt;/p&gt; &lt;p&gt;Bouleversé par la défaite de 1870 et la Commune, il consacre ses dernières années aux &lt;em&gt;Origines de la France contemporaine&lt;/em&gt;, où il accuse l’esprit abstrait des Jacobins et la centralisation de l’État. Ses idées ont inspiré le naturalisme de Zola, puis des auteurs conservateurs comme Bourget et Barrès. Sa &lt;em&gt;Philosophie de l’art&lt;/em&gt; (1865) applique la même méthode à la peinture et à la sculpture.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="H156" s="48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/taine-mini.webp</t>
+        </is>
+      </c>
+      <c r="J156" s="48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">epistemologie ; esthetique ; politique</t>
+        </is>
+      </c>
+      <c r="K156" s="48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Positivisme ; Déterminisme</t>
+        </is>
+      </c>
+      <c r="L156" s="48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">philosophe et historien français, qui expliquait les œuvres par « la race, le milieu et le moment ».</t>
+        </is>
+      </c>
+      <c r="N156" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+      <c r="O156"/>
+    </row>
+    <row r="157" ht="176.25" customHeight="1" s="49">
+      <c r="A157" s="47">
+        <v>1915</v>
+      </c>
+      <c r="B157" s="47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1980</t>
+        </is>
+      </c>
+      <c r="C157" s="47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1915 – 1980</t>
+        </is>
+      </c>
+      <c r="D157" s="47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Roland BARTHES</t>
+        </is>
+      </c>
+      <c r="E157" s="85" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Roland_Barthes" title=" Wikipedia"&gt;Roland BARTHES&lt;/a&gt; est un critique, sémiologue et écrivain français. Né à Cherbourg en 1915, il perd son père, officier de marine, l’année suivante et grandit à Bayonne puis à Paris avec sa mère, dont il restera très proche. Atteint de tuberculose, il passe de longues années en sanatorium. Il publie &lt;em&gt;Le Degré zéro de l’écriture&lt;/em&gt; en 1953, enseigne à l’École pratique des hautes études, puis entre au Collège de France en 1977. Renversé par une camionnette en sortant d’un déjeuner, il meurt en mars 1980.&lt;/p&gt; &lt;p&gt;Dans &lt;em&gt;Mythologies&lt;/em&gt; (1957), il analyse les objets de la culture de masse, le catch, le steak-frites, la nouvelle Citroën ou les publicités pour les lessives. Il montre que ces « mythes » font passer pour naturel ce qui est historique et social, au service de l’idéologie de la bourgeoisie. Il fonde ainsi une sémiologie, une science des signes inspirée de Saussure, qui étudie la mode, l’image ou la publicité. Il est l’une des grandes figures du &lt;a href="https://fr.wikipedia.org/wiki/Structuralisme" title=" Wikipedia"&gt;structuralisme&lt;/a&gt;.&lt;/p&gt; &lt;p&gt;Contre la critique universitaire, qui explique les œuvres par la vie de l’auteur, il proclame en 1968 la « mort de l’auteur » : un texte n’a pas un sens unique, il vit de ses lectures, et « la naissance du lecteur doit se payer de la mort de l’Auteur ». Il évolue ensuite vers une écriture plus personnelle, avec &lt;em&gt;Le Plaisir du texte&lt;/em&gt; (1973) et &lt;em&gt;Fragments d’un discours amoureux&lt;/em&gt; (1977). Dans &lt;em&gt;La Chambre claire&lt;/em&gt; (1980), il médite sur la photographie et sur la mort de sa mère.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="H157" s="48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/barthes-mini.webp</t>
+        </is>
+      </c>
+      <c r="J157" s="48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">langage ; esthetique</t>
+        </is>
+      </c>
+      <c r="K157" s="48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Structuralisme ; Post-structuralisme</t>
+        </is>
+      </c>
+      <c r="L157" s="48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">critique, sémiologue et écrivain français, auteur des Mythologies et théoricien de la « mort de l’auteur ».</t>
+        </is>
+      </c>
+      <c r="N157" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+      <c r="O157">
+        <v>2</v>
+      </c>
     </row>
     <row r="1048566" ht="12.75" customHeight="1" s="49"/>
     <row r="1048567" ht="12.75" customHeight="1" s="49"/>

--- a/data/frise-philosophes-france.xlsx
+++ b/data/frise-philosophes-france.xlsx
@@ -1789,11 +1789,14 @@
           <t>&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Paul_Janet_(philosophe)"  title=" Wikipedia"&gt;Paul JANET&lt;/a&gt; était un philosophe français, représentant important du spiritualisme éclectique dans la seconde moitié du XIXe siècle. Né à Paris, normalien et agrégé de philosophie, il fut professeur à la Faculté des lettres de Strasbourg puis à la Sorbonne, et membre de l'Académie des sciences morales et politiques. Oncle du célèbre psychologue Pierre Janet, il exerça une &lt;a href="http://metascience.fr/Paul_Janet_notice_historique_par_Picot.pdf" title="Paul Janet  par metascience"&gt;influence considérable &lt;/a&gt;  sur plusieurs générations d'étudiants et d'enseignants de philosophie. &lt;/p&gt; &lt;p&gt; Sa pensée philosophique s'inscrit dans la tradition spiritualiste fondée par Cousin, dont il fut l'un des continuateurs les plus fidèles et les plus rigoureux. Dans ses ouvrages principaux — &lt;em&gt;Histoire de la philosophie morale et politique&lt;/em&gt; (1858), &lt;em&gt;Les Causes finales&lt;/em&gt; (1876) et &lt;em&gt;Les Principes de métaphysique et de psychologie&lt;/em&gt; (1897) — il développe une philosophie de la finalité et de la liberté qui cherche à maintenir la légitimité d'une métaphysique spiritualiste face aux progrès du positivisme et du matérialisme scientifique. &lt;/p&gt; &lt;p&gt; Sa défense des causes finales est particulièrement caractéristique de sa pensée : contre les réductionnismes mécanicistes, il soutient que l'ordre et la finalité observables dans la nature et dans la vie ne peuvent s'expliquer que par un principe spirituel immanent. Son &lt;em&gt;Traité élémentaire de philosophie&lt;/em&gt; (1879), longtemps utilisé dans l'enseignement secondaire, témoigne de l'influence pédagogique considérable qu'il exerça. Philosophe consciencieux et pédagogue de talent, Janet représente une figure typique du spiritualisme universitaire français de la Belle Époque. &lt;/p&gt;</t>
         </is>
       </c>
-      <c r="F16" s="60" t="n"/>
+      <c r="F16" s="60" t="inlineStr">
+        <is>
+          <t xml:space="preserve">dny-CPut8ZY</t>
+        </is>
+      </c>
       <c r="G16" s="66" t="inlineStr">
         <is>
-          <t xml:space="preserve">
-</t>
+          <t xml:space="preserve">"Paul Janet La Philosophie dans les comédies de Molière" par Livres Audio Resumé en Français</t>
         </is>
       </c>
       <c r="H16" s="61" t="inlineStr">
@@ -2270,8 +2273,16 @@
           <t>&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Jules_Lagneau" title=" Wikipedia"&gt;Jules LAGNEAU&lt;/a&gt; était un philosophe français dont la pensée, transmise presque exclusivement par voie orale, exerça une influence profonde et durable sur quelques-uns de ses disciples, au premier rang desquels Alain (Émile Chartier). Né à Metz, normalien et agrégé de philosophie, il enseigna principalement dans des lycées de province et à Paris, où son enseignement au lycée Michelet marqua profondément ses élèves par sa rigueur, sa profondeur et sa dimension spirituelle. &lt;/p&gt; &lt;p&gt;Il  laissa &lt;a href="https://evene.lefigaro.fr/citations/jules-lagneau"  title="citations de lagneau par lefigaro"&gt;peu d'écrits publiés &lt;/a&gt; de son vivant. C'est surtout à travers les &lt;em&gt;Célèbres leçons et fragments&lt;/em&gt;, édités après sa mort par ses élèves, que l'on peut accéder à sa pensée. Sa philosophie s'inscrit dans la tradition spiritualiste française, fortement influencée par Descartes et par Kant, mais orientée vers une méditation personnelle et intérieure. Pour lui, la véritable philosophie est un effort de conscience sur soi-même : penser, c'est se saisir comme liberté et comme volonté au-delà de toute détermination naturelle. &lt;/p&gt; &lt;p&gt; Sa conception de la perception, développée dans ses cours, est particulièrement originale : il soutient que toute perception implique un acte de jugement actif, et non une simple réception passive de données sensorielles. Cette idée d'une activité constitutive de la conscience dans l'acte perceptif préfigure des thèmes centraux de la phénoménologie.Son influence sur Alain fut déterminante : ce dernier diffusa largement ses idées dans ses propres &lt;em&gt;Propos&lt;/em&gt; et lui consacra un livre d'hommage. Il reste ainsi un philosophe de l'ombre dont le rayonnement indirect fut considérable. &lt;/p&gt;</t>
         </is>
       </c>
-      <c r="F24" s="54" t="n"/>
-      <c r="G24" s="56" t="n"/>
+      <c r="F24" s="54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">nh_YQsWECJE</t>
+        </is>
+      </c>
+      <c r="G24" s="56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"Alain et Lagneau à Michelet" par Professeur Oudin</t>
+        </is>
+      </c>
       <c r="H24" s="56" t="inlineStr">
         <is>
           <t>https://www.laphilo.fr/pho/jlagneau-mini.webp</t>
@@ -2871,8 +2882,16 @@
 </t>
         </is>
       </c>
-      <c r="F34" s="69" t="n"/>
-      <c r="G34" s="72" t="n"/>
+      <c r="F34" s="69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1gFnGxScWwM</t>
+        </is>
+      </c>
+      <c r="G34" s="72" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"Frédéric Fruteau de Laclos: Le cheminement de la Pensée selon Emile Meyerson." par Jtgrandtour</t>
+        </is>
+      </c>
       <c r="H34" s="72" t="inlineStr">
         <is>
           <t>https://www.laphilo.fr/pho/emeyerson-mini.webp</t>
@@ -4553,8 +4572,16 @@
           <t>&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Martial_Gueroult"  title=" Wikipedia"&gt;Martial GUEROULT&lt;/a&gt; était un philosophe français, l'un des représentants les plus importants de la méthode d'histoire de la philosophie par analyse interne des textes. Né à Saint-Quentin, normalien et agrégé de philosophie, il fut professeur à la Sorbonne puis au Collège de France, où il occupa la chaire d'histoire et technologie des systèmes philosophiques. Ses travaux sur Descartes, Fichte, Leibniz et Spinoza constituent des monuments de l'érudition philosophique française. &lt;/p&gt; &lt;p&gt;   &lt;a href="https://fr.scribd.com/document/264871906/Gueroult-methode"  title=" Gueroult méthode par scribd"&gt;La méthode de Gueroult, &lt;/a&gt; qu'il développa et défendit tout au long de sa carrière, consiste à lire les grands textes philosophiques de l'intérieur, en suivant rigoureusement la logique propre de chaque système. Pour lui, tout grand philosophe a construit un système cohérent dont chaque élément est solidaire des autres, et la tâche de l'historien de la philosophie est de reconstituer cette architecture interne avec la même rigueur que celle du mathématicien étudiant un théorème. Cette approche s'oppose à la fois à l'histoire externe (contextualiste) et à la lecture éclectique des textes. &lt;/p&gt; &lt;p&gt; Son œuvre maîtresse, &lt;em&gt;Descartes selon l'ordre des raisons&lt;/em&gt; (2 volumes, 1953), est une analyse minutieuse et magistrale de l'enchaînement des arguments dans les &lt;em&gt;Méditations métaphysiques&lt;/em&gt; de Descartes. Ses études sur Spinoza (&lt;em&gt;Spinoza&lt;/em&gt;, 2 volumes publiés de 1968 à 1974) sont également des références incontournables. Dans &lt;em&gt;Dianoématique&lt;/em&gt;, son projet inachevé, il cherchait à établir une théorie générale des systèmes philosophiques. Il a profondément &lt;a href="https://www.persee.fr/doc/barb_0001-4133_1976_num_62_1_60408"  title="Hommage à martial Gueroult par persée"&gt;marqué l'histoire de la philosophie &lt;/a&gt; française et sa méthode continue d'influencer les études cartésiennes et spinozistes. &lt;/p&gt;</t>
         </is>
       </c>
-      <c r="F62" s="54" t="n"/>
-      <c r="G62" s="56" t="n"/>
+      <c r="F62" s="54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bq2z1EX8XzY</t>
+        </is>
+      </c>
+      <c r="G62" s="56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"Jacques Bouveresse - Martial Gueroult et la philosophie de l’histoire de la philosophie" par On The Top of Damavand for ever</t>
+        </is>
+      </c>
       <c r="H62" s="56" t="inlineStr">
         <is>
           <t>https://www.laphilo.fr/pho/gueroult-mini.webp</t>
@@ -5773,8 +5800,16 @@
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Jean_Beaufret"   title=" Wikipedia"&gt;Jean BEAUFRET&lt;/a&gt; était un philosophe français, connu principalement comme le principal introducteur et interprète de la philosophie de Martin Heidegger en France. Normalien et agrégé de philosophie, il enseigna dans plusieurs lycées parisiens et consacra l'essentiel de sa réflexion à la pensée heideggerienne, dont il fut à la fois le traducteur, le commentateur et le défenseur. La célèbre &lt;em&gt;Lettre sur l'humanisme&lt;/em&gt; de Heidegger (1946) fut écrite en réponse à des questions que Beaufret lui avait posées, témoignant de l'importance de ce dialogue franco-allemand. &lt;/p&gt; &lt;p&gt; Sa &lt;a href="https://www.persee.fr/doc/phlou_0035-3841_1983_num_81_50_6250"  title="in memory jean Beaufret par persée"&gt; contribution principale &lt;/a&gt; consiste dans l'introduction et la diffusion de la pensée de Heidegger dans le contexte philosophique français d'après-guerre, dominé par l'existentialisme de Sartre. Il soulignait la différence fondamentale entre la question heideggerienne de l'être et l'existentialisme sartrien, défendant la singularité de la « question de l'être » comme horizon ultime de toute philosophie. Ses cours et séminaires attirèrent de&lt;a href="https://www.youtube.com/watch?v=R9YGK09L2_Q"  title="jeanbeaufret par Michel Onfray"&gt; nombreux philosophes, &lt;/a&gt; parmi lesquels François Fédier, qui poursuivit son travail de traduction et d'interprétation. &lt;/p&gt; &lt;p&gt; Parmi ses publications, le &lt;em&gt;Dialogue avec Heidegger&lt;/em&gt; (4 volumes, 1973-1985) rassemble ses principaux essais et analyses de la pensée heideggerienne, couvrant la philosophie grecque, la modernité et la pensée contemporaine. Ces textes constituent un commentaire exigeant et pénétrant de l'œuvre de Heidegger, même si son rapport exclusif à cette unique source a parfois été critiqué. Son rôle dans la réception française de Heidegger, pour le meilleur et pour le pire — compte tenu de la controverse née de ses positions négationnistes à la fin de sa vie — reste incontournable. &lt;/p&gt; &lt;audio controls title="La vie absolument par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/15537-21.05.2018-ITEMA_21686393-1.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt; </t>
         </is>
       </c>
-      <c r="F82" s="57" t="n"/>
-      <c r="G82" s="59" t="n"/>
+      <c r="F82" s="57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TI7yi_X-wlE</t>
+        </is>
+      </c>
+      <c r="G82" s="59" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"L'héritage d'Héraclite • Kostas Axelos, Jean Beaufret, François Châtelet" par Andrea Cirla</t>
+        </is>
+      </c>
       <c r="H82" s="59" t="inlineStr">
         <is>
           <t>https://www.laphilo.fr/pho/jbeaufret-mini.webp</t>
@@ -7544,8 +7579,16 @@
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Fran%C3%A7ois_Wahl"  title=" Wikipedia"&gt;François WAHL&lt;/a&gt; était un philosophe et éditeur français, figure centrale de la vie intellectuelle française de la fin des années 1950 au début des années 1990, surtout connu pour avoir promu le structuralisme et la psychanalyse aux Éditions du Seuil. Il a régné pendant trente ans sur le domaine des sciences humaines et la littérature italienne au Seuil, publiant Jacques Lacan, Françoise Dolto, Paul Ricœur, Roland Barthes, Philippe Sollers, Alain Badiou, Jean-Claude Milner, ainsi que des auteurs italiens comme Carlo Emilio Gadda et Italo Calvino. Il est décrit comme un « structuraliste dans l’âme », construisant son activité éditoriale comme une structure où chaque choix (acceptations, refus, retraductions) faisait système, appliquant la doctrine structuraliste à son métier d’éditeur. &lt;/p&gt; &lt;p&gt; Il est l’auteur de trois ouvrages majeurs :  &lt;a href="https://philosophie.ac-normandie.fr/spip.php?article148" title="qu’est ce que la philosophie par françois Wahl "&gt;Qu’est-ce que le structuralisme ? &lt;/a&gt;, Philosophie (1973), Introduction au discours du tableau (1996) et Le Perçu (2007). Dans Introduction au discours du tableau, il étudie les œuvres de Poussin, Memling ou Bellini pour montrer que le « visible » apparaît sous deux espèces : le paysage et le tableau, articulant ainsi esthétique et théorie du signe. Le Perçu propose une exploration critique des phénoménologies du XXᵉ siècle, en mobilisant les concepts de discours, sujet, désir et énoncé pour formaliser une analyse du « fait esthétique ». &lt;/p&gt; &lt;p&gt; La ligne directrice de sa pensée peut se résumer à un repérage du concept de sujet dans la philosophie contemporaine et son introduction dans le champ de l’esthétique. Il a écrit de nombreux articles discutant les œuvres d’auteurs comme Badiou, Bataille, Barthes, Foucault ou Lacan, et son dernier grand livre, La dissidence du sujet, rassemble ces réflexions sur le sujet, le désir et le discours dans la philosophie et l’art. &lt;/p&gt; &lt;audio controls title="les fluides d’Aristote /hommage à f Wahl par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/12003-17.09.2014-ITEMA_20670365-2014C18006S0260-21.mp3" type="audio/mpeg" align="center"&gt;&lt;/audio&gt;  </t>
         </is>
       </c>
-      <c r="F111" s="57" t="n"/>
-      <c r="G111" s="59" t="n"/>
+      <c r="F111" s="57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">xDWD15et5Hw</t>
+        </is>
+      </c>
+      <c r="G111" s="59" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"Dante et la rhétorique — Roland Barthes &amp; François Wahl" par Andrea Cirla</t>
+        </is>
+      </c>
       <c r="H111" s="65" t="inlineStr">
         <is>
           <t>https://www.laphilo.fr/pho/fwahl-mini.webp</t>
@@ -9671,6 +9714,16 @@
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Charles_Maurras" title=" Wikipedia"&gt;Charles MAURRAS&lt;/a&gt; est un écrivain, journaliste et théoricien politique français, le maître à penser de l’&lt;a href="https://fr.wikipedia.org/wiki/Action_fran%C3%A7aise" title=" Wikipedia"&gt;Action française&lt;/a&gt;. Né en 1868 à Martigues, en Provence, il devient sourd vers quatorze ans, perd la foi, et monte à Paris, où il se fait connaître comme critique littéraire et poète, défenseur d’un classicisme inspiré de la Grèce contre le romantisme, qu’il juge source de désordre. L’affaire Dreyfus le jette dans la politique : en 1898, il justifie le faux du colonel Henry au nom de l’intérêt de l’armée et de l’État.&lt;/p&gt; &lt;p&gt;Avec son &lt;em&gt;Enquête sur la monarchie&lt;/em&gt; (1900), il convertit l’Action française à la royauté. Sa doctrine, le « nationalisme intégral », place la nation au-dessus de tout : seule une monarchie héréditaire, antiparlementaire et décentralisée pourrait garantir l’ordre et la durée que la République, gouvernement des partis et de l’opinion, détruirait. Agnostique, il défend pourtant l’Église catholique comme une force d’ordre. Il appelle sa méthode l’« empirisme organisateur » : tirer de l’histoire les lois du bon gouvernement. Il dénonce les « quatre États confédérés » qui, selon lui, rongent la France : les juifs, les protestants, les francs-maçons et les « métèques ». Cet antisémitisme d’État est au cœur de sa pensée.&lt;/p&gt; &lt;p&gt;Son quotidien, &lt;em&gt;L’Action française&lt;/em&gt;, exerce une influence considérable sur la droite et sur une partie de la jeunesse intellectuelle, malgré la condamnation du mouvement par le pape Pie XI en 1926. Maurras entre à l’Académie française en 1938. Hostile à l’Allemagne, il soutient pourtant en 1940 le maréchal Pétain, dont l’arrivée au pouvoir est pour lui une « divine surprise ». Condamné en 1945 à la réclusion à perpétuité et à la dégradation nationale pour intelligence avec l’ennemi, il s’écrie : « C’est la revanche de Dreyfus ! » Gracié pour raison de santé, il meurt en 1952. Sa pensée a durablement marqué l’extrême droite française.&lt;/p&gt;</t>
         </is>
       </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WZbjzmY8YVY</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"Charles Maurras et ses héritiers" par lostinthiswhirlpool</t>
+        </is>
+      </c>
       <c r="H146" s="48" t="inlineStr">
         <is>
           <t xml:space="preserve">https://www.laphilo.fr/pho/maurras-mini.webp</t>
@@ -9722,6 +9775,16 @@
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Marcellin_Berthelot" title=" Wikipedia"&gt;Marcellin BERTHELOT&lt;/a&gt; est un chimiste, historien des sciences et homme politique français, l’une des figures les plus représentatives du &lt;a href="https://fr.wikipedia.org/wiki/Scientisme" title=" Wikipedia"&gt;scientisme&lt;/a&gt;. Né à Paris en 1827, fils d’un médecin, il devient l’un des fondateurs de la chimie organique de synthèse : il montre qu’on peut fabriquer en laboratoire, à partir des éléments, des corps jusque-là produits seulement par les êtres vivants, comme l’acétylène, le méthane ou l’alcool. Il en tire une leçon philosophique : il n’existe pas de « force vitale » mystérieuse, la vie obéit aux mêmes lois que la matière.&lt;/p&gt; &lt;p&gt;Pour Berthelot, la science expérimentale est la seule voie vers la vérité, et elle doit aussi fonder la morale et la politique. « Le monde est aujourd’hui sans mystère », écrit-il en 1885 : ce que la science ne sait pas encore, elle le saura demain. Ami de &lt;a href="https://fr.wikipedia.org/wiki/Ernest_Renan" title=" Wikipedia"&gt;Ernest Renan&lt;/a&gt;, avec qui il partage la foi dans l’avenir de la science, il expose ses idées dans &lt;em&gt;Science et morale&lt;/em&gt; (1897). En 1895, quand le critique Ferdinand Brunetière proclame la « faillite de la science », qui n’aurait pas tenu ses promesses morales, Berthelot devient le porte-parole de la réplique républicaine et laïque.&lt;/p&gt; &lt;p&gt;Sénateur inamovible, il est ministre de l’Instruction publique (1886-1887) puis des Affaires étrangères (1895-1896), et défend une école laïque fondée sur les sciences. Professeur au Collège de France, secrétaire perpétuel de l’Académie des sciences, il s’oppose aussi à la théorie atomique, qu’il juge trop hypothétique. Il meurt en 1907 le même jour que sa femme, et tous deux sont inhumés au Panthéon.&lt;/p&gt;</t>
         </is>
       </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t xml:space="preserve">_OI9mUuWjOg</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"Marcellin Berthelot et le dévoilement de l'alchimie" par BAGLIS TV</t>
+        </is>
+      </c>
       <c r="H147" s="48" t="inlineStr">
         <is>
           <t xml:space="preserve">https://www.laphilo.fr/pho/berthelot-mini.webp</t>
@@ -9773,6 +9836,16 @@
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Pierre_Duhem" title=" Wikipedia"&gt;Pierre DUHEM&lt;/a&gt; est un physicien, philosophe et historien des sciences français. Né à Paris en 1861, brillant élève de l’École normale supérieure, il consacre ses travaux de physique à la thermodynamique. Une thèse où il critique les idées du chimiste Marcellin Berthelot est refusée ; Berthelot, très puissant, l’empêche ensuite d’obtenir un poste à Paris, et Duhem, catholique convaincu, fait sa carrière en province, à Lille, à Rennes, puis à Bordeaux.&lt;/p&gt; &lt;p&gt;Dans &lt;em&gt;La Théorie physique, son objet, sa structure&lt;/em&gt; (1906), il soutient qu’une théorie physique n’explique pas la réalité cachée des choses, ce qui relève de la métaphysique : elle est un système de propositions mathématiques qui représente et classe le plus simplement possible les lois expérimentales. Il faut, comme disaient les astronomes grecs, « sauver les phénomènes ». Surtout, une expérience ne peut jamais réfuter une hypothèse isolée : elle met en jeu tout un ensemble de théories et d’instruments, et si la prédiction échoue, on ne sait pas laquelle des hypothèses est fausse. Il n’y a donc pas d’« expérience cruciale ». Cette idée, reprise par Quine, est connue comme la &lt;a href="https://fr.wikipedia.org/wiki/Th%C3%A8se_de_Duhem-Quine" title=" Wikipedia"&gt;thèse de Duhem-Quine&lt;/a&gt;.&lt;/p&gt; &lt;p&gt;Duhem est aussi un grand historien des sciences. Dans les dix volumes du &lt;em&gt;Système du monde&lt;/em&gt;, il redécouvre la physique du Moyen Âge, celle de Jean Buridan et de Nicole Oresme, et montre que la science moderne ne naît pas d’une rupture brutale avec les siècles « obscurs », mais les prolonge. Il meurt en 1916. Son instrumentalisme et son holisme ont profondément marqué la philosophie des sciences du XXe siècle.&lt;/p&gt;</t>
         </is>
       </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Kw5b_7VYXZQ</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"Pierre Duhem: La théorie physique." par Jtgrandtour</t>
+        </is>
+      </c>
       <c r="H148" s="48" t="inlineStr">
         <is>
           <t xml:space="preserve">https://www.laphilo.fr/pho/duhem-mini.webp</t>
@@ -9824,6 +9897,16 @@
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Henri_Poincar%C3%A9" title=" Wikipedia"&gt;Henri POINCARÉ&lt;/a&gt; est un mathématicien, physicien et philosophe des sciences français, l’un des derniers savants universels. Né à Nancy en 1854, polytechnicien et ingénieur des mines, il enseigne à la Sorbonne à partir de 1881. Il renouvelle presque toutes les branches des mathématiques : il fonde la topologie, découvre en étudiant le mouvement de trois corps célestes les comportements imprévisibles qu’on appellera « chaos », et pose en 1905, en même temps qu’Einstein, les bases mathématiques de la relativité restreinte.&lt;/p&gt; &lt;p&gt;Dans &lt;em&gt;La Science et l’Hypothèse&lt;/em&gt; (1902), il défend le &lt;a href="https://fr.wikipedia.org/wiki/Conventionnalisme" title=" Wikipedia"&gt;conventionnalisme&lt;/a&gt; : certains principes de la science ne sont ni des vérités a priori ni des faits d’expérience, mais des conventions. Ainsi, aucune expérience ne peut dire si l’espace est euclidien ou non : nous choisissons la géométrie d’Euclide parce qu’elle est la plus commode. Ces conventions ne sont pas arbitraires, car l’expérience nous guide, mais elles ne peuvent être ni vraies ni fausses. La science ne connaît pas les choses elles-mêmes, mais les rapports entre les choses.&lt;/p&gt; &lt;p&gt;Dans &lt;em&gt;La Valeur de la science&lt;/em&gt; (1905) et &lt;em&gt;Science et méthode&lt;/em&gt; (1908), il s’oppose aussi aux logiciens, comme Russell, qui veulent réduire les mathématiques à la logique : pour lui, le raisonnement mathématique repose sur une intuition. Il décrit le rôle de l’inconscient dans la découverte, à partir de ses propres illuminations soudaines, comme celle qui lui vint en montant dans un omnibus. Élu à l’Académie française en 1908, il meurt à Paris en 1912.&lt;/p&gt;</t>
         </is>
       </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t xml:space="preserve">xn2kY8PojRA</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"Henri Poincaré, l'harmonie et le Chaos - Documentaire de Philippe Worms (2012)" par Culture Tube</t>
+        </is>
+      </c>
       <c r="H149" s="48" t="inlineStr">
         <is>
           <t xml:space="preserve">https://www.laphilo.fr/pho/poincare-mini.webp</t>
@@ -10030,6 +10113,16 @@
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Andr%C3%A9_Gorz" title=" Wikipedia"&gt;André GORZ&lt;/a&gt; est un philosophe et journaliste français d’origine autrichienne, l’un des fondateurs de l’écologie politique. Né Gerhart Hirsch à Vienne en 1923, d’un père juif et d’une mère catholique, il est envoyé en Suisse en 1939 pour échapper à la guerre et y devient ingénieur chimiste. En 1946, il rencontre &lt;a href="https://fr.wikipedia.org/wiki/Jean-Paul_Sartre" title=" Wikipedia"&gt;Jean-Paul Sartre&lt;/a&gt;, qui le marque profondément. Installé à Paris en 1949, il écrit sous le nom de Michel Bosquet pour &lt;em&gt;L’Express&lt;/em&gt;, puis participe en 1964 à la fondation du &lt;em&gt;Nouvel Observateur&lt;/em&gt;.&lt;/p&gt; &lt;p&gt;Dans &lt;em&gt;Le Traître&lt;/em&gt; (1958), préfacé par Sartre, il analyse sa propre vie en existentialiste. Penseur du marxisme critique, il s’intéresse ensuite au travail : dans &lt;em&gt;Adieux au prolétariat&lt;/em&gt; (1980), il affirme que la classe ouvrière n’est plus le sujet de l’émancipation, et que la libération passe par la réduction du temps de travail. L’automatisation permettrait de travailler beaucoup moins, et de développer les activités libres, choisies pour elles-mêmes, plutôt que de produire et consommer toujours plus.&lt;/p&gt; &lt;p&gt;Dès &lt;em&gt;Écologie et politique&lt;/em&gt; (1975), il relie la crise écologique au capitalisme : la croissance infinie détruit la nature et les liens humains. L’écologie doit être une politique de l’autonomie, qui permette de « produire moins, vivre mieux ». Il défendra plus tard un revenu d’existence versé à tous, indépendamment de l’emploi. Dans &lt;em&gt;Lettre à D.&lt;/em&gt; (2006), il écrit un émouvant livre d’amour à sa femme Dorine, gravement malade. Ils se donnent la mort ensemble en 2007, dans leur maison de Vosnon, dans l’Aube.&lt;/p&gt;</t>
         </is>
       </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t xml:space="preserve">wynLELIWjiY</t>
+        </is>
+      </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"André Gorz, penseur de l'écosocialisme" par France Culture</t>
+        </is>
+      </c>
       <c r="H153" s="48" t="inlineStr">
         <is>
           <t xml:space="preserve">https://www.laphilo.fr/pho/gorz-mini.webp</t>
@@ -10088,6 +10181,16 @@
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Alain_Roger" title=" Wikipedia"&gt;Alain ROGER&lt;/a&gt; est un philosophe et écrivain français. Né à Mirecourt, dans les Vosges, en 1936, ancien élève de l’École normale supérieure, agrégé de philosophie et élève de &lt;a href="https://fr.wikipedia.org/wiki/Gilles_Deleuze" title=" Wikipedia"&gt;Gilles Deleuze&lt;/a&gt;, il enseigne l’esthétique à l’université de Clermont-Ferrand. Romancier, il publie notamment &lt;em&gt;La Travestie&lt;/em&gt; (1987), adaptée au cinéma par Yves Boisset. Mais il est surtout connu comme le grand théoricien français du &lt;a href="https://fr.wikipedia.org/wiki/Paysage" title=" Wikipedia"&gt;paysage&lt;/a&gt;, auquel il consacre l’essentiel de son œuvre de philosophe.&lt;/p&gt; &lt;p&gt;Dans &lt;em&gt;Nus et paysages&lt;/em&gt; (1978) puis dans le &lt;em&gt;Court traité du paysage&lt;/em&gt; (1997), il soutient que la beauté de la nature n’est pas naturelle : nous voyons le monde à travers les œuvres d’art. Il reprend à Montaigne le mot « artialisation » pour désigner cette transformation de la nature par l’art. Elle peut être directe, « in situ », quand on façonne un jardin ou un corps, ou indirecte, « in visu », quand la peinture, la poésie ou la photographie éduquent notre regard. Le paysage naît ainsi au XVe siècle dans la peinture flamande, par la « fenêtre » ouverte au fond des tableaux.&lt;/p&gt; &lt;p&gt;Il montre que des lieux longtemps jugés affreux, comme la montagne ou le bord de mer, ne sont devenus beaux qu’au XVIIIe siècle, grâce aux écrivains et aux peintres. Ses travaux inspirent paysagistes et aménageurs, et il enseigne à l’école d’architecture de Paris-La Villette. Il est aussi l’auteur d’un &lt;em&gt;Bréviaire de la bêtise&lt;/em&gt; (2008), recueil d’aphorismes sur la sottise et ses formes les plus savantes. Il meurt à Belley, dans l’Ain, le 7 octobre 2025.&lt;/p&gt;</t>
         </is>
       </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PZI524sHiZ8</t>
+        </is>
+      </c>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"Alain ROGER : court traité du paysage" par INA Culture</t>
+        </is>
+      </c>
       <c r="H154" s="48" t="inlineStr">
         <is>
           <t xml:space="preserve">https://www.laphilo.fr/pho/alainroger-mini.webp</t>
@@ -10139,6 +10242,16 @@
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Albert_Schweitzer" title=" Wikipedia"&gt;Albert SCHWEITZER&lt;/a&gt; est un théologien, philosophe, musicien et médecin alsacien. Né en 1875 à Kaysersberg, alors allemand, fils de pasteur, il étudie à Strasbourg la théologie et la philosophie, avec une thèse sur la philosophie de la religion de Kant. Organiste réputé, il publie un grand livre sur Bach. Dans son &lt;em&gt;Histoire des recherches sur la vie de Jésus&lt;/em&gt; (1906), il montre que le Jésus historique était un prophète qui annonçait la fin imminente du monde, bien loin de l’image qu’en donnait la théologie libérale.&lt;/p&gt; &lt;p&gt;À trente ans, il décide de servir l’humanité souffrante : il étudie la médecine et part en 1913 avec sa femme Hélène à Lambaréné, au Gabon, où il fonde un hôpital au bord de l’Ogooué. En 1915, sur ce fleuve, au milieu d’un troupeau d’hippopotames, lui vient la formule qu’il cherchait : « respect de la vie ». « Je suis vie qui veut vivre, au milieu de vie qui veut vivre. » Le bien consiste à conserver et à favoriser la vie, le mal à la détruire ou à l’entraver. Cette éthique, qui s’étend à tous les êtres vivants, est au cœur de sa &lt;em&gt;Philosophie de la civilisation&lt;/em&gt; (1923).&lt;/p&gt; &lt;p&gt;Citoyen allemand, il est interné en France en 1917 avec sa femme, puis devient français après 1918. Ses tournées de concerts et de conférences en Europe financent l’hôpital, qu’il ne cesse d’agrandir. Il reçoit en 1953 le prix Nobel de la paix et, à la fin de sa vie, s’engage contre les essais nucléaires. On lui a aussi reproché un certain paternalisme envers les Africains. Il meurt à Lambaréné en 1965.&lt;/p&gt;</t>
         </is>
       </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cgPEOVISprc</t>
+        </is>
+      </c>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"La chronique de Pierre Nuss: le légendaire Albert Schweitzer" par BFM Alsace</t>
+        </is>
+      </c>
       <c r="H155" s="48" t="inlineStr">
         <is>
           <t xml:space="preserve">https://www.laphilo.fr/pho/schweitzer-mini.webp</t>
@@ -10190,6 +10303,16 @@
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Hippolyte_Taine" title=" Wikipedia"&gt;Hippolyte TAINE&lt;/a&gt; est un philosophe, historien et critique français. Né à Vouziers, dans les Ardennes, en 1828, il entre premier à l’École normale supérieure en 1848, mais échoue à l’agrégation de philosophie, son jury jugeant ses idées trop audacieuses. Dans &lt;em&gt;Les Philosophes classiques du XIXe siècle en France&lt;/em&gt; (1857), il attaque la philosophie officielle de Victor Cousin. Professeur d’esthétique à l’École des beaux-arts, il entre à l’Académie française en 1878. Il meurt à Paris en 1893.&lt;/p&gt; &lt;p&gt;Il veut appliquer aux œuvres humaines la méthode des sciences de la nature. Dans l’&lt;em&gt;Histoire de la littérature anglaise&lt;/em&gt; (1863), il explique chaque œuvre par trois causes : la « race », les dispositions héréditaires d’un peuple, le « milieu », c’est-à-dire le climat et la société, et le « moment », l’époque. Il écrit : « Le vice et la vertu sont des produits comme le vitriol et le sucre. » Dans &lt;em&gt;De l’intelligence&lt;/em&gt; (1870), il fonde une psychologie scientifique, pour qui la perception est une « hallucination vraie ». Il incarne ainsi le &lt;a href="https://fr.wikipedia.org/wiki/Positivisme" title=" Wikipedia"&gt;positivisme&lt;/a&gt; et le déterminisme de son temps.&lt;/p&gt; &lt;p&gt;Bouleversé par la défaite de 1870 et la Commune, il consacre ses dernières années aux &lt;em&gt;Origines de la France contemporaine&lt;/em&gt;, où il accuse l’esprit abstrait des Jacobins et la centralisation de l’État. Ses idées ont inspiré le naturalisme de Zola, puis des auteurs conservateurs comme Bourget et Barrès. Sa &lt;em&gt;Philosophie de l’art&lt;/em&gt; (1865) applique la même méthode à la peinture et à la sculpture.&lt;/p&gt;</t>
         </is>
       </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t xml:space="preserve">rqhNuXQFR_c</t>
+        </is>
+      </c>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"Hippolyte Taine: le penseur qui a réinventé l’histoire par la méthode" par Mémoires de la France Profonde</t>
+        </is>
+      </c>
       <c r="H156" s="48" t="inlineStr">
         <is>
           <t xml:space="preserve">https://www.laphilo.fr/pho/taine-mini.webp</t>
@@ -10239,6 +10362,16 @@
       <c r="E157" s="85" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Roland_Barthes" title=" Wikipedia"&gt;Roland BARTHES&lt;/a&gt; est un critique, sémiologue et écrivain français. Né à Cherbourg en 1915, il perd son père, officier de marine, l’année suivante et grandit à Bayonne puis à Paris avec sa mère, dont il restera très proche. Atteint de tuberculose, il passe de longues années en sanatorium. Il publie &lt;em&gt;Le Degré zéro de l’écriture&lt;/em&gt; en 1953, enseigne à l’École pratique des hautes études, puis entre au Collège de France en 1977. Renversé par une camionnette en sortant d’un déjeuner, il meurt en mars 1980.&lt;/p&gt; &lt;p&gt;Dans &lt;em&gt;Mythologies&lt;/em&gt; (1957), il analyse les objets de la culture de masse, le catch, le steak-frites, la nouvelle Citroën ou les publicités pour les lessives. Il montre que ces « mythes » font passer pour naturel ce qui est historique et social, au service de l’idéologie de la bourgeoisie. Il fonde ainsi une sémiologie, une science des signes inspirée de Saussure, qui étudie la mode, l’image ou la publicité. Il est l’une des grandes figures du &lt;a href="https://fr.wikipedia.org/wiki/Structuralisme" title=" Wikipedia"&gt;structuralisme&lt;/a&gt;.&lt;/p&gt; &lt;p&gt;Contre la critique universitaire, qui explique les œuvres par la vie de l’auteur, il proclame en 1968 la « mort de l’auteur » : un texte n’a pas un sens unique, il vit de ses lectures, et « la naissance du lecteur doit se payer de la mort de l’Auteur ». Il évolue ensuite vers une écriture plus personnelle, avec &lt;em&gt;Le Plaisir du texte&lt;/em&gt; (1973) et &lt;em&gt;Fragments d’un discours amoureux&lt;/em&gt; (1977). Dans &lt;em&gt;La Chambre claire&lt;/em&gt; (1980), il médite sur la photographie et sur la mort de sa mère.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t xml:space="preserve">yZX_D3AXHmw</t>
+        </is>
+      </c>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"Roland Barthes - Leçon inaugurale au Collège de France : La chaire de sémiologie littéraire" par Artesquieu</t>
         </is>
       </c>
       <c r="H157" s="48" t="inlineStr">
